--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83CA0FD-C8F7-42F4-86BA-21E9F0BC2266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B781FE6F-F0E1-4063-833E-25D7F34337AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="15525" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1035" yWindow="120" windowWidth="14160" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6214,7 +6214,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6236,7 +6236,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
@@ -6740,7 +6739,7 @@
       <c r="H7" t="s">
         <v>74</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7">
         <v>3</v>
       </c>
     </row>
@@ -6766,7 +6765,7 @@
       <c r="H8" t="s">
         <v>74</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8">
         <v>3</v>
       </c>
     </row>
@@ -6789,7 +6788,7 @@
       <c r="H9" t="s">
         <v>74</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9">
         <v>3</v>
       </c>
     </row>
@@ -7259,7 +7258,7 @@
       <c r="H28" t="s">
         <v>74</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28">
         <v>1</v>
       </c>
     </row>
@@ -7282,7 +7281,7 @@
       <c r="H29" t="s">
         <v>74</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29">
         <v>1</v>
       </c>
     </row>
@@ -7308,7 +7307,7 @@
       <c r="H30" t="s">
         <v>74</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30">
         <v>1</v>
       </c>
     </row>
@@ -7759,7 +7758,7 @@
         <v>139</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="49" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7811,7 +7810,7 @@
         <v>139</v>
       </c>
       <c r="I50">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="51" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7914,7 +7913,7 @@
       <c r="H54" t="s">
         <v>139</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54">
         <v>3</v>
       </c>
     </row>
@@ -7940,7 +7939,7 @@
       <c r="H55" t="s">
         <v>139</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55">
         <v>3</v>
       </c>
     </row>
@@ -7966,7 +7965,7 @@
       <c r="H56" t="s">
         <v>139</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56">
         <v>3</v>
       </c>
     </row>
@@ -7992,8 +7991,8 @@
       <c r="H57" t="s">
         <v>139</v>
       </c>
-      <c r="I57" s="9">
-        <v>2</v>
+      <c r="I57">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8018,7 +8017,7 @@
       <c r="H58" t="s">
         <v>139</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58">
         <v>3</v>
       </c>
     </row>
@@ -8128,8 +8127,8 @@
       <c r="H62" t="s">
         <v>139</v>
       </c>
-      <c r="I62">
-        <v>3</v>
+      <c r="I62" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8446,8 +8445,8 @@
       <c r="H74" t="s">
         <v>139</v>
       </c>
-      <c r="I74">
-        <v>2</v>
+      <c r="I74" s="10">
+        <v>1</v>
       </c>
     </row>
     <row r="75" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8554,7 +8553,7 @@
         <v>139</v>
       </c>
       <c r="I78">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="79" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8917,7 +8916,7 @@
       <c r="H92" t="s">
         <v>139</v>
       </c>
-      <c r="I92" s="9">
+      <c r="I92">
         <v>3</v>
       </c>
     </row>
@@ -9093,7 +9092,7 @@
       <c r="H99" t="s">
         <v>139</v>
       </c>
-      <c r="I99" s="9">
+      <c r="I99">
         <v>1</v>
       </c>
     </row>
@@ -9119,7 +9118,7 @@
       <c r="H100" t="s">
         <v>139</v>
       </c>
-      <c r="I100" s="9">
+      <c r="I100">
         <v>1</v>
       </c>
     </row>
@@ -9145,7 +9144,7 @@
       <c r="H101" t="s">
         <v>139</v>
       </c>
-      <c r="I101" s="9">
+      <c r="I101">
         <v>1</v>
       </c>
     </row>
@@ -9171,7 +9170,7 @@
       <c r="H102" t="s">
         <v>139</v>
       </c>
-      <c r="I102" s="9">
+      <c r="I102">
         <v>1</v>
       </c>
     </row>
@@ -9197,7 +9196,7 @@
       <c r="H103" t="s">
         <v>139</v>
       </c>
-      <c r="I103" s="9">
+      <c r="I103">
         <v>1</v>
       </c>
     </row>
@@ -9223,7 +9222,7 @@
       <c r="H104" t="s">
         <v>139</v>
       </c>
-      <c r="I104" s="9">
+      <c r="I104">
         <v>1</v>
       </c>
     </row>
@@ -9694,7 +9693,7 @@
       <c r="H122" t="s">
         <v>245</v>
       </c>
-      <c r="I122">
+      <c r="I122" s="10">
         <v>1</v>
       </c>
     </row>
@@ -9720,7 +9719,7 @@
       <c r="H123" t="s">
         <v>245</v>
       </c>
-      <c r="I123" s="9">
+      <c r="I123">
         <v>2</v>
       </c>
     </row>
@@ -9746,7 +9745,7 @@
       <c r="H124" t="s">
         <v>245</v>
       </c>
-      <c r="I124" s="9">
+      <c r="I124" s="10">
         <v>1</v>
       </c>
     </row>
@@ -9801,7 +9800,7 @@
       <c r="H126" t="s">
         <v>245</v>
       </c>
-      <c r="I126">
+      <c r="I126" s="10">
         <v>1</v>
       </c>
     </row>
@@ -10437,7 +10436,7 @@
       <c r="H150" t="s">
         <v>21</v>
       </c>
-      <c r="I150" s="9">
+      <c r="I150">
         <v>3</v>
       </c>
     </row>
@@ -10463,7 +10462,7 @@
       <c r="H151" t="s">
         <v>21</v>
       </c>
-      <c r="I151" s="9">
+      <c r="I151">
         <v>3</v>
       </c>
     </row>
@@ -10489,7 +10488,7 @@
       <c r="H152" t="s">
         <v>21</v>
       </c>
-      <c r="I152" s="9">
+      <c r="I152">
         <v>2</v>
       </c>
     </row>
@@ -12914,7 +12913,7 @@
       <c r="H244" t="s">
         <v>59</v>
       </c>
-      <c r="I244" s="9">
+      <c r="I244">
         <v>3</v>
       </c>
     </row>
@@ -12940,7 +12939,7 @@
       <c r="H245" t="s">
         <v>59</v>
       </c>
-      <c r="I245" s="9">
+      <c r="I245">
         <v>2</v>
       </c>
     </row>
@@ -12966,7 +12965,7 @@
       <c r="H246" t="s">
         <v>59</v>
       </c>
-      <c r="I246" s="9">
+      <c r="I246">
         <v>3</v>
       </c>
     </row>
@@ -12992,7 +12991,7 @@
       <c r="H247" t="s">
         <v>59</v>
       </c>
-      <c r="I247" s="9">
+      <c r="I247">
         <v>2</v>
       </c>
     </row>
@@ -13018,7 +13017,7 @@
       <c r="H248" t="s">
         <v>59</v>
       </c>
-      <c r="I248" s="9">
+      <c r="I248">
         <v>3</v>
       </c>
     </row>
@@ -13044,7 +13043,7 @@
       <c r="H249" t="s">
         <v>59</v>
       </c>
-      <c r="I249" s="9">
+      <c r="I249">
         <v>3</v>
       </c>
     </row>
@@ -14434,7 +14433,7 @@
       <c r="H302" t="s">
         <v>59</v>
       </c>
-      <c r="I302" s="9">
+      <c r="I302">
         <v>3</v>
       </c>
     </row>
@@ -14460,7 +14459,7 @@
       <c r="H303" t="s">
         <v>59</v>
       </c>
-      <c r="I303" s="9">
+      <c r="I303">
         <v>3</v>
       </c>
     </row>
@@ -14486,7 +14485,7 @@
       <c r="H304" t="s">
         <v>59</v>
       </c>
-      <c r="I304" s="9">
+      <c r="I304">
         <v>2</v>
       </c>
     </row>
@@ -14512,7 +14511,7 @@
       <c r="H305" t="s">
         <v>59</v>
       </c>
-      <c r="I305" s="9">
+      <c r="I305">
         <v>2</v>
       </c>
     </row>
@@ -14538,7 +14537,7 @@
       <c r="H306" t="s">
         <v>59</v>
       </c>
-      <c r="I306" s="9">
+      <c r="I306">
         <v>2</v>
       </c>
     </row>
@@ -16000,7 +15999,7 @@
       <c r="H362" t="s">
         <v>31</v>
       </c>
-      <c r="I362" s="9">
+      <c r="I362">
         <v>3</v>
       </c>
     </row>
@@ -16026,7 +16025,7 @@
       <c r="H363" t="s">
         <v>31</v>
       </c>
-      <c r="I363" s="9">
+      <c r="I363">
         <v>3</v>
       </c>
     </row>
@@ -17742,7 +17741,7 @@
       <c r="H429" t="s">
         <v>31</v>
       </c>
-      <c r="I429" s="9">
+      <c r="I429">
         <v>2</v>
       </c>
     </row>
@@ -17768,7 +17767,7 @@
       <c r="H430" t="s">
         <v>31</v>
       </c>
-      <c r="I430" s="9">
+      <c r="I430">
         <v>1</v>
       </c>
     </row>
@@ -18993,7 +18992,7 @@
       <c r="H477" t="s">
         <v>308</v>
       </c>
-      <c r="I477" s="9">
+      <c r="I477">
         <v>1</v>
       </c>
     </row>
@@ -19019,7 +19018,7 @@
       <c r="H478" t="s">
         <v>308</v>
       </c>
-      <c r="I478" s="9">
+      <c r="I478">
         <v>1</v>
       </c>
     </row>
@@ -19614,7 +19613,7 @@
       <c r="H501" t="s">
         <v>49</v>
       </c>
-      <c r="I501" s="9">
+      <c r="I501">
         <v>3</v>
       </c>
     </row>
@@ -19640,7 +19639,7 @@
       <c r="H502" t="s">
         <v>49</v>
       </c>
-      <c r="I502" s="9">
+      <c r="I502">
         <v>1</v>
       </c>
     </row>
@@ -19666,7 +19665,7 @@
       <c r="H503" t="s">
         <v>49</v>
       </c>
-      <c r="I503" s="9">
+      <c r="I503">
         <v>1</v>
       </c>
     </row>
@@ -19692,7 +19691,7 @@
       <c r="H504" t="s">
         <v>49</v>
       </c>
-      <c r="I504" s="9">
+      <c r="I504">
         <v>3</v>
       </c>
     </row>
@@ -20732,7 +20731,7 @@
       <c r="H544" t="s">
         <v>49</v>
       </c>
-      <c r="I544" s="9">
+      <c r="I544">
         <v>1</v>
       </c>
     </row>
@@ -21229,7 +21228,7 @@
       <c r="H563" t="s">
         <v>49</v>
       </c>
-      <c r="I563" s="9">
+      <c r="I563">
         <v>2</v>
       </c>
     </row>
@@ -21255,7 +21254,7 @@
       <c r="H564" t="s">
         <v>49</v>
       </c>
-      <c r="I564" s="9">
+      <c r="I564">
         <v>3</v>
       </c>
       <c r="K564" s="2" t="s">
@@ -21287,7 +21286,7 @@
       <c r="H565" t="s">
         <v>49</v>
       </c>
-      <c r="I565" s="9">
+      <c r="I565">
         <v>3</v>
       </c>
     </row>
@@ -22691,7 +22690,7 @@
       <c r="H619" t="s">
         <v>109</v>
       </c>
-      <c r="I619" s="10">
+      <c r="I619" s="9">
         <v>2</v>
       </c>
     </row>
@@ -22717,7 +22716,7 @@
       <c r="H620" t="s">
         <v>109</v>
       </c>
-      <c r="I620" s="10">
+      <c r="I620" s="9">
         <v>2</v>
       </c>
     </row>
@@ -22743,7 +22742,7 @@
       <c r="H621" t="s">
         <v>109</v>
       </c>
-      <c r="I621" s="10">
+      <c r="I621" s="9">
         <v>2</v>
       </c>
     </row>
@@ -22896,7 +22895,7 @@
       <c r="H627" t="s">
         <v>109</v>
       </c>
-      <c r="I627" s="10">
+      <c r="I627" s="9">
         <v>2</v>
       </c>
     </row>
@@ -22922,7 +22921,7 @@
       <c r="H628" t="s">
         <v>109</v>
       </c>
-      <c r="I628" s="11">
+      <c r="I628" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23000,7 +22999,7 @@
       <c r="H631" t="s">
         <v>109</v>
       </c>
-      <c r="I631" s="11">
+      <c r="I631" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23026,7 +23025,7 @@
       <c r="H632" t="s">
         <v>109</v>
       </c>
-      <c r="I632" s="11">
+      <c r="I632" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23078,7 +23077,7 @@
       <c r="H634" t="s">
         <v>109</v>
       </c>
-      <c r="I634" s="11">
+      <c r="I634" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23104,7 +23103,7 @@
       <c r="H635" t="s">
         <v>109</v>
       </c>
-      <c r="I635" s="10">
+      <c r="I635" s="9">
         <v>2</v>
       </c>
     </row>
@@ -23130,7 +23129,7 @@
       <c r="H636" t="s">
         <v>109</v>
       </c>
-      <c r="I636" s="11">
+      <c r="I636" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23182,7 +23181,7 @@
       <c r="H638" t="s">
         <v>109</v>
       </c>
-      <c r="I638" s="10">
+      <c r="I638" s="9">
         <v>2</v>
       </c>
     </row>
@@ -23208,7 +23207,7 @@
       <c r="H639" t="s">
         <v>109</v>
       </c>
-      <c r="I639" s="10">
+      <c r="I639" s="9">
         <v>2</v>
       </c>
     </row>
@@ -23234,7 +23233,7 @@
       <c r="H640" t="s">
         <v>109</v>
       </c>
-      <c r="I640" s="11">
+      <c r="I640" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23260,7 +23259,7 @@
       <c r="H641" t="s">
         <v>109</v>
       </c>
-      <c r="I641" s="11">
+      <c r="I641" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23312,7 +23311,7 @@
       <c r="H643" t="s">
         <v>109</v>
       </c>
-      <c r="I643" s="11">
+      <c r="I643" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23364,7 +23363,7 @@
       <c r="H645" t="s">
         <v>342</v>
       </c>
-      <c r="I645" s="11">
+      <c r="I645" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23468,7 +23467,7 @@
       <c r="H649" t="s">
         <v>109</v>
       </c>
-      <c r="I649" s="10">
+      <c r="I649" s="9">
         <v>2</v>
       </c>
     </row>
@@ -23523,7 +23522,7 @@
       <c r="H651" t="s">
         <v>109</v>
       </c>
-      <c r="I651" s="11">
+      <c r="I651" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23575,7 +23574,7 @@
       <c r="H653" t="s">
         <v>109</v>
       </c>
-      <c r="I653" s="11">
+      <c r="I653" s="10">
         <v>1</v>
       </c>
     </row>
@@ -23609,7 +23608,7 @@
       <c r="A655" t="s">
         <v>1610</v>
       </c>
-      <c r="B655" s="12" t="s">
+      <c r="B655" s="11" t="s">
         <v>1611</v>
       </c>
       <c r="D655" t="s">
@@ -23627,7 +23626,7 @@
       <c r="H655" t="s">
         <v>109</v>
       </c>
-      <c r="I655" s="10">
+      <c r="I655" s="9">
         <v>2</v>
       </c>
     </row>
@@ -23679,7 +23678,7 @@
       <c r="H657" t="s">
         <v>109</v>
       </c>
-      <c r="I657" s="10">
+      <c r="I657" s="9">
         <v>2</v>
       </c>
     </row>
@@ -23705,7 +23704,7 @@
       <c r="H658" t="s">
         <v>109</v>
       </c>
-      <c r="I658" s="10">
+      <c r="I658" s="9">
         <v>2</v>
       </c>
     </row>
@@ -24066,7 +24065,7 @@
       <c r="H672" t="s">
         <v>109</v>
       </c>
-      <c r="I672" s="9">
+      <c r="I672">
         <v>1</v>
       </c>
     </row>
@@ -24092,7 +24091,7 @@
       <c r="H673" t="s">
         <v>109</v>
       </c>
-      <c r="I673" s="9">
+      <c r="I673">
         <v>3</v>
       </c>
     </row>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B781FE6F-F0E1-4063-833E-25D7F34337AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4BD4999-E8DF-4CA0-AE4B-8F1ECB11A827}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1035" yWindow="120" windowWidth="14160" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7888,7 +7888,7 @@
         <v>139</v>
       </c>
       <c r="I53">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="54" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8264,7 +8264,7 @@
         <v>139</v>
       </c>
       <c r="I67">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="68" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8420,7 +8420,7 @@
         <v>139</v>
       </c>
       <c r="I73">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="74" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDD45B14-22CF-4BA4-A9B1-152652EB9A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{565F516D-D448-482E-B317-9D834700C2F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="420" windowWidth="28800" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -6204,7 +6204,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6231,6 +6231,7 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -30806,16 +30807,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L710"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="32.85546875" customWidth="1"/>
+    <col min="2" max="2" width="41.28515625" customWidth="1"/>
+    <col min="3" max="3" width="50.85546875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="78.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>1960</v>
       </c>
       <c r="D1" t="s">
@@ -30846,7 +30853,7 @@
         <v>1969</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>515</v>
       </c>
@@ -30854,12 +30861,12 @@
         <v>516</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>1738</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1118</v>
       </c>
@@ -30867,7 +30874,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>1122</v>
       </c>
@@ -30875,7 +30882,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1124</v>
       </c>
@@ -30883,7 +30890,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>394</v>
       </c>
@@ -30891,7 +30898,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>1478</v>
       </c>
@@ -30899,18 +30906,18 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>1270</v>
       </c>
       <c r="B9" t="s">
         <v>1271</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="14" t="s">
         <v>1970</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>634</v>
       </c>
@@ -30918,7 +30925,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>1126</v>
       </c>
@@ -30926,18 +30933,18 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>1275</v>
       </c>
       <c r="B12" t="s">
         <v>1276</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="14" t="s">
         <v>1971</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>384</v>
       </c>
@@ -30945,7 +30952,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -30953,7 +30960,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>292</v>
       </c>
@@ -30961,7 +30968,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>442</v>
       </c>
@@ -30969,7 +30976,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>571</v>
       </c>
@@ -30977,7 +30984,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>404</v>
       </c>
@@ -30985,7 +30992,7 @@
         <v>405</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>1447</v>
       </c>
@@ -30993,7 +31000,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>408</v>
       </c>
@@ -31001,18 +31008,18 @@
         <v>409</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>14</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="14" t="s">
         <v>1972</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>91</v>
       </c>
@@ -31020,7 +31027,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>1690</v>
       </c>
@@ -31028,7 +31035,7 @@
         <v>1691</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>1129</v>
       </c>
@@ -31036,7 +31043,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>522</v>
       </c>
@@ -31044,7 +31051,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>677</v>
       </c>
@@ -31052,7 +31059,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>345</v>
       </c>
@@ -31060,7 +31067,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>836</v>
       </c>
@@ -31068,18 +31075,18 @@
         <v>1132</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>1588</v>
       </c>
       <c r="B29" t="s">
         <v>1589</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="1" t="s">
         <v>1973</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>134</v>
       </c>
@@ -31087,7 +31094,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>102</v>
       </c>
@@ -31095,7 +31102,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>252</v>
       </c>
@@ -31103,7 +31110,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>926</v>
       </c>
@@ -31111,7 +31118,7 @@
         <v>1450</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>544</v>
       </c>
@@ -31119,7 +31126,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>102</v>
       </c>
@@ -31127,7 +31134,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>926</v>
       </c>
@@ -31135,7 +31142,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>414</v>
       </c>
@@ -31143,7 +31150,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>681</v>
       </c>
@@ -31151,7 +31158,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>1542</v>
       </c>
@@ -31159,7 +31166,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>418</v>
       </c>
@@ -31167,7 +31174,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>1452</v>
       </c>
@@ -31175,7 +31182,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>1454</v>
       </c>
@@ -31183,7 +31190,7 @@
         <v>1455</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>73</v>
       </c>
@@ -31191,7 +31198,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>329</v>
       </c>
@@ -31199,7 +31206,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>1457</v>
       </c>
@@ -31207,7 +31214,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>321</v>
       </c>
@@ -31215,7 +31222,7 @@
         <v>422</v>
       </c>
     </row>
-    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>633</v>
       </c>
@@ -31223,18 +31230,18 @@
         <v>960</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>1280</v>
       </c>
       <c r="B48" t="s">
         <v>1281</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C48" s="14" t="s">
         <v>1974</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>425</v>
       </c>
@@ -31242,7 +31249,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>1284</v>
       </c>
@@ -31250,7 +31257,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>95</v>
       </c>
@@ -31258,7 +31265,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>225</v>
       </c>
@@ -31266,7 +31273,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>549</v>
       </c>
@@ -31274,7 +31281,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>1591</v>
       </c>
@@ -31282,7 +31289,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>1459</v>
       </c>
@@ -31290,7 +31297,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>292</v>
       </c>
@@ -31298,7 +31305,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>138</v>
       </c>
@@ -31306,7 +31313,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>171</v>
       </c>
@@ -31314,7 +31321,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>102</v>
       </c>
@@ -31322,7 +31329,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>35</v>
       </c>
@@ -31330,7 +31337,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>1693</v>
       </c>
@@ -31338,7 +31345,7 @@
         <v>1694</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>142</v>
       </c>
@@ -31346,7 +31353,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>1286</v>
       </c>
@@ -31354,7 +31361,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>996</v>
       </c>
@@ -31362,7 +31369,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>825</v>
       </c>
@@ -31370,7 +31377,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>24</v>
       </c>
@@ -31378,7 +31385,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>24</v>
       </c>
@@ -31386,7 +31393,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>1137</v>
       </c>
@@ -31394,7 +31401,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>529</v>
       </c>
@@ -31402,7 +31409,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>379</v>
       </c>
@@ -31410,7 +31417,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>432</v>
       </c>
@@ -31418,7 +31425,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>1290</v>
       </c>
@@ -31426,7 +31433,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>552</v>
       </c>
@@ -31434,7 +31441,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>1695</v>
       </c>
@@ -31442,18 +31449,18 @@
         <v>1696</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>1026</v>
       </c>
       <c r="B75" t="s">
         <v>1262</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C75" s="14" t="s">
         <v>1975</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>1595</v>
       </c>
@@ -31461,7 +31468,7 @@
         <v>1596</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>1293</v>
       </c>
@@ -31469,7 +31476,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>1139</v>
       </c>
@@ -31477,7 +31484,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>42</v>
       </c>
@@ -31499,7 +31506,7 @@
         <v>1977</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>45</v>
       </c>
@@ -31507,7 +31514,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1296</v>
       </c>
@@ -31515,7 +31522,7 @@
         <v>1297</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>559</v>
       </c>
@@ -31523,7 +31530,7 @@
         <v>1571</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>559</v>
       </c>
@@ -31531,7 +31538,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>436</v>
       </c>
@@ -31539,7 +31546,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1697</v>
       </c>
@@ -31547,7 +31554,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>966</v>
       </c>
@@ -31555,7 +31562,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>371</v>
       </c>
@@ -31563,7 +31570,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1462</v>
       </c>
@@ -31571,7 +31578,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>146</v>
       </c>
@@ -31579,7 +31586,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1143</v>
       </c>
@@ -31587,7 +31594,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1415</v>
       </c>
@@ -31595,7 +31602,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>442</v>
       </c>
@@ -31603,7 +31610,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>1026</v>
       </c>
@@ -31611,7 +31618,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>699</v>
       </c>
@@ -31619,7 +31626,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>800</v>
       </c>
@@ -31627,7 +31634,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>77</v>
       </c>
@@ -31635,7 +31642,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>153</v>
       </c>
@@ -31643,7 +31650,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>24</v>
       </c>
@@ -31651,7 +31658,7 @@
         <v>1146</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1149</v>
       </c>
@@ -31659,7 +31666,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>42</v>
       </c>
@@ -31667,7 +31674,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>1152</v>
       </c>
@@ -31675,7 +31682,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -31683,7 +31690,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>126</v>
       </c>
@@ -31691,7 +31698,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>586</v>
       </c>
@@ -31699,7 +31706,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>394</v>
       </c>
@@ -31707,7 +31714,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>252</v>
       </c>
@@ -31715,7 +31722,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>748</v>
       </c>
@@ -31723,7 +31730,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>809</v>
       </c>
@@ -31731,7 +31738,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>532</v>
       </c>
@@ -31739,7 +31746,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>50</v>
       </c>
@@ -31747,7 +31754,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1301</v>
       </c>
@@ -31755,7 +31762,7 @@
         <v>1302</v>
       </c>
     </row>
-    <row r="113" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>836</v>
       </c>
@@ -31763,7 +31770,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="114" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>1155</v>
       </c>
@@ -31771,7 +31778,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="115" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>1305</v>
       </c>
@@ -31779,7 +31786,7 @@
         <v>1306</v>
       </c>
     </row>
-    <row r="116" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>840</v>
       </c>
@@ -31787,7 +31794,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="117" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>1158</v>
       </c>
@@ -31795,18 +31802,18 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="118" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>1308</v>
       </c>
       <c r="B118" t="s">
         <v>1309</v>
       </c>
-      <c r="C118" t="s">
+      <c r="C118" s="1" t="s">
         <v>1978</v>
       </c>
     </row>
-    <row r="119" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>1701</v>
       </c>
@@ -31814,7 +31821,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="120" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>108</v>
       </c>
@@ -31822,7 +31829,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="121" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>488</v>
       </c>
@@ -31830,7 +31837,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="122" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>99</v>
       </c>
@@ -31838,7 +31845,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="123" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>425</v>
       </c>
@@ -31846,7 +31853,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="124" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>529</v>
       </c>
@@ -31854,7 +31861,7 @@
         <v>828</v>
       </c>
     </row>
-    <row r="125" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>263</v>
       </c>
@@ -31862,7 +31869,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="126" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>1160</v>
       </c>
@@ -31870,7 +31877,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="127" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>157</v>
       </c>
@@ -31878,7 +31885,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="128" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>937</v>
       </c>
@@ -31886,7 +31893,7 @@
         <v>1466</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>669</v>
       </c>
@@ -31894,7 +31901,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>1467</v>
       </c>
@@ -31902,7 +31909,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>977</v>
       </c>
@@ -31910,7 +31917,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>1312</v>
       </c>
@@ -31918,7 +31925,7 @@
         <v>1313</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>42</v>
       </c>
@@ -31926,7 +31933,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>565</v>
       </c>
@@ -31934,7 +31941,7 @@
         <v>566</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>24</v>
       </c>
@@ -31942,7 +31949,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>569</v>
       </c>
@@ -31950,7 +31957,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>1181</v>
       </c>
@@ -31958,7 +31965,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>702</v>
       </c>
@@ -31966,7 +31973,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>1470</v>
       </c>
@@ -31974,7 +31981,7 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>138</v>
       </c>
@@ -31982,7 +31989,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>979</v>
       </c>
@@ -31990,7 +31997,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>1319</v>
       </c>
@@ -31998,7 +32005,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>996</v>
       </c>
@@ -32006,7 +32013,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>1473</v>
       </c>
@@ -32014,7 +32021,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>161</v>
       </c>
@@ -32022,7 +32029,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>1323</v>
       </c>
@@ -32030,7 +32037,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>844</v>
       </c>
@@ -32038,12 +32045,12 @@
         <v>845</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>42</v>
       </c>
@@ -32051,7 +32058,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>55</v>
       </c>
@@ -32059,7 +32066,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>201</v>
       </c>
@@ -32067,7 +32074,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>394</v>
       </c>
@@ -32075,7 +32082,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>664</v>
       </c>
@@ -32083,7 +32090,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>1391</v>
       </c>
@@ -32091,7 +32098,7 @@
         <v>1579</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>937</v>
       </c>
@@ -32099,7 +32106,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>442</v>
       </c>
@@ -32107,7 +32114,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>77</v>
       </c>
@@ -32115,7 +32122,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>926</v>
       </c>
@@ -32123,7 +32130,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>1163</v>
       </c>
@@ -32131,7 +32138,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>77</v>
       </c>
@@ -32139,7 +32146,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>571</v>
       </c>
@@ -32147,7 +32154,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>1786</v>
       </c>
@@ -32155,7 +32162,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>836</v>
       </c>
@@ -32163,7 +32170,7 @@
         <v>1327</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>982</v>
       </c>
@@ -32171,7 +32178,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>748</v>
       </c>
@@ -32179,7 +32186,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>345</v>
       </c>
@@ -32187,7 +32194,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>1597</v>
       </c>
@@ -32195,7 +32202,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>333</v>
       </c>
@@ -32203,7 +32210,7 @@
         <v>1167</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>1328</v>
       </c>
@@ -32211,7 +32218,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>263</v>
       </c>
@@ -32219,7 +32226,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>263</v>
       </c>
@@ -32227,7 +32234,7 @@
         <v>454</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>192</v>
       </c>
@@ -32235,7 +32242,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>188</v>
       </c>
@@ -32243,7 +32250,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>1308</v>
       </c>
@@ -32251,7 +32258,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>39</v>
       </c>
@@ -32259,7 +32266,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>77</v>
       </c>
@@ -32267,7 +32274,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>345</v>
       </c>
@@ -32275,7 +32282,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1170</v>
       </c>
@@ -32283,7 +32290,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1170</v>
       </c>
@@ -32291,7 +32298,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>800</v>
       </c>
@@ -32299,7 +32306,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>449</v>
       </c>
@@ -32307,7 +32314,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>449</v>
       </c>
@@ -32315,7 +32322,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1308</v>
       </c>
@@ -32323,7 +32330,7 @@
         <v>1477</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>168</v>
       </c>
@@ -32331,7 +32338,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>696</v>
       </c>
@@ -32339,7 +32346,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>35</v>
       </c>
@@ -32347,7 +32354,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1704</v>
       </c>
@@ -32355,7 +32362,7 @@
         <v>1705</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1481</v>
       </c>
@@ -32363,7 +32370,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>388</v>
       </c>
@@ -32371,7 +32378,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>252</v>
       </c>
@@ -32379,7 +32386,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1334</v>
       </c>
@@ -32387,7 +32394,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>373</v>
       </c>
@@ -32395,7 +32402,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1264</v>
       </c>
@@ -32403,7 +32410,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1485</v>
       </c>
@@ -32411,7 +32418,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1442</v>
       </c>
@@ -32419,7 +32426,7 @@
         <v>1443</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1339</v>
       </c>
@@ -32427,7 +32434,7 @@
         <v>1340</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1207</v>
       </c>
@@ -32435,7 +32442,7 @@
         <v>1600</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>327</v>
       </c>
@@ -32443,7 +32450,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1175</v>
       </c>
@@ -32451,7 +32458,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1343</v>
       </c>
@@ -32459,7 +32466,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>277</v>
       </c>
@@ -32467,7 +32474,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>661</v>
       </c>
@@ -32475,7 +32482,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1260</v>
       </c>
@@ -32483,7 +32490,7 @@
         <v>1261</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>280</v>
       </c>
@@ -32491,7 +32498,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>95</v>
       </c>
@@ -32499,7 +32506,7 @@
         <v>1602</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>519</v>
       </c>
@@ -32507,7 +32514,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>748</v>
       </c>
@@ -32515,7 +32522,7 @@
         <v>1706</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1682</v>
       </c>
@@ -32523,7 +32530,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="209" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1178</v>
       </c>
@@ -32531,7 +32538,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="210" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1308</v>
       </c>
@@ -32539,7 +32546,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="211" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>373</v>
       </c>
@@ -32547,7 +32554,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="212" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1803</v>
       </c>
@@ -32555,7 +32562,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="213" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>593</v>
       </c>
@@ -32563,7 +32570,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="214" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>992</v>
       </c>
@@ -32571,7 +32578,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="215" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>1181</v>
       </c>
@@ -32579,7 +32586,7 @@
         <v>1488</v>
       </c>
     </row>
-    <row r="216" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>596</v>
       </c>
@@ -32587,7 +32594,7 @@
         <v>597</v>
       </c>
     </row>
-    <row r="217" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>333</v>
       </c>
@@ -32595,7 +32602,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="218" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>996</v>
       </c>
@@ -32603,18 +32610,18 @@
         <v>997</v>
       </c>
     </row>
-    <row r="219" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1605</v>
       </c>
       <c r="B219" t="s">
         <v>1606</v>
       </c>
-      <c r="C219" t="s">
+      <c r="C219" s="1" t="s">
         <v>1979</v>
       </c>
     </row>
-    <row r="220" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>102</v>
       </c>
@@ -32622,7 +32629,7 @@
         <v>1489</v>
       </c>
     </row>
-    <row r="221" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>442</v>
       </c>
@@ -32630,7 +32637,7 @@
         <v>866</v>
       </c>
     </row>
-    <row r="222" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>371</v>
       </c>
@@ -32638,7 +32645,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="223" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>384</v>
       </c>
@@ -32646,7 +32653,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="224" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>800</v>
       </c>
@@ -32654,7 +32661,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>926</v>
       </c>
@@ -32662,7 +32669,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1181</v>
       </c>
@@ -32670,7 +32677,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>869</v>
       </c>
@@ -32678,7 +32685,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1348</v>
       </c>
@@ -32686,7 +32693,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>800</v>
       </c>
@@ -32694,7 +32701,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>252</v>
       </c>
@@ -32702,7 +32709,7 @@
         <v>1808</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>195</v>
       </c>
@@ -32710,7 +32717,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>283</v>
       </c>
@@ -32718,7 +32725,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1000</v>
       </c>
@@ -32726,7 +32733,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>171</v>
       </c>
@@ -32734,7 +32741,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>721</v>
       </c>
@@ -32742,7 +32749,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1183</v>
       </c>
@@ -32750,7 +32757,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1305</v>
       </c>
@@ -32758,7 +32765,7 @@
         <v>1492</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>269</v>
       </c>
@@ -32766,7 +32773,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>873</v>
       </c>
@@ -32774,7 +32781,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>269</v>
       </c>
@@ -32782,7 +32789,7 @@
         <v>875</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>102</v>
       </c>
@@ -32790,7 +32797,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>449</v>
       </c>
@@ -32798,7 +32805,7 @@
         <v>876</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1493</v>
       </c>
@@ -32806,7 +32813,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>878</v>
       </c>
@@ -32814,7 +32821,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>181</v>
       </c>
@@ -32822,7 +32829,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1186</v>
       </c>
@@ -32830,7 +32837,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>308</v>
       </c>
@@ -32838,7 +32845,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1608</v>
       </c>
@@ -32846,7 +32853,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>1610</v>
       </c>
@@ -32854,7 +32861,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>881</v>
       </c>
@@ -32862,7 +32869,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>42</v>
       </c>
@@ -32870,7 +32877,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>579</v>
       </c>
@@ -32878,7 +32885,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>836</v>
       </c>
@@ -32886,7 +32893,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1812</v>
       </c>
@@ -32894,7 +32901,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>736</v>
       </c>
@@ -32902,7 +32909,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>115</v>
       </c>
@@ -32910,7 +32917,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>465</v>
       </c>
@@ -32918,7 +32925,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>469</v>
       </c>
@@ -32926,7 +32933,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>388</v>
       </c>
@@ -32934,7 +32941,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>174</v>
       </c>
@@ -32942,7 +32949,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>600</v>
       </c>
@@ -32950,7 +32957,7 @@
         <v>601</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1191</v>
       </c>
@@ -32958,7 +32965,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>77</v>
       </c>
@@ -32966,7 +32973,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1004</v>
       </c>
@@ -32974,7 +32981,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>192</v>
       </c>
@@ -32982,7 +32989,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>110</v>
       </c>
@@ -32990,7 +32997,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1495</v>
       </c>
@@ -32998,7 +33005,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1707</v>
       </c>
@@ -33006,7 +33013,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1354</v>
       </c>
@@ -33014,7 +33021,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1612</v>
       </c>
@@ -33022,7 +33029,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1007</v>
       </c>
@@ -33030,7 +33037,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>57</v>
       </c>
@@ -33038,7 +33045,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>225</v>
       </c>
@@ -33046,7 +33053,7 @@
         <v>344</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>926</v>
       </c>
@@ -33054,7 +33061,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>222</v>
       </c>
@@ -33062,7 +33069,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1181</v>
       </c>
@@ -33070,7 +33077,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1170</v>
       </c>
@@ -33078,7 +33085,7 @@
         <v>1497</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>724</v>
       </c>
@@ -33086,7 +33093,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>388</v>
       </c>
@@ -33094,7 +33101,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>729</v>
       </c>
@@ -33102,7 +33109,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>732</v>
       </c>
@@ -33110,7 +33117,7 @@
         <v>730</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>345</v>
       </c>
@@ -33118,7 +33125,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>602</v>
       </c>
@@ -33126,7 +33133,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1319</v>
       </c>
@@ -33134,7 +33141,7 @@
         <v>1360</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1444</v>
       </c>
@@ -33142,7 +33149,7 @@
         <v>1445</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1823</v>
       </c>
@@ -33150,7 +33157,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>73</v>
       </c>
@@ -33158,7 +33165,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>225</v>
       </c>
@@ -33166,7 +33173,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>883</v>
       </c>
@@ -33174,7 +33181,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>836</v>
       </c>
@@ -33182,7 +33189,7 @@
         <v>1501</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1415</v>
       </c>
@@ -33190,7 +33197,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1709</v>
       </c>
@@ -33198,7 +33205,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>326</v>
       </c>
@@ -33206,7 +33213,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>188</v>
       </c>
@@ -33214,7 +33221,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>337</v>
       </c>
@@ -33222,7 +33229,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>201</v>
       </c>
@@ -33230,7 +33237,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>204</v>
       </c>
@@ -33238,7 +33245,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>27</v>
       </c>
@@ -33246,7 +33253,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>442</v>
       </c>
@@ -33254,7 +33261,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1012</v>
       </c>
@@ -33262,7 +33269,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1504</v>
       </c>
@@ -33270,7 +33277,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1194</v>
       </c>
@@ -33278,7 +33285,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1424</v>
       </c>
@@ -33286,7 +33293,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>228</v>
       </c>
@@ -33294,7 +33301,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="305" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1711</v>
       </c>
@@ -33302,7 +33309,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="306" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>283</v>
       </c>
@@ -33310,7 +33317,7 @@
         <v>473</v>
       </c>
     </row>
-    <row r="307" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>77</v>
       </c>
@@ -33318,7 +33325,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="308" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>714</v>
       </c>
@@ -33326,7 +33333,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="309" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>283</v>
       </c>
@@ -33334,7 +33341,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="310" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>232</v>
       </c>
@@ -33342,29 +33349,29 @@
         <v>233</v>
       </c>
     </row>
-    <row r="311" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1016</v>
       </c>
       <c r="B311" t="s">
         <v>1017</v>
       </c>
-      <c r="C311" t="s">
+      <c r="C311" s="1" t="s">
         <v>1980</v>
       </c>
     </row>
-    <row r="312" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>937</v>
       </c>
       <c r="B312" t="s">
         <v>1020</v>
       </c>
-      <c r="C312" t="s">
+      <c r="C312" s="1" t="s">
         <v>1981</v>
       </c>
     </row>
-    <row r="313" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>1614</v>
       </c>
@@ -33372,7 +33379,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="314" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>477</v>
       </c>
@@ -33380,7 +33387,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="315" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>188</v>
       </c>
@@ -33388,7 +33395,7 @@
         <v>1023</v>
       </c>
     </row>
-    <row r="316" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>195</v>
       </c>
@@ -33396,7 +33403,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="317" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>225</v>
       </c>
@@ -33404,7 +33411,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="318" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>249</v>
       </c>
@@ -33412,7 +33419,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="319" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1198</v>
       </c>
@@ -33420,7 +33427,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="320" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1198</v>
       </c>
@@ -33428,7 +33435,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>736</v>
       </c>
@@ -33436,7 +33443,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>1834</v>
       </c>
@@ -33444,7 +33451,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>188</v>
       </c>
@@ -33452,7 +33459,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>519</v>
       </c>
@@ -33460,7 +33467,7 @@
         <v>520</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1836</v>
       </c>
@@ -33468,7 +33475,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1838</v>
       </c>
@@ -33476,7 +33483,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1158</v>
       </c>
@@ -33484,7 +33491,7 @@
         <v>1363</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>608</v>
       </c>
@@ -33492,7 +33499,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>612</v>
       </c>
@@ -33500,7 +33507,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1564</v>
       </c>
@@ -33508,7 +33515,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>934</v>
       </c>
@@ -33516,7 +33523,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>739</v>
       </c>
@@ -33524,7 +33531,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1257</v>
       </c>
@@ -33532,7 +33539,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1026</v>
       </c>
@@ -33540,7 +33547,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>252</v>
       </c>
@@ -33548,7 +33555,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1365</v>
       </c>
@@ -33556,7 +33563,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>896</v>
       </c>
@@ -33564,7 +33571,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>805</v>
       </c>
@@ -33572,7 +33579,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>394</v>
       </c>
@@ -33580,7 +33587,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>449</v>
       </c>
@@ -33588,7 +33595,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1508</v>
       </c>
@@ -33596,7 +33603,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1103</v>
       </c>
@@ -33604,7 +33611,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>81</v>
       </c>
@@ -33612,7 +33619,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1368</v>
       </c>
@@ -33620,7 +33627,7 @@
         <v>1369</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1103</v>
       </c>
@@ -33628,7 +33635,7 @@
         <v>1714</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>465</v>
       </c>
@@ -33636,7 +33643,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>614</v>
       </c>
@@ -33644,7 +33651,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>616</v>
       </c>
@@ -33652,7 +33659,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>620</v>
       </c>
@@ -33660,7 +33667,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>1685</v>
       </c>
@@ -33668,7 +33675,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>1617</v>
       </c>
@@ -33676,7 +33683,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1371</v>
       </c>
@@ -33684,7 +33691,7 @@
         <v>1372</v>
       </c>
     </row>
-    <row r="353" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>742</v>
       </c>
@@ -33692,15 +33699,15 @@
         <v>743</v>
       </c>
     </row>
-    <row r="354" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B354" t="s">
         <v>1619</v>
       </c>
-      <c r="C354" t="s">
+      <c r="C354" s="1" t="s">
         <v>1982</v>
       </c>
     </row>
-    <row r="355" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>559</v>
       </c>
@@ -33708,7 +33715,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="356" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>579</v>
       </c>
@@ -33716,7 +33723,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="357" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>623</v>
       </c>
@@ -33724,7 +33731,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="358" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>240</v>
       </c>
@@ -33732,7 +33739,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="359" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1845</v>
       </c>
@@ -33740,7 +33747,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="360" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>664</v>
       </c>
@@ -33748,7 +33755,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="361" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1620</v>
       </c>
@@ -33756,7 +33763,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="362" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1205</v>
       </c>
@@ -33764,7 +33771,7 @@
         <v>1206</v>
       </c>
     </row>
-    <row r="363" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1029</v>
       </c>
@@ -33772,7 +33779,7 @@
         <v>1030</v>
       </c>
     </row>
-    <row r="364" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>677</v>
       </c>
@@ -33780,7 +33787,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="365" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1622</v>
       </c>
@@ -33788,7 +33795,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="366" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1625</v>
       </c>
@@ -33796,7 +33803,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="367" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1181</v>
       </c>
@@ -33804,7 +33811,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="368" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1628</v>
       </c>
@@ -33812,7 +33819,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="369" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1585</v>
       </c>
@@ -33820,7 +33827,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="370" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1510</v>
       </c>
@@ -33828,7 +33835,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>916</v>
       </c>
@@ -33836,7 +33843,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1717</v>
       </c>
@@ -33844,7 +33851,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>350</v>
       </c>
@@ -33852,7 +33859,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="374" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>252</v>
       </c>
@@ -33860,7 +33867,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1630</v>
       </c>
@@ -33868,7 +33875,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1032</v>
       </c>
@@ -33876,7 +33883,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1719</v>
       </c>
@@ -33884,7 +33891,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="378" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>1512</v>
       </c>
@@ -33892,7 +33899,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>345</v>
       </c>
@@ -33900,7 +33907,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="380" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>57</v>
       </c>
@@ -33908,7 +33915,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="381" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>345</v>
       </c>
@@ -33916,7 +33923,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="382" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>188</v>
       </c>
@@ -33924,7 +33931,7 @@
         <v>354</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="383" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>926</v>
       </c>
@@ -33932,7 +33939,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="384" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1632</v>
       </c>
@@ -33940,7 +33947,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>559</v>
       </c>
@@ -33948,7 +33955,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>559</v>
       </c>
@@ -33956,7 +33963,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="387" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1721</v>
       </c>
@@ -33964,7 +33971,7 @@
         <v>1722</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="388" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1514</v>
       </c>
@@ -33972,7 +33979,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="389" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>252</v>
       </c>
@@ -33980,7 +33987,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>115</v>
       </c>
@@ -33988,7 +33995,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="391" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>937</v>
       </c>
@@ -33996,7 +34003,7 @@
         <v>1208</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>630</v>
       </c>
@@ -34004,7 +34011,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="393" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>633</v>
       </c>
@@ -34012,7 +34019,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="394" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>634</v>
       </c>
@@ -34020,7 +34027,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="395" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1040</v>
       </c>
@@ -34028,7 +34035,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1516</v>
       </c>
@@ -34036,7 +34043,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="397" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>449</v>
       </c>
@@ -34044,7 +34051,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="398" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>761</v>
       </c>
@@ -34052,7 +34059,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="399" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>77</v>
       </c>
@@ -34060,7 +34067,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="400" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>283</v>
       </c>
@@ -34068,7 +34075,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="401" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1043</v>
       </c>
@@ -34076,7 +34083,7 @@
         <v>1044</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="402" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>237</v>
       </c>
@@ -34084,7 +34091,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="403" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>240</v>
       </c>
@@ -34092,7 +34099,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="404" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>243</v>
       </c>
@@ -34100,7 +34107,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>24</v>
       </c>
@@ -34108,7 +34115,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>24</v>
       </c>
@@ -34116,7 +34123,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="407" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1095</v>
       </c>
@@ -34124,7 +34131,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="408" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>61</v>
       </c>
@@ -34132,7 +34139,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="409" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>24</v>
       </c>
@@ -34140,7 +34147,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="410" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1207</v>
       </c>
@@ -34148,7 +34155,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="411" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>73</v>
       </c>
@@ -34156,7 +34163,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="412" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>379</v>
       </c>
@@ -34164,7 +34171,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="413" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>1636</v>
       </c>
@@ -34172,7 +34179,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="414" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>204</v>
       </c>
@@ -34180,7 +34187,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="415" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>765</v>
       </c>
@@ -34188,7 +34195,7 @@
         <v>766</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="416" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>634</v>
       </c>
@@ -34196,7 +34203,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="417" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>312</v>
       </c>
@@ -34204,7 +34211,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="418" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>1723</v>
       </c>
@@ -34212,7 +34219,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="419" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>465</v>
       </c>
@@ -34220,7 +34227,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="420" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>73</v>
       </c>
@@ -34228,12 +34235,12 @@
         <v>112</v>
       </c>
     </row>
-    <row r="421" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B421" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="422" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>1639</v>
       </c>
@@ -34241,7 +34248,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="423" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>1374</v>
       </c>
@@ -34249,18 +34256,18 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="424" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>138</v>
       </c>
       <c r="B424" t="s">
         <v>1641</v>
       </c>
-      <c r="C424" t="s">
+      <c r="C424" s="14" t="s">
         <v>1983</v>
       </c>
     </row>
-    <row r="425" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>42</v>
       </c>
@@ -34268,18 +34275,18 @@
         <v>246</v>
       </c>
     </row>
-    <row r="426" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1643</v>
       </c>
       <c r="B426" t="s">
         <v>1644</v>
       </c>
-      <c r="C426" t="s">
+      <c r="C426" s="14" t="s">
         <v>1984</v>
       </c>
     </row>
-    <row r="427" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>904</v>
       </c>
@@ -34287,7 +34294,7 @@
         <v>905</v>
       </c>
     </row>
-    <row r="428" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>249</v>
       </c>
@@ -34295,7 +34302,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="429" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1290</v>
       </c>
@@ -34303,7 +34310,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="430" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>854</v>
       </c>
@@ -34311,7 +34318,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="431" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>854</v>
       </c>
@@ -34319,7 +34326,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="432" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>579</v>
       </c>
@@ -34327,7 +34334,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="433" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>66</v>
       </c>
@@ -34335,7 +34342,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>138</v>
       </c>
@@ -34343,7 +34350,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>488</v>
       </c>
@@ -34351,7 +34358,7 @@
         <v>489</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="436" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>212</v>
       </c>
@@ -34359,7 +34366,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="437" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>637</v>
       </c>
@@ -34367,7 +34374,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="438" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1049</v>
       </c>
@@ -34375,7 +34382,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="439" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>252</v>
       </c>
@@ -34383,7 +34390,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="440" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>70</v>
       </c>
@@ -34391,7 +34398,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="441" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>858</v>
       </c>
@@ -34399,7 +34406,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="442" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>39</v>
       </c>
@@ -34407,7 +34414,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="443" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1052</v>
       </c>
@@ -34415,7 +34422,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="444" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1519</v>
       </c>
@@ -34423,7 +34430,7 @@
         <v>1520</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="445" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>532</v>
       </c>
@@ -34431,7 +34438,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="446" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1210</v>
       </c>
@@ -34439,7 +34446,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="447" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>178</v>
       </c>
@@ -34447,7 +34454,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="448" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>767</v>
       </c>
@@ -34455,7 +34462,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="449" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>491</v>
       </c>
@@ -34463,7 +34470,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="450" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1521</v>
       </c>
@@ -34471,7 +34478,7 @@
         <v>1522</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="451" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>724</v>
       </c>
@@ -34479,7 +34486,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="452" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1378</v>
       </c>
@@ -34487,7 +34494,7 @@
         <v>1379</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="453" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1523</v>
       </c>
@@ -34495,7 +34502,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="454" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1381</v>
       </c>
@@ -34503,7 +34510,7 @@
         <v>1382</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="455" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>188</v>
       </c>
@@ -34511,7 +34518,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="456" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>27</v>
       </c>
@@ -34519,7 +34526,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="457" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>1648</v>
       </c>
@@ -34527,7 +34534,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="458" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>1651</v>
       </c>
@@ -34535,7 +34542,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="459" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1215</v>
       </c>
@@ -34543,7 +34550,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="460" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1217</v>
       </c>
@@ -34551,7 +34558,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="461" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>73</v>
       </c>
@@ -34559,7 +34566,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1655</v>
       </c>
@@ -34567,7 +34574,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>77</v>
       </c>
@@ -34575,7 +34582,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="464" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>724</v>
       </c>
@@ -34583,7 +34590,7 @@
         <v>1383</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1882</v>
       </c>
@@ -34591,7 +34598,7 @@
         <v>1883</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>909</v>
       </c>
@@ -34599,7 +34606,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>712</v>
       </c>
@@ -34607,7 +34614,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1049</v>
       </c>
@@ -34615,7 +34622,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1308</v>
       </c>
@@ -34623,7 +34630,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>1524</v>
       </c>
@@ -34631,7 +34638,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>1385</v>
       </c>
@@ -34639,7 +34646,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>465</v>
       </c>
@@ -34647,7 +34654,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>465</v>
       </c>
@@ -34655,7 +34662,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>1388</v>
       </c>
@@ -34663,7 +34670,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>1658</v>
       </c>
@@ -34671,7 +34678,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1725</v>
       </c>
@@ -34679,7 +34686,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1576</v>
       </c>
@@ -34687,7 +34694,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>770</v>
       </c>
@@ -34695,7 +34702,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1525</v>
       </c>
@@ -34703,7 +34710,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>532</v>
       </c>
@@ -34711,7 +34718,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="481" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>1222</v>
       </c>
@@ -34719,7 +34726,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="482" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>751</v>
       </c>
@@ -34727,7 +34734,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="483" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>1181</v>
       </c>
@@ -34735,7 +34742,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="484" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1055</v>
       </c>
@@ -34743,7 +34750,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="485" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>1058</v>
       </c>
@@ -34751,7 +34758,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="486" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>321</v>
       </c>
@@ -34759,7 +34766,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="487" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>1661</v>
       </c>
@@ -34767,7 +34774,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="488" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>339</v>
       </c>
@@ -34775,7 +34782,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="489" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>996</v>
       </c>
@@ -34783,7 +34790,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="490" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>911</v>
       </c>
@@ -34791,7 +34798,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>142</v>
       </c>
@@ -34799,7 +34806,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>586</v>
       </c>
@@ -34807,7 +34814,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="493" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>937</v>
       </c>
@@ -34815,7 +34822,7 @@
         <v>1060</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="494" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>254</v>
       </c>
@@ -34823,7 +34830,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="495" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1225</v>
       </c>
@@ -34831,7 +34838,7 @@
         <v>1226</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="496" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>579</v>
       </c>
@@ -34839,7 +34846,7 @@
         <v>1889</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="497" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>115</v>
       </c>
@@ -34847,7 +34854,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="498" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>240</v>
       </c>
@@ -34855,7 +34862,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="499" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1481</v>
       </c>
@@ -34863,7 +34870,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="500" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>432</v>
       </c>
@@ -34871,7 +34878,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="501" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>1062</v>
       </c>
@@ -34879,7 +34886,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="502" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>77</v>
       </c>
@@ -34887,7 +34894,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="503" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>1227</v>
       </c>
@@ -34895,7 +34902,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="504" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1191</v>
       </c>
@@ -34903,7 +34910,7 @@
         <v>1528</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="505" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>937</v>
       </c>
@@ -34911,7 +34918,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="506" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>24</v>
       </c>
@@ -34919,7 +34926,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="507" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>916</v>
       </c>
@@ -34927,7 +34934,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="508" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>1470</v>
       </c>
@@ -34935,7 +34942,7 @@
         <v>1665</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="509" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>212</v>
       </c>
@@ -34943,7 +34950,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="510" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>73</v>
       </c>
@@ -34951,7 +34958,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="511" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>937</v>
       </c>
@@ -34959,7 +34966,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="512" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>645</v>
       </c>
@@ -34967,7 +34974,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="513" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>460</v>
       </c>
@@ -34975,7 +34982,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="514" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>712</v>
       </c>
@@ -34983,7 +34990,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="515" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>42</v>
       </c>
@@ -34991,7 +34998,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="516" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>102</v>
       </c>
@@ -34999,7 +35006,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="517" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>125</v>
       </c>
@@ -35007,7 +35014,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="518" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1391</v>
       </c>
@@ -35015,7 +35022,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="519" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>263</v>
       </c>
@@ -35023,7 +35030,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>263</v>
       </c>
@@ -35031,7 +35038,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>442</v>
       </c>
@@ -35039,7 +35046,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="522" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>321</v>
       </c>
@@ -35047,7 +35054,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="523" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>465</v>
       </c>
@@ -35055,7 +35062,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="524" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>591</v>
       </c>
@@ -35063,7 +35070,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="525" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>1900</v>
       </c>
@@ -35071,7 +35078,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="526" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>345</v>
       </c>
@@ -35079,7 +35086,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="527" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1532</v>
       </c>
@@ -35087,7 +35094,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="528" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>77</v>
       </c>
@@ -35095,7 +35102,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="529" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1348</v>
       </c>
@@ -35103,7 +35110,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="530" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>1728</v>
       </c>
@@ -35111,7 +35118,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="531" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>1454</v>
       </c>
@@ -35119,7 +35126,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="532" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>775</v>
       </c>
@@ -35127,7 +35134,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="533" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>195</v>
       </c>
@@ -35135,7 +35142,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="534" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>188</v>
       </c>
@@ -35143,7 +35150,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="535" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>77</v>
       </c>
@@ -35151,7 +35158,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="536" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>559</v>
       </c>
@@ -35159,7 +35166,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="537" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>559</v>
       </c>
@@ -35167,7 +35174,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="538" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>266</v>
       </c>
@@ -35175,7 +35182,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="539" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>188</v>
       </c>
@@ -35183,7 +35190,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="540" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>920</v>
       </c>
@@ -35191,7 +35198,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="541" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>920</v>
       </c>
@@ -35199,7 +35206,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="542" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>321</v>
       </c>
@@ -35207,7 +35214,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="543" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1007</v>
       </c>
@@ -35215,7 +35222,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="544" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>263</v>
       </c>
@@ -35223,7 +35230,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>1071</v>
       </c>
@@ -35231,7 +35238,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1537</v>
       </c>
@@ -35239,7 +35246,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>477</v>
       </c>
@@ -35247,7 +35254,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>1394</v>
       </c>
@@ -35255,7 +35262,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>926</v>
       </c>
@@ -35263,7 +35270,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>252</v>
       </c>
@@ -35271,7 +35278,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>1514</v>
       </c>
@@ -35279,7 +35286,7 @@
         <v>1540</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="552" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>212</v>
       </c>
@@ -35287,7 +35294,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="553" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>1396</v>
       </c>
@@ -35295,7 +35302,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>1399</v>
       </c>
@@ -35303,7 +35310,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>1075</v>
       </c>
@@ -35311,7 +35318,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>712</v>
       </c>
@@ -35319,7 +35326,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>651</v>
       </c>
@@ -35327,7 +35334,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>654</v>
       </c>
@@ -35335,7 +35342,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="559" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>1542</v>
       </c>
@@ -35343,7 +35350,7 @@
         <v>1543</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>948</v>
       </c>
@@ -35351,7 +35358,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="561" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>809</v>
       </c>
@@ -35359,7 +35366,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="562" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>42</v>
       </c>
@@ -35367,7 +35374,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="563" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>326</v>
       </c>
@@ -35375,7 +35382,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="564" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>602</v>
       </c>
@@ -35383,7 +35390,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="565" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>181</v>
       </c>
@@ -35391,7 +35398,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="566" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>321</v>
       </c>
@@ -35399,7 +35406,7 @@
         <v>504</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="567" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>1454</v>
       </c>
@@ -35407,7 +35414,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="568" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>345</v>
       </c>
@@ -35415,7 +35422,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="569" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>1544</v>
       </c>
@@ -35423,7 +35430,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="570" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>1081</v>
       </c>
@@ -35431,7 +35438,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="571" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>930</v>
       </c>
@@ -35439,7 +35446,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="572" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>858</v>
       </c>
@@ -35447,7 +35454,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="573" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>507</v>
       </c>
@@ -35455,7 +35462,7 @@
         <v>508</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="574" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>780</v>
       </c>
@@ -35463,7 +35470,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="575" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>1084</v>
       </c>
@@ -35471,7 +35478,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>269</v>
       </c>
@@ -35479,7 +35486,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="577" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>263</v>
       </c>
@@ -35487,7 +35494,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>35</v>
       </c>
@@ -35495,7 +35502,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>1402</v>
       </c>
@@ -35503,7 +35510,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="580" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>388</v>
       </c>
@@ -35511,7 +35518,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="581" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>1234</v>
       </c>
@@ -35519,7 +35526,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="582" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>138</v>
       </c>
@@ -35527,7 +35534,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="583" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>1319</v>
       </c>
@@ -35535,7 +35542,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="584" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>1668</v>
       </c>
@@ -35543,7 +35550,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="585" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
         <v>784</v>
       </c>
@@ -35551,7 +35558,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="586" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
         <v>442</v>
       </c>
@@ -35559,7 +35566,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="587" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
         <v>742</v>
       </c>
@@ -35567,7 +35574,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="588" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
         <v>904</v>
       </c>
@@ -35575,7 +35582,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="589" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
         <v>814</v>
       </c>
@@ -35583,7 +35590,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="590" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
         <v>1237</v>
       </c>
@@ -35591,7 +35598,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="591" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
         <v>1428</v>
       </c>
@@ -35599,7 +35606,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="592" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
         <v>1583</v>
       </c>
@@ -35607,7 +35614,7 @@
         <v>1584</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="593" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
         <v>596</v>
       </c>
@@ -35615,7 +35622,7 @@
         <v>1239</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="594" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
         <v>714</v>
       </c>
@@ -35623,7 +35630,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="595" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
         <v>529</v>
       </c>
@@ -35631,7 +35638,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="596" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
         <v>188</v>
       </c>
@@ -35639,7 +35646,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="597" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
         <v>408</v>
       </c>
@@ -35647,7 +35654,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="598" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
         <v>42</v>
       </c>
@@ -35655,7 +35662,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="599" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
         <v>321</v>
       </c>
@@ -35663,7 +35670,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="600" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
         <v>510</v>
       </c>
@@ -35671,7 +35678,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="601" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
         <v>1406</v>
       </c>
@@ -35679,7 +35686,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="602" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
         <v>596</v>
       </c>
@@ -35687,7 +35694,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="603" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
         <v>42</v>
       </c>
@@ -35695,7 +35702,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="604" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
         <v>1267</v>
       </c>
@@ -35703,7 +35710,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="605" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
         <v>1243</v>
       </c>
@@ -35711,7 +35718,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="606" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
         <v>1670</v>
       </c>
@@ -35719,7 +35726,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
         <v>1245</v>
       </c>
@@ -35727,7 +35734,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
         <v>957</v>
       </c>
@@ -35735,7 +35742,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="609" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
         <v>81</v>
       </c>
@@ -35743,7 +35750,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="610" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
         <v>1181</v>
       </c>
@@ -35751,7 +35758,7 @@
         <v>1409</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="611" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
         <v>315</v>
       </c>
@@ -35759,7 +35766,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="612" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
         <v>709</v>
       </c>
@@ -35767,7 +35774,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="613" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="613" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
         <v>1934</v>
       </c>
@@ -35775,7 +35782,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="614" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="614" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
         <v>1548</v>
       </c>
@@ -35783,7 +35790,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="615" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="615" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
         <v>1181</v>
       </c>
@@ -35791,7 +35798,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="616" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="616" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
         <v>326</v>
       </c>
@@ -35799,7 +35806,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="617" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="617" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
         <v>584</v>
       </c>
@@ -35807,7 +35814,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="618" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="618" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
         <v>318</v>
       </c>
@@ -35815,7 +35822,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="619" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="619" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
         <v>1550</v>
       </c>
@@ -35823,7 +35830,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="620" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="620" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
         <v>1415</v>
       </c>
@@ -35831,7 +35838,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="621" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="621" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
         <v>1591</v>
       </c>
@@ -35839,7 +35846,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="622" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="622" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
         <v>1247</v>
       </c>
@@ -35847,7 +35854,7 @@
         <v>1248</v>
       </c>
     </row>
-    <row r="623" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="623" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
         <v>128</v>
       </c>
@@ -35855,7 +35862,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="624" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="624" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
         <v>736</v>
       </c>
@@ -35863,7 +35870,7 @@
         <v>787</v>
       </c>
     </row>
-    <row r="625" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="625" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
         <v>1674</v>
       </c>
@@ -35871,7 +35878,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="626" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="626" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
         <v>345</v>
       </c>
@@ -35879,7 +35886,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="627" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="627" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
         <v>283</v>
       </c>
@@ -35887,7 +35894,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="628" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="628" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
         <v>1415</v>
       </c>
@@ -35895,7 +35902,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="629" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="629" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
         <v>934</v>
       </c>
@@ -35903,7 +35910,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="630" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="630" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
         <v>1555</v>
       </c>
@@ -35911,7 +35918,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="631" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="631" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
         <v>363</v>
       </c>
@@ -35919,7 +35926,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="632" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="632" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
         <v>937</v>
       </c>
@@ -35927,7 +35934,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="633" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="633" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
         <v>1251</v>
       </c>
@@ -35935,7 +35942,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="634" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="634" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
         <v>35</v>
       </c>
@@ -35943,7 +35950,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="635" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="635" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
         <v>1088</v>
       </c>
@@ -35951,7 +35958,7 @@
         <v>1089</v>
       </c>
     </row>
-    <row r="636" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
         <v>1091</v>
       </c>
@@ -35959,7 +35966,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="637" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
         <v>755</v>
       </c>
@@ -35967,7 +35974,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="638" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="638" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
         <v>602</v>
       </c>
@@ -35975,7 +35982,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="639" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="639" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
         <v>1730</v>
       </c>
@@ -35983,7 +35990,7 @@
         <v>1731</v>
       </c>
     </row>
-    <row r="640" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="640" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
         <v>240</v>
       </c>
@@ -35991,7 +35998,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="641" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="641" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
         <v>1677</v>
       </c>
@@ -35999,7 +36006,7 @@
         <v>1678</v>
       </c>
     </row>
-    <row r="642" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="642" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
         <v>1255</v>
       </c>
@@ -36007,7 +36014,7 @@
         <v>1256</v>
       </c>
     </row>
-    <row r="643" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="643" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
         <v>795</v>
       </c>
@@ -36015,7 +36022,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="644" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="644" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
         <v>664</v>
       </c>
@@ -36023,7 +36030,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="645" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="645" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
         <v>1557</v>
       </c>
@@ -36031,7 +36038,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="646" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="646" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
         <v>1559</v>
       </c>
@@ -36039,7 +36046,7 @@
         <v>1560</v>
       </c>
     </row>
-    <row r="647" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="647" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
         <v>1942</v>
       </c>
@@ -36047,7 +36054,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="648" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="648" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
         <v>465</v>
       </c>
@@ -36055,7 +36062,7 @@
         <v>1093</v>
       </c>
     </row>
-    <row r="649" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="649" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
         <v>1257</v>
       </c>
@@ -36063,7 +36070,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="650" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="650" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
         <v>1348</v>
       </c>
@@ -36071,7 +36078,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="651" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="651" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
         <v>408</v>
       </c>
@@ -36079,7 +36086,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="652" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="652" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
         <v>24</v>
       </c>
@@ -36087,7 +36094,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="653" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="653" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
         <v>138</v>
       </c>
@@ -36095,7 +36102,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="654" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="654" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
         <v>709</v>
       </c>
@@ -36103,7 +36110,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="655" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="655" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
         <v>987</v>
       </c>
@@ -36111,7 +36118,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="656" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="656" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
         <v>327</v>
       </c>
@@ -36119,7 +36126,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="657" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
         <v>1181</v>
       </c>
@@ -36127,7 +36134,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="658" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
         <v>937</v>
       </c>
@@ -36135,7 +36142,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="659" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
         <v>273</v>
       </c>
@@ -36143,7 +36150,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="660" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
         <v>1418</v>
       </c>
@@ -36151,7 +36158,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="661" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
         <v>85</v>
       </c>
@@ -36159,7 +36166,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="662" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
         <v>1343</v>
       </c>
@@ -36167,18 +36174,18 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="663" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
         <v>1680</v>
       </c>
       <c r="B663" t="s">
         <v>1681</v>
       </c>
-      <c r="C663" t="s">
+      <c r="C663" s="14" t="s">
         <v>1985</v>
       </c>
     </row>
-    <row r="664" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
         <v>240</v>
       </c>
@@ -36186,7 +36193,7 @@
         <v>1174</v>
       </c>
     </row>
-    <row r="665" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
         <v>1421</v>
       </c>
@@ -36194,7 +36201,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="666" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
         <v>751</v>
       </c>
@@ -36202,7 +36209,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="667" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
         <v>522</v>
       </c>
@@ -36210,7 +36217,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="668" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
         <v>388</v>
       </c>
@@ -36218,7 +36225,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="669" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
         <v>584</v>
       </c>
@@ -36226,7 +36233,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="670" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
         <v>664</v>
       </c>
@@ -36234,7 +36241,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="671" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
         <v>225</v>
       </c>
@@ -36242,7 +36249,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="672" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
         <v>85</v>
       </c>
@@ -36250,7 +36257,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="673" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="673" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
         <v>126</v>
       </c>
@@ -36258,7 +36265,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="674" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="674" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
         <v>940</v>
       </c>
@@ -36266,7 +36273,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="675" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="675" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
         <v>819</v>
       </c>
@@ -36274,7 +36281,7 @@
         <v>820</v>
       </c>
     </row>
-    <row r="676" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="676" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
         <v>1098</v>
       </c>
@@ -36282,7 +36289,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="677" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="677" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
         <v>85</v>
       </c>
@@ -36290,7 +36297,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="678" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="678" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
         <v>42</v>
       </c>
@@ -36298,7 +36305,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="679" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="679" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
         <v>1100</v>
       </c>
@@ -36306,7 +36313,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="680" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="680" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
         <v>1562</v>
       </c>
@@ -36314,7 +36321,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="681" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="681" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
         <v>375</v>
       </c>
@@ -36322,7 +36329,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="682" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="682" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
         <v>574</v>
       </c>
@@ -36330,7 +36337,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="683" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="683" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
         <v>115</v>
       </c>
@@ -36338,7 +36345,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="684" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="684" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
         <v>634</v>
       </c>
@@ -36346,7 +36353,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="685" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="685" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
         <v>287</v>
       </c>
@@ -36354,7 +36361,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="686" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="686" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
         <v>263</v>
       </c>
@@ -36362,7 +36369,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="687" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="687" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
         <v>292</v>
       </c>
@@ -36370,7 +36377,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="688" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="688" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
         <v>457</v>
       </c>
@@ -36378,7 +36385,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="689" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="689" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
         <v>249</v>
       </c>
@@ -36386,7 +36393,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="690" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="690" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
         <v>586</v>
       </c>
@@ -36394,7 +36401,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="691" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="691" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
         <v>1431</v>
       </c>
@@ -36402,7 +36409,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="692" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="692" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
         <v>1374</v>
       </c>
@@ -36410,7 +36417,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="693" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="693" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
         <v>77</v>
       </c>
@@ -36418,7 +36425,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="694" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
         <v>1435</v>
       </c>
@@ -36426,7 +36433,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="695" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
         <v>1103</v>
       </c>
@@ -36434,7 +36441,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="696" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="696" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
         <v>1687</v>
       </c>
@@ -36442,7 +36449,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="697" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="697" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
         <v>1106</v>
       </c>
@@ -36450,7 +36457,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="698" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="698" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
         <v>1439</v>
       </c>
@@ -36458,7 +36465,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="699" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="699" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
         <v>1568</v>
       </c>
@@ -36466,7 +36473,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="700" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="700" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
         <v>1734</v>
       </c>
@@ -36474,7 +36481,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="701" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="701" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
         <v>1109</v>
       </c>
@@ -36482,7 +36489,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="702" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="702" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
         <v>295</v>
       </c>
@@ -36490,7 +36497,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="703" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="703" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
         <v>1661</v>
       </c>
@@ -36498,7 +36505,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="704" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="704" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
         <v>1959</v>
       </c>
@@ -36506,7 +36513,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="705" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="705" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
         <v>996</v>
       </c>
@@ -36514,7 +36521,7 @@
         <v>1112</v>
       </c>
     </row>
-    <row r="706" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="706" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
         <v>225</v>
       </c>
@@ -36522,7 +36529,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="707" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
         <v>31</v>
       </c>
@@ -36530,18 +36537,18 @@
         <v>32</v>
       </c>
     </row>
-    <row r="708" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="708" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
         <v>1115</v>
       </c>
       <c r="B708" t="s">
         <v>1116</v>
       </c>
-      <c r="C708" t="s">
+      <c r="C708" s="1" t="s">
         <v>1986</v>
       </c>
     </row>
-    <row r="709" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
         <v>714</v>
       </c>
@@ -36549,7 +36556,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="710" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
         <v>945</v>
       </c>
@@ -36560,6 +36567,14 @@
   </sheetData>
   <hyperlinks>
     <hyperlink ref="C80" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="C9" r:id="rId2" xr:uid="{0BFC9787-0EF0-40D7-A9ED-DED72A2740F0}"/>
+    <hyperlink ref="C12" r:id="rId3" xr:uid="{65366C55-9694-4F97-A5FD-E8F9CE09F2E7}"/>
+    <hyperlink ref="C21" r:id="rId4" xr:uid="{48E128B3-0BC2-4A8F-9021-1C5209902DA7}"/>
+    <hyperlink ref="C48" r:id="rId5" xr:uid="{5010A52B-1933-4B0D-8945-6825FCF10538}"/>
+    <hyperlink ref="C75" r:id="rId6" xr:uid="{31197C11-DE2D-4242-88B9-D74E29521FC7}"/>
+    <hyperlink ref="C424" r:id="rId7" xr:uid="{615ECECA-FC28-4049-AF90-8282CFB5FB08}"/>
+    <hyperlink ref="C426" r:id="rId8" xr:uid="{3F258564-535C-4E31-84FD-F0B4224DEDFC}"/>
+    <hyperlink ref="C663" r:id="rId9" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{033EC726-D865-426A-819E-A799648AB3C1}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C64D5E9-6459-43A2-9266-611D057C018F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CF1704-F7F7-41D3-9B7F-A7A657C4593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="0" windowWidth="16275" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7192" uniqueCount="1964">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7200" uniqueCount="1972">
   <si>
     <t>Prénom</t>
   </si>
@@ -6059,6 +6059,30 @@
   </si>
   <si>
     <t>Niccolo dell'ARCA</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ea/Adam%2C_Lambert_Sigisbert.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/Nicolas-S%C3%A9bastien_Adam.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/af/DuplessisAllegrain.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/12/Pastel_portrait_of_John_Bacon_RA_%281740-1799%29%2C_by_John_Russell_RA_%281745-1806%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg/960px-Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3f/EdmeBouchardon-FrancoisHubertDrouais.JPG/960px-EdmeBouchardon-FrancoisHubertDrouais.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Pietro-Bracci-Accademia-San-Luca.jpg/960px-Pietro-Bracci-Accademia-San-Luca.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Adolf_Ulrik_Wertm%C3%BCller%2C_Portrait_of_Jean-Jacques_Caffieri_%281784%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -6136,7 +6160,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6157,6 +6181,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
@@ -28313,6 +28338,9 @@
       <c r="B5" t="s">
         <v>1079</v>
       </c>
+      <c r="C5" s="10" t="s">
+        <v>1964</v>
+      </c>
     </row>
     <row r="6" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
@@ -28321,6 +28349,9 @@
       <c r="B6" t="s">
         <v>1079</v>
       </c>
+      <c r="C6" s="10" t="s">
+        <v>1965</v>
+      </c>
     </row>
     <row r="7" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -28364,6 +28395,9 @@
       <c r="B11" t="s">
         <v>1086</v>
       </c>
+      <c r="C11" s="10" t="s">
+        <v>1966</v>
+      </c>
     </row>
     <row r="12" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -28506,6 +28540,9 @@
       <c r="B28" t="s">
         <v>1090</v>
       </c>
+      <c r="C28" s="10" t="s">
+        <v>1967</v>
+      </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
@@ -28576,6 +28613,9 @@
       <c r="B36" t="s">
         <v>1094</v>
       </c>
+      <c r="C36" s="10" t="s">
+        <v>1968</v>
+      </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
@@ -28941,7 +28981,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="81" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>45</v>
       </c>
@@ -28949,7 +28989,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="82" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>1246</v>
       </c>
@@ -28957,7 +28997,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="83" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>550</v>
       </c>
@@ -28965,7 +29005,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="84" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>550</v>
       </c>
@@ -28973,7 +29013,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="85" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>429</v>
       </c>
@@ -28981,7 +29021,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="86" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>1647</v>
       </c>
@@ -28989,7 +29029,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="87" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>926</v>
       </c>
@@ -28997,7 +29037,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="88" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>364</v>
       </c>
@@ -29005,7 +29045,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="89" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>1412</v>
       </c>
@@ -29013,7 +29053,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="90" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>146</v>
       </c>
@@ -29021,15 +29061,18 @@
         <v>147</v>
       </c>
     </row>
-    <row r="91" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>1101</v>
       </c>
       <c r="B91" t="s">
         <v>1102</v>
       </c>
-    </row>
-    <row r="92" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C91" s="10" t="s">
+        <v>1969</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>1365</v>
       </c>
@@ -29037,7 +29080,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="93" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>435</v>
       </c>
@@ -29045,7 +29088,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="94" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>986</v>
       </c>
@@ -29053,7 +29096,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="95" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>674</v>
       </c>
@@ -29061,7 +29104,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="96" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>775</v>
       </c>
@@ -29069,7 +29112,7 @@
         <v>1649</v>
       </c>
     </row>
-    <row r="97" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>77</v>
       </c>
@@ -29077,7 +29120,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="98" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>153</v>
       </c>
@@ -29085,15 +29128,18 @@
         <v>154</v>
       </c>
     </row>
-    <row r="99" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>24</v>
       </c>
       <c r="B99" t="s">
         <v>1104</v>
       </c>
-    </row>
-    <row r="100" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C99" s="10" t="s">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>1107</v>
       </c>
@@ -29101,7 +29147,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="101" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>42</v>
       </c>
@@ -29109,7 +29155,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="102" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>1110</v>
       </c>
@@ -29117,7 +29163,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="103" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>21</v>
       </c>
@@ -29125,7 +29171,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="104" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>126</v>
       </c>
@@ -29133,7 +29179,7 @@
         <v>1719</v>
       </c>
     </row>
-    <row r="105" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>571</v>
       </c>
@@ -29141,7 +29187,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="106" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>387</v>
       </c>
@@ -29149,7 +29195,7 @@
         <v>433</v>
       </c>
     </row>
-    <row r="107" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>251</v>
       </c>
@@ -29157,7 +29203,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="108" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>723</v>
       </c>
@@ -29165,7 +29211,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="109" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>784</v>
       </c>
@@ -29173,7 +29219,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="110" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>525</v>
       </c>
@@ -29181,7 +29227,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="111" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>50</v>
       </c>
@@ -29189,7 +29235,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="112" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>1251</v>
       </c>
@@ -29235,6 +29281,9 @@
       </c>
       <c r="B117" t="s">
         <v>1116</v>
+      </c>
+      <c r="C117" s="10" t="s">
+        <v>1971</v>
       </c>
     </row>
     <row r="118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -34011,6 +34060,14 @@
     <hyperlink ref="C426" r:id="rId8" xr:uid="{3F258564-535C-4E31-84FD-F0B4224DEDFC}"/>
     <hyperlink ref="C663" r:id="rId9" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{033EC726-D865-426A-819E-A799648AB3C1}"/>
     <hyperlink ref="C34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C5" r:id="rId11" xr:uid="{34387F5A-28DA-460F-9EEA-35D9435E3CC5}"/>
+    <hyperlink ref="C6" r:id="rId12" xr:uid="{B0D11795-BECA-4256-998B-45F81F8016F7}"/>
+    <hyperlink ref="C11" r:id="rId13" xr:uid="{823B3996-D38D-452A-9D1F-6801E5167310}"/>
+    <hyperlink ref="C28" r:id="rId14" xr:uid="{F61139C7-9B31-4B65-98E9-F7320A2B1B1C}"/>
+    <hyperlink ref="C36" r:id="rId15" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg/960px-Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{746DAB4B-92FA-464D-84AF-E68B5D3887D9}"/>
+    <hyperlink ref="C91" r:id="rId16" xr:uid="{C55EAA05-E5BD-4A5E-BFBE-FEB1F1FA656A}"/>
+    <hyperlink ref="C99" r:id="rId17" xr:uid="{EAA77CB6-CB26-4399-B714-2CDD461F42E0}"/>
+    <hyperlink ref="C117" r:id="rId18" xr:uid="{04DC73B6-E166-4AC3-A238-23818A086FEE}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22CF1704-F7F7-41D3-9B7F-A7A657C4593F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F315D3B0-7DB2-4CF0-A220-581CDD87C79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7200" uniqueCount="1972">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7203" uniqueCount="1977">
   <si>
     <t>Prénom</t>
   </si>
@@ -6083,6 +6083,21 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/7c/Adolf_Ulrik_Wertm%C3%BCller%2C_Portrait_of_Jean-Jacques_Caffieri_%281784%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/6b/Antonio_Canova_Selfportrait_1792.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/1e/Nicolas_Coustou.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/fe/Guillaume_Coustou.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/0c/Guillaume_Coustou_the_Younger.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/Filippo_della_Valle_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -28263,7 +28278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L710"/>
+  <dimension ref="A1:L709"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" customWidth="1"/>
@@ -29352,6 +29367,9 @@
       <c r="B125" t="s">
         <v>1216</v>
       </c>
+      <c r="C125" s="10" t="s">
+        <v>1972</v>
+      </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
@@ -29758,31 +29776,40 @@
         <v>439</v>
       </c>
     </row>
-    <row r="177" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>340</v>
       </c>
       <c r="B177" t="s">
         <v>913</v>
       </c>
-    </row>
-    <row r="178" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C177" s="10" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>1127</v>
       </c>
       <c r="B178" t="s">
         <v>1128</v>
       </c>
-    </row>
-    <row r="179" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C178" s="10" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>1127</v>
       </c>
       <c r="B179" t="s">
         <v>1130</v>
       </c>
-    </row>
-    <row r="180" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C179" s="10" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>775</v>
       </c>
@@ -29790,7 +29817,7 @@
         <v>824</v>
       </c>
     </row>
-    <row r="181" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>442</v>
       </c>
@@ -29798,7 +29825,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="182" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>442</v>
       </c>
@@ -29806,7 +29833,7 @@
         <v>445</v>
       </c>
     </row>
-    <row r="183" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>1258</v>
       </c>
@@ -29814,7 +29841,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="184" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>168</v>
       </c>
@@ -29822,7 +29849,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="185" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>671</v>
       </c>
@@ -29830,7 +29857,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="186" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>35</v>
       </c>
@@ -29838,7 +29865,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="187" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>1654</v>
       </c>
@@ -29846,7 +29873,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="188" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1431</v>
       </c>
@@ -29854,7 +29881,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="189" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>381</v>
       </c>
@@ -29862,7 +29889,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="190" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>251</v>
       </c>
@@ -29870,7 +29897,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="191" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1284</v>
       </c>
@@ -29878,7 +29905,7 @@
         <v>1285</v>
       </c>
     </row>
-    <row r="192" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>366</v>
       </c>
@@ -30659,55 +30686,55 @@
     </row>
     <row r="289" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>854</v>
+        <v>811</v>
       </c>
       <c r="B289" t="s">
-        <v>855</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="290" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>811</v>
+        <v>1365</v>
       </c>
       <c r="B290" t="s">
-        <v>1451</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="291" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>1365</v>
+        <v>1659</v>
       </c>
       <c r="B291" t="s">
-        <v>1530</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="292" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>1659</v>
+        <v>324</v>
       </c>
       <c r="B292" t="s">
-        <v>1660</v>
+        <v>709</v>
       </c>
     </row>
     <row r="293" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>324</v>
+        <v>188</v>
       </c>
       <c r="B293" t="s">
-        <v>709</v>
+        <v>332</v>
       </c>
     </row>
     <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>188</v>
+        <v>333</v>
       </c>
       <c r="B294" t="s">
-        <v>332</v>
+        <v>202</v>
       </c>
     </row>
     <row r="295" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>333</v>
+        <v>201</v>
       </c>
       <c r="B295" t="s">
         <v>202</v>
@@ -30715,7 +30742,7 @@
     </row>
     <row r="296" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="B296" t="s">
         <v>202</v>
@@ -30723,184 +30750,184 @@
     </row>
     <row r="297" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>204</v>
+        <v>27</v>
       </c>
       <c r="B297" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
     </row>
     <row r="298" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>27</v>
+        <v>435</v>
       </c>
       <c r="B298" t="s">
-        <v>208</v>
+        <v>857</v>
       </c>
     </row>
     <row r="299" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>435</v>
+        <v>972</v>
       </c>
       <c r="B299" t="s">
-        <v>857</v>
+        <v>973</v>
       </c>
     </row>
     <row r="300" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>972</v>
+        <v>1454</v>
       </c>
       <c r="B300" t="s">
-        <v>973</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="301" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
-        <v>1454</v>
+        <v>1150</v>
       </c>
       <c r="B301" t="s">
-        <v>1455</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="302" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
-        <v>1150</v>
+        <v>1374</v>
       </c>
       <c r="B302" t="s">
-        <v>1151</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="303" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>1374</v>
+        <v>227</v>
       </c>
       <c r="B303" t="s">
-        <v>1375</v>
+        <v>228</v>
       </c>
     </row>
     <row r="304" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>227</v>
+        <v>1661</v>
       </c>
       <c r="B304" t="s">
-        <v>228</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>1661</v>
+        <v>282</v>
       </c>
       <c r="B305" t="s">
-        <v>1662</v>
+        <v>466</v>
       </c>
     </row>
     <row r="306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
-        <v>282</v>
+        <v>77</v>
       </c>
       <c r="B306" t="s">
-        <v>466</v>
+        <v>589</v>
       </c>
     </row>
     <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
-        <v>77</v>
+        <v>689</v>
       </c>
       <c r="B307" t="s">
-        <v>589</v>
+        <v>1215</v>
       </c>
     </row>
     <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
-        <v>689</v>
+        <v>282</v>
       </c>
       <c r="B308" t="s">
-        <v>1215</v>
+        <v>778</v>
       </c>
     </row>
     <row r="309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
-        <v>282</v>
+        <v>231</v>
       </c>
       <c r="B309" t="s">
-        <v>778</v>
+        <v>232</v>
       </c>
     </row>
     <row r="310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
-        <v>231</v>
+        <v>976</v>
       </c>
       <c r="B310" t="s">
-        <v>232</v>
+        <v>977</v>
+      </c>
+      <c r="C310" s="1" t="s">
+        <v>1930</v>
       </c>
     </row>
     <row r="311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="B311" t="s">
-        <v>977</v>
+        <v>980</v>
       </c>
       <c r="C311" s="1" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
     </row>
     <row r="312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>898</v>
+        <v>1564</v>
       </c>
       <c r="B312" t="s">
-        <v>980</v>
-      </c>
-      <c r="C312" s="1" t="s">
-        <v>1931</v>
+        <v>1565</v>
       </c>
     </row>
     <row r="313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>1564</v>
+        <v>470</v>
       </c>
       <c r="B313" t="s">
-        <v>1565</v>
+        <v>471</v>
       </c>
     </row>
     <row r="314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>470</v>
+        <v>188</v>
       </c>
       <c r="B314" t="s">
-        <v>471</v>
+        <v>983</v>
       </c>
     </row>
     <row r="315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="B315" t="s">
-        <v>983</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>195</v>
+        <v>224</v>
       </c>
       <c r="B316" t="s">
-        <v>1153</v>
+        <v>859</v>
       </c>
     </row>
     <row r="317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
-        <v>224</v>
+        <v>248</v>
       </c>
       <c r="B317" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
     </row>
     <row r="318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
-        <v>248</v>
+        <v>1154</v>
       </c>
       <c r="B318" t="s">
-        <v>860</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -30913,47 +30940,47 @@
     </row>
     <row r="320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>1154</v>
+        <v>711</v>
       </c>
       <c r="B320" t="s">
-        <v>1155</v>
+        <v>712</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>711</v>
+        <v>1784</v>
       </c>
       <c r="B321" t="s">
-        <v>712</v>
+        <v>1785</v>
       </c>
     </row>
     <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>1784</v>
+        <v>188</v>
       </c>
       <c r="B322" t="s">
-        <v>1785</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>188</v>
+        <v>512</v>
       </c>
       <c r="B323" t="s">
-        <v>1311</v>
+        <v>513</v>
       </c>
     </row>
     <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>512</v>
+        <v>1786</v>
       </c>
       <c r="B324" t="s">
-        <v>513</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="B325" t="s">
         <v>1787</v>
@@ -30961,474 +30988,474 @@
     </row>
     <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1788</v>
+        <v>1115</v>
       </c>
       <c r="B326" t="s">
-        <v>1787</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>1115</v>
+        <v>591</v>
       </c>
       <c r="B327" t="s">
-        <v>1313</v>
+        <v>592</v>
       </c>
     </row>
     <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B328" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
     </row>
     <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>593</v>
+        <v>1514</v>
       </c>
       <c r="B329" t="s">
-        <v>594</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>1514</v>
+        <v>896</v>
       </c>
       <c r="B330" t="s">
-        <v>1515</v>
+        <v>1789</v>
       </c>
     </row>
     <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>896</v>
+        <v>714</v>
       </c>
       <c r="B331" t="s">
-        <v>1789</v>
+        <v>715</v>
       </c>
     </row>
     <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>714</v>
+        <v>1207</v>
       </c>
       <c r="B332" t="s">
-        <v>715</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>1207</v>
+        <v>986</v>
       </c>
       <c r="B333" t="s">
-        <v>1524</v>
+        <v>987</v>
       </c>
     </row>
     <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>986</v>
+        <v>251</v>
       </c>
       <c r="B334" t="s">
-        <v>987</v>
+        <v>473</v>
       </c>
     </row>
     <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>251</v>
+        <v>1315</v>
       </c>
       <c r="B335" t="s">
-        <v>473</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>1315</v>
+        <v>864</v>
       </c>
       <c r="B336" t="s">
-        <v>1316</v>
+        <v>865</v>
       </c>
     </row>
     <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>864</v>
+        <v>780</v>
       </c>
       <c r="B337" t="s">
-        <v>865</v>
+        <v>781</v>
       </c>
     </row>
     <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>780</v>
+        <v>387</v>
       </c>
       <c r="B338" t="s">
-        <v>781</v>
+        <v>681</v>
       </c>
     </row>
     <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>387</v>
+        <v>442</v>
       </c>
       <c r="B339" t="s">
-        <v>681</v>
+        <v>1790</v>
       </c>
     </row>
     <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>442</v>
+        <v>1458</v>
       </c>
       <c r="B340" t="s">
-        <v>1790</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1458</v>
+        <v>1063</v>
       </c>
       <c r="B341" t="s">
-        <v>1459</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>1063</v>
+        <v>81</v>
       </c>
       <c r="B342" t="s">
-        <v>1156</v>
+        <v>234</v>
       </c>
     </row>
     <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>81</v>
+        <v>1318</v>
       </c>
       <c r="B343" t="s">
-        <v>234</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1318</v>
+        <v>1063</v>
       </c>
       <c r="B344" t="s">
-        <v>1319</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>1063</v>
+        <v>458</v>
       </c>
       <c r="B345" t="s">
-        <v>1664</v>
+        <v>459</v>
       </c>
     </row>
     <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
-        <v>458</v>
+        <v>595</v>
       </c>
       <c r="B346" t="s">
-        <v>459</v>
+        <v>596</v>
       </c>
     </row>
     <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B347" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="B348" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
     </row>
     <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>600</v>
+        <v>1635</v>
       </c>
       <c r="B349" t="s">
-        <v>601</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1635</v>
+        <v>1567</v>
       </c>
       <c r="B350" t="s">
-        <v>1636</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1567</v>
+        <v>1321</v>
       </c>
       <c r="B351" t="s">
-        <v>1568</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>1321</v>
+        <v>717</v>
       </c>
       <c r="B352" t="s">
-        <v>1322</v>
+        <v>718</v>
       </c>
     </row>
     <row r="353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A353" t="s">
-        <v>717</v>
-      </c>
       <c r="B353" t="s">
-        <v>718</v>
+        <v>1569</v>
+      </c>
+      <c r="C353" s="1" t="s">
+        <v>1932</v>
       </c>
     </row>
     <row r="354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A354" t="s">
+        <v>550</v>
+      </c>
       <c r="B354" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C354" s="1" t="s">
-        <v>1932</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="B355" t="s">
-        <v>1157</v>
+        <v>566</v>
       </c>
     </row>
     <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>565</v>
+        <v>603</v>
       </c>
       <c r="B356" t="s">
-        <v>566</v>
+        <v>604</v>
       </c>
     </row>
     <row r="357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>603</v>
+        <v>239</v>
       </c>
       <c r="B357" t="s">
-        <v>604</v>
+        <v>1159</v>
       </c>
     </row>
     <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>239</v>
+        <v>1795</v>
       </c>
       <c r="B358" t="s">
-        <v>1159</v>
+        <v>1796</v>
       </c>
     </row>
     <row r="359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>1795</v>
+        <v>639</v>
       </c>
       <c r="B359" t="s">
-        <v>1796</v>
+        <v>720</v>
       </c>
     </row>
     <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>639</v>
+        <v>1570</v>
       </c>
       <c r="B360" t="s">
-        <v>720</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1570</v>
+        <v>1160</v>
       </c>
       <c r="B361" t="s">
-        <v>1571</v>
+        <v>1161</v>
       </c>
     </row>
     <row r="362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>1160</v>
+        <v>989</v>
       </c>
       <c r="B362" t="s">
-        <v>1161</v>
+        <v>990</v>
       </c>
     </row>
     <row r="363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>989</v>
+        <v>652</v>
       </c>
       <c r="B363" t="s">
-        <v>990</v>
+        <v>826</v>
       </c>
     </row>
     <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>652</v>
+        <v>1572</v>
       </c>
       <c r="B364" t="s">
-        <v>826</v>
+        <v>1573</v>
       </c>
     </row>
     <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="B365" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
     </row>
     <row r="366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1575</v>
+        <v>1138</v>
       </c>
       <c r="B366" t="s">
-        <v>1576</v>
+        <v>1577</v>
       </c>
     </row>
     <row r="367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1138</v>
+        <v>1578</v>
       </c>
       <c r="B367" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1578</v>
+        <v>1535</v>
       </c>
       <c r="B368" t="s">
-        <v>1579</v>
+        <v>1536</v>
       </c>
     </row>
     <row r="369" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1535</v>
+        <v>1460</v>
       </c>
       <c r="B369" t="s">
-        <v>1536</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>1460</v>
+        <v>882</v>
       </c>
       <c r="B370" t="s">
-        <v>1461</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="371" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>882</v>
+        <v>1667</v>
       </c>
       <c r="B371" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>1667</v>
+        <v>344</v>
       </c>
       <c r="B372" t="s">
-        <v>1668</v>
+        <v>345</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>344</v>
+        <v>251</v>
       </c>
       <c r="B373" t="s">
-        <v>345</v>
+        <v>862</v>
       </c>
     </row>
     <row r="374" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>251</v>
+        <v>1580</v>
       </c>
       <c r="B374" t="s">
-        <v>862</v>
+        <v>1581</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>1580</v>
+        <v>992</v>
       </c>
       <c r="B375" t="s">
-        <v>1581</v>
+        <v>993</v>
       </c>
     </row>
     <row r="376" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>992</v>
+        <v>1669</v>
       </c>
       <c r="B376" t="s">
-        <v>993</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="377" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>1669</v>
+        <v>1462</v>
       </c>
       <c r="B377" t="s">
-        <v>1670</v>
+        <v>1463</v>
       </c>
     </row>
     <row r="378" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>1462</v>
+        <v>340</v>
       </c>
       <c r="B378" t="s">
-        <v>1463</v>
+        <v>996</v>
       </c>
     </row>
     <row r="379" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>340</v>
+        <v>57</v>
       </c>
       <c r="B379" t="s">
-        <v>996</v>
+        <v>605</v>
       </c>
     </row>
     <row r="380" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>57</v>
+        <v>340</v>
       </c>
       <c r="B380" t="s">
-        <v>605</v>
+        <v>950</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>340</v>
+        <v>188</v>
       </c>
       <c r="B381" t="s">
-        <v>950</v>
+        <v>348</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>188</v>
+        <v>890</v>
       </c>
       <c r="B382" t="s">
-        <v>348</v>
+        <v>997</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>890</v>
+        <v>1582</v>
       </c>
       <c r="B383" t="s">
-        <v>997</v>
+        <v>1583</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>1582</v>
+        <v>550</v>
       </c>
       <c r="B384" t="s">
-        <v>1583</v>
+        <v>866</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31436,60 +31463,60 @@
         <v>550</v>
       </c>
       <c r="B385" t="s">
-        <v>866</v>
+        <v>868</v>
       </c>
     </row>
     <row r="386" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>550</v>
+        <v>1671</v>
       </c>
       <c r="B386" t="s">
-        <v>868</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="387" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>1671</v>
+        <v>1464</v>
       </c>
       <c r="B387" t="s">
-        <v>1672</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="388" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>1464</v>
+        <v>251</v>
       </c>
       <c r="B388" t="s">
-        <v>1465</v>
+        <v>608</v>
       </c>
     </row>
     <row r="389" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>251</v>
+        <v>115</v>
       </c>
       <c r="B389" t="s">
-        <v>608</v>
+        <v>734</v>
       </c>
     </row>
     <row r="390" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>115</v>
+        <v>898</v>
       </c>
       <c r="B390" t="s">
-        <v>734</v>
+        <v>1163</v>
       </c>
     </row>
     <row r="391" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>898</v>
+        <v>609</v>
       </c>
       <c r="B391" t="s">
-        <v>1163</v>
+        <v>610</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B392" t="s">
         <v>610</v>
@@ -31497,79 +31524,79 @@
     </row>
     <row r="393" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B393" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
     </row>
     <row r="394" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>613</v>
+        <v>1000</v>
       </c>
       <c r="B394" t="s">
-        <v>614</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="395" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>1000</v>
+        <v>1466</v>
       </c>
       <c r="B395" t="s">
-        <v>1001</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>1466</v>
+        <v>442</v>
       </c>
       <c r="B396" t="s">
-        <v>1467</v>
+        <v>514</v>
       </c>
     </row>
     <row r="397" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>442</v>
+        <v>736</v>
       </c>
       <c r="B397" t="s">
-        <v>514</v>
+        <v>737</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>736</v>
+        <v>77</v>
       </c>
       <c r="B398" t="s">
-        <v>737</v>
+        <v>104</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>77</v>
+        <v>282</v>
       </c>
       <c r="B399" t="s">
-        <v>104</v>
+        <v>738</v>
       </c>
     </row>
     <row r="400" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>282</v>
+        <v>1003</v>
       </c>
       <c r="B400" t="s">
-        <v>738</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="401" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>1003</v>
+        <v>236</v>
       </c>
       <c r="B401" t="s">
-        <v>1004</v>
+        <v>237</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B402" t="s">
         <v>237</v>
@@ -31577,18 +31604,18 @@
     </row>
     <row r="403" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B403" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>242</v>
+        <v>24</v>
       </c>
       <c r="B404" t="s">
-        <v>243</v>
+        <v>350</v>
       </c>
     </row>
     <row r="405" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31596,28 +31623,28 @@
         <v>24</v>
       </c>
       <c r="B405" t="s">
-        <v>350</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="406" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>24</v>
+        <v>1055</v>
       </c>
       <c r="B406" t="s">
-        <v>1006</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>1055</v>
+        <v>61</v>
       </c>
       <c r="B407" t="s">
-        <v>1056</v>
+        <v>62</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="B408" t="s">
         <v>62</v>
@@ -31625,173 +31652,173 @@
     </row>
     <row r="409" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>24</v>
+        <v>1162</v>
       </c>
       <c r="B409" t="s">
-        <v>62</v>
+        <v>701</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>1162</v>
+        <v>73</v>
       </c>
       <c r="B410" t="s">
-        <v>701</v>
+        <v>475</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>73</v>
+        <v>372</v>
       </c>
       <c r="B411" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>372</v>
+        <v>1586</v>
       </c>
       <c r="B412" t="s">
-        <v>477</v>
+        <v>1587</v>
       </c>
     </row>
     <row r="413" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>1586</v>
+        <v>204</v>
       </c>
       <c r="B413" t="s">
-        <v>1587</v>
+        <v>869</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>204</v>
+        <v>740</v>
       </c>
       <c r="B414" t="s">
-        <v>869</v>
+        <v>741</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>740</v>
+        <v>613</v>
       </c>
       <c r="B415" t="s">
-        <v>741</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>613</v>
+        <v>310</v>
       </c>
       <c r="B416" t="s">
-        <v>1008</v>
+        <v>311</v>
       </c>
     </row>
     <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>310</v>
+        <v>1673</v>
       </c>
       <c r="B417" t="s">
-        <v>311</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>1673</v>
+        <v>458</v>
       </c>
       <c r="B418" t="s">
-        <v>1674</v>
+        <v>1164</v>
       </c>
     </row>
     <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
-        <v>458</v>
+        <v>73</v>
       </c>
       <c r="B419" t="s">
-        <v>1164</v>
+        <v>112</v>
       </c>
     </row>
     <row r="420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A420" t="s">
-        <v>73</v>
-      </c>
       <c r="B420" t="s">
-        <v>112</v>
+        <v>64</v>
       </c>
     </row>
     <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A421" t="s">
+        <v>1589</v>
+      </c>
       <c r="B421" t="s">
-        <v>64</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>1589</v>
+        <v>1324</v>
       </c>
       <c r="B422" t="s">
-        <v>1590</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>1324</v>
+        <v>138</v>
       </c>
       <c r="B423" t="s">
-        <v>1325</v>
+        <v>1591</v>
+      </c>
+      <c r="C423" s="2" t="s">
+        <v>1933</v>
       </c>
     </row>
     <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="B424" t="s">
-        <v>1591</v>
-      </c>
-      <c r="C424" s="2" t="s">
-        <v>1933</v>
+        <v>245</v>
       </c>
     </row>
     <row r="425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>42</v>
+        <v>1593</v>
       </c>
       <c r="B425" t="s">
-        <v>245</v>
+        <v>1594</v>
+      </c>
+      <c r="C425" s="2" t="s">
+        <v>1934</v>
       </c>
     </row>
     <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>1593</v>
+        <v>871</v>
       </c>
       <c r="B426" t="s">
-        <v>1594</v>
-      </c>
-      <c r="C426" s="2" t="s">
-        <v>1934</v>
+        <v>872</v>
       </c>
     </row>
     <row r="427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>871</v>
+        <v>248</v>
       </c>
       <c r="B427" t="s">
-        <v>872</v>
+        <v>249</v>
       </c>
     </row>
     <row r="428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>248</v>
+        <v>1240</v>
       </c>
       <c r="B428" t="s">
-        <v>249</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>1240</v>
+        <v>828</v>
       </c>
       <c r="B429" t="s">
-        <v>1595</v>
+        <v>829</v>
       </c>
     </row>
     <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -31799,188 +31826,188 @@
         <v>828</v>
       </c>
       <c r="B430" t="s">
-        <v>829</v>
+        <v>873</v>
       </c>
     </row>
     <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>828</v>
+        <v>565</v>
       </c>
       <c r="B431" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
     </row>
     <row r="432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>565</v>
+        <v>66</v>
       </c>
       <c r="B432" t="s">
-        <v>874</v>
+        <v>67</v>
       </c>
     </row>
     <row r="433" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>66</v>
+        <v>138</v>
       </c>
       <c r="B433" t="s">
-        <v>67</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>138</v>
+        <v>481</v>
       </c>
       <c r="B434" t="s">
-        <v>1596</v>
+        <v>482</v>
       </c>
     </row>
     <row r="435" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>481</v>
+        <v>212</v>
       </c>
       <c r="B435" t="s">
-        <v>482</v>
+        <v>352</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>212</v>
+        <v>615</v>
       </c>
       <c r="B436" t="s">
-        <v>352</v>
+        <v>616</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>615</v>
+        <v>1009</v>
       </c>
       <c r="B437" t="s">
-        <v>616</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>1009</v>
+        <v>251</v>
       </c>
       <c r="B438" t="s">
-        <v>1010</v>
+        <v>252</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>251</v>
+        <v>70</v>
       </c>
       <c r="B439" t="s">
-        <v>252</v>
+        <v>71</v>
       </c>
     </row>
     <row r="440" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>70</v>
+        <v>831</v>
       </c>
       <c r="B440" t="s">
-        <v>71</v>
+        <v>832</v>
       </c>
     </row>
     <row r="441" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>831</v>
+        <v>39</v>
       </c>
       <c r="B441" t="s">
-        <v>832</v>
+        <v>40</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>39</v>
+        <v>1012</v>
       </c>
       <c r="B442" t="s">
-        <v>40</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="443" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>1012</v>
+        <v>1469</v>
       </c>
       <c r="B443" t="s">
-        <v>1013</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>1469</v>
+        <v>525</v>
       </c>
       <c r="B444" t="s">
-        <v>1470</v>
+        <v>649</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>525</v>
+        <v>1165</v>
       </c>
       <c r="B445" t="s">
-        <v>649</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>1165</v>
+        <v>178</v>
       </c>
       <c r="B446" t="s">
-        <v>1166</v>
+        <v>179</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>178</v>
+        <v>742</v>
       </c>
       <c r="B447" t="s">
-        <v>179</v>
+        <v>743</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>742</v>
+        <v>484</v>
       </c>
       <c r="B448" t="s">
-        <v>743</v>
+        <v>485</v>
       </c>
     </row>
     <row r="449" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>484</v>
+        <v>1471</v>
       </c>
       <c r="B449" t="s">
-        <v>485</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="450" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>1471</v>
+        <v>699</v>
       </c>
       <c r="B450" t="s">
-        <v>1472</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="451" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>699</v>
+        <v>1328</v>
       </c>
       <c r="B451" t="s">
-        <v>1167</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="452" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>1328</v>
+        <v>1473</v>
       </c>
       <c r="B452" t="s">
-        <v>1329</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="453" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>1473</v>
+        <v>1331</v>
       </c>
       <c r="B453" t="s">
         <v>1332</v>
@@ -31988,127 +32015,127 @@
     </row>
     <row r="454" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>1331</v>
+        <v>188</v>
       </c>
       <c r="B454" t="s">
-        <v>1332</v>
+        <v>875</v>
       </c>
     </row>
     <row r="455" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>188</v>
+        <v>27</v>
       </c>
       <c r="B455" t="s">
-        <v>875</v>
+        <v>28</v>
       </c>
     </row>
     <row r="456" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>27</v>
+        <v>1598</v>
       </c>
       <c r="B456" t="s">
-        <v>28</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="457" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="B457" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="458" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>1601</v>
+        <v>1170</v>
       </c>
       <c r="B458" t="s">
-        <v>1602</v>
+        <v>1171</v>
       </c>
     </row>
     <row r="459" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="B459" t="s">
-        <v>1171</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="460" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>1172</v>
+        <v>73</v>
       </c>
       <c r="B460" t="s">
-        <v>1173</v>
+        <v>74</v>
       </c>
     </row>
     <row r="461" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>73</v>
+        <v>1605</v>
       </c>
       <c r="B461" t="s">
-        <v>74</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="462" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>1605</v>
+        <v>77</v>
       </c>
       <c r="B462" t="s">
-        <v>1606</v>
+        <v>618</v>
       </c>
     </row>
     <row r="463" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>77</v>
+        <v>699</v>
       </c>
       <c r="B463" t="s">
-        <v>618</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="464" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>699</v>
+        <v>1832</v>
       </c>
       <c r="B464" t="s">
-        <v>1333</v>
+        <v>1833</v>
       </c>
     </row>
     <row r="465" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>1832</v>
+        <v>876</v>
       </c>
       <c r="B465" t="s">
-        <v>1833</v>
+        <v>877</v>
       </c>
     </row>
     <row r="466" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>876</v>
+        <v>687</v>
       </c>
       <c r="B466" t="s">
-        <v>877</v>
+        <v>834</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>687</v>
+        <v>1009</v>
       </c>
       <c r="B467" t="s">
-        <v>834</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="468" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>1009</v>
+        <v>1258</v>
       </c>
       <c r="B468" t="s">
-        <v>1834</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="469" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1258</v>
+        <v>1474</v>
       </c>
       <c r="B469" t="s">
         <v>1334</v>
@@ -32116,18 +32143,18 @@
     </row>
     <row r="470" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1474</v>
+        <v>1335</v>
       </c>
       <c r="B470" t="s">
-        <v>1334</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="471" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>1335</v>
+        <v>458</v>
       </c>
       <c r="B471" t="s">
-        <v>1336</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32135,300 +32162,300 @@
         <v>458</v>
       </c>
       <c r="B472" t="s">
-        <v>1174</v>
+        <v>486</v>
       </c>
     </row>
     <row r="473" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>458</v>
+        <v>1338</v>
       </c>
       <c r="B473" t="s">
-        <v>486</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="474" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>1338</v>
+        <v>1608</v>
       </c>
       <c r="B474" t="s">
-        <v>1339</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="475" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>1608</v>
+        <v>1675</v>
       </c>
       <c r="B475" t="s">
-        <v>1609</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="476" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>1675</v>
+        <v>1526</v>
       </c>
       <c r="B476" t="s">
-        <v>1676</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="477" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>1526</v>
+        <v>745</v>
       </c>
       <c r="B477" t="s">
-        <v>1527</v>
+        <v>746</v>
       </c>
     </row>
     <row r="478" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>745</v>
+        <v>1475</v>
       </c>
       <c r="B478" t="s">
-        <v>746</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="479" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>1475</v>
+        <v>525</v>
       </c>
       <c r="B479" t="s">
-        <v>1476</v>
+        <v>619</v>
       </c>
     </row>
     <row r="480" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>525</v>
+        <v>1176</v>
       </c>
       <c r="B480" t="s">
-        <v>619</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="481" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>1176</v>
+        <v>726</v>
       </c>
       <c r="B481" t="s">
-        <v>1177</v>
+        <v>727</v>
       </c>
     </row>
     <row r="482" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>726</v>
+        <v>1138</v>
       </c>
       <c r="B482" t="s">
-        <v>727</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="483" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1138</v>
+        <v>1015</v>
       </c>
       <c r="B483" t="s">
-        <v>1610</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="484" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1015</v>
+        <v>1018</v>
       </c>
       <c r="B484" t="s">
-        <v>1016</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="485" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>1018</v>
+        <v>319</v>
       </c>
       <c r="B485" t="s">
-        <v>1019</v>
+        <v>489</v>
       </c>
     </row>
     <row r="486" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>319</v>
+        <v>1611</v>
       </c>
       <c r="B486" t="s">
-        <v>489</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="487" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>1611</v>
+        <v>334</v>
       </c>
       <c r="B487" t="s">
-        <v>1612</v>
+        <v>335</v>
       </c>
     </row>
     <row r="488" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>334</v>
+        <v>956</v>
       </c>
       <c r="B488" t="s">
-        <v>335</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="489" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>956</v>
+        <v>878</v>
       </c>
       <c r="B489" t="s">
-        <v>1178</v>
+        <v>879</v>
       </c>
     </row>
     <row r="490" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>878</v>
+        <v>142</v>
       </c>
       <c r="B490" t="s">
-        <v>879</v>
+        <v>621</v>
       </c>
     </row>
     <row r="491" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>142</v>
+        <v>571</v>
       </c>
       <c r="B491" t="s">
-        <v>621</v>
+        <v>782</v>
       </c>
     </row>
     <row r="492" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>571</v>
+        <v>898</v>
       </c>
       <c r="B492" t="s">
-        <v>782</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="493" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>898</v>
+        <v>253</v>
       </c>
       <c r="B493" t="s">
-        <v>1020</v>
+        <v>254</v>
       </c>
     </row>
     <row r="494" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>253</v>
+        <v>1179</v>
       </c>
       <c r="B494" t="s">
-        <v>254</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="495" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>1179</v>
+        <v>565</v>
       </c>
       <c r="B495" t="s">
-        <v>1180</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="496" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>565</v>
+        <v>115</v>
       </c>
       <c r="B496" t="s">
-        <v>1839</v>
+        <v>116</v>
       </c>
     </row>
     <row r="497" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>115</v>
+        <v>239</v>
       </c>
       <c r="B497" t="s">
-        <v>116</v>
+        <v>880</v>
       </c>
     </row>
     <row r="498" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>239</v>
+        <v>1431</v>
       </c>
       <c r="B498" t="s">
-        <v>880</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="499" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>1431</v>
+        <v>425</v>
       </c>
       <c r="B499" t="s">
-        <v>1613</v>
+        <v>491</v>
       </c>
     </row>
     <row r="500" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>425</v>
+        <v>1022</v>
       </c>
       <c r="B500" t="s">
-        <v>491</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="501" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>1022</v>
+        <v>77</v>
       </c>
       <c r="B501" t="s">
-        <v>1023</v>
+        <v>120</v>
       </c>
     </row>
     <row r="502" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>77</v>
+        <v>1181</v>
       </c>
       <c r="B502" t="s">
-        <v>120</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="503" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1181</v>
+        <v>1148</v>
       </c>
       <c r="B503" t="s">
-        <v>1182</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="504" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>1148</v>
+        <v>898</v>
       </c>
       <c r="B504" t="s">
-        <v>1478</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="505" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>898</v>
+        <v>24</v>
       </c>
       <c r="B505" t="s">
-        <v>1025</v>
+        <v>258</v>
       </c>
     </row>
     <row r="506" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>24</v>
+        <v>882</v>
       </c>
       <c r="B506" t="s">
-        <v>258</v>
+        <v>883</v>
       </c>
     </row>
     <row r="507" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>882</v>
+        <v>1420</v>
       </c>
       <c r="B507" t="s">
-        <v>883</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="508" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>1420</v>
+        <v>212</v>
       </c>
       <c r="B508" t="s">
-        <v>1615</v>
+        <v>213</v>
       </c>
     </row>
     <row r="509" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>212</v>
+        <v>73</v>
       </c>
       <c r="B509" t="s">
         <v>213</v>
@@ -32436,47 +32463,47 @@
     </row>
     <row r="510" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>73</v>
+        <v>898</v>
       </c>
       <c r="B510" t="s">
-        <v>213</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="511" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="B511" t="s">
-        <v>1183</v>
+        <v>623</v>
       </c>
     </row>
     <row r="512" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>622</v>
+        <v>453</v>
       </c>
       <c r="B512" t="s">
-        <v>623</v>
+        <v>454</v>
       </c>
     </row>
     <row r="513" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>453</v>
+        <v>687</v>
       </c>
       <c r="B513" t="s">
-        <v>454</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="514" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>687</v>
+        <v>42</v>
       </c>
       <c r="B514" t="s">
-        <v>1480</v>
+        <v>122</v>
       </c>
     </row>
     <row r="515" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="B515" t="s">
         <v>122</v>
@@ -32484,7 +32511,7 @@
     </row>
     <row r="516" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="B516" t="s">
         <v>122</v>
@@ -32492,18 +32519,18 @@
     </row>
     <row r="517" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>125</v>
+        <v>1341</v>
       </c>
       <c r="B517" t="s">
-        <v>122</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="518" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>1341</v>
+        <v>262</v>
       </c>
       <c r="B518" t="s">
-        <v>1342</v>
+        <v>318</v>
       </c>
     </row>
     <row r="519" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32511,36 +32538,36 @@
         <v>262</v>
       </c>
       <c r="B519" t="s">
-        <v>318</v>
+        <v>263</v>
       </c>
     </row>
     <row r="520" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>262</v>
+        <v>435</v>
       </c>
       <c r="B520" t="s">
-        <v>263</v>
+        <v>1677</v>
       </c>
     </row>
     <row r="521" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>435</v>
+        <v>319</v>
       </c>
       <c r="B521" t="s">
-        <v>1677</v>
+        <v>493</v>
       </c>
     </row>
     <row r="522" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>319</v>
+        <v>458</v>
       </c>
       <c r="B522" t="s">
-        <v>493</v>
+        <v>574</v>
       </c>
     </row>
     <row r="523" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>458</v>
+        <v>576</v>
       </c>
       <c r="B523" t="s">
         <v>574</v>
@@ -32548,98 +32575,98 @@
     </row>
     <row r="524" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>576</v>
+        <v>1850</v>
       </c>
       <c r="B524" t="s">
-        <v>574</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="525" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>1850</v>
+        <v>340</v>
       </c>
       <c r="B525" t="s">
-        <v>1851</v>
+        <v>748</v>
       </c>
     </row>
     <row r="526" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>340</v>
+        <v>1482</v>
       </c>
       <c r="B526" t="s">
-        <v>748</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="527" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>1482</v>
+        <v>77</v>
       </c>
       <c r="B527" t="s">
-        <v>1483</v>
+        <v>384</v>
       </c>
     </row>
     <row r="528" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>77</v>
+        <v>1298</v>
       </c>
       <c r="B528" t="s">
-        <v>384</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="529" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1298</v>
+        <v>1678</v>
       </c>
       <c r="B529" t="s">
-        <v>1485</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="530" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1678</v>
+        <v>1404</v>
       </c>
       <c r="B530" t="s">
-        <v>1679</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="531" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>1404</v>
+        <v>750</v>
       </c>
       <c r="B531" t="s">
-        <v>1486</v>
+        <v>751</v>
       </c>
     </row>
     <row r="532" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>750</v>
+        <v>195</v>
       </c>
       <c r="B532" t="s">
-        <v>751</v>
+        <v>625</v>
       </c>
     </row>
     <row r="533" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="B533" t="s">
-        <v>625</v>
+        <v>495</v>
       </c>
     </row>
     <row r="534" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="B534" t="s">
-        <v>495</v>
+        <v>78</v>
       </c>
     </row>
     <row r="535" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>77</v>
+        <v>550</v>
       </c>
       <c r="B535" t="s">
-        <v>78</v>
+        <v>884</v>
       </c>
     </row>
     <row r="536" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32647,31 +32674,31 @@
         <v>550</v>
       </c>
       <c r="B536" t="s">
-        <v>884</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="537" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>550</v>
+        <v>265</v>
       </c>
       <c r="B537" t="s">
-        <v>1343</v>
+        <v>266</v>
       </c>
     </row>
     <row r="538" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>265</v>
+        <v>188</v>
       </c>
       <c r="B538" t="s">
-        <v>266</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="539" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>188</v>
+        <v>885</v>
       </c>
       <c r="B539" t="s">
-        <v>1184</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="540" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32679,180 +32706,180 @@
         <v>885</v>
       </c>
       <c r="B540" t="s">
-        <v>1185</v>
+        <v>886</v>
       </c>
     </row>
     <row r="541" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>885</v>
+        <v>319</v>
       </c>
       <c r="B541" t="s">
-        <v>886</v>
+        <v>320</v>
       </c>
     </row>
     <row r="542" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>319</v>
+        <v>967</v>
       </c>
       <c r="B542" t="s">
-        <v>320</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="543" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>967</v>
+        <v>262</v>
       </c>
       <c r="B543" t="s">
-        <v>1027</v>
+        <v>888</v>
       </c>
     </row>
     <row r="544" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>262</v>
+        <v>1031</v>
       </c>
       <c r="B544" t="s">
-        <v>888</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="545" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1031</v>
+        <v>1487</v>
       </c>
       <c r="B545" t="s">
-        <v>1032</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="546" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>1487</v>
+        <v>470</v>
       </c>
       <c r="B546" t="s">
-        <v>1488</v>
+        <v>889</v>
       </c>
     </row>
     <row r="547" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>470</v>
+        <v>1344</v>
       </c>
       <c r="B547" t="s">
-        <v>889</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="548" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>1344</v>
+        <v>890</v>
       </c>
       <c r="B548" t="s">
-        <v>1345</v>
+        <v>891</v>
       </c>
     </row>
     <row r="549" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>890</v>
+        <v>251</v>
       </c>
       <c r="B549" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
     </row>
     <row r="550" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>251</v>
+        <v>1464</v>
       </c>
       <c r="B550" t="s">
-        <v>892</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="551" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>1464</v>
+        <v>212</v>
       </c>
       <c r="B551" t="s">
-        <v>1490</v>
+        <v>753</v>
       </c>
     </row>
     <row r="552" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>212</v>
+        <v>1346</v>
       </c>
       <c r="B552" t="s">
-        <v>753</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="553" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1346</v>
+        <v>1349</v>
       </c>
       <c r="B553" t="s">
-        <v>1347</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="554" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1349</v>
+        <v>1035</v>
       </c>
       <c r="B554" t="s">
-        <v>1350</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="555" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>1035</v>
+        <v>687</v>
       </c>
       <c r="B555" t="s">
-        <v>1036</v>
+        <v>688</v>
       </c>
     </row>
     <row r="556" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>687</v>
+        <v>627</v>
       </c>
       <c r="B556" t="s">
-        <v>688</v>
+        <v>628</v>
       </c>
     </row>
     <row r="557" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="B557" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>630</v>
+        <v>1492</v>
       </c>
       <c r="B558" t="s">
-        <v>631</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="559" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>1492</v>
+        <v>908</v>
       </c>
       <c r="B559" t="s">
-        <v>1493</v>
+        <v>909</v>
       </c>
     </row>
     <row r="560" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>908</v>
+        <v>784</v>
       </c>
       <c r="B560" t="s">
-        <v>909</v>
+        <v>785</v>
       </c>
     </row>
     <row r="561" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>784</v>
+        <v>42</v>
       </c>
       <c r="B561" t="s">
-        <v>785</v>
+        <v>322</v>
       </c>
     </row>
     <row r="562" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>42</v>
+        <v>324</v>
       </c>
       <c r="B562" t="s">
         <v>322</v>
@@ -32860,71 +32887,71 @@
     </row>
     <row r="563" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>324</v>
+        <v>585</v>
       </c>
       <c r="B563" t="s">
-        <v>322</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="564" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>585</v>
+        <v>181</v>
       </c>
       <c r="B564" t="s">
-        <v>1039</v>
+        <v>182</v>
       </c>
     </row>
     <row r="565" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>181</v>
+        <v>319</v>
       </c>
       <c r="B565" t="s">
-        <v>182</v>
+        <v>497</v>
       </c>
     </row>
     <row r="566" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>319</v>
+        <v>1404</v>
       </c>
       <c r="B566" t="s">
-        <v>497</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="567" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>1404</v>
+        <v>340</v>
       </c>
       <c r="B567" t="s">
-        <v>1532</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="568" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>340</v>
+        <v>1494</v>
       </c>
       <c r="B568" t="s">
-        <v>1616</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="569" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1494</v>
+        <v>1041</v>
       </c>
       <c r="B569" t="s">
-        <v>1495</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="570" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>1041</v>
+        <v>893</v>
       </c>
       <c r="B570" t="s">
-        <v>1042</v>
+        <v>894</v>
       </c>
     </row>
     <row r="571" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>893</v>
+        <v>831</v>
       </c>
       <c r="B571" t="s">
         <v>894</v>
@@ -32932,47 +32959,47 @@
     </row>
     <row r="572" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>831</v>
+        <v>500</v>
       </c>
       <c r="B572" t="s">
-        <v>894</v>
+        <v>501</v>
       </c>
     </row>
     <row r="573" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>500</v>
+        <v>755</v>
       </c>
       <c r="B573" t="s">
-        <v>501</v>
+        <v>756</v>
       </c>
     </row>
     <row r="574" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>755</v>
+        <v>1044</v>
       </c>
       <c r="B574" t="s">
-        <v>756</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="575" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>1044</v>
+        <v>268</v>
       </c>
       <c r="B575" t="s">
-        <v>1045</v>
+        <v>269</v>
       </c>
     </row>
     <row r="576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B576" t="s">
-        <v>269</v>
+        <v>355</v>
       </c>
     </row>
     <row r="577" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>262</v>
+        <v>35</v>
       </c>
       <c r="B577" t="s">
         <v>355</v>
@@ -32980,39 +33007,39 @@
     </row>
     <row r="578" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>35</v>
+        <v>1352</v>
       </c>
       <c r="B578" t="s">
-        <v>355</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="579" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>1352</v>
+        <v>381</v>
       </c>
       <c r="B579" t="s">
-        <v>1353</v>
+        <v>568</v>
       </c>
     </row>
     <row r="580" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>381</v>
+        <v>1186</v>
       </c>
       <c r="B580" t="s">
-        <v>568</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="581" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>1186</v>
+        <v>138</v>
       </c>
       <c r="B581" t="s">
-        <v>1187</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="582" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>138</v>
+        <v>1269</v>
       </c>
       <c r="B582" t="s">
         <v>1354</v>
@@ -33020,127 +33047,127 @@
     </row>
     <row r="583" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1269</v>
+        <v>1618</v>
       </c>
       <c r="B583" t="s">
-        <v>1354</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="584" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>1618</v>
+        <v>759</v>
       </c>
       <c r="B584" t="s">
-        <v>1619</v>
+        <v>760</v>
       </c>
     </row>
     <row r="585" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>759</v>
+        <v>435</v>
       </c>
       <c r="B585" t="s">
-        <v>760</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="586" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>435</v>
+        <v>717</v>
       </c>
       <c r="B586" t="s">
-        <v>1496</v>
+        <v>787</v>
       </c>
     </row>
     <row r="587" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>717</v>
+        <v>871</v>
       </c>
       <c r="B587" t="s">
-        <v>787</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="588" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>871</v>
+        <v>789</v>
       </c>
       <c r="B588" t="s">
-        <v>1188</v>
+        <v>790</v>
       </c>
     </row>
     <row r="589" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>789</v>
+        <v>1189</v>
       </c>
       <c r="B589" t="s">
-        <v>790</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="590" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1189</v>
+        <v>1378</v>
       </c>
       <c r="B590" t="s">
-        <v>1190</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="591" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" t="s">
-        <v>1378</v>
+        <v>1533</v>
       </c>
       <c r="B591" t="s">
-        <v>1379</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="592" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" t="s">
-        <v>1533</v>
+        <v>580</v>
       </c>
       <c r="B592" t="s">
-        <v>1534</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="593" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>580</v>
+        <v>689</v>
       </c>
       <c r="B593" t="s">
-        <v>1191</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="594" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" t="s">
-        <v>689</v>
+        <v>522</v>
       </c>
       <c r="B594" t="s">
-        <v>1193</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="595" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" t="s">
-        <v>522</v>
+        <v>188</v>
       </c>
       <c r="B595" t="s">
-        <v>1875</v>
+        <v>560</v>
       </c>
     </row>
     <row r="596" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" t="s">
-        <v>188</v>
+        <v>401</v>
       </c>
       <c r="B596" t="s">
-        <v>560</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="597" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" t="s">
-        <v>401</v>
+        <v>42</v>
       </c>
       <c r="B597" t="s">
-        <v>1194</v>
+        <v>633</v>
       </c>
     </row>
     <row r="598" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" t="s">
-        <v>42</v>
+        <v>319</v>
       </c>
       <c r="B598" t="s">
         <v>633</v>
@@ -33148,151 +33175,151 @@
     </row>
     <row r="599" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" t="s">
-        <v>319</v>
+        <v>503</v>
       </c>
       <c r="B599" t="s">
-        <v>633</v>
+        <v>504</v>
       </c>
     </row>
     <row r="600" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" t="s">
-        <v>503</v>
+        <v>1356</v>
       </c>
       <c r="B600" t="s">
-        <v>504</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="601" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" t="s">
-        <v>1356</v>
+        <v>580</v>
       </c>
       <c r="B601" t="s">
-        <v>1357</v>
+        <v>895</v>
       </c>
     </row>
     <row r="602" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>580</v>
+        <v>42</v>
       </c>
       <c r="B602" t="s">
-        <v>895</v>
+        <v>456</v>
       </c>
     </row>
     <row r="603" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" t="s">
-        <v>42</v>
+        <v>1217</v>
       </c>
       <c r="B603" t="s">
-        <v>456</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="604" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" t="s">
-        <v>1217</v>
+        <v>1195</v>
       </c>
       <c r="B604" t="s">
-        <v>1218</v>
+        <v>1196</v>
       </c>
     </row>
     <row r="605" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
-        <v>1195</v>
+        <v>1620</v>
       </c>
       <c r="B605" t="s">
-        <v>1196</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="606" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" t="s">
-        <v>1620</v>
+        <v>1197</v>
       </c>
       <c r="B606" t="s">
-        <v>1621</v>
+        <v>1198</v>
       </c>
     </row>
     <row r="607" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
-        <v>1197</v>
+        <v>917</v>
       </c>
       <c r="B607" t="s">
-        <v>1198</v>
+        <v>918</v>
       </c>
     </row>
     <row r="608" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" t="s">
-        <v>917</v>
+        <v>81</v>
       </c>
       <c r="B608" t="s">
-        <v>918</v>
+        <v>82</v>
       </c>
     </row>
     <row r="609" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" t="s">
-        <v>81</v>
+        <v>1138</v>
       </c>
       <c r="B609" t="s">
-        <v>82</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="610" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" t="s">
-        <v>1138</v>
+        <v>313</v>
       </c>
       <c r="B610" t="s">
-        <v>1359</v>
+        <v>314</v>
       </c>
     </row>
     <row r="611" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" t="s">
-        <v>313</v>
+        <v>684</v>
       </c>
       <c r="B611" t="s">
-        <v>314</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="612" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" t="s">
-        <v>684</v>
+        <v>1884</v>
       </c>
       <c r="B612" t="s">
-        <v>1361</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="613" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
-        <v>1884</v>
+        <v>1498</v>
       </c>
       <c r="B613" t="s">
-        <v>1885</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="614" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
-        <v>1498</v>
+        <v>1138</v>
       </c>
       <c r="B614" t="s">
-        <v>1499</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="615" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" t="s">
-        <v>1138</v>
+        <v>324</v>
       </c>
       <c r="B615" t="s">
-        <v>1363</v>
+        <v>385</v>
       </c>
     </row>
     <row r="616" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" t="s">
-        <v>324</v>
+        <v>569</v>
       </c>
       <c r="B616" t="s">
-        <v>385</v>
+        <v>317</v>
       </c>
     </row>
     <row r="617" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" t="s">
-        <v>569</v>
+        <v>316</v>
       </c>
       <c r="B617" t="s">
         <v>317</v>
@@ -33300,159 +33327,159 @@
     </row>
     <row r="618" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>316</v>
+        <v>1500</v>
       </c>
       <c r="B618" t="s">
-        <v>317</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="619" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" t="s">
-        <v>1500</v>
+        <v>1365</v>
       </c>
       <c r="B619" t="s">
-        <v>1501</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="620" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" t="s">
-        <v>1365</v>
+        <v>1541</v>
       </c>
       <c r="B620" t="s">
-        <v>1366</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="621" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" t="s">
-        <v>1541</v>
+        <v>1199</v>
       </c>
       <c r="B621" t="s">
-        <v>1622</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="622" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" t="s">
-        <v>1199</v>
+        <v>128</v>
       </c>
       <c r="B622" t="s">
-        <v>1200</v>
+        <v>129</v>
       </c>
     </row>
     <row r="623" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
-        <v>128</v>
+        <v>711</v>
       </c>
       <c r="B623" t="s">
-        <v>129</v>
+        <v>762</v>
       </c>
     </row>
     <row r="624" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" t="s">
-        <v>711</v>
+        <v>1624</v>
       </c>
       <c r="B624" t="s">
-        <v>762</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="625" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" t="s">
-        <v>1624</v>
+        <v>340</v>
       </c>
       <c r="B625" t="s">
-        <v>1625</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="626" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" t="s">
-        <v>340</v>
+        <v>282</v>
       </c>
       <c r="B626" t="s">
-        <v>1889</v>
+        <v>765</v>
       </c>
     </row>
     <row r="627" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" t="s">
-        <v>282</v>
+        <v>1365</v>
       </c>
       <c r="B627" t="s">
-        <v>765</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="628" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" t="s">
-        <v>1365</v>
+        <v>896</v>
       </c>
       <c r="B628" t="s">
-        <v>1504</v>
+        <v>897</v>
       </c>
     </row>
     <row r="629" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>896</v>
+        <v>1505</v>
       </c>
       <c r="B629" t="s">
-        <v>897</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="630" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" t="s">
-        <v>1505</v>
+        <v>356</v>
       </c>
       <c r="B630" t="s">
-        <v>1506</v>
+        <v>357</v>
       </c>
     </row>
     <row r="631" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" t="s">
-        <v>356</v>
+        <v>898</v>
       </c>
       <c r="B631" t="s">
-        <v>357</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="632" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" t="s">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="B632" t="s">
-        <v>1201</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="633" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
-        <v>1202</v>
+        <v>35</v>
       </c>
       <c r="B633" t="s">
-        <v>1203</v>
+        <v>767</v>
       </c>
     </row>
     <row r="634" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" t="s">
-        <v>35</v>
+        <v>1048</v>
       </c>
       <c r="B634" t="s">
-        <v>767</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="635" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="B635" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="636" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" t="s">
-        <v>1051</v>
+        <v>730</v>
       </c>
       <c r="B636" t="s">
-        <v>1052</v>
+        <v>731</v>
       </c>
     </row>
     <row r="637" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" t="s">
-        <v>730</v>
+        <v>585</v>
       </c>
       <c r="B637" t="s">
         <v>731</v>
@@ -33460,135 +33487,135 @@
     </row>
     <row r="638" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" t="s">
-        <v>585</v>
+        <v>1680</v>
       </c>
       <c r="B638" t="s">
-        <v>731</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="639" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" t="s">
-        <v>1680</v>
+        <v>239</v>
       </c>
       <c r="B639" t="s">
-        <v>1681</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="640" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" t="s">
-        <v>239</v>
+        <v>1627</v>
       </c>
       <c r="B640" t="s">
-        <v>1204</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="641" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" t="s">
-        <v>1627</v>
+        <v>1205</v>
       </c>
       <c r="B641" t="s">
-        <v>1628</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="642" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
-        <v>1205</v>
+        <v>770</v>
       </c>
       <c r="B642" t="s">
-        <v>1206</v>
+        <v>771</v>
       </c>
     </row>
     <row r="643" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" t="s">
-        <v>770</v>
+        <v>639</v>
       </c>
       <c r="B643" t="s">
-        <v>771</v>
+        <v>640</v>
       </c>
     </row>
     <row r="644" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" t="s">
-        <v>639</v>
+        <v>1507</v>
       </c>
       <c r="B644" t="s">
-        <v>640</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="645" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="B645" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="646" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" t="s">
-        <v>1509</v>
+        <v>1892</v>
       </c>
       <c r="B646" t="s">
-        <v>1510</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="647" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
-        <v>1892</v>
+        <v>458</v>
       </c>
       <c r="B647" t="s">
-        <v>1893</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="648" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" t="s">
-        <v>458</v>
+        <v>1207</v>
       </c>
       <c r="B648" t="s">
-        <v>1053</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="649" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" t="s">
-        <v>1207</v>
+        <v>1298</v>
       </c>
       <c r="B649" t="s">
-        <v>1208</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="650" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" t="s">
-        <v>1298</v>
+        <v>401</v>
       </c>
       <c r="B650" t="s">
-        <v>1367</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="651" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" t="s">
-        <v>401</v>
+        <v>24</v>
       </c>
       <c r="B651" t="s">
-        <v>1209</v>
+        <v>635</v>
       </c>
     </row>
     <row r="652" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" t="s">
-        <v>24</v>
+        <v>138</v>
       </c>
       <c r="B652" t="s">
-        <v>635</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="653" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" t="s">
-        <v>138</v>
+        <v>684</v>
       </c>
       <c r="B653" t="s">
-        <v>1287</v>
+        <v>685</v>
       </c>
     </row>
     <row r="654" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" t="s">
-        <v>684</v>
+        <v>947</v>
       </c>
       <c r="B654" t="s">
         <v>685</v>
@@ -33596,138 +33623,141 @@
     </row>
     <row r="655" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" t="s">
-        <v>947</v>
+        <v>325</v>
       </c>
       <c r="B655" t="s">
-        <v>685</v>
+        <v>636</v>
       </c>
     </row>
     <row r="656" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" t="s">
-        <v>325</v>
+        <v>1138</v>
       </c>
       <c r="B656" t="s">
-        <v>636</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" t="s">
-        <v>1138</v>
+        <v>898</v>
       </c>
       <c r="B657" t="s">
-        <v>1683</v>
+        <v>899</v>
       </c>
     </row>
     <row r="658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" t="s">
-        <v>898</v>
+        <v>272</v>
       </c>
       <c r="B658" t="s">
-        <v>899</v>
+        <v>273</v>
       </c>
     </row>
     <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" t="s">
-        <v>272</v>
+        <v>1368</v>
       </c>
       <c r="B659" t="s">
-        <v>273</v>
+        <v>1369</v>
       </c>
     </row>
     <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" t="s">
-        <v>1368</v>
+        <v>85</v>
       </c>
       <c r="B660" t="s">
-        <v>1369</v>
+        <v>274</v>
       </c>
     </row>
     <row r="661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" t="s">
-        <v>85</v>
+        <v>1293</v>
       </c>
       <c r="B661" t="s">
-        <v>274</v>
+        <v>1629</v>
       </c>
     </row>
     <row r="662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" t="s">
-        <v>1293</v>
+        <v>1630</v>
       </c>
       <c r="B662" t="s">
-        <v>1629</v>
+        <v>1631</v>
+      </c>
+      <c r="C662" s="2" t="s">
+        <v>1935</v>
       </c>
     </row>
     <row r="663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" t="s">
-        <v>1630</v>
+        <v>239</v>
       </c>
       <c r="B663" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C663" s="2" t="s">
-        <v>1935</v>
+        <v>1131</v>
+      </c>
+      <c r="C663" s="10" t="s">
+        <v>1976</v>
       </c>
     </row>
     <row r="664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" t="s">
-        <v>239</v>
+        <v>1371</v>
       </c>
       <c r="B664" t="s">
-        <v>1131</v>
+        <v>1372</v>
       </c>
     </row>
     <row r="665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" t="s">
-        <v>1371</v>
+        <v>726</v>
       </c>
       <c r="B665" t="s">
-        <v>1372</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" t="s">
-        <v>726</v>
+        <v>515</v>
       </c>
       <c r="B666" t="s">
-        <v>1896</v>
+        <v>516</v>
       </c>
     </row>
     <row r="667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" t="s">
-        <v>515</v>
+        <v>381</v>
       </c>
       <c r="B667" t="s">
-        <v>516</v>
+        <v>1511</v>
       </c>
     </row>
     <row r="668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" t="s">
-        <v>381</v>
+        <v>569</v>
       </c>
       <c r="B668" t="s">
-        <v>1511</v>
+        <v>793</v>
       </c>
     </row>
     <row r="669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" t="s">
-        <v>569</v>
+        <v>639</v>
       </c>
       <c r="B669" t="s">
-        <v>793</v>
+        <v>772</v>
       </c>
     </row>
     <row r="670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" t="s">
-        <v>639</v>
+        <v>224</v>
       </c>
       <c r="B670" t="s">
-        <v>772</v>
+        <v>86</v>
       </c>
     </row>
     <row r="671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" t="s">
-        <v>224</v>
+        <v>85</v>
       </c>
       <c r="B671" t="s">
         <v>86</v>
@@ -33735,111 +33765,111 @@
     </row>
     <row r="672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" t="s">
-        <v>85</v>
+        <v>126</v>
       </c>
       <c r="B672" t="s">
-        <v>86</v>
+        <v>127</v>
       </c>
     </row>
     <row r="673" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" t="s">
-        <v>126</v>
+        <v>901</v>
       </c>
       <c r="B673" t="s">
-        <v>127</v>
+        <v>902</v>
       </c>
     </row>
     <row r="674" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
-        <v>901</v>
+        <v>794</v>
       </c>
       <c r="B674" t="s">
-        <v>902</v>
+        <v>795</v>
       </c>
     </row>
     <row r="675" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" t="s">
-        <v>794</v>
+        <v>1058</v>
       </c>
       <c r="B675" t="s">
-        <v>795</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="676" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" t="s">
-        <v>1058</v>
+        <v>85</v>
       </c>
       <c r="B676" t="s">
-        <v>1059</v>
+        <v>520</v>
       </c>
     </row>
     <row r="677" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" t="s">
-        <v>85</v>
+        <v>42</v>
       </c>
       <c r="B677" t="s">
-        <v>520</v>
+        <v>296</v>
       </c>
     </row>
     <row r="678" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" t="s">
-        <v>42</v>
+        <v>1060</v>
       </c>
       <c r="B678" t="s">
-        <v>296</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="679" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" t="s">
-        <v>1060</v>
+        <v>1512</v>
       </c>
       <c r="B679" t="s">
-        <v>1061</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="680" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
-        <v>1512</v>
+        <v>368</v>
       </c>
       <c r="B680" t="s">
-        <v>1513</v>
+        <v>369</v>
       </c>
     </row>
     <row r="681" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" t="s">
-        <v>368</v>
+        <v>561</v>
       </c>
       <c r="B681" t="s">
-        <v>369</v>
+        <v>562</v>
       </c>
     </row>
     <row r="682" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
-        <v>561</v>
+        <v>115</v>
       </c>
       <c r="B682" t="s">
-        <v>562</v>
+        <v>642</v>
       </c>
     </row>
     <row r="683" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" t="s">
-        <v>115</v>
+        <v>613</v>
       </c>
       <c r="B683" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="684" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" t="s">
-        <v>613</v>
+        <v>286</v>
       </c>
       <c r="B684" t="s">
-        <v>643</v>
+        <v>287</v>
       </c>
     </row>
     <row r="685" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
-        <v>286</v>
+        <v>262</v>
       </c>
       <c r="B685" t="s">
         <v>287</v>
@@ -33847,7 +33877,7 @@
     </row>
     <row r="686" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" t="s">
-        <v>262</v>
+        <v>291</v>
       </c>
       <c r="B686" t="s">
         <v>287</v>
@@ -33855,135 +33885,135 @@
     </row>
     <row r="687" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" t="s">
-        <v>291</v>
+        <v>450</v>
       </c>
       <c r="B687" t="s">
-        <v>287</v>
+        <v>451</v>
       </c>
     </row>
     <row r="688" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" t="s">
-        <v>450</v>
+        <v>248</v>
       </c>
       <c r="B688" t="s">
-        <v>451</v>
+        <v>796</v>
       </c>
     </row>
     <row r="689" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" t="s">
-        <v>248</v>
+        <v>571</v>
       </c>
       <c r="B689" t="s">
-        <v>796</v>
+        <v>572</v>
       </c>
     </row>
     <row r="690" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" t="s">
-        <v>571</v>
+        <v>1381</v>
       </c>
       <c r="B690" t="s">
-        <v>572</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="691" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
-        <v>1381</v>
+        <v>1324</v>
       </c>
       <c r="B691" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="692" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" t="s">
-        <v>1324</v>
+        <v>77</v>
       </c>
       <c r="B692" t="s">
-        <v>1383</v>
+        <v>904</v>
       </c>
     </row>
     <row r="693" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" t="s">
-        <v>77</v>
+        <v>1385</v>
       </c>
       <c r="B693" t="s">
-        <v>904</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="694" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
-        <v>1385</v>
+        <v>1063</v>
       </c>
       <c r="B694" t="s">
-        <v>1386</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="695" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" t="s">
-        <v>1063</v>
+        <v>1637</v>
       </c>
       <c r="B695" t="s">
-        <v>1064</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="696" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
-        <v>1637</v>
+        <v>1066</v>
       </c>
       <c r="B696" t="s">
-        <v>1638</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="697" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
-        <v>1066</v>
+        <v>1389</v>
       </c>
       <c r="B697" t="s">
-        <v>1067</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="698" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
-        <v>1389</v>
+        <v>1518</v>
       </c>
       <c r="B698" t="s">
-        <v>1390</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="699" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
-        <v>1518</v>
+        <v>1684</v>
       </c>
       <c r="B699" t="s">
-        <v>1519</v>
+        <v>1685</v>
       </c>
     </row>
     <row r="700" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
-        <v>1684</v>
+        <v>1069</v>
       </c>
       <c r="B700" t="s">
-        <v>1685</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="701" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
-        <v>1069</v>
+        <v>294</v>
       </c>
       <c r="B701" t="s">
-        <v>1070</v>
+        <v>295</v>
       </c>
     </row>
     <row r="702" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
-        <v>294</v>
+        <v>1611</v>
       </c>
       <c r="B702" t="s">
-        <v>295</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="703" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" t="s">
-        <v>1611</v>
+        <v>1909</v>
       </c>
       <c r="B703" t="s">
         <v>1639</v>
@@ -33991,60 +34021,52 @@
     </row>
     <row r="704" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>1909</v>
+        <v>956</v>
       </c>
       <c r="B704" t="s">
-        <v>1639</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="705" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" t="s">
-        <v>956</v>
+        <v>224</v>
       </c>
       <c r="B705" t="s">
-        <v>1072</v>
+        <v>798</v>
       </c>
     </row>
     <row r="706" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" t="s">
-        <v>224</v>
+        <v>31</v>
       </c>
       <c r="B706" t="s">
-        <v>798</v>
+        <v>32</v>
       </c>
     </row>
     <row r="707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
-        <v>31</v>
+        <v>1075</v>
       </c>
       <c r="B707" t="s">
-        <v>32</v>
+        <v>1076</v>
+      </c>
+      <c r="C707" s="1" t="s">
+        <v>1936</v>
       </c>
     </row>
     <row r="708" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
-        <v>1075</v>
+        <v>689</v>
       </c>
       <c r="B708" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C708" s="1" t="s">
-        <v>1936</v>
+        <v>690</v>
       </c>
     </row>
     <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" t="s">
-        <v>689</v>
+        <v>905</v>
       </c>
       <c r="B709" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="710" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A710" t="s">
-        <v>905</v>
-      </c>
-      <c r="B710" t="s">
         <v>906</v>
       </c>
     </row>
@@ -34056,9 +34078,9 @@
     <hyperlink ref="C21" r:id="rId4" xr:uid="{48E128B3-0BC2-4A8F-9021-1C5209902DA7}"/>
     <hyperlink ref="C48" r:id="rId5" xr:uid="{5010A52B-1933-4B0D-8945-6825FCF10538}"/>
     <hyperlink ref="C75" r:id="rId6" xr:uid="{31197C11-DE2D-4242-88B9-D74E29521FC7}"/>
-    <hyperlink ref="C424" r:id="rId7" xr:uid="{615ECECA-FC28-4049-AF90-8282CFB5FB08}"/>
-    <hyperlink ref="C426" r:id="rId8" xr:uid="{3F258564-535C-4E31-84FD-F0B4224DEDFC}"/>
-    <hyperlink ref="C663" r:id="rId9" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{033EC726-D865-426A-819E-A799648AB3C1}"/>
+    <hyperlink ref="C423" r:id="rId7" xr:uid="{615ECECA-FC28-4049-AF90-8282CFB5FB08}"/>
+    <hyperlink ref="C425" r:id="rId8" xr:uid="{3F258564-535C-4E31-84FD-F0B4224DEDFC}"/>
+    <hyperlink ref="C662" r:id="rId9" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{033EC726-D865-426A-819E-A799648AB3C1}"/>
     <hyperlink ref="C34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C5" r:id="rId11" xr:uid="{34387F5A-28DA-460F-9EEA-35D9435E3CC5}"/>
     <hyperlink ref="C6" r:id="rId12" xr:uid="{B0D11795-BECA-4256-998B-45F81F8016F7}"/>
@@ -34068,6 +34090,11 @@
     <hyperlink ref="C91" r:id="rId16" xr:uid="{C55EAA05-E5BD-4A5E-BFBE-FEB1F1FA656A}"/>
     <hyperlink ref="C99" r:id="rId17" xr:uid="{EAA77CB6-CB26-4399-B714-2CDD461F42E0}"/>
     <hyperlink ref="C117" r:id="rId18" xr:uid="{04DC73B6-E166-4AC3-A238-23818A086FEE}"/>
+    <hyperlink ref="C125" r:id="rId19" xr:uid="{AE2AFA72-EF6B-4BC0-BD2C-0182BB7C13E0}"/>
+    <hyperlink ref="C177" r:id="rId20" xr:uid="{CD60C327-19B4-45B0-9491-342058598A3B}"/>
+    <hyperlink ref="C178" r:id="rId21" xr:uid="{6215C244-43F9-41FE-A1A7-5F310D1022D8}"/>
+    <hyperlink ref="C179" r:id="rId22" xr:uid="{F451DBB9-EE1C-466F-B9C2-EC4C19833ED9}"/>
+    <hyperlink ref="C663" r:id="rId23" xr:uid="{8E7A3AC7-543E-4975-85FD-8A692F211657}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F315D3B0-7DB2-4CF0-A220-581CDD87C79F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669C7C70-9FDA-413D-AFF0-91C24AFDC85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7203" uniqueCount="1977">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7205" uniqueCount="1979">
   <si>
     <t>Prénom</t>
   </si>
@@ -6098,6 +6098,12 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/7/7f/Filippo_della_Valle_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Portret_van_Laurent_Delvaux%2C_RP-P-1906-3308.jpg/960px-Portret_van_Laurent_Delvaux%2C_RP-P-1906-3308.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Lemoyne_the_Younger_-_%C3%89tienne_Maurice_Falconet.jpg/960px-Lemoyne_the_Younger_-_%C3%89tienne_Maurice_Falconet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -29913,7 +29919,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="193" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1214</v>
       </c>
@@ -29921,7 +29927,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="194" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1435</v>
       </c>
@@ -29929,7 +29935,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="195" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>1392</v>
       </c>
@@ -29937,7 +29943,7 @@
         <v>1393</v>
       </c>
     </row>
-    <row r="196" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1289</v>
       </c>
@@ -29945,7 +29951,7 @@
         <v>1290</v>
       </c>
     </row>
-    <row r="197" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1162</v>
       </c>
@@ -29953,7 +29959,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="198" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>325</v>
       </c>
@@ -29961,15 +29967,18 @@
         <v>326</v>
       </c>
     </row>
-    <row r="199" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1132</v>
       </c>
       <c r="B199" t="s">
         <v>1133</v>
       </c>
-    </row>
-    <row r="200" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C199" s="10" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1293</v>
       </c>
@@ -29977,7 +29986,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="201" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>276</v>
       </c>
@@ -29985,7 +29994,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="202" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>637</v>
       </c>
@@ -29993,7 +30002,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="203" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>1210</v>
       </c>
@@ -30001,7 +30010,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="204" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>279</v>
       </c>
@@ -30009,7 +30018,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="205" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>95</v>
       </c>
@@ -30017,7 +30026,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="206" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>512</v>
       </c>
@@ -30025,7 +30034,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="207" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>723</v>
       </c>
@@ -30033,7 +30042,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="208" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1632</v>
       </c>
@@ -30172,7 +30181,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="225" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>890</v>
       </c>
@@ -30180,7 +30189,7 @@
         <v>1296</v>
       </c>
     </row>
-    <row r="226" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1138</v>
       </c>
@@ -30188,7 +30197,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="227" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>842</v>
       </c>
@@ -30196,7 +30205,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="228" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>1298</v>
       </c>
@@ -30204,7 +30213,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="229" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>775</v>
       </c>
@@ -30212,7 +30221,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="230" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>251</v>
       </c>
@@ -30220,7 +30229,7 @@
         <v>1758</v>
       </c>
     </row>
-    <row r="231" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>195</v>
       </c>
@@ -30228,7 +30237,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="232" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>282</v>
       </c>
@@ -30236,7 +30245,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="233" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>960</v>
       </c>
@@ -30244,7 +30253,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="234" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>171</v>
       </c>
@@ -30252,7 +30261,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="235" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>696</v>
       </c>
@@ -30260,15 +30269,18 @@
         <v>697</v>
       </c>
     </row>
-    <row r="236" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1140</v>
       </c>
       <c r="B236" t="s">
         <v>1141</v>
       </c>
-    </row>
-    <row r="237" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="C236" s="10" t="s">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1255</v>
       </c>
@@ -30276,7 +30288,7 @@
         <v>1442</v>
       </c>
     </row>
-    <row r="238" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>268</v>
       </c>
@@ -30284,7 +30296,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>845</v>
       </c>
@@ -30292,7 +30304,7 @@
         <v>844</v>
       </c>
     </row>
-    <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>268</v>
       </c>
@@ -34095,6 +34107,8 @@
     <hyperlink ref="C178" r:id="rId21" xr:uid="{6215C244-43F9-41FE-A1A7-5F310D1022D8}"/>
     <hyperlink ref="C179" r:id="rId22" xr:uid="{F451DBB9-EE1C-466F-B9C2-EC4C19833ED9}"/>
     <hyperlink ref="C663" r:id="rId23" xr:uid="{8E7A3AC7-543E-4975-85FD-8A692F211657}"/>
+    <hyperlink ref="C199" r:id="rId24" xr:uid="{00D9C921-7C4C-4488-B8AB-86BC60D54D53}"/>
+    <hyperlink ref="C236" r:id="rId25" xr:uid="{43B616DF-585A-49FE-A512-858CA43A442E}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{669C7C70-9FDA-413D-AFF0-91C24AFDC85B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CD1B6CC-96F6-42FA-ABA2-AE9957D30A07}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-225" yWindow="465" windowWidth="16275" windowHeight="15060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7205" uniqueCount="1979">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7025" uniqueCount="2037">
   <si>
     <t>Prénom</t>
   </si>
@@ -6104,6 +6104,180 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/ce/Lemoyne_the_Younger_-_%C3%89tienne_Maurice_Falconet.jpg/960px-Lemoyne_the_Younger_-_%C3%89tienne_Maurice_Falconet.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/El_Greco_-_Portrait_of_a_Man_-_WGA10554.jpg/960px-El_Greco_-_Portrait_of_a_Man_-_WGA10554.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://commons.wikimedia.org/wiki/Creator:Pieter_Aertsen#/media/File:Portret_van_Pieter_Aertsen_Petrus_Petri,_Longus,_Amstelr._Pictor._(titel_op_object)_Pictorum_Aliquot_Celebrium_Praecipuae_Germaniae_Inferioris_Effigies_(serietitel),_RP-P-OB-55.210.jpg</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d3/COURBET_Gustave_Le_sculpteur_Marcello_%28Duchesse_de_Castiglione-Colonna%29_Huile_sur_toile.jpg/960px-COURBET_Gustave_Le_sculpteur_Marcello_%28Duchesse_de_Castiglione-Colonna%29_Huile_sur_toile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Ignoto%2C_ritratto_di_alessandro_algardi%2C_1654%2C_01.JPG/960px-Ignoto%2C_ritratto_di_alessandro_algardi%2C_1654%2C_01.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/46/Altdorfer.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Santi_di_Tito%2C_Fabbrica_del_Tempio_di_Salomone%2C_1570-71%2C_04%2C2_ritratti_di_architetti_-_bartolomeo_ammannati.jpg/960px-Santi_di_Tito%2C_Fabbrica_del_Tempio_di_Salomone%2C_1570-71%2C_04%2C2_ritratti_di_architetti_-_bartolomeo_ammannati.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Sofonisba_Anguissola%2C_Selvportr%C3%A6t_ved_staffeliet%2C_1556%2C_Museum_Castle_in_%C5%81a%C5%84cut.jpg/960px-Sofonisba_Anguissola%2C_Selvportr%C3%A6t_ved_staffeliet%2C_1556%2C_Museum_Castle_in_%C5%81a%C5%84cut.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f3/Mark_Antokolsky.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/Giuseppe_Arcimboldo_-_Self_Portrait_-_Google_Art_Project.jpg/960px-Giuseppe_Arcimboldo_-_Self_Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/17/Kustodiev_Portrait_of_Naum_Aronson.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Leandro_Bassano_%281557-1622%29_-_Portrait_of_Tiziano_Aspetti_holding_a_Statuette_-_RCIN_405988_-_Royal_Collection.jpg/960px-Leandro_Bassano_%281557-1622%29_-_Portrait_of_Tiziano_Aspetti_holding_a_Statuette_-_RCIN_405988_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Alesso_Baldovinetti_selfportrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Kw11_0012025_20190129_001_Baldung_Jugendliches_Selbstbildnis.jpg/960px-Kw11_0012025_20190129_001_Baldung_Jugendliches_Selbstbildnis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Thomas_Ball_by_an_unidentified_artist%2C_c._1863%2C_albumen_silver_print%2C_from_the_National_Portrait_Gallery_-_NPG-S_NPG_77_141Ball-000002.jpg/960px-Thomas_Ball_by_an_unidentified_artist%2C_c._1863%2C_albumen_silver_print%2C_from_the_National_Portrait_Gallery_-_NPG-S_NPG_77_141Ball-000002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/Giorgione_059.jpg/960px-Giorgione_059.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Self-portrait_by_Guercino.jpg/960px-Self-portrait_by_Guercino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/e1/ErnstBarlachYoung.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Federico_Barocci_-_Autoportrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d9/Portrait_of_Louis-Ernest_Barrias.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/Bartholdi%2C_Auguste%2C_Nadar%2C_GALLICA.jpg/500px-Bartholdi%2C_Auguste%2C_Nadar%2C_GALLICA.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Mus%C3%A9e_Ingres-Bourdelle_-_Portrait_de_Lorenzo_Bartolin_-_Close-up-_Ingres_-_Joconde06070000015.jpg/1280px-Mus%C3%A9e_Ingres-Bourdelle_-_Portrait_de_Lorenzo_Bartolin_-_Close-up-_Ingres_-_Joconde06070000015.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/Antoine-Louis_Barye%2C_by_Charles_Camino.jpg/960px-Antoine-Louis_Barye%2C_by_Charles_Camino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/48/Jacopo_da_Ponte_012.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Pompeo_Batoni_-_Selbstbildnis_-_1057_-_Bavarian_State_Painting_Collections.jpg/960px-Pompeo_Batoni_-_Selbstbildnis_-_1057_-_Bavarian_State_Painting_Collections.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Giovanni_Antonio_Bazzi.jpg/960px-Giovanni_Antonio_Bazzi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/13/Domenico_di_Pace_Beccafumi.jpg/960px-Domenico_di_Pace_Beccafumi.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Max_Beckmann_Selbstbildnis_Gelb-Rosa.jpg/960px-Max_Beckmann_Selbstbildnis_Gelb-Rosa.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/a6/Reinhold_Begas_photo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Delle_vite_de%27_pi%C3%B9_eccellenti_pittori%2C_scultori%2C_et_architetti_%281648%29_%2814779777285%29.jpg/960px-Delle_vite_de%27_pi%C3%B9_eccellenti_pittori%2C_scultori%2C_et_architetti_%281648%29_%2814779777285%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bd/Bellini_selfportrait.jpg/960px-Bellini_selfportrait.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c1/Portr%C3%A6t_af_den_venezianske_maler_Giovanni_Bellini.jpg/960px-Portr%C3%A6t_af_den_venezianske_maler_Giovanni_Bellini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/4/4d/Bernardo_Bellotto.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/d/d4/Luna_Mariano_Benlliure.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e4/Henri_de_Toulouse-Lautrec_-_Portrait_de_%C3%89mile_Bernard.jpg/960px-Henri_de_Toulouse-Lautrec_-_Portrait_de_%C3%89mile_Bernard.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/fc/Joseph_Bernard%2C_French_sculptor_01.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg/960px-Gian_Lorenzo_Bernini%2C_self-portrait%2C_c1623.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/93/Pietro_Bernini.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Ajaccio_Da_Cortona_Autoportrait.JPG/960px-Ajaccio_Da_Cortona_Autoportrait.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/2/27/Alonso_Berruguete_%28por_Jos%C3%A9_Alcoverro%29_01b.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/7/7a/Pinturicchio_self.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Portret_van_Joachim_Beuckelaer_Ioachimus_Bueckelaer%2C_Antverp._Pictor._%28titel_op_object%29_Pictorum_Aliquot_Celebrium_Praecipuae_Germaniae_Inferioris_Effigies_%28serietitel%29%2C_RP-P-1907-353.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/3/30/Albert_Bierstadt.jpg/960px-Albert_Bierstadt.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/19/Umberto_Boccioni%2C_by_Umberto_Boccioni.jpg/960px-Umberto_Boccioni%2C_by_Umberto_Boccioni.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/e/ef/Arnold_B%C3%B6cklin_%281827_-_1901%29%2C_Selbstportrait_%281873%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Five_Famous_Men_of_the_Florentine_Renaissance%2C_Giotto_%28cropped%29.jpg/960px-Five_Famous_Men_of_the_Florentine_Renaissance%2C_Giotto_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/7/76/Andr%C3%A9_Adolphe-Eug%C3%A8ne_Disd%C3%A9ri_%28French_-_%28Rosa_Bonheur%29_-_Google_Art_Project.jpg/960px-Andr%C3%A9_Adolphe-Eug%C3%A8ne_Disd%C3%A9ri_%28French_-_%28Rosa_Bonheur%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/a/af/Self-portrait-1889.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/26/Bordon%2C_Paris_-_Autorretrato%2C_P000372.jpg/960px-Bordon%2C_Paris_-_Autorretrato%2C_P000372.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/0/0a/Portrait_of_Gutzon_Borglum.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/9/9e/Borovikovsky_By_Bugaevsky_Blagodatny.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2d/Jheronimus_Bosch_%28cropped%29.jpg/960px-Jheronimus_Bosch_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e9/Sandro_Botticelli_Self-portrait_ca_1475.jpg/960px-Sandro_Botticelli_Self-portrait_ca_1475.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Autoportrait_d%27Alfred_Boucher.jpg/960px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Autoportrait_d%27Alfred_Boucher.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/f9/Boucher_par_Gustav_Lundberg_1741.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/c/ce/William-Adolphe_Bouguereau_photo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/1/18/Antoine_Bourdelle_b_Meurisse_1925.jpg/960px-Antoine_Bourdelle_b_Meurisse_1925.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Portret_van_de_schilder_Dieric_Bouts_Portretten_van_schilders_%28serietitel%29_Pictorum_Aliquot_Celebrium_Praecipuae_Germaniae_Inferioris_Effigies_%28serietitel%29%2C_RP-P-OB-67.052.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/Alessandro_Allori%2C_santissima_trinit%C3%A0_e_putti%2C_1567-1571%2C_05_ritratto_del_bronzino.jpg/960px-Alessandro_Allori%2C_santissima_trinit%C3%A0_e_putti%2C_1567-1571%2C_05_ritratto_del_bronzino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -28284,7 +28458,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:L709"/>
+  <dimension ref="A1:L590"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" customWidth="1"/>
@@ -28338,6 +28512,9 @@
       <c r="B2" t="s">
         <v>509</v>
       </c>
+      <c r="C2" s="10" t="s">
+        <v>1979</v>
+      </c>
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
@@ -28381,6 +28558,9 @@
       <c r="B7" t="s">
         <v>388</v>
       </c>
+      <c r="C7" s="10" t="s">
+        <v>1980</v>
+      </c>
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
@@ -28389,6 +28569,9 @@
       <c r="B8" t="s">
         <v>1429</v>
       </c>
+      <c r="C8" s="10" t="s">
+        <v>1981</v>
+      </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
@@ -28408,6 +28591,9 @@
       <c r="B10" t="s">
         <v>805</v>
       </c>
+      <c r="C10" s="10" t="s">
+        <v>1982</v>
+      </c>
     </row>
     <row r="11" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
@@ -28438,6 +28624,9 @@
       <c r="B13" t="s">
         <v>394</v>
       </c>
+      <c r="C13" s="10" t="s">
+        <v>1983</v>
+      </c>
     </row>
     <row r="14" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
@@ -28454,6 +28643,9 @@
       <c r="B15" t="s">
         <v>530</v>
       </c>
+      <c r="C15" s="10" t="s">
+        <v>1984</v>
+      </c>
     </row>
     <row r="16" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
@@ -28478,6 +28670,9 @@
       <c r="B18" t="s">
         <v>398</v>
       </c>
+      <c r="C18" s="10" t="s">
+        <v>1985</v>
+      </c>
     </row>
     <row r="19" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
@@ -28486,6 +28681,9 @@
       <c r="B19" t="s">
         <v>1398</v>
       </c>
+      <c r="C19" s="10" t="s">
+        <v>1986</v>
+      </c>
     </row>
     <row r="20" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -28494,6 +28692,9 @@
       <c r="B20" t="s">
         <v>402</v>
       </c>
+      <c r="C20" s="10" t="s">
+        <v>1987</v>
+      </c>
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
@@ -28521,83 +28722,101 @@
       <c r="B23" t="s">
         <v>1641</v>
       </c>
+      <c r="C23" s="10" t="s">
+        <v>1988</v>
+      </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>1088</v>
+        <v>515</v>
       </c>
       <c r="B24" t="s">
-        <v>1089</v>
+        <v>532</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>1989</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>515</v>
+        <v>652</v>
       </c>
       <c r="B25" t="s">
-        <v>532</v>
+        <v>653</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>652</v>
+        <v>811</v>
       </c>
       <c r="B26" t="s">
-        <v>653</v>
+        <v>1090</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>1967</v>
       </c>
     </row>
     <row r="27" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>340</v>
+        <v>1538</v>
       </c>
       <c r="B27" t="s">
-        <v>535</v>
+        <v>1539</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>1923</v>
       </c>
     </row>
     <row r="28" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>811</v>
+        <v>134</v>
       </c>
       <c r="B28" t="s">
-        <v>1090</v>
+        <v>135</v>
       </c>
       <c r="C28" s="10" t="s">
-        <v>1967</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="29" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>1538</v>
+        <v>102</v>
       </c>
       <c r="B29" t="s">
-        <v>1539</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>1923</v>
+        <v>106</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>134</v>
+        <v>251</v>
       </c>
       <c r="B30" t="s">
-        <v>135</v>
+        <v>405</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>1991</v>
       </c>
     </row>
     <row r="31" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>102</v>
+        <v>890</v>
       </c>
       <c r="B31" t="s">
-        <v>106</v>
+        <v>1400</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>1992</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>251</v>
+        <v>536</v>
       </c>
       <c r="B32" t="s">
-        <v>405</v>
+        <v>537</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>1434</v>
       </c>
     </row>
     <row r="33" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -28605,5510 +28824,4745 @@
         <v>890</v>
       </c>
       <c r="B33" t="s">
-        <v>1400</v>
+        <v>1094</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>1968</v>
       </c>
     </row>
     <row r="34" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>536</v>
+        <v>407</v>
       </c>
       <c r="B34" t="s">
-        <v>537</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>1434</v>
+        <v>408</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>1993</v>
       </c>
     </row>
     <row r="35" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>102</v>
+        <v>656</v>
       </c>
       <c r="B35" t="s">
-        <v>539</v>
+        <v>657</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>1994</v>
       </c>
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>890</v>
+        <v>1492</v>
       </c>
       <c r="B36" t="s">
-        <v>1094</v>
+        <v>1642</v>
       </c>
       <c r="C36" s="10" t="s">
-        <v>1968</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B37" t="s">
-        <v>408</v>
+        <v>412</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>1996</v>
       </c>
     </row>
     <row r="38" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>656</v>
+        <v>1402</v>
       </c>
       <c r="B38" t="s">
-        <v>657</v>
+        <v>1403</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>1997</v>
       </c>
     </row>
     <row r="39" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>1492</v>
+        <v>1404</v>
       </c>
       <c r="B39" t="s">
-        <v>1642</v>
+        <v>1405</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>1998</v>
       </c>
     </row>
     <row r="40" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>411</v>
+        <v>73</v>
       </c>
       <c r="B40" t="s">
-        <v>412</v>
+        <v>1406</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>1999</v>
       </c>
     </row>
     <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>1402</v>
+        <v>327</v>
       </c>
       <c r="B41" t="s">
-        <v>1403</v>
+        <v>328</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>1404</v>
+        <v>1407</v>
       </c>
       <c r="B42" t="s">
-        <v>1405</v>
+        <v>1408</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>2000</v>
       </c>
     </row>
     <row r="43" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>73</v>
+        <v>319</v>
       </c>
       <c r="B43" t="s">
-        <v>1406</v>
+        <v>415</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>2001</v>
       </c>
     </row>
     <row r="44" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>327</v>
+        <v>612</v>
       </c>
       <c r="B44" t="s">
-        <v>328</v>
+        <v>920</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>2002</v>
       </c>
     </row>
     <row r="45" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>1407</v>
+        <v>1230</v>
       </c>
       <c r="B45" t="s">
-        <v>1408</v>
+        <v>1231</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>1924</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>319</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s">
-        <v>415</v>
+        <v>419</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>2003</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>612</v>
+        <v>95</v>
       </c>
       <c r="B47" t="s">
-        <v>920</v>
+        <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>1230</v>
+        <v>224</v>
       </c>
       <c r="B48" t="s">
-        <v>1231</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>422</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="49" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>418</v>
+        <v>1541</v>
       </c>
       <c r="B49" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1542</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>2005</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>1234</v>
+        <v>1409</v>
       </c>
       <c r="B50" t="s">
-        <v>1235</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1410</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>2006</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>95</v>
+        <v>291</v>
       </c>
       <c r="B51" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>299</v>
+      </c>
+      <c r="C51" s="10" t="s">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="52" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>224</v>
+        <v>138</v>
       </c>
       <c r="B52" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="53" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>541</v>
+        <v>171</v>
       </c>
       <c r="B53" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="C53" s="10" t="s">
+        <v>2008</v>
+      </c>
+    </row>
+    <row r="54" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>1541</v>
+        <v>102</v>
       </c>
       <c r="B54" t="s">
-        <v>1542</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>360</v>
+      </c>
+      <c r="C54" s="10" t="s">
+        <v>2009</v>
+      </c>
+    </row>
+    <row r="55" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>1409</v>
+        <v>35</v>
       </c>
       <c r="B55" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+      <c r="C55" s="10" t="s">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>291</v>
+        <v>1643</v>
       </c>
       <c r="B56" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1644</v>
+      </c>
+      <c r="C56" s="10" t="s">
+        <v>2011</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B57" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>171</v>
+        <v>1236</v>
       </c>
       <c r="B58" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1237</v>
+      </c>
+      <c r="C58" s="10" t="s">
+        <v>2012</v>
+      </c>
+    </row>
+    <row r="59" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>102</v>
+        <v>956</v>
       </c>
       <c r="B59" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1237</v>
+      </c>
+      <c r="C59" s="10" t="s">
+        <v>2013</v>
+      </c>
+    </row>
+    <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>35</v>
+        <v>800</v>
       </c>
       <c r="B60" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>801</v>
+      </c>
+      <c r="C60" s="10" t="s">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="61" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>1643</v>
+        <v>24</v>
       </c>
       <c r="B61" t="s">
-        <v>1644</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>801</v>
+      </c>
+      <c r="C61" s="10" t="s">
+        <v>2015</v>
+      </c>
+    </row>
+    <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>142</v>
+        <v>24</v>
       </c>
       <c r="B62" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>661</v>
+      </c>
+      <c r="C62" s="10" t="s">
+        <v>2016</v>
+      </c>
+    </row>
+    <row r="63" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>1236</v>
+        <v>522</v>
       </c>
       <c r="B63" t="s">
-        <v>1237</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>523</v>
+      </c>
+      <c r="C63" s="10" t="s">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="64" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>956</v>
+        <v>372</v>
       </c>
       <c r="B64" t="s">
-        <v>1237</v>
+        <v>373</v>
+      </c>
+      <c r="C64" s="10" t="s">
+        <v>2018</v>
       </c>
     </row>
     <row r="65" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>800</v>
+        <v>425</v>
       </c>
       <c r="B65" t="s">
-        <v>801</v>
+        <v>426</v>
+      </c>
+      <c r="C65" s="10" t="s">
+        <v>2019</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>24</v>
+        <v>1240</v>
       </c>
       <c r="B66" t="s">
-        <v>801</v>
+        <v>1241</v>
+      </c>
+      <c r="C66" s="10" t="s">
+        <v>2020</v>
       </c>
     </row>
     <row r="67" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>24</v>
+        <v>986</v>
       </c>
       <c r="B67" t="s">
-        <v>661</v>
+        <v>1212</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>1925</v>
       </c>
     </row>
     <row r="68" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>1095</v>
+        <v>1545</v>
       </c>
       <c r="B68" t="s">
-        <v>1096</v>
+        <v>1546</v>
+      </c>
+      <c r="C68" s="10" t="s">
+        <v>2021</v>
       </c>
     </row>
     <row r="69" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>522</v>
+        <v>1243</v>
       </c>
       <c r="B69" t="s">
-        <v>523</v>
+        <v>1244</v>
+      </c>
+      <c r="C69" s="10" t="s">
+        <v>2022</v>
       </c>
     </row>
     <row r="70" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>372</v>
+        <v>77</v>
       </c>
       <c r="B70" t="s">
-        <v>373</v>
+        <v>546</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="D70" t="s">
+        <v>1927</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>425</v>
+        <v>45</v>
       </c>
       <c r="B71" t="s">
-        <v>426</v>
+        <v>46</v>
+      </c>
+      <c r="C71" s="10" t="s">
+        <v>2023</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>1240</v>
+        <v>1246</v>
       </c>
       <c r="B72" t="s">
-        <v>1241</v>
+        <v>1247</v>
+      </c>
+      <c r="C72" s="10" t="s">
+        <v>2024</v>
       </c>
     </row>
     <row r="73" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="B73" t="s">
-        <v>545</v>
+        <v>1521</v>
+      </c>
+      <c r="C73" s="10" t="s">
+        <v>2025</v>
       </c>
     </row>
     <row r="74" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>1645</v>
+        <v>550</v>
       </c>
       <c r="B74" t="s">
-        <v>1646</v>
+        <v>551</v>
       </c>
     </row>
     <row r="75" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>986</v>
+        <v>429</v>
       </c>
       <c r="B75" t="s">
-        <v>1212</v>
-      </c>
-      <c r="C75" s="2" t="s">
-        <v>1925</v>
+        <v>430</v>
+      </c>
+      <c r="C75" s="10" t="s">
+        <v>2026</v>
       </c>
     </row>
     <row r="76" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>1545</v>
+        <v>1647</v>
       </c>
       <c r="B76" t="s">
-        <v>1546</v>
+        <v>1648</v>
+      </c>
+      <c r="C76" s="10" t="s">
+        <v>2027</v>
       </c>
     </row>
     <row r="77" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>1243</v>
+        <v>926</v>
       </c>
       <c r="B77" t="s">
-        <v>1244</v>
+        <v>927</v>
+      </c>
+      <c r="C77" s="10" t="s">
+        <v>2028</v>
       </c>
     </row>
     <row r="78" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>1097</v>
+        <v>364</v>
       </c>
       <c r="B78" t="s">
-        <v>1098</v>
+        <v>365</v>
+      </c>
+      <c r="C78" s="10" t="s">
+        <v>2029</v>
       </c>
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>42</v>
+        <v>1412</v>
       </c>
       <c r="B79" t="s">
-        <v>810</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>77</v>
+        <v>146</v>
       </c>
       <c r="B80" t="s">
-        <v>546</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>1926</v>
-      </c>
-      <c r="D80" t="s">
-        <v>1927</v>
+        <v>147</v>
+      </c>
+      <c r="C80" s="10" t="s">
+        <v>2030</v>
       </c>
     </row>
     <row r="81" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>45</v>
+        <v>1101</v>
       </c>
       <c r="B81" t="s">
-        <v>46</v>
+        <v>1102</v>
+      </c>
+      <c r="C81" s="10" t="s">
+        <v>1969</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>1246</v>
+        <v>1365</v>
       </c>
       <c r="B82" t="s">
-        <v>1247</v>
+        <v>931</v>
+      </c>
+      <c r="C82" s="10" t="s">
+        <v>2031</v>
       </c>
     </row>
     <row r="83" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>550</v>
+        <v>435</v>
       </c>
       <c r="B83" t="s">
-        <v>1521</v>
+        <v>931</v>
+      </c>
+      <c r="C83" s="10" t="s">
+        <v>2032</v>
       </c>
     </row>
     <row r="84" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>550</v>
+        <v>986</v>
       </c>
       <c r="B84" t="s">
-        <v>551</v>
+        <v>1249</v>
+      </c>
+      <c r="C84" s="10" t="s">
+        <v>2033</v>
       </c>
     </row>
     <row r="85" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>429</v>
+        <v>674</v>
       </c>
       <c r="B85" t="s">
-        <v>430</v>
+        <v>675</v>
       </c>
     </row>
     <row r="86" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>1647</v>
+        <v>775</v>
       </c>
       <c r="B86" t="s">
-        <v>1648</v>
+        <v>1649</v>
+      </c>
+      <c r="C86" s="10" t="s">
+        <v>2034</v>
       </c>
     </row>
     <row r="87" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>926</v>
+        <v>77</v>
       </c>
       <c r="B87" t="s">
-        <v>927</v>
+        <v>150</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>364</v>
+        <v>153</v>
       </c>
       <c r="B88" t="s">
-        <v>365</v>
+        <v>154</v>
+      </c>
+      <c r="C88" s="10" t="s">
+        <v>2035</v>
       </c>
     </row>
     <row r="89" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>1412</v>
+        <v>24</v>
       </c>
       <c r="B89" t="s">
-        <v>1413</v>
+        <v>1104</v>
+      </c>
+      <c r="C89" s="10" t="s">
+        <v>1970</v>
       </c>
     </row>
     <row r="90" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>146</v>
+        <v>21</v>
       </c>
       <c r="B90" t="s">
-        <v>147</v>
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>1101</v>
+        <v>126</v>
       </c>
       <c r="B91" t="s">
-        <v>1102</v>
+        <v>1719</v>
       </c>
       <c r="C91" s="10" t="s">
-        <v>1969</v>
+        <v>2036</v>
       </c>
     </row>
     <row r="92" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>1365</v>
+        <v>571</v>
       </c>
       <c r="B92" t="s">
-        <v>931</v>
+        <v>663</v>
       </c>
     </row>
     <row r="93" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>435</v>
+        <v>387</v>
       </c>
       <c r="B93" t="s">
-        <v>931</v>
+        <v>433</v>
       </c>
     </row>
     <row r="94" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>986</v>
+        <v>723</v>
       </c>
       <c r="B94" t="s">
-        <v>1249</v>
+        <v>724</v>
       </c>
     </row>
     <row r="95" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>674</v>
+        <v>784</v>
       </c>
       <c r="B95" t="s">
-        <v>675</v>
+        <v>1650</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>775</v>
+        <v>525</v>
       </c>
       <c r="B96" t="s">
-        <v>1649</v>
+        <v>526</v>
       </c>
     </row>
     <row r="97" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>77</v>
+        <v>50</v>
       </c>
       <c r="B97" t="s">
-        <v>150</v>
+        <v>51</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>153</v>
+        <v>1251</v>
       </c>
       <c r="B98" t="s">
-        <v>154</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="99" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>24</v>
+        <v>1255</v>
       </c>
       <c r="B99" t="s">
-        <v>1104</v>
-      </c>
-      <c r="C99" s="10" t="s">
-        <v>1970</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="100" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>1107</v>
+        <v>814</v>
       </c>
       <c r="B100" t="s">
-        <v>1108</v>
+        <v>815</v>
       </c>
     </row>
     <row r="101" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>42</v>
+        <v>1115</v>
       </c>
       <c r="B101" t="s">
-        <v>301</v>
+        <v>1116</v>
+      </c>
+      <c r="C101" s="10" t="s">
+        <v>1971</v>
       </c>
     </row>
     <row r="102" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>1110</v>
+        <v>1258</v>
       </c>
       <c r="B102" t="s">
-        <v>1111</v>
+        <v>1259</v>
+      </c>
+      <c r="C102" s="1" t="s">
+        <v>1928</v>
       </c>
     </row>
     <row r="103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>21</v>
+        <v>1651</v>
       </c>
       <c r="B103" t="s">
-        <v>22</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="B104" t="s">
-        <v>1719</v>
+        <v>109</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>571</v>
+        <v>99</v>
       </c>
       <c r="B105" t="s">
-        <v>663</v>
+        <v>100</v>
       </c>
     </row>
     <row r="106" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="B106" t="s">
-        <v>433</v>
+        <v>934</v>
       </c>
     </row>
     <row r="107" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>251</v>
+        <v>522</v>
       </c>
       <c r="B107" t="s">
-        <v>553</v>
+        <v>803</v>
       </c>
     </row>
     <row r="108" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>723</v>
+        <v>262</v>
       </c>
       <c r="B108" t="s">
-        <v>724</v>
+        <v>1216</v>
+      </c>
+      <c r="C108" s="10" t="s">
+        <v>1972</v>
       </c>
     </row>
     <row r="109" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>784</v>
+        <v>1117</v>
       </c>
       <c r="B109" t="s">
-        <v>1650</v>
+        <v>1118</v>
       </c>
     </row>
     <row r="110" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>525</v>
+        <v>157</v>
       </c>
       <c r="B110" t="s">
-        <v>526</v>
+        <v>158</v>
       </c>
     </row>
     <row r="111" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>50</v>
+        <v>898</v>
       </c>
       <c r="B111" t="s">
-        <v>51</v>
+        <v>1416</v>
       </c>
     </row>
     <row r="112" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>1251</v>
+        <v>644</v>
       </c>
       <c r="B112" t="s">
-        <v>1252</v>
-      </c>
-    </row>
-    <row r="113" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="113" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>811</v>
+        <v>1417</v>
       </c>
       <c r="B113" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="114" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1418</v>
+      </c>
+    </row>
+    <row r="114" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>1113</v>
+        <v>937</v>
       </c>
       <c r="B114" t="s">
-        <v>1114</v>
-      </c>
-    </row>
-    <row r="115" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="115" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>1255</v>
+        <v>1262</v>
       </c>
       <c r="B115" t="s">
-        <v>1256</v>
-      </c>
-    </row>
-    <row r="116" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="116" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>814</v>
+        <v>42</v>
       </c>
       <c r="B116" t="s">
-        <v>815</v>
-      </c>
-    </row>
-    <row r="117" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="117" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>1115</v>
+        <v>557</v>
       </c>
       <c r="B117" t="s">
-        <v>1116</v>
-      </c>
-      <c r="C117" s="10" t="s">
-        <v>1971</v>
-      </c>
-    </row>
-    <row r="118" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="118" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>1258</v>
+        <v>1138</v>
       </c>
       <c r="B118" t="s">
-        <v>1259</v>
-      </c>
-      <c r="C118" s="1" t="s">
-        <v>1928</v>
-      </c>
-    </row>
-    <row r="119" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="119" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>1651</v>
+        <v>677</v>
       </c>
       <c r="B119" t="s">
-        <v>1652</v>
-      </c>
-    </row>
-    <row r="120" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="120" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>108</v>
+        <v>1420</v>
       </c>
       <c r="B120" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="121" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="121" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>481</v>
+        <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="122" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1422</v>
+      </c>
+    </row>
+    <row r="122" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>99</v>
+        <v>939</v>
       </c>
       <c r="B122" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="123" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="123" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>418</v>
+        <v>1269</v>
       </c>
       <c r="B123" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="124" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>522</v>
+        <v>1423</v>
       </c>
       <c r="B124" t="s">
-        <v>803</v>
-      </c>
-    </row>
-    <row r="125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="125" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>262</v>
+        <v>161</v>
       </c>
       <c r="B125" t="s">
-        <v>1216</v>
-      </c>
-      <c r="C125" s="10" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="126" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>1117</v>
+        <v>1273</v>
       </c>
       <c r="B126" t="s">
-        <v>1118</v>
-      </c>
-    </row>
-    <row r="127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" t="s">
-        <v>157</v>
-      </c>
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="127" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B127" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="128" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="128" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>898</v>
+        <v>42</v>
       </c>
       <c r="B128" t="s">
-        <v>1416</v>
+        <v>56</v>
       </c>
     </row>
     <row r="129" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>644</v>
+        <v>55</v>
       </c>
       <c r="B129" t="s">
-        <v>645</v>
+        <v>56</v>
       </c>
     </row>
     <row r="130" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>1417</v>
+        <v>201</v>
       </c>
       <c r="B130" t="s">
-        <v>1418</v>
+        <v>303</v>
       </c>
     </row>
     <row r="131" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>937</v>
+        <v>387</v>
       </c>
       <c r="B131" t="s">
-        <v>938</v>
+        <v>666</v>
       </c>
     </row>
     <row r="132" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>1262</v>
+        <v>639</v>
       </c>
       <c r="B132" t="s">
-        <v>1263</v>
+        <v>669</v>
       </c>
     </row>
     <row r="133" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>42</v>
+        <v>1341</v>
       </c>
       <c r="B133" t="s">
-        <v>185</v>
+        <v>1529</v>
       </c>
     </row>
     <row r="134" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>555</v>
+        <v>898</v>
       </c>
       <c r="B134" t="s">
-        <v>556</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="135" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>24</v>
+        <v>435</v>
       </c>
       <c r="B135" t="s">
-        <v>25</v>
+        <v>436</v>
       </c>
     </row>
     <row r="136" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>557</v>
+        <v>77</v>
       </c>
       <c r="B136" t="s">
-        <v>558</v>
+        <v>436</v>
       </c>
     </row>
     <row r="137" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>1138</v>
+        <v>890</v>
       </c>
       <c r="B137" t="s">
-        <v>1266</v>
+        <v>1275</v>
       </c>
     </row>
     <row r="138" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>677</v>
+        <v>77</v>
       </c>
       <c r="B138" t="s">
-        <v>678</v>
+        <v>165</v>
       </c>
     </row>
     <row r="139" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>1420</v>
+        <v>811</v>
       </c>
       <c r="B139" t="s">
-        <v>1421</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="140" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>138</v>
+        <v>942</v>
       </c>
       <c r="B140" t="s">
-        <v>1422</v>
+        <v>943</v>
       </c>
     </row>
     <row r="141" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>939</v>
+        <v>723</v>
       </c>
       <c r="B141" t="s">
-        <v>940</v>
+        <v>823</v>
       </c>
     </row>
     <row r="142" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>1269</v>
+        <v>340</v>
       </c>
       <c r="B142" t="s">
-        <v>1270</v>
+        <v>823</v>
       </c>
     </row>
     <row r="143" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>956</v>
+        <v>1547</v>
       </c>
       <c r="B143" t="s">
-        <v>1119</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="144" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
-        <v>1423</v>
+        <v>1278</v>
       </c>
       <c r="B144" t="s">
-        <v>1424</v>
-      </c>
-    </row>
-    <row r="145" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
-        <v>161</v>
+        <v>262</v>
       </c>
       <c r="B145" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="146" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
-        <v>1273</v>
+        <v>262</v>
       </c>
       <c r="B146" t="s">
-        <v>1274</v>
-      </c>
-    </row>
-    <row r="147" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>818</v>
+        <v>192</v>
       </c>
       <c r="B147" t="s">
-        <v>819</v>
-      </c>
-    </row>
-    <row r="148" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>188</v>
+      </c>
       <c r="B148" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="149" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>42</v>
+        <v>1258</v>
       </c>
       <c r="B149" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="150" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1282</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="B150" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="151" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>201</v>
+        <v>340</v>
       </c>
       <c r="B151" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="152" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+      <c r="C151" s="10" t="s">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>387</v>
+        <v>1127</v>
       </c>
       <c r="B152" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="153" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1128</v>
+      </c>
+      <c r="C152" s="10" t="s">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
-        <v>639</v>
+        <v>1127</v>
       </c>
       <c r="B153" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="154" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1130</v>
+      </c>
+      <c r="C153" s="10" t="s">
+        <v>1975</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
-        <v>1341</v>
+        <v>775</v>
       </c>
       <c r="B154" t="s">
-        <v>1529</v>
-      </c>
-    </row>
-    <row r="155" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
-        <v>898</v>
+        <v>442</v>
       </c>
       <c r="B155" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="156" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
-        <v>435</v>
+        <v>442</v>
       </c>
       <c r="B156" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="157" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
-        <v>77</v>
+        <v>1258</v>
       </c>
       <c r="B157" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="158" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
-        <v>890</v>
+        <v>168</v>
       </c>
       <c r="B158" t="s">
-        <v>1275</v>
-      </c>
-    </row>
-    <row r="159" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
-        <v>1120</v>
+        <v>671</v>
       </c>
       <c r="B159" t="s">
-        <v>1121</v>
-      </c>
-    </row>
-    <row r="160" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="B160" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="161" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>559</v>
+        <v>1654</v>
       </c>
       <c r="B161" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="162" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>1736</v>
+        <v>1431</v>
       </c>
       <c r="B162" t="s">
-        <v>1737</v>
-      </c>
-    </row>
-    <row r="163" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>811</v>
+        <v>381</v>
       </c>
       <c r="B163" t="s">
-        <v>1277</v>
-      </c>
-    </row>
-    <row r="164" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>942</v>
+        <v>1284</v>
       </c>
       <c r="B164" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="165" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1285</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>723</v>
+        <v>366</v>
       </c>
       <c r="B165" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="166" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>340</v>
+        <v>1214</v>
       </c>
       <c r="B166" t="s">
-        <v>823</v>
-      </c>
-    </row>
-    <row r="167" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>1547</v>
+        <v>1435</v>
       </c>
       <c r="B167" t="s">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="168" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>330</v>
+        <v>1392</v>
       </c>
       <c r="B168" t="s">
-        <v>1124</v>
-      </c>
-    </row>
-    <row r="169" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="169" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>1278</v>
+        <v>1289</v>
       </c>
       <c r="B169" t="s">
-        <v>1279</v>
-      </c>
-    </row>
-    <row r="170" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="170" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>262</v>
+        <v>1162</v>
       </c>
       <c r="B170" t="s">
-        <v>1125</v>
-      </c>
-    </row>
-    <row r="171" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="171" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>262</v>
+        <v>325</v>
       </c>
       <c r="B171" t="s">
-        <v>447</v>
-      </c>
-    </row>
-    <row r="172" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="172" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>192</v>
+        <v>1132</v>
       </c>
       <c r="B172" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="173" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1133</v>
+      </c>
+      <c r="C172" s="10" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="173" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>188</v>
+        <v>1293</v>
       </c>
       <c r="B173" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="174" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
-        <v>1258</v>
+        <v>276</v>
       </c>
       <c r="B174" t="s">
-        <v>1282</v>
-      </c>
-    </row>
-    <row r="175" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="175" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
-        <v>39</v>
+        <v>279</v>
       </c>
       <c r="B175" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="176" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="176" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B176" t="s">
-        <v>439</v>
+        <v>1552</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
-        <v>340</v>
+        <v>512</v>
       </c>
       <c r="B177" t="s">
-        <v>913</v>
-      </c>
-      <c r="C177" s="10" t="s">
-        <v>1973</v>
+        <v>836</v>
       </c>
     </row>
     <row r="178" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
-        <v>1127</v>
+        <v>723</v>
       </c>
       <c r="B178" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C178" s="10" t="s">
-        <v>1974</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="179" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>1127</v>
+        <v>1632</v>
       </c>
       <c r="B179" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C179" s="10" t="s">
-        <v>1975</v>
+        <v>1633</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>775</v>
+        <v>1135</v>
       </c>
       <c r="B180" t="s">
-        <v>824</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="181" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>442</v>
+        <v>1258</v>
       </c>
       <c r="B181" t="s">
-        <v>443</v>
+        <v>1437</v>
       </c>
     </row>
     <row r="182" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>442</v>
+        <v>366</v>
       </c>
       <c r="B182" t="s">
-        <v>445</v>
+        <v>693</v>
       </c>
     </row>
     <row r="183" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>1258</v>
+        <v>952</v>
       </c>
       <c r="B183" t="s">
-        <v>1427</v>
+        <v>953</v>
       </c>
     </row>
     <row r="184" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
-        <v>168</v>
+        <v>1138</v>
       </c>
       <c r="B184" t="s">
-        <v>169</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="185" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
-        <v>671</v>
+        <v>330</v>
       </c>
       <c r="B185" t="s">
-        <v>672</v>
+        <v>331</v>
       </c>
     </row>
     <row r="186" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>35</v>
+        <v>956</v>
       </c>
       <c r="B186" t="s">
-        <v>36</v>
+        <v>957</v>
       </c>
     </row>
     <row r="187" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>1654</v>
+        <v>1555</v>
       </c>
       <c r="B187" t="s">
-        <v>1655</v>
+        <v>1556</v>
+      </c>
+      <c r="C187" s="1" t="s">
+        <v>1929</v>
       </c>
     </row>
     <row r="188" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>1431</v>
+        <v>102</v>
       </c>
       <c r="B188" t="s">
-        <v>1432</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1439</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
-        <v>381</v>
+        <v>435</v>
       </c>
       <c r="B189" t="s">
-        <v>563</v>
+        <v>839</v>
       </c>
     </row>
     <row r="190" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>251</v>
+        <v>377</v>
       </c>
       <c r="B190" t="s">
-        <v>564</v>
+        <v>378</v>
       </c>
     </row>
     <row r="191" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
-        <v>1284</v>
+        <v>775</v>
       </c>
       <c r="B191" t="s">
-        <v>1285</v>
+        <v>776</v>
       </c>
     </row>
     <row r="192" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>366</v>
+        <v>890</v>
       </c>
       <c r="B192" t="s">
-        <v>367</v>
+        <v>1296</v>
       </c>
     </row>
     <row r="193" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>1214</v>
+        <v>1298</v>
       </c>
       <c r="B193" t="s">
-        <v>367</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="194" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>1435</v>
+        <v>775</v>
       </c>
       <c r="B194" t="s">
-        <v>367</v>
+        <v>1440</v>
       </c>
     </row>
     <row r="195" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
-        <v>1392</v>
+        <v>195</v>
       </c>
       <c r="B195" t="s">
-        <v>1393</v>
+        <v>196</v>
       </c>
     </row>
     <row r="196" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
-        <v>1289</v>
+        <v>282</v>
       </c>
       <c r="B196" t="s">
-        <v>1290</v>
+        <v>283</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
-        <v>1162</v>
+        <v>960</v>
       </c>
       <c r="B197" t="s">
-        <v>1550</v>
+        <v>961</v>
       </c>
     </row>
     <row r="198" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
-        <v>325</v>
+        <v>171</v>
       </c>
       <c r="B198" t="s">
-        <v>326</v>
+        <v>172</v>
       </c>
     </row>
     <row r="199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
-        <v>1132</v>
+        <v>696</v>
       </c>
       <c r="B199" t="s">
-        <v>1133</v>
-      </c>
-      <c r="C199" s="10" t="s">
-        <v>1977</v>
+        <v>697</v>
       </c>
     </row>
     <row r="200" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
-        <v>1293</v>
+        <v>1140</v>
       </c>
       <c r="B200" t="s">
-        <v>1294</v>
+        <v>1141</v>
+      </c>
+      <c r="C200" s="10" t="s">
+        <v>1978</v>
       </c>
     </row>
     <row r="201" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
-        <v>276</v>
+        <v>1255</v>
       </c>
       <c r="B201" t="s">
-        <v>277</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
-        <v>637</v>
+        <v>268</v>
       </c>
       <c r="B202" t="s">
-        <v>638</v>
+        <v>844</v>
       </c>
     </row>
     <row r="203" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>1210</v>
+        <v>845</v>
       </c>
       <c r="B203" t="s">
-        <v>1211</v>
+        <v>844</v>
       </c>
     </row>
     <row r="204" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="B204" t="s">
-        <v>280</v>
+        <v>846</v>
       </c>
     </row>
     <row r="205" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="B205" t="s">
-        <v>1552</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="206" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>512</v>
+        <v>1443</v>
       </c>
       <c r="B206" t="s">
-        <v>836</v>
+        <v>1444</v>
       </c>
     </row>
     <row r="207" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>723</v>
+        <v>849</v>
       </c>
       <c r="B207" t="s">
-        <v>1656</v>
+        <v>850</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>1632</v>
+        <v>181</v>
       </c>
       <c r="B208" t="s">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="209" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>851</v>
+      </c>
+    </row>
+    <row r="209" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
-        <v>1135</v>
+        <v>1143</v>
       </c>
       <c r="B209" t="s">
-        <v>1136</v>
-      </c>
-    </row>
-    <row r="210" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="210" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>1258</v>
+        <v>306</v>
       </c>
       <c r="B210" t="s">
-        <v>1437</v>
-      </c>
-    </row>
-    <row r="211" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="211" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>366</v>
+        <v>1558</v>
       </c>
       <c r="B211" t="s">
-        <v>693</v>
-      </c>
-    </row>
-    <row r="212" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="212" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>1753</v>
+        <v>1560</v>
       </c>
       <c r="B212" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="213" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="213" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>578</v>
+        <v>852</v>
       </c>
       <c r="B213" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="214" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="214" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>952</v>
+        <v>42</v>
       </c>
       <c r="B214" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="215" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="215" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
+        <v>811</v>
+      </c>
+      <c r="B215" t="s">
+        <v>1146</v>
+      </c>
+    </row>
+    <row r="216" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>115</v>
+      </c>
+      <c r="B216" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="217" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>458</v>
+      </c>
+      <c r="B217" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="218" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>462</v>
+      </c>
+      <c r="B218" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="219" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>381</v>
+      </c>
+      <c r="B219" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="220" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>174</v>
+      </c>
+      <c r="B220" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="221" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>583</v>
+      </c>
+      <c r="B221" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="222" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>77</v>
+      </c>
+      <c r="B222" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="223" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>964</v>
+      </c>
+      <c r="B223" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="224" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>192</v>
+      </c>
+      <c r="B224" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="225" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>110</v>
+      </c>
+      <c r="B225" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="226" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B226" t="s">
+        <v>1446</v>
+      </c>
+    </row>
+    <row r="227" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>1657</v>
+      </c>
+      <c r="B227" t="s">
+        <v>1658</v>
+      </c>
+    </row>
+    <row r="228" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>1304</v>
+      </c>
+      <c r="B228" t="s">
+        <v>1305</v>
+      </c>
+    </row>
+    <row r="229" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B229" t="s">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="230" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>967</v>
+      </c>
+      <c r="B230" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="231" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>57</v>
+      </c>
+      <c r="B231" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="232" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>890</v>
+      </c>
+      <c r="B232" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="233" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>221</v>
+      </c>
+      <c r="B233" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="234" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
         <v>1138</v>
       </c>
-      <c r="B215" t="s">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="216" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>580</v>
-      </c>
-      <c r="B216" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="217" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" t="s">
-        <v>330</v>
-      </c>
-      <c r="B217" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="218" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" t="s">
-        <v>956</v>
-      </c>
-      <c r="B218" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="219" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>1555</v>
-      </c>
-      <c r="B219" t="s">
-        <v>1556</v>
-      </c>
-      <c r="C219" s="1" t="s">
-        <v>1929</v>
-      </c>
-    </row>
-    <row r="220" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>102</v>
-      </c>
-      <c r="B220" t="s">
-        <v>1439</v>
-      </c>
-    </row>
-    <row r="221" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>435</v>
-      </c>
-      <c r="B221" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="222" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>364</v>
-      </c>
-      <c r="B222" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="223" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>377</v>
-      </c>
-      <c r="B223" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="224" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>775</v>
-      </c>
-      <c r="B224" t="s">
-        <v>776</v>
-      </c>
-    </row>
-    <row r="225" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" t="s">
-        <v>890</v>
-      </c>
-      <c r="B225" t="s">
-        <v>1296</v>
-      </c>
-    </row>
-    <row r="226" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B226" t="s">
-        <v>1139</v>
-      </c>
-    </row>
-    <row r="227" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" t="s">
-        <v>842</v>
-      </c>
-      <c r="B227" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="228" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B228" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="229" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>775</v>
-      </c>
-      <c r="B229" t="s">
-        <v>1440</v>
-      </c>
-    </row>
-    <row r="230" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>251</v>
-      </c>
-      <c r="B230" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="231" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>195</v>
-      </c>
-      <c r="B231" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="232" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>282</v>
-      </c>
-      <c r="B232" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="233" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>960</v>
-      </c>
-      <c r="B233" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="234" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" t="s">
-        <v>171</v>
-      </c>
       <c r="B234" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="235" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1308</v>
+      </c>
+    </row>
+    <row r="235" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>696</v>
+        <v>1127</v>
       </c>
       <c r="B235" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="236" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1447</v>
+      </c>
+    </row>
+    <row r="236" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>1140</v>
+        <v>699</v>
       </c>
       <c r="B236" t="s">
-        <v>1141</v>
-      </c>
-      <c r="C236" s="10" t="s">
-        <v>1978</v>
-      </c>
-    </row>
-    <row r="237" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="237" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
-        <v>1255</v>
+        <v>381</v>
       </c>
       <c r="B237" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="238" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="238" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>268</v>
+        <v>704</v>
       </c>
       <c r="B238" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="239" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>845</v>
+        <v>707</v>
       </c>
       <c r="B239" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="240" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>268</v>
+        <v>585</v>
       </c>
       <c r="B240" t="s">
-        <v>846</v>
+        <v>586</v>
       </c>
     </row>
     <row r="241" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>102</v>
+        <v>1269</v>
       </c>
       <c r="B241" t="s">
-        <v>1302</v>
+        <v>1310</v>
       </c>
     </row>
     <row r="242" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>442</v>
+        <v>1394</v>
       </c>
       <c r="B242" t="s">
-        <v>847</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="243" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
-        <v>1443</v>
+        <v>73</v>
       </c>
       <c r="B243" t="s">
-        <v>1444</v>
+        <v>342</v>
       </c>
     </row>
     <row r="244" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
-        <v>849</v>
+        <v>224</v>
       </c>
       <c r="B244" t="s">
-        <v>850</v>
+        <v>225</v>
       </c>
     </row>
     <row r="245" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
-        <v>181</v>
+        <v>811</v>
       </c>
       <c r="B245" t="s">
-        <v>851</v>
+        <v>1451</v>
       </c>
     </row>
     <row r="246" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
-        <v>1143</v>
+        <v>1365</v>
       </c>
       <c r="B246" t="s">
-        <v>1144</v>
+        <v>1530</v>
       </c>
     </row>
     <row r="247" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
-        <v>306</v>
+        <v>1659</v>
       </c>
       <c r="B247" t="s">
-        <v>307</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="248" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
-        <v>1558</v>
+        <v>324</v>
       </c>
       <c r="B248" t="s">
-        <v>1559</v>
+        <v>709</v>
       </c>
     </row>
     <row r="249" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
-        <v>1560</v>
+        <v>201</v>
       </c>
       <c r="B249" t="s">
-        <v>1561</v>
+        <v>202</v>
       </c>
     </row>
     <row r="250" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
-        <v>852</v>
+        <v>27</v>
       </c>
       <c r="B250" t="s">
-        <v>853</v>
+        <v>208</v>
       </c>
     </row>
     <row r="251" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>42</v>
+        <v>435</v>
       </c>
       <c r="B251" t="s">
-        <v>43</v>
+        <v>857</v>
       </c>
     </row>
     <row r="252" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>565</v>
+        <v>972</v>
       </c>
       <c r="B252" t="s">
-        <v>1761</v>
+        <v>973</v>
       </c>
     </row>
     <row r="253" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>811</v>
+        <v>1454</v>
       </c>
       <c r="B253" t="s">
-        <v>1146</v>
+        <v>1455</v>
       </c>
     </row>
     <row r="254" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
-        <v>1762</v>
+        <v>1374</v>
       </c>
       <c r="B254" t="s">
-        <v>1763</v>
+        <v>1375</v>
       </c>
     </row>
     <row r="255" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
-        <v>711</v>
+        <v>227</v>
       </c>
       <c r="B255" t="s">
-        <v>1763</v>
+        <v>228</v>
       </c>
     </row>
     <row r="256" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
-        <v>115</v>
+        <v>1661</v>
       </c>
       <c r="B256" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="257" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1662</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>458</v>
+        <v>282</v>
       </c>
       <c r="B257" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="258" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>462</v>
+        <v>77</v>
       </c>
       <c r="B258" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="259" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>381</v>
+        <v>689</v>
       </c>
       <c r="B259" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="260" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
-        <v>174</v>
+        <v>282</v>
       </c>
       <c r="B260" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="261" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
-        <v>583</v>
+        <v>231</v>
       </c>
       <c r="B261" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="262" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
-        <v>1148</v>
+        <v>976</v>
       </c>
       <c r="B262" t="s">
-        <v>1149</v>
-      </c>
-    </row>
-    <row r="263" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>977</v>
+      </c>
+      <c r="C262" s="1" t="s">
+        <v>1930</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
-        <v>77</v>
+        <v>898</v>
       </c>
       <c r="B263" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="264" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>980</v>
+      </c>
+      <c r="C263" s="1" t="s">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
-        <v>964</v>
+        <v>1564</v>
       </c>
       <c r="B264" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="265" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1565</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
-        <v>192</v>
+        <v>470</v>
       </c>
       <c r="B265" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="266" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
-        <v>110</v>
+        <v>188</v>
       </c>
       <c r="B266" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="267" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
-        <v>1445</v>
+        <v>224</v>
       </c>
       <c r="B267" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="268" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
-        <v>1657</v>
+        <v>1154</v>
       </c>
       <c r="B268" t="s">
-        <v>1658</v>
-      </c>
-    </row>
-    <row r="269" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
-        <v>1304</v>
+        <v>711</v>
       </c>
       <c r="B269" t="s">
-        <v>1305</v>
-      </c>
-    </row>
-    <row r="270" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
-        <v>1562</v>
+        <v>188</v>
       </c>
       <c r="B270" t="s">
-        <v>1563</v>
-      </c>
-    </row>
-    <row r="271" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1311</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
-        <v>967</v>
+        <v>512</v>
       </c>
       <c r="B271" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="272" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>57</v>
+        <v>1115</v>
       </c>
       <c r="B272" t="s">
-        <v>58</v>
+        <v>1313</v>
       </c>
     </row>
     <row r="273" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>224</v>
+        <v>1514</v>
       </c>
       <c r="B273" t="s">
-        <v>339</v>
+        <v>1515</v>
       </c>
     </row>
     <row r="274" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>890</v>
+        <v>714</v>
       </c>
       <c r="B274" t="s">
-        <v>971</v>
+        <v>715</v>
       </c>
     </row>
     <row r="275" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>221</v>
+        <v>1207</v>
       </c>
       <c r="B275" t="s">
-        <v>222</v>
+        <v>1524</v>
       </c>
     </row>
     <row r="276" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
-        <v>1138</v>
+        <v>986</v>
       </c>
       <c r="B276" t="s">
-        <v>1308</v>
+        <v>987</v>
       </c>
     </row>
     <row r="277" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
-        <v>1127</v>
+        <v>251</v>
       </c>
       <c r="B277" t="s">
-        <v>1447</v>
+        <v>473</v>
       </c>
     </row>
     <row r="278" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>699</v>
+        <v>1315</v>
       </c>
       <c r="B278" t="s">
-        <v>700</v>
+        <v>1316</v>
       </c>
     </row>
     <row r="279" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>381</v>
+        <v>780</v>
       </c>
       <c r="B279" t="s">
-        <v>1448</v>
+        <v>781</v>
       </c>
     </row>
     <row r="280" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>704</v>
+        <v>387</v>
       </c>
       <c r="B280" t="s">
-        <v>705</v>
+        <v>681</v>
       </c>
     </row>
     <row r="281" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>707</v>
+        <v>1458</v>
       </c>
       <c r="B281" t="s">
-        <v>705</v>
+        <v>1459</v>
       </c>
     </row>
     <row r="282" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
-        <v>340</v>
+        <v>1063</v>
       </c>
       <c r="B282" t="s">
-        <v>341</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="283" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
-        <v>585</v>
+        <v>81</v>
       </c>
       <c r="B283" t="s">
-        <v>586</v>
+        <v>234</v>
       </c>
     </row>
     <row r="284" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
-        <v>1269</v>
+        <v>1318</v>
       </c>
       <c r="B284" t="s">
-        <v>1310</v>
+        <v>1319</v>
       </c>
     </row>
     <row r="285" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
-        <v>1394</v>
+        <v>1063</v>
       </c>
       <c r="B285" t="s">
-        <v>1395</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="286" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>1773</v>
+        <v>458</v>
       </c>
       <c r="B286" t="s">
-        <v>1774</v>
+        <v>459</v>
       </c>
     </row>
     <row r="287" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>73</v>
+        <v>1635</v>
       </c>
       <c r="B287" t="s">
-        <v>342</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="288" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>224</v>
+        <v>1567</v>
       </c>
       <c r="B288" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="289" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1568</v>
+      </c>
+    </row>
+    <row r="289" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>811</v>
+        <v>1321</v>
       </c>
       <c r="B289" t="s">
-        <v>1451</v>
-      </c>
-    </row>
-    <row r="290" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1322</v>
+      </c>
+    </row>
+    <row r="290" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>1365</v>
+        <v>717</v>
       </c>
       <c r="B290" t="s">
-        <v>1530</v>
-      </c>
-    </row>
-    <row r="291" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" t="s">
-        <v>1659</v>
-      </c>
+        <v>718</v>
+      </c>
+    </row>
+    <row r="291" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B291" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="292" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1569</v>
+      </c>
+      <c r="C291" s="1" t="s">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="292" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>324</v>
+        <v>565</v>
       </c>
       <c r="B292" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="293" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="293" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
+        <v>639</v>
+      </c>
+      <c r="B293" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="294" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>1570</v>
+      </c>
+      <c r="B294" t="s">
+        <v>1571</v>
+      </c>
+    </row>
+    <row r="295" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A295" t="s">
+        <v>989</v>
+      </c>
+      <c r="B295" t="s">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="296" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A296" t="s">
+        <v>652</v>
+      </c>
+      <c r="B296" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="297" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B297" t="s">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="298" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>1575</v>
+      </c>
+      <c r="B298" t="s">
+        <v>1576</v>
+      </c>
+    </row>
+    <row r="299" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>1138</v>
+      </c>
+      <c r="B299" t="s">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="300" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>1578</v>
+      </c>
+      <c r="B300" t="s">
+        <v>1579</v>
+      </c>
+    </row>
+    <row r="301" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>1535</v>
+      </c>
+      <c r="B301" t="s">
+        <v>1536</v>
+      </c>
+    </row>
+    <row r="302" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B302" t="s">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="303" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>882</v>
+      </c>
+      <c r="B303" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="304" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>1667</v>
+      </c>
+      <c r="B304" t="s">
+        <v>1668</v>
+      </c>
+    </row>
+    <row r="305" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>1580</v>
+      </c>
+      <c r="B305" t="s">
+        <v>1581</v>
+      </c>
+    </row>
+    <row r="306" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A306" t="s">
+        <v>992</v>
+      </c>
+      <c r="B306" t="s">
+        <v>993</v>
+      </c>
+    </row>
+    <row r="307" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A307" t="s">
+        <v>1669</v>
+      </c>
+      <c r="B307" t="s">
+        <v>1670</v>
+      </c>
+    </row>
+    <row r="308" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A308" t="s">
+        <v>1462</v>
+      </c>
+      <c r="B308" t="s">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="309" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>340</v>
+      </c>
+      <c r="B309" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="310" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>57</v>
+      </c>
+      <c r="B310" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="311" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>340</v>
+      </c>
+      <c r="B311" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="312" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A312" t="s">
         <v>188</v>
       </c>
-      <c r="B293" t="s">
-        <v>332</v>
-      </c>
-    </row>
-    <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A294" t="s">
-        <v>333</v>
-      </c>
-      <c r="B294" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="295" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>201</v>
-      </c>
-      <c r="B295" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="296" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>204</v>
-      </c>
-      <c r="B296" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="297" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>27</v>
-      </c>
-      <c r="B297" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>435</v>
-      </c>
-      <c r="B298" t="s">
-        <v>857</v>
-      </c>
-    </row>
-    <row r="299" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>972</v>
-      </c>
-      <c r="B299" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="300" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" t="s">
-        <v>1454</v>
-      </c>
-      <c r="B300" t="s">
-        <v>1455</v>
-      </c>
-    </row>
-    <row r="301" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
-        <v>1150</v>
-      </c>
-      <c r="B301" t="s">
-        <v>1151</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A302" t="s">
-        <v>1374</v>
-      </c>
-      <c r="B302" t="s">
-        <v>1375</v>
-      </c>
-    </row>
-    <row r="303" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A303" t="s">
-        <v>227</v>
-      </c>
-      <c r="B303" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="304" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" t="s">
-        <v>1661</v>
-      </c>
-      <c r="B304" t="s">
-        <v>1662</v>
-      </c>
-    </row>
-    <row r="305" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A305" t="s">
-        <v>282</v>
-      </c>
-      <c r="B305" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="306" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A306" t="s">
-        <v>77</v>
-      </c>
-      <c r="B306" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="307" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" t="s">
-        <v>689</v>
-      </c>
-      <c r="B307" t="s">
-        <v>1215</v>
-      </c>
-    </row>
-    <row r="308" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>282</v>
-      </c>
-      <c r="B308" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="309" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A309" t="s">
-        <v>231</v>
-      </c>
-      <c r="B309" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="310" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" t="s">
-        <v>976</v>
-      </c>
-      <c r="B310" t="s">
-        <v>977</v>
-      </c>
-      <c r="C310" s="1" t="s">
-        <v>1930</v>
-      </c>
-    </row>
-    <row r="311" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" t="s">
+      <c r="B312" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="313" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A313" t="s">
+        <v>890</v>
+      </c>
+      <c r="B313" t="s">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="314" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A314" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B314" t="s">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="315" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A315" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B315" t="s">
+        <v>1672</v>
+      </c>
+    </row>
+    <row r="316" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A316" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B316" t="s">
+        <v>1465</v>
+      </c>
+    </row>
+    <row r="317" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>115</v>
+      </c>
+      <c r="B317" t="s">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="318" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A318" t="s">
         <v>898</v>
       </c>
-      <c r="B311" t="s">
-        <v>980</v>
-      </c>
-      <c r="C311" s="1" t="s">
-        <v>1931</v>
-      </c>
-    </row>
-    <row r="312" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A312" t="s">
-        <v>1564</v>
-      </c>
-      <c r="B312" t="s">
-        <v>1565</v>
-      </c>
-    </row>
-    <row r="313" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A313" t="s">
-        <v>470</v>
-      </c>
-      <c r="B313" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="314" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A314" t="s">
-        <v>188</v>
-      </c>
-      <c r="B314" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="315" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A315" t="s">
-        <v>195</v>
-      </c>
-      <c r="B315" t="s">
-        <v>1153</v>
-      </c>
-    </row>
-    <row r="316" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A316" t="s">
-        <v>224</v>
-      </c>
-      <c r="B316" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="317" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A317" t="s">
-        <v>248</v>
-      </c>
-      <c r="B317" t="s">
-        <v>860</v>
-      </c>
-    </row>
-    <row r="318" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A318" t="s">
-        <v>1154</v>
-      </c>
       <c r="B318" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="319" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1163</v>
+      </c>
+    </row>
+    <row r="319" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
-        <v>1154</v>
+        <v>609</v>
       </c>
       <c r="B319" t="s">
-        <v>1155</v>
-      </c>
-    </row>
-    <row r="320" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="320" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
-        <v>711</v>
+        <v>612</v>
       </c>
       <c r="B320" t="s">
-        <v>712</v>
+        <v>610</v>
       </c>
     </row>
     <row r="321" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
-        <v>1784</v>
+        <v>1000</v>
       </c>
       <c r="B321" t="s">
-        <v>1785</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="322" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
-        <v>188</v>
+        <v>1466</v>
       </c>
       <c r="B322" t="s">
-        <v>1311</v>
+        <v>1467</v>
       </c>
     </row>
     <row r="323" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
-        <v>512</v>
+        <v>442</v>
       </c>
       <c r="B323" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="324" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
-        <v>1786</v>
+        <v>736</v>
       </c>
       <c r="B324" t="s">
-        <v>1787</v>
+        <v>737</v>
       </c>
     </row>
     <row r="325" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
-        <v>1788</v>
+        <v>77</v>
       </c>
       <c r="B325" t="s">
-        <v>1787</v>
+        <v>104</v>
       </c>
     </row>
     <row r="326" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>1115</v>
+        <v>282</v>
       </c>
       <c r="B326" t="s">
-        <v>1313</v>
+        <v>738</v>
       </c>
     </row>
     <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
-        <v>591</v>
+        <v>1003</v>
       </c>
       <c r="B327" t="s">
-        <v>592</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
-        <v>593</v>
+        <v>236</v>
       </c>
       <c r="B328" t="s">
-        <v>594</v>
+        <v>237</v>
       </c>
     </row>
     <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
-        <v>1514</v>
+        <v>239</v>
       </c>
       <c r="B329" t="s">
-        <v>1515</v>
+        <v>237</v>
       </c>
     </row>
     <row r="330" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
-        <v>896</v>
+        <v>242</v>
       </c>
       <c r="B330" t="s">
-        <v>1789</v>
+        <v>243</v>
       </c>
     </row>
     <row r="331" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
-        <v>714</v>
+        <v>24</v>
       </c>
       <c r="B331" t="s">
-        <v>715</v>
+        <v>350</v>
       </c>
     </row>
     <row r="332" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
-        <v>1207</v>
+        <v>24</v>
       </c>
       <c r="B332" t="s">
-        <v>1524</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="333" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
-        <v>986</v>
+        <v>1055</v>
       </c>
       <c r="B333" t="s">
-        <v>987</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="334" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
-        <v>251</v>
+        <v>61</v>
       </c>
       <c r="B334" t="s">
-        <v>473</v>
+        <v>62</v>
       </c>
     </row>
     <row r="335" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
-        <v>1315</v>
+        <v>24</v>
       </c>
       <c r="B335" t="s">
-        <v>1316</v>
+        <v>62</v>
       </c>
     </row>
     <row r="336" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
-        <v>864</v>
+        <v>1162</v>
       </c>
       <c r="B336" t="s">
-        <v>865</v>
-      </c>
-    </row>
-    <row r="337" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="337" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
-        <v>780</v>
+        <v>73</v>
       </c>
       <c r="B337" t="s">
-        <v>781</v>
-      </c>
-    </row>
-    <row r="338" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="338" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
-        <v>387</v>
+        <v>372</v>
       </c>
       <c r="B338" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="339" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
-        <v>442</v>
+        <v>1586</v>
       </c>
       <c r="B339" t="s">
-        <v>1790</v>
-      </c>
-    </row>
-    <row r="340" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
-        <v>1458</v>
+        <v>204</v>
       </c>
       <c r="B340" t="s">
-        <v>1459</v>
-      </c>
-    </row>
-    <row r="341" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="341" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
-        <v>1063</v>
+        <v>740</v>
       </c>
       <c r="B341" t="s">
-        <v>1156</v>
-      </c>
-    </row>
-    <row r="342" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="342" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
-        <v>81</v>
+        <v>613</v>
       </c>
       <c r="B342" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="343" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="343" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
-        <v>1318</v>
+        <v>310</v>
       </c>
       <c r="B343" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="344" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="344" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
-        <v>1063</v>
+        <v>1673</v>
       </c>
       <c r="B344" t="s">
-        <v>1664</v>
-      </c>
-    </row>
-    <row r="345" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="345" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
-        <v>458</v>
+        <v>73</v>
       </c>
       <c r="B345" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="346" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A346" t="s">
-        <v>595</v>
-      </c>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="346" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B346" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="347" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="347" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
-        <v>597</v>
+        <v>1589</v>
       </c>
       <c r="B347" t="s">
-        <v>598</v>
-      </c>
-    </row>
-    <row r="348" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1590</v>
+      </c>
+    </row>
+    <row r="348" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
-        <v>600</v>
+        <v>1324</v>
       </c>
       <c r="B348" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="349" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="349" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
-        <v>1635</v>
+        <v>138</v>
       </c>
       <c r="B349" t="s">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="350" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1591</v>
+      </c>
+      <c r="C349" s="2" t="s">
+        <v>1933</v>
+      </c>
+    </row>
+    <row r="350" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
-        <v>1567</v>
+        <v>42</v>
       </c>
       <c r="B350" t="s">
-        <v>1568</v>
-      </c>
-    </row>
-    <row r="351" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="351" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>1321</v>
+        <v>1593</v>
       </c>
       <c r="B351" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="352" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1594</v>
+      </c>
+      <c r="C351" s="2" t="s">
+        <v>1934</v>
+      </c>
+    </row>
+    <row r="352" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
-        <v>717</v>
+        <v>871</v>
       </c>
       <c r="B352" t="s">
-        <v>718</v>
-      </c>
-    </row>
-    <row r="353" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="353" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A353" t="s">
+        <v>248</v>
+      </c>
       <c r="B353" t="s">
-        <v>1569</v>
-      </c>
-      <c r="C353" s="1" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="354" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="354" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
-        <v>550</v>
+        <v>1240</v>
       </c>
       <c r="B354" t="s">
-        <v>1157</v>
-      </c>
-    </row>
-    <row r="355" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1595</v>
+      </c>
+    </row>
+    <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>565</v>
       </c>
       <c r="B355" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="356" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
-        <v>603</v>
+        <v>66</v>
       </c>
       <c r="B356" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="357" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>239</v>
+        <v>138</v>
       </c>
       <c r="B357" t="s">
-        <v>1159</v>
-      </c>
-    </row>
-    <row r="358" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
-        <v>1795</v>
+        <v>481</v>
       </c>
       <c r="B358" t="s">
-        <v>1796</v>
-      </c>
-    </row>
-    <row r="359" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="359" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
-        <v>639</v>
+        <v>212</v>
       </c>
       <c r="B359" t="s">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="360" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="360" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
-        <v>1570</v>
+        <v>1009</v>
       </c>
       <c r="B360" t="s">
-        <v>1571</v>
-      </c>
-    </row>
-    <row r="361" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="361" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
-        <v>1160</v>
+        <v>251</v>
       </c>
       <c r="B361" t="s">
-        <v>1161</v>
-      </c>
-    </row>
-    <row r="362" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="362" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
-        <v>989</v>
+        <v>70</v>
       </c>
       <c r="B362" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="363" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="363" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
-        <v>652</v>
+        <v>831</v>
       </c>
       <c r="B363" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="364" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="364" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
-        <v>1572</v>
+        <v>39</v>
       </c>
       <c r="B364" t="s">
-        <v>1573</v>
-      </c>
-    </row>
-    <row r="365" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="365" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
-        <v>1575</v>
+        <v>1012</v>
       </c>
       <c r="B365" t="s">
-        <v>1576</v>
-      </c>
-    </row>
-    <row r="366" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="366" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
-        <v>1138</v>
+        <v>1469</v>
       </c>
       <c r="B366" t="s">
-        <v>1577</v>
-      </c>
-    </row>
-    <row r="367" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1470</v>
+      </c>
+    </row>
+    <row r="367" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
-        <v>1578</v>
+        <v>525</v>
       </c>
       <c r="B367" t="s">
-        <v>1579</v>
-      </c>
-    </row>
-    <row r="368" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="368" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>1535</v>
+        <v>1165</v>
       </c>
       <c r="B368" t="s">
-        <v>1536</v>
+        <v>1166</v>
       </c>
     </row>
     <row r="369" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
-        <v>1460</v>
+        <v>178</v>
       </c>
       <c r="B369" t="s">
-        <v>1461</v>
+        <v>179</v>
       </c>
     </row>
     <row r="370" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
-        <v>882</v>
+        <v>742</v>
       </c>
       <c r="B370" t="s">
-        <v>1666</v>
+        <v>743</v>
       </c>
     </row>
     <row r="371" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
-        <v>1667</v>
+        <v>484</v>
       </c>
       <c r="B371" t="s">
-        <v>1668</v>
+        <v>485</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>344</v>
+        <v>1471</v>
       </c>
       <c r="B372" t="s">
-        <v>345</v>
+        <v>1472</v>
       </c>
     </row>
     <row r="373" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
-        <v>251</v>
+        <v>699</v>
       </c>
       <c r="B373" t="s">
-        <v>862</v>
+        <v>1167</v>
       </c>
     </row>
     <row r="374" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
-        <v>1580</v>
+        <v>1328</v>
       </c>
       <c r="B374" t="s">
-        <v>1581</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="375" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
-        <v>992</v>
+        <v>1473</v>
       </c>
       <c r="B375" t="s">
-        <v>993</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="376" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
-        <v>1669</v>
+        <v>1331</v>
       </c>
       <c r="B376" t="s">
-        <v>1670</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="377" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
-        <v>1462</v>
+        <v>188</v>
       </c>
       <c r="B377" t="s">
-        <v>1463</v>
+        <v>875</v>
       </c>
     </row>
     <row r="378" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
-        <v>340</v>
+        <v>27</v>
       </c>
       <c r="B378" t="s">
-        <v>996</v>
+        <v>28</v>
       </c>
     </row>
     <row r="379" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>57</v>
+        <v>1598</v>
       </c>
       <c r="B379" t="s">
-        <v>605</v>
+        <v>1599</v>
       </c>
     </row>
     <row r="380" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
-        <v>340</v>
+        <v>1601</v>
       </c>
       <c r="B380" t="s">
-        <v>950</v>
+        <v>1602</v>
       </c>
     </row>
     <row r="381" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
-        <v>188</v>
+        <v>73</v>
       </c>
       <c r="B381" t="s">
-        <v>348</v>
+        <v>74</v>
       </c>
     </row>
     <row r="382" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
-        <v>890</v>
+        <v>1605</v>
       </c>
       <c r="B382" t="s">
-        <v>997</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="383" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
-        <v>1582</v>
+        <v>699</v>
       </c>
       <c r="B383" t="s">
-        <v>1583</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="384" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
-        <v>550</v>
+        <v>687</v>
       </c>
       <c r="B384" t="s">
-        <v>866</v>
+        <v>834</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
-        <v>550</v>
+        <v>1258</v>
       </c>
       <c r="B385" t="s">
-        <v>868</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="386" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
-        <v>1671</v>
+        <v>1474</v>
       </c>
       <c r="B386" t="s">
-        <v>1672</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="387" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
-        <v>1464</v>
+        <v>1335</v>
       </c>
       <c r="B387" t="s">
-        <v>1465</v>
+        <v>1336</v>
       </c>
     </row>
     <row r="388" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
-        <v>251</v>
+        <v>458</v>
       </c>
       <c r="B388" t="s">
-        <v>608</v>
+        <v>486</v>
       </c>
     </row>
     <row r="389" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
-        <v>115</v>
+        <v>1338</v>
       </c>
       <c r="B389" t="s">
-        <v>734</v>
+        <v>1339</v>
       </c>
     </row>
     <row r="390" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
-        <v>898</v>
+        <v>1608</v>
       </c>
       <c r="B390" t="s">
-        <v>1163</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="391" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>609</v>
+        <v>1675</v>
       </c>
       <c r="B391" t="s">
-        <v>610</v>
+        <v>1676</v>
       </c>
     </row>
     <row r="392" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>612</v>
+        <v>1526</v>
       </c>
       <c r="B392" t="s">
-        <v>610</v>
+        <v>1527</v>
       </c>
     </row>
     <row r="393" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>613</v>
+        <v>745</v>
       </c>
       <c r="B393" t="s">
-        <v>614</v>
+        <v>746</v>
       </c>
     </row>
     <row r="394" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
-        <v>1000</v>
+        <v>1475</v>
       </c>
       <c r="B394" t="s">
-        <v>1001</v>
+        <v>1476</v>
       </c>
     </row>
     <row r="395" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
-        <v>1466</v>
+        <v>726</v>
       </c>
       <c r="B395" t="s">
-        <v>1467</v>
+        <v>727</v>
       </c>
     </row>
     <row r="396" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
-        <v>442</v>
+        <v>1138</v>
       </c>
       <c r="B396" t="s">
-        <v>514</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="397" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
-        <v>736</v>
+        <v>1015</v>
       </c>
       <c r="B397" t="s">
-        <v>737</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="398" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
-        <v>77</v>
+        <v>1018</v>
       </c>
       <c r="B398" t="s">
-        <v>104</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="399" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
-        <v>282</v>
+        <v>319</v>
       </c>
       <c r="B399" t="s">
-        <v>738</v>
+        <v>489</v>
       </c>
     </row>
     <row r="400" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
-        <v>1003</v>
+        <v>1611</v>
       </c>
       <c r="B400" t="s">
-        <v>1004</v>
+        <v>1612</v>
       </c>
     </row>
     <row r="401" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
-        <v>236</v>
+        <v>334</v>
       </c>
       <c r="B401" t="s">
-        <v>237</v>
+        <v>335</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
-        <v>239</v>
+        <v>956</v>
       </c>
       <c r="B402" t="s">
-        <v>237</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="403" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
-        <v>242</v>
+        <v>142</v>
       </c>
       <c r="B403" t="s">
-        <v>243</v>
+        <v>621</v>
       </c>
     </row>
     <row r="404" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
-        <v>24</v>
+        <v>571</v>
       </c>
       <c r="B404" t="s">
-        <v>350</v>
+        <v>782</v>
       </c>
     </row>
     <row r="405" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
-        <v>24</v>
+        <v>898</v>
       </c>
       <c r="B405" t="s">
-        <v>1006</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="406" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
-        <v>1055</v>
+        <v>253</v>
       </c>
       <c r="B406" t="s">
-        <v>1056</v>
+        <v>254</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>61</v>
+        <v>1179</v>
       </c>
       <c r="B407" t="s">
-        <v>62</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
-        <v>24</v>
+        <v>115</v>
       </c>
       <c r="B408" t="s">
-        <v>62</v>
+        <v>116</v>
       </c>
     </row>
     <row r="409" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
-        <v>1162</v>
+        <v>239</v>
       </c>
       <c r="B409" t="s">
-        <v>701</v>
+        <v>880</v>
       </c>
     </row>
     <row r="410" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
-        <v>73</v>
+        <v>1431</v>
       </c>
       <c r="B410" t="s">
-        <v>475</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="411" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
-        <v>372</v>
+        <v>425</v>
       </c>
       <c r="B411" t="s">
-        <v>477</v>
+        <v>491</v>
       </c>
     </row>
     <row r="412" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
-        <v>1586</v>
+        <v>1022</v>
       </c>
       <c r="B412" t="s">
-        <v>1587</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="413" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
-        <v>204</v>
+        <v>77</v>
       </c>
       <c r="B413" t="s">
-        <v>869</v>
+        <v>120</v>
       </c>
     </row>
     <row r="414" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
-        <v>740</v>
+        <v>1148</v>
       </c>
       <c r="B414" t="s">
-        <v>741</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="415" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
-        <v>613</v>
+        <v>898</v>
       </c>
       <c r="B415" t="s">
-        <v>1008</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="416" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
-        <v>310</v>
+        <v>24</v>
       </c>
       <c r="B416" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="417" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="417" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
-        <v>1673</v>
+        <v>1420</v>
       </c>
       <c r="B417" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="418" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1615</v>
+      </c>
+    </row>
+    <row r="418" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>458</v>
+        <v>212</v>
       </c>
       <c r="B418" t="s">
-        <v>1164</v>
-      </c>
-    </row>
-    <row r="419" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="419" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>73</v>
       </c>
       <c r="B419" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="420" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="420" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A420" t="s">
+        <v>898</v>
+      </c>
       <c r="B420" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="421" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1183</v>
+      </c>
+    </row>
+    <row r="421" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
-        <v>1589</v>
+        <v>622</v>
       </c>
       <c r="B421" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="422" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="422" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
-        <v>1324</v>
+        <v>453</v>
       </c>
       <c r="B422" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="423" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="423" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
-        <v>138</v>
+        <v>42</v>
       </c>
       <c r="B423" t="s">
-        <v>1591</v>
-      </c>
-      <c r="C423" s="2" t="s">
-        <v>1933</v>
-      </c>
-    </row>
-    <row r="424" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="424" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
-        <v>42</v>
+        <v>102</v>
       </c>
       <c r="B424" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="425" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="425" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
-        <v>1593</v>
+        <v>125</v>
       </c>
       <c r="B425" t="s">
-        <v>1594</v>
-      </c>
-      <c r="C425" s="2" t="s">
-        <v>1934</v>
-      </c>
-    </row>
-    <row r="426" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="426" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
-        <v>871</v>
+        <v>1341</v>
       </c>
       <c r="B426" t="s">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="427" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1342</v>
+      </c>
+    </row>
+    <row r="427" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="B427" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="428" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="428" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
-        <v>1240</v>
+        <v>435</v>
       </c>
       <c r="B428" t="s">
-        <v>1595</v>
-      </c>
-    </row>
-    <row r="429" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="429" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
-        <v>828</v>
+        <v>319</v>
       </c>
       <c r="B429" t="s">
-        <v>829</v>
-      </c>
-    </row>
-    <row r="430" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="430" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
-        <v>828</v>
+        <v>458</v>
       </c>
       <c r="B430" t="s">
-        <v>873</v>
-      </c>
-    </row>
-    <row r="431" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="431" spans="1:2" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="B431" t="s">
-        <v>874</v>
-      </c>
-    </row>
-    <row r="432" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="432" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
-        <v>66</v>
+        <v>340</v>
       </c>
       <c r="B432" t="s">
-        <v>67</v>
+        <v>748</v>
       </c>
     </row>
     <row r="433" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
-        <v>138</v>
+        <v>1482</v>
       </c>
       <c r="B433" t="s">
-        <v>1596</v>
+        <v>1483</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
-        <v>481</v>
+        <v>77</v>
       </c>
       <c r="B434" t="s">
-        <v>482</v>
+        <v>384</v>
       </c>
     </row>
     <row r="435" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>212</v>
+        <v>1298</v>
       </c>
       <c r="B435" t="s">
-        <v>352</v>
+        <v>1485</v>
       </c>
     </row>
     <row r="436" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
-        <v>615</v>
+        <v>1678</v>
       </c>
       <c r="B436" t="s">
-        <v>616</v>
+        <v>1679</v>
       </c>
     </row>
     <row r="437" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
-        <v>1009</v>
+        <v>1404</v>
       </c>
       <c r="B437" t="s">
-        <v>1010</v>
+        <v>1486</v>
       </c>
     </row>
     <row r="438" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
-        <v>251</v>
+        <v>750</v>
       </c>
       <c r="B438" t="s">
-        <v>252</v>
+        <v>751</v>
       </c>
     </row>
     <row r="439" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="B439" t="s">
-        <v>71</v>
+        <v>495</v>
       </c>
     </row>
     <row r="440" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
-        <v>831</v>
+        <v>77</v>
       </c>
       <c r="B440" t="s">
-        <v>832</v>
+        <v>78</v>
       </c>
     </row>
     <row r="441" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
-        <v>39</v>
+        <v>550</v>
       </c>
       <c r="B441" t="s">
-        <v>40</v>
+        <v>884</v>
       </c>
     </row>
     <row r="442" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>1012</v>
+        <v>550</v>
       </c>
       <c r="B442" t="s">
-        <v>1013</v>
+        <v>1343</v>
       </c>
     </row>
     <row r="443" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
-        <v>1469</v>
+        <v>265</v>
       </c>
       <c r="B443" t="s">
-        <v>1470</v>
+        <v>266</v>
       </c>
     </row>
     <row r="444" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
-        <v>525</v>
+        <v>188</v>
       </c>
       <c r="B444" t="s">
-        <v>649</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="445" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
-        <v>1165</v>
+        <v>885</v>
       </c>
       <c r="B445" t="s">
-        <v>1166</v>
+        <v>886</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
-        <v>178</v>
+        <v>319</v>
       </c>
       <c r="B446" t="s">
-        <v>179</v>
+        <v>320</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
-        <v>742</v>
+        <v>967</v>
       </c>
       <c r="B447" t="s">
-        <v>743</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="448" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
-        <v>484</v>
+        <v>262</v>
       </c>
       <c r="B448" t="s">
-        <v>485</v>
+        <v>888</v>
       </c>
     </row>
     <row r="449" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
-        <v>1471</v>
+        <v>1031</v>
       </c>
       <c r="B449" t="s">
-        <v>1472</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="450" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
-        <v>699</v>
+        <v>1487</v>
       </c>
       <c r="B450" t="s">
-        <v>1167</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="451" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
-        <v>1328</v>
+        <v>1344</v>
       </c>
       <c r="B451" t="s">
-        <v>1329</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="452" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
-        <v>1473</v>
+        <v>890</v>
       </c>
       <c r="B452" t="s">
-        <v>1332</v>
+        <v>891</v>
       </c>
     </row>
     <row r="453" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>1331</v>
+        <v>1464</v>
       </c>
       <c r="B453" t="s">
-        <v>1332</v>
+        <v>1490</v>
       </c>
     </row>
     <row r="454" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="B454" t="s">
-        <v>875</v>
+        <v>753</v>
       </c>
     </row>
     <row r="455" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
-        <v>27</v>
+        <v>1346</v>
       </c>
       <c r="B455" t="s">
-        <v>28</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="456" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
-        <v>1598</v>
+        <v>1349</v>
       </c>
       <c r="B456" t="s">
-        <v>1599</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="457" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
-        <v>1601</v>
+        <v>1035</v>
       </c>
       <c r="B457" t="s">
-        <v>1602</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="458" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
-        <v>1170</v>
+        <v>687</v>
       </c>
       <c r="B458" t="s">
-        <v>1171</v>
+        <v>688</v>
       </c>
     </row>
     <row r="459" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
-        <v>1172</v>
+        <v>627</v>
       </c>
       <c r="B459" t="s">
-        <v>1173</v>
+        <v>628</v>
       </c>
     </row>
     <row r="460" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
-        <v>73</v>
+        <v>630</v>
       </c>
       <c r="B460" t="s">
-        <v>74</v>
+        <v>631</v>
       </c>
     </row>
     <row r="461" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
-        <v>1605</v>
+        <v>1492</v>
       </c>
       <c r="B461" t="s">
-        <v>1606</v>
+        <v>1493</v>
       </c>
     </row>
     <row r="462" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
-        <v>77</v>
+        <v>908</v>
       </c>
       <c r="B462" t="s">
-        <v>618</v>
+        <v>909</v>
       </c>
     </row>
     <row r="463" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
-        <v>699</v>
+        <v>784</v>
       </c>
       <c r="B463" t="s">
-        <v>1333</v>
+        <v>785</v>
       </c>
     </row>
     <row r="464" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
-        <v>1832</v>
+        <v>42</v>
       </c>
       <c r="B464" t="s">
-        <v>1833</v>
+        <v>322</v>
       </c>
     </row>
     <row r="465" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
-        <v>876</v>
+        <v>324</v>
       </c>
       <c r="B465" t="s">
-        <v>877</v>
+        <v>322</v>
       </c>
     </row>
     <row r="466" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
-        <v>687</v>
+        <v>585</v>
       </c>
       <c r="B466" t="s">
-        <v>834</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="467" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
-        <v>1009</v>
+        <v>181</v>
       </c>
       <c r="B467" t="s">
-        <v>1834</v>
+        <v>182</v>
       </c>
     </row>
     <row r="468" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
-        <v>1258</v>
+        <v>319</v>
       </c>
       <c r="B468" t="s">
-        <v>1334</v>
+        <v>497</v>
       </c>
     </row>
     <row r="469" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
-        <v>1474</v>
+        <v>1404</v>
       </c>
       <c r="B469" t="s">
-        <v>1334</v>
+        <v>1532</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>1335</v>
+        <v>340</v>
       </c>
       <c r="B470" t="s">
-        <v>1336</v>
+        <v>1616</v>
       </c>
     </row>
     <row r="471" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
-        <v>458</v>
+        <v>1494</v>
       </c>
       <c r="B471" t="s">
-        <v>1174</v>
+        <v>1495</v>
       </c>
     </row>
     <row r="472" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
-        <v>458</v>
+        <v>1041</v>
       </c>
       <c r="B472" t="s">
-        <v>486</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="473" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
-        <v>1338</v>
+        <v>500</v>
       </c>
       <c r="B473" t="s">
-        <v>1339</v>
+        <v>501</v>
       </c>
     </row>
     <row r="474" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
-        <v>1608</v>
+        <v>755</v>
       </c>
       <c r="B474" t="s">
-        <v>1609</v>
+        <v>756</v>
       </c>
     </row>
     <row r="475" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
-        <v>1675</v>
+        <v>1044</v>
       </c>
       <c r="B475" t="s">
-        <v>1676</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="476" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
-        <v>1526</v>
+        <v>268</v>
       </c>
       <c r="B476" t="s">
-        <v>1527</v>
+        <v>269</v>
       </c>
     </row>
     <row r="477" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
-        <v>745</v>
+        <v>262</v>
       </c>
       <c r="B477" t="s">
-        <v>746</v>
+        <v>355</v>
       </c>
     </row>
     <row r="478" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
-        <v>1475</v>
+        <v>35</v>
       </c>
       <c r="B478" t="s">
-        <v>1476</v>
+        <v>355</v>
       </c>
     </row>
     <row r="479" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
-        <v>525</v>
+        <v>1352</v>
       </c>
       <c r="B479" t="s">
-        <v>619</v>
+        <v>1353</v>
       </c>
     </row>
     <row r="480" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
-        <v>1176</v>
+        <v>1186</v>
       </c>
       <c r="B480" t="s">
-        <v>1177</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="481" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
-        <v>726</v>
+        <v>138</v>
       </c>
       <c r="B481" t="s">
-        <v>727</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="482" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
-        <v>1138</v>
+        <v>1269</v>
       </c>
       <c r="B482" t="s">
-        <v>1610</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="483" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
-        <v>1015</v>
+        <v>1618</v>
       </c>
       <c r="B483" t="s">
-        <v>1016</v>
+        <v>1619</v>
       </c>
     </row>
     <row r="484" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
-        <v>1018</v>
+        <v>759</v>
       </c>
       <c r="B484" t="s">
-        <v>1019</v>
+        <v>760</v>
       </c>
     </row>
     <row r="485" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
-        <v>319</v>
+        <v>435</v>
       </c>
       <c r="B485" t="s">
-        <v>489</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="486" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
-        <v>1611</v>
+        <v>717</v>
       </c>
       <c r="B486" t="s">
-        <v>1612</v>
+        <v>787</v>
       </c>
     </row>
     <row r="487" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
-        <v>334</v>
+        <v>871</v>
       </c>
       <c r="B487" t="s">
-        <v>335</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="488" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
-        <v>956</v>
+        <v>789</v>
       </c>
       <c r="B488" t="s">
-        <v>1178</v>
+        <v>790</v>
       </c>
     </row>
     <row r="489" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
-        <v>878</v>
+        <v>1189</v>
       </c>
       <c r="B489" t="s">
-        <v>879</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="490" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
-        <v>142</v>
+        <v>1378</v>
       </c>
       <c r="B490" t="s">
-        <v>621</v>
+        <v>1379</v>
       </c>
     </row>
     <row r="491" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
-        <v>571</v>
+        <v>1533</v>
       </c>
       <c r="B491" t="s">
-        <v>782</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="492" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
-        <v>898</v>
+        <v>689</v>
       </c>
       <c r="B492" t="s">
-        <v>1020</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="493" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
-        <v>253</v>
+        <v>188</v>
       </c>
       <c r="B493" t="s">
-        <v>254</v>
+        <v>560</v>
       </c>
     </row>
     <row r="494" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
-        <v>1179</v>
+        <v>401</v>
       </c>
       <c r="B494" t="s">
-        <v>1180</v>
+        <v>1194</v>
       </c>
     </row>
     <row r="495" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
-        <v>565</v>
+        <v>42</v>
       </c>
       <c r="B495" t="s">
-        <v>1839</v>
+        <v>633</v>
       </c>
     </row>
     <row r="496" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
-        <v>115</v>
+        <v>319</v>
       </c>
       <c r="B496" t="s">
-        <v>116</v>
+        <v>633</v>
       </c>
     </row>
     <row r="497" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
-        <v>239</v>
+        <v>503</v>
       </c>
       <c r="B497" t="s">
-        <v>880</v>
+        <v>504</v>
       </c>
     </row>
     <row r="498" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
-        <v>1431</v>
+        <v>1356</v>
       </c>
       <c r="B498" t="s">
-        <v>1613</v>
+        <v>1357</v>
       </c>
     </row>
     <row r="499" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
-        <v>425</v>
+        <v>42</v>
       </c>
       <c r="B499" t="s">
-        <v>491</v>
+        <v>456</v>
       </c>
     </row>
     <row r="500" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
-        <v>1022</v>
+        <v>1217</v>
       </c>
       <c r="B500" t="s">
-        <v>1023</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="501" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
-        <v>77</v>
+        <v>1620</v>
       </c>
       <c r="B501" t="s">
-        <v>120</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="502" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
-        <v>1181</v>
+        <v>917</v>
       </c>
       <c r="B502" t="s">
-        <v>1182</v>
+        <v>918</v>
       </c>
     </row>
     <row r="503" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
-        <v>1148</v>
+        <v>81</v>
       </c>
       <c r="B503" t="s">
-        <v>1478</v>
+        <v>82</v>
       </c>
     </row>
     <row r="504" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>898</v>
+        <v>1138</v>
       </c>
       <c r="B504" t="s">
-        <v>1025</v>
+        <v>1359</v>
       </c>
     </row>
     <row r="505" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
-        <v>24</v>
+        <v>313</v>
       </c>
       <c r="B505" t="s">
-        <v>258</v>
+        <v>314</v>
       </c>
     </row>
     <row r="506" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
-        <v>882</v>
+        <v>684</v>
       </c>
       <c r="B506" t="s">
-        <v>883</v>
+        <v>1361</v>
       </c>
     </row>
     <row r="507" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>1420</v>
+        <v>1498</v>
       </c>
       <c r="B507" t="s">
-        <v>1615</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="508" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
-        <v>212</v>
+        <v>1138</v>
       </c>
       <c r="B508" t="s">
-        <v>213</v>
+        <v>1363</v>
       </c>
     </row>
     <row r="509" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
-        <v>73</v>
+        <v>324</v>
       </c>
       <c r="B509" t="s">
-        <v>213</v>
+        <v>385</v>
       </c>
     </row>
     <row r="510" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
-        <v>898</v>
+        <v>569</v>
       </c>
       <c r="B510" t="s">
-        <v>1183</v>
+        <v>317</v>
       </c>
     </row>
     <row r="511" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
-        <v>622</v>
+        <v>1500</v>
       </c>
       <c r="B511" t="s">
-        <v>623</v>
+        <v>1501</v>
       </c>
     </row>
     <row r="512" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
-        <v>453</v>
+        <v>1365</v>
       </c>
       <c r="B512" t="s">
-        <v>454</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="513" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
-        <v>687</v>
+        <v>1541</v>
       </c>
       <c r="B513" t="s">
-        <v>1480</v>
+        <v>1622</v>
       </c>
     </row>
     <row r="514" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
-        <v>42</v>
+        <v>1199</v>
       </c>
       <c r="B514" t="s">
-        <v>122</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="515" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="B515" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
     </row>
     <row r="516" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
-        <v>125</v>
+        <v>711</v>
       </c>
       <c r="B516" t="s">
-        <v>122</v>
+        <v>762</v>
       </c>
     </row>
     <row r="517" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
-        <v>1341</v>
+        <v>1624</v>
       </c>
       <c r="B517" t="s">
-        <v>1342</v>
+        <v>1625</v>
       </c>
     </row>
     <row r="518" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
-        <v>262</v>
+        <v>340</v>
       </c>
       <c r="B518" t="s">
-        <v>318</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="519" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="B519" t="s">
-        <v>263</v>
+        <v>765</v>
       </c>
     </row>
     <row r="520" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
-        <v>435</v>
+        <v>1365</v>
       </c>
       <c r="B520" t="s">
-        <v>1677</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="521" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
-        <v>319</v>
+        <v>1505</v>
       </c>
       <c r="B521" t="s">
-        <v>493</v>
+        <v>1506</v>
       </c>
     </row>
     <row r="522" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
-        <v>458</v>
+        <v>356</v>
       </c>
       <c r="B522" t="s">
-        <v>574</v>
+        <v>357</v>
       </c>
     </row>
     <row r="523" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
-        <v>576</v>
+        <v>898</v>
       </c>
       <c r="B523" t="s">
-        <v>574</v>
+        <v>1201</v>
       </c>
     </row>
     <row r="524" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
-        <v>1850</v>
+        <v>35</v>
       </c>
       <c r="B524" t="s">
-        <v>1851</v>
+        <v>767</v>
       </c>
     </row>
     <row r="525" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
-        <v>340</v>
+        <v>1048</v>
       </c>
       <c r="B525" t="s">
-        <v>748</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="526" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
-        <v>1482</v>
+        <v>1051</v>
       </c>
       <c r="B526" t="s">
-        <v>1483</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="527" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
-        <v>77</v>
+        <v>730</v>
       </c>
       <c r="B527" t="s">
-        <v>384</v>
+        <v>731</v>
       </c>
     </row>
     <row r="528" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
-        <v>1298</v>
+        <v>24</v>
       </c>
       <c r="B528" t="s">
-        <v>1485</v>
+        <v>1943</v>
       </c>
     </row>
     <row r="529" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="B529" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="530" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
-        <v>1404</v>
+        <v>1627</v>
       </c>
       <c r="B530" t="s">
-        <v>1486</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="531" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="B531" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
     </row>
     <row r="532" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
-        <v>195</v>
+        <v>639</v>
       </c>
       <c r="B532" t="s">
-        <v>625</v>
+        <v>640</v>
       </c>
     </row>
     <row r="533" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>188</v>
+        <v>1507</v>
       </c>
       <c r="B533" t="s">
-        <v>495</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="534" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
-        <v>77</v>
+        <v>1509</v>
       </c>
       <c r="B534" t="s">
-        <v>78</v>
+        <v>1510</v>
       </c>
     </row>
     <row r="535" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
-        <v>550</v>
+        <v>458</v>
       </c>
       <c r="B535" t="s">
-        <v>884</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="536" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
-        <v>550</v>
+        <v>1298</v>
       </c>
       <c r="B536" t="s">
-        <v>1343</v>
+        <v>1367</v>
       </c>
     </row>
     <row r="537" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
-        <v>265</v>
+        <v>24</v>
       </c>
       <c r="B537" t="s">
-        <v>266</v>
+        <v>635</v>
       </c>
     </row>
     <row r="538" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
-        <v>188</v>
+        <v>138</v>
       </c>
       <c r="B538" t="s">
-        <v>1184</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="539" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
-        <v>885</v>
+        <v>684</v>
       </c>
       <c r="B539" t="s">
-        <v>1185</v>
+        <v>685</v>
       </c>
     </row>
     <row r="540" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
-        <v>885</v>
+        <v>947</v>
       </c>
       <c r="B540" t="s">
-        <v>886</v>
+        <v>685</v>
       </c>
     </row>
     <row r="541" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B541" t="s">
-        <v>320</v>
+        <v>636</v>
       </c>
     </row>
     <row r="542" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
-        <v>967</v>
+        <v>1138</v>
       </c>
       <c r="B542" t="s">
-        <v>1027</v>
+        <v>1683</v>
       </c>
     </row>
     <row r="543" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
-        <v>262</v>
+        <v>898</v>
       </c>
       <c r="B543" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
     </row>
     <row r="544" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
-        <v>1031</v>
+        <v>272</v>
       </c>
       <c r="B544" t="s">
-        <v>1032</v>
-      </c>
-    </row>
-    <row r="545" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="545" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
-        <v>1487</v>
+        <v>1368</v>
       </c>
       <c r="B545" t="s">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="546" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="546" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
-        <v>470</v>
+        <v>85</v>
       </c>
       <c r="B546" t="s">
-        <v>889</v>
-      </c>
-    </row>
-    <row r="547" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="547" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
-        <v>1344</v>
+        <v>1293</v>
       </c>
       <c r="B547" t="s">
-        <v>1345</v>
-      </c>
-    </row>
-    <row r="548" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1629</v>
+      </c>
+    </row>
+    <row r="548" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
-        <v>890</v>
+        <v>1630</v>
       </c>
       <c r="B548" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="549" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1631</v>
+      </c>
+      <c r="C548" s="2" t="s">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="549" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="B549" t="s">
-        <v>892</v>
-      </c>
-    </row>
-    <row r="550" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1131</v>
+      </c>
+      <c r="C549" s="10" t="s">
+        <v>1976</v>
+      </c>
+    </row>
+    <row r="550" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
-        <v>1464</v>
+        <v>1371</v>
       </c>
       <c r="B550" t="s">
-        <v>1490</v>
-      </c>
-    </row>
-    <row r="551" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="551" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
-        <v>212</v>
+        <v>407</v>
       </c>
       <c r="B551" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="552" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="552" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
-        <v>1346</v>
+        <v>515</v>
       </c>
       <c r="B552" t="s">
-        <v>1347</v>
-      </c>
-    </row>
-    <row r="553" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="553" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
-        <v>1349</v>
+        <v>381</v>
       </c>
       <c r="B553" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="554" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1511</v>
+      </c>
+    </row>
+    <row r="554" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
-        <v>1035</v>
+        <v>569</v>
       </c>
       <c r="B554" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="555" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="555" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
-        <v>687</v>
+        <v>639</v>
       </c>
       <c r="B555" t="s">
-        <v>688</v>
-      </c>
-    </row>
-    <row r="556" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>772</v>
+      </c>
+    </row>
+    <row r="556" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
-        <v>627</v>
+        <v>224</v>
       </c>
       <c r="B556" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="557" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="557" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
-        <v>630</v>
+        <v>85</v>
       </c>
       <c r="B557" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="558" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
-        <v>1492</v>
+        <v>126</v>
       </c>
       <c r="B558" t="s">
-        <v>1493</v>
-      </c>
-    </row>
-    <row r="559" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="559" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>908</v>
+        <v>901</v>
       </c>
       <c r="B559" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="560" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="560" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
-        <v>784</v>
+        <v>794</v>
       </c>
       <c r="B560" t="s">
-        <v>785</v>
+        <v>795</v>
       </c>
     </row>
     <row r="561" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
-        <v>42</v>
+        <v>1058</v>
       </c>
       <c r="B561" t="s">
-        <v>322</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="562" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
-        <v>324</v>
+        <v>85</v>
       </c>
       <c r="B562" t="s">
-        <v>322</v>
+        <v>520</v>
       </c>
     </row>
     <row r="563" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
-        <v>585</v>
+        <v>42</v>
       </c>
       <c r="B563" t="s">
-        <v>1039</v>
+        <v>296</v>
       </c>
     </row>
     <row r="564" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
-        <v>181</v>
+        <v>1060</v>
       </c>
       <c r="B564" t="s">
-        <v>182</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="565" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
-        <v>319</v>
+        <v>1512</v>
       </c>
       <c r="B565" t="s">
-        <v>497</v>
+        <v>1513</v>
       </c>
     </row>
     <row r="566" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
-        <v>1404</v>
+        <v>368</v>
       </c>
       <c r="B566" t="s">
-        <v>1532</v>
+        <v>369</v>
       </c>
     </row>
     <row r="567" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
-        <v>340</v>
+        <v>613</v>
       </c>
       <c r="B567" t="s">
-        <v>1616</v>
+        <v>643</v>
       </c>
     </row>
     <row r="568" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
-        <v>1494</v>
+        <v>286</v>
       </c>
       <c r="B568" t="s">
-        <v>1495</v>
+        <v>287</v>
       </c>
     </row>
     <row r="569" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
-        <v>1041</v>
+        <v>262</v>
       </c>
       <c r="B569" t="s">
-        <v>1042</v>
+        <v>287</v>
       </c>
     </row>
     <row r="570" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
-        <v>893</v>
+        <v>291</v>
       </c>
       <c r="B570" t="s">
-        <v>894</v>
+        <v>287</v>
       </c>
     </row>
     <row r="571" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
-        <v>831</v>
+        <v>450</v>
       </c>
       <c r="B571" t="s">
-        <v>894</v>
+        <v>451</v>
       </c>
     </row>
     <row r="572" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
-        <v>500</v>
+        <v>248</v>
       </c>
       <c r="B572" t="s">
-        <v>501</v>
+        <v>796</v>
       </c>
     </row>
     <row r="573" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
-        <v>755</v>
+        <v>571</v>
       </c>
       <c r="B573" t="s">
-        <v>756</v>
+        <v>572</v>
       </c>
     </row>
     <row r="574" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
-        <v>1044</v>
+        <v>1381</v>
       </c>
       <c r="B574" t="s">
-        <v>1045</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="575" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
-        <v>268</v>
+        <v>1324</v>
       </c>
       <c r="B575" t="s">
-        <v>269</v>
+        <v>1383</v>
       </c>
     </row>
     <row r="576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
-        <v>262</v>
+        <v>1385</v>
       </c>
       <c r="B576" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="577" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1386</v>
+      </c>
+    </row>
+    <row r="577" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
-        <v>35</v>
+        <v>1063</v>
       </c>
       <c r="B577" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="578" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="578" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
-        <v>1352</v>
+        <v>1637</v>
       </c>
       <c r="B578" t="s">
-        <v>1353</v>
-      </c>
-    </row>
-    <row r="579" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1638</v>
+      </c>
+    </row>
+    <row r="579" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
-        <v>381</v>
+        <v>1066</v>
       </c>
       <c r="B579" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="580" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1067</v>
+      </c>
+    </row>
+    <row r="580" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
-        <v>1186</v>
+        <v>1389</v>
       </c>
       <c r="B580" t="s">
-        <v>1187</v>
-      </c>
-    </row>
-    <row r="581" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1390</v>
+      </c>
+    </row>
+    <row r="581" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
-        <v>138</v>
+        <v>1518</v>
       </c>
       <c r="B581" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="582" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="582" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
-        <v>1269</v>
+        <v>1684</v>
       </c>
       <c r="B582" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="583" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="583" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
-        <v>1618</v>
+        <v>1069</v>
       </c>
       <c r="B583" t="s">
-        <v>1619</v>
-      </c>
-    </row>
-    <row r="584" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="584" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
-        <v>759</v>
+        <v>294</v>
       </c>
       <c r="B584" t="s">
-        <v>760</v>
-      </c>
-    </row>
-    <row r="585" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="585" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" t="s">
-        <v>435</v>
+        <v>1611</v>
       </c>
       <c r="B585" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="586" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="586" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" t="s">
-        <v>717</v>
+        <v>956</v>
       </c>
       <c r="B586" t="s">
-        <v>787</v>
-      </c>
-    </row>
-    <row r="587" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1072</v>
+      </c>
+    </row>
+    <row r="587" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" t="s">
-        <v>871</v>
+        <v>31</v>
       </c>
       <c r="B587" t="s">
-        <v>1188</v>
-      </c>
-    </row>
-    <row r="588" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="588" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" t="s">
-        <v>789</v>
+        <v>1075</v>
       </c>
       <c r="B588" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="589" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1076</v>
+      </c>
+      <c r="C588" s="1" t="s">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="589" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" t="s">
-        <v>1189</v>
+        <v>689</v>
       </c>
       <c r="B589" t="s">
-        <v>1190</v>
-      </c>
-    </row>
-    <row r="590" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="590" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" t="s">
-        <v>1378</v>
+        <v>905</v>
       </c>
       <c r="B590" t="s">
-        <v>1379</v>
-      </c>
-    </row>
-    <row r="591" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A591" t="s">
-        <v>1533</v>
-      </c>
-      <c r="B591" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="592" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A592" t="s">
-        <v>580</v>
-      </c>
-      <c r="B592" t="s">
-        <v>1191</v>
-      </c>
-    </row>
-    <row r="593" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A593" t="s">
-        <v>689</v>
-      </c>
-      <c r="B593" t="s">
-        <v>1193</v>
-      </c>
-    </row>
-    <row r="594" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A594" t="s">
-        <v>522</v>
-      </c>
-      <c r="B594" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="595" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A595" t="s">
-        <v>188</v>
-      </c>
-      <c r="B595" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="596" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A596" t="s">
-        <v>401</v>
-      </c>
-      <c r="B596" t="s">
-        <v>1194</v>
-      </c>
-    </row>
-    <row r="597" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A597" t="s">
-        <v>42</v>
-      </c>
-      <c r="B597" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="598" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A598" t="s">
-        <v>319</v>
-      </c>
-      <c r="B598" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="599" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A599" t="s">
-        <v>503</v>
-      </c>
-      <c r="B599" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="600" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A600" t="s">
-        <v>1356</v>
-      </c>
-      <c r="B600" t="s">
-        <v>1357</v>
-      </c>
-    </row>
-    <row r="601" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A601" t="s">
-        <v>580</v>
-      </c>
-      <c r="B601" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="602" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A602" t="s">
-        <v>42</v>
-      </c>
-      <c r="B602" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="603" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A603" t="s">
-        <v>1217</v>
-      </c>
-      <c r="B603" t="s">
-        <v>1218</v>
-      </c>
-    </row>
-    <row r="604" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A604" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B604" t="s">
-        <v>1196</v>
-      </c>
-    </row>
-    <row r="605" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A605" t="s">
-        <v>1620</v>
-      </c>
-      <c r="B605" t="s">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="606" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A606" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B606" t="s">
-        <v>1198</v>
-      </c>
-    </row>
-    <row r="607" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A607" t="s">
-        <v>917</v>
-      </c>
-      <c r="B607" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="608" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A608" t="s">
-        <v>81</v>
-      </c>
-      <c r="B608" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="609" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A609" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B609" t="s">
-        <v>1359</v>
-      </c>
-    </row>
-    <row r="610" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A610" t="s">
-        <v>313</v>
-      </c>
-      <c r="B610" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="611" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A611" t="s">
-        <v>684</v>
-      </c>
-      <c r="B611" t="s">
-        <v>1361</v>
-      </c>
-    </row>
-    <row r="612" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A612" t="s">
-        <v>1884</v>
-      </c>
-      <c r="B612" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="613" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A613" t="s">
-        <v>1498</v>
-      </c>
-      <c r="B613" t="s">
-        <v>1499</v>
-      </c>
-    </row>
-    <row r="614" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A614" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B614" t="s">
-        <v>1363</v>
-      </c>
-    </row>
-    <row r="615" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A615" t="s">
-        <v>324</v>
-      </c>
-      <c r="B615" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="616" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A616" t="s">
-        <v>569</v>
-      </c>
-      <c r="B616" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="617" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A617" t="s">
-        <v>316</v>
-      </c>
-      <c r="B617" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="618" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A618" t="s">
-        <v>1500</v>
-      </c>
-      <c r="B618" t="s">
-        <v>1501</v>
-      </c>
-    </row>
-    <row r="619" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A619" t="s">
-        <v>1365</v>
-      </c>
-      <c r="B619" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="620" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A620" t="s">
-        <v>1541</v>
-      </c>
-      <c r="B620" t="s">
-        <v>1622</v>
-      </c>
-    </row>
-    <row r="621" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A621" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B621" t="s">
-        <v>1200</v>
-      </c>
-    </row>
-    <row r="622" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A622" t="s">
-        <v>128</v>
-      </c>
-      <c r="B622" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="623" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A623" t="s">
-        <v>711</v>
-      </c>
-      <c r="B623" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="624" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A624" t="s">
-        <v>1624</v>
-      </c>
-      <c r="B624" t="s">
-        <v>1625</v>
-      </c>
-    </row>
-    <row r="625" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A625" t="s">
-        <v>340</v>
-      </c>
-      <c r="B625" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="626" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A626" t="s">
-        <v>282</v>
-      </c>
-      <c r="B626" t="s">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="627" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A627" t="s">
-        <v>1365</v>
-      </c>
-      <c r="B627" t="s">
-        <v>1504</v>
-      </c>
-    </row>
-    <row r="628" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A628" t="s">
-        <v>896</v>
-      </c>
-      <c r="B628" t="s">
-        <v>897</v>
-      </c>
-    </row>
-    <row r="629" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A629" t="s">
-        <v>1505</v>
-      </c>
-      <c r="B629" t="s">
-        <v>1506</v>
-      </c>
-    </row>
-    <row r="630" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A630" t="s">
-        <v>356</v>
-      </c>
-      <c r="B630" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="631" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A631" t="s">
-        <v>898</v>
-      </c>
-      <c r="B631" t="s">
-        <v>1201</v>
-      </c>
-    </row>
-    <row r="632" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A632" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B632" t="s">
-        <v>1203</v>
-      </c>
-    </row>
-    <row r="633" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A633" t="s">
-        <v>35</v>
-      </c>
-      <c r="B633" t="s">
-        <v>767</v>
-      </c>
-    </row>
-    <row r="634" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A634" t="s">
-        <v>1048</v>
-      </c>
-      <c r="B634" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="635" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A635" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B635" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="636" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A636" t="s">
-        <v>730</v>
-      </c>
-      <c r="B636" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="637" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A637" t="s">
-        <v>585</v>
-      </c>
-      <c r="B637" t="s">
-        <v>731</v>
-      </c>
-    </row>
-    <row r="638" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A638" t="s">
-        <v>1680</v>
-      </c>
-      <c r="B638" t="s">
-        <v>1681</v>
-      </c>
-    </row>
-    <row r="639" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A639" t="s">
-        <v>239</v>
-      </c>
-      <c r="B639" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="640" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A640" t="s">
-        <v>1627</v>
-      </c>
-      <c r="B640" t="s">
-        <v>1628</v>
-      </c>
-    </row>
-    <row r="641" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A641" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B641" t="s">
-        <v>1206</v>
-      </c>
-    </row>
-    <row r="642" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A642" t="s">
-        <v>770</v>
-      </c>
-      <c r="B642" t="s">
-        <v>771</v>
-      </c>
-    </row>
-    <row r="643" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A643" t="s">
-        <v>639</v>
-      </c>
-      <c r="B643" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="644" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A644" t="s">
-        <v>1507</v>
-      </c>
-      <c r="B644" t="s">
-        <v>1508</v>
-      </c>
-    </row>
-    <row r="645" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A645" t="s">
-        <v>1509</v>
-      </c>
-      <c r="B645" t="s">
-        <v>1510</v>
-      </c>
-    </row>
-    <row r="646" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A646" t="s">
-        <v>1892</v>
-      </c>
-      <c r="B646" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="647" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A647" t="s">
-        <v>458</v>
-      </c>
-      <c r="B647" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="648" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A648" t="s">
-        <v>1207</v>
-      </c>
-      <c r="B648" t="s">
-        <v>1208</v>
-      </c>
-    </row>
-    <row r="649" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A649" t="s">
-        <v>1298</v>
-      </c>
-      <c r="B649" t="s">
-        <v>1367</v>
-      </c>
-    </row>
-    <row r="650" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A650" t="s">
-        <v>401</v>
-      </c>
-      <c r="B650" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="651" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A651" t="s">
-        <v>24</v>
-      </c>
-      <c r="B651" t="s">
-        <v>635</v>
-      </c>
-    </row>
-    <row r="652" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A652" t="s">
-        <v>138</v>
-      </c>
-      <c r="B652" t="s">
-        <v>1287</v>
-      </c>
-    </row>
-    <row r="653" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A653" t="s">
-        <v>684</v>
-      </c>
-      <c r="B653" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="654" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A654" t="s">
-        <v>947</v>
-      </c>
-      <c r="B654" t="s">
-        <v>685</v>
-      </c>
-    </row>
-    <row r="655" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A655" t="s">
-        <v>325</v>
-      </c>
-      <c r="B655" t="s">
-        <v>636</v>
-      </c>
-    </row>
-    <row r="656" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A656" t="s">
-        <v>1138</v>
-      </c>
-      <c r="B656" t="s">
-        <v>1683</v>
-      </c>
-    </row>
-    <row r="657" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A657" t="s">
-        <v>898</v>
-      </c>
-      <c r="B657" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="658" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A658" t="s">
-        <v>272</v>
-      </c>
-      <c r="B658" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="659" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A659" t="s">
-        <v>1368</v>
-      </c>
-      <c r="B659" t="s">
-        <v>1369</v>
-      </c>
-    </row>
-    <row r="660" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A660" t="s">
-        <v>85</v>
-      </c>
-      <c r="B660" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="661" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A661" t="s">
-        <v>1293</v>
-      </c>
-      <c r="B661" t="s">
-        <v>1629</v>
-      </c>
-    </row>
-    <row r="662" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A662" t="s">
-        <v>1630</v>
-      </c>
-      <c r="B662" t="s">
-        <v>1631</v>
-      </c>
-      <c r="C662" s="2" t="s">
-        <v>1935</v>
-      </c>
-    </row>
-    <row r="663" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A663" t="s">
-        <v>239</v>
-      </c>
-      <c r="B663" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C663" s="10" t="s">
-        <v>1976</v>
-      </c>
-    </row>
-    <row r="664" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A664" t="s">
-        <v>1371</v>
-      </c>
-      <c r="B664" t="s">
-        <v>1372</v>
-      </c>
-    </row>
-    <row r="665" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A665" t="s">
-        <v>726</v>
-      </c>
-      <c r="B665" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="666" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A666" t="s">
-        <v>515</v>
-      </c>
-      <c r="B666" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="667" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A667" t="s">
-        <v>381</v>
-      </c>
-      <c r="B667" t="s">
-        <v>1511</v>
-      </c>
-    </row>
-    <row r="668" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A668" t="s">
-        <v>569</v>
-      </c>
-      <c r="B668" t="s">
-        <v>793</v>
-      </c>
-    </row>
-    <row r="669" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A669" t="s">
-        <v>639</v>
-      </c>
-      <c r="B669" t="s">
-        <v>772</v>
-      </c>
-    </row>
-    <row r="670" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A670" t="s">
-        <v>224</v>
-      </c>
-      <c r="B670" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="671" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A671" t="s">
-        <v>85</v>
-      </c>
-      <c r="B671" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="672" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A672" t="s">
-        <v>126</v>
-      </c>
-      <c r="B672" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="673" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A673" t="s">
-        <v>901</v>
-      </c>
-      <c r="B673" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="674" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A674" t="s">
-        <v>794</v>
-      </c>
-      <c r="B674" t="s">
-        <v>795</v>
-      </c>
-    </row>
-    <row r="675" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A675" t="s">
-        <v>1058</v>
-      </c>
-      <c r="B675" t="s">
-        <v>1059</v>
-      </c>
-    </row>
-    <row r="676" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A676" t="s">
-        <v>85</v>
-      </c>
-      <c r="B676" t="s">
-        <v>520</v>
-      </c>
-    </row>
-    <row r="677" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A677" t="s">
-        <v>42</v>
-      </c>
-      <c r="B677" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="678" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A678" t="s">
-        <v>1060</v>
-      </c>
-      <c r="B678" t="s">
-        <v>1061</v>
-      </c>
-    </row>
-    <row r="679" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A679" t="s">
-        <v>1512</v>
-      </c>
-      <c r="B679" t="s">
-        <v>1513</v>
-      </c>
-    </row>
-    <row r="680" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A680" t="s">
-        <v>368</v>
-      </c>
-      <c r="B680" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="681" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A681" t="s">
-        <v>561</v>
-      </c>
-      <c r="B681" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="682" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A682" t="s">
-        <v>115</v>
-      </c>
-      <c r="B682" t="s">
-        <v>642</v>
-      </c>
-    </row>
-    <row r="683" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A683" t="s">
-        <v>613</v>
-      </c>
-      <c r="B683" t="s">
-        <v>643</v>
-      </c>
-    </row>
-    <row r="684" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A684" t="s">
-        <v>286</v>
-      </c>
-      <c r="B684" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="685" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A685" t="s">
-        <v>262</v>
-      </c>
-      <c r="B685" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="686" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A686" t="s">
-        <v>291</v>
-      </c>
-      <c r="B686" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="687" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A687" t="s">
-        <v>450</v>
-      </c>
-      <c r="B687" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="688" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A688" t="s">
-        <v>248</v>
-      </c>
-      <c r="B688" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="689" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A689" t="s">
-        <v>571</v>
-      </c>
-      <c r="B689" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="690" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A690" t="s">
-        <v>1381</v>
-      </c>
-      <c r="B690" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="691" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A691" t="s">
-        <v>1324</v>
-      </c>
-      <c r="B691" t="s">
-        <v>1383</v>
-      </c>
-    </row>
-    <row r="692" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A692" t="s">
-        <v>77</v>
-      </c>
-      <c r="B692" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="693" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A693" t="s">
-        <v>1385</v>
-      </c>
-      <c r="B693" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="694" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A694" t="s">
-        <v>1063</v>
-      </c>
-      <c r="B694" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="695" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A695" t="s">
-        <v>1637</v>
-      </c>
-      <c r="B695" t="s">
-        <v>1638</v>
-      </c>
-    </row>
-    <row r="696" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A696" t="s">
-        <v>1066</v>
-      </c>
-      <c r="B696" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="697" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A697" t="s">
-        <v>1389</v>
-      </c>
-      <c r="B697" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="698" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A698" t="s">
-        <v>1518</v>
-      </c>
-      <c r="B698" t="s">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="699" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A699" t="s">
-        <v>1684</v>
-      </c>
-      <c r="B699" t="s">
-        <v>1685</v>
-      </c>
-    </row>
-    <row r="700" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A700" t="s">
-        <v>1069</v>
-      </c>
-      <c r="B700" t="s">
-        <v>1070</v>
-      </c>
-    </row>
-    <row r="701" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A701" t="s">
-        <v>294</v>
-      </c>
-      <c r="B701" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="702" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A702" t="s">
-        <v>1611</v>
-      </c>
-      <c r="B702" t="s">
-        <v>1639</v>
-      </c>
-    </row>
-    <row r="703" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A703" t="s">
-        <v>1909</v>
-      </c>
-      <c r="B703" t="s">
-        <v>1639</v>
-      </c>
-    </row>
-    <row r="704" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A704" t="s">
-        <v>956</v>
-      </c>
-      <c r="B704" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="705" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A705" t="s">
-        <v>224</v>
-      </c>
-      <c r="B705" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="706" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A706" t="s">
-        <v>31</v>
-      </c>
-      <c r="B706" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="707" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A707" t="s">
-        <v>1075</v>
-      </c>
-      <c r="B707" t="s">
-        <v>1076</v>
-      </c>
-      <c r="C707" s="1" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="708" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A708" t="s">
-        <v>689</v>
-      </c>
-      <c r="B708" t="s">
-        <v>690</v>
-      </c>
-    </row>
-    <row r="709" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A709" t="s">
-        <v>905</v>
-      </c>
-      <c r="B709" t="s">
         <v>906</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="C80" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
+    <hyperlink ref="C70" r:id="rId1" xr:uid="{00000000-0004-0000-0200-000000000000}"/>
     <hyperlink ref="C9" r:id="rId2" xr:uid="{0BFC9787-0EF0-40D7-A9ED-DED72A2740F0}"/>
     <hyperlink ref="C12" r:id="rId3" xr:uid="{65366C55-9694-4F97-A5FD-E8F9CE09F2E7}"/>
     <hyperlink ref="C21" r:id="rId4" xr:uid="{48E128B3-0BC2-4A8F-9021-1C5209902DA7}"/>
-    <hyperlink ref="C48" r:id="rId5" xr:uid="{5010A52B-1933-4B0D-8945-6825FCF10538}"/>
-    <hyperlink ref="C75" r:id="rId6" xr:uid="{31197C11-DE2D-4242-88B9-D74E29521FC7}"/>
-    <hyperlink ref="C423" r:id="rId7" xr:uid="{615ECECA-FC28-4049-AF90-8282CFB5FB08}"/>
-    <hyperlink ref="C425" r:id="rId8" xr:uid="{3F258564-535C-4E31-84FD-F0B4224DEDFC}"/>
-    <hyperlink ref="C662" r:id="rId9" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{033EC726-D865-426A-819E-A799648AB3C1}"/>
-    <hyperlink ref="C34" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
+    <hyperlink ref="C45" r:id="rId5" xr:uid="{5010A52B-1933-4B0D-8945-6825FCF10538}"/>
+    <hyperlink ref="C67" r:id="rId6" xr:uid="{31197C11-DE2D-4242-88B9-D74E29521FC7}"/>
+    <hyperlink ref="C349" r:id="rId7" xr:uid="{615ECECA-FC28-4049-AF90-8282CFB5FB08}"/>
+    <hyperlink ref="C351" r:id="rId8" xr:uid="{3F258564-535C-4E31-84FD-F0B4224DEDFC}"/>
+    <hyperlink ref="C548" r:id="rId9" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/3/38/Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg/960px-Suzanne_Valadon._Portrait_au_chapeau%2C_photographie%2C_vers_1885._Ville_de_Paris_Biblioth%C3%A8que_Marguerite_Durand_%28BMD%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{033EC726-D865-426A-819E-A799648AB3C1}"/>
+    <hyperlink ref="C32" r:id="rId10" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
     <hyperlink ref="C5" r:id="rId11" xr:uid="{34387F5A-28DA-460F-9EEA-35D9435E3CC5}"/>
     <hyperlink ref="C6" r:id="rId12" xr:uid="{B0D11795-BECA-4256-998B-45F81F8016F7}"/>
     <hyperlink ref="C11" r:id="rId13" xr:uid="{823B3996-D38D-452A-9D1F-6801E5167310}"/>
-    <hyperlink ref="C28" r:id="rId14" xr:uid="{F61139C7-9B31-4B65-98E9-F7320A2B1B1C}"/>
-    <hyperlink ref="C36" r:id="rId15" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg/960px-Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{746DAB4B-92FA-464D-84AF-E68B5D3887D9}"/>
-    <hyperlink ref="C91" r:id="rId16" xr:uid="{C55EAA05-E5BD-4A5E-BFBE-FEB1F1FA656A}"/>
-    <hyperlink ref="C99" r:id="rId17" xr:uid="{EAA77CB6-CB26-4399-B714-2CDD461F42E0}"/>
-    <hyperlink ref="C117" r:id="rId18" xr:uid="{04DC73B6-E166-4AC3-A238-23818A086FEE}"/>
-    <hyperlink ref="C125" r:id="rId19" xr:uid="{AE2AFA72-EF6B-4BC0-BD2C-0182BB7C13E0}"/>
-    <hyperlink ref="C177" r:id="rId20" xr:uid="{CD60C327-19B4-45B0-9491-342058598A3B}"/>
-    <hyperlink ref="C178" r:id="rId21" xr:uid="{6215C244-43F9-41FE-A1A7-5F310D1022D8}"/>
-    <hyperlink ref="C179" r:id="rId22" xr:uid="{F451DBB9-EE1C-466F-B9C2-EC4C19833ED9}"/>
-    <hyperlink ref="C663" r:id="rId23" xr:uid="{8E7A3AC7-543E-4975-85FD-8A692F211657}"/>
-    <hyperlink ref="C199" r:id="rId24" xr:uid="{00D9C921-7C4C-4488-B8AB-86BC60D54D53}"/>
-    <hyperlink ref="C236" r:id="rId25" xr:uid="{43B616DF-585A-49FE-A512-858CA43A442E}"/>
+    <hyperlink ref="C26" r:id="rId14" xr:uid="{F61139C7-9B31-4B65-98E9-F7320A2B1B1C}"/>
+    <hyperlink ref="C33" r:id="rId15" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg/960px-Thomas_Banks_RA_by_James_Northcote%2C_1792%2C_oil_on_canvas_-_Royal_Academy_of_Arts_-_London%2C_UK_-_DSC06891.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{746DAB4B-92FA-464D-84AF-E68B5D3887D9}"/>
+    <hyperlink ref="C81" r:id="rId16" xr:uid="{C55EAA05-E5BD-4A5E-BFBE-FEB1F1FA656A}"/>
+    <hyperlink ref="C89" r:id="rId17" xr:uid="{EAA77CB6-CB26-4399-B714-2CDD461F42E0}"/>
+    <hyperlink ref="C101" r:id="rId18" xr:uid="{04DC73B6-E166-4AC3-A238-23818A086FEE}"/>
+    <hyperlink ref="C108" r:id="rId19" xr:uid="{AE2AFA72-EF6B-4BC0-BD2C-0182BB7C13E0}"/>
+    <hyperlink ref="C151" r:id="rId20" xr:uid="{CD60C327-19B4-45B0-9491-342058598A3B}"/>
+    <hyperlink ref="C152" r:id="rId21" xr:uid="{6215C244-43F9-41FE-A1A7-5F310D1022D8}"/>
+    <hyperlink ref="C153" r:id="rId22" xr:uid="{F451DBB9-EE1C-466F-B9C2-EC4C19833ED9}"/>
+    <hyperlink ref="C549" r:id="rId23" xr:uid="{8E7A3AC7-543E-4975-85FD-8A692F211657}"/>
+    <hyperlink ref="C172" r:id="rId24" xr:uid="{00D9C921-7C4C-4488-B8AB-86BC60D54D53}"/>
+    <hyperlink ref="C200" r:id="rId25" xr:uid="{43B616DF-585A-49FE-A512-858CA43A442E}"/>
+    <hyperlink ref="C2" r:id="rId26" xr:uid="{14E469D9-B81B-4995-AA07-B988BE19CF1E}"/>
+    <hyperlink ref="C7" r:id="rId27" location="/media/File:Portret_van_Pieter_Aertsen_Petrus_Petri,_Longus,_Amstelr._Pictor._(titel_op_object)_Pictorum_Aliquot_Celebrium_Praecipuae_Germaniae_Inferioris_Effigies_(serietitel),_RP-P-OB-55.210.jpg" xr:uid="{14235CCF-403B-44B1-ADBA-D46FB1C4DDD1}"/>
+    <hyperlink ref="C8" r:id="rId28" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d3/COURBET_Gustave_Le_sculpteur_Marcello_%28Duchesse_de_Castiglione-Colonna%29_Huile_sur_toile.jpg/960px-COURBET_Gustave_Le_sculpteur_Marcello_%28Duchesse_de_Castiglione-Colonna%29_Huile_sur_toile.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{381DBD64-F9F1-4AA3-BE7B-E783C18EB1E8}"/>
+    <hyperlink ref="C10" r:id="rId29" xr:uid="{10D8CE5D-2038-444C-AB9A-D06B467C3094}"/>
+    <hyperlink ref="C13" r:id="rId30" xr:uid="{E0C7FE6E-21D5-49E4-BB30-6525B74A3450}"/>
+    <hyperlink ref="C15" r:id="rId31" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/Santi_di_Tito%2C_Fabbrica_del_Tempio_di_Salomone%2C_1570-71%2C_04%2C2_ritratti_di_architetti_-_bartolomeo_ammannati.jpg/960px-Santi_di_Tito%2C_Fabbrica_del_Tempio_di_Salomone%2C_1570-71%2C_04%2C2_ritratti_di_architetti_-_bartolomeo_ammannati.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{D9320B19-B2A7-48B3-9AF7-D8577EABDEBF}"/>
+    <hyperlink ref="C18" r:id="rId32" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Sofonisba_Anguissola%2C_Selvportr%C3%A6t_ved_staffeliet%2C_1556%2C_Museum_Castle_in_%C5%81a%C5%84cut.jpg/960px-Sofonisba_Anguissola%2C_Selvportr%C3%A6t_ved_staffeliet%2C_1556%2C_Museum_Castle_in_%C5%81a%C5%84cut.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{27BEE7E1-D5FC-4DAD-AE42-0C37921018B2}"/>
+    <hyperlink ref="C19" r:id="rId33" xr:uid="{8EE223AF-1565-4D59-8A73-2D229A0F5C86}"/>
+    <hyperlink ref="C20" r:id="rId34" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/81/Giuseppe_Arcimboldo_-_Self_Portrait_-_Google_Art_Project.jpg/960px-Giuseppe_Arcimboldo_-_Self_Portrait_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{E891DAF1-C13F-493B-8B25-EF70B12F8EC7}"/>
+    <hyperlink ref="C23" r:id="rId35" xr:uid="{86B1FAFD-3814-4477-9311-AA86BECC1A79}"/>
+    <hyperlink ref="C24" r:id="rId36" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/70/Leandro_Bassano_%281557-1622%29_-_Portrait_of_Tiziano_Aspetti_holding_a_Statuette_-_RCIN_405988_-_Royal_Collection.jpg/960px-Leandro_Bassano_%281557-1622%29_-_Portrait_of_Tiziano_Aspetti_holding_a_Statuette_-_RCIN_405988_-_Royal_Collection.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{F9805144-220A-402F-9B5C-A2930BD5CB2D}"/>
+    <hyperlink ref="C28" r:id="rId37" xr:uid="{11997A65-C0EC-4028-A7C4-4AA9D83D8076}"/>
+    <hyperlink ref="C30" r:id="rId38" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Kw11_0012025_20190129_001_Baldung_Jugendliches_Selbstbildnis.jpg/960px-Kw11_0012025_20190129_001_Baldung_Jugendliches_Selbstbildnis.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{36049487-C7F2-4BE3-A962-9AD2DDF400EE}"/>
+    <hyperlink ref="C31" r:id="rId39" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Thomas_Ball_by_an_unidentified_artist%2C_c._1863%2C_albumen_silver_print%2C_from_the_National_Portrait_Gallery_-_NPG-S_NPG_77_141Ball-000002.jpg/960px-Thomas_Ball_by_an_unidentified_artist%2C_c._1863%2C_albumen_silver_print%2C_from_the_National_Portrait_Gallery_-_NPG-S_NPG_77_141Ball-000002.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{5E2C570E-D2D3-4AEC-BED0-91D5642F9939}"/>
+    <hyperlink ref="C34" r:id="rId40" xr:uid="{E6CE4A84-9F72-4B8B-BCC6-56896F5030C4}"/>
+    <hyperlink ref="C35" r:id="rId41" xr:uid="{8C427F8F-85BA-44A1-B243-04C22831908E}"/>
+    <hyperlink ref="C36" r:id="rId42" xr:uid="{006A22DD-9575-4B31-9D9D-E52832CBA507}"/>
+    <hyperlink ref="C37" r:id="rId43" xr:uid="{A17483E9-86D8-4D46-B0F7-F44E33EBDDEF}"/>
+    <hyperlink ref="C38" r:id="rId44" xr:uid="{09087229-B1BD-422C-8A77-6E4CF67A6570}"/>
+    <hyperlink ref="C39" r:id="rId45" xr:uid="{327AE044-69AA-4BCD-B537-F011B9BBC80F}"/>
+    <hyperlink ref="C40" r:id="rId46" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/9/93/Mus%C3%A9e_Ingres-Bourdelle_-_Portrait_de_Lorenzo_Bartolin_-_Close-up-_Ingres_-_Joconde06070000015.jpg/1280px-Mus%C3%A9e_Ingres-Bourdelle_-_Portrait_de_Lorenzo_Bartolin_-_Close-up-_Ingres_-_Joconde06070000015.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{1F61520F-3038-4D80-8A14-B329E9A2C3A0}"/>
+    <hyperlink ref="C42" r:id="rId47" xr:uid="{49FD3F73-B6C5-45A9-838D-CA4ACB3509D2}"/>
+    <hyperlink ref="C43" r:id="rId48" xr:uid="{453C7648-4532-4909-8656-7376DAE48256}"/>
+    <hyperlink ref="C44" r:id="rId49" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/0/06/Pompeo_Batoni_-_Selbstbildnis_-_1057_-_Bavarian_State_Painting_Collections.jpg/960px-Pompeo_Batoni_-_Selbstbildnis_-_1057_-_Bavarian_State_Painting_Collections.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FB8EC7DD-0A6C-43E4-AA26-5CD0507E4CB0}"/>
+    <hyperlink ref="C46" r:id="rId50" xr:uid="{4B29CB25-2A11-4293-BEB3-60A4A64E4E77}"/>
+    <hyperlink ref="C48" r:id="rId51" xr:uid="{575E29D6-EB27-4E16-804B-92679202233C}"/>
+    <hyperlink ref="C49" r:id="rId52" xr:uid="{4E494389-AF92-46BC-B10D-93435F10315C}"/>
+    <hyperlink ref="C50" r:id="rId53" xr:uid="{3FE1F043-4E97-4A2C-832E-BF4F02C73473}"/>
+    <hyperlink ref="C51" r:id="rId54" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Delle_vite_de%27_pi%C3%B9_eccellenti_pittori%2C_scultori%2C_et_architetti_%281648%29_%2814779777285%29.jpg/960px-Delle_vite_de%27_pi%C3%B9_eccellenti_pittori%2C_scultori%2C_et_architetti_%281648%29_%2814779777285%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{679BE548-B7AE-47C1-9F47-F7774B1E0C4A}"/>
+    <hyperlink ref="C53" r:id="rId55" xr:uid="{3ACD9AC0-2CD5-4686-BAC1-4A33C1457E9B}"/>
+    <hyperlink ref="C54" r:id="rId56" xr:uid="{F82613B9-F12A-46B5-B6C9-E1B778722879}"/>
+    <hyperlink ref="C55" r:id="rId57" xr:uid="{1E3079C0-0ECB-47EA-9BC0-587007D7B628}"/>
+    <hyperlink ref="C56" r:id="rId58" xr:uid="{60E45D9F-79A3-449A-A8A9-9750B4BAFE2A}"/>
+    <hyperlink ref="C58" r:id="rId59" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e4/Henri_de_Toulouse-Lautrec_-_Portrait_de_%C3%89mile_Bernard.jpg/960px-Henri_de_Toulouse-Lautrec_-_Portrait_de_%C3%89mile_Bernard.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{4446DCE9-B1C1-4382-9552-CF167AE5D42B}"/>
+    <hyperlink ref="C59" r:id="rId60" xr:uid="{7EC9448A-1213-4F35-B0D2-EC80DA631E28}"/>
+    <hyperlink ref="C60" r:id="rId61" xr:uid="{A9AB3E9F-5A07-424E-A29C-3845D5D6A672}"/>
+    <hyperlink ref="C61" r:id="rId62" xr:uid="{4AEBEA85-B27B-4883-8DE1-1FC93C883C81}"/>
+    <hyperlink ref="C62" r:id="rId63" xr:uid="{7B26A8B2-09E5-4EE2-9B70-EC01628DDAA7}"/>
+    <hyperlink ref="C63" r:id="rId64" xr:uid="{51581071-9D3B-48BC-A365-9A2FDC4D0A6A}"/>
+    <hyperlink ref="C64" r:id="rId65" xr:uid="{DD6BE342-99BF-4A0A-A233-0EAA18C98DE2}"/>
+    <hyperlink ref="C65" r:id="rId66" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/72/Portret_van_Joachim_Beuckelaer_Ioachimus_Bueckelaer%2C_Antverp._Pictor._%28titel_op_object%29_Pictorum_Aliquot_Celebrium_Praecipuae_Germaniae_Inferioris_Effigies_%28serietitel%29%2C_RP-P-1907-353.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{9DA68CA8-3E26-4C8D-8B6F-E5F2E38DA362}"/>
+    <hyperlink ref="C66" r:id="rId67" xr:uid="{58B07D25-BE1A-4616-A0F2-CABDFC6A7C69}"/>
+    <hyperlink ref="C68" r:id="rId68" xr:uid="{DA2C309A-035A-4AEF-A881-CEFA73BA491D}"/>
+    <hyperlink ref="C69" r:id="rId69" xr:uid="{9E3180FE-DD3B-448A-8BC6-14527FFC5B03}"/>
+    <hyperlink ref="C71" r:id="rId70" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Five_Famous_Men_of_the_Florentine_Renaissance%2C_Giotto_%28cropped%29.jpg/960px-Five_Famous_Men_of_the_Florentine_Renaissance%2C_Giotto_%28cropped%29.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{C0039E5D-451C-4E27-869F-BF6C3126633D}"/>
+    <hyperlink ref="C72" r:id="rId71" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/7/76/Andr%C3%A9_Adolphe-Eug%C3%A8ne_Disd%C3%A9ri_%28French_-_%28Rosa_Bonheur%29_-_Google_Art_Project.jpg/960px-Andr%C3%A9_Adolphe-Eug%C3%A8ne_Disd%C3%A9ri_%28French_-_%28Rosa_Bonheur%29_-_Google_Art_Project.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{3B092067-1C1F-46EE-8202-5C6226080C72}"/>
+    <hyperlink ref="C73" r:id="rId72" xr:uid="{CF8FBD7D-0315-4683-9C38-8F363E02EC63}"/>
+    <hyperlink ref="C75" r:id="rId73" xr:uid="{830BF4BD-E085-4985-89E0-BC8BB387A378}"/>
+    <hyperlink ref="C76" r:id="rId74" xr:uid="{1C81E1E2-3DC2-42A3-8A3C-3058C4BEA168}"/>
+    <hyperlink ref="C77" r:id="rId75" xr:uid="{EDFDFC91-448A-4498-94EB-1B900022C794}"/>
+    <hyperlink ref="C78" r:id="rId76" xr:uid="{83B21D6A-13F6-4E53-B75D-72636A97D475}"/>
+    <hyperlink ref="C80" r:id="rId77" xr:uid="{379AE8FD-A3D8-434C-A4B7-CE91808F9F95}"/>
+    <hyperlink ref="C82" r:id="rId78" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/4/42/Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Autoportrait_d%27Alfred_Boucher.jpg/960px-Aix-les-Bains_-_Mus%C3%A9e_Faure_-_Autoportrait_d%27Alfred_Boucher.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{2781CDA5-7F66-46DE-95A3-4F465FE5FC06}"/>
+    <hyperlink ref="C83" r:id="rId79" xr:uid="{902BF8C8-1C27-4C08-9DCD-42D5CC726A21}"/>
+    <hyperlink ref="C84" r:id="rId80" xr:uid="{84A4C2E9-7A4F-4273-8561-B9AF8F5134F7}"/>
+    <hyperlink ref="C86" r:id="rId81" xr:uid="{B83B6213-A8AD-442A-92EC-B575C4CF0D03}"/>
+    <hyperlink ref="C88" r:id="rId82" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Portret_van_de_schilder_Dieric_Bouts_Portretten_van_schilders_%28serietitel%29_Pictorum_Aliquot_Celebrium_Praecipuae_Germaniae_Inferioris_Effigies_%28serietitel%29%2C_RP-P-OB-67.052.jpg/960px-thumbnail.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr" xr:uid="{253620CB-F4A9-41AD-AE87-C9AFCCC2ACD7}"/>
+    <hyperlink ref="C91" r:id="rId83" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/Alessandro_Allori%2C_santissima_trinit%C3%A0_e_putti%2C_1567-1571%2C_05_ritratto_del_bronzino.jpg/960px-Alessandro_Allori%2C_santissima_trinit%C3%A0_e_putti%2C_1567-1571%2C_05_ritratto_del_bronzino.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FA7B5780-9E19-4BDB-B5B5-4EA30AE33F51}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A66E8836-B6E4-47E7-967C-37D12241F3B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BA1568-E218-45F9-89F5-84330F4933A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-495" yWindow="0" windowWidth="14655" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,14 +18,14 @@
     <sheet name="Images" sheetId="3" state="hidden" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$509</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$W$507</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7098" uniqueCount="2357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7084" uniqueCount="2357">
   <si>
     <t>Prénom</t>
   </si>
@@ -8160,7 +8160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W509"/>
+  <dimension ref="A1:W507"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="5" customWidth="1"/>
@@ -10939,7 +10939,7 @@
         <v>156</v>
       </c>
       <c r="I86" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S86" s="1" t="s">
         <v>548</v>
@@ -13421,7 +13421,7 @@
         <v>156</v>
       </c>
       <c r="I167" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S167" s="1" t="s">
         <v>925</v>
@@ -17172,7 +17172,7 @@
         <v>156</v>
       </c>
       <c r="I295" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S295" s="1" t="s">
         <v>1454</v>
@@ -17201,7 +17201,7 @@
         <v>156</v>
       </c>
       <c r="I296" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S296" s="1" t="s">
         <v>1457</v>
@@ -19368,25 +19368,25 @@
     </row>
     <row r="371" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="5" t="s">
-        <v>365</v>
+        <v>1107</v>
       </c>
       <c r="B371" s="5" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="D371" s="5" t="s">
-        <v>25</v>
+        <v>362</v>
       </c>
       <c r="E371" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F371" s="7" t="s">
-        <v>275</v>
+        <v>1238</v>
       </c>
       <c r="G371" s="7" t="s">
-        <v>1715</v>
+        <v>1216</v>
       </c>
       <c r="H371" s="7" t="s">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="I371" s="7">
         <v>3</v>
@@ -19394,25 +19394,25 @@
     </row>
     <row r="372" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="5" t="s">
-        <v>1107</v>
+        <v>1720</v>
       </c>
       <c r="B372" s="5" t="s">
-        <v>1716</v>
+        <v>1721</v>
       </c>
       <c r="D372" s="5" t="s">
-        <v>362</v>
+        <v>60</v>
       </c>
       <c r="E372" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F372" s="7" t="s">
-        <v>1238</v>
+        <v>1070</v>
       </c>
       <c r="G372" s="7" t="s">
-        <v>1216</v>
+        <v>594</v>
       </c>
       <c r="H372" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I372" s="7">
         <v>3</v>
@@ -19420,10 +19420,10 @@
     </row>
     <row r="373" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="5" t="s">
-        <v>1720</v>
+        <v>770</v>
       </c>
       <c r="B373" s="5" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="D373" s="5" t="s">
         <v>60</v>
@@ -19432,13 +19432,13 @@
         <v>40</v>
       </c>
       <c r="F373" s="7" t="s">
-        <v>1070</v>
+        <v>1453</v>
       </c>
       <c r="G373" s="7" t="s">
-        <v>594</v>
+        <v>1723</v>
       </c>
       <c r="H373" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I373" s="7">
         <v>3</v>
@@ -19446,28 +19446,37 @@
     </row>
     <row r="374" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="5" t="s">
-        <v>770</v>
+        <v>380</v>
       </c>
       <c r="B374" s="5" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="D374" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E374" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F374" s="7" t="s">
-        <v>1453</v>
+        <v>735</v>
       </c>
       <c r="G374" s="7" t="s">
-        <v>1723</v>
+        <v>985</v>
       </c>
       <c r="H374" s="7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I374" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S374" s="1" t="s">
+        <v>1726</v>
+      </c>
+      <c r="V374" t="s">
+        <v>1727</v>
+      </c>
+      <c r="W374" t="s">
+        <v>1728</v>
       </c>
     </row>
     <row r="375" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19475,42 +19484,33 @@
         <v>380</v>
       </c>
       <c r="B375" s="5" t="s">
-        <v>1725</v>
+        <v>1729</v>
       </c>
       <c r="D375" s="5" t="s">
         <v>25</v>
       </c>
       <c r="E375" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F375" s="7" t="s">
-        <v>735</v>
+        <v>568</v>
       </c>
       <c r="G375" s="7" t="s">
-        <v>985</v>
+        <v>496</v>
       </c>
       <c r="H375" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I375" s="7">
-        <v>1</v>
-      </c>
-      <c r="S375" s="1" t="s">
-        <v>1726</v>
-      </c>
-      <c r="V375" t="s">
-        <v>1727</v>
-      </c>
-      <c r="W375" t="s">
-        <v>1728</v>
+        <v>3</v>
       </c>
     </row>
     <row r="376" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="5" t="s">
-        <v>380</v>
+        <v>1730</v>
       </c>
       <c r="B376" s="5" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="D376" s="5" t="s">
         <v>25</v>
@@ -19519,13 +19519,13 @@
         <v>40</v>
       </c>
       <c r="F376" s="7" t="s">
-        <v>568</v>
+        <v>608</v>
       </c>
       <c r="G376" s="7" t="s">
-        <v>496</v>
+        <v>1732</v>
       </c>
       <c r="H376" s="7" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="I376" s="7">
         <v>3</v>
@@ -19533,80 +19533,80 @@
     </row>
     <row r="377" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="5" t="s">
-        <v>1730</v>
+        <v>770</v>
       </c>
       <c r="B377" s="5" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="D377" s="5" t="s">
-        <v>25</v>
+        <v>457</v>
       </c>
       <c r="E377" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F377" s="7" t="s">
-        <v>608</v>
+        <v>860</v>
       </c>
       <c r="G377" s="7" t="s">
-        <v>1732</v>
+        <v>425</v>
       </c>
       <c r="H377" s="7" t="s">
-        <v>156</v>
+        <v>29</v>
       </c>
       <c r="I377" s="7">
         <v>3</v>
       </c>
+      <c r="S377" s="1" t="s">
+        <v>1734</v>
+      </c>
     </row>
     <row r="378" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
-        <v>770</v>
+        <v>1735</v>
       </c>
       <c r="B378" s="5" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="D378" s="5" t="s">
-        <v>457</v>
+        <v>273</v>
       </c>
       <c r="E378" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F378" s="7" t="s">
-        <v>860</v>
+        <v>558</v>
       </c>
       <c r="G378" s="7" t="s">
-        <v>425</v>
+        <v>1737</v>
       </c>
       <c r="H378" s="7" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I378" s="7">
         <v>3</v>
       </c>
-      <c r="S378" s="1" t="s">
-        <v>1734</v>
-      </c>
     </row>
     <row r="379" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
-        <v>1735</v>
+        <v>1194</v>
       </c>
       <c r="B379" s="5" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="D379" s="5" t="s">
-        <v>273</v>
+        <v>1739</v>
       </c>
       <c r="E379" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F379" s="7" t="s">
-        <v>558</v>
+        <v>1740</v>
       </c>
       <c r="G379" s="7" t="s">
-        <v>1737</v>
+        <v>500</v>
       </c>
       <c r="H379" s="7" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="I379" s="7">
         <v>3</v>
@@ -19614,25 +19614,25 @@
     </row>
     <row r="380" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
-        <v>1194</v>
+        <v>536</v>
       </c>
       <c r="B380" s="5" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="D380" s="5" t="s">
-        <v>1739</v>
+        <v>60</v>
       </c>
       <c r="E380" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F380" s="7" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="G380" s="7" t="s">
-        <v>500</v>
+        <v>102</v>
       </c>
       <c r="H380" s="7" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I380" s="7">
         <v>3</v>
@@ -19640,25 +19640,25 @@
     </row>
     <row r="381" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
-        <v>536</v>
+        <v>1743</v>
       </c>
       <c r="B381" s="5" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="D381" s="5" t="s">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="E381" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F381" s="7" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="G381" s="7" t="s">
-        <v>102</v>
+        <v>1746</v>
       </c>
       <c r="H381" s="7" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="I381" s="7">
         <v>3</v>
@@ -19666,48 +19666,51 @@
     </row>
     <row r="382" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="5" t="s">
-        <v>1743</v>
+        <v>1747</v>
       </c>
       <c r="B382" s="5" t="s">
-        <v>1744</v>
+        <v>1748</v>
       </c>
       <c r="D382" s="5" t="s">
-        <v>349</v>
+        <v>82</v>
       </c>
       <c r="E382" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F382" s="7" t="s">
-        <v>1745</v>
+        <v>218</v>
       </c>
       <c r="G382" s="7" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="H382" s="7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I382" s="7">
         <v>3</v>
       </c>
+      <c r="S382" s="1" t="s">
+        <v>1750</v>
+      </c>
     </row>
     <row r="383" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="5" t="s">
-        <v>1747</v>
+        <v>1751</v>
       </c>
       <c r="B383" s="5" t="s">
-        <v>1748</v>
+        <v>1752</v>
       </c>
       <c r="D383" s="5" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="E383" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F383" s="7" t="s">
-        <v>218</v>
+        <v>1191</v>
       </c>
       <c r="G383" s="7" t="s">
-        <v>1749</v>
+        <v>358</v>
       </c>
       <c r="H383" s="7" t="s">
         <v>56</v>
@@ -19715,31 +19718,28 @@
       <c r="I383" s="7">
         <v>3</v>
       </c>
-      <c r="S383" s="1" t="s">
-        <v>1750</v>
-      </c>
     </row>
     <row r="384" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="5" t="s">
-        <v>1751</v>
+        <v>1047</v>
       </c>
       <c r="B384" s="5" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="D384" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E384" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F384" s="7" t="s">
-        <v>1191</v>
+        <v>42</v>
       </c>
       <c r="G384" s="7" t="s">
-        <v>358</v>
+        <v>873</v>
       </c>
       <c r="H384" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I384" s="7">
         <v>3</v>
@@ -19747,86 +19747,86 @@
     </row>
     <row r="385" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
-        <v>1047</v>
+        <v>1756</v>
       </c>
       <c r="B385" s="5" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="D385" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E385" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F385" s="7" t="s">
-        <v>42</v>
+        <v>208</v>
       </c>
       <c r="G385" s="7" t="s">
-        <v>873</v>
+        <v>1421</v>
       </c>
       <c r="H385" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I385" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S385" s="1" t="s">
+        <v>1758</v>
+      </c>
+      <c r="V385" t="s">
+        <v>1759</v>
+      </c>
+      <c r="W385" t="s">
+        <v>1760</v>
       </c>
     </row>
     <row r="386" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
-        <v>1756</v>
+        <v>1761</v>
       </c>
       <c r="B386" s="5" t="s">
-        <v>1757</v>
+        <v>1762</v>
       </c>
       <c r="D386" s="5" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E386" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F386" s="7" t="s">
-        <v>208</v>
+        <v>573</v>
       </c>
       <c r="G386" s="7" t="s">
-        <v>1421</v>
+        <v>1615</v>
       </c>
       <c r="H386" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I386" s="7">
-        <v>1</v>
-      </c>
-      <c r="S386" s="1" t="s">
-        <v>1758</v>
-      </c>
-      <c r="V386" t="s">
-        <v>1759</v>
-      </c>
-      <c r="W386" t="s">
-        <v>1760</v>
+        <v>3</v>
       </c>
     </row>
     <row r="387" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="5" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B387" s="5" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="D387" s="5" t="s">
-        <v>53</v>
+        <v>349</v>
       </c>
       <c r="E387" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F387" s="7" t="s">
-        <v>573</v>
+        <v>1765</v>
       </c>
       <c r="G387" s="7" t="s">
-        <v>1615</v>
+        <v>513</v>
       </c>
       <c r="H387" s="7" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I387" s="7">
         <v>3</v>
@@ -19834,94 +19834,94 @@
     </row>
     <row r="388" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="5" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="B388" s="5" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="D388" s="5" t="s">
-        <v>349</v>
+        <v>25</v>
       </c>
       <c r="E388" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F388" s="7" t="s">
-        <v>1765</v>
+        <v>949</v>
       </c>
       <c r="G388" s="7" t="s">
-        <v>513</v>
+        <v>662</v>
       </c>
       <c r="H388" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I388" s="7">
         <v>3</v>
       </c>
+      <c r="S388" s="1" t="s">
+        <v>1768</v>
+      </c>
     </row>
     <row r="389" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="5" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="B389" s="5" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="D389" s="5" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="E389" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F389" s="7" t="s">
-        <v>949</v>
+        <v>815</v>
       </c>
       <c r="G389" s="7" t="s">
-        <v>662</v>
+        <v>1771</v>
       </c>
       <c r="H389" s="7" t="s">
         <v>43</v>
       </c>
       <c r="I389" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S389" s="1" t="s">
-        <v>1768</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="390" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
-        <v>1769</v>
+        <v>1774</v>
       </c>
       <c r="B390" s="5" t="s">
-        <v>1770</v>
+        <v>1775</v>
       </c>
       <c r="D390" s="5" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="E390" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F390" s="7" t="s">
-        <v>815</v>
+        <v>1776</v>
       </c>
       <c r="G390" s="7" t="s">
-        <v>1771</v>
+        <v>1392</v>
       </c>
       <c r="H390" s="7" t="s">
-        <v>43</v>
+        <v>692</v>
       </c>
       <c r="I390" s="7">
-        <v>2</v>
-      </c>
-      <c r="S390" s="1" t="s">
-        <v>1772</v>
+        <v>3</v>
       </c>
     </row>
     <row r="391" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
-        <v>1774</v>
+        <v>1221</v>
       </c>
       <c r="B391" s="5" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="D391" s="5" t="s">
         <v>25</v>
@@ -19930,126 +19930,126 @@
         <v>40</v>
       </c>
       <c r="F391" s="7" t="s">
-        <v>1776</v>
+        <v>691</v>
       </c>
       <c r="G391" s="7" t="s">
-        <v>1392</v>
+        <v>811</v>
       </c>
       <c r="H391" s="7" t="s">
-        <v>692</v>
+        <v>29</v>
       </c>
       <c r="I391" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S391" s="1" t="s">
+        <v>1778</v>
       </c>
     </row>
     <row r="392" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="5" t="s">
-        <v>1221</v>
+        <v>231</v>
       </c>
       <c r="B392" s="5" t="s">
-        <v>1777</v>
+        <v>1779</v>
+      </c>
+      <c r="C392" s="5" t="s">
+        <v>1780</v>
       </c>
       <c r="D392" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E392" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F392" s="7" t="s">
-        <v>691</v>
+        <v>1533</v>
       </c>
       <c r="G392" s="7" t="s">
-        <v>811</v>
+        <v>630</v>
       </c>
       <c r="H392" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I392" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S392" s="1" t="s">
-        <v>1778</v>
+        <v>1781</v>
+      </c>
+      <c r="V392" t="s">
+        <v>1782</v>
+      </c>
+      <c r="W392" t="s">
+        <v>1783</v>
       </c>
     </row>
     <row r="393" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="s">
-        <v>231</v>
+        <v>211</v>
       </c>
       <c r="B393" s="5" t="s">
-        <v>1779</v>
-      </c>
-      <c r="C393" s="5" t="s">
-        <v>1780</v>
+        <v>1784</v>
       </c>
       <c r="D393" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E393" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F393" s="7" t="s">
-        <v>1533</v>
+        <v>1191</v>
       </c>
       <c r="G393" s="7" t="s">
-        <v>630</v>
+        <v>904</v>
       </c>
       <c r="H393" s="7" t="s">
-        <v>43</v>
+        <v>384</v>
       </c>
       <c r="I393" s="7">
         <v>1</v>
       </c>
       <c r="S393" s="1" t="s">
-        <v>1781</v>
+        <v>1785</v>
       </c>
       <c r="V393" t="s">
-        <v>1782</v>
+        <v>1786</v>
       </c>
       <c r="W393" t="s">
-        <v>1783</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="394" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="5" t="s">
-        <v>211</v>
+        <v>660</v>
       </c>
       <c r="B394" s="5" t="s">
-        <v>1784</v>
+        <v>1788</v>
       </c>
       <c r="D394" s="5" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E394" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F394" s="7" t="s">
-        <v>1191</v>
-      </c>
-      <c r="G394" s="7" t="s">
-        <v>904</v>
+        <v>40</v>
+      </c>
+      <c r="F394" s="7">
+        <v>1874</v>
+      </c>
+      <c r="G394" s="7">
+        <v>1947</v>
       </c>
       <c r="H394" s="7" t="s">
-        <v>384</v>
+        <v>50</v>
       </c>
       <c r="I394" s="7">
-        <v>1</v>
-      </c>
-      <c r="S394" s="1" t="s">
-        <v>1785</v>
-      </c>
-      <c r="V394" t="s">
-        <v>1786</v>
-      </c>
-      <c r="W394" t="s">
-        <v>1787</v>
+        <v>3</v>
       </c>
     </row>
     <row r="395" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="5" t="s">
-        <v>660</v>
+        <v>1792</v>
       </c>
       <c r="B395" s="5" t="s">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="D395" s="5" t="s">
         <v>53</v>
@@ -20057,14 +20057,14 @@
       <c r="E395" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F395" s="7">
-        <v>1874</v>
-      </c>
-      <c r="G395" s="7">
-        <v>1947</v>
+      <c r="F395" s="7" t="s">
+        <v>1794</v>
+      </c>
+      <c r="G395" s="7" t="s">
+        <v>811</v>
       </c>
       <c r="H395" s="7" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="I395" s="7">
         <v>3</v>
@@ -20072,25 +20072,25 @@
     </row>
     <row r="396" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="5" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="B396" s="5" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="D396" s="5" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="E396" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F396" s="7" t="s">
-        <v>1794</v>
+        <v>155</v>
       </c>
       <c r="G396" s="7" t="s">
-        <v>811</v>
+        <v>1160</v>
       </c>
       <c r="H396" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I396" s="7">
         <v>3</v>
@@ -20098,10 +20098,10 @@
     </row>
     <row r="397" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="5" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="B397" s="5" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="D397" s="5" t="s">
         <v>60</v>
@@ -20110,13 +20110,13 @@
         <v>40</v>
       </c>
       <c r="F397" s="7" t="s">
-        <v>155</v>
+        <v>1799</v>
       </c>
       <c r="G397" s="7" t="s">
-        <v>1160</v>
+        <v>564</v>
       </c>
       <c r="H397" s="7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I397" s="7">
         <v>3</v>
@@ -20124,135 +20124,135 @@
     </row>
     <row r="398" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="5" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="B398" s="5" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="D398" s="5" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E398" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F398" s="7" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="G398" s="7" t="s">
-        <v>564</v>
+        <v>1294</v>
       </c>
       <c r="H398" s="7" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="I398" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="399" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A399" s="5" t="s">
-        <v>1800</v>
-      </c>
-      <c r="B399" s="5" t="s">
-        <v>1801</v>
+      <c r="A399" s="11" t="s">
+        <v>292</v>
+      </c>
+      <c r="B399" s="11" t="s">
+        <v>1804</v>
       </c>
       <c r="D399" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="E399" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F399" s="7" t="s">
-        <v>1802</v>
-      </c>
-      <c r="G399" s="7" t="s">
-        <v>1294</v>
-      </c>
-      <c r="H399" s="7" t="s">
-        <v>29</v>
+        <v>60</v>
+      </c>
+      <c r="E399" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F399" s="7">
+        <v>1409</v>
+      </c>
+      <c r="G399" s="7">
+        <v>1464</v>
+      </c>
+      <c r="H399" s="11" t="s">
+        <v>156</v>
       </c>
       <c r="I399" s="7">
         <v>3</v>
       </c>
+      <c r="S399" s="1" t="s">
+        <v>1806</v>
+      </c>
     </row>
     <row r="400" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B400" s="11" t="s">
+      <c r="A400" s="5" t="s">
+        <v>536</v>
+      </c>
+      <c r="B400" s="5" t="s">
         <v>1804</v>
       </c>
       <c r="D400" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E400" s="11" t="s">
+      <c r="E400" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F400" s="7">
-        <v>1409</v>
+        <v>1427</v>
       </c>
       <c r="G400" s="7">
-        <v>1464</v>
-      </c>
-      <c r="H400" s="11" t="s">
-        <v>156</v>
+        <v>1479</v>
+      </c>
+      <c r="H400" s="7" t="s">
+        <v>43</v>
       </c>
       <c r="I400" s="7">
         <v>3</v>
       </c>
       <c r="S400" s="1" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
     </row>
     <row r="401" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="s">
-        <v>536</v>
+        <v>1807</v>
       </c>
       <c r="B401" s="5" t="s">
-        <v>1804</v>
+        <v>1808</v>
       </c>
       <c r="D401" s="5" t="s">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="E401" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F401" s="7">
-        <v>1427</v>
-      </c>
-      <c r="G401" s="7">
-        <v>1479</v>
+        <v>40</v>
+      </c>
+      <c r="F401" s="7" t="s">
+        <v>842</v>
+      </c>
+      <c r="G401" s="7" t="s">
+        <v>357</v>
       </c>
       <c r="H401" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I401" s="7">
         <v>3</v>
       </c>
-      <c r="S401" s="1" t="s">
-        <v>1805</v>
-      </c>
     </row>
     <row r="402" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="5" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="B402" s="5" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="D402" s="5" t="s">
-        <v>349</v>
+        <v>60</v>
       </c>
       <c r="E402" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F402" s="7" t="s">
-        <v>842</v>
-      </c>
-      <c r="G402" s="7" t="s">
-        <v>357</v>
+        <v>26</v>
+      </c>
+      <c r="F402" s="7">
+        <v>1858</v>
+      </c>
+      <c r="G402" s="7">
+        <v>1928</v>
       </c>
       <c r="H402" s="7" t="s">
-        <v>56</v>
+        <v>384</v>
       </c>
       <c r="I402" s="7">
         <v>3</v>
@@ -20260,72 +20260,75 @@
     </row>
     <row r="403" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="5" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B403" s="5" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="D403" s="5" t="s">
-        <v>60</v>
+        <v>423</v>
       </c>
       <c r="E403" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F403" s="7">
-        <v>1858</v>
-      </c>
-      <c r="G403" s="7">
-        <v>1928</v>
+      <c r="F403" s="7" t="s">
+        <v>1449</v>
+      </c>
+      <c r="G403" s="7" t="s">
+        <v>425</v>
       </c>
       <c r="H403" s="7" t="s">
-        <v>384</v>
+        <v>29</v>
       </c>
       <c r="I403" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S403" s="1" t="s">
+        <v>1813</v>
+      </c>
+      <c r="V403" t="s">
+        <v>1814</v>
+      </c>
+      <c r="W403" t="s">
+        <v>1815</v>
       </c>
     </row>
     <row r="404" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="5" t="s">
-        <v>1811</v>
+        <v>600</v>
       </c>
       <c r="B404" s="5" t="s">
-        <v>1812</v>
+        <v>1816</v>
       </c>
       <c r="D404" s="5" t="s">
-        <v>423</v>
+        <v>25</v>
       </c>
       <c r="E404" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F404" s="7" t="s">
-        <v>1449</v>
+        <v>1817</v>
       </c>
       <c r="G404" s="7" t="s">
-        <v>425</v>
+        <v>382</v>
       </c>
       <c r="H404" s="7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I404" s="7">
-        <v>1</v>
-      </c>
-      <c r="S404" s="1" t="s">
-        <v>1813</v>
-      </c>
-      <c r="V404" t="s">
-        <v>1814</v>
-      </c>
-      <c r="W404" t="s">
-        <v>1815</v>
+        <v>3</v>
       </c>
     </row>
     <row r="405" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="s">
-        <v>600</v>
+        <v>271</v>
       </c>
       <c r="B405" s="5" t="s">
         <v>1816</v>
       </c>
+      <c r="C405" s="5" t="s">
+        <v>1818</v>
+      </c>
       <c r="D405" s="5" t="s">
         <v>25</v>
       </c>
@@ -20333,27 +20336,33 @@
         <v>40</v>
       </c>
       <c r="F405" s="7" t="s">
-        <v>1817</v>
+        <v>573</v>
       </c>
       <c r="G405" s="7" t="s">
-        <v>382</v>
+        <v>1185</v>
       </c>
       <c r="H405" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I405" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S405" s="1" t="s">
+        <v>1819</v>
+      </c>
+      <c r="V405" t="s">
+        <v>1820</v>
+      </c>
+      <c r="W405" t="s">
+        <v>1821</v>
       </c>
     </row>
     <row r="406" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="5" t="s">
-        <v>271</v>
+        <v>1822</v>
       </c>
       <c r="B406" s="5" t="s">
-        <v>1816</v>
-      </c>
-      <c r="C406" s="5" t="s">
-        <v>1818</v>
+        <v>1823</v>
       </c>
       <c r="D406" s="5" t="s">
         <v>25</v>
@@ -20362,132 +20371,123 @@
         <v>40</v>
       </c>
       <c r="F406" s="7" t="s">
-        <v>573</v>
+        <v>382</v>
       </c>
       <c r="G406" s="7" t="s">
-        <v>1185</v>
+        <v>49</v>
       </c>
       <c r="H406" s="7" t="s">
         <v>50</v>
       </c>
       <c r="I406" s="7">
-        <v>1</v>
-      </c>
-      <c r="S406" s="1" t="s">
-        <v>1819</v>
-      </c>
-      <c r="V406" t="s">
-        <v>1820</v>
-      </c>
-      <c r="W406" t="s">
-        <v>1821</v>
+        <v>3</v>
       </c>
     </row>
     <row r="407" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="B407" s="5" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="D407" s="5" t="s">
-        <v>25</v>
+        <v>273</v>
       </c>
       <c r="E407" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F407" s="7" t="s">
-        <v>382</v>
+        <v>850</v>
       </c>
       <c r="G407" s="7" t="s">
-        <v>49</v>
+        <v>708</v>
       </c>
       <c r="H407" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I407" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S407" s="1" t="s">
+        <v>1826</v>
+      </c>
+      <c r="V407" t="s">
+        <v>1827</v>
+      </c>
+      <c r="W407" t="s">
+        <v>1828</v>
       </c>
     </row>
     <row r="408" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="5" t="s">
-        <v>1824</v>
+        <v>95</v>
       </c>
       <c r="B408" s="5" t="s">
-        <v>1825</v>
+        <v>1829</v>
       </c>
       <c r="D408" s="5" t="s">
-        <v>273</v>
+        <v>25</v>
       </c>
       <c r="E408" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F408" s="7" t="s">
-        <v>850</v>
+        <v>1746</v>
       </c>
       <c r="G408" s="7" t="s">
-        <v>708</v>
+        <v>1699</v>
       </c>
       <c r="H408" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I408" s="7">
         <v>1</v>
       </c>
-      <c r="S408" s="1" t="s">
-        <v>1826</v>
-      </c>
-      <c r="V408" t="s">
-        <v>1827</v>
-      </c>
-      <c r="W408" t="s">
-        <v>1828</v>
-      </c>
     </row>
     <row r="409" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="5" t="s">
-        <v>95</v>
+        <v>1512</v>
       </c>
       <c r="B409" s="5" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="D409" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E409" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F409" s="7" t="s">
-        <v>1746</v>
+        <v>690</v>
       </c>
       <c r="G409" s="7" t="s">
-        <v>1699</v>
+        <v>1544</v>
       </c>
       <c r="H409" s="7" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I409" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="410" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="s">
-        <v>1512</v>
+        <v>1831</v>
       </c>
       <c r="B410" s="5" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="D410" s="5" t="s">
-        <v>60</v>
+        <v>273</v>
       </c>
       <c r="E410" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F410" s="7" t="s">
-        <v>690</v>
+        <v>985</v>
       </c>
       <c r="G410" s="7" t="s">
-        <v>1544</v>
+        <v>432</v>
       </c>
       <c r="H410" s="7" t="s">
         <v>29</v>
@@ -20495,89 +20495,89 @@
       <c r="I410" s="7">
         <v>3</v>
       </c>
+      <c r="S410" s="1" t="s">
+        <v>1833</v>
+      </c>
     </row>
     <row r="411" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="B411" s="5" t="s">
-        <v>1832</v>
+        <v>1835</v>
       </c>
       <c r="D411" s="5" t="s">
-        <v>273</v>
+        <v>165</v>
       </c>
       <c r="E411" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F411" s="7" t="s">
-        <v>985</v>
+        <v>518</v>
       </c>
       <c r="G411" s="7" t="s">
-        <v>432</v>
+        <v>1439</v>
       </c>
       <c r="H411" s="7" t="s">
-        <v>29</v>
+        <v>384</v>
       </c>
       <c r="I411" s="7">
         <v>3</v>
       </c>
       <c r="S411" s="1" t="s">
-        <v>1833</v>
+        <v>1836</v>
+      </c>
+      <c r="V411" t="s">
+        <v>1837</v>
+      </c>
+      <c r="W411" t="s">
+        <v>1838</v>
       </c>
     </row>
     <row r="412" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="s">
-        <v>1834</v>
+        <v>840</v>
       </c>
       <c r="B412" s="5" t="s">
-        <v>1835</v>
+        <v>1839</v>
       </c>
       <c r="D412" s="5" t="s">
-        <v>165</v>
+        <v>299</v>
       </c>
       <c r="E412" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F412" s="7" t="s">
-        <v>518</v>
+        <v>1840</v>
       </c>
       <c r="G412" s="7" t="s">
-        <v>1439</v>
+        <v>1554</v>
       </c>
       <c r="H412" s="7" t="s">
-        <v>384</v>
+        <v>29</v>
       </c>
       <c r="I412" s="7">
         <v>3</v>
       </c>
-      <c r="S412" s="1" t="s">
-        <v>1836</v>
-      </c>
-      <c r="V412" t="s">
-        <v>1837</v>
-      </c>
-      <c r="W412" t="s">
-        <v>1838</v>
-      </c>
-    </row>
-    <row r="413" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="5" t="s">
-        <v>840</v>
+        <v>114</v>
       </c>
       <c r="B413" s="5" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="D413" s="5" t="s">
-        <v>299</v>
+        <v>457</v>
       </c>
       <c r="E413" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F413" s="7" t="s">
-        <v>1840</v>
+        <v>709</v>
       </c>
       <c r="G413" s="7" t="s">
-        <v>1554</v>
+        <v>1294</v>
       </c>
       <c r="H413" s="7" t="s">
         <v>29</v>
@@ -20585,39 +20585,48 @@
       <c r="I413" s="7">
         <v>3</v>
       </c>
-    </row>
-    <row r="414" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="S413" s="1" t="s">
+        <v>1842</v>
+      </c>
+    </row>
+    <row r="414" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="s">
-        <v>114</v>
+        <v>909</v>
       </c>
       <c r="B414" s="5" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="D414" s="5" t="s">
-        <v>457</v>
+        <v>60</v>
       </c>
       <c r="E414" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F414" s="7" t="s">
-        <v>709</v>
+        <v>1844</v>
       </c>
       <c r="G414" s="7" t="s">
-        <v>1294</v>
+        <v>368</v>
       </c>
       <c r="H414" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I414" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S414" s="1" t="s">
-        <v>1842</v>
+        <v>1845</v>
+      </c>
+      <c r="V414" t="s">
+        <v>1846</v>
+      </c>
+      <c r="W414" t="s">
+        <v>1847</v>
       </c>
     </row>
     <row r="415" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="5" t="s">
-        <v>909</v>
+        <v>231</v>
       </c>
       <c r="B415" s="5" t="s">
         <v>1843</v>
@@ -20629,10 +20638,10 @@
         <v>26</v>
       </c>
       <c r="F415" s="7" t="s">
-        <v>1844</v>
+        <v>254</v>
       </c>
       <c r="G415" s="7" t="s">
-        <v>368</v>
+        <v>1723</v>
       </c>
       <c r="H415" s="7" t="s">
         <v>43</v>
@@ -20641,33 +20650,36 @@
         <v>1</v>
       </c>
       <c r="S415" s="1" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="V415" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="W415" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
     </row>
     <row r="416" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="s">
-        <v>231</v>
+        <v>1851</v>
       </c>
       <c r="B416" s="5" t="s">
-        <v>1843</v>
+        <v>1852</v>
+      </c>
+      <c r="C416" s="5" t="s">
+        <v>1853</v>
       </c>
       <c r="D416" s="5" t="s">
         <v>60</v>
       </c>
       <c r="E416" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F416" s="7" t="s">
-        <v>254</v>
+        <v>1854</v>
       </c>
       <c r="G416" s="7" t="s">
-        <v>1723</v>
+        <v>1645</v>
       </c>
       <c r="H416" s="7" t="s">
         <v>43</v>
@@ -20676,207 +20688,195 @@
         <v>1</v>
       </c>
       <c r="S416" s="1" t="s">
-        <v>1848</v>
+        <v>1855</v>
       </c>
       <c r="V416" t="s">
-        <v>1849</v>
+        <v>1856</v>
       </c>
       <c r="W416" t="s">
-        <v>1850</v>
+        <v>1857</v>
       </c>
     </row>
     <row r="417" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="5" t="s">
-        <v>1851</v>
+        <v>1858</v>
       </c>
       <c r="B417" s="5" t="s">
-        <v>1852</v>
-      </c>
-      <c r="C417" s="5" t="s">
-        <v>1853</v>
+        <v>1859</v>
       </c>
       <c r="D417" s="5" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="E417" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F417" s="7" t="s">
-        <v>1854</v>
+        <v>602</v>
       </c>
       <c r="G417" s="7" t="s">
-        <v>1645</v>
+        <v>669</v>
       </c>
       <c r="H417" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I417" s="7">
-        <v>1</v>
-      </c>
-      <c r="S417" s="1" t="s">
-        <v>1855</v>
-      </c>
-      <c r="V417" t="s">
-        <v>1856</v>
-      </c>
-      <c r="W417" t="s">
-        <v>1857</v>
+        <v>3</v>
       </c>
     </row>
     <row r="418" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B418" s="5" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="D418" s="5" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="E418" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F418" s="7" t="s">
-        <v>602</v>
+        <v>1313</v>
       </c>
       <c r="G418" s="7" t="s">
-        <v>669</v>
+        <v>219</v>
       </c>
       <c r="H418" s="7" t="s">
-        <v>56</v>
+        <v>352</v>
       </c>
       <c r="I418" s="7">
         <v>3</v>
       </c>
+      <c r="S418" s="1" t="s">
+        <v>1862</v>
+      </c>
     </row>
     <row r="419" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="5" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="B419" s="5" t="s">
-        <v>1861</v>
+        <v>1864</v>
       </c>
       <c r="D419" s="5" t="s">
-        <v>82</v>
+        <v>1368</v>
       </c>
       <c r="E419" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F419" s="7" t="s">
-        <v>1313</v>
+        <v>1865</v>
       </c>
       <c r="G419" s="7" t="s">
-        <v>219</v>
+        <v>1311</v>
       </c>
       <c r="H419" s="7" t="s">
-        <v>352</v>
+        <v>50</v>
       </c>
       <c r="I419" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S419" s="1" t="s">
-        <v>1862</v>
+        <v>1866</v>
+      </c>
+      <c r="V419" t="s">
+        <v>1867</v>
+      </c>
+      <c r="W419" t="s">
+        <v>1868</v>
       </c>
     </row>
     <row r="420" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="s">
-        <v>1863</v>
+        <v>982</v>
       </c>
       <c r="B420" s="5" t="s">
-        <v>1864</v>
+        <v>1869</v>
       </c>
       <c r="D420" s="5" t="s">
-        <v>1368</v>
+        <v>25</v>
       </c>
       <c r="E420" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F420" s="7" t="s">
-        <v>1865</v>
-      </c>
-      <c r="G420" s="7" t="s">
-        <v>1311</v>
+        <v>275</v>
+      </c>
+      <c r="G420" s="7">
+        <v>1491</v>
       </c>
       <c r="H420" s="7" t="s">
-        <v>50</v>
+        <v>156</v>
       </c>
       <c r="I420" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S420" s="1" t="s">
-        <v>1866</v>
-      </c>
-      <c r="V420" t="s">
-        <v>1867</v>
-      </c>
-      <c r="W420" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
     </row>
     <row r="421" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="5" t="s">
-        <v>982</v>
+        <v>1871</v>
       </c>
       <c r="B421" s="5" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D421" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E421" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F421" s="7" t="s">
-        <v>275</v>
-      </c>
-      <c r="G421" s="7">
-        <v>1491</v>
+        <v>862</v>
+      </c>
+      <c r="G421" s="7" t="s">
+        <v>1178</v>
       </c>
       <c r="H421" s="7" t="s">
-        <v>156</v>
+        <v>692</v>
       </c>
       <c r="I421" s="7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S421" s="1" t="s">
-        <v>1870</v>
+        <v>1873</v>
       </c>
     </row>
     <row r="422" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="5" t="s">
-        <v>1871</v>
+        <v>580</v>
       </c>
       <c r="B422" s="5" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="D422" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E422" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F422" s="7" t="s">
-        <v>862</v>
+        <v>633</v>
       </c>
       <c r="G422" s="7" t="s">
-        <v>1178</v>
+        <v>1345</v>
       </c>
       <c r="H422" s="7" t="s">
-        <v>692</v>
+        <v>56</v>
       </c>
       <c r="I422" s="7">
-        <v>2</v>
-      </c>
-      <c r="S422" s="1" t="s">
-        <v>1873</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="5" t="s">
-        <v>580</v>
+        <v>855</v>
       </c>
       <c r="B423" s="5" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="D423" s="5" t="s">
         <v>25</v>
@@ -20885,36 +20885,39 @@
         <v>40</v>
       </c>
       <c r="F423" s="7" t="s">
-        <v>633</v>
+        <v>1877</v>
       </c>
       <c r="G423" s="7" t="s">
-        <v>1345</v>
+        <v>591</v>
       </c>
       <c r="H423" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I423" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S423" s="1" t="s">
+        <v>1878</v>
       </c>
     </row>
     <row r="424" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="s">
-        <v>855</v>
+        <v>1879</v>
       </c>
       <c r="B424" s="5" t="s">
-        <v>1876</v>
+        <v>1880</v>
       </c>
       <c r="D424" s="5" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="E424" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F424" s="7" t="s">
-        <v>1877</v>
+        <v>1256</v>
       </c>
       <c r="G424" s="7" t="s">
-        <v>591</v>
+        <v>209</v>
       </c>
       <c r="H424" s="7" t="s">
         <v>56</v>
@@ -20922,109 +20925,106 @@
       <c r="I424" s="7">
         <v>2</v>
       </c>
-      <c r="S424" s="1" t="s">
-        <v>1878</v>
-      </c>
     </row>
     <row r="425" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="5" t="s">
-        <v>1879</v>
+        <v>580</v>
       </c>
       <c r="B425" s="5" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="D425" s="5" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="E425" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F425" s="7" t="s">
-        <v>1256</v>
+        <v>930</v>
       </c>
       <c r="G425" s="7" t="s">
-        <v>209</v>
+        <v>1491</v>
       </c>
       <c r="H425" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I425" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="426" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="s">
-        <v>580</v>
+        <v>959</v>
       </c>
       <c r="B426" s="5" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="D426" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E426" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F426" s="7" t="s">
-        <v>930</v>
+        <v>1883</v>
       </c>
       <c r="G426" s="7" t="s">
-        <v>1491</v>
+        <v>816</v>
       </c>
       <c r="H426" s="7" t="s">
-        <v>56</v>
+        <v>280</v>
       </c>
       <c r="I426" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S426" s="1" t="s">
+        <v>1884</v>
       </c>
     </row>
     <row r="427" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="5" t="s">
-        <v>959</v>
+        <v>1885</v>
       </c>
       <c r="B427" s="5" t="s">
-        <v>1882</v>
+        <v>1886</v>
       </c>
       <c r="D427" s="5" t="s">
-        <v>60</v>
+        <v>1620</v>
       </c>
       <c r="E427" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F427" s="7" t="s">
-        <v>1883</v>
+        <v>1887</v>
       </c>
       <c r="G427" s="7" t="s">
-        <v>816</v>
+        <v>1630</v>
       </c>
       <c r="H427" s="7" t="s">
-        <v>280</v>
+        <v>56</v>
       </c>
       <c r="I427" s="7">
         <v>2</v>
       </c>
-      <c r="S427" s="1" t="s">
-        <v>1884</v>
-      </c>
     </row>
     <row r="428" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="s">
-        <v>1885</v>
+        <v>437</v>
       </c>
       <c r="B428" s="5" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="D428" s="5" t="s">
-        <v>1620</v>
+        <v>25</v>
       </c>
       <c r="E428" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F428" s="7" t="s">
-        <v>1887</v>
+        <v>582</v>
       </c>
       <c r="G428" s="7" t="s">
-        <v>1630</v>
+        <v>378</v>
       </c>
       <c r="H428" s="7" t="s">
         <v>56</v>
@@ -21032,167 +21032,167 @@
       <c r="I428" s="7">
         <v>2</v>
       </c>
+      <c r="S428" s="1" t="s">
+        <v>1889</v>
+      </c>
     </row>
     <row r="429" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="5" t="s">
-        <v>437</v>
+        <v>257</v>
       </c>
       <c r="B429" s="5" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="D429" s="5" t="s">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="E429" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F429" s="7" t="s">
-        <v>582</v>
+        <v>307</v>
       </c>
       <c r="G429" s="7" t="s">
-        <v>378</v>
+        <v>1891</v>
       </c>
       <c r="H429" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I429" s="7">
-        <v>2</v>
-      </c>
-      <c r="S429" s="1" t="s">
-        <v>1889</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="s">
-        <v>257</v>
+        <v>1892</v>
       </c>
       <c r="B430" s="5" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="D430" s="5" t="s">
-        <v>82</v>
+        <v>423</v>
       </c>
       <c r="E430" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F430" s="7" t="s">
-        <v>307</v>
+        <v>33</v>
       </c>
       <c r="G430" s="7" t="s">
-        <v>1891</v>
+        <v>1313</v>
       </c>
       <c r="H430" s="7" t="s">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="I430" s="7">
         <v>3</v>
       </c>
+      <c r="S430" s="1" t="s">
+        <v>1894</v>
+      </c>
     </row>
     <row r="431" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
-        <v>1892</v>
+        <v>1300</v>
       </c>
       <c r="B431" s="5" t="s">
-        <v>1893</v>
+        <v>1898</v>
       </c>
       <c r="D431" s="5" t="s">
-        <v>423</v>
+        <v>273</v>
       </c>
       <c r="E431" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F431" s="7" t="s">
-        <v>33</v>
+        <v>1899</v>
       </c>
       <c r="G431" s="7" t="s">
-        <v>1313</v>
+        <v>1900</v>
       </c>
       <c r="H431" s="7" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I431" s="7">
         <v>3</v>
       </c>
-      <c r="S431" s="1" t="s">
-        <v>1894</v>
-      </c>
     </row>
     <row r="432" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="s">
-        <v>1300</v>
+        <v>1901</v>
       </c>
       <c r="B432" s="5" t="s">
-        <v>1898</v>
+        <v>1902</v>
       </c>
       <c r="D432" s="5" t="s">
-        <v>273</v>
+        <v>1903</v>
       </c>
       <c r="E432" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F432" s="7" t="s">
-        <v>1899</v>
-      </c>
-      <c r="G432" s="7" t="s">
-        <v>1900</v>
+      <c r="F432" s="7">
+        <v>1893</v>
+      </c>
+      <c r="G432" s="7">
+        <v>1943</v>
       </c>
       <c r="H432" s="7" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I432" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S432" s="1" t="s">
+        <v>1904</v>
       </c>
     </row>
     <row r="433" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="5" t="s">
-        <v>1901</v>
+        <v>1264</v>
       </c>
       <c r="B433" s="5" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="D433" s="5" t="s">
-        <v>1903</v>
+        <v>39</v>
       </c>
       <c r="E433" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="F433" s="7">
-        <v>1893</v>
-      </c>
-      <c r="G433" s="7">
-        <v>1943</v>
+      <c r="F433" s="7" t="s">
+        <v>896</v>
+      </c>
+      <c r="G433" s="7" t="s">
+        <v>1906</v>
       </c>
       <c r="H433" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I433" s="7">
-        <v>2</v>
-      </c>
-      <c r="S433" s="1" t="s">
-        <v>1904</v>
+        <v>3</v>
       </c>
     </row>
     <row r="434" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="5" t="s">
-        <v>1264</v>
+        <v>437</v>
       </c>
       <c r="B434" s="5" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="D434" s="5" t="s">
-        <v>39</v>
+        <v>349</v>
       </c>
       <c r="E434" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F434" s="7" t="s">
-        <v>896</v>
+        <v>54</v>
       </c>
       <c r="G434" s="7" t="s">
-        <v>1906</v>
+        <v>226</v>
       </c>
       <c r="H434" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I434" s="7">
         <v>3</v>
@@ -21200,109 +21200,109 @@
     </row>
     <row r="435" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="5" t="s">
-        <v>437</v>
+        <v>1908</v>
       </c>
       <c r="B435" s="5" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="D435" s="5" t="s">
-        <v>349</v>
+        <v>165</v>
       </c>
       <c r="E435" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F435" s="7" t="s">
-        <v>54</v>
+        <v>166</v>
       </c>
       <c r="G435" s="7" t="s">
-        <v>226</v>
+        <v>1590</v>
       </c>
       <c r="H435" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I435" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S435" s="1" t="s">
+        <v>1910</v>
       </c>
     </row>
     <row r="436" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="5" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="B436" s="5" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
       <c r="D436" s="5" t="s">
-        <v>165</v>
+        <v>82</v>
       </c>
       <c r="E436" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F436" s="7" t="s">
-        <v>166</v>
+        <v>1913</v>
       </c>
       <c r="G436" s="7" t="s">
-        <v>1590</v>
+        <v>1914</v>
       </c>
       <c r="H436" s="7" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="I436" s="7">
         <v>2</v>
       </c>
       <c r="S436" s="1" t="s">
-        <v>1910</v>
+        <v>1915</v>
       </c>
     </row>
     <row r="437" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="5" t="s">
-        <v>1911</v>
+        <v>292</v>
       </c>
       <c r="B437" s="5" t="s">
-        <v>1912</v>
+        <v>1916</v>
       </c>
       <c r="D437" s="5" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="E437" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F437" s="7" t="s">
-        <v>1913</v>
+        <v>1917</v>
       </c>
       <c r="G437" s="7" t="s">
-        <v>1914</v>
+        <v>1918</v>
       </c>
       <c r="H437" s="7" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="I437" s="7">
-        <v>2</v>
-      </c>
-      <c r="S437" s="1" t="s">
-        <v>1915</v>
+        <v>3</v>
       </c>
     </row>
     <row r="438" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="5" t="s">
-        <v>292</v>
+        <v>1919</v>
       </c>
       <c r="B438" s="5" t="s">
-        <v>1916</v>
+        <v>1920</v>
       </c>
       <c r="D438" s="5" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="E438" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F438" s="7" t="s">
-        <v>1917</v>
+        <v>1154</v>
       </c>
       <c r="G438" s="7" t="s">
-        <v>1918</v>
+        <v>842</v>
       </c>
       <c r="H438" s="7" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="I438" s="7">
         <v>3</v>
@@ -21310,22 +21310,22 @@
     </row>
     <row r="439" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="5" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="B439" s="5" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="D439" s="5" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="E439" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F439" s="7" t="s">
-        <v>1154</v>
+        <v>874</v>
       </c>
       <c r="G439" s="7" t="s">
-        <v>842</v>
+        <v>1179</v>
       </c>
       <c r="H439" s="7" t="s">
         <v>29</v>
@@ -21336,77 +21336,77 @@
     </row>
     <row r="440" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="5" t="s">
-        <v>1921</v>
+        <v>322</v>
       </c>
       <c r="B440" s="5" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="D440" s="5" t="s">
-        <v>349</v>
+        <v>60</v>
       </c>
       <c r="E440" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F440" s="7" t="s">
-        <v>874</v>
-      </c>
-      <c r="G440" s="7" t="s">
-        <v>1179</v>
+        <v>26</v>
+      </c>
+      <c r="F440" s="7">
+        <v>1577</v>
+      </c>
+      <c r="G440" s="7">
+        <v>1640</v>
       </c>
       <c r="H440" s="7" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I440" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S440" s="1" t="s">
+        <v>1924</v>
       </c>
     </row>
     <row r="441" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="5" t="s">
-        <v>322</v>
+        <v>1925</v>
       </c>
       <c r="B441" s="5" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="D441" s="5" t="s">
-        <v>60</v>
+        <v>165</v>
       </c>
       <c r="E441" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F441" s="7">
-        <v>1577</v>
-      </c>
-      <c r="G441" s="7">
-        <v>1640</v>
+      <c r="F441" s="7" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G441" s="7" t="s">
+        <v>1927</v>
       </c>
       <c r="H441" s="7" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
       <c r="I441" s="7">
-        <v>2</v>
-      </c>
-      <c r="S441" s="1" t="s">
-        <v>1924</v>
+        <v>3</v>
       </c>
     </row>
     <row r="442" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="5" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="B442" s="5" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="D442" s="5" t="s">
-        <v>165</v>
+        <v>25</v>
       </c>
       <c r="E442" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F442" s="7" t="s">
-        <v>1109</v>
+        <v>55</v>
       </c>
       <c r="G442" s="7" t="s">
-        <v>1927</v>
+        <v>1415</v>
       </c>
       <c r="H442" s="7" t="s">
         <v>50</v>
@@ -21417,25 +21417,25 @@
     </row>
     <row r="443" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="5" t="s">
-        <v>1928</v>
+        <v>491</v>
       </c>
       <c r="B443" s="5" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="D443" s="5" t="s">
-        <v>25</v>
+        <v>273</v>
       </c>
       <c r="E443" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F443" s="7" t="s">
-        <v>55</v>
+        <v>1143</v>
       </c>
       <c r="G443" s="7" t="s">
-        <v>1415</v>
+        <v>1391</v>
       </c>
       <c r="H443" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I443" s="7">
         <v>3</v>
@@ -21443,187 +21443,190 @@
     </row>
     <row r="444" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="s">
-        <v>491</v>
+        <v>1931</v>
       </c>
       <c r="B444" s="5" t="s">
-        <v>1930</v>
+        <v>1932</v>
+      </c>
+      <c r="C444" s="5" t="s">
+        <v>1933</v>
       </c>
       <c r="D444" s="5" t="s">
-        <v>273</v>
+        <v>1934</v>
       </c>
       <c r="E444" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F444" s="7" t="s">
-        <v>1143</v>
+        <v>645</v>
       </c>
       <c r="G444" s="7" t="s">
-        <v>1391</v>
+        <v>1166</v>
       </c>
       <c r="H444" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I444" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S444" s="1" t="s">
+        <v>1935</v>
+      </c>
+      <c r="T444" s="1" t="s">
+        <v>1936</v>
+      </c>
+      <c r="V444" t="s">
+        <v>1937</v>
+      </c>
+      <c r="W444" t="s">
+        <v>1938</v>
       </c>
     </row>
     <row r="445" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="5" t="s">
-        <v>1931</v>
+        <v>1939</v>
       </c>
       <c r="B445" s="5" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C445" s="5" t="s">
-        <v>1933</v>
+        <v>1940</v>
       </c>
       <c r="D445" s="5" t="s">
-        <v>1934</v>
+        <v>349</v>
       </c>
       <c r="E445" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F445" s="7" t="s">
-        <v>645</v>
+        <v>219</v>
       </c>
       <c r="G445" s="7" t="s">
-        <v>1166</v>
+        <v>669</v>
       </c>
       <c r="H445" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I445" s="7">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="S445" s="1" t="s">
-        <v>1935</v>
-      </c>
-      <c r="T445" s="1" t="s">
-        <v>1936</v>
-      </c>
-      <c r="V445" t="s">
-        <v>1937</v>
-      </c>
-      <c r="W445" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
     </row>
     <row r="446" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="5" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="B446" s="5" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="D446" s="5" t="s">
-        <v>349</v>
+        <v>1944</v>
       </c>
       <c r="E446" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F446" s="7" t="s">
-        <v>219</v>
+        <v>432</v>
       </c>
       <c r="G446" s="7" t="s">
-        <v>669</v>
+        <v>573</v>
       </c>
       <c r="H446" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I446" s="7">
-        <v>2</v>
-      </c>
-      <c r="S446" s="1" t="s">
-        <v>1941</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="5" t="s">
-        <v>1942</v>
+        <v>1036</v>
       </c>
       <c r="B447" s="5" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="D447" s="5" t="s">
-        <v>1944</v>
+        <v>60</v>
       </c>
       <c r="E447" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F447" s="7" t="s">
+        <v>971</v>
+      </c>
+      <c r="G447" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="G447" s="7" t="s">
-        <v>573</v>
-      </c>
       <c r="H447" s="7" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I447" s="7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="448" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
-        <v>1036</v>
+        <v>1107</v>
       </c>
       <c r="B448" s="5" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D448" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E448" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F448" s="7" t="s">
-        <v>971</v>
+        <v>77</v>
       </c>
       <c r="G448" s="7" t="s">
-        <v>432</v>
+        <v>112</v>
       </c>
       <c r="H448" s="7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I448" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S448" s="1" t="s">
+        <v>1947</v>
       </c>
     </row>
     <row r="449" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="s">
-        <v>1107</v>
+        <v>322</v>
       </c>
       <c r="B449" s="5" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="D449" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E449" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F449" s="7" t="s">
-        <v>77</v>
+        <v>716</v>
       </c>
       <c r="G449" s="7" t="s">
-        <v>112</v>
+        <v>1100</v>
       </c>
       <c r="H449" s="7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I449" s="7">
         <v>2</v>
       </c>
       <c r="S449" s="1" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
     </row>
     <row r="450" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="5" t="s">
-        <v>322</v>
+        <v>1950</v>
       </c>
       <c r="B450" s="5" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="D450" s="5" t="s">
         <v>60</v>
@@ -21632,71 +21635,68 @@
         <v>26</v>
       </c>
       <c r="F450" s="7" t="s">
-        <v>716</v>
+        <v>393</v>
       </c>
       <c r="G450" s="7" t="s">
-        <v>1100</v>
+        <v>1952</v>
       </c>
       <c r="H450" s="7" t="s">
         <v>43</v>
       </c>
       <c r="I450" s="7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="S450" s="1" t="s">
-        <v>1949</v>
+        <v>1953</v>
       </c>
     </row>
     <row r="451" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A451" s="5" t="s">
-        <v>1950</v>
+      <c r="A451" s="11" t="s">
+        <v>1963</v>
       </c>
       <c r="B451" s="5" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="D451" s="5" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="E451" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F451" s="7" t="s">
-        <v>393</v>
+        <v>149</v>
       </c>
       <c r="G451" s="7" t="s">
-        <v>1952</v>
+        <v>199</v>
       </c>
       <c r="H451" s="7" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="I451" s="7">
         <v>3</v>
       </c>
-      <c r="S451" s="1" t="s">
-        <v>1953</v>
-      </c>
     </row>
     <row r="452" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A452" s="11" t="s">
-        <v>1963</v>
+      <c r="A452" s="5" t="s">
+        <v>552</v>
       </c>
       <c r="B452" s="5" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="D452" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E452" s="5" t="s">
         <v>26</v>
       </c>
       <c r="F452" s="7" t="s">
-        <v>149</v>
+        <v>1956</v>
       </c>
       <c r="G452" s="7" t="s">
-        <v>199</v>
+        <v>27</v>
       </c>
       <c r="H452" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I452" s="7">
         <v>3</v>
@@ -21704,25 +21704,25 @@
     </row>
     <row r="453" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="s">
-        <v>552</v>
+        <v>1957</v>
       </c>
       <c r="B453" s="5" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="D453" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E453" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F453" s="7" t="s">
-        <v>1956</v>
+        <v>286</v>
       </c>
       <c r="G453" s="7" t="s">
-        <v>27</v>
+        <v>1027</v>
       </c>
       <c r="H453" s="7" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="I453" s="7">
         <v>3</v>
@@ -21730,94 +21730,97 @@
     </row>
     <row r="454" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="B454" s="5" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="D454" s="5" t="s">
-        <v>60</v>
+        <v>349</v>
       </c>
       <c r="E454" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F454" s="7" t="s">
-        <v>286</v>
+        <v>1076</v>
       </c>
       <c r="G454" s="7" t="s">
-        <v>1027</v>
+        <v>1961</v>
       </c>
       <c r="H454" s="7" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="I454" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S454" s="1" t="s">
+        <v>1962</v>
       </c>
     </row>
     <row r="455" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="5" t="s">
-        <v>1959</v>
+        <v>1963</v>
       </c>
       <c r="B455" s="5" t="s">
-        <v>1960</v>
+        <v>1964</v>
       </c>
       <c r="D455" s="5" t="s">
-        <v>349</v>
+        <v>60</v>
       </c>
       <c r="E455" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F455" s="7" t="s">
-        <v>1076</v>
+        <v>1965</v>
       </c>
       <c r="G455" s="7" t="s">
-        <v>1961</v>
+        <v>454</v>
       </c>
       <c r="H455" s="7" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="I455" s="7">
         <v>2</v>
       </c>
       <c r="S455" s="1" t="s">
-        <v>1962</v>
+        <v>1966</v>
       </c>
     </row>
     <row r="456" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="5" t="s">
-        <v>1963</v>
+        <v>974</v>
       </c>
       <c r="B456" s="5" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="D456" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E456" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F456" s="7" t="s">
-        <v>1965</v>
+        <v>640</v>
       </c>
       <c r="G456" s="7" t="s">
-        <v>454</v>
+        <v>1415</v>
       </c>
       <c r="H456" s="7" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="I456" s="7">
         <v>2</v>
       </c>
       <c r="S456" s="1" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="457" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="s">
-        <v>974</v>
+        <v>1969</v>
       </c>
       <c r="B457" s="5" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="D457" s="5" t="s">
         <v>25</v>
@@ -21826,10 +21829,10 @@
         <v>40</v>
       </c>
       <c r="F457" s="7" t="s">
-        <v>640</v>
+        <v>1971</v>
       </c>
       <c r="G457" s="7" t="s">
-        <v>1415</v>
+        <v>199</v>
       </c>
       <c r="H457" s="7" t="s">
         <v>50</v>
@@ -21838,18 +21841,21 @@
         <v>2</v>
       </c>
       <c r="S457" s="1" t="s">
-        <v>1968</v>
+        <v>1972</v>
+      </c>
+      <c r="T457" s="1" t="s">
+        <v>1973</v>
       </c>
     </row>
     <row r="458" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="5" t="s">
-        <v>1969</v>
+        <v>1974</v>
       </c>
       <c r="B458" s="5" t="s">
-        <v>1970</v>
+        <v>1975</v>
       </c>
       <c r="D458" s="5" t="s">
-        <v>25</v>
+        <v>362</v>
       </c>
       <c r="E458" s="5" t="s">
         <v>40</v>
@@ -21858,42 +21864,36 @@
         <v>1971</v>
       </c>
       <c r="G458" s="7" t="s">
-        <v>199</v>
+        <v>669</v>
       </c>
       <c r="H458" s="7" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="I458" s="7">
-        <v>2</v>
-      </c>
-      <c r="S458" s="1" t="s">
-        <v>1972</v>
-      </c>
-      <c r="T458" s="1" t="s">
-        <v>1973</v>
+        <v>3</v>
       </c>
     </row>
     <row r="459" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="s">
-        <v>1974</v>
+        <v>628</v>
       </c>
       <c r="B459" s="5" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="D459" s="5" t="s">
-        <v>362</v>
+        <v>39</v>
       </c>
       <c r="E459" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F459" s="7" t="s">
-        <v>1971</v>
+        <v>1977</v>
       </c>
       <c r="G459" s="7" t="s">
-        <v>669</v>
+        <v>1840</v>
       </c>
       <c r="H459" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I459" s="7">
         <v>3</v>
@@ -21901,36 +21901,39 @@
     </row>
     <row r="460" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="5" t="s">
-        <v>628</v>
+        <v>1978</v>
       </c>
       <c r="B460" s="5" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="D460" s="5" t="s">
-        <v>39</v>
+        <v>273</v>
       </c>
       <c r="E460" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F460" s="7" t="s">
-        <v>1977</v>
+        <v>303</v>
       </c>
       <c r="G460" s="7" t="s">
-        <v>1840</v>
+        <v>961</v>
       </c>
       <c r="H460" s="7" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="I460" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S460" s="1" t="s">
+        <v>1980</v>
       </c>
     </row>
     <row r="461" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="5" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="B461" s="5" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="D461" s="5" t="s">
         <v>273</v>
@@ -21939,94 +21942,97 @@
         <v>40</v>
       </c>
       <c r="F461" s="7" t="s">
-        <v>303</v>
+        <v>960</v>
       </c>
       <c r="G461" s="7" t="s">
-        <v>961</v>
+        <v>776</v>
       </c>
       <c r="H461" s="7" t="s">
         <v>156</v>
       </c>
       <c r="I461" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S461" s="1" t="s">
-        <v>1980</v>
+        <v>1983</v>
+      </c>
+      <c r="T461" s="1" t="s">
+        <v>1984</v>
+      </c>
+      <c r="V461" t="s">
+        <v>1827</v>
+      </c>
+      <c r="W461" t="s">
+        <v>1985</v>
       </c>
     </row>
     <row r="462" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="5" t="s">
-        <v>1981</v>
+        <v>1986</v>
       </c>
       <c r="B462" s="5" t="s">
-        <v>1982</v>
+        <v>1987</v>
       </c>
       <c r="D462" s="5" t="s">
-        <v>273</v>
+        <v>39</v>
       </c>
       <c r="E462" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F462" s="7" t="s">
-        <v>960</v>
+        <v>640</v>
       </c>
       <c r="G462" s="7" t="s">
-        <v>776</v>
+        <v>311</v>
       </c>
       <c r="H462" s="7" t="s">
-        <v>156</v>
+        <v>50</v>
       </c>
       <c r="I462" s="7">
-        <v>1</v>
-      </c>
-      <c r="S462" s="1" t="s">
-        <v>1983</v>
+        <v>3</v>
       </c>
       <c r="T462" s="1" t="s">
-        <v>1984</v>
-      </c>
-      <c r="V462" t="s">
-        <v>1827</v>
-      </c>
-      <c r="W462" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
     </row>
     <row r="463" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="5" t="s">
-        <v>1986</v>
+        <v>442</v>
       </c>
       <c r="B463" s="5" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="D463" s="5" t="s">
-        <v>39</v>
+        <v>273</v>
       </c>
       <c r="E463" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F463" s="7" t="s">
-        <v>640</v>
+        <v>1990</v>
       </c>
       <c r="G463" s="7" t="s">
-        <v>311</v>
+        <v>1991</v>
       </c>
       <c r="H463" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I463" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S463" s="1" t="s">
+        <v>1992</v>
       </c>
       <c r="T463" s="1" t="s">
-        <v>1988</v>
+        <v>1993</v>
       </c>
     </row>
     <row r="464" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="5" t="s">
-        <v>442</v>
+        <v>1264</v>
       </c>
       <c r="B464" s="5" t="s">
-        <v>1989</v>
+        <v>1994</v>
       </c>
       <c r="D464" s="5" t="s">
         <v>273</v>
@@ -22035,68 +22041,71 @@
         <v>40</v>
       </c>
       <c r="F464" s="7" t="s">
-        <v>1990</v>
+        <v>784</v>
       </c>
       <c r="G464" s="7" t="s">
-        <v>1991</v>
+        <v>1995</v>
       </c>
       <c r="H464" s="7" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="I464" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S464" s="1" t="s">
-        <v>1992</v>
+        <v>1996</v>
       </c>
       <c r="T464" s="1" t="s">
-        <v>1993</v>
+        <v>1997</v>
+      </c>
+      <c r="V464" t="s">
+        <v>1998</v>
+      </c>
+      <c r="W464" t="s">
+        <v>1999</v>
       </c>
     </row>
     <row r="465" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
-        <v>1264</v>
+        <v>2000</v>
       </c>
       <c r="B465" s="5" t="s">
-        <v>1994</v>
+        <v>2001</v>
       </c>
       <c r="D465" s="5" t="s">
-        <v>273</v>
+        <v>39</v>
       </c>
       <c r="E465" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F465" s="7" t="s">
-        <v>784</v>
+        <v>1310</v>
       </c>
       <c r="G465" s="7" t="s">
-        <v>1995</v>
+        <v>1865</v>
       </c>
       <c r="H465" s="7" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="I465" s="7">
         <v>1</v>
       </c>
       <c r="S465" s="1" t="s">
-        <v>1996</v>
-      </c>
-      <c r="T465" s="1" t="s">
-        <v>1997</v>
+        <v>2002</v>
       </c>
       <c r="V465" t="s">
-        <v>1998</v>
+        <v>2003</v>
       </c>
       <c r="W465" t="s">
-        <v>1999</v>
+        <v>2004</v>
       </c>
     </row>
     <row r="466" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="s">
-        <v>2000</v>
+        <v>1264</v>
       </c>
       <c r="B466" s="5" t="s">
-        <v>2001</v>
+        <v>2005</v>
       </c>
       <c r="D466" s="5" t="s">
         <v>39</v>
@@ -22105,33 +22114,24 @@
         <v>40</v>
       </c>
       <c r="F466" s="7" t="s">
-        <v>1310</v>
+        <v>330</v>
       </c>
       <c r="G466" s="7" t="s">
-        <v>1865</v>
+        <v>862</v>
       </c>
       <c r="H466" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I466" s="7">
-        <v>1</v>
-      </c>
-      <c r="S466" s="1" t="s">
-        <v>2002</v>
-      </c>
-      <c r="V466" t="s">
-        <v>2003</v>
-      </c>
-      <c r="W466" t="s">
-        <v>2004</v>
+        <v>3</v>
       </c>
     </row>
     <row r="467" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="5" t="s">
-        <v>1264</v>
+        <v>982</v>
       </c>
       <c r="B467" s="5" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="D467" s="5" t="s">
         <v>39</v>
@@ -22140,13 +22140,13 @@
         <v>40</v>
       </c>
       <c r="F467" s="7" t="s">
-        <v>330</v>
+        <v>1649</v>
       </c>
       <c r="G467" s="7" t="s">
-        <v>862</v>
+        <v>341</v>
       </c>
       <c r="H467" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I467" s="7">
         <v>3</v>
@@ -22154,10 +22154,10 @@
     </row>
     <row r="468" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="s">
-        <v>982</v>
+        <v>2007</v>
       </c>
       <c r="B468" s="5" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="D468" s="5" t="s">
         <v>39</v>
@@ -22166,13 +22166,13 @@
         <v>40</v>
       </c>
       <c r="F468" s="7" t="s">
-        <v>1649</v>
+        <v>89</v>
       </c>
       <c r="G468" s="7" t="s">
-        <v>341</v>
+        <v>862</v>
       </c>
       <c r="H468" s="7" t="s">
-        <v>43</v>
+        <v>63</v>
       </c>
       <c r="I468" s="7">
         <v>3</v>
@@ -22180,10 +22180,10 @@
     </row>
     <row r="469" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="5" t="s">
-        <v>2007</v>
+        <v>714</v>
       </c>
       <c r="B469" s="5" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="D469" s="5" t="s">
         <v>39</v>
@@ -22192,13 +22192,13 @@
         <v>40</v>
       </c>
       <c r="F469" s="7" t="s">
-        <v>89</v>
+        <v>759</v>
       </c>
       <c r="G469" s="7" t="s">
-        <v>862</v>
+        <v>1914</v>
       </c>
       <c r="H469" s="7" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="I469" s="7">
         <v>3</v>
@@ -22206,25 +22206,25 @@
     </row>
     <row r="470" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="s">
-        <v>714</v>
+        <v>2010</v>
       </c>
       <c r="B470" s="5" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D470" s="5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E470" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F470" s="7" t="s">
-        <v>759</v>
+        <v>33</v>
       </c>
       <c r="G470" s="7" t="s">
-        <v>1914</v>
+        <v>2012</v>
       </c>
       <c r="H470" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I470" s="7">
         <v>3</v>
@@ -22232,25 +22232,25 @@
     </row>
     <row r="471" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="s">
-        <v>2010</v>
+        <v>470</v>
       </c>
       <c r="B471" s="5" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D471" s="5" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="E471" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F471" s="7" t="s">
-        <v>33</v>
+        <v>1143</v>
       </c>
       <c r="G471" s="7" t="s">
-        <v>2012</v>
+        <v>1637</v>
       </c>
       <c r="H471" s="7" t="s">
-        <v>29</v>
+        <v>63</v>
       </c>
       <c r="I471" s="7">
         <v>3</v>
@@ -22258,10 +22258,13 @@
     </row>
     <row r="472" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="5" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
       <c r="B472" s="5" t="s">
-        <v>2013</v>
+        <v>2014</v>
+      </c>
+      <c r="C472" s="5" t="s">
+        <v>2015</v>
       </c>
       <c r="D472" s="5" t="s">
         <v>39</v>
@@ -22270,27 +22273,33 @@
         <v>40</v>
       </c>
       <c r="F472" s="7" t="s">
-        <v>1143</v>
+        <v>134</v>
       </c>
       <c r="G472" s="7" t="s">
-        <v>1637</v>
+        <v>98</v>
       </c>
       <c r="H472" s="7" t="s">
         <v>63</v>
       </c>
       <c r="I472" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S472" s="1" t="s">
+        <v>2016</v>
+      </c>
+      <c r="V472" t="s">
+        <v>2017</v>
+      </c>
+      <c r="W472" t="s">
+        <v>2018</v>
       </c>
     </row>
     <row r="473" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="s">
-        <v>482</v>
+        <v>1342</v>
       </c>
       <c r="B473" s="5" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C473" s="5" t="s">
-        <v>2015</v>
+        <v>2019</v>
       </c>
       <c r="D473" s="5" t="s">
         <v>39</v>
@@ -22299,33 +22308,24 @@
         <v>40</v>
       </c>
       <c r="F473" s="7" t="s">
-        <v>134</v>
+        <v>867</v>
       </c>
       <c r="G473" s="7" t="s">
-        <v>98</v>
+        <v>1214</v>
       </c>
       <c r="H473" s="7" t="s">
         <v>63</v>
       </c>
       <c r="I473" s="7">
-        <v>1</v>
-      </c>
-      <c r="S473" s="1" t="s">
-        <v>2016</v>
-      </c>
-      <c r="V473" t="s">
-        <v>2017</v>
-      </c>
-      <c r="W473" t="s">
-        <v>2018</v>
+        <v>3</v>
       </c>
     </row>
     <row r="474" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="5" t="s">
-        <v>1342</v>
+        <v>2020</v>
       </c>
       <c r="B474" s="5" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D474" s="5" t="s">
         <v>39</v>
@@ -22334,10 +22334,10 @@
         <v>40</v>
       </c>
       <c r="F474" s="7" t="s">
-        <v>867</v>
+        <v>2022</v>
       </c>
       <c r="G474" s="7" t="s">
-        <v>1214</v>
+        <v>2023</v>
       </c>
       <c r="H474" s="7" t="s">
         <v>63</v>
@@ -22348,25 +22348,25 @@
     </row>
     <row r="475" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="5" t="s">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="B475" s="5" t="s">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D475" s="5" t="s">
-        <v>39</v>
+        <v>273</v>
       </c>
       <c r="E475" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F475" s="7" t="s">
-        <v>2022</v>
+        <v>48</v>
       </c>
       <c r="G475" s="7" t="s">
-        <v>2023</v>
+        <v>574</v>
       </c>
       <c r="H475" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I475" s="7">
         <v>3</v>
@@ -22374,36 +22374,42 @@
     </row>
     <row r="476" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="5" t="s">
-        <v>2024</v>
+        <v>183</v>
       </c>
       <c r="B476" s="5" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D476" s="5" t="s">
-        <v>273</v>
+        <v>60</v>
       </c>
       <c r="E476" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F476" s="7" t="s">
-        <v>48</v>
-      </c>
-      <c r="G476" s="7" t="s">
-        <v>574</v>
+        <v>60</v>
+      </c>
+      <c r="F476" s="7">
+        <v>1511</v>
+      </c>
+      <c r="G476" s="7">
+        <v>1574</v>
       </c>
       <c r="H476" s="7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I476" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S476" s="1" t="s">
+        <v>2027</v>
       </c>
     </row>
     <row r="477" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="5" t="s">
-        <v>183</v>
+        <v>131</v>
       </c>
       <c r="B477" s="5" t="s">
-        <v>2026</v>
+        <v>2028</v>
+      </c>
+      <c r="C477" s="5" t="s">
+        <v>2029</v>
       </c>
       <c r="D477" s="5" t="s">
         <v>60</v>
@@ -22411,11 +22417,11 @@
       <c r="E477" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F477" s="7">
-        <v>1511</v>
-      </c>
-      <c r="G477" s="7">
-        <v>1574</v>
+      <c r="F477" s="7" t="s">
+        <v>334</v>
+      </c>
+      <c r="G477" s="7" t="s">
+        <v>772</v>
       </c>
       <c r="H477" s="7" t="s">
         <v>43</v>
@@ -22424,129 +22430,123 @@
         <v>1</v>
       </c>
       <c r="S477" s="1" t="s">
-        <v>2027</v>
+        <v>2030</v>
+      </c>
+      <c r="V477" t="s">
+        <v>2031</v>
+      </c>
+      <c r="W477" t="s">
+        <v>2032</v>
       </c>
     </row>
     <row r="478" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="5" t="s">
-        <v>131</v>
+        <v>801</v>
       </c>
       <c r="B478" s="5" t="s">
-        <v>2028</v>
-      </c>
-      <c r="C478" s="5" t="s">
-        <v>2029</v>
+        <v>2033</v>
       </c>
       <c r="D478" s="5" t="s">
-        <v>60</v>
+        <v>362</v>
       </c>
       <c r="E478" s="5" t="s">
-        <v>60</v>
+        <v>26</v>
       </c>
       <c r="F478" s="7" t="s">
-        <v>334</v>
+        <v>2034</v>
       </c>
       <c r="G478" s="7" t="s">
-        <v>772</v>
+        <v>591</v>
       </c>
       <c r="H478" s="7" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I478" s="7">
-        <v>1</v>
-      </c>
-      <c r="S478" s="1" t="s">
-        <v>2030</v>
-      </c>
-      <c r="V478" t="s">
-        <v>2031</v>
-      </c>
-      <c r="W478" t="s">
-        <v>2032</v>
+        <v>3</v>
       </c>
     </row>
     <row r="479" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="s">
-        <v>801</v>
+        <v>880</v>
       </c>
       <c r="B479" s="5" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="D479" s="5" t="s">
-        <v>362</v>
+        <v>299</v>
       </c>
       <c r="E479" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F479" s="7" t="s">
-        <v>2034</v>
+        <v>1990</v>
       </c>
       <c r="G479" s="7" t="s">
-        <v>591</v>
+        <v>626</v>
       </c>
       <c r="H479" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I479" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S479" s="1" t="s">
+        <v>2036</v>
+      </c>
+      <c r="V479" t="s">
+        <v>2037</v>
+      </c>
+      <c r="W479" t="s">
+        <v>2038</v>
       </c>
     </row>
     <row r="480" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="s">
-        <v>880</v>
+        <v>252</v>
       </c>
       <c r="B480" s="5" t="s">
-        <v>2035</v>
+        <v>2039</v>
       </c>
       <c r="D480" s="5" t="s">
-        <v>299</v>
+        <v>60</v>
       </c>
       <c r="E480" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F480" s="7" t="s">
-        <v>1990</v>
+        <v>608</v>
       </c>
       <c r="G480" s="7" t="s">
-        <v>626</v>
+        <v>2040</v>
       </c>
       <c r="H480" s="7" t="s">
-        <v>63</v>
+        <v>156</v>
       </c>
       <c r="I480" s="7">
-        <v>1</v>
-      </c>
-      <c r="S480" s="1" t="s">
-        <v>2036</v>
-      </c>
-      <c r="V480" t="s">
-        <v>2037</v>
-      </c>
-      <c r="W480" t="s">
-        <v>2038</v>
+        <v>3</v>
       </c>
     </row>
     <row r="481" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="5" t="s">
-        <v>252</v>
+        <v>2043</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>2039</v>
+        <v>2044</v>
       </c>
       <c r="D481" s="5" t="s">
-        <v>60</v>
+        <v>273</v>
       </c>
       <c r="E481" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F481" s="7" t="s">
-        <v>608</v>
+        <v>1742</v>
       </c>
       <c r="G481" s="7" t="s">
-        <v>2040</v>
+        <v>424</v>
       </c>
       <c r="H481" s="7" t="s">
-        <v>156</v>
+        <v>63</v>
       </c>
       <c r="I481" s="7">
         <v>3</v>
@@ -22554,187 +22554,187 @@
     </row>
     <row r="482" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="5" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B482" s="5" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="D482" s="5" t="s">
-        <v>273</v>
+        <v>39</v>
       </c>
       <c r="E482" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F482" s="7" t="s">
-        <v>1742</v>
+        <v>831</v>
       </c>
       <c r="G482" s="7" t="s">
-        <v>424</v>
+        <v>1071</v>
       </c>
       <c r="H482" s="7" t="s">
         <v>63</v>
       </c>
       <c r="I482" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S482" s="1" t="s">
+        <v>2047</v>
+      </c>
+      <c r="V482" t="s">
+        <v>2048</v>
+      </c>
+      <c r="W482" t="s">
+        <v>2049</v>
       </c>
     </row>
     <row r="483" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="s">
-        <v>2045</v>
+        <v>2050</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>2046</v>
+        <v>2051</v>
       </c>
       <c r="D483" s="5" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="E483" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F483" s="7" t="s">
-        <v>831</v>
+        <v>1678</v>
       </c>
       <c r="G483" s="7" t="s">
-        <v>1071</v>
+        <v>1450</v>
       </c>
       <c r="H483" s="7" t="s">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="I483" s="7">
-        <v>1</v>
-      </c>
-      <c r="S483" s="1" t="s">
-        <v>2047</v>
-      </c>
-      <c r="V483" t="s">
-        <v>2048</v>
-      </c>
-      <c r="W483" t="s">
-        <v>2049</v>
+        <v>3</v>
       </c>
     </row>
     <row r="484" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="5" t="s">
-        <v>2050</v>
+        <v>1963</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="D484" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E484" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F484" s="7" t="s">
-        <v>1678</v>
+        <v>1100</v>
       </c>
       <c r="G484" s="7" t="s">
-        <v>1450</v>
+        <v>2053</v>
       </c>
       <c r="H484" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I484" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S484" s="1" t="s">
+        <v>2054</v>
+      </c>
+      <c r="V484" t="s">
+        <v>2055</v>
+      </c>
+      <c r="W484" t="s">
+        <v>2056</v>
       </c>
     </row>
     <row r="485" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="5" t="s">
-        <v>1963</v>
+        <v>2057</v>
       </c>
       <c r="B485" s="5" t="s">
-        <v>2052</v>
+        <v>2058</v>
       </c>
       <c r="D485" s="5" t="s">
-        <v>60</v>
+        <v>25</v>
       </c>
       <c r="E485" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F485" s="7" t="s">
-        <v>1100</v>
+        <v>1154</v>
       </c>
       <c r="G485" s="7" t="s">
-        <v>2053</v>
+        <v>2059</v>
       </c>
       <c r="H485" s="7" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I485" s="7">
         <v>2</v>
       </c>
       <c r="S485" s="1" t="s">
-        <v>2054</v>
-      </c>
-      <c r="V485" t="s">
-        <v>2055</v>
-      </c>
-      <c r="W485" t="s">
-        <v>2056</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="486" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="5" t="s">
-        <v>2057</v>
+        <v>58</v>
       </c>
       <c r="B486" s="5" t="s">
-        <v>2058</v>
+        <v>2063</v>
       </c>
       <c r="D486" s="5" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="E486" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F486" s="7" t="s">
-        <v>1154</v>
+        <v>955</v>
       </c>
       <c r="G486" s="7" t="s">
-        <v>2059</v>
+        <v>369</v>
       </c>
       <c r="H486" s="7" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="I486" s="7">
         <v>2</v>
       </c>
       <c r="S486" s="1" t="s">
-        <v>2060</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="487" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
-        <v>58</v>
+        <v>2065</v>
       </c>
       <c r="B487" s="5" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="D487" s="5" t="s">
         <v>60</v>
       </c>
       <c r="E487" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F487" s="7" t="s">
-        <v>955</v>
+        <v>2067</v>
       </c>
       <c r="G487" s="7" t="s">
-        <v>369</v>
+        <v>1715</v>
       </c>
       <c r="H487" s="7" t="s">
-        <v>43</v>
+        <v>156</v>
       </c>
       <c r="I487" s="7">
-        <v>2</v>
-      </c>
-      <c r="S487" s="1" t="s">
-        <v>2064</v>
+        <v>3</v>
       </c>
     </row>
     <row r="488" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="5" t="s">
-        <v>2065</v>
+        <v>536</v>
       </c>
       <c r="B488" s="5" t="s">
         <v>2066</v>
@@ -22746,10 +22746,10 @@
         <v>40</v>
       </c>
       <c r="F488" s="7" t="s">
-        <v>2067</v>
+        <v>453</v>
       </c>
       <c r="G488" s="7" t="s">
-        <v>1715</v>
+        <v>2068</v>
       </c>
       <c r="H488" s="7" t="s">
         <v>156</v>
@@ -22760,7 +22760,7 @@
     </row>
     <row r="489" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="5" t="s">
-        <v>536</v>
+        <v>86</v>
       </c>
       <c r="B489" s="5" t="s">
         <v>2066</v>
@@ -22772,10 +22772,10 @@
         <v>40</v>
       </c>
       <c r="F489" s="7" t="s">
-        <v>453</v>
+        <v>2069</v>
       </c>
       <c r="G489" s="7" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="H489" s="7" t="s">
         <v>156</v>
@@ -22786,25 +22786,25 @@
     </row>
     <row r="490" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="5" t="s">
-        <v>86</v>
+        <v>2071</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>2066</v>
+        <v>2072</v>
       </c>
       <c r="D490" s="5" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E490" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F490" s="7" t="s">
-        <v>2069</v>
+        <v>2073</v>
       </c>
       <c r="G490" s="7" t="s">
-        <v>2070</v>
+        <v>2074</v>
       </c>
       <c r="H490" s="7" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="I490" s="7">
         <v>3</v>
@@ -22812,25 +22812,25 @@
     </row>
     <row r="491" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="5" t="s">
-        <v>2071</v>
+        <v>2075</v>
       </c>
       <c r="B491" s="5" t="s">
-        <v>2072</v>
+        <v>2076</v>
       </c>
       <c r="D491" s="5" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="E491" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F491" s="7" t="s">
-        <v>2073</v>
+        <v>633</v>
       </c>
       <c r="G491" s="7" t="s">
-        <v>2074</v>
+        <v>308</v>
       </c>
       <c r="H491" s="7" t="s">
-        <v>56</v>
+        <v>50</v>
       </c>
       <c r="I491" s="7">
         <v>3</v>
@@ -22838,10 +22838,10 @@
     </row>
     <row r="492" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="5" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="D492" s="5" t="s">
         <v>53</v>
@@ -22850,10 +22850,10 @@
         <v>40</v>
       </c>
       <c r="F492" s="7" t="s">
-        <v>633</v>
+        <v>1109</v>
       </c>
       <c r="G492" s="7" t="s">
-        <v>308</v>
+        <v>199</v>
       </c>
       <c r="H492" s="7" t="s">
         <v>50</v>
@@ -22864,25 +22864,25 @@
     </row>
     <row r="493" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="5" t="s">
-        <v>2077</v>
+        <v>1514</v>
       </c>
       <c r="B493" s="5" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="D493" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E493" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F493" s="7" t="s">
-        <v>1109</v>
+        <v>1432</v>
       </c>
       <c r="G493" s="7" t="s">
-        <v>199</v>
+        <v>1520</v>
       </c>
       <c r="H493" s="7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="I493" s="7">
         <v>3</v>
@@ -22890,25 +22890,25 @@
     </row>
     <row r="494" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="5" t="s">
-        <v>1514</v>
+        <v>2080</v>
       </c>
       <c r="B494" s="5" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="D494" s="5" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="E494" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F494" s="7" t="s">
-        <v>1432</v>
+        <v>602</v>
       </c>
       <c r="G494" s="7" t="s">
-        <v>1520</v>
+        <v>1185</v>
       </c>
       <c r="H494" s="7" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="I494" s="7">
         <v>3</v>
@@ -22916,126 +22916,126 @@
     </row>
     <row r="495" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="5" t="s">
-        <v>2080</v>
+        <v>1495</v>
       </c>
       <c r="B495" s="5" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="D495" s="5" t="s">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E495" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F495" s="7" t="s">
-        <v>602</v>
+        <v>307</v>
       </c>
       <c r="G495" s="7" t="s">
-        <v>1185</v>
+        <v>1244</v>
       </c>
       <c r="H495" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I495" s="7">
-        <v>3</v>
+        <v>2</v>
+      </c>
+      <c r="S495" s="1" t="s">
+        <v>2083</v>
       </c>
     </row>
     <row r="496" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="5" t="s">
-        <v>1495</v>
+        <v>2084</v>
       </c>
       <c r="B496" s="5" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="D496" s="5" t="s">
-        <v>25</v>
+        <v>349</v>
       </c>
       <c r="E496" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F496" s="7" t="s">
-        <v>307</v>
+        <v>2086</v>
       </c>
       <c r="G496" s="7" t="s">
-        <v>1244</v>
+        <v>904</v>
       </c>
       <c r="H496" s="7" t="s">
         <v>56</v>
       </c>
       <c r="I496" s="7">
-        <v>2</v>
-      </c>
-      <c r="S496" s="1" t="s">
-        <v>2083</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="5" t="s">
-        <v>2084</v>
+        <v>1323</v>
       </c>
       <c r="B497" s="5" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="D497" s="5" t="s">
-        <v>349</v>
+        <v>25</v>
       </c>
       <c r="E497" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F497" s="7" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="G497" s="7" t="s">
-        <v>904</v>
+        <v>294</v>
       </c>
       <c r="H497" s="7" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I497" s="7">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="S497" s="1" t="s">
+        <v>2089</v>
+      </c>
+      <c r="V497" t="s">
+        <v>2090</v>
+      </c>
+      <c r="W497" t="s">
+        <v>2091</v>
       </c>
     </row>
     <row r="498" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="5" t="s">
-        <v>1323</v>
+        <v>2092</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>2087</v>
+        <v>2093</v>
       </c>
       <c r="D498" s="5" t="s">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="E498" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F498" s="7" t="s">
-        <v>2088</v>
+        <v>657</v>
       </c>
       <c r="G498" s="7" t="s">
-        <v>294</v>
+        <v>2034</v>
       </c>
       <c r="H498" s="7" t="s">
         <v>29</v>
       </c>
       <c r="I498" s="7">
-        <v>1</v>
-      </c>
-      <c r="S498" s="1" t="s">
-        <v>2089</v>
-      </c>
-      <c r="V498" t="s">
-        <v>2090</v>
-      </c>
-      <c r="W498" t="s">
-        <v>2091</v>
+        <v>3</v>
       </c>
     </row>
     <row r="499" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="5" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="B499" s="5" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="D499" s="5" t="s">
         <v>165</v>
@@ -23044,13 +23044,13 @@
         <v>40</v>
       </c>
       <c r="F499" s="7" t="s">
-        <v>657</v>
+        <v>213</v>
       </c>
       <c r="G499" s="7" t="s">
-        <v>2034</v>
+        <v>1205</v>
       </c>
       <c r="H499" s="7" t="s">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="I499" s="7">
         <v>3</v>
@@ -23058,22 +23058,22 @@
     </row>
     <row r="500" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="5" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B500" s="5" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="D500" s="5" t="s">
         <v>165</v>
       </c>
       <c r="E500" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F500" s="7" t="s">
-        <v>213</v>
+        <v>2098</v>
       </c>
       <c r="G500" s="7" t="s">
-        <v>1205</v>
+        <v>2099</v>
       </c>
       <c r="H500" s="7" t="s">
         <v>56</v>
@@ -23081,48 +23081,48 @@
       <c r="I500" s="7">
         <v>3</v>
       </c>
+      <c r="S500" s="1" t="s">
+        <v>2100</v>
+      </c>
+      <c r="V500" t="s">
+        <v>2101</v>
+      </c>
+      <c r="W500" t="s">
+        <v>2102</v>
+      </c>
     </row>
     <row r="501" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="5" t="s">
-        <v>2096</v>
+        <v>2105</v>
       </c>
       <c r="B501" s="5" t="s">
-        <v>2097</v>
+        <v>2106</v>
       </c>
       <c r="D501" s="5" t="s">
-        <v>165</v>
+        <v>349</v>
       </c>
       <c r="E501" s="5" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="F501" s="7" t="s">
-        <v>2098</v>
+        <v>1678</v>
       </c>
       <c r="G501" s="7" t="s">
-        <v>2099</v>
+        <v>2107</v>
       </c>
       <c r="H501" s="7" t="s">
-        <v>56</v>
+        <v>29</v>
       </c>
       <c r="I501" s="7">
         <v>3</v>
       </c>
-      <c r="S501" s="1" t="s">
-        <v>2100</v>
-      </c>
-      <c r="V501" t="s">
-        <v>2101</v>
-      </c>
-      <c r="W501" t="s">
-        <v>2102</v>
-      </c>
     </row>
     <row r="502" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="5" t="s">
-        <v>2105</v>
+        <v>1640</v>
       </c>
       <c r="B502" s="5" t="s">
-        <v>2106</v>
+        <v>2110</v>
       </c>
       <c r="D502" s="5" t="s">
         <v>349</v>
@@ -23131,13 +23131,13 @@
         <v>40</v>
       </c>
       <c r="F502" s="7" t="s">
-        <v>1678</v>
+        <v>363</v>
       </c>
       <c r="G502" s="7" t="s">
-        <v>2107</v>
+        <v>1615</v>
       </c>
       <c r="H502" s="7" t="s">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="I502" s="7">
         <v>3</v>
@@ -23145,51 +23145,51 @@
     </row>
     <row r="503" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="5" t="s">
-        <v>2108</v>
+        <v>727</v>
       </c>
       <c r="B503" s="5" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="D503" s="5" t="s">
-        <v>82</v>
+        <v>349</v>
       </c>
       <c r="E503" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F503" s="7" t="s">
-        <v>274</v>
-      </c>
-      <c r="G503" s="7" t="s">
-        <v>275</v>
+        <v>26</v>
+      </c>
+      <c r="F503" s="7">
+        <v>1825</v>
+      </c>
+      <c r="G503" s="7">
+        <v>1892</v>
       </c>
       <c r="H503" s="7" t="s">
-        <v>156</v>
+        <v>56</v>
       </c>
       <c r="I503" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="504" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A504" s="5" t="s">
-        <v>1640</v>
-      </c>
-      <c r="B504" s="5" t="s">
-        <v>2110</v>
+      <c r="A504" s="12" t="s">
+        <v>310</v>
+      </c>
+      <c r="B504" s="12" t="s">
+        <v>2112</v>
       </c>
       <c r="D504" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="E504" s="5" t="s">
+      <c r="E504" s="12" t="s">
         <v>40</v>
       </c>
       <c r="F504" s="7" t="s">
-        <v>363</v>
+        <v>2113</v>
       </c>
       <c r="G504" s="7" t="s">
-        <v>1615</v>
-      </c>
-      <c r="H504" s="7" t="s">
-        <v>50</v>
+        <v>2114</v>
+      </c>
+      <c r="H504" s="13" t="s">
+        <v>29</v>
       </c>
       <c r="I504" s="7">
         <v>3</v>
@@ -23197,77 +23197,80 @@
     </row>
     <row r="505" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="5" t="s">
-        <v>727</v>
+        <v>252</v>
       </c>
       <c r="B505" s="5" t="s">
-        <v>2111</v>
+        <v>2115</v>
+      </c>
+      <c r="C505" s="5" t="s">
+        <v>2116</v>
       </c>
       <c r="D505" s="5" t="s">
-        <v>349</v>
+        <v>60</v>
       </c>
       <c r="E505" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F505" s="7">
-        <v>1825</v>
-      </c>
-      <c r="G505" s="7">
-        <v>1892</v>
+        <v>40</v>
+      </c>
+      <c r="F505" s="7" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G505" s="7" t="s">
+        <v>1991</v>
       </c>
       <c r="H505" s="7" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="I505" s="7">
         <v>3</v>
       </c>
     </row>
     <row r="506" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A506" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="B506" s="12" t="s">
-        <v>2112</v>
+      <c r="A506" s="5" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B506" s="5" t="s">
+        <v>2118</v>
       </c>
       <c r="D506" s="5" t="s">
-        <v>349</v>
-      </c>
-      <c r="E506" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="E506" s="5" t="s">
         <v>40</v>
       </c>
       <c r="F506" s="7" t="s">
-        <v>2113</v>
+        <v>691</v>
       </c>
       <c r="G506" s="7" t="s">
-        <v>2114</v>
-      </c>
-      <c r="H506" s="13" t="s">
+        <v>2119</v>
+      </c>
+      <c r="H506" s="7" t="s">
         <v>29</v>
       </c>
       <c r="I506" s="7">
         <v>3</v>
       </c>
+      <c r="T506" s="1" t="s">
+        <v>2120</v>
+      </c>
     </row>
     <row r="507" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="5" t="s">
-        <v>252</v>
+        <v>2121</v>
       </c>
       <c r="B507" s="5" t="s">
-        <v>2115</v>
-      </c>
-      <c r="C507" s="5" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
       <c r="D507" s="5" t="s">
-        <v>60</v>
+        <v>82</v>
       </c>
       <c r="E507" s="5" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="F507" s="7" t="s">
-        <v>1917</v>
+        <v>2123</v>
       </c>
       <c r="G507" s="7" t="s">
-        <v>1991</v>
+        <v>473</v>
       </c>
       <c r="H507" s="7" t="s">
         <v>63</v>
@@ -23276,65 +23279,10 @@
         <v>3</v>
       </c>
     </row>
-    <row r="508" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A508" s="5" t="s">
-        <v>2117</v>
-      </c>
-      <c r="B508" s="5" t="s">
-        <v>2118</v>
-      </c>
-      <c r="D508" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E508" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="F508" s="7" t="s">
-        <v>691</v>
-      </c>
-      <c r="G508" s="7" t="s">
-        <v>2119</v>
-      </c>
-      <c r="H508" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="I508" s="7">
-        <v>3</v>
-      </c>
-      <c r="T508" s="1" t="s">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="509" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A509" s="5" t="s">
-        <v>2121</v>
-      </c>
-      <c r="B509" s="5" t="s">
-        <v>2122</v>
-      </c>
-      <c r="D509" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E509" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F509" s="7" t="s">
-        <v>2123</v>
-      </c>
-      <c r="G509" s="7" t="s">
-        <v>473</v>
-      </c>
-      <c r="H509" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="I509" s="7">
-        <v>3</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:W509" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W509">
-    <sortCondition ref="B2:B509"/>
+  <autoFilter ref="A1:W507" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:W507">
+    <sortCondition ref="B2:B507"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="I43" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="T43" s="1" t="inlineStr">
         <is>
@@ -7465,7 +7465,7 @@
         </is>
       </c>
       <c r="I138" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L138" s="2" t="n"/>
       <c r="T138" s="1" t="inlineStr">
@@ -8211,7 +8211,7 @@
         </is>
       </c>
       <c r="I154" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
@@ -8511,7 +8511,7 @@
         </is>
       </c>
       <c r="I160" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="161" ht="15" customHeight="1">
@@ -11627,7 +11627,7 @@
         </is>
       </c>
       <c r="I224" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -11985,7 +11985,7 @@
         </is>
       </c>
       <c r="I232" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="233" ht="15" customHeight="1">
@@ -12653,7 +12653,7 @@
         </is>
       </c>
       <c r="I247" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="248" ht="15" customHeight="1">
@@ -13278,7 +13278,7 @@
         </is>
       </c>
       <c r="I261" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="262" ht="15" customHeight="1">
@@ -13949,7 +13949,7 @@
         </is>
       </c>
       <c r="I276" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="277" ht="15" customHeight="1">
@@ -14224,7 +14224,7 @@
         </is>
       </c>
       <c r="I282" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="283" ht="15" customHeight="1">
@@ -14664,7 +14664,7 @@
         </is>
       </c>
       <c r="I292" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="293" ht="15" customHeight="1">
@@ -15230,7 +15230,7 @@
         </is>
       </c>
       <c r="I305" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S305" s="1" t="inlineStr">
         <is>
@@ -18247,7 +18247,7 @@
         </is>
       </c>
       <c r="I369" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="370" ht="15" customHeight="1">
@@ -18709,7 +18709,7 @@
         </is>
       </c>
       <c r="I380" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S380" s="1" t="inlineStr">
         <is>
@@ -18796,7 +18796,7 @@
         </is>
       </c>
       <c r="I382" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="383" ht="15" customHeight="1">
@@ -18936,7 +18936,7 @@
         </is>
       </c>
       <c r="I385" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386" ht="15" customHeight="1">
@@ -19592,7 +19592,7 @@
         </is>
       </c>
       <c r="I400" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="401" ht="15" customHeight="1">
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="I409" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S409" s="1" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         </is>
       </c>
       <c r="I430" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="431" ht="15" customHeight="1">
@@ -21589,7 +21589,7 @@
         </is>
       </c>
       <c r="I443" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="444" ht="15" customHeight="1">
@@ -22810,7 +22810,7 @@
         </is>
       </c>
       <c r="I469" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="470" ht="15" customHeight="1">
@@ -23241,7 +23241,7 @@
         </is>
       </c>
       <c r="I478" s="7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="479" ht="15" customHeight="1">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -17999,7 +17999,7 @@
       <c r="S107" s="1" t="inlineStr">
         <is>
           <t xml:space="preserve">Je suis né en 1801 à Bolton, dans le Lancashire. À mes dix-sept ans, ma famille a émigré aux États-Unis. J'ai appris à peindre seul, en parcourant les collines et les forêts de l'État de New York.
-[image: https://upload.wikimedia.org/wikipedia/commons/f/fa/Cole_Thomas_Lake_with_Dead_Trees_%28Catskill%29_1825.jpg | Lac aux arbres morts, 1825 | enchaîné 5]À l'été 1825, j'ai exposé dans une vitrine de New York des vues des monts Catskill. Elles ont été remarquées, achetées, admirées. C'était le début de l'école du fleuve [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg | Vue depuis le mont Holyoke, après un orage — The Oxbow., 1836 | enchaîné 10]Hudson, dont on m'a appelé le fondateur. Frédéric Edwin Church, mon ami,  et, plus tard, Albert Bierstadt en ont fait partie. J'ai peint la nature américaine, sauvage et grandiose.  J'ai imaginé aussi des allégories à travers des grands cycles. Le premier, *La Vie humaine*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole_-_The_Voyage_of_Life_Childhood%2C_1842_%28National_Gallery_of_Art%29FXD.jpg | Le Voyage de la vie : L'Enfance, 1842 | enchaîné 10] est une série de quatre tableaux où un voyageur navigue sur une rivière dont les changements évoquent les différentes étapes de l'existence. Le second, *Le Cours de l'Empire*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Architect-s_Dream_1840.jpg | Le Rêve de l'Architecte, 1840 | enchaîné 10] est constitué de cinq tableaux qui décrivent la naissance et le déclin d'une civilisation imaginaire. J'ai voulu mettre en garde mes contemporains [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg/1280px-Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg | Le Cours de l'Empire, La Désolation, 1836 | enchaîné 10] en peignant les ravages possibles sur la Nature et la Civilisation d'une course effrénée vers une société industrielle et marchande.  [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg | Le Départ, 1837 | enchaîné 10]J'ai été un des pionniers du mouvement environnementaliste. Je me suis installé à Catskill, où je suis mort en 1848, à quarante-sept ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Gibbon_River_at_Madison_in_Yellowstone.JPG/1280px-Gibbon_River_at_Madison_in_Yellowstone.JPG | La rivière Gibbon dans le parc de Yellowstone.]Mes convictions écologistes ont ouvert la voie à la création des grands parcs nationaux américains comme celui de Yellowstone. Je crois cette voie prometteuse pour ↩l'avenir de l'Amérique.</t>
+[image: https://upload.wikimedia.org/wikipedia/commons/f/fa/Cole_Thomas_Lake_with_Dead_Trees_%28Catskill%29_1825.jpg | Lac aux arbres morts, 1825 | enchaîné 5]À l'été 1825, j'ai exposé dans une vitrine de New York des vues des monts Catskill. Elles ont été remarquées, achetées, admirées. C'était le début de l'école du fleuve [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg | Vue depuis le mont Holyoke, après un orage — The Oxbow., 1836 | enchaîné 10]Hudson, dont on m'a appelé le fondateur. Frédéric Edwin Church, mon ami,  et, plus tard, Albert Bierstadt en ont fait partie. J'ai peint la nature américaine, sauvage et grandiose.  J'ai imaginé aussi des allégories à travers des grands cycles. Le premier, *La Vie humaine*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole_-_The_Voyage_of_Life_Childhood%2C_1842_%28National_Gallery_of_Art%29FXD.jpg | Le Voyage de la vie : L'Enfance, 1842 | enchaîné 10] est une série de quatre tableaux où un voyageur navigue sur une rivière dont les changements évoquent les différentes étapes de l'existence. Le second, *Le Cours de l'Empire*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Architect-s_Dream_1840.jpg | Le Rêve de l'Architecte, 1840 | enchaîné 10] est constitué de cinq tableaux qui décrivent la naissance et le déclin d'une civilisation imaginaire. J'ai voulu mettre en garde mes contemporains [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg/1280px-Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg | Le Cours de l'Empire, La Désolation, 1836 | enchaîné 10] en peignant les ravages possibles sur la Nature et la Civilisation d'une course effrénée vers une société industrielle [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg | Le Départ, 1837 | enchaîné 10]et marchande.  J'ai été un des pionniers du mouvement environnementaliste. Je me suis installé à Catskill, où je suis mort en 1848, à quarante-sept ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Gibbon_River_at_Madison_in_Yellowstone.JPG/1280px-Gibbon_River_at_Madison_in_Yellowstone.JPG | La rivière Gibbon dans le parc de Yellowstone. | enchaîné 10]Mes convictions écologistes ont ouvert la voie à la création des grands parcs nationaux américains comme celui de Yellowstone. Je crois cette voie prometteuse pour [retour | 5]l'avenir de l'Amérique.</t>
         </is>
       </c>
       <c r="T107" s="1" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -16942,8 +16942,10 @@
       <c r="I81" s="7">
         <v>2</v>
       </c>
-      <c r="S81" s="1" t="s">
-        <v>653</v>
+      <c r="S81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né vers 1375 à Valenciennes, [retour | 5]et je me suis établi à Tournai, enclave française dans ce territoire bourguignon, [image: https://mnemart.fr/cartes/foyer-artistique-bourguignon-1430.png |  | enchaîné 10]si riche en tapissiers, enlumineurs, sculpteurs et peintres. Depuis, leur capitale, Dijon, les ducs de Bourgogne, Jean sans peur, et surtout son fils, Philippe le Bon, ont su créer un foyer artistique exceptionnel. Pour ma part, j'ai obtenu le titre de maître en 1406 qui m'a assuré un statut de chef d'atelier indépendant au sein de la corporation locale des peintres. J'ai eu des élèves de talent : Jacques Daret, et surtout, celui qui a peint le portrait du duc Philippe, Rogier de la Pasture, que vous connaissez sous le nom de Rogier van der Weyden. Il s'installera plus tard et réussira brillamment à Bruxelles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Eyck%2C_Jan_van_-_Portrait_of_a_Man_%28Self_Portrait%3F%29_-_National_Gallery%2C_London.jpg/960px-Eyck%2C_Jan_van_-_Portrait_of_a_Man_%28Self_Portrait%3F%29_-_National_Gallery%2C_London.jpg | Van Eyck Portrait d’un homme 1433 | enchaîné 10]J'ai pu rencontrer aussi Jan van Eyck, venu de Gand ou de Bruges,  lors de ses séjours à Tournai, notre maître à tous, celui que l'histoire retiendra comme le plus doué d'entre nous. Pendant longtemps, on ne m'a pas connu sous mon nom. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Robert_Campin_013.jpg | Portrait d'un homme, 1435 | enchaîné 10]On parlait du Maître de Flémalle, et c'est seulement l'étude des archives qui a permis de rapprocher ce nom du mien. En 1423, en tant qu'artisan fier de sa réussite matérielle, j'ai été l'un des chefs de la révolte des métiers de Tournai contre le pouvoir de l'aristocratie, et je me suis rangé du côté des Français contre le parti bourguignon. J'ai ensuite exercé des fonctions dans le nouveau gouvernement et présidé la corporation des peintres et des orfèvres, mais en 1429 j'ai été condamné à une amende, à un pèlerinage et à l'interdiction de toute charge publique pour avoir pris part à ce soulèvement. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Robert_Campin_-_Triptych_with_the_Annunciation%2C_known_as_the_%22Merode_Altarpiece%22_-_Google_Art_Project.jpg | Le Triptyque de Mérode, 1427-1432 | enchaîné 10]Est-ce pour cela que mon Triptyque de Mérode montre l'Annonciation dans un intérieur bourgeois ordinaire ? Loin des palais princiers, on y voit un banc, une cheminée, une bougie qui vient de s'éteindre, et dans l'atelier voisin, saint Joseph qui fabrique des pièges à souris. [image: https://upload.wikimedia.org/wikipedia/commons/c/c9/Robert_campin%2C_trinity.jpg | Campin, La Trinité du Corps brisé, 1430 | enchaîné 10]J'ai voulu que le divin entre dans le quotidien. Mes figures ont du poids et du volume, presque comme des sculptures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Robert_Campin_012.jpg/960px-Robert_Campin_012.jpg | Robert Campin, "Portrait de femme", 1435 | enchaîné 10]Les portraits de bourgeois que je suis un des premiers à avoir peints sont empreints d'une grande dignité. [retour | 5]Je suis  mort à Tournai en 1444.</t>
+        </is>
       </c>
       <c r="T81" s="10" t="s">
         <v>3492</v>
@@ -39945,7 +39947,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:U583"/>
+  <dimension ref="A1:U584"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="32.85546875" customWidth="1"/>
@@ -45175,6 +45177,23 @@
         <v>3463</v>
       </c>
     </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Robert</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">CAMPIN</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Statue de Saint-Luc dessinant la Vierge, Tournai</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -13584,7 +13584,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X501"/>
+  <dimension ref="A1:Y501"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="5" customWidth="1"/>
@@ -13679,6 +13679,11 @@
       <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Voix</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -18000,8 +18005,11 @@
       <c r="I107" s="7">
         <v>3</v>
       </c>
-      <c r="S107" s="1" t="s">
-        <v>3492</v>
+      <c r="S107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né en 1801 à Bolton, dans le Lancashire. À mes dix-sept ans, ma famille a émigré aux États-Unis. J'ai appris à peindre seul, en parcourant les collines et les forêts de l'État de New York.
+[image: https://upload.wikimedia.org/wikipedia/commons/f/fa/Cole_Thomas_Lake_with_Dead_Trees_%28Catskill%29_1825.jpg | Lac aux arbres morts, 1825 | enchaîné 5]À l'été 1825, j'ai exposé dans une vitrine de New York des vues des monts Catskill. Elles ont été remarquées, achetées, admirées. C'était le début de l'école du fleuve [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg | Vue depuis le mont Holyoke, après un orage — The Oxbow., 1836 | enchaîné 10]Hudson, dont on m'a appelé le fondateur. Frédéric Edwin Church, mon ami,  et, plus tard, Albert Bierstadt en ont fait partie. J'ai peint la nature américaine, sauvage et grandiose.  J'ai imaginé aussi des allégories à travers des grands cycles. Le premier, *La Vie humaine*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole_-_The_Voyage_of_Life_Childhood%2C_1842_%28National_Gallery_of_Art%29FXD.jpg | Le Voyage de la vie : L'Enfance, 1842 | enchaîné 10] est une série de quatre tableaux où un voyageur navigue sur une rivière dont les changements évoquent les différentes étapes de l'existence. Le second, *Le Cours de l'Empire*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Architect-s_Dream_1840.jpg | Le Rêve de l'Architecte, 1840 | enchaîné 10] est constitué de cinq tableaux qui décrivent la naissance et le déclin d'une civilisation imaginaire. J'ai voulu mettre en garde mes contemporains [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg/1280px-Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg | Le Cours de l'Empire, La Désolation, 1836 | enchaîné 10] en peignant les ravages possibles sur la Nature et la Civilisation d'une course effrénée vers une société industrielle [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg | Le Départ, 1837 | enchaîné 10]et marchande.  J'ai été un des pionniers du mouvement environnementaliste. Je me suis installé à Catskill, où je suis mort en 1848, à quarante-sept ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Gibbon_River_at_Madison_in_Yellowstone.JPG/1280px-Gibbon_River_at_Madison_in_Yellowstone.JPG | La rivière Gibbon dans le parc de Yellowstone. | enchaîné 10]Mes convictions écologistes ont ouvert la voie à la création des grands parcs nationaux américains comme celui de Yellowstone. Je crois cette voie prometteuse pour [retour | 5]l'avenir de l'Amérique.</t>
+        </is>
       </c>
       <c r="T107" s="1" t="s">
         <v>829</v>
@@ -32642,8 +32650,10 @@
       <c r="I480" s="7">
         <v>2</v>
       </c>
-      <c r="S480" s="1" t="s">
-        <v>2964</v>
+      <c r="S480" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis née à Paris en 1755, fille d'un pastelliste. [retour | 5]Il est mort quand j'avais douze ans, et j'ai appris à peindre en regardant ses [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg/960px-%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg | Autportait,1781 | 5]amis. À vingt ans, je gagnais déjà ma vie en faisant des portraits. J'ai révolutionné cet art en le rendant plus sensible, plus léger, fluide et aérien. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg | Autoportrait au chapeau de paille, 1782 | enchaîné 10]Mais j'ai été aussi une travailleuse acharnée, une vraie femme d'affaires, et j'ai aimé raconter que j'ai travaillé entre deux contractions, le jour de mon accouchement. Marie-Antoinette m'a remarquée en 1778, [image: https://upload.wikimedia.org/wikipedia/commons/0/00/MA-Lebrun.jpg | Marie-Antoinette en gaulle, 1783 | enchaîné 10]elle qui aimait tant la liberté et le naturel, et je suis devenue sa portraitiste favorite : plus de trente portraits en quelques années, dont la reine en gaulle. Celui-là a provoqué un vrai scandale! La simple robe de mousseline blanche de Marie-Antoinette ressemblait, disaient les mauvaises langues, à une chemise de nuit. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg | Marie-Antoinette avec une rose, 1783 | enchaîné 10]Quelle honte! Alors nous avons décidé de revenir à un portrait plus conventionnel! [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_de_Lorraine-Habsbourg%2C_reine_de_France_et_ses_enfants_-_Google_Art_Project.jpg | Marie-Antoinette et ses enfants, 1787 | enchaîné 10]Cette chère Reine! Je l'ai peinte aussi avec ses enfants qu'elle aimait tant! En 1783, l'Académie royale m'a reçue, sur ordre de Louis XVI, malgré l'opposition de certains. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%C3%89lisabeth-Louise_Vig%C3%A9e-Le_Brun_-_Hubert_Robert_%281788%29.jpg | Portrait du peintre Hubert Robert, 1788 | enchaîné 10]Heureusement j'avais le soutien de mon cher ami Hubert Robert dont j'ai fait le portrait. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_with_Her_Daughter_by_Elisabeth-Louise_Vig%C3%A9e_Le_Brun.jpg | Autoportrait avec sa fille Julie, 1789 | enchaîné 10]La Révolution m'a obligée à fuir, comme tant d'autres, en 1789. J'ai vécu pendant douze ans à Rome, Naples, Vienne, Saint-Pétersbourg, partout fêtée et employée par les cours d'Europe, avec ma fille Julie. J'ai transformé mon exil en triomphe et je crois que partout, j'ai fait avancer la cause de la femme, avec sourire, malice mais aussi avec une grande détermination. Je suis rentrée en France en 1802, et j'ai publié mes Souvenirs, où je raconte ces années. [retour | 5]Je suis morte à Paris en 1842, âgée de quatre-vingt-six ans.</t>
+        </is>
       </c>
       <c r="T480" s="10" t="s">
         <v>3495</v>
@@ -32656,6 +32666,11 @@
       </c>
       <c r="W480" t="s">
         <v>2966</v>
+      </c>
+      <c r="Y480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">femme</t>
+        </is>
       </c>
     </row>
     <row r="481" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44966,6 +44981,11 @@
       <c r="B557" t="s">
         <v>2962</v>
       </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Autoportait, 1790</t>
+        </is>
+      </c>
     </row>
     <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -32652,7 +32652,7 @@
       </c>
       <c r="S480" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis née à Paris en 1755, fille d'un pastelliste. [retour | 5]Il est mort quand j'avais douze ans, et j'ai appris à peindre en regardant ses [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg/960px-%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg | Autportait,1781 | 5]amis. À vingt ans, je gagnais déjà ma vie en faisant des portraits. J'ai révolutionné cet art en le rendant plus sensible, plus léger, fluide et aérien. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg | Autoportrait au chapeau de paille, 1782 | enchaîné 10]Mais j'ai été aussi une travailleuse acharnée, une vraie femme d'affaires, et j'ai aimé raconter que j'ai travaillé entre deux contractions, le jour de mon accouchement. Marie-Antoinette m'a remarquée en 1778, [image: https://upload.wikimedia.org/wikipedia/commons/0/00/MA-Lebrun.jpg | Marie-Antoinette en gaulle, 1783 | enchaîné 10]elle qui aimait tant la liberté et le naturel, et je suis devenue sa portraitiste favorite : plus de trente portraits en quelques années, dont la reine en gaulle. Celui-là a provoqué un vrai scandale! La simple robe de mousseline blanche de Marie-Antoinette ressemblait, disaient les mauvaises langues, à une chemise de nuit. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg | Marie-Antoinette avec une rose, 1783 | enchaîné 10]Quelle honte! Alors nous avons décidé de revenir à un portrait plus conventionnel! [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_de_Lorraine-Habsbourg%2C_reine_de_France_et_ses_enfants_-_Google_Art_Project.jpg | Marie-Antoinette et ses enfants, 1787 | enchaîné 10]Cette chère Reine! Je l'ai peinte aussi avec ses enfants qu'elle aimait tant! En 1783, l'Académie royale m'a reçue, sur ordre de Louis XVI, malgré l'opposition de certains. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%C3%89lisabeth-Louise_Vig%C3%A9e-Le_Brun_-_Hubert_Robert_%281788%29.jpg | Portrait du peintre Hubert Robert, 1788 | enchaîné 10]Heureusement j'avais le soutien de mon cher ami Hubert Robert dont j'ai fait le portrait. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_with_Her_Daughter_by_Elisabeth-Louise_Vig%C3%A9e_Le_Brun.jpg | Autoportrait avec sa fille Julie, 1789 | enchaîné 10]La Révolution m'a obligée à fuir, comme tant d'autres, en 1789. J'ai vécu pendant douze ans à Rome, Naples, Vienne, Saint-Pétersbourg, partout fêtée et employée par les cours d'Europe, avec ma fille Julie. J'ai transformé mon exil en triomphe et je crois que partout, j'ai fait avancer la cause de la femme, avec sourire, malice mais aussi avec une grande détermination. Je suis rentrée en France en 1802, et j'ai publié mes Souvenirs, où je raconte ces années. [retour | 5]Je suis morte à Paris en 1842, âgée de quatre-vingt-six ans.</t>
+          <t xml:space="preserve">Je suis née à Paris en 1755, fille d'un pastelliste. [retour | 5]Il est mort quand j'avais douze ans, et j'ai appris à peindre en regardant ses [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg/960px-%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg | Autportait,1781 | 5]amis. À vingt ans, je gagnais déjà ma vie en faisant des portraits. J'ai révolutionné cet art en le rendant plus sensible, plus léger, fluide et aérien. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg | Autoportrait au chapeau de paille, 1782 | enchaîné 10]Mais j'ai été aussi une travailleuse acharnée, une vraie femme d'affaires, et j'ai aimé raconter que j'ai travaillé entre deux contractions, le jour de mon accouchement. Marie-Antoinette m'a remarquée en 1778, [image: https://upload.wikimedia.org/wikipedia/commons/0/00/MA-Lebrun.jpg | Marie-Antoinette en gaulle, 1783 | enchaîné 10]elle qui aimait tant la liberté et le naturel, et je suis devenue sa portraitiste favorite : plus de trente portraits en quelques années, dont la reine en gaulle. Celui-là a provoqué un vrai scandale! La simple robe de mousseline blanche de Marie-Antoinette ressemblait, disaient les mauvaises langues, à une chemise de nuit. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg | Marie-Antoinette avec une rose, 1783 | enchaîné 10]Quelle honte! Alors nous avons décidé de revenir à un portrait plus conventionnel! [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_de_Lorraine-Habsbourg%2C_reine_de_France_et_ses_enfants_-_Google_Art_Project.jpg | Marie-Antoinette et ses enfants, 1787 | enchaîné 10]Cette chère Reine! Je l'ai peinte aussi avec ses enfants qu'elle aimait tant! En 1783, l'Académie royale m'a reçue, sur ordre de Louis XVI, malgré l'opposition de certains. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%C3%89lisabeth-Louise_Vig%C3%A9e-Le_Brun_-_Hubert_Robert_%281788%29.jpg | Portrait du peintre Hubert Robert, 1788 | enchaîné 10]Heureusement j'avais le soutien de mon cher ami Hubert Robert dont j'ai fait le portrait. La Révolution m'a obligée à fuir, comme tant d'autres, en 1789. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_with_Her_Daughter_by_Elisabeth-Louise_Vig%C3%A9e_Le_Brun.jpg | Autoportrait avec sa fille Julie, 1789 | enchaîné 10]J'ai vécu pendant douze ans à Rome, Naples, Vienne, Saint-Pétersbourg, partout fêtée et employée par les cours d'Europe, avec ma fille Julie. J'ai transformé mon exil en triomphe et je crois que partout, j'ai fait avancer la cause de la femme, avec sourire, malice mais aussi avec une grande détermination. Je suis rentrée en France en 1802, et j'ai publié mes Souvenirs, où je raconte ces années. [retour | 5]Je suis morte à Paris en 1842, âgée de quatre-vingt-six ans.</t>
         </is>
       </c>
       <c r="T480" s="10" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -24510,8 +24510,10 @@
       <c r="I269" s="7">
         <v>1</v>
       </c>
-      <c r="S269" s="1" t="s">
-        <v>1862</v>
+      <c r="S269" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère Ernst, je suis entré à l'École des Arts Appliqués ; [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]reconnus pour notre talent, quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par son désir de mort. Les Viennois ont crié au scandale. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]Deux ans plus tard, dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]Derrière Fritza Riedler, dont le mari ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* — je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]Mon projet le plus ambitieux a été la décoration de la salle à manger du Palais Stoclet, à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* est le centre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]Quand j'ai peint à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]J'ai soutenu le jeune Egon Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. La Mort qui guette d'un côté, la Vie de l'autre : ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
+        </is>
       </c>
       <c r="T269" s="10" t="s">
         <v>1863</v>
@@ -42857,6 +42859,11 @@
       <c r="B293" t="s">
         <v>1860</v>
       </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Portrait de 1914 par le photographe Anton Josef Trčka l’artiste</t>
+        </is>
+      </c>
     </row>
     <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -24512,7 +24512,7 @@
       </c>
       <c r="S269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère Ernst, je suis entré à l'École des Arts Appliqués ; [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]reconnus pour notre talent, quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par son désir de mort. Les Viennois ont crié au scandale. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]Deux ans plus tard, dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]Derrière Fritza Riedler, dont le mari ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* — je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]Mon projet le plus ambitieux a été la décoration de la salle à manger du Palais Stoclet, à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* est le centre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]Quand j'ai peint à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]J'ai soutenu le jeune Egon Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. La Mort qui guette d'un côté, la Vie de l'autre : ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
+          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par son désir de mort. Les Viennois ont crié au scandale. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]Deux ans plus tard, dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]En 1903 un voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]couleurs. Mon projet le plus ambitieux a été la décoration de la salle à manger du [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]Palais Stoclet, à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]est le centre. Quand j'ai peint à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]je ne voulais pas me répéter. Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]de la couleur pure. J'ai soutenu le jeune Egon Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]que je n'avais plus. La Mort qui guette d'un côté, la Vie de l'autre : ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
         </is>
       </c>
       <c r="T269" s="10" t="s">
@@ -42861,7 +42861,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t xml:space="preserve">Portrait de 1914 par le photographe Anton Josef Trčka l’artiste</t>
+          <t xml:space="preserve">Klimt en 1914</t>
         </is>
       </c>
     </row>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -24512,7 +24512,7 @@
       </c>
       <c r="S269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par son désir de mort. Les Viennois ont crié au scandale. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]Deux ans plus tard, dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]En 1903 un voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]couleurs. Mon projet le plus ambitieux a été la décoration de la salle à manger du [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]Palais Stoclet, à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]est le centre. Quand j'ai peint à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]je ne voulais pas me répéter. Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]de la couleur pure. J'ai soutenu le jeune Egon Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]que je n'avais plus. La Mort qui guette d'un côté, la Vie de l'autre : ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
+          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par le meurtre qu'elle vient d'accomplir. Les Viennois ont crié au scandale. Deux ans plus tard, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. Mon projet [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]le plus ambitieux a été la décoration de la salle à manger du Palais Stoclet, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* est le centre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]Quand j'ai peint à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]J'ai soutenu le jeune Egon Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]La Mort qui guette d'un côté, la Vie de l'autre, cela aura été ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
         </is>
       </c>
       <c r="T269" s="10" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -24512,7 +24512,7 @@
       </c>
       <c r="S269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par le meurtre qu'elle vient d'accomplir. Les Viennois ont crié au scandale. Deux ans plus tard, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. Mon projet [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]le plus ambitieux a été la décoration de la salle à manger du Palais Stoclet, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* est le centre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]Quand j'ai peint à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]J'ai soutenu le jeune Egon Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]La Mort qui guette d'un côté, la Vie de l'autre, cela aura été ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
+          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par le meurtre qu'elle vient d'accomplir. Les Viennois ont crié au scandale. Deux ans plus tard, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec Emilie, je me reposais de la ville au bord de l'Attersee [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]: je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. Mon projet le plus ambitieux [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]a été la décoration de la salle à manger du Palais Stoclet, à Bruxelles, une œuvre d'art totale dont [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]*« L'Arbre de vie »* est le centre. Quand j'ai peint [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. J'ai soutenu le jeune Egon [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]La Mort qui guette d'un côté, la Vie de l'autre, cela aura été ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
         </is>
       </c>
       <c r="T269" s="10" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -24512,7 +24512,7 @@
       </c>
       <c r="S269" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par le meurtre qu'elle vient d'accomplir. Les Viennois ont crié au scandale. Deux ans plus tard, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec Emilie, je me reposais de la ville au bord de l'Attersee [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]: je peignais des jardins et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. Mon projet le plus ambitieux [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]a été la décoration de la salle à manger du Palais Stoclet, à Bruxelles, une œuvre d'art totale dont [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]*« L'Arbre de vie »* est le centre. Quand j'ai peint [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]à nouveau Adele, en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. J'ai soutenu le jeune Egon [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]La Mort qui guette d'un côté, la Vie de l'autre, cela aura été ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
+          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par le meurtre qu'elle vient d'accomplir. Les Viennois ont crié au scandale. Deux ans plus tard, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. Mon projet le plus ambitieux [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]a été la décoration de la salle à manger du Palais Stoclet, à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]est le centre. Quand j'ai peint à nouveau Adele, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. J'ai soutenu le jeune Egon [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]La Mort qui guette d'un côté, la Vie de l'autre, cela aura été ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
         </is>
       </c>
       <c r="T269" s="10" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBAF68AA-B111-4894-BDB1-ECCA61157E6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7340BE-4FC1-4B1C-8779-EA09039026EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8700" uniqueCount="3496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8709" uniqueCount="3506">
   <si>
     <t>Prénom</t>
   </si>
@@ -11462,12 +11462,6 @@
     <t>1842</t>
   </si>
   <si>
-    <t>Je suis née à Paris en 1755, fille d'un pastelliste. Il est mort quand j'avais douze ans, et j'ai appris à peindre en regardant ses amis. À vingt ans, je gagnais déjà ma vie en faisant des portraits.
-Marie-Antoinette m'a remarquée en 1778, et je suis devenue son portraitiste favori : plus de trente portraits en quelques années, dont la reine à la rose, la reine en gaulle, ou encore avec ses enfants. En 1783, l'Académie royale m'a reçue, sur ordre de Louis XVI, malgré l'opposition de certains.
-La Révolution m'a obligée à fuir en 1789. J'ai vécu pendant douze ans à Rome, Naples, Vienne, Saint-Pétersbourg, partout fêtée et employée par les cours d'Europe, avec ma fille Julie.
-Je suis rentrée en France en 1802, et j'ai publié mes Souvenirs, où je raconte ces années. Je suis morte à Paris en 1842, âgée de quatre-vingt-six ans.</t>
-  </si>
-  <si>
     <t>Autoportrait au chapeau de paille</t>
   </si>
   <si>
@@ -13184,6 +13178,39 @@
   </si>
   <si>
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Self-portrait_%28by_Elisabeth_Vig%C3%A9e-Lebrun%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg/960px-Self-portrait_%28by_Elisabeth_Vig%C3%A9e-Lebrun%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Voix</t>
+  </si>
+  <si>
+    <t>Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par le meurtre qu'elle vient d'accomplir. Les Viennois ont crié au scandale. Deux ans plus tard, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. Mon projet le plus ambitieux [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]a été la décoration de la salle à manger du Palais Stoclet, à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]est le centre. Quand j'ai peint à nouveau Adele, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. J'ai soutenu le jeune Egon [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]La Mort qui guette d'un côté, la Vie de l'autre, cela aura été ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
+  </si>
+  <si>
+    <t>Je suis née à Paris en 1755, fille d'un pastelliste. [retour | 5]Il est mort quand j'avais douze ans, et j'ai appris à peindre en regardant ses [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg/960px-%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg | Autportait,1781 | 5]amis. À vingt ans, je gagnais déjà ma vie en faisant des portraits. J'ai révolutionné cet art en le rendant plus sensible, plus léger, fluide et aérien. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg | Autoportrait au chapeau de paille, 1782 | enchaîné 10]Mais j'ai été aussi une travailleuse acharnée, une vraie femme d'affaires, et j'ai aimé raconter que j'ai travaillé entre deux contractions, le jour de mon accouchement. Marie-Antoinette m'a remarquée en 1778, [image: https://upload.wikimedia.org/wikipedia/commons/0/00/MA-Lebrun.jpg | Marie-Antoinette en gaulle, 1783 | enchaîné 10]elle qui aimait tant la liberté et le naturel, et je suis devenue sa portraitiste favorite : plus de trente portraits en quelques années, dont la reine en gaulle. Celui-là a provoqué un vrai scandale! La simple robe de mousseline blanche de Marie-Antoinette ressemblait, disaient les mauvaises langues, à une chemise de nuit. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg | Marie-Antoinette avec une rose, 1783 | enchaîné 10]Quelle honte! Alors nous avons décidé de revenir à un portrait plus conventionnel! [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_de_Lorraine-Habsbourg%2C_reine_de_France_et_ses_enfants_-_Google_Art_Project.jpg | Marie-Antoinette et ses enfants, 1787 | enchaîné 10]Cette chère Reine! Je l'ai peinte aussi avec ses enfants qu'elle aimait tant! En 1783, l'Académie royale m'a reçue, sur ordre de Louis XVI, malgré l'opposition de certains. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%C3%89lisabeth-Louise_Vig%C3%A9e-Le_Brun_-_Hubert_Robert_%281788%29.jpg | Portrait du peintre Hubert Robert, 1788 | enchaîné 10]Heureusement j'avais le soutien de mon cher ami Hubert Robert dont j'ai fait le portrait. La Révolution m'a obligée à fuir, comme tant d'autres, en 1789. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_with_Her_Daughter_by_Elisabeth-Louise_Vig%C3%A9e_Le_Brun.jpg | Autoportrait avec sa fille Julie, 1789 | enchaîné 10]J'ai vécu pendant douze ans à Rome, Naples, Vienne, Saint-Pétersbourg, partout fêtée et employée par les cours d'Europe, avec ma fille Julie. J'ai transformé mon exil en triomphe et je crois que partout, j'ai fait avancer la cause de la femme, avec sourire, malice mais aussi avec une grande détermination. Je suis rentrée en France en 1802, et j'ai publié mes Souvenirs, où je raconte ces années. [retour | 5]Je suis morte à Paris en 1842, âgée de quatre-vingt-six ans.</t>
+  </si>
+  <si>
+    <t>femme</t>
+  </si>
+  <si>
+    <t>Klimt en 1914</t>
+  </si>
+  <si>
+    <t>Autoportait, 1790</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Portrett_av_Edvard_Munch.jpg/960px-Portrett_av_Edvard_Munch.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Portrait_of_Henri_Matisse_1933_May_20.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/1/14/Egon_Schiele_photo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d6/Mondrian%2C_Piet_-_Self-portret_c._1900_A137.jpg/960px-Mondrian%2C_Piet_-_Self-portret_c._1900_A137.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/f/fd/Rousseau_Joyeux_Farceurs_Dornac.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -13606,7 +13633,7 @@
     <col min="24" max="24" width="28" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -13679,13 +13706,11 @@
       <c r="X1" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Voix</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Y1" t="s">
+        <v>3495</v>
+      </c>
+    </row>
+    <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>23</v>
       </c>
@@ -13726,7 +13751,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>34</v>
       </c>
@@ -13767,7 +13792,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>41</v>
       </c>
@@ -13808,7 +13833,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="5" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>52</v>
       </c>
@@ -13846,7 +13871,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>61</v>
       </c>
@@ -13887,7 +13912,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="7" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>71</v>
       </c>
@@ -13928,7 +13953,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>81</v>
       </c>
@@ -13969,7 +13994,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>89</v>
       </c>
@@ -14010,7 +14035,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="10" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>98</v>
       </c>
@@ -14051,7 +14076,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>107</v>
       </c>
@@ -14092,7 +14117,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>117</v>
       </c>
@@ -14130,7 +14155,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>124</v>
       </c>
@@ -14168,7 +14193,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="14" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>130</v>
       </c>
@@ -14209,7 +14234,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>138</v>
       </c>
@@ -14250,7 +14275,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>146</v>
       </c>
@@ -16952,10 +16977,10 @@
         <v>2</v>
       </c>
       <c r="S81" s="1" t="s">
-        <v>3491</v>
+        <v>3490</v>
       </c>
       <c r="T81" s="10" t="s">
-        <v>3490</v>
+        <v>3489</v>
       </c>
       <c r="U81" s="5" t="s">
         <v>652</v>
@@ -18005,11 +18030,8 @@
       <c r="I107" s="7">
         <v>3</v>
       </c>
-      <c r="S107" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né en 1801 à Bolton, dans le Lancashire. À mes dix-sept ans, ma famille a émigré aux États-Unis. J'ai appris à peindre seul, en parcourant les collines et les forêts de l'État de New York.
-[image: https://upload.wikimedia.org/wikipedia/commons/f/fa/Cole_Thomas_Lake_with_Dead_Trees_%28Catskill%29_1825.jpg | Lac aux arbres morts, 1825 | enchaîné 5]À l'été 1825, j'ai exposé dans une vitrine de New York des vues des monts Catskill. Elles ont été remarquées, achetées, admirées. C'était le début de l'école du fleuve [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg | Vue depuis le mont Holyoke, après un orage — The Oxbow., 1836 | enchaîné 10]Hudson, dont on m'a appelé le fondateur. Frédéric Edwin Church, mon ami,  et, plus tard, Albert Bierstadt en ont fait partie. J'ai peint la nature américaine, sauvage et grandiose.  J'ai imaginé aussi des allégories à travers des grands cycles. Le premier, *La Vie humaine*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole_-_The_Voyage_of_Life_Childhood%2C_1842_%28National_Gallery_of_Art%29FXD.jpg | Le Voyage de la vie : L'Enfance, 1842 | enchaîné 10] est une série de quatre tableaux où un voyageur navigue sur une rivière dont les changements évoquent les différentes étapes de l'existence. Le second, *Le Cours de l'Empire*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Architect-s_Dream_1840.jpg | Le Rêve de l'Architecte, 1840 | enchaîné 10] est constitué de cinq tableaux qui décrivent la naissance et le déclin d'une civilisation imaginaire. J'ai voulu mettre en garde mes contemporains [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg/1280px-Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg | Le Cours de l'Empire, La Désolation, 1836 | enchaîné 10] en peignant les ravages possibles sur la Nature et la Civilisation d'une course effrénée vers une société industrielle [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg | Le Départ, 1837 | enchaîné 10]et marchande.  J'ai été un des pionniers du mouvement environnementaliste. Je me suis installé à Catskill, où je suis mort en 1848, à quarante-sept ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Gibbon_River_at_Madison_in_Yellowstone.JPG/1280px-Gibbon_River_at_Madison_in_Yellowstone.JPG | La rivière Gibbon dans le parc de Yellowstone. | enchaîné 10]Mes convictions écologistes ont ouvert la voie à la création des grands parcs nationaux américains comme celui de Yellowstone. Je crois cette voie prometteuse pour [retour | 5]l'avenir de l'Amérique.</t>
-        </is>
+      <c r="S107" s="1" t="s">
+        <v>3491</v>
       </c>
       <c r="T107" s="1" t="s">
         <v>829</v>
@@ -24510,10 +24532,8 @@
       <c r="I269" s="7">
         <v>1</v>
       </c>
-      <c r="S269" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né en 1862 à Baumgarten, près de Vienne. [retour | 5]Mon père était orfèvre, d'origine tchèque, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Gustav_Klimt_-_Mutter_mit_zwei_Kindern_%28Familie%29_-_10501_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Famille, 1909 | 5]et nous étions sept enfants, très pauvres. J'ai trouvé dans le dessin un refuge.  Une de mes petites sœurs est morte à cinq ans. J'en avais douze et je suis resté marqué par sa mort. À quatorze ans, avec mon frère [image: https://upload.wikimedia.org/wikipedia/commons/3/3a/Gustav_Klimt_in_1887.jpg | Photo de Klimt, 1887 | enchaîné 10]Ernst, je suis entré à l'École des Arts Appliqués. Nous avons été reconnus pour notre talent, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b3/Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg/1280px-Hermesvilla_Schlafzimmer_Kaiserin_Deckenmalerei_Detail_1.jpg | Villa Hermès | enchaîné 10]et quelques années plus tard, nous avons décoré théâtres et palais dans le style rococo de l'époque.  Mais en 1897, avec des amis [image: https://upload.wikimedia.org/wikipedia/commons/7/72/Secession_Group%2C_Wien_1902.png | Le Membres de la Sécession viennoise en 1902 | enchaîné 10]artistes et artisans, nous avons créé  la Sécession, un mouvement contre cet art académique, qui nous semblait déjà mort. Nous avons construit notre Palais de la Sécession, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5e/Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg/960px-Budynek_Secesji_w_Wiedniu%2C_20210730_1054_1131.jpg | La Palais de la Sécession | enchaîné 10]pour exposer nos œuvres et promouvoir notre idéal.  L'Art devait se rapprocher de la Vie, cette vie [image: https://upload.wikimedia.org/wikipedia/commons/thumb/e/e2/Judith_1_%28cropped%29.jpg/1280px-Judith_1_%28cropped%29.jpg | Judith et Holopherne, 1901 | enchaîné 10]si belle mais aussi tellement angoissante. Judith, l'héroïne biblique, est une vraie femme, la bouche entrouverte, grisée par le meurtre qu'elle vient d'accomplir. Les Viennois ont crié au scandale. Deux ans plus tard, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/41/Klimt_-_Hoffnung_I_-_1903.jpeg/500px-Klimt_-_Hoffnung_I_-_1903.jpeg | Espoir I, 1903 | enchaîné 10]dans *« L'Espoir »*, j'ai peint une femme enceinte, nue, avec la mort encore qui rôde à ses pieds : la vie et la mort ensemble, voilà ce qui m'obsédait.  En 1903 un [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Italie%2C_Ravenne%2C_basilique_San_Vitale%2C_mosa%C3%AFque_du_R%C3%A9dempteur_entour%C3%A9_de_deux_anges_et_de_saint_Vital_%C3%A0_gauche_et_de_l%27%C3%A9v%C3%AAque_Ecclesius_%C3%A0_droite_%2848087024931%29.jpg/1280px-thumbnail.jpg | Basilique San Vitale, Ravenne | enchaîné 10]voyage à Ravenne m'a ébloui et les mosaïques byzantines m'ont inspiré. Derrière Fritza Riedler, dont le mari [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_-_Fritza_Riedler_-_3379_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Fritza Riedler, 1906 | enchaîné 10]ingénieur voulait un portrait, j'ai fait surgir un fragment de mosaïque, et toute la bourgeoisie viennoise s'est pressée à mon atelier pour obtenir le même style de portrait. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/18/Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg/1280px-Gustav_Klimt%2C_1907%2C_Adele_Bloch-Bauer_I%2C_Neue_Galerie_New_York.jpg | Portrait d'Adele Bloch-Bauer I, 1907 | enchaîné 10]Avec Adèle Bloch-Bauer, j'ai poussé l'idée à l'extrême : près de trois ans de travail, des feuilles d'or et d'argent, des spirales ; seuls le visage et les mains restent peints. [image: https://commons.wikimedia.org/wiki/Special:FilePath/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Le Baiser, 1907-1908 | enchaîné 10]Cette période dorée, avec la feuille d'or posée comme une caresse sur la toile, a donné naissance à mon oeuvre  la plus fameuse *« Le Baiser »* mais je ne pensais pas qu'elle deviendrait si célèbre. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Klimt_Danae.jpg | Danaé, 1907-1908 | enchaîné 10]J'ai aussi peint *« Danaé »*, que Zeus féconde en pluie d'or.  J'ai aimé le désir et le corps des femmes ; mes modèles ont été nombreuses, et Vienne a beaucoup jasé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Photo prise par Moritz Nehr, 1910 | enchaîné 10]Dans la vie, pourtant, je n'ai rien eu d'un dandy, malgré mon aisance matérielle : une longue blouse bleue, des sandales, mes chats. Je ne me suis jamais marié ; j'ai vécu auprès de ma mère et de [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/27/Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg/960px-Heinrich_B%C3%B6hler_1909_Emilie_Fl%C3%B6ge_Gustav_Klimt_003.jpg | Gustav Klimt et Emilie Flöge à Attersee, photo prise en 19099 | enchaîné 10]mes sœurs, et ma complice a été Emilie Flöge, une ancienne couturière. Chaque été, avec Emilie, je me reposais de la ville au bord de l'Attersee : je peignais des jardins [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt%2C_1907%2C_Farm_Garden_with_Sunflowers%2C_%C3%96sterreichische_Galerie_Belvedere.jpg | Le Tournesol, 1907 | enchaîné 10]et des fleurs sur des toiles carrées, sans ciel, comme des tapis de couleurs. Mon projet le plus ambitieux [image: https://upload.wikimedia.org/wikipedia/commons/7/77/Stoclet_Frieze_left.jpg | Décoration de la salle à manger du Palais Stoclet,1909 | enchaîné 10]a été la décoration de la salle à manger du Palais Stoclet, à Bruxelles, une œuvre d'art totale dont *« L'Arbre de vie »* [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_032.jpg | L'Arbre de vie, 1909 | enchaîné 10]est le centre. Quand j'ai peint à nouveau Adele, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Gustav_Klimt_047.jpg | Portrait d'Adele Bloch-Bauer II, 1912 | enchaîné 10]en 1912, l'or avait disparu, remplacé par des couleurs vives inspirées des estampes japonaises : je ne voulais pas me répéter. [image: https://commons.wikimedia.org/wiki/Special:FilePath/KlimtPanna.jpg | La Vierge, 1913 | enchaîné 10]Dans « *La Vierge* », un grand manteau coloré enveloppe des femmes endormies : plus d'or, de la couleur pure. J'ai soutenu le jeune Egon [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/58/Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg/960px-Egon_Schiele_-_Gustav_Klimt_im_blauen_Malerkittel_-_1913.jpeg | Egon Schiele, Klimt dans sa blouse bleue | enchaîné 10]Schiele qui m'a dessiné en 1913 ; je voyais en lui une intensité que je n'avais plus. [image: https://upload.wikimedia.org/wikipedia/commons/2/29/Friedrich_Walker%2C_plaque_autochrome-Lumi%C3%A8re%2C_Gustav_Klimt_vers_1910.jpg | Klimt vers 1910 | enchaîné 10]La Mort qui guette d'un côté, la Vie de l'autre, cela aura été ma question constante. [retour | 5]Je suis mort à Vienne en 1918.</t>
-        </is>
+      <c r="S269" s="1" t="s">
+        <v>3496</v>
       </c>
       <c r="T269" s="10" t="s">
         <v>1863</v>
@@ -26301,6 +26321,9 @@
       <c r="S315" s="1" t="s">
         <v>2113</v>
       </c>
+      <c r="T315" s="10" t="s">
+        <v>3502</v>
+      </c>
       <c r="U315" s="5" t="s">
         <v>2111</v>
       </c>
@@ -27070,6 +27093,9 @@
       <c r="S335" s="1" t="s">
         <v>2217</v>
       </c>
+      <c r="T335" s="10" t="s">
+        <v>3504</v>
+      </c>
       <c r="U335" s="5" t="s">
         <v>2215</v>
       </c>
@@ -27336,6 +27362,9 @@
       <c r="S342" s="1" t="s">
         <v>2253</v>
       </c>
+      <c r="T342" s="10" t="s">
+        <v>3501</v>
+      </c>
       <c r="U342" s="5" t="s">
         <v>2251</v>
       </c>
@@ -29666,6 +29695,9 @@
       <c r="S403" s="1" t="s">
         <v>2562</v>
       </c>
+      <c r="T403" s="10" t="s">
+        <v>3505</v>
+      </c>
       <c r="U403" s="5" t="s">
         <v>2556</v>
       </c>
@@ -30201,6 +30233,9 @@
       <c r="S417" s="1" t="s">
         <v>2630</v>
       </c>
+      <c r="T417" s="10" t="s">
+        <v>3503</v>
+      </c>
       <c r="U417" s="5" t="s">
         <v>2628</v>
       </c>
@@ -32051,7 +32086,7 @@
         <v>2886</v>
       </c>
     </row>
-    <row r="465" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="465" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
         <v>920</v>
       </c>
@@ -32089,7 +32124,7 @@
         <v>2890</v>
       </c>
     </row>
-    <row r="466" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="466" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="s">
         <v>2891</v>
       </c>
@@ -32127,7 +32162,7 @@
         <v>2896</v>
       </c>
     </row>
-    <row r="467" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="467" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="5" t="s">
         <v>575</v>
       </c>
@@ -32165,7 +32200,7 @@
         <v>2900</v>
       </c>
     </row>
-    <row r="468" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="468" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="s">
         <v>2901</v>
       </c>
@@ -32206,7 +32241,7 @@
         <v>2906</v>
       </c>
     </row>
-    <row r="469" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="469" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="5" t="s">
         <v>1811</v>
       </c>
@@ -32244,7 +32279,7 @@
         <v>2910</v>
       </c>
     </row>
-    <row r="470" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="470" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="s">
         <v>2911</v>
       </c>
@@ -32282,7 +32317,7 @@
         <v>2917</v>
       </c>
     </row>
-    <row r="471" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="471" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="s">
         <v>2918</v>
       </c>
@@ -32320,7 +32355,7 @@
         <v>2922</v>
       </c>
     </row>
-    <row r="472" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="472" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="5" t="s">
         <v>219</v>
       </c>
@@ -32358,7 +32393,7 @@
         <v>2926</v>
       </c>
     </row>
-    <row r="473" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="473" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="s">
         <v>154</v>
       </c>
@@ -32399,7 +32434,7 @@
         <v>2931</v>
       </c>
     </row>
-    <row r="474" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="474" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="5" t="s">
         <v>1027</v>
       </c>
@@ -32437,7 +32472,7 @@
         <v>2936</v>
       </c>
     </row>
-    <row r="475" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="475" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="5" t="s">
         <v>1160</v>
       </c>
@@ -32475,7 +32510,7 @@
         <v>2940</v>
       </c>
     </row>
-    <row r="476" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="476" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="5" t="s">
         <v>305</v>
       </c>
@@ -32513,7 +32548,7 @@
         <v>2945</v>
       </c>
     </row>
-    <row r="477" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="477" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="5" t="s">
         <v>2946</v>
       </c>
@@ -32551,7 +32586,7 @@
         <v>2950</v>
       </c>
     </row>
-    <row r="478" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="478" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="5" t="s">
         <v>2951</v>
       </c>
@@ -32589,7 +32624,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="479" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="479" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="s">
         <v>2785</v>
       </c>
@@ -32627,7 +32662,7 @@
         <v>2960</v>
       </c>
     </row>
-    <row r="480" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="480" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="s">
         <v>2961</v>
       </c>
@@ -32652,27 +32687,23 @@
       <c r="I480" s="7">
         <v>2</v>
       </c>
-      <c r="S480" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis née à Paris en 1755, fille d'un pastelliste. [retour | 5]Il est mort quand j'avais douze ans, et j'ai appris à peindre en regardant ses [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg/960px-%C3%89lisabeth_Vig%C3%A9e-Lebrun_-_selfportrait_%28Kimbell_Art_Museum%2C_1781-2%29.jpg | Autportait,1781 | 5]amis. À vingt ans, je gagnais déjà ma vie en faisant des portraits. J'ai révolutionné cet art en le rendant plus sensible, plus léger, fluide et aérien. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_in_a_Straw_Hat_by_Elisabeth-Louise_Vig%C3%A9e-Lebrun.jpg | Autoportrait au chapeau de paille, 1782 | enchaîné 10]Mais j'ai été aussi une travailleuse acharnée, une vraie femme d'affaires, et j'ai aimé raconter que j'ai travaillé entre deux contractions, le jour de mon accouchement. Marie-Antoinette m'a remarquée en 1778, [image: https://upload.wikimedia.org/wikipedia/commons/0/00/MA-Lebrun.jpg | Marie-Antoinette en gaulle, 1783 | enchaîné 10]elle qui aimait tant la liberté et le naturel, et je suis devenue sa portraitiste favorite : plus de trente portraits en quelques années, dont la reine en gaulle. Celui-là a provoqué un vrai scandale! La simple robe de mousseline blanche de Marie-Antoinette ressemblait, disaient les mauvaises langues, à une chemise de nuit. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_dit_%C2%AB_%C3%A0_la_Rose_%C2%BB_-_Google_Art_Project.jpg | Marie-Antoinette avec une rose, 1783 | enchaîné 10]Quelle honte! Alors nous avons décidé de revenir à un portrait plus conventionnel! [image: https://commons.wikimedia.org/wiki/Special:FilePath/Louise_Elisabeth_Vig%C3%A9e-Lebrun_-_Marie-Antoinette_de_Lorraine-Habsbourg%2C_reine_de_France_et_ses_enfants_-_Google_Art_Project.jpg | Marie-Antoinette et ses enfants, 1787 | enchaîné 10]Cette chère Reine! Je l'ai peinte aussi avec ses enfants qu'elle aimait tant! En 1783, l'Académie royale m'a reçue, sur ordre de Louis XVI, malgré l'opposition de certains. [image: https://commons.wikimedia.org/wiki/Special:FilePath/%C3%89lisabeth-Louise_Vig%C3%A9e-Le_Brun_-_Hubert_Robert_%281788%29.jpg | Portrait du peintre Hubert Robert, 1788 | enchaîné 10]Heureusement j'avais le soutien de mon cher ami Hubert Robert dont j'ai fait le portrait. La Révolution m'a obligée à fuir, comme tant d'autres, en 1789. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Self-portrait_with_Her_Daughter_by_Elisabeth-Louise_Vig%C3%A9e_Le_Brun.jpg | Autoportrait avec sa fille Julie, 1789 | enchaîné 10]J'ai vécu pendant douze ans à Rome, Naples, Vienne, Saint-Pétersbourg, partout fêtée et employée par les cours d'Europe, avec ma fille Julie. J'ai transformé mon exil en triomphe et je crois que partout, j'ai fait avancer la cause de la femme, avec sourire, malice mais aussi avec une grande détermination. Je suis rentrée en France en 1802, et j'ai publié mes Souvenirs, où je raconte ces années. [retour | 5]Je suis morte à Paris en 1842, âgée de quatre-vingt-six ans.</t>
-        </is>
+      <c r="S480" s="1" t="s">
+        <v>3497</v>
       </c>
       <c r="T480" s="10" t="s">
-        <v>3495</v>
+        <v>3494</v>
       </c>
       <c r="U480" s="5" t="s">
         <v>2962</v>
       </c>
       <c r="V480" t="s">
+        <v>2964</v>
+      </c>
+      <c r="W480" t="s">
         <v>2965</v>
       </c>
-      <c r="W480" t="s">
-        <v>2966</v>
-      </c>
-      <c r="Y480" t="inlineStr">
-        <is>
-          <t xml:space="preserve">femme</t>
-        </is>
+      <c r="Y480" t="s">
+        <v>3498</v>
       </c>
     </row>
     <row r="481" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32680,7 +32711,7 @@
         <v>71</v>
       </c>
       <c r="B481" s="5" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="D481" s="5" t="s">
         <v>73</v>
@@ -32701,24 +32732,24 @@
         <v>2</v>
       </c>
       <c r="S481" s="1" t="s">
-        <v>2968</v>
+        <v>2967</v>
       </c>
       <c r="U481" s="5" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
       <c r="V481" t="s">
         <v>1875</v>
       </c>
       <c r="W481" t="s">
-        <v>2969</v>
+        <v>2968</v>
       </c>
     </row>
     <row r="482" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="5" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B482" s="5" t="s">
         <v>2970</v>
-      </c>
-      <c r="B482" s="5" t="s">
-        <v>2971</v>
       </c>
       <c r="D482" s="5" t="s">
         <v>73</v>
@@ -32727,10 +32758,10 @@
         <v>44</v>
       </c>
       <c r="F482" s="7" t="s">
+        <v>2971</v>
+      </c>
+      <c r="G482" s="7" t="s">
         <v>2972</v>
-      </c>
-      <c r="G482" s="7" t="s">
-        <v>2973</v>
       </c>
       <c r="H482" s="7" t="s">
         <v>190</v>
@@ -32739,16 +32770,16 @@
         <v>3</v>
       </c>
       <c r="S482" s="1" t="s">
+        <v>2973</v>
+      </c>
+      <c r="U482" s="5" t="s">
+        <v>2970</v>
+      </c>
+      <c r="V482" t="s">
         <v>2974</v>
       </c>
-      <c r="U482" s="5" t="s">
-        <v>2971</v>
-      </c>
-      <c r="V482" t="s">
+      <c r="W482" t="s">
         <v>2975</v>
-      </c>
-      <c r="W482" t="s">
-        <v>2976</v>
       </c>
     </row>
     <row r="483" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32756,7 +32787,7 @@
         <v>669</v>
       </c>
       <c r="B483" s="5" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D483" s="5" t="s">
         <v>73</v>
@@ -32768,7 +32799,7 @@
         <v>554</v>
       </c>
       <c r="G483" s="7" t="s">
-        <v>2977</v>
+        <v>2976</v>
       </c>
       <c r="H483" s="7" t="s">
         <v>190</v>
@@ -32777,16 +32808,16 @@
         <v>3</v>
       </c>
       <c r="S483" s="1" t="s">
-        <v>2978</v>
+        <v>2977</v>
       </c>
       <c r="U483" s="5" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="V483" t="s">
         <v>2003</v>
       </c>
       <c r="W483" t="s">
-        <v>2979</v>
+        <v>2978</v>
       </c>
     </row>
     <row r="484" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32794,7 +32825,7 @@
         <v>107</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
       <c r="D484" s="5" t="s">
         <v>73</v>
@@ -32803,10 +32834,10 @@
         <v>44</v>
       </c>
       <c r="F484" s="7" t="s">
+        <v>2979</v>
+      </c>
+      <c r="G484" s="7" t="s">
         <v>2980</v>
-      </c>
-      <c r="G484" s="7" t="s">
-        <v>2981</v>
       </c>
       <c r="H484" s="7" t="s">
         <v>190</v>
@@ -32815,24 +32846,24 @@
         <v>3</v>
       </c>
       <c r="S484" s="1" t="s">
+        <v>2981</v>
+      </c>
+      <c r="U484" s="5" t="s">
+        <v>2970</v>
+      </c>
+      <c r="V484" t="s">
         <v>2982</v>
       </c>
-      <c r="U484" s="5" t="s">
-        <v>2971</v>
-      </c>
-      <c r="V484" t="s">
+      <c r="W484" t="s">
         <v>2983</v>
-      </c>
-      <c r="W484" t="s">
-        <v>2984</v>
       </c>
     </row>
     <row r="485" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="5" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B485" s="5" t="s">
         <v>2985</v>
-      </c>
-      <c r="B485" s="5" t="s">
-        <v>2986</v>
       </c>
       <c r="D485" s="5" t="s">
         <v>100</v>
@@ -32841,10 +32872,10 @@
         <v>26</v>
       </c>
       <c r="F485" s="7" t="s">
+        <v>2986</v>
+      </c>
+      <c r="G485" s="7" t="s">
         <v>2987</v>
-      </c>
-      <c r="G485" s="7" t="s">
-        <v>2988</v>
       </c>
       <c r="H485" s="7" t="s">
         <v>66</v>
@@ -32853,24 +32884,24 @@
         <v>3</v>
       </c>
       <c r="S485" s="1" t="s">
+        <v>2988</v>
+      </c>
+      <c r="U485" s="5" t="s">
+        <v>2985</v>
+      </c>
+      <c r="V485" t="s">
         <v>2989</v>
       </c>
-      <c r="U485" s="5" t="s">
-        <v>2986</v>
-      </c>
-      <c r="V485" t="s">
+      <c r="W485" t="s">
         <v>2990</v>
-      </c>
-      <c r="W485" t="s">
-        <v>2991</v>
       </c>
     </row>
     <row r="486" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="5" t="s">
+        <v>2991</v>
+      </c>
+      <c r="B486" s="5" t="s">
         <v>2992</v>
-      </c>
-      <c r="B486" s="5" t="s">
-        <v>2993</v>
       </c>
       <c r="D486" s="5" t="s">
         <v>63</v>
@@ -32891,24 +32922,24 @@
         <v>3</v>
       </c>
       <c r="S486" s="1" t="s">
+        <v>2993</v>
+      </c>
+      <c r="U486" s="5" t="s">
+        <v>2992</v>
+      </c>
+      <c r="V486" t="s">
         <v>2994</v>
       </c>
-      <c r="U486" s="5" t="s">
-        <v>2993</v>
-      </c>
-      <c r="V486" t="s">
+      <c r="W486" t="s">
         <v>2995</v>
-      </c>
-      <c r="W486" t="s">
-        <v>2996</v>
       </c>
     </row>
     <row r="487" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B487" s="5" t="s">
         <v>2997</v>
-      </c>
-      <c r="B487" s="5" t="s">
-        <v>2998</v>
       </c>
       <c r="D487" s="5" t="s">
         <v>63</v>
@@ -32929,16 +32960,16 @@
         <v>3</v>
       </c>
       <c r="S487" s="1" t="s">
+        <v>2998</v>
+      </c>
+      <c r="U487" s="5" t="s">
+        <v>2997</v>
+      </c>
+      <c r="V487" t="s">
         <v>2999</v>
       </c>
-      <c r="U487" s="5" t="s">
-        <v>2998</v>
-      </c>
-      <c r="V487" t="s">
+      <c r="W487" t="s">
         <v>3000</v>
-      </c>
-      <c r="W487" t="s">
-        <v>3001</v>
       </c>
     </row>
     <row r="488" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -32946,7 +32977,7 @@
         <v>2096</v>
       </c>
       <c r="B488" s="5" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
       <c r="D488" s="5" t="s">
         <v>25</v>
@@ -32967,24 +32998,24 @@
         <v>3</v>
       </c>
       <c r="S488" s="1" t="s">
+        <v>3002</v>
+      </c>
+      <c r="U488" s="5" t="s">
+        <v>3001</v>
+      </c>
+      <c r="V488" t="s">
         <v>3003</v>
       </c>
-      <c r="U488" s="5" t="s">
-        <v>3002</v>
-      </c>
-      <c r="V488" t="s">
+      <c r="W488" t="s">
         <v>3004</v>
-      </c>
-      <c r="W488" t="s">
-        <v>3005</v>
       </c>
     </row>
     <row r="489" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="5" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B489" s="5" t="s">
         <v>3006</v>
-      </c>
-      <c r="B489" s="5" t="s">
-        <v>3007</v>
       </c>
       <c r="D489" s="5" t="s">
         <v>63</v>
@@ -33005,19 +33036,19 @@
         <v>3</v>
       </c>
       <c r="S489" s="1" t="s">
+        <v>3007</v>
+      </c>
+      <c r="T489" s="10" t="s">
         <v>3008</v>
       </c>
-      <c r="T489" s="10" t="s">
+      <c r="U489" s="5" t="s">
+        <v>3006</v>
+      </c>
+      <c r="V489" t="s">
         <v>3009</v>
       </c>
-      <c r="U489" s="5" t="s">
-        <v>3007</v>
-      </c>
-      <c r="V489" t="s">
+      <c r="W489" t="s">
         <v>3010</v>
-      </c>
-      <c r="W489" t="s">
-        <v>3011</v>
       </c>
     </row>
     <row r="490" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33025,7 +33056,7 @@
         <v>2066</v>
       </c>
       <c r="B490" s="5" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
       <c r="D490" s="5" t="s">
         <v>25</v>
@@ -33046,27 +33077,27 @@
         <v>2</v>
       </c>
       <c r="S490" s="1" t="s">
+        <v>3012</v>
+      </c>
+      <c r="T490" s="10" t="s">
         <v>3013</v>
       </c>
-      <c r="T490" s="10" t="s">
+      <c r="U490" s="5" t="s">
+        <v>3011</v>
+      </c>
+      <c r="V490" t="s">
         <v>3014</v>
       </c>
-      <c r="U490" s="5" t="s">
-        <v>3012</v>
-      </c>
-      <c r="V490" t="s">
+      <c r="W490" t="s">
         <v>3015</v>
-      </c>
-      <c r="W490" t="s">
-        <v>3016</v>
       </c>
     </row>
     <row r="491" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="5" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B491" s="5" t="s">
         <v>3017</v>
-      </c>
-      <c r="B491" s="5" t="s">
-        <v>3018</v>
       </c>
       <c r="D491" s="5" t="s">
         <v>427</v>
@@ -33075,7 +33106,7 @@
         <v>44</v>
       </c>
       <c r="F491" s="7" t="s">
-        <v>3019</v>
+        <v>3018</v>
       </c>
       <c r="G491" s="7" t="s">
         <v>1190</v>
@@ -33087,19 +33118,19 @@
         <v>3</v>
       </c>
       <c r="S491" s="1" t="s">
+        <v>3019</v>
+      </c>
+      <c r="T491" s="10" t="s">
         <v>3020</v>
       </c>
-      <c r="T491" s="10" t="s">
+      <c r="U491" s="5" t="s">
+        <v>3017</v>
+      </c>
+      <c r="V491" t="s">
         <v>3021</v>
       </c>
-      <c r="U491" s="5" t="s">
-        <v>3018</v>
-      </c>
-      <c r="V491" t="s">
+      <c r="W491" t="s">
         <v>3022</v>
-      </c>
-      <c r="W491" t="s">
-        <v>3023</v>
       </c>
     </row>
     <row r="492" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33107,7 +33138,7 @@
         <v>1783</v>
       </c>
       <c r="B492" s="5" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="D492" s="5" t="s">
         <v>25</v>
@@ -33116,7 +33147,7 @@
         <v>44</v>
       </c>
       <c r="F492" s="7" t="s">
-        <v>3025</v>
+        <v>3024</v>
       </c>
       <c r="G492" s="7" t="s">
         <v>362</v>
@@ -33128,27 +33159,27 @@
         <v>1</v>
       </c>
       <c r="S492" s="1" t="s">
+        <v>3025</v>
+      </c>
+      <c r="T492" s="10" t="s">
         <v>3026</v>
       </c>
-      <c r="T492" s="10" t="s">
+      <c r="U492" s="5" t="s">
+        <v>3023</v>
+      </c>
+      <c r="V492" t="s">
         <v>3027</v>
       </c>
-      <c r="U492" s="5" t="s">
-        <v>3024</v>
-      </c>
-      <c r="V492" t="s">
+      <c r="W492" t="s">
         <v>3028</v>
-      </c>
-      <c r="W492" t="s">
-        <v>3029</v>
       </c>
     </row>
     <row r="493" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="5" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B493" s="5" t="s">
         <v>3030</v>
-      </c>
-      <c r="B493" s="5" t="s">
-        <v>3031</v>
       </c>
       <c r="D493" s="5" t="s">
         <v>419</v>
@@ -33169,27 +33200,27 @@
         <v>3</v>
       </c>
       <c r="S493" s="1" t="s">
+        <v>3031</v>
+      </c>
+      <c r="T493" s="10" t="s">
         <v>3032</v>
       </c>
-      <c r="T493" s="10" t="s">
+      <c r="U493" s="5" t="s">
+        <v>3030</v>
+      </c>
+      <c r="V493" t="s">
         <v>3033</v>
       </c>
-      <c r="U493" s="5" t="s">
-        <v>3031</v>
-      </c>
-      <c r="V493" t="s">
+      <c r="W493" t="s">
         <v>3034</v>
-      </c>
-      <c r="W493" t="s">
-        <v>3035</v>
       </c>
     </row>
     <row r="494" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="5" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B494" s="5" t="s">
         <v>3036</v>
-      </c>
-      <c r="B494" s="5" t="s">
-        <v>3037</v>
       </c>
       <c r="D494" s="5" t="s">
         <v>419</v>
@@ -33210,27 +33241,27 @@
         <v>3</v>
       </c>
       <c r="S494" s="1" t="s">
+        <v>3037</v>
+      </c>
+      <c r="T494" s="10" t="s">
         <v>3038</v>
       </c>
-      <c r="T494" s="10" t="s">
+      <c r="U494" s="5" t="s">
+        <v>3036</v>
+      </c>
+      <c r="V494" t="s">
         <v>3039</v>
       </c>
-      <c r="U494" s="5" t="s">
-        <v>3037</v>
-      </c>
-      <c r="V494" t="s">
+      <c r="W494" t="s">
         <v>3040</v>
-      </c>
-      <c r="W494" t="s">
-        <v>3041</v>
       </c>
     </row>
     <row r="495" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="5" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B495" s="5" t="s">
         <v>3042</v>
-      </c>
-      <c r="B495" s="5" t="s">
-        <v>3043</v>
       </c>
       <c r="D495" s="5" t="s">
         <v>419</v>
@@ -33239,10 +33270,10 @@
         <v>26</v>
       </c>
       <c r="F495" s="7" t="s">
+        <v>3043</v>
+      </c>
+      <c r="G495" s="7" t="s">
         <v>3044</v>
-      </c>
-      <c r="G495" s="7" t="s">
-        <v>3045</v>
       </c>
       <c r="H495" s="7" t="s">
         <v>66</v>
@@ -33251,24 +33282,24 @@
         <v>3</v>
       </c>
       <c r="S495" s="1" t="s">
+        <v>3045</v>
+      </c>
+      <c r="U495" s="5" t="s">
+        <v>3042</v>
+      </c>
+      <c r="V495" t="s">
         <v>3046</v>
       </c>
-      <c r="U495" s="5" t="s">
-        <v>3043</v>
-      </c>
-      <c r="V495" t="s">
+      <c r="W495" t="s">
         <v>3047</v>
-      </c>
-      <c r="W495" t="s">
-        <v>3048</v>
       </c>
     </row>
     <row r="496" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="5" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B496" s="5" t="s">
         <v>3049</v>
-      </c>
-      <c r="B496" s="5" t="s">
-        <v>3050</v>
       </c>
       <c r="D496" s="5" t="s">
         <v>427</v>
@@ -33280,7 +33311,7 @@
         <v>2349</v>
       </c>
       <c r="G496" s="7" t="s">
-        <v>3051</v>
+        <v>3050</v>
       </c>
       <c r="H496" s="7" t="s">
         <v>29</v>
@@ -33289,16 +33320,16 @@
         <v>3</v>
       </c>
       <c r="S496" s="1" t="s">
+        <v>3051</v>
+      </c>
+      <c r="U496" s="5" t="s">
+        <v>3049</v>
+      </c>
+      <c r="V496" t="s">
         <v>3052</v>
       </c>
-      <c r="U496" s="5" t="s">
-        <v>3050</v>
-      </c>
-      <c r="V496" t="s">
+      <c r="W496" t="s">
         <v>3053</v>
-      </c>
-      <c r="W496" t="s">
-        <v>3054</v>
       </c>
     </row>
     <row r="497" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33306,7 +33337,7 @@
         <v>2282</v>
       </c>
       <c r="B497" s="5" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
       <c r="D497" s="5" t="s">
         <v>427</v>
@@ -33327,16 +33358,16 @@
         <v>3</v>
       </c>
       <c r="S497" s="1" t="s">
+        <v>3055</v>
+      </c>
+      <c r="U497" s="5" t="s">
+        <v>3054</v>
+      </c>
+      <c r="V497" t="s">
         <v>3056</v>
       </c>
-      <c r="U497" s="5" t="s">
-        <v>3055</v>
-      </c>
-      <c r="V497" t="s">
+      <c r="W497" t="s">
         <v>3057</v>
-      </c>
-      <c r="W497" t="s">
-        <v>3058</v>
       </c>
     </row>
     <row r="498" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33344,7 +33375,7 @@
         <v>211</v>
       </c>
       <c r="B498" s="5" t="s">
-        <v>3059</v>
+        <v>3058</v>
       </c>
       <c r="D498" s="5" t="s">
         <v>427</v>
@@ -33365,16 +33396,16 @@
         <v>3</v>
       </c>
       <c r="S498" s="1" t="s">
+        <v>3059</v>
+      </c>
+      <c r="U498" s="5" t="s">
+        <v>3058</v>
+      </c>
+      <c r="V498" t="s">
         <v>3060</v>
       </c>
-      <c r="U498" s="5" t="s">
-        <v>3059</v>
-      </c>
-      <c r="V498" t="s">
+      <c r="W498" t="s">
         <v>3061</v>
-      </c>
-      <c r="W498" t="s">
-        <v>3062</v>
       </c>
     </row>
     <row r="499" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33382,7 +33413,7 @@
         <v>1379</v>
       </c>
       <c r="B499" s="6" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
       <c r="D499" s="5" t="s">
         <v>427</v>
@@ -33391,10 +33422,10 @@
         <v>44</v>
       </c>
       <c r="F499" s="7" t="s">
+        <v>3063</v>
+      </c>
+      <c r="G499" s="7" t="s">
         <v>3064</v>
-      </c>
-      <c r="G499" s="7" t="s">
-        <v>3065</v>
       </c>
       <c r="H499" s="12" t="s">
         <v>29</v>
@@ -33403,16 +33434,16 @@
         <v>3</v>
       </c>
       <c r="S499" s="1" t="s">
+        <v>3065</v>
+      </c>
+      <c r="U499" s="6" t="s">
+        <v>3062</v>
+      </c>
+      <c r="V499" t="s">
         <v>3066</v>
       </c>
-      <c r="U499" s="6" t="s">
-        <v>3063</v>
-      </c>
-      <c r="V499" t="s">
+      <c r="W499" t="s">
         <v>3067</v>
-      </c>
-      <c r="W499" t="s">
-        <v>3068</v>
       </c>
     </row>
     <row r="500" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -33420,10 +33451,10 @@
         <v>305</v>
       </c>
       <c r="B500" s="5" t="s">
+        <v>3068</v>
+      </c>
+      <c r="C500" s="5" t="s">
         <v>3069</v>
-      </c>
-      <c r="C500" s="5" t="s">
-        <v>3070</v>
       </c>
       <c r="D500" s="5" t="s">
         <v>73</v>
@@ -33444,24 +33475,24 @@
         <v>3</v>
       </c>
       <c r="S500" s="1" t="s">
+        <v>3070</v>
+      </c>
+      <c r="U500" s="5" t="s">
+        <v>3068</v>
+      </c>
+      <c r="V500" t="s">
         <v>3071</v>
       </c>
-      <c r="U500" s="5" t="s">
-        <v>3069</v>
-      </c>
-      <c r="V500" t="s">
+      <c r="W500" t="s">
         <v>3072</v>
-      </c>
-      <c r="W500" t="s">
-        <v>3073</v>
       </c>
     </row>
     <row r="501" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="5" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B501" s="5" t="s">
         <v>3074</v>
-      </c>
-      <c r="B501" s="5" t="s">
-        <v>3075</v>
       </c>
       <c r="D501" s="5" t="s">
         <v>100</v>
@@ -33473,7 +33504,7 @@
         <v>893</v>
       </c>
       <c r="G501" s="7" t="s">
-        <v>3076</v>
+        <v>3075</v>
       </c>
       <c r="H501" s="7" t="s">
         <v>29</v>
@@ -33482,19 +33513,19 @@
         <v>3</v>
       </c>
       <c r="S501" s="1" t="s">
+        <v>3076</v>
+      </c>
+      <c r="T501" s="1" t="s">
         <v>3077</v>
       </c>
-      <c r="T501" s="1" t="s">
+      <c r="U501" s="5" t="s">
+        <v>3074</v>
+      </c>
+      <c r="V501" t="s">
         <v>3078</v>
       </c>
-      <c r="U501" s="5" t="s">
-        <v>3075</v>
-      </c>
-      <c r="V501" t="s">
+      <c r="W501" t="s">
         <v>3079</v>
-      </c>
-      <c r="W501" t="s">
-        <v>3080</v>
       </c>
     </row>
   </sheetData>
@@ -33715,6 +33746,11 @@
     <hyperlink ref="T501" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
     <hyperlink ref="T81" r:id="rId214" xr:uid="{510BBB2D-DE5F-4FD2-8657-CA730A58D193}"/>
     <hyperlink ref="T480" r:id="rId215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Self-portrait_%28by_Elisabeth_Vig%C3%A9e-Lebrun%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg/960px-Self-portrait_%28by_Elisabeth_Vig%C3%A9e-Lebrun%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDD44873-E746-4519-B0AF-9B6C0CBC5979}"/>
+    <hyperlink ref="T342" r:id="rId216" xr:uid="{394A8A35-4623-42F8-BC8F-42EFBE766765}"/>
+    <hyperlink ref="T315" r:id="rId217" xr:uid="{25987D31-B8E5-4F13-9BD1-E5D170A25532}"/>
+    <hyperlink ref="T417" r:id="rId218" xr:uid="{E0B6CCDF-3F8A-4F03-B63F-9E00E96FEE94}"/>
+    <hyperlink ref="T335" r:id="rId219" xr:uid="{8AC30FBA-DF83-43EE-B058-49BF3FDF320F}"/>
+    <hyperlink ref="T403" r:id="rId220" xr:uid="{314F00E6-9A0F-40A2-9DF1-6029865709D0}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -33749,12 +33785,12 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -33792,10 +33828,10 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B8" t="s">
         <v>3083</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3084</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
@@ -33849,10 +33885,10 @@
         <v>353</v>
       </c>
       <c r="B14" t="s">
+        <v>3084</v>
+      </c>
+      <c r="C14" t="s">
         <v>3085</v>
-      </c>
-      <c r="C14" t="s">
-        <v>3086</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.25">
@@ -33908,40 +33944,40 @@
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B21" t="s">
         <v>3087</v>
-      </c>
-      <c r="B21" t="s">
-        <v>3088</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B22" t="s">
         <v>3089</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>3090</v>
-      </c>
-      <c r="C22" t="s">
-        <v>3091</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B23" t="s">
         <v>3092</v>
-      </c>
-      <c r="B23" t="s">
-        <v>3093</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>3093</v>
+      </c>
+      <c r="B24" t="s">
         <v>3094</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>3095</v>
-      </c>
-      <c r="C24" t="s">
-        <v>3096</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.25">
@@ -33968,10 +34004,10 @@
         <v>847</v>
       </c>
       <c r="B27" t="s">
+        <v>3096</v>
+      </c>
+      <c r="C27" t="s">
         <v>3097</v>
-      </c>
-      <c r="C27" t="s">
-        <v>3098</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.25">
@@ -34003,10 +34039,10 @@
         <v>353</v>
       </c>
       <c r="B31" t="s">
+        <v>3098</v>
+      </c>
+      <c r="C31" t="s">
         <v>3099</v>
-      </c>
-      <c r="C31" t="s">
-        <v>3100</v>
       </c>
     </row>
     <row r="32" spans="1:3" x14ac:dyDescent="0.25">
@@ -34022,10 +34058,10 @@
         <v>211</v>
       </c>
       <c r="B33" t="s">
+        <v>3100</v>
+      </c>
+      <c r="C33" t="s">
         <v>3101</v>
-      </c>
-      <c r="C33" t="s">
-        <v>3102</v>
       </c>
     </row>
     <row r="34" spans="1:3" x14ac:dyDescent="0.25">
@@ -34044,7 +34080,7 @@
         <v>353</v>
       </c>
       <c r="B35" t="s">
-        <v>3103</v>
+        <v>3102</v>
       </c>
     </row>
     <row r="36" spans="1:3" x14ac:dyDescent="0.25">
@@ -34073,10 +34109,10 @@
     </row>
     <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B39" t="s">
         <v>3104</v>
-      </c>
-      <c r="B39" t="s">
-        <v>3105</v>
       </c>
     </row>
     <row r="40" spans="1:3" x14ac:dyDescent="0.25">
@@ -34116,13 +34152,13 @@
     </row>
     <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B44" t="s">
         <v>3106</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>3107</v>
-      </c>
-      <c r="C44" t="s">
-        <v>3108</v>
       </c>
     </row>
     <row r="45" spans="1:3" x14ac:dyDescent="0.25">
@@ -34170,10 +34206,10 @@
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
+        <v>3108</v>
+      </c>
+      <c r="B50" t="s">
         <v>3109</v>
-      </c>
-      <c r="B50" t="s">
-        <v>3110</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.25">
@@ -34181,10 +34217,10 @@
         <v>1289</v>
       </c>
       <c r="B51" t="s">
+        <v>3110</v>
+      </c>
+      <c r="C51" t="s">
         <v>3111</v>
-      </c>
-      <c r="C51" t="s">
-        <v>3112</v>
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
@@ -34197,10 +34233,10 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>3112</v>
+      </c>
+      <c r="B53" t="s">
         <v>3113</v>
-      </c>
-      <c r="B53" t="s">
-        <v>3114</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -34264,10 +34300,10 @@
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
+        <v>3114</v>
+      </c>
+      <c r="B61" t="s">
         <v>3115</v>
-      </c>
-      <c r="B61" t="s">
-        <v>3116</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.25">
@@ -34313,7 +34349,7 @@
         <v>385</v>
       </c>
       <c r="C66" t="s">
-        <v>3117</v>
+        <v>3116</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
@@ -34326,10 +34362,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>3117</v>
+      </c>
+      <c r="B68" t="s">
         <v>3118</v>
-      </c>
-      <c r="B68" t="s">
-        <v>3119</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
@@ -34366,18 +34402,18 @@
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
+        <v>3119</v>
+      </c>
+      <c r="B73" t="s">
         <v>3120</v>
-      </c>
-      <c r="B73" t="s">
-        <v>3121</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
+        <v>3121</v>
+      </c>
+      <c r="B74" t="s">
         <v>3122</v>
-      </c>
-      <c r="B74" t="s">
-        <v>3123</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.25">
@@ -34406,10 +34442,10 @@
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
+        <v>3123</v>
+      </c>
+      <c r="B78" t="s">
         <v>3124</v>
-      </c>
-      <c r="B78" t="s">
-        <v>3125</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
@@ -34417,7 +34453,7 @@
         <v>1195</v>
       </c>
       <c r="B79" t="s">
-        <v>3126</v>
+        <v>3125</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.25">
@@ -34433,13 +34469,13 @@
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B81" t="s">
         <v>3127</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>3128</v>
-      </c>
-      <c r="C81" t="s">
-        <v>3129</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.25">
@@ -34506,10 +34542,10 @@
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B89" t="s">
         <v>3130</v>
-      </c>
-      <c r="B89" t="s">
-        <v>3131</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.25">
@@ -34582,7 +34618,7 @@
         <v>451</v>
       </c>
       <c r="B97" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.25">
@@ -34606,10 +34642,10 @@
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
+        <v>3132</v>
+      </c>
+      <c r="B100" t="s">
         <v>3133</v>
-      </c>
-      <c r="B100" t="s">
-        <v>3134</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.25">
@@ -34617,29 +34653,29 @@
         <v>1195</v>
       </c>
       <c r="B101" t="s">
+        <v>3134</v>
+      </c>
+      <c r="C101" t="s">
         <v>3135</v>
-      </c>
-      <c r="C101" t="s">
-        <v>3136</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
+        <v>3136</v>
+      </c>
+      <c r="B102" t="s">
         <v>3137</v>
       </c>
-      <c r="B102" t="s">
+      <c r="C102" t="s">
         <v>3138</v>
-      </c>
-      <c r="C102" t="s">
-        <v>3139</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B103" t="s">
         <v>3140</v>
-      </c>
-      <c r="B103" t="s">
-        <v>3141</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.25">
@@ -34647,7 +34683,7 @@
         <v>567</v>
       </c>
       <c r="B104" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.25">
@@ -34674,7 +34710,7 @@
         <v>195</v>
       </c>
       <c r="B107" t="s">
-        <v>3143</v>
+        <v>3142</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.25">
@@ -34690,7 +34726,7 @@
         <v>2901</v>
       </c>
       <c r="B109" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
@@ -34706,13 +34742,13 @@
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B111" t="s">
         <v>3145</v>
       </c>
-      <c r="B111" t="s">
+      <c r="C111" t="s">
         <v>3146</v>
-      </c>
-      <c r="C111" t="s">
-        <v>3147</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.25">
@@ -34728,15 +34764,15 @@
         <v>169</v>
       </c>
       <c r="B113" t="s">
-        <v>3148</v>
+        <v>3147</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
+        <v>3148</v>
+      </c>
+      <c r="B114" t="s">
         <v>3149</v>
-      </c>
-      <c r="B114" t="s">
-        <v>3150</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.25">
@@ -34773,40 +34809,40 @@
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B119" t="s">
         <v>3151</v>
-      </c>
-      <c r="B119" t="s">
-        <v>3152</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B120" t="s">
         <v>3153</v>
       </c>
-      <c r="B120" t="s">
+      <c r="C120" t="s">
         <v>3154</v>
-      </c>
-      <c r="C120" t="s">
-        <v>3155</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
+        <v>3155</v>
+      </c>
+      <c r="B121" t="s">
         <v>3156</v>
-      </c>
-      <c r="B121" t="s">
-        <v>3157</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
+        <v>3157</v>
+      </c>
+      <c r="B122" t="s">
         <v>3158</v>
       </c>
-      <c r="B122" t="s">
+      <c r="C122" t="s">
         <v>3159</v>
-      </c>
-      <c r="C122" t="s">
-        <v>3160</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.25">
@@ -34905,10 +34941,10 @@
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
+        <v>3160</v>
+      </c>
+      <c r="B134" t="s">
         <v>3161</v>
-      </c>
-      <c r="B134" t="s">
-        <v>3162</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.25">
@@ -34916,7 +34952,7 @@
         <v>392</v>
       </c>
       <c r="B135" t="s">
-        <v>3163</v>
+        <v>3162</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.25">
@@ -34954,7 +34990,7 @@
         <v>2343</v>
       </c>
       <c r="B139" t="s">
-        <v>3164</v>
+        <v>3163</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.25">
@@ -34962,7 +34998,7 @@
         <v>336</v>
       </c>
       <c r="B140" t="s">
-        <v>3165</v>
+        <v>3164</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
@@ -34989,15 +35025,15 @@
         <v>1379</v>
       </c>
       <c r="B143" t="s">
-        <v>3166</v>
+        <v>3165</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>3166</v>
+      </c>
+      <c r="B144" t="s">
         <v>3167</v>
-      </c>
-      <c r="B144" t="s">
-        <v>3168</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.25">
@@ -35018,15 +35054,15 @@
     </row>
     <row r="147" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
+        <v>3168</v>
+      </c>
+      <c r="B147" t="s">
         <v>3169</v>
-      </c>
-      <c r="B147" t="s">
-        <v>3170</v>
       </c>
     </row>
     <row r="148" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B148" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
     </row>
     <row r="149" spans="1:3" x14ac:dyDescent="0.25">
@@ -35034,21 +35070,21 @@
         <v>1195</v>
       </c>
       <c r="B149" t="s">
+        <v>3171</v>
+      </c>
+      <c r="C149" t="s">
         <v>3172</v>
-      </c>
-      <c r="C149" t="s">
-        <v>3173</v>
       </c>
     </row>
     <row r="150" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
+        <v>3173</v>
+      </c>
+      <c r="B150" t="s">
+        <v>3171</v>
+      </c>
+      <c r="C150" t="s">
         <v>3174</v>
-      </c>
-      <c r="B150" t="s">
-        <v>3172</v>
-      </c>
-      <c r="C150" t="s">
-        <v>3175</v>
       </c>
     </row>
     <row r="151" spans="1:3" x14ac:dyDescent="0.25">
@@ -35123,13 +35159,13 @@
     </row>
     <row r="159" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
+        <v>3175</v>
+      </c>
+      <c r="B159" t="s">
         <v>3176</v>
       </c>
-      <c r="B159" t="s">
+      <c r="C159" t="s">
         <v>3177</v>
-      </c>
-      <c r="C159" t="s">
-        <v>3178</v>
       </c>
     </row>
     <row r="160" spans="1:3" x14ac:dyDescent="0.25">
@@ -35137,7 +35173,7 @@
         <v>451</v>
       </c>
       <c r="B160" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.25">
@@ -35145,18 +35181,18 @@
         <v>124</v>
       </c>
       <c r="B161" t="s">
+        <v>3178</v>
+      </c>
+      <c r="C161" t="s">
         <v>3179</v>
-      </c>
-      <c r="C161" t="s">
-        <v>3180</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
+        <v>3180</v>
+      </c>
+      <c r="B162" t="s">
         <v>3181</v>
-      </c>
-      <c r="B162" t="s">
-        <v>3182</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.25">
@@ -35201,10 +35237,10 @@
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B168" t="s">
         <v>3183</v>
-      </c>
-      <c r="B168" t="s">
-        <v>3184</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.25">
@@ -35263,10 +35299,10 @@
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>3184</v>
+      </c>
+      <c r="B175" t="s">
         <v>3185</v>
-      </c>
-      <c r="B175" t="s">
-        <v>3186</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.25">
@@ -35339,7 +35375,7 @@
         <v>643</v>
       </c>
       <c r="B183" t="s">
-        <v>3187</v>
+        <v>3186</v>
       </c>
     </row>
     <row r="184" spans="1:3" x14ac:dyDescent="0.25">
@@ -35363,7 +35399,7 @@
         <v>360</v>
       </c>
       <c r="B186" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
     </row>
     <row r="187" spans="1:3" x14ac:dyDescent="0.25">
@@ -35398,7 +35434,7 @@
         <v>195</v>
       </c>
       <c r="B190" t="s">
-        <v>3189</v>
+        <v>3188</v>
       </c>
     </row>
     <row r="191" spans="1:3" x14ac:dyDescent="0.25">
@@ -35471,10 +35507,10 @@
         <v>2779</v>
       </c>
       <c r="B198" t="s">
+        <v>3189</v>
+      </c>
+      <c r="C198" t="s">
         <v>3190</v>
-      </c>
-      <c r="C198" t="s">
-        <v>3191</v>
       </c>
     </row>
     <row r="199" spans="1:3" x14ac:dyDescent="0.25">
@@ -35506,21 +35542,21 @@
     </row>
     <row r="202" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>3191</v>
+      </c>
+      <c r="B202" t="s">
         <v>3192</v>
-      </c>
-      <c r="B202" t="s">
-        <v>3193</v>
       </c>
     </row>
     <row r="203" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
+        <v>3193</v>
+      </c>
+      <c r="B203" t="s">
         <v>3194</v>
       </c>
-      <c r="B203" t="s">
+      <c r="C203" t="s">
         <v>3195</v>
-      </c>
-      <c r="C203" t="s">
-        <v>3196</v>
       </c>
     </row>
     <row r="204" spans="1:3" x14ac:dyDescent="0.25">
@@ -35558,7 +35594,7 @@
         <v>853</v>
       </c>
       <c r="B207" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
     </row>
     <row r="208" spans="1:3" x14ac:dyDescent="0.25">
@@ -35585,7 +35621,7 @@
         <v>643</v>
       </c>
       <c r="B210" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
     </row>
     <row r="211" spans="1:3" x14ac:dyDescent="0.25">
@@ -35598,18 +35634,18 @@
     </row>
     <row r="212" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
+        <v>3198</v>
+      </c>
+      <c r="B212" t="s">
         <v>3199</v>
-      </c>
-      <c r="B212" t="s">
-        <v>3200</v>
       </c>
     </row>
     <row r="213" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
+        <v>3200</v>
+      </c>
+      <c r="B213" t="s">
         <v>3201</v>
-      </c>
-      <c r="B213" t="s">
-        <v>3202</v>
       </c>
     </row>
     <row r="214" spans="1:3" x14ac:dyDescent="0.25">
@@ -35625,26 +35661,26 @@
         <v>732</v>
       </c>
       <c r="B215" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
     </row>
     <row r="216" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
+        <v>3203</v>
+      </c>
+      <c r="B216" t="s">
         <v>3204</v>
-      </c>
-      <c r="B216" t="s">
-        <v>3205</v>
       </c>
     </row>
     <row r="217" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B217" t="s">
+        <v>3205</v>
+      </c>
+      <c r="C217" t="s">
         <v>3206</v>
-      </c>
-      <c r="C217" t="s">
-        <v>3207</v>
       </c>
     </row>
     <row r="218" spans="1:3" x14ac:dyDescent="0.25">
@@ -35687,7 +35723,7 @@
         <v>504</v>
       </c>
       <c r="B222" t="s">
-        <v>3208</v>
+        <v>3207</v>
       </c>
     </row>
     <row r="223" spans="1:3" x14ac:dyDescent="0.25">
@@ -35722,15 +35758,15 @@
         <v>732</v>
       </c>
       <c r="B226" t="s">
-        <v>3209</v>
+        <v>3208</v>
       </c>
     </row>
     <row r="227" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
+        <v>3209</v>
+      </c>
+      <c r="B227" t="s">
         <v>3210</v>
-      </c>
-      <c r="B227" t="s">
-        <v>3211</v>
       </c>
     </row>
     <row r="228" spans="1:3" x14ac:dyDescent="0.25">
@@ -35746,7 +35782,7 @@
         <v>544</v>
       </c>
       <c r="B229" t="s">
-        <v>3212</v>
+        <v>3211</v>
       </c>
     </row>
     <row r="230" spans="1:3" x14ac:dyDescent="0.25">
@@ -35754,15 +35790,15 @@
         <v>195</v>
       </c>
       <c r="B230" t="s">
-        <v>3213</v>
+        <v>3212</v>
       </c>
     </row>
     <row r="231" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
+        <v>3213</v>
+      </c>
+      <c r="B231" t="s">
         <v>3214</v>
-      </c>
-      <c r="B231" t="s">
-        <v>3215</v>
       </c>
     </row>
     <row r="232" spans="1:3" x14ac:dyDescent="0.25">
@@ -35821,15 +35857,15 @@
         <v>1451</v>
       </c>
       <c r="B238" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="239" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>3217</v>
+        <v>3216</v>
       </c>
       <c r="B239" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="240" spans="1:3" x14ac:dyDescent="0.25">
@@ -35853,15 +35889,15 @@
         <v>920</v>
       </c>
       <c r="B242" t="s">
-        <v>3218</v>
+        <v>3217</v>
       </c>
     </row>
     <row r="243" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B243" t="s">
         <v>3219</v>
-      </c>
-      <c r="B243" t="s">
-        <v>3220</v>
       </c>
     </row>
     <row r="244" spans="1:3" x14ac:dyDescent="0.25">
@@ -35882,10 +35918,10 @@
     </row>
     <row r="246" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B246" t="s">
         <v>3221</v>
-      </c>
-      <c r="B246" t="s">
-        <v>3222</v>
       </c>
     </row>
     <row r="247" spans="1:3" x14ac:dyDescent="0.25">
@@ -35928,7 +35964,7 @@
         <v>1195</v>
       </c>
       <c r="B251" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="252" spans="1:3" x14ac:dyDescent="0.25">
@@ -35936,7 +35972,7 @@
         <v>1104</v>
       </c>
       <c r="B252" t="s">
-        <v>3224</v>
+        <v>3223</v>
       </c>
     </row>
     <row r="253" spans="1:3" x14ac:dyDescent="0.25">
@@ -35949,13 +35985,13 @@
     </row>
     <row r="254" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
+        <v>3224</v>
+      </c>
+      <c r="B254" t="s">
         <v>3225</v>
       </c>
-      <c r="B254" t="s">
+      <c r="C254" t="s">
         <v>3226</v>
-      </c>
-      <c r="C254" t="s">
-        <v>3227</v>
       </c>
     </row>
     <row r="255" spans="1:3" x14ac:dyDescent="0.25">
@@ -35963,7 +35999,7 @@
         <v>1735</v>
       </c>
       <c r="B255" t="s">
-        <v>3226</v>
+        <v>3225</v>
       </c>
     </row>
     <row r="256" spans="1:3" x14ac:dyDescent="0.25">
@@ -36019,13 +36055,13 @@
     </row>
     <row r="262" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
+        <v>3227</v>
+      </c>
+      <c r="B262" t="s">
         <v>3228</v>
       </c>
-      <c r="B262" t="s">
+      <c r="C262" t="s">
         <v>3229</v>
-      </c>
-      <c r="C262" t="s">
-        <v>3230</v>
       </c>
     </row>
     <row r="263" spans="1:3" x14ac:dyDescent="0.25">
@@ -36057,13 +36093,13 @@
     </row>
     <row r="266" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B266" t="s">
         <v>3231</v>
       </c>
-      <c r="B266" t="s">
+      <c r="C266" t="s">
         <v>3232</v>
-      </c>
-      <c r="C266" t="s">
-        <v>3233</v>
       </c>
     </row>
     <row r="267" spans="1:3" x14ac:dyDescent="0.25">
@@ -36076,10 +36112,10 @@
     </row>
     <row r="268" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B268" t="s">
         <v>3234</v>
-      </c>
-      <c r="B268" t="s">
-        <v>3235</v>
       </c>
     </row>
     <row r="269" spans="1:3" x14ac:dyDescent="0.25">
@@ -36111,7 +36147,7 @@
         <v>1892</v>
       </c>
       <c r="B272" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="273" spans="1:3" x14ac:dyDescent="0.25">
@@ -36119,10 +36155,10 @@
         <v>305</v>
       </c>
       <c r="B273" t="s">
+        <v>3236</v>
+      </c>
+      <c r="C273" t="s">
         <v>3237</v>
-      </c>
-      <c r="C273" t="s">
-        <v>3238</v>
       </c>
     </row>
     <row r="274" spans="1:3" x14ac:dyDescent="0.25">
@@ -36135,10 +36171,10 @@
     </row>
     <row r="275" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B275" t="s">
         <v>3239</v>
-      </c>
-      <c r="B275" t="s">
-        <v>3240</v>
       </c>
     </row>
     <row r="276" spans="1:3" x14ac:dyDescent="0.25">
@@ -36157,7 +36193,7 @@
         <v>899</v>
       </c>
       <c r="B277" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="278" spans="1:3" x14ac:dyDescent="0.25">
@@ -36173,7 +36209,7 @@
         <v>1027</v>
       </c>
       <c r="B279" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="280" spans="1:3" x14ac:dyDescent="0.25">
@@ -36197,10 +36233,10 @@
         <v>847</v>
       </c>
       <c r="B282" t="s">
+        <v>3242</v>
+      </c>
+      <c r="C282" t="s">
         <v>3243</v>
-      </c>
-      <c r="C282" t="s">
-        <v>3244</v>
       </c>
     </row>
     <row r="283" spans="1:3" x14ac:dyDescent="0.25">
@@ -36232,10 +36268,10 @@
     </row>
     <row r="286" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
+        <v>3244</v>
+      </c>
+      <c r="B286" t="s">
         <v>3245</v>
-      </c>
-      <c r="B286" t="s">
-        <v>3246</v>
       </c>
     </row>
     <row r="287" spans="1:3" x14ac:dyDescent="0.25">
@@ -36259,10 +36295,10 @@
     </row>
     <row r="289" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
+        <v>3246</v>
+      </c>
+      <c r="B289" t="s">
         <v>3247</v>
-      </c>
-      <c r="B289" t="s">
-        <v>3248</v>
       </c>
     </row>
     <row r="290" spans="1:3" x14ac:dyDescent="0.25">
@@ -36270,10 +36306,10 @@
         <v>169</v>
       </c>
       <c r="B290" t="s">
+        <v>3248</v>
+      </c>
+      <c r="C290" t="s">
         <v>3249</v>
-      </c>
-      <c r="C290" t="s">
-        <v>3250</v>
       </c>
     </row>
     <row r="291" spans="1:3" x14ac:dyDescent="0.25">
@@ -36286,10 +36322,10 @@
     </row>
     <row r="292" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B292" t="s">
         <v>3251</v>
-      </c>
-      <c r="B292" t="s">
-        <v>3252</v>
       </c>
     </row>
     <row r="293" spans="1:3" x14ac:dyDescent="0.25">
@@ -36305,21 +36341,21 @@
         <v>995</v>
       </c>
       <c r="B294" t="s">
+        <v>3252</v>
+      </c>
+      <c r="C294" t="s">
         <v>3253</v>
-      </c>
-      <c r="C294" t="s">
-        <v>3254</v>
       </c>
     </row>
     <row r="295" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
+        <v>3254</v>
+      </c>
+      <c r="B295" t="s">
         <v>3255</v>
       </c>
-      <c r="B295" t="s">
+      <c r="C295" t="s">
         <v>3256</v>
-      </c>
-      <c r="C295" t="s">
-        <v>3257</v>
       </c>
     </row>
     <row r="296" spans="1:3" x14ac:dyDescent="0.25">
@@ -36327,7 +36363,7 @@
         <v>781</v>
       </c>
       <c r="B296" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="297" spans="1:3" x14ac:dyDescent="0.25">
@@ -36335,7 +36371,7 @@
         <v>2040</v>
       </c>
       <c r="B297" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="298" spans="1:3" x14ac:dyDescent="0.25">
@@ -36367,21 +36403,21 @@
     </row>
     <row r="301" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B301" t="s">
         <v>3258</v>
-      </c>
-      <c r="B301" t="s">
-        <v>3259</v>
       </c>
     </row>
     <row r="302" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
+        <v>3259</v>
+      </c>
+      <c r="B302" t="s">
         <v>3260</v>
       </c>
-      <c r="B302" t="s">
+      <c r="C302" t="s">
         <v>3261</v>
-      </c>
-      <c r="C302" t="s">
-        <v>3262</v>
       </c>
     </row>
     <row r="303" spans="1:3" x14ac:dyDescent="0.25">
@@ -36405,10 +36441,10 @@
     </row>
     <row r="305" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B305" t="s">
         <v>3263</v>
-      </c>
-      <c r="B305" t="s">
-        <v>3264</v>
       </c>
     </row>
     <row r="306" spans="1:3" x14ac:dyDescent="0.25">
@@ -36499,10 +36535,10 @@
     </row>
     <row r="316" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="B316" t="s">
-        <v>3265</v>
+        <v>3264</v>
       </c>
     </row>
     <row r="317" spans="1:3" x14ac:dyDescent="0.25">
@@ -36518,7 +36554,7 @@
         <v>2096</v>
       </c>
       <c r="B318" t="s">
-        <v>3266</v>
+        <v>3265</v>
       </c>
     </row>
     <row r="319" spans="1:3" x14ac:dyDescent="0.25">
@@ -36547,10 +36583,10 @@
     </row>
     <row r="322" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
+        <v>3266</v>
+      </c>
+      <c r="B322" t="s">
         <v>3267</v>
-      </c>
-      <c r="B322" t="s">
-        <v>3268</v>
       </c>
     </row>
     <row r="323" spans="1:2" x14ac:dyDescent="0.25">
@@ -36571,18 +36607,18 @@
     </row>
     <row r="325" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
+        <v>3268</v>
+      </c>
+      <c r="B325" t="s">
         <v>3269</v>
-      </c>
-      <c r="B325" t="s">
-        <v>3270</v>
       </c>
     </row>
     <row r="326" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
-        <v>3271</v>
+        <v>3270</v>
       </c>
       <c r="B326" t="s">
-        <v>3270</v>
+        <v>3269</v>
       </c>
     </row>
     <row r="327" spans="1:2" x14ac:dyDescent="0.25">
@@ -36595,34 +36631,34 @@
     </row>
     <row r="328" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
+        <v>3271</v>
+      </c>
+      <c r="B328" t="s">
         <v>3272</v>
-      </c>
-      <c r="B328" t="s">
-        <v>3273</v>
       </c>
     </row>
     <row r="329" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
+        <v>3273</v>
+      </c>
+      <c r="B329" t="s">
         <v>3274</v>
-      </c>
-      <c r="B329" t="s">
-        <v>3275</v>
       </c>
     </row>
     <row r="330" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B330" t="s">
         <v>2985</v>
-      </c>
-      <c r="B330" t="s">
-        <v>2986</v>
       </c>
     </row>
     <row r="331" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
+        <v>3275</v>
+      </c>
+      <c r="B331" t="s">
         <v>3276</v>
-      </c>
-      <c r="B331" t="s">
-        <v>3277</v>
       </c>
     </row>
     <row r="332" spans="1:2" x14ac:dyDescent="0.25">
@@ -36667,10 +36703,10 @@
     </row>
     <row r="337" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
+        <v>3277</v>
+      </c>
+      <c r="B337" t="s">
         <v>3278</v>
-      </c>
-      <c r="B337" t="s">
-        <v>3279</v>
       </c>
     </row>
     <row r="338" spans="1:3" x14ac:dyDescent="0.25">
@@ -36694,7 +36730,7 @@
         <v>920</v>
       </c>
       <c r="B340" t="s">
-        <v>3280</v>
+        <v>3279</v>
       </c>
     </row>
     <row r="341" spans="1:3" x14ac:dyDescent="0.25">
@@ -36737,7 +36773,7 @@
         <v>1783</v>
       </c>
       <c r="B345" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="346" spans="1:3" x14ac:dyDescent="0.25">
@@ -36750,34 +36786,34 @@
     </row>
     <row r="347" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
+        <v>3281</v>
+      </c>
+      <c r="B347" t="s">
         <v>3282</v>
-      </c>
-      <c r="B347" t="s">
-        <v>3283</v>
       </c>
     </row>
     <row r="348" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
+        <v>3283</v>
+      </c>
+      <c r="B348" t="s">
         <v>3284</v>
-      </c>
-      <c r="B348" t="s">
-        <v>3285</v>
       </c>
     </row>
     <row r="349" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>3285</v>
+      </c>
+      <c r="B349" t="s">
         <v>3286</v>
-      </c>
-      <c r="B349" t="s">
-        <v>3287</v>
       </c>
     </row>
     <row r="350" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
+        <v>2991</v>
+      </c>
+      <c r="B350" t="s">
         <v>2992</v>
-      </c>
-      <c r="B350" t="s">
-        <v>2993</v>
       </c>
     </row>
     <row r="351" spans="1:3" x14ac:dyDescent="0.25">
@@ -36814,10 +36850,10 @@
         <v>468</v>
       </c>
       <c r="B355" t="s">
+        <v>3287</v>
+      </c>
+      <c r="C355" t="s">
         <v>3288</v>
-      </c>
-      <c r="C355" t="s">
-        <v>3289</v>
       </c>
     </row>
     <row r="356" spans="1:3" x14ac:dyDescent="0.25">
@@ -36833,10 +36869,10 @@
     </row>
     <row r="357" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
+        <v>3289</v>
+      </c>
+      <c r="B357" t="s">
         <v>3290</v>
-      </c>
-      <c r="B357" t="s">
-        <v>3291</v>
       </c>
     </row>
     <row r="358" spans="1:3" x14ac:dyDescent="0.25">
@@ -36844,21 +36880,21 @@
         <v>596</v>
       </c>
       <c r="B358" t="s">
+        <v>3291</v>
+      </c>
+      <c r="C358" t="s">
         <v>3292</v>
-      </c>
-      <c r="C358" t="s">
-        <v>3293</v>
       </c>
     </row>
     <row r="359" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
+        <v>3293</v>
+      </c>
+      <c r="B359" t="s">
         <v>3294</v>
       </c>
-      <c r="B359" t="s">
+      <c r="C359" t="s">
         <v>3295</v>
-      </c>
-      <c r="C359" t="s">
-        <v>3296</v>
       </c>
     </row>
     <row r="360" spans="1:3" x14ac:dyDescent="0.25">
@@ -36882,10 +36918,10 @@
     </row>
     <row r="362" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
+        <v>3296</v>
+      </c>
+      <c r="B362" t="s">
         <v>3297</v>
-      </c>
-      <c r="B362" t="s">
-        <v>3298</v>
       </c>
     </row>
     <row r="363" spans="1:3" x14ac:dyDescent="0.25">
@@ -36963,29 +36999,29 @@
     </row>
     <row r="371" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B371" t="s">
         <v>3299</v>
-      </c>
-      <c r="B371" t="s">
-        <v>3300</v>
       </c>
     </row>
     <row r="372" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
+        <v>3300</v>
+      </c>
+      <c r="B372" t="s">
         <v>3301</v>
-      </c>
-      <c r="B372" t="s">
-        <v>3302</v>
       </c>
     </row>
     <row r="373" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
+        <v>3302</v>
+      </c>
+      <c r="B373" t="s">
         <v>3303</v>
       </c>
-      <c r="B373" t="s">
+      <c r="C373" t="s">
         <v>3304</v>
-      </c>
-      <c r="C373" t="s">
-        <v>3305</v>
       </c>
     </row>
     <row r="374" spans="1:3" x14ac:dyDescent="0.25">
@@ -36993,7 +37029,7 @@
         <v>195</v>
       </c>
       <c r="B374" t="s">
-        <v>3306</v>
+        <v>3305</v>
       </c>
     </row>
     <row r="375" spans="1:3" x14ac:dyDescent="0.25">
@@ -37014,21 +37050,21 @@
     </row>
     <row r="377" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B377" t="s">
         <v>3307</v>
-      </c>
-      <c r="B377" t="s">
-        <v>3308</v>
       </c>
     </row>
     <row r="378" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
+        <v>3308</v>
+      </c>
+      <c r="B378" t="s">
         <v>3309</v>
       </c>
-      <c r="B378" t="s">
+      <c r="C378" t="s">
         <v>3310</v>
-      </c>
-      <c r="C378" t="s">
-        <v>3311</v>
       </c>
     </row>
     <row r="379" spans="1:3" x14ac:dyDescent="0.25">
@@ -37090,7 +37126,7 @@
         <v>468</v>
       </c>
       <c r="B385" t="s">
-        <v>3312</v>
+        <v>3311</v>
       </c>
     </row>
     <row r="386" spans="1:3" x14ac:dyDescent="0.25">
@@ -37098,7 +37134,7 @@
         <v>468</v>
       </c>
       <c r="B386" t="s">
-        <v>3313</v>
+        <v>3312</v>
       </c>
     </row>
     <row r="387" spans="1:3" x14ac:dyDescent="0.25">
@@ -37122,7 +37158,7 @@
         <v>195</v>
       </c>
       <c r="B389" t="s">
-        <v>3314</v>
+        <v>3313</v>
       </c>
     </row>
     <row r="390" spans="1:3" x14ac:dyDescent="0.25">
@@ -37171,7 +37207,7 @@
         <v>71</v>
       </c>
       <c r="B394" t="s">
-        <v>3315</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="395" spans="1:3" x14ac:dyDescent="0.25">
@@ -37214,10 +37250,10 @@
         <v>451</v>
       </c>
       <c r="B399" t="s">
+        <v>3315</v>
+      </c>
+      <c r="C399" t="s">
         <v>3316</v>
-      </c>
-      <c r="C399" t="s">
-        <v>3317</v>
       </c>
     </row>
     <row r="400" spans="1:3" x14ac:dyDescent="0.25">
@@ -37289,13 +37325,13 @@
     </row>
     <row r="408" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B408" t="s">
         <v>3318</v>
       </c>
-      <c r="B408" t="s">
+      <c r="C408" t="s">
         <v>3319</v>
-      </c>
-      <c r="C408" t="s">
-        <v>3320</v>
       </c>
     </row>
     <row r="409" spans="1:3" x14ac:dyDescent="0.25">
@@ -37303,10 +37339,10 @@
         <v>392</v>
       </c>
       <c r="B409" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
       <c r="C409" t="s">
-        <v>3321</v>
+        <v>3320</v>
       </c>
     </row>
     <row r="410" spans="1:3" x14ac:dyDescent="0.25">
@@ -37392,7 +37428,7 @@
         <v>1328</v>
       </c>
       <c r="B419" t="s">
-        <v>3322</v>
+        <v>3321</v>
       </c>
     </row>
     <row r="420" spans="1:3" x14ac:dyDescent="0.25">
@@ -37400,15 +37436,15 @@
         <v>260</v>
       </c>
       <c r="B420" t="s">
+        <v>3322</v>
+      </c>
+      <c r="C420" t="s">
         <v>3323</v>
-      </c>
-      <c r="C420" t="s">
-        <v>3324</v>
       </c>
     </row>
     <row r="421" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B421" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="422" spans="1:3" x14ac:dyDescent="0.25">
@@ -37483,21 +37519,21 @@
     </row>
     <row r="430" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
+        <v>3325</v>
+      </c>
+      <c r="B430" t="s">
         <v>3326</v>
-      </c>
-      <c r="B430" t="s">
-        <v>3327</v>
       </c>
     </row>
     <row r="431" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
-        <v>3326</v>
+        <v>3325</v>
       </c>
       <c r="B431" t="s">
+        <v>3327</v>
+      </c>
+      <c r="C431" t="s">
         <v>3328</v>
-      </c>
-      <c r="C431" t="s">
-        <v>3329</v>
       </c>
     </row>
     <row r="432" spans="1:3" x14ac:dyDescent="0.25">
@@ -37510,13 +37546,13 @@
     </row>
     <row r="433" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
+        <v>3329</v>
+      </c>
+      <c r="B433" t="s">
         <v>3330</v>
       </c>
-      <c r="B433" t="s">
+      <c r="C433" t="s">
         <v>3331</v>
-      </c>
-      <c r="C433" t="s">
-        <v>3332</v>
       </c>
     </row>
     <row r="434" spans="1:3" x14ac:dyDescent="0.25">
@@ -37532,7 +37568,7 @@
     </row>
     <row r="435" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B435" t="s">
         <v>2116</v>
@@ -37551,10 +37587,10 @@
     </row>
     <row r="437" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
+        <v>3332</v>
+      </c>
+      <c r="B437" t="s">
         <v>3333</v>
-      </c>
-      <c r="B437" t="s">
-        <v>3334</v>
       </c>
     </row>
     <row r="438" spans="1:3" x14ac:dyDescent="0.25">
@@ -37575,13 +37611,13 @@
     </row>
     <row r="440" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B440" t="s">
         <v>3335</v>
       </c>
-      <c r="B440" t="s">
+      <c r="C440" t="s">
         <v>3336</v>
-      </c>
-      <c r="C440" t="s">
-        <v>3337</v>
       </c>
     </row>
     <row r="441" spans="1:3" x14ac:dyDescent="0.25">
@@ -37594,10 +37630,10 @@
     </row>
     <row r="442" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B442" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="443" spans="1:3" x14ac:dyDescent="0.25">
@@ -37691,7 +37727,7 @@
     </row>
     <row r="453" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="B453" t="s">
         <v>2183</v>
@@ -37718,7 +37754,7 @@
         <v>1320</v>
       </c>
       <c r="B456" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="457" spans="1:3" x14ac:dyDescent="0.25">
@@ -37742,21 +37778,21 @@
     </row>
     <row r="459" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
+        <v>3340</v>
+      </c>
+      <c r="B459" t="s">
         <v>3341</v>
-      </c>
-      <c r="B459" t="s">
-        <v>3342</v>
       </c>
     </row>
     <row r="460" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
+        <v>3342</v>
+      </c>
+      <c r="B460" t="s">
         <v>3343</v>
       </c>
-      <c r="B460" t="s">
+      <c r="C460" t="s">
         <v>3344</v>
-      </c>
-      <c r="C460" t="s">
-        <v>3345</v>
       </c>
     </row>
     <row r="461" spans="1:3" x14ac:dyDescent="0.25">
@@ -37767,7 +37803,7 @@
         <v>2211</v>
       </c>
       <c r="C461" t="s">
-        <v>3346</v>
+        <v>3345</v>
       </c>
     </row>
     <row r="462" spans="1:3" x14ac:dyDescent="0.25">
@@ -37786,7 +37822,7 @@
         <v>451</v>
       </c>
       <c r="B463" t="s">
-        <v>3347</v>
+        <v>3346</v>
       </c>
     </row>
     <row r="464" spans="1:3" x14ac:dyDescent="0.25">
@@ -37802,18 +37838,18 @@
     </row>
     <row r="465" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
+        <v>3347</v>
+      </c>
+      <c r="B465" t="s">
         <v>3348</v>
-      </c>
-      <c r="B465" t="s">
-        <v>3349</v>
       </c>
     </row>
     <row r="466" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
+        <v>3349</v>
+      </c>
+      <c r="B466" t="s">
         <v>3350</v>
-      </c>
-      <c r="B466" t="s">
-        <v>3351</v>
       </c>
     </row>
     <row r="467" spans="1:3" x14ac:dyDescent="0.25">
@@ -37829,7 +37865,7 @@
         <v>2125</v>
       </c>
       <c r="B468" t="s">
-        <v>3352</v>
+        <v>3351</v>
       </c>
     </row>
     <row r="469" spans="1:3" x14ac:dyDescent="0.25">
@@ -37842,7 +37878,7 @@
     </row>
     <row r="470" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="B470" t="s">
         <v>2224</v>
@@ -37861,7 +37897,7 @@
         <v>1328</v>
       </c>
       <c r="B472" t="s">
-        <v>3354</v>
+        <v>3353</v>
       </c>
     </row>
     <row r="473" spans="1:3" x14ac:dyDescent="0.25">
@@ -37890,10 +37926,10 @@
     </row>
     <row r="476" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B476" t="s">
         <v>3355</v>
-      </c>
-      <c r="B476" t="s">
-        <v>3356</v>
       </c>
     </row>
     <row r="477" spans="1:3" x14ac:dyDescent="0.25">
@@ -37917,13 +37953,13 @@
     </row>
     <row r="479" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B479" t="s">
         <v>3357</v>
       </c>
-      <c r="B479" t="s">
+      <c r="C479" t="s">
         <v>3358</v>
-      </c>
-      <c r="C479" t="s">
-        <v>3359</v>
       </c>
     </row>
     <row r="480" spans="1:3" x14ac:dyDescent="0.25">
@@ -37931,15 +37967,15 @@
         <v>603</v>
       </c>
       <c r="B480" t="s">
-        <v>3360</v>
+        <v>3359</v>
       </c>
     </row>
     <row r="481" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
+        <v>3360</v>
+      </c>
+      <c r="B481" t="s">
         <v>3361</v>
-      </c>
-      <c r="B481" t="s">
-        <v>3362</v>
       </c>
     </row>
     <row r="482" spans="1:3" x14ac:dyDescent="0.25">
@@ -38014,10 +38050,10 @@
     </row>
     <row r="490" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
+        <v>3362</v>
+      </c>
+      <c r="B490" t="s">
         <v>3363</v>
-      </c>
-      <c r="B490" t="s">
-        <v>3364</v>
       </c>
     </row>
     <row r="491" spans="1:3" x14ac:dyDescent="0.25">
@@ -38065,7 +38101,7 @@
         <v>1104</v>
       </c>
       <c r="B496" t="s">
-        <v>3365</v>
+        <v>3364</v>
       </c>
     </row>
     <row r="497" spans="1:3" x14ac:dyDescent="0.25">
@@ -38073,10 +38109,10 @@
         <v>1501</v>
       </c>
       <c r="B497" t="s">
+        <v>3365</v>
+      </c>
+      <c r="C497" t="s">
         <v>3366</v>
-      </c>
-      <c r="C497" t="s">
-        <v>3367</v>
       </c>
     </row>
     <row r="498" spans="1:3" x14ac:dyDescent="0.25">
@@ -38116,29 +38152,29 @@
         <v>451</v>
       </c>
       <c r="B502" t="s">
+        <v>3367</v>
+      </c>
+      <c r="C502" t="s">
         <v>3368</v>
-      </c>
-      <c r="C502" t="s">
-        <v>3369</v>
       </c>
     </row>
     <row r="503" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
+        <v>3369</v>
+      </c>
+      <c r="B503" t="s">
         <v>3370</v>
       </c>
-      <c r="B503" t="s">
+      <c r="C503" t="s">
         <v>3371</v>
-      </c>
-      <c r="C503" t="s">
-        <v>3372</v>
       </c>
     </row>
     <row r="504" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="B504" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="505" spans="1:3" x14ac:dyDescent="0.25">
@@ -38159,10 +38195,10 @@
     </row>
     <row r="507" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
-        <v>3299</v>
+        <v>3298</v>
       </c>
       <c r="B507" t="s">
-        <v>3374</v>
+        <v>3373</v>
       </c>
     </row>
     <row r="508" spans="1:3" x14ac:dyDescent="0.25">
@@ -38224,7 +38260,7 @@
         <v>1141</v>
       </c>
       <c r="B514" t="s">
-        <v>3375</v>
+        <v>3374</v>
       </c>
     </row>
     <row r="515" spans="1:3" x14ac:dyDescent="0.25">
@@ -38232,10 +38268,10 @@
         <v>1195</v>
       </c>
       <c r="B515" t="s">
+        <v>3375</v>
+      </c>
+      <c r="C515" t="s">
         <v>3376</v>
-      </c>
-      <c r="C515" t="s">
-        <v>3377</v>
       </c>
     </row>
     <row r="516" spans="1:3" x14ac:dyDescent="0.25">
@@ -38243,21 +38279,21 @@
         <v>353</v>
       </c>
       <c r="B516" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
       <c r="C516" t="s">
-        <v>3378</v>
+        <v>3377</v>
       </c>
     </row>
     <row r="517" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
+        <v>3378</v>
+      </c>
+      <c r="B517" t="s">
+        <v>3375</v>
+      </c>
+      <c r="C517" t="s">
         <v>3379</v>
-      </c>
-      <c r="B517" t="s">
-        <v>3376</v>
-      </c>
-      <c r="C517" t="s">
-        <v>3380</v>
       </c>
     </row>
     <row r="518" spans="1:3" x14ac:dyDescent="0.25">
@@ -38273,10 +38309,10 @@
         <v>669</v>
       </c>
       <c r="B519" t="s">
+        <v>3380</v>
+      </c>
+      <c r="C519" t="s">
         <v>3381</v>
-      </c>
-      <c r="C519" t="s">
-        <v>3382</v>
       </c>
     </row>
     <row r="520" spans="1:3" x14ac:dyDescent="0.25">
@@ -38324,10 +38360,10 @@
     </row>
     <row r="525" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
+        <v>3382</v>
+      </c>
+      <c r="B525" t="s">
         <v>3383</v>
-      </c>
-      <c r="B525" t="s">
-        <v>3384</v>
       </c>
     </row>
     <row r="526" spans="1:3" x14ac:dyDescent="0.25">
@@ -38357,7 +38393,7 @@
         <v>451</v>
       </c>
       <c r="B528" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="529" spans="1:3" x14ac:dyDescent="0.25">
@@ -38370,10 +38406,10 @@
     </row>
     <row r="530" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B530" t="s">
         <v>3386</v>
-      </c>
-      <c r="B530" t="s">
-        <v>3387</v>
       </c>
     </row>
     <row r="531" spans="1:3" x14ac:dyDescent="0.25">
@@ -38381,7 +38417,7 @@
         <v>252</v>
       </c>
       <c r="B531" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="532" spans="1:3" x14ac:dyDescent="0.25">
@@ -38394,13 +38430,13 @@
     </row>
     <row r="533" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
-        <v>3214</v>
+        <v>3213</v>
       </c>
       <c r="B533" t="s">
+        <v>3388</v>
+      </c>
+      <c r="C533" t="s">
         <v>3389</v>
-      </c>
-      <c r="C533" t="s">
-        <v>3390</v>
       </c>
     </row>
     <row r="534" spans="1:3" x14ac:dyDescent="0.25">
@@ -38416,7 +38452,7 @@
         <v>451</v>
       </c>
       <c r="B535" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="536" spans="1:3" x14ac:dyDescent="0.25">
@@ -38462,10 +38498,10 @@
         <v>2423</v>
       </c>
       <c r="B540" t="s">
+        <v>3391</v>
+      </c>
+      <c r="C540" t="s">
         <v>3392</v>
-      </c>
-      <c r="C540" t="s">
-        <v>3393</v>
       </c>
     </row>
     <row r="541" spans="1:3" x14ac:dyDescent="0.25">
@@ -38524,7 +38560,7 @@
         <v>1711</v>
       </c>
       <c r="B547" t="s">
-        <v>3394</v>
+        <v>3393</v>
       </c>
     </row>
     <row r="548" spans="1:3" x14ac:dyDescent="0.25">
@@ -38540,7 +38576,7 @@
         <v>211</v>
       </c>
       <c r="B549" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="550" spans="1:3" x14ac:dyDescent="0.25">
@@ -38548,7 +38584,7 @@
         <v>195</v>
       </c>
       <c r="B550" t="s">
-        <v>3396</v>
+        <v>3395</v>
       </c>
     </row>
     <row r="551" spans="1:3" x14ac:dyDescent="0.25">
@@ -38556,10 +38592,10 @@
         <v>1948</v>
       </c>
       <c r="B551" t="s">
+        <v>3396</v>
+      </c>
+      <c r="C551" t="s">
         <v>3397</v>
-      </c>
-      <c r="C551" t="s">
-        <v>3398</v>
       </c>
     </row>
     <row r="552" spans="1:3" x14ac:dyDescent="0.25">
@@ -38629,10 +38665,10 @@
     </row>
     <row r="559" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="B559" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="560" spans="1:3" x14ac:dyDescent="0.25">
@@ -38724,13 +38760,13 @@
     </row>
     <row r="569" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
+        <v>3399</v>
+      </c>
+      <c r="B569" t="s">
         <v>3400</v>
       </c>
-      <c r="B569" t="s">
+      <c r="C569" t="s">
         <v>3401</v>
-      </c>
-      <c r="C569" t="s">
-        <v>3402</v>
       </c>
     </row>
     <row r="570" spans="1:3" x14ac:dyDescent="0.25">
@@ -38743,10 +38779,10 @@
     </row>
     <row r="571" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
+        <v>3402</v>
+      </c>
+      <c r="B571" t="s">
         <v>3403</v>
-      </c>
-      <c r="B571" t="s">
-        <v>3404</v>
       </c>
     </row>
     <row r="572" spans="1:3" x14ac:dyDescent="0.25">
@@ -38754,7 +38790,7 @@
         <v>1135</v>
       </c>
       <c r="B572" t="s">
-        <v>3404</v>
+        <v>3403</v>
       </c>
     </row>
     <row r="573" spans="1:3" x14ac:dyDescent="0.25">
@@ -38786,7 +38822,7 @@
         <v>1451</v>
       </c>
       <c r="B576" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="577" spans="1:3" x14ac:dyDescent="0.25">
@@ -38824,7 +38860,7 @@
         <v>1027</v>
       </c>
       <c r="B580" t="s">
-        <v>3406</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="581" spans="1:3" x14ac:dyDescent="0.25">
@@ -38937,10 +38973,10 @@
     </row>
     <row r="593" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A593" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B593" t="s">
-        <v>3407</v>
+        <v>3406</v>
       </c>
     </row>
     <row r="594" spans="1:3" x14ac:dyDescent="0.25">
@@ -38956,7 +38992,7 @@
         <v>400</v>
       </c>
       <c r="B595" t="s">
-        <v>3408</v>
+        <v>3407</v>
       </c>
     </row>
     <row r="596" spans="1:3" x14ac:dyDescent="0.25">
@@ -39021,10 +39057,10 @@
     </row>
     <row r="602" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A602" t="s">
-        <v>3204</v>
+        <v>3203</v>
       </c>
       <c r="B602" t="s">
-        <v>3409</v>
+        <v>3408</v>
       </c>
     </row>
     <row r="603" spans="1:3" x14ac:dyDescent="0.25">
@@ -39048,10 +39084,10 @@
     </row>
     <row r="605" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A605" t="s">
+        <v>3409</v>
+      </c>
+      <c r="B605" t="s">
         <v>3410</v>
-      </c>
-      <c r="B605" t="s">
-        <v>3411</v>
       </c>
     </row>
     <row r="606" spans="1:3" x14ac:dyDescent="0.25">
@@ -39067,13 +39103,13 @@
     </row>
     <row r="607" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A607" t="s">
+        <v>3411</v>
+      </c>
+      <c r="B607" t="s">
         <v>3412</v>
       </c>
-      <c r="B607" t="s">
+      <c r="C607" t="s">
         <v>3413</v>
-      </c>
-      <c r="C607" t="s">
-        <v>3414</v>
       </c>
     </row>
     <row r="608" spans="1:3" x14ac:dyDescent="0.25">
@@ -39089,7 +39125,7 @@
         <v>1788</v>
       </c>
       <c r="B609" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="610" spans="1:3" x14ac:dyDescent="0.25">
@@ -39121,18 +39157,18 @@
     </row>
     <row r="613" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A613" t="s">
+        <v>3415</v>
+      </c>
+      <c r="B613" t="s">
         <v>3416</v>
-      </c>
-      <c r="B613" t="s">
-        <v>3417</v>
       </c>
     </row>
     <row r="614" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A614" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B614" t="s">
         <v>3418</v>
-      </c>
-      <c r="B614" t="s">
-        <v>3419</v>
       </c>
     </row>
     <row r="615" spans="1:3" x14ac:dyDescent="0.25">
@@ -39161,13 +39197,13 @@
     </row>
     <row r="618" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A618" t="s">
-        <v>3420</v>
+        <v>3419</v>
       </c>
       <c r="B618" t="s">
         <v>1161</v>
       </c>
       <c r="C618" t="s">
-        <v>3421</v>
+        <v>3420</v>
       </c>
     </row>
     <row r="619" spans="1:3" x14ac:dyDescent="0.25">
@@ -39207,13 +39243,13 @@
     </row>
     <row r="623" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A623" t="s">
+        <v>3421</v>
+      </c>
+      <c r="B623" t="s">
         <v>3422</v>
       </c>
-      <c r="B623" t="s">
+      <c r="C623" t="s">
         <v>3423</v>
-      </c>
-      <c r="C623" t="s">
-        <v>3424</v>
       </c>
     </row>
     <row r="624" spans="1:3" x14ac:dyDescent="0.25">
@@ -39237,7 +39273,7 @@
         <v>847</v>
       </c>
       <c r="B626" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="627" spans="1:3" x14ac:dyDescent="0.25">
@@ -39253,15 +39289,15 @@
         <v>534</v>
       </c>
       <c r="B628" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="629" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A629" t="s">
-        <v>3276</v>
+        <v>3275</v>
       </c>
       <c r="B629" t="s">
-        <v>3427</v>
+        <v>3426</v>
       </c>
     </row>
     <row r="630" spans="1:3" x14ac:dyDescent="0.25">
@@ -39288,15 +39324,15 @@
         <v>688</v>
       </c>
       <c r="B632" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="633" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A633" t="s">
+        <v>3428</v>
+      </c>
+      <c r="B633" t="s">
         <v>3429</v>
-      </c>
-      <c r="B633" t="s">
-        <v>3430</v>
       </c>
     </row>
     <row r="634" spans="1:3" x14ac:dyDescent="0.25">
@@ -39352,7 +39388,7 @@
         <v>596</v>
       </c>
       <c r="B640" t="s">
-        <v>3431</v>
+        <v>3430</v>
       </c>
     </row>
     <row r="641" spans="1:3" x14ac:dyDescent="0.25">
@@ -39365,13 +39401,13 @@
     </row>
     <row r="642" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A642" t="s">
+        <v>3431</v>
+      </c>
+      <c r="B642" t="s">
         <v>3432</v>
       </c>
-      <c r="B642" t="s">
+      <c r="C642" t="s">
         <v>3433</v>
-      </c>
-      <c r="C642" t="s">
-        <v>3434</v>
       </c>
     </row>
     <row r="643" spans="1:3" x14ac:dyDescent="0.25">
@@ -39387,7 +39423,7 @@
         <v>795</v>
       </c>
       <c r="B644" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="645" spans="1:3" x14ac:dyDescent="0.25">
@@ -39408,10 +39444,10 @@
     </row>
     <row r="647" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A647" t="s">
+        <v>3435</v>
+      </c>
+      <c r="B647" t="s">
         <v>3436</v>
-      </c>
-      <c r="B647" t="s">
-        <v>3437</v>
       </c>
     </row>
     <row r="648" spans="1:3" x14ac:dyDescent="0.25">
@@ -39427,7 +39463,7 @@
         <v>1756</v>
       </c>
       <c r="B649" t="s">
-        <v>3438</v>
+        <v>3437</v>
       </c>
     </row>
     <row r="650" spans="1:3" x14ac:dyDescent="0.25">
@@ -39443,7 +39479,7 @@
         <v>146</v>
       </c>
       <c r="B651" t="s">
-        <v>3439</v>
+        <v>3438</v>
       </c>
     </row>
     <row r="652" spans="1:3" x14ac:dyDescent="0.25">
@@ -39569,7 +39605,7 @@
         <v>1916</v>
       </c>
       <c r="B666" t="s">
-        <v>3440</v>
+        <v>3439</v>
       </c>
     </row>
     <row r="667" spans="1:3" x14ac:dyDescent="0.25">
@@ -39631,18 +39667,18 @@
         <v>567</v>
       </c>
       <c r="B673" t="s">
+        <v>3440</v>
+      </c>
+      <c r="C673" t="s">
         <v>3441</v>
-      </c>
-      <c r="C673" t="s">
-        <v>3442</v>
       </c>
     </row>
     <row r="674" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A674" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B674" t="s">
         <v>3443</v>
-      </c>
-      <c r="B674" t="s">
-        <v>3444</v>
       </c>
     </row>
     <row r="675" spans="1:3" x14ac:dyDescent="0.25">
@@ -39693,10 +39729,10 @@
     </row>
     <row r="680" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A680" t="s">
+        <v>3444</v>
+      </c>
+      <c r="B680" t="s">
         <v>3445</v>
-      </c>
-      <c r="B680" t="s">
-        <v>3446</v>
       </c>
     </row>
     <row r="681" spans="1:3" x14ac:dyDescent="0.25">
@@ -39712,13 +39748,13 @@
     </row>
     <row r="682" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A682" t="s">
+        <v>3446</v>
+      </c>
+      <c r="B682" t="s">
         <v>3447</v>
       </c>
-      <c r="B682" t="s">
+      <c r="C682" t="s">
         <v>3448</v>
-      </c>
-      <c r="C682" t="s">
-        <v>3449</v>
       </c>
     </row>
     <row r="683" spans="1:3" x14ac:dyDescent="0.25">
@@ -39726,10 +39762,10 @@
         <v>1501</v>
       </c>
       <c r="B683" t="s">
+        <v>3449</v>
+      </c>
+      <c r="C683" t="s">
         <v>3450</v>
-      </c>
-      <c r="C683" t="s">
-        <v>3451</v>
       </c>
     </row>
     <row r="684" spans="1:3" x14ac:dyDescent="0.25">
@@ -39737,18 +39773,18 @@
         <v>71</v>
       </c>
       <c r="B684" t="s">
+        <v>2966</v>
+      </c>
+      <c r="C684" t="s">
         <v>2967</v>
-      </c>
-      <c r="C684" t="s">
-        <v>2968</v>
       </c>
     </row>
     <row r="685" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A685" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B685" t="s">
         <v>2970</v>
-      </c>
-      <c r="B685" t="s">
-        <v>2971</v>
       </c>
     </row>
     <row r="686" spans="1:3" x14ac:dyDescent="0.25">
@@ -39756,7 +39792,7 @@
         <v>669</v>
       </c>
       <c r="B686" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="687" spans="1:3" x14ac:dyDescent="0.25">
@@ -39764,7 +39800,7 @@
         <v>107</v>
       </c>
       <c r="B687" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="688" spans="1:3" x14ac:dyDescent="0.25">
@@ -39780,7 +39816,7 @@
         <v>2096</v>
       </c>
       <c r="B689" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="690" spans="1:3" x14ac:dyDescent="0.25">
@@ -39796,10 +39832,10 @@
     </row>
     <row r="691" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A691" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B691" t="s">
         <v>3006</v>
-      </c>
-      <c r="B691" t="s">
-        <v>3007</v>
       </c>
     </row>
     <row r="692" spans="1:3" x14ac:dyDescent="0.25">
@@ -39807,7 +39843,7 @@
         <v>2066</v>
       </c>
       <c r="B692" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="693" spans="1:3" x14ac:dyDescent="0.25">
@@ -39815,15 +39851,15 @@
         <v>451</v>
       </c>
       <c r="B693" t="s">
-        <v>3452</v>
+        <v>3451</v>
       </c>
     </row>
     <row r="694" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A694" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B694" t="s">
         <v>3017</v>
-      </c>
-      <c r="B694" t="s">
-        <v>3018</v>
       </c>
     </row>
     <row r="695" spans="1:3" x14ac:dyDescent="0.25">
@@ -39831,69 +39867,69 @@
         <v>1783</v>
       </c>
       <c r="B695" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
       <c r="C695" t="s">
-        <v>3026</v>
+        <v>3025</v>
       </c>
     </row>
     <row r="696" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A696" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B696" t="s">
         <v>2997</v>
-      </c>
-      <c r="B696" t="s">
-        <v>2998</v>
       </c>
     </row>
     <row r="697" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A697" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B697" t="s">
         <v>3030</v>
-      </c>
-      <c r="B697" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="698" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A698" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B698" t="s">
         <v>3036</v>
-      </c>
-      <c r="B698" t="s">
-        <v>3037</v>
       </c>
     </row>
     <row r="699" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A699" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B699" t="s">
         <v>3042</v>
       </c>
-      <c r="B699" t="s">
-        <v>3043</v>
-      </c>
       <c r="C699" t="s">
-        <v>3046</v>
+        <v>3045</v>
       </c>
     </row>
     <row r="700" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A700" t="s">
+        <v>3452</v>
+      </c>
+      <c r="B700" t="s">
         <v>3453</v>
-      </c>
-      <c r="B700" t="s">
-        <v>3454</v>
       </c>
     </row>
     <row r="701" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A701" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B701" t="s">
         <v>3049</v>
-      </c>
-      <c r="B701" t="s">
-        <v>3050</v>
       </c>
     </row>
     <row r="702" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A702" t="s">
+        <v>3454</v>
+      </c>
+      <c r="B702" t="s">
         <v>3455</v>
-      </c>
-      <c r="B702" t="s">
-        <v>3456</v>
       </c>
     </row>
     <row r="703" spans="1:3" x14ac:dyDescent="0.25">
@@ -39901,15 +39937,15 @@
         <v>2282</v>
       </c>
       <c r="B703" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="704" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A704" t="s">
-        <v>3457</v>
+        <v>3456</v>
       </c>
       <c r="B704" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="705" spans="1:2" x14ac:dyDescent="0.25">
@@ -39917,7 +39953,7 @@
         <v>1379</v>
       </c>
       <c r="B705" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="706" spans="1:2" x14ac:dyDescent="0.25">
@@ -39925,23 +39961,23 @@
         <v>305</v>
       </c>
       <c r="B706" t="s">
-        <v>3069</v>
+        <v>3068</v>
       </c>
     </row>
     <row r="707" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A707" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B707" t="s">
         <v>3458</v>
-      </c>
-      <c r="B707" t="s">
-        <v>3459</v>
       </c>
     </row>
     <row r="708" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A708" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B708" t="s">
         <v>3074</v>
-      </c>
-      <c r="B708" t="s">
-        <v>3075</v>
       </c>
     </row>
     <row r="709" spans="1:2" x14ac:dyDescent="0.25">
@@ -39954,10 +39990,10 @@
     </row>
     <row r="710" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A710" t="s">
+        <v>3459</v>
+      </c>
+      <c r="B710" t="s">
         <v>3460</v>
-      </c>
-      <c r="B710" t="s">
-        <v>3461</v>
       </c>
     </row>
   </sheetData>
@@ -39985,34 +40021,34 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>3461</v>
+      </c>
+      <c r="D1" t="s">
         <v>3462</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>3463</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>3464</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>3465</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>3466</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>3467</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>3468</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>3469</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>3470</v>
-      </c>
-      <c r="L1" t="s">
-        <v>3471</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40028,12 +40064,12 @@
     </row>
     <row r="3" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3081</v>
+        <v>3080</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>3082</v>
+        <v>3081</v>
       </c>
       <c r="B4" t="s">
         <v>24</v>
@@ -40074,13 +40110,13 @@
     </row>
     <row r="8" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>3082</v>
+      </c>
+      <c r="B8" t="s">
         <v>3083</v>
       </c>
-      <c r="B8" t="s">
-        <v>3084</v>
-      </c>
       <c r="C8" s="10" t="s">
-        <v>3472</v>
+        <v>3471</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40143,7 +40179,7 @@
         <v>353</v>
       </c>
       <c r="B14" t="s">
-        <v>3085</v>
+        <v>3084</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40208,32 +40244,32 @@
     </row>
     <row r="21" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>3086</v>
+      </c>
+      <c r="B21" t="s">
         <v>3087</v>
       </c>
-      <c r="B21" t="s">
-        <v>3088</v>
-      </c>
       <c r="C21" s="2" t="s">
-        <v>3473</v>
+        <v>3472</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>3088</v>
+      </c>
+      <c r="B22" t="s">
         <v>3089</v>
-      </c>
-      <c r="B22" t="s">
-        <v>3090</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>3091</v>
+      </c>
+      <c r="B23" t="s">
         <v>3092</v>
       </c>
-      <c r="B23" t="s">
-        <v>3093</v>
-      </c>
       <c r="C23" s="10" t="s">
-        <v>3474</v>
+        <v>3473</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40293,7 +40329,7 @@
         <v>353</v>
       </c>
       <c r="B29" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
     </row>
     <row r="30" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40312,10 +40348,10 @@
         <v>211</v>
       </c>
       <c r="B31" t="s">
-        <v>3101</v>
+        <v>3100</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>3475</v>
+        <v>3474</v>
       </c>
     </row>
     <row r="32" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40364,13 +40400,13 @@
     </row>
     <row r="36" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
+        <v>3103</v>
+      </c>
+      <c r="B36" t="s">
         <v>3104</v>
       </c>
-      <c r="B36" t="s">
-        <v>3105</v>
-      </c>
       <c r="C36" s="10" t="s">
-        <v>3476</v>
+        <v>3475</v>
       </c>
     </row>
     <row r="37" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40419,10 +40455,10 @@
     </row>
     <row r="41" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
+        <v>3105</v>
+      </c>
+      <c r="B41" t="s">
         <v>3106</v>
-      </c>
-      <c r="B41" t="s">
-        <v>3107</v>
       </c>
     </row>
     <row r="42" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40485,7 +40521,7 @@
         <v>1289</v>
       </c>
       <c r="B47" t="s">
-        <v>3111</v>
+        <v>3110</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40575,13 +40611,13 @@
     </row>
     <row r="56" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
+        <v>3114</v>
+      </c>
+      <c r="B56" t="s">
         <v>3115</v>
       </c>
-      <c r="B56" t="s">
-        <v>3116</v>
-      </c>
       <c r="C56" s="10" t="s">
-        <v>3477</v>
+        <v>3476</v>
       </c>
     </row>
     <row r="57" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40611,7 +40647,7 @@
         <v>377</v>
       </c>
       <c r="C59" s="10" t="s">
-        <v>3478</v>
+        <v>3477</v>
       </c>
     </row>
     <row r="60" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40633,7 +40669,7 @@
         <v>385</v>
       </c>
       <c r="C61" s="10" t="s">
-        <v>3479</v>
+        <v>3478</v>
       </c>
     </row>
     <row r="62" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40735,18 +40771,18 @@
         <v>457</v>
       </c>
       <c r="D70" t="s">
-        <v>3480</v>
+        <v>3479</v>
       </c>
     </row>
     <row r="71" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>3126</v>
+      </c>
+      <c r="B71" t="s">
         <v>3127</v>
       </c>
-      <c r="B71" t="s">
-        <v>3128</v>
-      </c>
       <c r="C71" s="10" t="s">
-        <v>3481</v>
+        <v>3480</v>
       </c>
     </row>
     <row r="72" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40825,10 +40861,10 @@
     </row>
     <row r="79" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
+        <v>3129</v>
+      </c>
+      <c r="B79" t="s">
         <v>3130</v>
-      </c>
-      <c r="B79" t="s">
-        <v>3131</v>
       </c>
     </row>
     <row r="80" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40910,7 +40946,7 @@
         <v>451</v>
       </c>
       <c r="B87" t="s">
-        <v>3132</v>
+        <v>3131</v>
       </c>
     </row>
     <row r="88" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40937,10 +40973,10 @@
     </row>
     <row r="90" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>3139</v>
+      </c>
+      <c r="B90" t="s">
         <v>3140</v>
-      </c>
-      <c r="B90" t="s">
-        <v>3141</v>
       </c>
     </row>
     <row r="91" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -40948,7 +40984,7 @@
         <v>567</v>
       </c>
       <c r="B91" t="s">
-        <v>3142</v>
+        <v>3141</v>
       </c>
       <c r="C91" s="10" t="s">
         <v>572</v>
@@ -40992,10 +41028,10 @@
         <v>2901</v>
       </c>
       <c r="B95" t="s">
-        <v>3144</v>
+        <v>3143</v>
       </c>
       <c r="C95" s="10" t="s">
-        <v>3482</v>
+        <v>3481</v>
       </c>
     </row>
     <row r="96" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41011,13 +41047,13 @@
     </row>
     <row r="97" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
+        <v>3144</v>
+      </c>
+      <c r="B97" t="s">
         <v>3145</v>
       </c>
-      <c r="B97" t="s">
-        <v>3146</v>
-      </c>
       <c r="C97" s="10" t="s">
-        <v>3483</v>
+        <v>3482</v>
       </c>
     </row>
     <row r="98" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41077,29 +41113,29 @@
     </row>
     <row r="103" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
+        <v>3150</v>
+      </c>
+      <c r="B103" t="s">
         <v>3151</v>
       </c>
-      <c r="B103" t="s">
-        <v>3152</v>
-      </c>
       <c r="C103" t="s">
-        <v>3484</v>
+        <v>3483</v>
       </c>
     </row>
     <row r="104" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
+        <v>3152</v>
+      </c>
+      <c r="B104" t="s">
         <v>3153</v>
-      </c>
-      <c r="B104" t="s">
-        <v>3154</v>
       </c>
     </row>
     <row r="105" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
+        <v>3157</v>
+      </c>
+      <c r="B105" t="s">
         <v>3158</v>
-      </c>
-      <c r="B105" t="s">
-        <v>3159</v>
       </c>
       <c r="C105" s="10"/>
     </row>
@@ -41299,10 +41335,10 @@
     </row>
     <row r="124" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
-        <v>3171</v>
+        <v>3170</v>
       </c>
       <c r="C124" s="10" t="s">
-        <v>3485</v>
+        <v>3484</v>
       </c>
     </row>
     <row r="125" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41310,18 +41346,18 @@
         <v>1195</v>
       </c>
       <c r="B125" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
       <c r="C125" t="s">
-        <v>3486</v>
+        <v>3485</v>
       </c>
     </row>
     <row r="126" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>3174</v>
+        <v>3173</v>
       </c>
       <c r="B126" t="s">
-        <v>3172</v>
+        <v>3171</v>
       </c>
     </row>
     <row r="127" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41408,7 +41444,7 @@
         <v>829</v>
       </c>
       <c r="D134" t="s">
-        <v>3493</v>
+        <v>3492</v>
       </c>
     </row>
     <row r="135" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41416,7 +41452,7 @@
         <v>451</v>
       </c>
       <c r="B135" t="s">
-        <v>3179</v>
+        <v>3178</v>
       </c>
       <c r="C135" s="10"/>
     </row>
@@ -41632,7 +41668,7 @@
         <v>360</v>
       </c>
       <c r="B156" t="s">
-        <v>3188</v>
+        <v>3187</v>
       </c>
       <c r="C156" s="10"/>
     </row>
@@ -41740,7 +41776,7 @@
         <v>2779</v>
       </c>
       <c r="B166" t="s">
-        <v>3190</v>
+        <v>3189</v>
       </c>
       <c r="C166" s="10"/>
     </row>
@@ -41813,10 +41849,10 @@
         <v>853</v>
       </c>
       <c r="B173" t="s">
-        <v>3197</v>
+        <v>3196</v>
       </c>
       <c r="C173" s="10" t="s">
-        <v>3487</v>
+        <v>3486</v>
       </c>
     </row>
     <row r="174" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41846,10 +41882,10 @@
         <v>643</v>
       </c>
       <c r="B176" t="s">
-        <v>3198</v>
+        <v>3197</v>
       </c>
       <c r="C176" s="10" t="s">
-        <v>3488</v>
+        <v>3487</v>
       </c>
     </row>
     <row r="177" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -41877,18 +41913,18 @@
         <v>732</v>
       </c>
       <c r="B179" t="s">
-        <v>3203</v>
+        <v>3202</v>
       </c>
       <c r="C179" t="s">
-        <v>3489</v>
+        <v>3488</v>
       </c>
     </row>
     <row r="180" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>3183</v>
+        <v>3182</v>
       </c>
       <c r="B180" t="s">
-        <v>3206</v>
+        <v>3205</v>
       </c>
       <c r="C180" s="10"/>
     </row>
@@ -41982,10 +42018,10 @@
     </row>
     <row r="189" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
+        <v>3213</v>
+      </c>
+      <c r="B189" t="s">
         <v>3214</v>
-      </c>
-      <c r="B189" t="s">
-        <v>3215</v>
       </c>
       <c r="C189" s="10"/>
     </row>
@@ -42060,7 +42096,7 @@
         <v>1451</v>
       </c>
       <c r="B196" t="s">
-        <v>3216</v>
+        <v>3215</v>
       </c>
     </row>
     <row r="197" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42085,10 +42121,10 @@
     </row>
     <row r="199" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
+        <v>3218</v>
+      </c>
+      <c r="B199" t="s">
         <v>3219</v>
-      </c>
-      <c r="B199" t="s">
-        <v>3220</v>
       </c>
       <c r="C199" s="10"/>
     </row>
@@ -42116,10 +42152,10 @@
     </row>
     <row r="202" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
+        <v>3220</v>
+      </c>
+      <c r="B202" t="s">
         <v>3221</v>
-      </c>
-      <c r="B202" t="s">
-        <v>3222</v>
       </c>
       <c r="C202" s="10"/>
     </row>
@@ -42163,7 +42199,7 @@
         <v>1195</v>
       </c>
       <c r="B207" t="s">
-        <v>3223</v>
+        <v>3222</v>
       </c>
     </row>
     <row r="208" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42248,10 +42284,10 @@
     </row>
     <row r="218" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
+        <v>3230</v>
+      </c>
+      <c r="B218" t="s">
         <v>3231</v>
-      </c>
-      <c r="B218" t="s">
-        <v>3232</v>
       </c>
     </row>
     <row r="219" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42264,10 +42300,10 @@
     </row>
     <row r="220" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
+        <v>3233</v>
+      </c>
+      <c r="B220" t="s">
         <v>3234</v>
-      </c>
-      <c r="B220" t="s">
-        <v>3235</v>
       </c>
     </row>
     <row r="221" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42299,7 +42335,7 @@
         <v>1892</v>
       </c>
       <c r="B224" t="s">
-        <v>3236</v>
+        <v>3235</v>
       </c>
     </row>
     <row r="225" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42312,10 +42348,10 @@
     </row>
     <row r="226" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
+        <v>3238</v>
+      </c>
+      <c r="B226" t="s">
         <v>3239</v>
-      </c>
-      <c r="B226" t="s">
-        <v>3240</v>
       </c>
     </row>
     <row r="227" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42331,7 +42367,7 @@
         <v>899</v>
       </c>
       <c r="B228" t="s">
-        <v>3241</v>
+        <v>3240</v>
       </c>
     </row>
     <row r="229" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42347,7 +42383,7 @@
         <v>1027</v>
       </c>
       <c r="B230" t="s">
-        <v>3242</v>
+        <v>3241</v>
       </c>
     </row>
     <row r="231" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42411,7 +42447,7 @@
         <v>169</v>
       </c>
       <c r="B238" t="s">
-        <v>3249</v>
+        <v>3248</v>
       </c>
     </row>
     <row r="239" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42424,10 +42460,10 @@
     </row>
     <row r="240" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
+        <v>3250</v>
+      </c>
+      <c r="B240" t="s">
         <v>3251</v>
-      </c>
-      <c r="B240" t="s">
-        <v>3252</v>
       </c>
     </row>
     <row r="241" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42443,7 +42479,7 @@
         <v>781</v>
       </c>
       <c r="B242" t="s">
-        <v>3256</v>
+        <v>3255</v>
       </c>
     </row>
     <row r="243" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42472,10 +42508,10 @@
     </row>
     <row r="246" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
+        <v>3257</v>
+      </c>
+      <c r="B246" t="s">
         <v>3258</v>
-      </c>
-      <c r="B246" t="s">
-        <v>3259</v>
       </c>
     </row>
     <row r="247" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42496,10 +42532,10 @@
     </row>
     <row r="249" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
+        <v>3262</v>
+      </c>
+      <c r="B249" t="s">
         <v>3263</v>
-      </c>
-      <c r="B249" t="s">
-        <v>3264</v>
       </c>
     </row>
     <row r="250" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42638,10 +42674,10 @@
     </row>
     <row r="266" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
+        <v>2984</v>
+      </c>
+      <c r="B266" t="s">
         <v>2985</v>
-      </c>
-      <c r="B266" t="s">
-        <v>2986</v>
       </c>
     </row>
     <row r="267" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42737,7 +42773,7 @@
         <v>1783</v>
       </c>
       <c r="B278" t="s">
-        <v>3281</v>
+        <v>3280</v>
       </c>
     </row>
     <row r="279" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42750,10 +42786,10 @@
     </row>
     <row r="280" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
+        <v>2991</v>
+      </c>
+      <c r="B280" t="s">
         <v>2992</v>
-      </c>
-      <c r="B280" t="s">
-        <v>2993</v>
       </c>
     </row>
     <row r="281" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -42820,7 +42856,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="289" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>162</v>
       </c>
@@ -42828,7 +42864,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="290" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1839</v>
       </c>
@@ -42836,7 +42872,7 @@
         <v>1840</v>
       </c>
     </row>
-    <row r="291" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1846</v>
       </c>
@@ -42844,7 +42880,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="292" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>732</v>
       </c>
@@ -42852,20 +42888,18 @@
         <v>1853</v>
       </c>
     </row>
-    <row r="293" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1859</v>
       </c>
       <c r="B293" t="s">
         <v>1860</v>
       </c>
-      <c r="D293" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Klimt en 1914</t>
-        </is>
-      </c>
-    </row>
-    <row r="294" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D293" t="s">
+        <v>3499</v>
+      </c>
+    </row>
+    <row r="294" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>52</v>
       </c>
@@ -42873,7 +42907,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="295" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1865</v>
       </c>
@@ -42881,23 +42915,23 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="296" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
+        <v>3298</v>
+      </c>
+      <c r="B296" t="s">
         <v>3299</v>
       </c>
-      <c r="B296" t="s">
+    </row>
+    <row r="297" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A297" t="s">
         <v>3300</v>
       </c>
-    </row>
-    <row r="297" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
+      <c r="B297" t="s">
         <v>3301</v>
       </c>
-      <c r="B297" t="s">
-        <v>3302</v>
-      </c>
-    </row>
-    <row r="298" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1871</v>
       </c>
@@ -42905,7 +42939,7 @@
         <v>1872</v>
       </c>
     </row>
-    <row r="299" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1877</v>
       </c>
@@ -42913,23 +42947,23 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="300" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
+        <v>3306</v>
+      </c>
+      <c r="B300" t="s">
         <v>3307</v>
       </c>
-      <c r="B300" t="s">
+    </row>
+    <row r="301" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
         <v>3308</v>
       </c>
-    </row>
-    <row r="301" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A301" t="s">
+      <c r="B301" t="s">
         <v>3309</v>
       </c>
-      <c r="B301" t="s">
-        <v>3310</v>
-      </c>
-    </row>
-    <row r="302" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>847</v>
       </c>
@@ -42937,7 +42971,7 @@
         <v>1885</v>
       </c>
     </row>
-    <row r="303" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1892</v>
       </c>
@@ -42945,7 +42979,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="304" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>847</v>
       </c>
@@ -43062,7 +43096,7 @@
         <v>451</v>
       </c>
       <c r="B318" t="s">
-        <v>3316</v>
+        <v>3315</v>
       </c>
     </row>
     <row r="319" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43131,10 +43165,10 @@
     </row>
     <row r="327" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
+        <v>3317</v>
+      </c>
+      <c r="B327" t="s">
         <v>3318</v>
-      </c>
-      <c r="B327" t="s">
-        <v>3319</v>
       </c>
     </row>
     <row r="328" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43142,7 +43176,7 @@
         <v>392</v>
       </c>
       <c r="B328" t="s">
-        <v>3319</v>
+        <v>3318</v>
       </c>
     </row>
     <row r="329" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43222,12 +43256,12 @@
         <v>260</v>
       </c>
       <c r="B338" t="s">
-        <v>3323</v>
+        <v>3322</v>
       </c>
     </row>
     <row r="339" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
-        <v>3325</v>
+        <v>3324</v>
       </c>
     </row>
     <row r="340" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43311,10 +43345,10 @@
     </row>
     <row r="349" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
+        <v>3329</v>
+      </c>
+      <c r="B349" t="s">
         <v>3330</v>
-      </c>
-      <c r="B349" t="s">
-        <v>3331</v>
       </c>
     </row>
     <row r="350" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43327,7 +43361,7 @@
     </row>
     <row r="351" spans="1:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
-        <v>3156</v>
+        <v>3155</v>
       </c>
       <c r="B351" t="s">
         <v>2116</v>
@@ -43359,10 +43393,10 @@
     </row>
     <row r="355" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
+        <v>3334</v>
+      </c>
+      <c r="B355" t="s">
         <v>3335</v>
-      </c>
-      <c r="B355" t="s">
-        <v>3336</v>
       </c>
     </row>
     <row r="356" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43375,10 +43409,10 @@
     </row>
     <row r="357" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
-        <v>3185</v>
+        <v>3184</v>
       </c>
       <c r="B357" t="s">
-        <v>3338</v>
+        <v>3337</v>
       </c>
     </row>
     <row r="358" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43463,7 +43497,7 @@
     </row>
     <row r="368" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
-        <v>3339</v>
+        <v>3338</v>
       </c>
       <c r="B368" t="s">
         <v>2183</v>
@@ -43490,7 +43524,7 @@
         <v>1320</v>
       </c>
       <c r="B371" t="s">
-        <v>3340</v>
+        <v>3339</v>
       </c>
     </row>
     <row r="372" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43551,7 +43585,7 @@
     </row>
     <row r="379" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
-        <v>3353</v>
+        <v>3352</v>
       </c>
       <c r="B379" t="s">
         <v>2224</v>
@@ -43591,10 +43625,10 @@
     </row>
     <row r="384" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
+        <v>3354</v>
+      </c>
+      <c r="B384" t="s">
         <v>3355</v>
-      </c>
-      <c r="B384" t="s">
-        <v>3356</v>
       </c>
     </row>
     <row r="385" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43615,10 +43649,10 @@
     </row>
     <row r="387" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
+        <v>3356</v>
+      </c>
+      <c r="B387" t="s">
         <v>3357</v>
-      </c>
-      <c r="B387" t="s">
-        <v>3358</v>
       </c>
     </row>
     <row r="388" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43730,7 +43764,7 @@
         <v>1501</v>
       </c>
       <c r="B401" t="s">
-        <v>3366</v>
+        <v>3365</v>
       </c>
     </row>
     <row r="402" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43770,15 +43804,15 @@
         <v>451</v>
       </c>
       <c r="B406" t="s">
-        <v>3368</v>
+        <v>3367</v>
       </c>
     </row>
     <row r="407" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
-        <v>3228</v>
+        <v>3227</v>
       </c>
       <c r="B407" t="s">
-        <v>3373</v>
+        <v>3372</v>
       </c>
     </row>
     <row r="408" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43850,7 +43884,7 @@
         <v>1195</v>
       </c>
       <c r="B416" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="417" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43858,15 +43892,15 @@
         <v>353</v>
       </c>
       <c r="B417" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="418" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
-        <v>3379</v>
+        <v>3378</v>
       </c>
       <c r="B418" t="s">
-        <v>3376</v>
+        <v>3375</v>
       </c>
     </row>
     <row r="419" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43938,7 +43972,7 @@
         <v>451</v>
       </c>
       <c r="B427" t="s">
-        <v>3385</v>
+        <v>3384</v>
       </c>
     </row>
     <row r="428" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43951,10 +43985,10 @@
     </row>
     <row r="429" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
+        <v>3385</v>
+      </c>
+      <c r="B429" t="s">
         <v>3386</v>
-      </c>
-      <c r="B429" t="s">
-        <v>3387</v>
       </c>
     </row>
     <row r="430" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43962,7 +43996,7 @@
         <v>252</v>
       </c>
       <c r="B430" t="s">
-        <v>3388</v>
+        <v>3387</v>
       </c>
     </row>
     <row r="431" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -43986,7 +44020,7 @@
         <v>451</v>
       </c>
       <c r="B433" t="s">
-        <v>3391</v>
+        <v>3390</v>
       </c>
     </row>
     <row r="434" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44082,7 +44116,7 @@
         <v>211</v>
       </c>
       <c r="B445" t="s">
-        <v>3395</v>
+        <v>3394</v>
       </c>
     </row>
     <row r="446" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44090,7 +44124,7 @@
         <v>1948</v>
       </c>
       <c r="B446" t="s">
-        <v>3397</v>
+        <v>3396</v>
       </c>
     </row>
     <row r="447" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44151,10 +44185,10 @@
     </row>
     <row r="454" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
-        <v>3104</v>
+        <v>3103</v>
       </c>
       <c r="B454" t="s">
-        <v>3399</v>
+        <v>3398</v>
       </c>
     </row>
     <row r="455" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44231,10 +44265,10 @@
     </row>
     <row r="464" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
+        <v>3399</v>
+      </c>
+      <c r="B464" t="s">
         <v>3400</v>
-      </c>
-      <c r="B464" t="s">
-        <v>3401</v>
       </c>
     </row>
     <row r="465" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44274,7 +44308,7 @@
         <v>1451</v>
       </c>
       <c r="B469" t="s">
-        <v>3405</v>
+        <v>3404</v>
       </c>
     </row>
     <row r="470" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44490,7 +44524,7 @@
         <v>1788</v>
       </c>
       <c r="B496" t="s">
-        <v>3415</v>
+        <v>3414</v>
       </c>
     </row>
     <row r="497" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44519,10 +44553,10 @@
     </row>
     <row r="500" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
+        <v>3417</v>
+      </c>
+      <c r="B500" t="s">
         <v>3418</v>
-      </c>
-      <c r="B500" t="s">
-        <v>3419</v>
       </c>
     </row>
     <row r="501" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44583,10 +44617,10 @@
     </row>
     <row r="508" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
+        <v>3421</v>
+      </c>
+      <c r="B508" t="s">
         <v>3422</v>
-      </c>
-      <c r="B508" t="s">
-        <v>3423</v>
       </c>
     </row>
     <row r="509" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44610,7 +44644,7 @@
         <v>847</v>
       </c>
       <c r="B511" t="s">
-        <v>3425</v>
+        <v>3424</v>
       </c>
     </row>
     <row r="512" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44626,7 +44660,7 @@
         <v>534</v>
       </c>
       <c r="B513" t="s">
-        <v>3426</v>
+        <v>3425</v>
       </c>
     </row>
     <row r="514" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44650,7 +44684,7 @@
         <v>688</v>
       </c>
       <c r="B516" t="s">
-        <v>3428</v>
+        <v>3427</v>
       </c>
     </row>
     <row r="517" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44722,7 +44756,7 @@
         <v>795</v>
       </c>
       <c r="B525" t="s">
-        <v>3435</v>
+        <v>3434</v>
       </c>
     </row>
     <row r="526" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -44885,7 +44919,7 @@
         <v>2923</v>
       </c>
     </row>
-    <row r="545" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="545" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>154</v>
       </c>
@@ -44893,7 +44927,7 @@
         <v>2927</v>
       </c>
     </row>
-    <row r="546" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="546" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>1027</v>
       </c>
@@ -44901,7 +44935,7 @@
         <v>2932</v>
       </c>
     </row>
-    <row r="547" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="547" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>1160</v>
       </c>
@@ -44909,7 +44943,7 @@
         <v>2937</v>
       </c>
     </row>
-    <row r="548" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="548" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>795</v>
       </c>
@@ -44917,7 +44951,7 @@
         <v>2833</v>
       </c>
     </row>
-    <row r="549" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>305</v>
       </c>
@@ -44925,7 +44959,7 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="550" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>2785</v>
       </c>
@@ -44933,23 +44967,23 @@
         <v>2941</v>
       </c>
     </row>
-    <row r="551" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="551" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>567</v>
       </c>
       <c r="B551" t="s">
-        <v>3441</v>
-      </c>
-    </row>
-    <row r="552" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3440</v>
+      </c>
+    </row>
+    <row r="552" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
+        <v>3442</v>
+      </c>
+      <c r="B552" t="s">
         <v>3443</v>
       </c>
-      <c r="B552" t="s">
-        <v>3444</v>
-      </c>
-    </row>
-    <row r="553" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="553" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>2946</v>
       </c>
@@ -44957,7 +44991,7 @@
         <v>2947</v>
       </c>
     </row>
-    <row r="554" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="554" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>2951</v>
       </c>
@@ -44965,7 +44999,7 @@
         <v>2952</v>
       </c>
     </row>
-    <row r="555" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="555" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>2785</v>
       </c>
@@ -44973,7 +45007,7 @@
         <v>2956</v>
       </c>
     </row>
-    <row r="556" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="556" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>1195</v>
       </c>
@@ -44981,28 +45015,26 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="557" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="557" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>2961</v>
       </c>
       <c r="B557" t="s">
         <v>2962</v>
       </c>
-      <c r="D557" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Autoportait, 1790</t>
-        </is>
-      </c>
-    </row>
-    <row r="558" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D557" t="s">
+        <v>3500</v>
+      </c>
+    </row>
+    <row r="558" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
+        <v>3444</v>
+      </c>
+      <c r="B558" t="s">
         <v>3445</v>
       </c>
-      <c r="B558" t="s">
-        <v>3446</v>
-      </c>
-    </row>
-    <row r="559" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="559" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>1170</v>
       </c>
@@ -45010,20 +45042,20 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="560" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="560" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>71</v>
       </c>
       <c r="B560" t="s">
-        <v>2967</v>
+        <v>2966</v>
       </c>
     </row>
     <row r="561" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
+        <v>2969</v>
+      </c>
+      <c r="B561" t="s">
         <v>2970</v>
-      </c>
-      <c r="B561" t="s">
-        <v>2971</v>
       </c>
     </row>
     <row r="562" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45031,7 +45063,7 @@
         <v>669</v>
       </c>
       <c r="B562" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="563" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45039,7 +45071,7 @@
         <v>107</v>
       </c>
       <c r="B563" t="s">
-        <v>2971</v>
+        <v>2970</v>
       </c>
     </row>
     <row r="564" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45055,7 +45087,7 @@
         <v>2096</v>
       </c>
       <c r="B565" t="s">
-        <v>3002</v>
+        <v>3001</v>
       </c>
     </row>
     <row r="566" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45068,10 +45100,10 @@
     </row>
     <row r="567" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
+        <v>3005</v>
+      </c>
+      <c r="B567" t="s">
         <v>3006</v>
-      </c>
-      <c r="B567" t="s">
-        <v>3007</v>
       </c>
     </row>
     <row r="568" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45079,15 +45111,15 @@
         <v>2066</v>
       </c>
       <c r="B568" t="s">
-        <v>3012</v>
+        <v>3011</v>
       </c>
     </row>
     <row r="569" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
+        <v>3016</v>
+      </c>
+      <c r="B569" t="s">
         <v>3017</v>
-      </c>
-      <c r="B569" t="s">
-        <v>3018</v>
       </c>
     </row>
     <row r="570" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45095,63 +45127,63 @@
         <v>1783</v>
       </c>
       <c r="B570" t="s">
-        <v>3024</v>
+        <v>3023</v>
       </c>
     </row>
     <row r="571" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
+        <v>2996</v>
+      </c>
+      <c r="B571" t="s">
         <v>2997</v>
-      </c>
-      <c r="B571" t="s">
-        <v>2998</v>
       </c>
     </row>
     <row r="572" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
+        <v>3029</v>
+      </c>
+      <c r="B572" t="s">
         <v>3030</v>
-      </c>
-      <c r="B572" t="s">
-        <v>3031</v>
       </c>
     </row>
     <row r="573" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
+        <v>3035</v>
+      </c>
+      <c r="B573" t="s">
         <v>3036</v>
-      </c>
-      <c r="B573" t="s">
-        <v>3037</v>
       </c>
     </row>
     <row r="574" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
+        <v>3041</v>
+      </c>
+      <c r="B574" t="s">
         <v>3042</v>
-      </c>
-      <c r="B574" t="s">
-        <v>3043</v>
       </c>
     </row>
     <row r="575" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
+        <v>3452</v>
+      </c>
+      <c r="B575" t="s">
         <v>3453</v>
-      </c>
-      <c r="B575" t="s">
-        <v>3454</v>
       </c>
     </row>
     <row r="576" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
+        <v>3048</v>
+      </c>
+      <c r="B576" t="s">
         <v>3049</v>
-      </c>
-      <c r="B576" t="s">
-        <v>3050</v>
       </c>
     </row>
     <row r="577" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
+        <v>3454</v>
+      </c>
+      <c r="B577" t="s">
         <v>3455</v>
-      </c>
-      <c r="B577" t="s">
-        <v>3456</v>
       </c>
     </row>
     <row r="578" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45159,7 +45191,7 @@
         <v>2282</v>
       </c>
       <c r="B578" t="s">
-        <v>3055</v>
+        <v>3054</v>
       </c>
     </row>
     <row r="579" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -45167,26 +45199,26 @@
         <v>1379</v>
       </c>
       <c r="B579" t="s">
-        <v>3063</v>
+        <v>3062</v>
       </c>
     </row>
     <row r="580" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
+        <v>3457</v>
+      </c>
+      <c r="B580" t="s">
         <v>3458</v>
-      </c>
-      <c r="B580" t="s">
-        <v>3459</v>
       </c>
     </row>
     <row r="581" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
+        <v>3073</v>
+      </c>
+      <c r="B581" t="s">
         <v>3074</v>
       </c>
-      <c r="B581" t="s">
-        <v>3075</v>
-      </c>
       <c r="C581" t="s">
-        <v>3078</v>
+        <v>3077</v>
       </c>
     </row>
     <row r="582" spans="1:4" x14ac:dyDescent="0.25">
@@ -45199,10 +45231,10 @@
     </row>
     <row r="583" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
+        <v>3459</v>
+      </c>
+      <c r="B583" t="s">
         <v>3460</v>
-      </c>
-      <c r="B583" t="s">
-        <v>3461</v>
       </c>
     </row>
     <row r="584" spans="1:4" x14ac:dyDescent="0.25">
@@ -45213,7 +45245,7 @@
         <v>652</v>
       </c>
       <c r="D584" t="s">
-        <v>3494</v>
+        <v>3493</v>
       </c>
     </row>
   </sheetData>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD7340BE-4FC1-4B1C-8779-EA09039026EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DB174C3-0A07-443E-B41B-D799225793DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13198,9 +13198,6 @@
     <t>Autoportait, 1790</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Portrett_av_Edvard_Munch.jpg/960px-Portrett_av_Edvard_Munch.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
-  </si>
-  <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/b1/Portrait_of_Henri_Matisse_1933_May_20.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled&amp;uselang=fr</t>
   </si>
   <si>
@@ -13211,6 +13208,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/f/fd/Rousseau_Joyeux_Farceurs_Dornac.jpg?utm_source=fr.wikipedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4a/Edvard_Munch_1933-2.jpg/960px-Edvard_Munch_1933-2.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -16976,8 +16976,10 @@
       <c r="I81" s="7">
         <v>2</v>
       </c>
-      <c r="S81" s="1" t="s">
-        <v>3490</v>
+      <c r="S81" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né vers 1375 à Valenciennes, [retour | 5]et je me suis établi à Tournai, enclave française dans ce territoire bourguignon, [image: https://mnemart.fr/cartes/foyer-artistique-bourguignon-1430.png |  | 5]si riche en tapissiers, enlumineurs, sculpteurs et peintres. Depuis, leur capitale, Dijon, les ducs de Bourgogne, Jean sans peur, et surtout son fils, Philippe le Bon, ont su créer un foyer artistique exceptionnel. Pour ma part, j'ai obtenu le titre de maître en 1406 qui m'a assuré un statut de chef d'atelier indépendant au sein de la corporation locale des peintres. J'ai eu des élèves de talent : Jacques Daret, et surtout, celui qui a peint le portrait du duc Philippe, Rogier de la Pasture, que vous connaissez sous le nom de Rogier van der Weyden. Il s'installera plus tard et réussira brillamment à Bruxelles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Eyck%2C_Jan_van_-_Portrait_of_a_Man_%28Self_Portrait%3F%29_-_National_Gallery%2C_London.jpg/960px-Eyck%2C_Jan_van_-_Portrait_of_a_Man_%28Self_Portrait%3F%29_-_National_Gallery%2C_London.jpg | Van Eyck Portrait d’un homme 1433 | enchaîné 10]J'ai pu rencontrer aussi Jan van Eyck, venu de Gand ou de Bruges,  lors de ses séjours à Tournai, notre maître à tous, celui que l'histoire retiendra comme le plus doué d'entre nous. Pendant longtemps, on ne m'a pas connu sous mon nom. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Robert_Campin_013.jpg | Portrait d'un homme, 1435 | enchaîné 10]On parlait du Maître de Flémalle, et c'est seulement l'étude des archives qui a permis de rapprocher ce nom du mien. En 1423, en tant qu'artisan fier de sa réussite matérielle, j'ai été l'un des chefs de la révolte des métiers de Tournai contre le pouvoir de l'aristocratie, et je me suis rangé du côté des Français contre le parti bourguignon. J'ai ensuite exercé des fonctions dans le nouveau gouvernement et présidé la corporation des peintres et des orfèvres, mais en 1429 j'ai été condamné à une amende, à un pèlerinage et à l'interdiction de toute charge publique pour avoir pris part à ce soulèvement. [image: https://commons.wikimedia.org/wiki/Special:FilePath/Robert_Campin_-_Triptych_with_the_Annunciation%2C_known_as_the_%22Merode_Altarpiece%22_-_Google_Art_Project.jpg | Le Triptyque de Mérode, 1427-1432 | enchaîné 10]Est-ce pour cela que mon Triptyque de Mérode montre l'Annonciation dans un intérieur bourgeois ordinaire ? Loin des palais princiers, on y voit un banc, une cheminée, une bougie qui vient de s'éteindre, et dans l'atelier voisin, saint Joseph qui fabrique des pièges à souris. [image: https://upload.wikimedia.org/wikipedia/commons/c/c9/Robert_campin%2C_trinity.jpg | Campin, La Trinité du Corps brisé, 1430 | enchaîné 10]J'ai voulu que le divin entre dans le quotidien. Mes figures ont du poids et du volume, presque comme des sculptures. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Robert_Campin_012.jpg/960px-Robert_Campin_012.jpg | Robert Campin, "Portrait de femme", 1435 | enchaîné 10]Les portraits de bourgeois que je suis un des premiers à avoir peints sont empreints d'une grande dignité. [retour | 5]Je suis  mort à Tournai en 1444.</t>
+        </is>
       </c>
       <c r="T81" s="10" t="s">
         <v>3489</v>
@@ -18030,8 +18032,11 @@
       <c r="I107" s="7">
         <v>3</v>
       </c>
-      <c r="S107" s="1" t="s">
-        <v>3491</v>
+      <c r="S107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né en 1801 à Bolton, dans le Lancashire. À mes dix-sept ans, ma famille a émigré aux États-Unis. J'ai appris à peindre seul, en parcourant les collines et les forêts de l'État de New York.
+[image: https://upload.wikimedia.org/wikipedia/commons/f/fa/Cole_Thomas_Lake_with_Dead_Trees_%28Catskill%29_1825.jpg | Lac aux arbres morts, 1825 | enchaîné 5]À l'été 1825, j'ai exposé dans une vitrine de New York des vues des monts Catskill. Elles ont été remarquées, achetées, admirées. C'était le début de l'école du fleuve [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg | Vue depuis le mont Holyoke, après un orage — The Oxbow., 1836 | enchaîné 10]Hudson, dont on m'a appelé le fondateur. Frédéric Edwin Church, mon ami,  et, plus tard, Albert Bierstadt en ont fait partie. J'ai peint la nature américaine, sauvage et grandiose.  J'ai imaginé aussi des allégories à travers des grands cycles. Le premier, *La Vie humaine*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole_-_The_Voyage_of_Life_Childhood%2C_1842_%28National_Gallery_of_Art%29FXD.jpg | Le Voyage de la vie : L'Enfance, 1842 | enchaîné 10] est une série de quatre tableaux où un voyageur navigue sur une rivière dont les changements évoquent les différentes étapes de l'existence. Le second, *Le Cours de l'Empire*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Architect-s_Dream_1840.jpg | Le Rêve de l'Architecte, 1840 | enchaîné 10] est constitué de cinq tableaux qui décrivent la naissance et le déclin d'une civilisation imaginaire. J'ai voulu mettre en garde mes contemporains [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg/1280px-Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg | Le Cours de l'Empire, La Désolation, 1836 | enchaîné 10] en peignant les ravages possibles sur la Nature et la Civilisation d'une course effrénée vers une société industrielle [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg | Le Départ, 1837 | enchaîné 10]et marchande.  J'ai été un des pionniers du mouvement environnementaliste. Je me suis installé à Catskill, où je suis mort en 1848, à quarante-sept ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Gibbon_River_at_Madison_in_Yellowstone.JPG/1280px-Gibbon_River_at_Madison_in_Yellowstone.JPG | La rivière Gibbon dans le parc de Yellowstone. | enchaîné 10]Mes convictions écologistes ont ouvert la voie à la création des grands parcs nationaux américains comme celui de Yellowstone. Je crois cette voie prometteuse pour [retour | 5]l'avenir de l'Amérique.</t>
+        </is>
       </c>
       <c r="T107" s="1" t="s">
         <v>829</v>
@@ -26322,7 +26327,7 @@
         <v>2113</v>
       </c>
       <c r="T315" s="10" t="s">
-        <v>3502</v>
+        <v>3501</v>
       </c>
       <c r="U315" s="5" t="s">
         <v>2111</v>
@@ -27094,7 +27099,7 @@
         <v>2217</v>
       </c>
       <c r="T335" s="10" t="s">
-        <v>3504</v>
+        <v>3503</v>
       </c>
       <c r="U335" s="5" t="s">
         <v>2215</v>
@@ -27359,11 +27364,13 @@
       <c r="I342" s="7">
         <v>1</v>
       </c>
-      <c r="S342" s="1" t="s">
-        <v>2253</v>
+      <c r="S342" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né en 1863 à Loten, en Norvège. [retour | 5]Mon père, médecin militaire, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/be/Edvard_Munch_-_Christian_Munch_on_the_Couch_-_MM.M.01048_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Christian_Munch_on_the_Couch_-_MM.M.01048_-_Munch_Museum.jpg | Christian Munch sur le canapé,1881 | 5]était pieux et sombre ; il nous parlait de l'enfer. Ma mère est morte de la tuberculose quand j'avais cinq ans, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Munch_Det_Syke_Barn_1885-86.jpg/1280px-Munch_Det_Syke_Barn_1885-86.jpg | L'Enfant malade, 1885-1886 | enchaîné 10]et ma sœur Sophie, que j'adorais, en est morte à quinze ans. Dans *L'Enfant malade*, que j'ai repris pendant des années, j'ai évoqué cette image traumatisante et obsessionnelle de ma Sophie mourante. La femme et la mort ne faisaient plus qu'un. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Puberty_%281894-95%29_by_Edvard_Munch.jpg/960px-Puberty_%281894-95%29_by_Edvard_Munch.jpg | Puberté, 1894 | enchaîné 10]Dans *Puberté*, une jeune fille nue, assise sur son lit, croise les bras ; derrière elle, son ombre grandit comme une menace qu'elle ne comprend pas encore.. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Edvard_Munch_-_Self-Portrait_-_MM.M.01049_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Self-Portrait_-_MM.M.01049_-_Munch_Museum.jpg | Autoportrait, 1882 | enchaîné 10]Mon père voulait que je sois ingénieur ; j'ai abandonné l'école technique pour la peinture, avec une idée fixe : peindre non pas ce que je voyais mais mes tourments intérieurs. [image: https://upload.wikimedia.org/wikipedia/commons/8/84/Edvard_Munch_-_The_Absinth_Drinkers_-_Woll_217.jpg | Les Buveurs d'absinthe, 1890 | enchaîné 10]En 1885, j'ai décidé de quitter la Norvège et j'ai mené une existence [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Evening_on_Karl_Johan_Street.jpg/1280px-Evening_on_Karl_Johan_Street.jpg | Soirée dans la rue Karl Johan,1892 | enchaîné 10]bohême à Paris et à Berlin. Ma vie était alors un chaos, entre alcool, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Edvard_Munch_-_The_Kiss_-_NG.M.02812_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg/1280px-Edvard_Munch_-_The_Kiss_-_NG.M.02812_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg | Baiser près de la fenêtre, 1892 | enchaîné 10]passions jalouses pour les femmes et peinture. C'est à Berlin qu' en 1892, ma première exposition de tableaux que le public [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e4/Edvard_Munch_Despair_Thielska_286.tif/lossy-page1-960px-Edvard_Munch_Despair_Thielska_286.tif.jpg | Désespoir,1892 | enchaîné 10]a jugés bâclés et anarchistes, a fait scandale. Elle a été interdite, et finalement m'a rendu célèbre!  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Edvard_Munch_-_The_Scream.jpg/960px-Edvard_Munch_-_The_Scream.jpg | Le Cri, 1893 | enchaîné 10]Un soir, sur une colline au-dessus d'Oslo, le ciel est devenu rouge sang: j'ai senti un cri immense traverser la nature. J'ai peint *Le Cri*, et j'ai conçu le grand projet d'une *Frise de la vie* sur l'amour, l'angoisse et la mort. En 1902, une dispute avec Tulla Larsen, qui voulait m'épouser, s'est terminée par un coup de feu : je me suis blessé à la main gauche. Depuis toujours, la femme m'attirait autant qu'elle m'effrayait  Déjà en 1896  [image: https://upload.wikimedia.org/wikipedia/commons/5/5f/Edvard_Munch_-_Madonna_-_Google_Art_Project.jpg | Madonne, 1894 | enchaîné 10]*Madonne* exprimait mon angoisse avec une femme nue, les yeux fermés, dans un halo rouge. L'amour et la fatalité s'y mêlaient inexorablement. En 1908, assailli par mes tourments, je me suis effondré et j'ai pris la décision de me faire interner huit mois dans une clinique de Copenhague. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/960px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg | Le Cri (version de 1910), 1910 | enchaîné 10]Je suis sorti de cette épreuve plus calme et plus lumineux. J'ai repris *Le Cri* en 1910: c'était la même angoisse, mais la forme était plus simple, plus dépouillée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/%22The_Sun%22_by_Edvard_Munch%2C_canvas_mounted_on_wall%2C_at_the_hall_of_ceremonies_at_University_of_Oslo.jpg/1280px-%22The_Sun%22_by_Edvard_Munch%2C_canvas_mounted_on_wall%2C_at_the_hall_of_ceremonies_at_University_of_Oslo.jpg | Le Soleil, 1911 | enchaîné 10]On m'a alors confié la décoration de la grande salle de l'université d'Oslo. Au centre, j'ai figuré un *Le Soleil* qui se levait : plus de cri, mais une énergie de vie, qui inonde tout l'espace, des couleurs lumineuses, des paysages, la vie revenue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bc/Edvard_Munch_-_Galloping_Horse_-_MM.M.00541_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Galloping_Horse_-_MM.M.00541_-_Munch_Museum.jpg | Cheval au galop, 1910-1912 | enchaîné 10]Dans *Cheval au galop*, un cheval fonce droit vers nous : la vie est aussi une force. [image: https://upload.wikimedia.org/wikipedia/commons/8/85/Rekkehus_p%C3%A5_Ekely.jpg | Ekely | enchaîné 10]En 1916, j'ai acheté ma maison d'Ekely, près d'Oslo, où j'ai vécu seul ; je laissais mes toiles dehors, sous la pluie et la neige. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Edvard_Munch_-_Self-Portrait_with_the_Spanish_Flu_-_NG.M.01867_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg/1280px-Edvard_Munch_-_Self-Portrait_with_the_Spanish_Flu_-_NG.M.01867_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg | Autoportrait avec la grippe espagnole, 1919 | enchaîné 10]En 1919, la grippe espagnole m'a frappé et je me suis peint assis, en robe de chambre, le visage jaune. Je m'en suis sorti, comme je me suis en partie guéri de ma maladie mentale, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Jalousi_i_haven.jpg/1280px-Jalousi_i_haven.jpg | Jalousie dans le jardin, 1929-1930 | enchaîné 10]mais un tableau comme *Jalousie dans le jardin* montre que, jusqu'au bout, l'amour et la jalousie m'ont hanté. En 1937, les nazis ont retiré mes tableaux des musées allemands, au nom de l'art dégénéré. [retour | 5]Je suis mort en 1944, pendant l'Occupation. J'ai légué à la ville d'Oslo les 25000 œuvres que j'avais conservées et que je considérais comme mes enfants.</t>
+        </is>
       </c>
       <c r="T342" s="10" t="s">
-        <v>3501</v>
+        <v>3505</v>
       </c>
       <c r="U342" s="5" t="s">
         <v>2251</v>
@@ -29696,7 +29703,7 @@
         <v>2562</v>
       </c>
       <c r="T403" s="10" t="s">
-        <v>3505</v>
+        <v>3504</v>
       </c>
       <c r="U403" s="5" t="s">
         <v>2556</v>
@@ -30234,7 +30241,7 @@
         <v>2630</v>
       </c>
       <c r="T417" s="10" t="s">
-        <v>3503</v>
+        <v>3502</v>
       </c>
       <c r="U417" s="5" t="s">
         <v>2628</v>
@@ -33746,11 +33753,11 @@
     <hyperlink ref="T501" r:id="rId213" xr:uid="{00000000-0004-0000-0000-0000D4000000}"/>
     <hyperlink ref="T81" r:id="rId214" xr:uid="{510BBB2D-DE5F-4FD2-8657-CA730A58D193}"/>
     <hyperlink ref="T480" r:id="rId215" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Self-portrait_%28by_Elisabeth_Vig%C3%A9e-Lebrun%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg/960px-Self-portrait_%28by_Elisabeth_Vig%C3%A9e-Lebrun%29_%E2%80%93_Galleria_degli_Uffizi%2C_Florence.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{FDD44873-E746-4519-B0AF-9B6C0CBC5979}"/>
-    <hyperlink ref="T342" r:id="rId216" xr:uid="{394A8A35-4623-42F8-BC8F-42EFBE766765}"/>
-    <hyperlink ref="T315" r:id="rId217" xr:uid="{25987D31-B8E5-4F13-9BD1-E5D170A25532}"/>
-    <hyperlink ref="T417" r:id="rId218" xr:uid="{E0B6CCDF-3F8A-4F03-B63F-9E00E96FEE94}"/>
-    <hyperlink ref="T335" r:id="rId219" xr:uid="{8AC30FBA-DF83-43EE-B058-49BF3FDF320F}"/>
-    <hyperlink ref="T403" r:id="rId220" xr:uid="{314F00E6-9A0F-40A2-9DF1-6029865709D0}"/>
+    <hyperlink ref="T315" r:id="rId216" xr:uid="{25987D31-B8E5-4F13-9BD1-E5D170A25532}"/>
+    <hyperlink ref="T417" r:id="rId217" xr:uid="{E0B6CCDF-3F8A-4F03-B63F-9E00E96FEE94}"/>
+    <hyperlink ref="T335" r:id="rId218" xr:uid="{8AC30FBA-DF83-43EE-B058-49BF3FDF320F}"/>
+    <hyperlink ref="T403" r:id="rId219" xr:uid="{314F00E6-9A0F-40A2-9DF1-6029865709D0}"/>
+    <hyperlink ref="T342" r:id="rId220" xr:uid="{14CC0579-8AB0-40ED-A1B4-B98E97B3FC93}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -43638,6 +43645,11 @@
       <c r="B385" t="s">
         <v>2251</v>
       </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Edvard Munch en 1933</t>
+        </is>
+      </c>
     </row>
     <row r="386" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -27366,7 +27366,7 @@
       </c>
       <c r="S342" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né en 1863 à Loten, en Norvège. [retour | 5]Mon père, médecin militaire, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/be/Edvard_Munch_-_Christian_Munch_on_the_Couch_-_MM.M.01048_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Christian_Munch_on_the_Couch_-_MM.M.01048_-_Munch_Museum.jpg | Christian Munch sur le canapé,1881 | 5]était pieux et sombre ; il nous parlait de l'enfer. Ma mère est morte de la tuberculose quand j'avais cinq ans, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Munch_Det_Syke_Barn_1885-86.jpg/1280px-Munch_Det_Syke_Barn_1885-86.jpg | L'Enfant malade, 1885-1886 | enchaîné 10]et ma sœur Sophie, que j'adorais, en est morte à quinze ans. Dans *L'Enfant malade*, que j'ai repris pendant des années, j'ai évoqué cette image traumatisante et obsessionnelle de ma Sophie mourante. La femme et la mort ne faisaient plus qu'un. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Puberty_%281894-95%29_by_Edvard_Munch.jpg/960px-Puberty_%281894-95%29_by_Edvard_Munch.jpg | Puberté, 1894 | enchaîné 10]Dans *Puberté*, une jeune fille nue, assise sur son lit, croise les bras ; derrière elle, son ombre grandit comme une menace qu'elle ne comprend pas encore.. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Edvard_Munch_-_Self-Portrait_-_MM.M.01049_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Self-Portrait_-_MM.M.01049_-_Munch_Museum.jpg | Autoportrait, 1882 | enchaîné 10]Mon père voulait que je sois ingénieur ; j'ai abandonné l'école technique pour la peinture, avec une idée fixe : peindre non pas ce que je voyais mais mes tourments intérieurs. [image: https://upload.wikimedia.org/wikipedia/commons/8/84/Edvard_Munch_-_The_Absinth_Drinkers_-_Woll_217.jpg | Les Buveurs d'absinthe, 1890 | enchaîné 10]En 1885, j'ai décidé de quitter la Norvège et j'ai mené une existence [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Evening_on_Karl_Johan_Street.jpg/1280px-Evening_on_Karl_Johan_Street.jpg | Soirée dans la rue Karl Johan,1892 | enchaîné 10]bohême à Paris et à Berlin. Ma vie était alors un chaos, entre alcool, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Edvard_Munch_-_The_Kiss_-_NG.M.02812_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg/1280px-Edvard_Munch_-_The_Kiss_-_NG.M.02812_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg | Baiser près de la fenêtre, 1892 | enchaîné 10]passions jalouses pour les femmes et peinture. C'est à Berlin qu' en 1892, ma première exposition de tableaux que le public [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e4/Edvard_Munch_Despair_Thielska_286.tif/lossy-page1-960px-Edvard_Munch_Despair_Thielska_286.tif.jpg | Désespoir,1892 | enchaîné 10]a jugés bâclés et anarchistes, a fait scandale. Elle a été interdite, et finalement m'a rendu célèbre!  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Edvard_Munch_-_The_Scream.jpg/960px-Edvard_Munch_-_The_Scream.jpg | Le Cri, 1893 | enchaîné 10]Un soir, sur une colline au-dessus d'Oslo, le ciel est devenu rouge sang: j'ai senti un cri immense traverser la nature. J'ai peint *Le Cri*, et j'ai conçu le grand projet d'une *Frise de la vie* sur l'amour, l'angoisse et la mort. En 1902, une dispute avec Tulla Larsen, qui voulait m'épouser, s'est terminée par un coup de feu : je me suis blessé à la main gauche. Depuis toujours, la femme m'attirait autant qu'elle m'effrayait  Déjà en 1896  [image: https://upload.wikimedia.org/wikipedia/commons/5/5f/Edvard_Munch_-_Madonna_-_Google_Art_Project.jpg | Madonne, 1894 | enchaîné 10]*Madonne* exprimait mon angoisse avec une femme nue, les yeux fermés, dans un halo rouge. L'amour et la fatalité s'y mêlaient inexorablement. En 1908, assailli par mes tourments, je me suis effondré et j'ai pris la décision de me faire interner huit mois dans une clinique de Copenhague. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/960px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg | Le Cri (version de 1910), 1910 | enchaîné 10]Je suis sorti de cette épreuve plus calme et plus lumineux. J'ai repris *Le Cri* en 1910: c'était la même angoisse, mais la forme était plus simple, plus dépouillée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/%22The_Sun%22_by_Edvard_Munch%2C_canvas_mounted_on_wall%2C_at_the_hall_of_ceremonies_at_University_of_Oslo.jpg/1280px-%22The_Sun%22_by_Edvard_Munch%2C_canvas_mounted_on_wall%2C_at_the_hall_of_ceremonies_at_University_of_Oslo.jpg | Le Soleil, 1911 | enchaîné 10]On m'a alors confié la décoration de la grande salle de l'université d'Oslo. Au centre, j'ai figuré un *Le Soleil* qui se levait : plus de cri, mais une énergie de vie, qui inonde tout l'espace, des couleurs lumineuses, des paysages, la vie revenue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bc/Edvard_Munch_-_Galloping_Horse_-_MM.M.00541_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Galloping_Horse_-_MM.M.00541_-_Munch_Museum.jpg | Cheval au galop, 1910-1912 | enchaîné 10]Dans *Cheval au galop*, un cheval fonce droit vers nous : la vie est aussi une force. [image: https://upload.wikimedia.org/wikipedia/commons/8/85/Rekkehus_p%C3%A5_Ekely.jpg | Ekely | enchaîné 10]En 1916, j'ai acheté ma maison d'Ekely, près d'Oslo, où j'ai vécu seul ; je laissais mes toiles dehors, sous la pluie et la neige. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Edvard_Munch_-_Self-Portrait_with_the_Spanish_Flu_-_NG.M.01867_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg/1280px-Edvard_Munch_-_Self-Portrait_with_the_Spanish_Flu_-_NG.M.01867_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg | Autoportrait avec la grippe espagnole, 1919 | enchaîné 10]En 1919, la grippe espagnole m'a frappé et je me suis peint assis, en robe de chambre, le visage jaune. Je m'en suis sorti, comme je me suis en partie guéri de ma maladie mentale, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Jalousi_i_haven.jpg/1280px-Jalousi_i_haven.jpg | Jalousie dans le jardin, 1929-1930 | enchaîné 10]mais un tableau comme *Jalousie dans le jardin* montre que, jusqu'au bout, l'amour et la jalousie m'ont hanté. En 1937, les nazis ont retiré mes tableaux des musées allemands, au nom de l'art dégénéré. [retour | 5]Je suis mort en 1944, pendant l'Occupation. J'ai légué à la ville d'Oslo les 25000 œuvres que j'avais conservées et que je considérais comme mes enfants.</t>
+          <t xml:space="preserve">Je suis né en 1863 à Loten, en Norvège. [retour | 5]Mon père, médecin militaire, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/be/Edvard_Munch_-_Christian_Munch_on_the_Couch_-_MM.M.01048_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Christian_Munch_on_the_Couch_-_MM.M.01048_-_Munch_Museum.jpg | Christian Munch sur le canapé,1881 | 5]était pieux et sombre ; il nous parlait de l'enfer. Ma mère est morte de la tuberculose quand j'avais cinq ans, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c2/Munch_Det_Syke_Barn_1885-86.jpg/1280px-Munch_Det_Syke_Barn_1885-86.jpg | L'Enfant malade, 1885-1886 | enchaîné 10]et ma sœur Sophie, que j'adorais, en est morte à quinze ans. Dans *L'Enfant malade*, que j'ai repris pendant des années, j'ai évoqué cette image traumatisante et obsessionnelle de ma Sophie mourante. La femme et la mort ne faisaient plus qu'un. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Puberty_%281894-95%29_by_Edvard_Munch.jpg/960px-Puberty_%281894-95%29_by_Edvard_Munch.jpg | Puberté, 1894 | enchaîné 10]Dans *Puberté*, une jeune fille nue, assise sur son lit, croise les bras; derrière elle, son ombre grandit comme une menace qu'elle ne comprend pas encore.. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/36/Edvard_Munch_-_Self-Portrait_-_MM.M.01049_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Self-Portrait_-_MM.M.01049_-_Munch_Museum.jpg | Autoportrait, 1882 | enchaîné 10]Mon père voulait que je sois ingénieur ; j'ai abandonné l'école technique pour la peinture, avec une idée fixe: peindre non pas ce que je voyais mais mes tourments intérieurs. [image: https://upload.wikimedia.org/wikipedia/commons/8/84/Edvard_Munch_-_The_Absinth_Drinkers_-_Woll_217.jpg | Les Buveurs d'absinthe, 1890 | enchaîné 10]En 1885, j'ai décidé de quitter la Norvège et j'ai mené une existence [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Evening_on_Karl_Johan_Street.jpg/1280px-Evening_on_Karl_Johan_Street.jpg | Soirée dans la rue Karl Johan,1892 | enchaîné 10]bohême à Paris et à Berlin. Ma vie était alors un chaos, entre alcool, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0c/Edvard_Munch_-_The_Kiss_-_NG.M.02812_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg/1280px-Edvard_Munch_-_The_Kiss_-_NG.M.02812_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg | Baiser près de la fenêtre, 1892 | enchaîné 10]passions jalouses pour les femmes et peinture. C'est à Berlin qu' en 1892, ma première exposition de tableaux que le public [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e4/Edvard_Munch_Despair_Thielska_286.tif/lossy-page1-960px-Edvard_Munch_Despair_Thielska_286.tif.jpg | Désespoir,1892 | enchaîné 10]a jugés bâclés et anarchistes, a fait scandale. Elle a été interdite, et finalement m'a rendu célèbre!  [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/65/Edvard_Munch_-_The_Scream.jpg/960px-Edvard_Munch_-_The_Scream.jpg | Le Cri, 1893 | enchaîné 10]Un soir, sur une colline au-dessus d'Oslo, le ciel est devenu rouge sang: j'ai senti un cri immense traverser la nature. J'ai peint *Le Cri*, et j'ai conçu le grand projet d'une *Frise de la vie* sur l'amour, l'angoisse et la mort. En 1902, une dispute avec Tulla Larsen, qui voulait m'épouser, s'est terminée par un coup de feu : je me suis blessé à la main gauche. Depuis toujours, la femme m'attirait autant qu'elle m'effrayait.  Déjà en 1896  [image: https://upload.wikimedia.org/wikipedia/commons/5/5f/Edvard_Munch_-_Madonna_-_Google_Art_Project.jpg | Madonne, 1894 | enchaîné 10]*Madonne* exprimait mon angoisse avec une femme nue, les yeux fermés, dans un halo rouge. L'amour et la fatalité s'y mêlaient inexorablement. En 1908, assailli par mes tourments, je me suis effondré et j'ai pris la décision de me faire interner huit mois dans une clinique de Copenhague. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/f/fe/Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg/960px-Edvard_Munch_-_The_Scream%2C_1910_%28Munch_Museum%29.jpg | Le Cri (version de 1910), 1910 | enchaîné 10]Je suis sorti de cette épreuve plus calme et plus lumineux. J'ai repris *Le Cri* en 1910: c'était la même angoisse, mais la forme était plus simple, plus dépouillée. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f4/%22The_Sun%22_by_Edvard_Munch%2C_canvas_mounted_on_wall%2C_at_the_hall_of_ceremonies_at_University_of_Oslo.jpg/1280px-%22The_Sun%22_by_Edvard_Munch%2C_canvas_mounted_on_wall%2C_at_the_hall_of_ceremonies_at_University_of_Oslo.jpg | Le Soleil, 1911 | enchaîné 10]On m'a alors confié la décoration de la grande salle de l'université d'Oslo. Au centre, j'ai figuré un *Le Soleil* qui se levait comme une énergie de vie, qui inonde tout l'espace, des couleurs lumineuses, des paysages, la vie revenue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/bc/Edvard_Munch_-_Galloping_Horse_-_MM.M.00541_-_Munch_Museum.jpg/960px-Edvard_Munch_-_Galloping_Horse_-_MM.M.00541_-_Munch_Museum.jpg | Cheval au galop, 1910-1912 | enchaîné 10]Dans *Cheval au galop*, un cheval fonce droit vers nous : la vie est aussi une force. [image: https://upload.wikimedia.org/wikipedia/commons/8/85/Rekkehus_p%C3%A5_Ekely.jpg | Ekely | enchaîné 10]En 1916, j'ai acheté ma maison d'Ekely, près d'Oslo, où j'ai vécu seul ; je laissais mes toiles dehors, sous la pluie et la neige. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/6/60/Edvard_Munch_-_Self-Portrait_with_the_Spanish_Flu_-_NG.M.01867_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg/1280px-Edvard_Munch_-_Self-Portrait_with_the_Spanish_Flu_-_NG.M.01867_-_National_Museum_of_Art%2C_Architecture_and_Design.jpg | Autoportrait avec la grippe espagnole, 1919 | enchaîné 10]En 1919, la grippe espagnole m'a frappé et je me suis peint assis, en robe de chambre, le visage jaune. Je m'en suis sorti, comme je me suis en partie guéri de ma maladie mentale, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/44/Jalousi_i_haven.jpg/1280px-Jalousi_i_haven.jpg | Jalousie dans le jardin, 1929-1930 | enchaîné 10]mais un tableau comme *Jalousie dans le jardin* montre que, jusqu'au bout, l'amour et la jalousie m'ont hanté. En 1937, les nazis ont retiré mes tableaux des musées allemands, au nom de l'art dégénéré. [retour | 5]Je suis mort en 1944, pendant l'Occupation. J'ai légué à la ville d'Oslo les 25000 œuvres que j'avais conservées et que je considérais comme mes enfants.</t>
         </is>
       </c>
       <c r="T342" s="10" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -30237,8 +30237,10 @@
       <c r="I417" s="7">
         <v>1</v>
       </c>
-      <c r="S417" s="1" t="s">
-        <v>2630</v>
+      <c r="S417" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né en 1890 à Tulln, près de Vienne, où mon père était chef de gare. [image: https://upload.wikimedia.org/wikipedia/commons/2/20/Egon_Schiele_family.jpg | La famille Schiele, 1893 | 5]Enfant, je dessinais des trains sans arrêt. Mon père, qui me voyait ingénieur, a brûlé un de mes carnets. Il est mort en 1905, la raison obscurcie par la syphilis, quand j'avais quatorze ans. Je me suis réfugié dans le dessin, avec ma sœur Gerti, ma complice. [image: https://upload.wikimedia.org/wikipedia/commons/3/31/Egon_Scheile_as_boy.jpg | Egon Schiele, 1906 | enchaîné 10]À seize ans, je suis entré à l'Académie des Beaux-Arts de Vienne dont le conservatisme m'a vite lassé. [image: https://upload.wikimedia.org/wikipedia/commons/0/09/Austrian_symbolist_painter_-_Gustav_Klimt.jpg | Gustav Klimt, 1910 | enchaîné 10]En 1908 j'ai rencontré Gustav Klimt, qui m'a encouragé, m'a acheté des dessins et m'a prêté ses modèles. Il a pu m'inspirer un moment mais j'ai développé rapidement un style personnel plus expressionniste à travers huiles sur toile et surtout dessins aquarellés ou gouachés: [image: https://upload.wikimedia.org/wikipedia/commons/thumb/1/1c/Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Lowered_Head_-_Google_Art_Project.jpg | Autoportrait à la tête baissée, 1912 | enchaîné 10]dans *Autoportrait à la tête baissée* la ligne est nerveuse, anguleuse, et montre ce qu'on cache, l'angoisse qui ronge les coeurs et les corps. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/02/Egon_Schiele_037.jpg/960px-Egon_Schiele_037.jpg | Autoportrait, 1910 | enchaîné 10]Je me suis peint souvent moi-même, nu, tordu, sans me flatter, dans des poses érotiques: je cherchais qui j'étais, ce que nous sommes sous les [image: https://upload.wikimedia.org/wikipedia/commons/thumb/d/d2/Egon_Schiele_-_Cardinal_and_Nun_%28Caress%29_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Cardinal_and_Nun_%28Caress%29_-_Google_Art_Project.jpg | Cardinal et Nonne, 1912 | enchaîné 10]apparences sociales factices. *Cardinal et Nonne* a été ma réponse [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/40/The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg/1280px-The_Kiss_-_Gustav_Klimt_-_Google_Cultural_Institute.jpg | Klimt, Le Baiser, 1907-1908 | enchaîné 10]provocatrice et satirique au *Baiser* de Klimt : plus d'or, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Egon_Schiele_-_Cardinal_and_Nun_%28Caress%29_-_Google_Art_Project.jpg | Cardinal et Nonne, 1912 | enchaîné 10]mais un cardinal et une nonne enlacés, l'hypocrisie de la religion dévoilée. [image: https://upload.wikimedia.org/wikipedia/commons/d/dc/Walburga_Neuzil.jpg | Wally Neuzil, 1915 | enchaîné 10]Dégoûté de Vienne, endetté, avec Wally Neuzil, ancienne modèle de Klimt, je [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e8/%C4%8Cesk%C3%BD_Krumlov%2C_domek_Egona_Schieleho_%283%29.jpg/1280px-%C4%8Cesk%C3%BD_Krumlov%2C_domek_Egona_Schieleho_%283%29.jpg | Maison de Schiele à Krumau | enchaîné 10]me suis installé à Krumau, la ville de ma mère, puis à Neulengbach et [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/66/Egon_Schiele_-_Portrait_of_Wally_Neuzil_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Portrait_of_Wally_Neuzil_-_Google_Art_Project.jpg | Portrait de Wally Neuzil, 1912 | enchaîné 10]j'ai peint le *Portrait de Wally Neuzil*. Mais les voisins ont fait courir toutes [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Egon_Schiele_-_Reinerbub_%28Bildnis_Herbert_Reiner%29_-_4766_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Egon_Schiele_-_Reinerbub_%28Bildnis_Herbert_Reiner%29_-_4766_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Portrait de Herbert Reiner,1910 | enchaîné 10]sortes de rumeurs car  je choisissais comme  modèles des enfants que je peignais parfois nus, et en 1912, on m'a arrêté:  j'ai été condamné à vingt-quatre jours de prison. Le juge a même brûlé un de mes dessins. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b8/Egon_Schiele_-_Self-Portrait_with_Physalis_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_Self-Portrait_with_Physalis_-_Google_Art_Project.jpg | Autoportrait à la plante de lanterne chinoise, 1912 | enchaîné 10]À ma sortie, j'ai peint l'*Autoportrait à la plante de lanterne chinoise* : un visage fin, nerveux, et le fruit orange à côté, fragile comme moi, comme la vie. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Egon_Schiele_015.jpg/1280px-Egon_Schiele_015.jpg | La Petite Ville II, 1912-1913 | enchaîné 10]*La Petite Ville II* est Krumau, que j'ai peinte comme un empilement de maisons ocres, serrées les unes contre les autres, sans ciel, comme une ville étouffant les rêves. En 1915, j'ai quitté Wally. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/0/0a/Egon_Schiele_-_Der_Tod_und_das_M%C3%A4dchen.jpg/1280px-Egon_Schiele_-_Der_Tod_und_das_M%C3%A4dchen.jpg | La Mort et la Jeune Fille, 1915 | enchaîné 10]*La Mort et la Jeune Fille* a été notre adieu : l'homme enlaçant, c'est moi ; la jeune fille, c'est elle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/90/Egon_Schiele_055.jpg/960px-Egon_Schiele_055.jpg | Portrait d'Edith Schiele, 1915 | enchaîné 10]Je me suis marié avec Edith Harms, plus comme il faut aux yeux de la société.  Trois jours après le mariage, j'étais mobilisé, mais je suis  resté à [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/01/Schiele_-_Kriegsgefangener_russischer_Offizier_-_1916.jpg/500px-Schiele_-_Kriegsgefangener_russischer_Offizier_-_1916.jpg | Prisonnier de guerre - officier russe, 1916 | enchaîné 10]l'arrière. J'ai dessiné des prisonniers de guerre russes [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/26/Egon_Schiele_-_House_with_Shingle_Roof_%28Old_House_II%29_-_Google_Art_Project.jpg/1280px-Egon_Schiele_-_House_with_Shingle_Roof_%28Old_House_II%29_-_Google_Art_Project.jpg | Maison avec toit de bardeaux (Vieille maison II), 1915 | enchaîné 10]et j'ai peint une vieille maison, la *Maison avec toit de bardeaux*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d9/Egon_Schiele_-_Umarmung_%281917%29.jpg/1280px-Egon_Schiele_-_Umarmung_%281917%29.jpg | L'Étreinte, 1917 | enchaîné 10]Dans *L'Étreinte*, le couple est plus apaisé : les contours s'adoucissent, et une vraie douceur a pris la place de la violence d'autrefois, du moins pour un temps. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Egon_Schiele_-_Vier_B%C3%A4ume_-_3917_-_%C3%96sterreichische_Galerie_Belvedere.jpg/1280px-Egon_Schiele_-_Vier_B%C3%A4ume_-_3917_-_%C3%96sterreichische_Galerie_Belvedere.jpg | Quatre arbres, 1917 | enchaîné 10]*Quatre arbres* est un paysage d'automne, où quatre troncs se détachent dans la lumière du soir, et où je trouve une paix que je ne connaissais pas. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b6/Schiele_-_Sitzende_Frau_mit_hochgezogenem_Knie_-_1917.jpg/960px-Schiele_-_Sitzende_Frau_mit_hochgezogenem_Knie_-_1917.jpg | Femme assise aux genoux pliés, 1917 | enchaîné 10]Mon trait s'est assoupli; dans *Femme assise aux genoux pliés*, le corps est plein, modelé, sans la tension d'avant : on dit que je me suis assagi. En 1918, Klimt est mort ; j'ai dessiné son visage à la morgue. À l'exposition de la Sécession, mes œuvres ont triomphé, et je trouvais enfin une certaine aisance matérielle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/61/Egon_Schiele_-_Die_Familie_%281918%29.jpg/1280px-Egon_Schiele_-_Die_Familie_%281918%29.jpg | La Famille, 1918 | enchaîné 10]J'ai peint *La Famille* : moi, Edith enceinte, et l'enfant que nous attendions. La grippe espagnole a emporté [retour | 5]Edith le 28 octobre 1918, moi le 31, à vingt-huit ans.</t>
+        </is>
       </c>
       <c r="T417" s="10" t="s">
         <v>3502</v>
@@ -44522,6 +44524,11 @@
       <c r="B494" t="s">
         <v>2628</v>
       </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Egon Schiele, 1918</t>
+        </is>
+      </c>
     </row>
     <row r="495" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EF6CE08-903E-46FE-B4EB-973CB9A89CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF0DA08-8E94-4FFB-94B2-D103D6DE3382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8785" uniqueCount="3576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8786" uniqueCount="3577">
   <si>
     <t>Prénom</t>
   </si>
@@ -13416,6 +13416,9 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/2/24/Amedeo_Modigliani_1918_restored.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8b/Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg/960px-Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -23204,6 +23207,9 @@
       <c r="S230" s="1" t="s">
         <v>1633</v>
       </c>
+      <c r="T230" s="10" t="s">
+        <v>3576</v>
+      </c>
       <c r="U230" s="5" t="s">
         <v>1631</v>
       </c>
@@ -34243,6 +34249,7 @@
     <hyperlink ref="T348" r:id="rId277" xr:uid="{9BB270DC-5096-43E5-BA8C-D7469796998B}"/>
     <hyperlink ref="T333" r:id="rId278" xr:uid="{9980C49E-1986-481B-89F5-F1B7DFC18C63}"/>
     <hyperlink ref="T332" r:id="rId279" xr:uid="{189D77F4-2560-4DF7-BDE1-F9B0047B268D}"/>
+    <hyperlink ref="T230" r:id="rId280" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8b/Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg/960px-Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A85B84AC-FF33-4B24-B264-BB6A1736B87F}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAF0DA08-8E94-4FFB-94B2-D103D6DE3382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E57A69-1E3A-4AF6-9D58-CBD70C24B560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13418,7 +13418,7 @@
     <t>https://upload.wikimedia.org/wikipedia/commons/2/24/Amedeo_Modigliani_1918_restored.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
   <si>
-    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8b/Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg/960px-Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+    <t>https://upload.wikimedia.org/wikipedia/commons/b/bf/Ghiberti.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
   </si>
 </sst>
 </file>
@@ -13818,7 +13818,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y503"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
@@ -14792,8 +14792,10 @@
       <c r="I23" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S23" s="1" t="s">
-        <v>208</v>
+      <c r="S23" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Florence en 1493, fils d'un orfèvre, et j'ai rêvé de devenir plus grand que Michel-Ange. Tout mon malheur est là. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e2/2793_-_Firenze_-_Palazzo_Medici_Riccardi_-_Baccio_Bandinelli%2C_Orfeo_e_Cerbero_%281519%29_-_Foto_Giovanni_Dall%27Orto%2C_27-Oct-2007.jpg/960px-2793_-_Firenze_-_Palazzo_Medici_Riccardi_-_Baccio_Bandinelli%2C_Orfeo_e_Cerbero_%281519%29_-_Foto_Giovanni_Dall%27Orto%2C_27-Oct-2007.jpg | Orphée charmant Cerbère, Palazzo Medici-Riccardi, Florence, 1519 | 5]Pour le cardinal Jules de Médicis, le futur pape Clément VII, je sculpte en 1519 *Orphée charmant Cerbère* : le poète joue de sa lyre, le chien à trois têtes l'écoute, apaisé. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Baccio_Bandinelli_%28dall%27antico%29%2C_Gruppo_del_Laocoonte%2C_1523-25_ca._02.jpg/960px-Baccio_Bandinelli_%28dall%27antico%29%2C_Gruppo_del_Laocoonte%2C_1523-25_ca._02.jpg | Laocoon, copie du groupe antique, Offices, Florence, 1520-1525 | enchaîné 10]Le même cardinal me demande ensuite une copie du *Laocoon*, découvert à Rome quelques années plus tôt, destinée au roi de France. Je l'achève ; les Médicis la gardent, et elle est aujourd'hui aux Offices. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Hercule_et_Cacus_Bandinelli_Florence_Signoria.jpg/1280px-Hercule_et_Cacus_Bandinelli_Florence_Signoria.jpg | Hercule et Cacus, Piazza della Signoria, Florence, 1525-1534 | enchaîné 10]En 1525, on me confie un énorme bloc de marbre, destiné d'abord à Michel-Ange : un *Hercule et Cacus*. On raconte que j'ai intrigué auprès du pape pour l'obtenir. Mon groupe est installé en 1534, place de la Seigneurie, tout près du *David* de mon rival, et Florence se moque : Cellini dit qu'il ressemble à un sac de melons, des poèmes satiriques s'accrochent à ses pieds. Je n'ai jamais pardonné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg | Buste de Cosme Ier de Médicis, Palais Pitti, Florence, 1554-1558 | enchaîné 10]Quand les Médicis reviennent en maîtres, le duc Cosme Ier devient mon grand protecteur : voici son *Buste*, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Baccio_bandinelli%2C_cosimo_I.JPG/960px-Baccio_bandinelli%2C_cosimo_I.JPG | Monument à Cosme Ier de Médicis, Palazzo Vecchio, Florence, 1547-1572 | enchaîné 10]puis son *Monument*, que je continue jusqu'à ma mort. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg | Bacchus, Palais Pitti, Florence, 1547-1549 | enchaîné 10]Pour son palais, un *Bacchus*, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg | Adam et Ève, Bargello, Florence, 1554-1559 | enchaîné 10]et pour la cathédrale, un *Adam et Ève* en marbre, deux corps nus qui s'appuient sur une étude minutieuse de l'anatomie : mes élèves ne s'en lassent pas, mes ennemis se moquent. J'ai ouvert une académie de dessin : j'y forme des élèves qui deviendront célèbres. Mon style est froid, plus savant que sensible. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/Baccio_bandinelli%2C_piet%C3%A0_per_la_propria_tomba.JPG/960px-Baccio_bandinelli%2C_piet%C3%A0_per_la_propria_tomba.JPG | Pietà, Santissima Annunziata, Florence, 1559 | enchaîné 10]Pour ma propre chapelle, à la Santissima Annunziata, je sculpte une *Pietà* : sous les traits de Nicodème, c'est mon visage. En 1559, Cosme lance le concours de la fontaine de Neptune : c'est Ammannati, mon élève, qui l'emporte, avec le marbre que j'avais commencé. [retour | 5]Je suis mort en 1560, à Florence, et je repose sous ma Pietà.</t>
+        </is>
       </c>
       <c r="T23" s="1" t="s">
         <v>209</v>
@@ -16075,8 +16077,10 @@
       <c r="I54" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S54" s="1" t="s">
-        <v>457</v>
+      <c r="S54" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né en 1529 à Douai, en Flandre, et je m'appelle Jean de Boulogne ; en Italie, on dira Giambologna. J'ai appris à Anvers, puis, en 1550, à Rome, j'ai regardé l'antique et Michel-Ange. Au retour, je m'arrête à Florence : un riche amateur, Bernardo Vecchietti, me retient, me présente aux Médicis, et je n'en repartirai plus. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Giambologna%2C_bacco%2C_1560_ca.%2C_dalle_collezioni_medicee_poi_su_una_fontana_in_borgo_s._jacopo%2C_01.jpg/500px-Giambologna%2C_bacco%2C_1560_ca.%2C_dalle_collezioni_medicee_poi_su_una_fontana_in_borgo_s._jacopo%2C_01.jpg | Bacchus, Bargello, Florence, 1560-1562 | 5]Mon *Bacchus* est un jeune dieu à demi renversé, qui lève sa coupe : on le regarde de face, on tourne autour de lui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, sur la place, je fonds la *Fontaine de Neptune* : le dieu, nu, bras tendu, domine des nymphes et des dauphins. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg | Florence triomphant de Pise, Bargello, Florence, 1567-1570 | enchaîné 10]*Florence triomphant de Pise* est une femme debout, qui domine un captif à genoux : un seul bloc, plusieurs points de vue. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Giambologna_raptodasabina.jpg/1280px-Giambologna_raptodasabina.jpg | L'Enlèvement des Sabines, Loggia dei Lanzi, Florence, 1579-1583 | enchaîné 10]Mon plus grand défi est *L'Enlèvement des Sabines* : trois corps, un homme, une femme, un vieillard, taillés dans un seul bloc, qui montent en spirale. Je ne lui avais donné aucun sujet : c'est après coup qu'on lui a trouvé ce titre. Ce qui m'importe, c'est qu'on puisse le regarder de tous côtés. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg/500px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg | Mercure volant, Bargello, Florence, 1580 | enchaîné 10]Mon *Mercure volant* tient sur la pointe d'un pied, porté par le souffle du vent : les princes d'Europe s'en arrachent les copies. [image: https://upload.wikimedia.org/wikipedia/commons/d/da/Appennino.jpg | Colosse de l'Apennin, Pratolino, 1579-1583 | enchaîné 10]À Pratolino, pour le prince François, un colosse de pierre, l'*Apennin* : un géant de dix mètres, accroupi, dont le corps est creusé de grottes et de fontaines. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Monument équestre de Cosme Ier de Médicis, Florence, 1594 | enchaîné 10]Après la mort de Cosme Ier, je fonds son *Monument équestre*, place de la Seigneurie. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9a/Herakles_Nessos_Loggia_dei_Lanzi_2005_09_13.jpg/960px-Herakles_Nessos_Loggia_dei_Lanzi_2005_09_13.jpg | Hercule et le centaure Nessus, Loggia dei Lanzi, Florence, 1595-1600 | enchaîné 10]Puis *Hercule et le centaure Nessus*, deux corps en lutte, à la loge des Lanzi. Mon atelier est une ruche : Pietro Tacca, mon fidèle assistant, et Antonio Susini diffusent mon style en petits bronzes dans toute l'Europe. [retour | 5]Je suis mort à Florence en 1608, flamand de naissance, florentin de cœur.</t>
+        </is>
       </c>
       <c r="T54" s="1" t="s">
         <v>458</v>
@@ -16938,8 +16942,10 @@
       <c r="I75" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S75" s="1" t="s">
-        <v>608</v>
+      <c r="S75" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On m'a surnommé *il Divino*. Je suis né en 1475 à Caprese, en Toscane, et je suis confié à une nourrice de Settignano, femme d'un tailleur de pierre : je dis souvent que j'ai sucé le ciseau avec le lait. À treize ans, j'entre chez le peintre Ghirlandaio, puis dans le jardin de Laurent de Médicis, où je copie les statues antiques. Un camarade, Torrigiano, me casse le nez d'un coup de poing : je garderai ce nez toute ma vie. À vingt-quatre ans, j'ai déjà sculpté à Rome la *Pietà* de Saint-Pierre. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Madonna_michelangelo.jpg | Vierge de Bruges, église Notre-Dame, Bruges, 1501-1504 | 5]Voici la *Vierge de Bruges* : une Madone sereine, qui tient son enfant entre ses genoux, destinée à des marchands flamands. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg | David, Galerie de l'Académie, Florence, 1501-1504 | enchaîné 10]De retour à Florence en 1501, la ville me confie un bloc de marbre abandonné depuis vingt-cinq ans, que deux sculpteurs avaient renoncé à tailler. J'y vois un géant. Trois ans plus tard, le *David* est dressé devant le Palazzo Vecchio : non plus le jeune vainqueur de Donatello, mais le héros avant le combat, tendu, qui regarde l'ennemi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/%27Moses%27_by_Michelangelo_JBU010.jpg/960px-%27Moses%27_by_Michelangelo_JBU010.jpg | Tombeau de Jules II, Saint-Pierre-aux-Liens, Rome, 1505-1545 | enchaîné 10]En 1505, le pape Jules II me commande son tombeau : quarante statues, un monument grand comme une maison. Je pars à Carrare choisir les blocs ; le pape change d'avis, me charge du plafond de la Sixtine. Le tombeau me poursuivra quarante ans, et il ne sera jamais celui que j'avais rêvé ; il aura quand même son *Moïse*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG | L'Esclave mourant, Louvre, 1513 | enchaîné 10]Pour le premier projet, j'ai sculpté des Esclaves : le *Mourant*, qui s'abandonne, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/%27Rebellious_Slave%27_Michelangelo_JBU81.jpg/960px-%27Rebellious_Slave%27_Michelangelo_JBU81.jpg | L'Esclave rebelle, Louvre, 1513 | enchaîné 10]et le *Rebelle*, qui se débat contre ses liens. Ils partiront en France, et ils sont aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg | Le Christ de la Minerve, Rome, 1519-1521 | enchaîné 10]À Rome, mon *Christ de la Minerve* est un Christ nu, dressé, tenant sa croix : on lui a ajouté plus tard un voile de bronze par pudeur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg | Tombeau de Laurent de Médicis, chapelles des Médicis, Florence, 1520-1534 | enchaîné 10]À Florence, pour les Médicis, je travaille à la sacristie de San Lorenzo : voici le *Tombeau de Laurent*, duc d'Urbin, avec l'Aurore et le Crépuscule ; en face, celui de son frère Julien porte le Jour et la Nuit. À un poète qui trouvait ma Nuit trop vivante, j'ai fait répondre qu'il m'est doux de dormir, et plus doux encore d'être de pierre, tant que dure la honte. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg | Pietà Bandini, Florence, 1547-1555 | enchaîné 10]Dans ma *Pietà Bandini*, destinée à ma propre tombe, Nicodème qui soutient le Christ a mon visage. Mécontent d'un défaut du marbre, je l'ai brisée à coups de marteau ; un élève l'a recomposée. [retour | 5]Je suis mort à Rome en 1564, presque nonagénaire, et Florence a ramené mon corps pour l'enterrer à Santa Croce.</t>
+        </is>
       </c>
       <c r="T75" s="1" t="s">
         <v>609</v>
@@ -17638,8 +17644,10 @@
       <c r="I92" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S92" s="1" t="s">
-        <v>731</v>
+      <c r="S92" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Florence en 1500. Mon père, musicien, voulait faire de moi un flûtiste ; j'ai préféré l'orfèvrerie, puis la sculpture, deux arts que je n'ai jamais séparés. Ma vie ressemble à un roman : chassé de Florence à seize ans après une rixe, artilleur lors du sac de Rome en 1527, prisonnier au château Saint-Ange d'où je m'évade, plusieurs duels, un meurtre, des fuites. J'ai tout raconté dans ma *Vie*, sans me ménager. [image: https://upload.wikimedia.org/wikipedia/commons/3/39/Saliera_Cellini_Vienna_18_04_2013_01_B.jpg | Salière de François Ier, Vienne, 1540-1543 | 5]François Ier m'accueille à Paris. Pour lui, j'achève la *Salière*, en or et en émail : Neptune, la mer, et la Terre, assise, jambes entrelacées ; une petite barque porte le sel, un petit temple le poivre. Le roi, raconte-t-on, s'écria que c'était cent fois plus divin que tout ce qu'il avait imaginé. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/La_Nymphe_de_Fontainebleau_-_Benvenuto_Cellini_-_Musée_du_Louvre_Sculptures_MR_1706_;_N_15050.jpg | Nymphe de Fontainebleau, Louvre, 1542-1543 | enchaîné 10]Pour la porte du château de Fontainebleau, je fonds la *Nymphe de Fontainebleau* en bronze : longue, allongée, le coude sur un cerf, d'une sensualité toute de ligne et de proportion. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/Bust_of_Cosimo_I_by_Benvenuto_Cellini.jpg | Buste de Cosme Ier de Médicis, Bargello, Florence, 1545-1548 | enchaîné 10]De retour à Florence, le duc Cosme Ier me prend pour son artiste : mon *Buste* de bronze le montre en armure, le regard sûr. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/Busto_di_Bindo_Altoviti.jpg | Buste de Bindo Altoviti, Boston, 1549 | enchaîné 10]Et voici le banquier Bindo Altoviti, dont j'ai fait le *Buste*, d'une élégance rare. [image: https://upload.wikimedia.org/wikipedia/commons/4/48/Firenze.Loggia.Perseus01.JPG | Persée avec la tête de Méduse, Loggia dei Lanzi, Florence, 1545-1554 | enchaîné 10]Pour la place de la Seigneurie, mon *Persée* est ma plus grande fierté. Le soir de la fonte, la fournaise s'éteint ; je jette dans le métal toute la vaisselle d'étain de la maison, et le bronze coule jusqu'au bout. En 1554, le peuple se presse devant la statue : des sonnets s'accrochent aux piliers. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/Benvenuto_cellini_su_un_torso_antico%2C_ganimede%2C_1548%2C_02.jpg/500px-Benvenuto_cellini_su_un_torso_antico%2C_ganimede%2C_1548%2C_02.jpg | Ganymède, Bargello, Florence, 1545-1550 | enchaîné 10]Je restaure un torse antique en *Ganymède*, et j'y ajoute la tête, les bras, l'aigle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Benvenuto_cellini%2C_narciso%2C_1545-47%2C_01.jpg/500px-Benvenuto_cellini%2C_narciso%2C_1545-47%2C_01.jpg | Narcisse, Bargello, Florence, 1548-1565 environ | enchaîné 10]Puis mon *Narcisse* s'incline sur lui-même, pour montrer que je sais aussi tailler le marbre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/Benvenuto_cellini%2C_crocifisso_di_marmo%2C_1556-1562%2C_03.jpg/960px-Benvenuto_cellini%2C_crocifisso_di_marmo%2C_1556-1562%2C_03.jpg | Crucifix de l'Escurial, 1559-1562 | enchaîné 10]Mon *Crucifix* de marbre blanc sur une croix de marbre noir, je le destinais à ma propre tombe ; il finira offert au roi d'Espagne, à l'Escurial. [retour | 5]Je suis mort en 1571, ayant vécu avec la même flamboyance que mes œuvres, sans renoncer à mon orgueil ni à mon talent.</t>
+        </is>
       </c>
       <c r="T92" s="1" t="s">
         <v>732</v>
@@ -18238,8 +18246,11 @@
       <c r="I107" s="7">
         <v>3</v>
       </c>
-      <c r="S107" s="1" t="s">
-        <v>832</v>
+      <c r="S107" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né en 1801 à Bolton, dans le Lancashire. À mes dix-sept ans, ma famille a émigré aux États-Unis. J'ai appris à peindre seul, en parcourant les collines et les forêts de l'État de New York.
+[image: https://upload.wikimedia.org/wikipedia/commons/f/fa/Cole_Thomas_Lake_with_Dead_Trees_%28Catskill%29_1825.jpg | Lac aux arbres morts, 1825 | enchaîné 5]À l'été 1825, j'ai exposé dans une vitrine de New York des vues des monts Catskill. Elles ont été remarquées, achetées, admirées. C'était le début de l'école du fleuve [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg | Vue depuis le mont Holyoke, après un orage — The Oxbow., 1836 | enchaîné 10]Hudson, dont on m'a appelé le fondateur. Frédéric Edwin Church, mon ami,  et, plus tard, Albert Bierstadt en ont fait partie. J'ai peint la nature américaine, sauvage et grandiose.  J'ai imaginé aussi des allégories à travers des grands cycles. Le premier, *La Vie humaine*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole_-_The_Voyage_of_Life_Childhood%2C_1842_%28National_Gallery_of_Art%29FXD.jpg | Le Voyage de la vie : L'Enfance, 1842 | enchaîné 10] est une série de quatre tableaux où un voyageur navigue sur une rivière dont les changements évoquent les différentes étapes de l'existence. Le second, *Le Cours de l'Empire*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Architect-s_Dream_1840.jpg | Le Rêve de l'Architecte, 1840 | enchaîné 10] est constitué de cinq tableaux qui décrivent la naissance et le déclin d'une civilisation imaginaire. J'ai voulu mettre en garde mes contemporains [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg/1280px-Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg | Le Cours de l'Empire, La Désolation, 1836 | enchaîné 10] en peignant les ravages possibles sur la Nature et la Civilisation d'une course effrénée vers une société industrielle [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg | Le Départ, 1837 | enchaîné 10]et marchande.  J'ai été un des pionniers du mouvement environnementaliste. Je me suis installé à Catskill, où je suis mort en 1848, à quarante-sept ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Gibbon_River_at_Madison_in_Yellowstone.JPG/1280px-Gibbon_River_at_Madison_in_Yellowstone.JPG | La rivière Gibbon dans le parc de Yellowstone. | enchaîné 10]Mes convictions écologistes ont ouvert la voie à la création des grands parcs nationaux américains comme celui de Yellowstone. Je crois cette voie prometteuse pour [retour | 5]l'avenir de l'Amérique.</t>
+        </is>
       </c>
       <c r="T107" s="1" t="s">
         <v>833</v>
@@ -20926,8 +20937,10 @@
       <c r="I174" s="7">
         <v>1</v>
       </c>
-      <c r="S174" s="1" t="s">
-        <v>1265</v>
+      <c r="S174" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Florence en 1435 et mon oncle Luca m'a pris dans son atelier, où il m'a confié son secret : la terre cuite émaillée, blanche et bleue. Luca est mort en 1482 ; à moi de faire vivre l'entreprise. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg/960px-Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg | L'Adoration de l'Enfant, Washington, après 1477 | 5]J'élargis la palette : à côté du blanc et du bleu, je glisse du vert, du jaune, du violet, pour peindre les feuilles et les fruits des guirlandes qui encadrent mes tableaux. Ici, *L'Adoration de l'Enfant* : la Vierge à genoux devant le Christ nu, des anges, une guirlande de fruits. Mes figures sont plus tendres, plus familières que celles de mon oncle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg | L'Annonciation, La Verna, 1475 | enchaîné 10]À La Verna, là où saint François a reçu les stigmates, je livre une *Annonciation* : l'ange et la Vierge se font face dans un blanc éclatant, sur un fond d'azur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Autel des Médicis, Santa Croce, Florence, 1475-1480 | enchaîné 10]À Santa Croce, dans la chapelle des Médicis, je réalise un autel en haut-relief : la terre cuite émaillée entre dans l'église des grandes familles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg | Retable de la Trinité, Arezzo, 1484 | enchaîné 10]À Arezzo, pour la cathédrale, un retable de la *Trinité*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG | Tondi de l'Hôpital des Innocents, Florence, 1487 environ | enchaîné 10]Pour l'Hôpital des Innocents, dessiné par Brunelleschi, je modèle des médaillons : des nourrissons emmaillotés sur un fond bleu, qui rappellent que cette maison recueille les enfants abandonnés. Ce sont les images les plus connues de ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg | Lunette de la Vierge entre saint Étienne et saint Laurent, Prato, 1489 | enchaîné 10]À Prato, au-dessus d'une porte de la cathédrale, une lunette : la Vierge entre saint Étienne et saint Laurent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG | Lunette de la Vierge à l'Enfant et anges, Florence, 1489 | enchaîné 10]Pour la cathédrale de Florence, une autre lunette, avec la Vierge, l'Enfant et des anges. L'atelier travaille sans relâche : les paroisses toscanes, qui ne peuvent pas payer le marbre, achètent notre terre cuite. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg | Vierge au coussin, Séville, 1520 | enchaîné 10]Vers 1520, je suis un vieil homme et ma *Vierge au coussin* a pris la mer pour l'Espagne, jusqu'à la cathédrale de Séville. Mes fils Giovanni, Luca le Jeune et Girolamo ont repris l'atelier ; Girolamo est parti en France, travailler pour François Ier. [retour | 5]Je suis mort en 1525, presque nonagénaire.</t>
+        </is>
       </c>
       <c r="U174" s="5" t="s">
         <v>1263</v>
@@ -20964,8 +20977,10 @@
       <c r="I175" s="7">
         <v>1</v>
       </c>
-      <c r="S175" s="1" t="s">
-        <v>1271</v>
+      <c r="S175" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Florence en 1399, et j'ai d'abord appris l'orfèvrerie avant de sculpter le marbre. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | La Cantoria, Florence, 1431-1438 | 5]En 1431, la cathédrale me confie sa *Cantoria*, la tribune des chanteurs : sur dix panneaux de marbre, des enfants chantent, jouent du luth, de la harpe, des cymbales, dansent, comme le psaume qui appelle à louer Dieu par la musique. Donatello fait au même moment la sienne, plus agitée, plus sauvage ; la mienne est plus claire, plus sereine. Mais c'est une autre invention qui va faire ma réputation. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | La Résurrection, Florence, 1442-1444 | enchaîné 10]Au-dessus de la porte de la sacristie, je modèle *La Résurrection* en terre cuite, puis je la recouvre d'une glaçure d'étain, blanche, brillante, qui ne s'altère pas : le Christ blanc sort du tombeau sur un fond bleu intense. Je tiens la recette secrète, je ne la confie qu'à ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | Vierge à la pomme, Bargello, Florence, 1442-1444 | enchaîné 10]La terre cuite émaillée me permet de produire plus vite et à moindre coût que le marbre : voici une *Vierge à la pomme*, douce et grave, qui tient son enfant contre sa joue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | Vierge à l'Enfant avec trois chérubins, Louvre, 1450 environ | enchaîné 10]Mes Vierges à l'Enfant se retrouvent dans toute la Toscane, et jusque dans les collections royales : celle-ci, avec trois chérubins, est aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg | Vierge à l'Enfant, Bargello, Florence, 1450 environ | enchaîné 10]Celle-ci, au Bargello, est plus simple encore : deux visages, un bleu, un blanc, et tout est dit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | Tabernacle de la Sainte Croix, Impruneta, 1445-1450 | enchaîné 10]À Impruneta, le *Tabernacle de la Sainte Croix* mêle bas-relief et haut-relief en terre cuite émaillée : des anges portent des cierges, des enfants soutiennent des guirlandes. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | Porte de bronze de la sacristie, Florence, 1446-1475 | enchaîné 10]Je n'ai pas abandonné le bronze : avec Michelozzo et Maso di Bartolomeo, je réalise la *Porte de la sacristie* de la cathédrale, dix panneaux de saints, de docteurs et d'anges, qui m'occuperont longtemps. [image: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | Les Quatre Vertus cardinales, San Miniato al Monte, Florence, 1461-1466 | enchaîné 10]À San Miniato, dans la chapelle du cardinal de Portugal, j'orne le plafond des *Quatre Vertus cardinales* : la Prudence, la Justice, la Tempérance et la Force entourent le Saint-Esprit. [retour | 5]Je suis mort en 1482, et c'est mon neveu Andrea qui a gardé le secret après moi.</t>
+        </is>
       </c>
       <c r="U175" s="5" t="s">
         <v>1263</v>
@@ -21374,8 +21389,10 @@
       <c r="I185" s="7">
         <v>1</v>
       </c>
-      <c r="S185" s="1" t="s">
-        <v>1343</v>
+      <c r="S185" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Florence vers 1386, fils d'un cardeur de laine, et l'on m'appelle Donatello, un diminutif affectueux qui a fini par effacer mon vrai nom. J'ai appris le métier dans l'atelier de Ghiberti, puis, avec Brunelleschi, mon ami, j'ai parcouru Rome pour mesurer les ruines antiques. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg | David, Florence, 1408-1409 | 5]Mon premier *David*, en marbre, sculpté pour la cathédrale, est encore de style gothique : un jeune héros élégant, qui foule du pied la tête de Goliath. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG | Saint Marc, Orsanmichele, Florence, 1411-1413 | enchaîné 10]Pour Orsanmichele, les tisserands de lin m'ont commandé *Saint Marc*. On raconte que Michel-Ange, devant lui, aurait dit n'avoir jamais vu figure qui eût plus l'air d'un honnête homme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg | Saint Georges, Florence, 1415-1417 | enchaîné 10]Mon *Saint Georges*, pour les armuriers, est un jeune soldat debout, les pieds bien plantés, le regard tendu. Sur le socle, j'ai creusé un relief à peine épais où le dragon et la princesse s'enfoncent dans un paysage : c'est la première fois que la perspective entre dans la sculpture. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg | Le Festin d'Hérode, Sienne, 1423-1425 | enchaîné 10]À Sienne, pour le baptistère, je fonds *Le Festin d'Hérode* en bronze doré : la tête de saint Jean-Baptiste vient d'être apportée sur un plat, Hérode recule d'horreur, les convives se bousculent, et au fond s'ouvrent des arcades qui fuient. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg/960px-Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg | Annonciation Cavalcanti, Santa Croce, Florence, 1435 environ | enchaîné 10]Dans l'*Annonciation Cavalcanti*, à Santa Croce, la Vierge se détourne avec pudeur de l'ange, entre des pilastres dorés, et des petits enfants ailés jouent au-dessus. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg | David, Bargello, Florence, 1440 environ | enchaîné 10]Vers 1440, sans doute pour Cosme de Médicis, mon protecteur, je coule un nouveau *David*, en bronze : un adolescent nu, coiffé d'un chapeau de berger, le premier nu en ronde-bosse depuis l'Antiquité. Sa nudité, son sourire, son pied sur la tête de Goliath ont fait couler beaucoup d'encre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG/1280px-Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Monument à Gattamelata, Padoue, 1445-1453 | enchaîné 10]En 1443, Padoue m'appelle. Pour le général Gattamelata, mort l'année même, je fonds le *Monument équestre* : c'est la première grande statue équestre en bronze depuis l'empereur Marc Aurèle. Je reste dix ans en Vénétie, et mon style inspire toute une génération de peintres, Mantegna le premier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Donatello%2C_maria_maddalena_02.JPG/960px-Donatello%2C_maria_maddalena_02.JPG | Madeleine pénitente, Florence, 1453-1455 | enchaîné 10]De retour à Florence, vieux et fatigué, je sculpte une *Madeleine pénitente* en bois : un corps décharné, les mains jointes, les joues creusées, l'inverse de la beauté idéale. [retour | 5]Je suis mort en 1466, et Cosme avait demandé que je sois enterré près de lui, à Saint-Laurent.</t>
+        </is>
       </c>
       <c r="U185" s="5" t="s">
         <v>1339</v>
@@ -23204,8 +23221,10 @@
       <c r="I230" s="7">
         <v>1</v>
       </c>
-      <c r="S230" s="1" t="s">
-        <v>1633</v>
+      <c r="S230" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Florence en 1378 [retour | 5]et j'ai appris l'orfèvrerie auprès de mon beau-père : ciseler l'or, graver, fondre de petites pièces, c'est là que ma main s'est formée. [image: https://upload.wikimedia.org/wikipedia/commons/5/52/Wga_ghiberti_sacrifice_of_Isaac.jpg | Le Sacrifice d'Isaac, 1401 | 5]En 1401, j'ai vingt-deux ans quand les marchands de Florence ouvrent un concours pour les nouvelles portes de bronze du baptistère. Chaque candidat doit livrer le même panneau, le *Sacrifice d'Isaac*. Mon bronze, fondu d'un seul jet, est jugé le plus léger et le plus gracieux ; Brunelleschi, dit-on, refuse de partager la commande et s'en va. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG | Porte nord du baptistère, Florence, 1403-1424 | enchaîné 10]Je vais passer plus de vingt ans sur cette première porte : vingt-huit panneaux sur la vie du Christ, encadrés de quadrilobes comme dans les cathédrales gothiques, avec des figures souples, aux draperies fluides, dans l'élégance courtoise du gothique international. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG | Saint Jean-Baptiste, Orsanmichele, Florence, 1412-1416 | enchaîné 10]Dans le même temps, les marchands de drap me demandent pour Orsanmichele un *Saint Jean-Baptiste* : c'est la première grande statue de bronze de la Renaissance, et je dois apprendre le métier de fondeur à l'échelle d'un homme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg | Le Baptême du Christ, Sienne, 1417-1427 | enchaîné 10]À Sienne, pour les fonts baptismaux, je livre deux reliefs, aux côtés de Donatello et de Jacopo della Quercia. *Le Baptême du Christ*, en bronze doré, me sert de terrain d'essai pour l'espace en relief. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG | L'Arrestation de saint Jean-Baptiste, Sienne, 1417-1427 | enchaîné 10]Dans *L'Arrestation de saint Jean-Baptiste*, j'essaie la perspective que Brunelleschi vient de découvrir : les soldats s'avancent dans un espace qui se creuse. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG | Saint Matthieu, Orsanmichele, Florence, 1419-1423 | enchaîné 10]Les banquiers me confient ensuite un *Saint Matthieu* : sa draperie tombe en plis larges, à la manière antique, et le gothique s'éloigne. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg | Saint Étienne, Orsanmichele, Florence, 1425-1429 | enchaîné 10]Pour les lainiers, mon *Saint Étienne* se tient déjà en équilibre, une hanche relevée, comme une statue romaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG | La Porte du Paradis, Florence, 1425-1452 | enchaîné 10]En 1425, on me confie la seconde porte. J'abandonne les quadrilobes : dix grands panneaux carrés, en bronze doré, pour l'Ancien Testament. Dans chacun, plusieurs épisodes d'une même histoire se déroulent dans un espace profond, les figures du premier plan presque détachées du fond, celles du lointain à peine effleurées. Il me faudra vingt-sept ans. Michel-Ange, dit-on, la jugea si belle qu'elle méritait d'être la porte du Paradis : le nom lui est resté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg | Châsse de saint Zénobe, Florence, 1432-1442 | enchaîné 10]Entre-temps, j'ai sculpté pour la cathédrale la châsse de saint Zénobe, premier évêque de Florence, dont les miracles se déroulent dans des architectures en perspective. Dans mes *Commentaires*, le premier récit de vie écrit par un artiste, je raconte mes maîtres, mes concurrents et l'atelier où Donatello a fait ses débuts, avec Paolo Uccello. [retour | 5]Je suis mort en 1455, après avoir passé presque toute ma vie sur deux portes.</t>
+        </is>
       </c>
       <c r="T230" s="10" t="s">
         <v>3576</v>
@@ -23535,8 +23554,10 @@
       <c r="I238" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S238" s="1" t="s">
-        <v>1684</v>
+      <c r="S238" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né vers 1510, sans doute en Normandie, et l'on ne sait presque rien de ma jeunesse : mon nom apparaît d'abord à Rouen, en 1540. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/Tombeau_de_Louis_de_Br%C3%A9z%C3%A9.jpg/960px-Tombeau_de_Louis_de_Br%C3%A9z%C3%A9.jpg | Bas-reliefs du tombeau de Louis de Brézé, cathédrale de Rouen, 1540-1542 | 5]À la cathédrale, on dit que j'ai travaillé au tombeau de Louis de Brézé, le mari de Diane de Poitiers : de l'albâtre blanc, du marbre noir, des figures fines. En 1544, à Paris, j'exécute pour le jubé de Saint-Germain-l'Auxerrois des reliefs si minces qu'on dirait du papier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg | Déploration du Christ, Louvre, 1544-1545 | enchaîné 10]Dans la *Déploration du Christ*, les saintes femmes s'inclinent, les plis de leurs robes coulent comme de l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg | Saint Jean, Louvre, 1544-1545 | enchaîné 10]*Saint Jean* a la même grâce, étirée, presque dansante. Je ne suis jamais allé en Italie ; pourtant on me compare aux maniéristes de Fontainebleau. J'ai illustré la première traduction française de Vitruve, et je travaille avec l'architecte Pierre Lescot. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg | Nymphe et Triton entourés de deux petits génies, Louvre, 1547-1549 | enchaîné 10]Pour la fontaine des Innocents, à Paris, je sculpte des nymphes en bas-relief, aux draperies mouillées qui collent à leur corps : on dirait que l'eau les a façonnées. Ici, *Nymphe et Triton*, aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Tribune-louvre_%283%29.jpg/1280px-Tribune-louvre_%283%29.jpg | Cariatides de la tribune, Louvre, 1547-1549 | enchaîné 10]Au Louvre, pour la nouvelle aile voulue par Henri II, ce sont mes *Cariatides* : quatre femmes de pierre qui soutiennent la tribune des musiciens, d'une élégance qui deviendra l'emblème de la Renaissance française. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg/960px-Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg | Cérès, Louvre, 1548-1550 | enchaîné 10]Toujours au Louvre, *Cérès*, déesse des moissons, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg | Le Départ de Phaéton, Chantilly, 1547-1550 | enchaîné 10]et *Le Départ de Phaéton*, qui est aujourd'hui à Chantilly : les chevaux du soleil emportent le fils d'Apollon. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg | Les Quatre Saisons, hôtel Carnavalet, Paris, 1555-1560 | enchaîné 10]Pour l'hôtel de Ligneris, aujourd'hui Carnavalet, *Les Quatre Saisons*. On dit que j'adhère aux idées de la Réforme ; dans la France des guerres de religion, ce n'est pas sans danger. [retour | 5]Ma trace se perd vers 1565, peut-être à Bologne, loin de la France que j'ai tant embellie.</t>
+        </is>
       </c>
       <c r="U238" s="5" t="s">
         <v>1682</v>
@@ -28515,8 +28536,10 @@
       <c r="I362" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S362" s="1" t="s">
-        <v>2363</v>
+      <c r="S362" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Paris vers 1528, fils d'un sculpteur, et j'ai appris l'art de Fontainebleau : des corps allongés, des visages fins, des plis qui ondulent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg | Monument du cœur d'Henri II, Louvre, 1559 | 5]Quand Henri II meurt en 1559, sa veuve, Catherine de Médicis, me confie le *Monument du cœur* du roi : trois figures de marbre, les Grâces, enlacées, dos à dos, portent sur leur tête l'urne où repose son cœur. Elles ont la grâce d'une danse. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg | Le Christ ressuscité, Louvre, 1565 environ | enchaîné 10]Mon *Christ ressuscité* garde la même élégance : un corps léger, une draperie qui s'envole. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG/1280px-Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG | Tombeau d'Henri II et de Catherine de Médicis, Saint-Denis, 1560-1573 | enchaîné 10]Catherine me commande ensuite le *Tombeau* d'Henri II et de Catherine, à Saint-Denis, sur des dessins de l'architecte Primatice. Je sculpte le roi et la reine deux fois : nus, couchés sur le sarcophage, dans la vérité crue de la mort ; [image: https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Henri_II_et_Catherine_de_M%C3%A9dicis.JPG/1280px-Henri_II_et_Catherine_de_M%C3%A9dicis.JPG | Gisants d'Henri II et de Catherine de Médicis, Saint-Denis, 1583 | enchaîné 10]et en haut, agenouillés et vêtus de leurs habits royaux, en prière. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Germain_Pilon_Vierge_et_enfant.jpg/960px-Germain_Pilon_Vierge_et_enfant.jpg | Vierge à l'Enfant, Le Mans, 1570 | enchaîné 10]Pour l'abbaye de la Couture, au Mans, une *Vierge à l'Enfant* de marbre, plus douce. Charles IX me nomme contrôleur général des effigies : je dirige les ateliers royaux, je modèle les visages des rois. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tombeau_Valentine_Balbiani_details_Pilon_LP397_MR1643.png/1280px-Tombeau_Valentine_Balbiani_details_Pilon_LP397_MR1643.png | Tombeau de Valentine Balbiani, Louvre, 1583 | enchaîné 10]Voici le *Tombeau de Valentine Balbiani*, épouse du chancelier René de Birague, avec une vérité de portrait qui saisit, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg | Tombeau du cardinal René de Birague, Louvre, 1585 | enchaîné 10]et celui du cardinal de Birague lui-même, en bronze. La France est alors déchirée par les guerres de religion, et mon art devient plus grave. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg | Vierge de douleur, Louvre, 1586 | enchaîné 10]Ma *Vierge de douleur*, en terre cuite peinte, lève un visage ruisselant de larmes : tout le maniérisme élégant de ma jeunesse a cédé la place à une émotion nue. [retour | 5]Je suis mort à Paris en 1590, considéré déjà comme le plus grand sculpteur français de mon siècle.</t>
+        </is>
       </c>
       <c r="U362" s="5" t="s">
         <v>2361</v>
@@ -30424,8 +30447,10 @@
       <c r="I412" s="7">
         <v>1</v>
       </c>
-      <c r="S412" s="1" t="s">
-        <v>2612</v>
+      <c r="S412" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né vers 1467 à Monte San Savino, en Toscane : c'est de cette petite ville que vient mon nom de Sansovino, mon vrai nom étant Contucci. On raconte que, enfant, je gardais les troupeaux en dessinant sur le sol, jusqu'au jour où le sculpteur Antonio Pollaiuolo m'a remarqué. J'ai passé près de dix ans au Portugal, au service du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Andrea_sansovino%2C_madonna_col_bambino%2C_1504%2C_01.JPG/960px-Andrea_sansovino%2C_madonna_col_bambino%2C_1504%2C_01.JPG | Vierge à l'Enfant, cathédrale San Lorenzo, Gênes, 1501-1502 | 5]À Gênes, pour la cathédrale, dans la chapelle de saint Jean-Baptiste, je sculpte en marbre une *Vierge à l'Enfant* d'une grande douceur, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/14/Andrea_sansovino%2C_giovanni_battista%2C_1504%2C_01.JPG/960px-Andrea_sansovino%2C_giovanni_battista%2C_1504%2C_01.JPG | Saint Jean-Baptiste, cathédrale San Lorenzo, Gênes, 1501-1502 | enchaîné 10]et un *Saint Jean-Baptiste* qui lui répond, simple et grave. [image: https://upload.wikimedia.org/wikipedia/commons/f/f6/Andrea_sansovino%2C_battesimo_di_cristo%2C_1502-05_%28con_restauri_di_v._danti_del_1569%29_e_angelo_di_innocenzo_spinazzi%2C_1792%2C_01.JPG | Baptême du Christ, Florence, 1502-1505 | enchaîné 10]À Florence, la ville me confie le *Baptême du Christ* pour le portail du baptistère : le Christ et saint Jean se font face, dans une sérénité qui annonce la Haute Renaissance. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Santa_Maria_del_Popolo_Presbyterium_Grabmal_Ascanio_Sforza.JPG/960px-Santa_Maria_del_Popolo_Presbyterium_Grabmal_Ascanio_Sforza.JPG | Tombeau d'Ascanio Sforza, Santa Maria del Popolo, Rome, 1505-1507 | enchaîné 10]Le pape Jules II m'appelle à Rome. Pour l'église Santa Maria del Popolo, je sculpte deux tombeaux de cardinaux. Voici celui d'Ascanio Sforza, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b6/Sansovino%2C_monumento_funebre_di_girolamo_basso_della_rovere_01.JPG/960px-Sansovino%2C_monumento_funebre_di_girolamo_basso_della_rovere_01.JPG | Tombeau de Girolamo Basso della Rovere, Santa Maria del Popolo, Rome, 1505-1507 | enchaîné 10]et celui de Girolamo Basso della Rovere. J'y invente un modèle : un arc de triomphe en marbre, où le défunt repose, la tête appuyée sur la main, comme endormi, sous une Vierge qui l'accueille. Pendant des générations, tous les tombeaux de Rome s'en inspireront. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/S_Agostino_Anna_selbtritt.jpg/960px-S_Agostino_Anna_selbtritt.jpg | La Vierge à l'Enfant avec sainte Anne, Sant'Agostino, Rome, 1512 | enchaîné 10]À Sant'Agostino, j'ai sculpté *La Vierge à l'Enfant avec sainte Anne* : trois figures liées dans un même bloc, où sainte Anne regarde sa fille et l'Enfant. Au-dessus, Raphaël a peint le prophète Isaïe, comme pour me répondre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/Andrea_sansovino%2C_annunciazione%2C_1523%2C_01.jpg/1280px-Andrea_sansovino%2C_annunciazione%2C_1523%2C_01.jpg | L'Annonciation, Lorette, 1513-1528 | enchaîné 10]À partir de 1513, à Lorette, je recouvre de marbre la Santa Casa, la maison de la Vierge, que les anges, selon la légende, ont transportée de Nazareth. J'y sculpte *L'Annonciation*, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Andrea_sansovino%2C_nativit%C3%A0_di_ges%C3%B9_e_annuncio_ai_pastori_01.jpg/1280px-Andrea_sansovino%2C_nativit%C3%A0_di_ges%C3%B9_e_annuncio_ai_pastori_01.jpg | La Nativité du Christ, Lorette, 1513-1528 | enchaîné 10]puis *La Nativité*, en haut-relief, et j'y travaille jusqu'à la fin de ma vie. Je suis mort en 1529, à Monte San Savino. [retour | 5]Mon élève Jacopo Tatti avait pris mon nom : il est devenu Jacopo Sansovino.</t>
+        </is>
       </c>
       <c r="U412" s="5" t="s">
         <v>2610</v>
@@ -30462,8 +30487,10 @@
       <c r="I413" s="7">
         <v>1</v>
       </c>
-      <c r="S413" s="1" t="s">
-        <v>2615</v>
+      <c r="S413" s="1" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Je suis né à Florence en 1486 sous le nom de Jacopo Tatti. Mon maître, Andrea Sansovino, m'a appris le marbre, et par admiration j'ai pris son nom. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg/960px-Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg | Saint Jacques, cathédrale de Florence, 1511-1518 | 5]À vingt-cinq ans, je sculpte pour la cathédrale de Florence un *Saint Jacques*, l'un des apôtres qui doivent encadrer la nef. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b9/Bacchus_by_Jacopo_Sansovino.jpg/1280px-Bacchus_by_Jacopo_Sansovino.jpg | Bacchus, Bargello, Florence, 1515 | enchaîné 10]Mon *Bacchus*, lui, est un jeune dieu nu, un peu ivre, qui lève sa coupe : Vasari dit qu'on le prenait pour de la chair vivante. Je pars pour Rome, je regarde Bramante, je regarde les statues antiques. En 1527, les soldats de l'empereur mettent Rome à sac ; je m'enfuis, et je m'arrête à Venise. Je comptais repartir pour la France : le doge Gritti me retient, et en 1529 je deviens l'architecte de la République. À Venise, je construis la Monnaie, la Bibliothèque de Saint-Marc, que Palladio dit la plus riche construction depuis l'Antiquité. En 1545, la voûte de la bibliothèque s'effondre : on me jette en prison, on me condamne à une amende ; Titien et l'Arétin, mes amis, plaident pour moi, et je reconstruis à mes frais. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Loggetta_Sansovino_Minerva_Venezia.jpg/960px-Loggetta_Sansovino_Minerva_Venezia.jpg | Minerve, Loggetta, Venise, 1537-1541 | enchaîné 10]Au pied du campanile de la place Saint-Marc, je bâtis la Loggetta, et j'y place quatre bronzes pour célébrer le bon gouvernement de Venise : *Minerve*, la sagesse, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Loggetta_Sansovino_Apollo_Venezia.jpg/960px-Loggetta_Sansovino_Apollo_Venezia.jpg | Apollon, Loggetta, Venise, 1537-1541 | enchaîné 10]*Apollon*, l'harmonie, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Loggetta_Sansovino_Mercurio_Venezia.jpg/960px-Loggetta_Sansovino_Mercurio_Venezia.jpg | Mercure, Loggetta, Venise, 1537-1541 | enchaîné 10]*Mercure*, l'éloquence, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Loggetta_Sansovino_allegoria_Pace_Venezia.jpg/960px-Loggetta_Sansovino_allegoria_Pace_Venezia.jpg | La Paix, Loggetta, Venise, 1537-1541 | enchaîné 10]et *La Paix*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG | Mars, escalier des Géants, Venise, 1554-1566 | enchaîné 10]Au palais des Doges, je dresse en haut de l'escalier des Géants deux colosses de marbre, *Mars*, le dieu de la guerre, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a0/Jacopo_sansovino%2C_nettuno%2C_1554%2C_04.jpg/330px-Jacopo_sansovino%2C_nettuno%2C_1554%2C_04.jpg | Neptune, escalier des Géants, Venise, 1554-1566 | enchaîné 10]et *Neptune*, le dieu de la mer : c'est entre eux que les doges sont couronnés. Venise règne alors sur la terre et sur les eaux. [retour | 5]Je suis mort en 1570, ayant fait de la place Saint-Marc ce que l'on voit encore.</t>
+        </is>
       </c>
       <c r="U413" s="5" t="s">
         <v>2610</v>
@@ -34249,7 +34276,7 @@
     <hyperlink ref="T348" r:id="rId277" xr:uid="{9BB270DC-5096-43E5-BA8C-D7469796998B}"/>
     <hyperlink ref="T333" r:id="rId278" xr:uid="{9980C49E-1986-481B-89F5-F1B7DFC18C63}"/>
     <hyperlink ref="T332" r:id="rId279" xr:uid="{189D77F4-2560-4DF7-BDE1-F9B0047B268D}"/>
-    <hyperlink ref="T230" r:id="rId280" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8b/Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg/960px-Lorenzo_Ghiberti%27s_Self_Portrait-The_Gates_of_Paradise_-_Original-Museo_dell%27Opera_del_Duomo.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{A85B84AC-FF33-4B24-B264-BB6A1736B87F}"/>
+    <hyperlink ref="T230" r:id="rId280" xr:uid="{28843888-6AE5-48A8-9403-E28B93F68D75}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\fichiers excel de la base\version 4 - corrections\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81E57A69-1E3A-4AF6-9D58-CBD70C24B560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86BF37D9-756B-4AAA-A12A-AF6F3377A8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1170" yWindow="420" windowWidth="13770" windowHeight="15060" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8786" uniqueCount="3577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8788" uniqueCount="3582">
   <si>
     <t>Prénom</t>
   </si>
@@ -13419,6 +13419,21 @@
   </si>
   <si>
     <t>https://upload.wikimedia.org/wikipedia/commons/b/bf/Ghiberti.png?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail_unscaled</t>
+  </si>
+  <si>
+    <t>Je suis né à Florence en 1500. [retour | 5]Mon père, musicien, voulait faire de moi un flûtiste ; j'ai préféré l'orfèvrerie, puis la sculpture, deux arts que je n'ai jamais séparés. Ma vie a ressemblé à un roman : chassé de Florence à seize ans après une rixe, artilleur lors du sac de Rome en 1527, prisonnier au château Saint-Ange d'où je me suis évadé, j'ai connu plusieurs duels, un meurtre, des fuites. J'ai tout raconté dans ma *Vie*, sans me ménager. [image: https://upload.wikimedia.org/wikipedia/commons/3/39/Saliera_Cellini_Vienna_18_04_2013_01_B.jpg | Salière de François Ier, Vienne, 1540-1543 | 5]François Ier m'a accueilli à Paris. Pour lui, j'ai achevé la *Salière*, en or et en émail : j'ai représenté Neptune, la mer, et la Terre, assise, jambes entrelacées ; j'ai donné une petite barque au sel et un petit temple au poivre. Le roi, a-t-on raconté, s'est écrié que c'était cent fois plus divin que tout ce qu'il avait imaginé. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/La_Nymphe_de_Fontainebleau_-_Benvenuto_Cellini_-_Musée_du_Louvre_Sculptures_MR_1706_;_N_15050.jpg | Nymphe de Fontainebleau, Louvre, 1542-1543 | enchaîné 10]Pour la porte du château de Fontainebleau, j'ai fondu la *Nymphe de Fontainebleau* en bronze : longue, allongée, le coude sur un cerf, d'une sensualité toute de ligne et de proportion. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/Bust_of_Cosimo_I_by_Benvenuto_Cellini.jpg | Buste de Cosme Ier de Médicis, Bargello, Florence, 1545-1548 | enchaîné 10]De retour à Florence, le duc Cosme Ier m'a pris pour son artiste : j'ai représenté Cosme en armure, le regard sûr, dans un *Buste* de bronze. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/Busto_di_Bindo_Altoviti.jpg | Buste de Bindo Altoviti, Boston, 1549 | enchaîné 10]J'ai aussi fait le *Buste* du banquier Bindo Altoviti, d'une élégance rare. [image: https://upload.wikimedia.org/wikipedia/commons/4/48/Firenze.Loggia.Perseus01.JPG | Persée avec la tête de Méduse, Loggia dei Lanzi, Florence, 1545-1554 | enchaîné 10]Pour la place de la Seigneurie, mon *Persée* a été ma plus grande fierté. Le soir de la fonte, la fournaise s'est éteinte ; j'ai jeté dans le métal toute la vaisselle d'étain de la maison, et le bronze a coulé jusqu'au bout. En 1554, le peuple s'est pressé devant la statue : des sonnets se sont accrochés aux piliers. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/Benvenuto_cellini_su_un_torso_antico%2C_ganimede%2C_1548%2C_02.jpg/500px-Benvenuto_cellini_su_un_torso_antico%2C_ganimede%2C_1548%2C_02.jpg | Ganymède, Bargello, Florence, 1545-1550 | enchaîné 10]J'ai restauré un torse antique en *Ganymède*, et j'y ai ajouté la tête, les bras, l'aigle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Benvenuto_cellini%2C_narciso%2C_1545-47%2C_01.jpg/500px-Benvenuto_cellini%2C_narciso%2C_1545-47%2C_01.jpg | Narcisse, Bargello, Florence, 1548-1565 environ | enchaîné 10]Puis j'ai fait s'incliner mon *Narcisse* sur lui-même, pour montrer que je savais aussi tailler le marbre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/Benvenuto_cellini%2C_crocifisso_di_marmo%2C_1556-1562%2C_03.jpg/960px-Benvenuto_cellini%2C_crocifisso_di_marmo%2C_1556-1562%2C_03.jpg | Crucifix de l'Escurial, 1559-1562 | enchaîné 10]Mon *Crucifix* de marbre blanc sur une croix de marbre noir, je l'avais destiné à ma propre tombe ; il a fini offert au roi d'Espagne, à l'Escurial. [retour | 5]Je suis mort en 1571, après avoir vécu avec la même flamboyance que mes œuvres, sans renoncer à mon orgueil ni à mon talent.</t>
+  </si>
+  <si>
+    <t>Je suis né à Florence en 1378 [retour | 5]et j'ai appris l'orfèvrerie auprès de mon beau-père : ciseler l'or, graver, fondre de petites pièces, c'est là que ma main s'est formée. [image: https://upload.wikimedia.org/wikipedia/commons/5/52/Wga_ghiberti_sacrifice_of_Isaac.jpg | Le Sacrifice d'Isaac, 1401 | 5]En 1401, j'ai vingt-deux ans quand les marchands de Florence ouvrent un concours pour les nouvelles portes de bronze du baptistère. Chaque candidat doit livrer le même panneau, le *Sacrifice d'Isaac*. Mon bronze, fondu d'un seul jet, est jugé le plus léger et le plus gracieux ; Brunelleschi, dit-on, refuse de partager la commande et s'en va. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG | Porte nord du baptistère, Florence, 1403-1424 | enchaîné 10]Je vais passer plus de vingt ans sur cette première porte : vingt-huit panneaux sur la vie du Christ, encadrés de quadrilobes comme dans les cathédrales gothiques, avec des figures souples, aux draperies fluides, dans l'élégance courtoise du gothique international. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG | Saint Jean-Baptiste, Orsanmichele, Florence, 1412-1416 | enchaîné 10]Dans le même temps, les marchands de drap me demandent pour Orsanmichele un *Saint Jean-Baptiste* : c'est la première grande statue de bronze de la Renaissance, et je dois apprendre le métier de fondeur à l'échelle d'un homme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg | Le Baptême du Christ, Sienne, 1417-1427 | enchaîné 10]À Sienne, pour les fonts baptismaux, je livre deux reliefs, aux côtés de Donatello et de Jacopo della Quercia. *Le Baptême du Christ*, en bronze doré, me sert de terrain d'essai pour l'espace en relief. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG | L'Arrestation de saint Jean-Baptiste, Sienne, 1417-1427 | enchaîné 10]Dans *L'Arrestation de saint Jean-Baptiste*, j'essaie la perspective que Brunelleschi vient de découvrir : les soldats s'avancent dans un espace qui se creuse. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG | Saint Matthieu, Orsanmichele, Florence, 1419-1423 | enchaîné 10]Les banquiers me confient ensuite un *Saint Matthieu* : sa draperie tombe en plis larges, à la manière antique, et le gothique s'éloigne. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg | Saint Étienne, Orsanmichele, Florence, 1425-1429 | enchaîné 10]Pour les lainiers, mon *Saint Étienne* se tient déjà en équilibre, une hanche relevée, comme une statue romaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG | La Porte du Paradis, Florence, 1425-1452 | enchaîné 10]En 1425, on me confie la seconde porte. J'abandonne les quadrilobes : dix grands panneaux carrés, en bronze doré, pour l'Ancien Testament. Dans chacun, plusieurs épisodes d'une même histoire se déroulent dans un espace profond, les figures du premier plan presque détachées du fond, celles du lointain à peine effleurées. Il me faudra vingt-sept ans. Michel-Ange, dit-on, la jugea si belle qu'elle méritait d'être la porte du Paradis : le nom lui est resté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg | Châsse de saint Zénobe, Florence, 1432-1442 | enchaîné 10]Entre-temps, j'ai sculpté pour la cathédrale la châsse de saint Zénobe, premier évêque de Florence, dont les miracles se déroulent dans des architectures en perspective. Dans mes *Commentaires*, le premier récit de vie écrit par un artiste, je raconte mes maîtres, mes concurrents et l'atelier où Donatello a fait ses débuts, avec Paolo Uccello. [retour | 5]Je suis mort en 1455, après avoir passé presque toute ma vie sur deux portes.</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Andrea_del_sarto%2C_Devozione_dei_fiorentini_alle_reliquie_di_san_Filippo%2C_1510%2C_08_vecchio%2C_ritratto_di_andrea_della_robbia_-_dett.jpg/960px-Andrea_del_sarto%2C_Devozione_dei_fiorentini_alle_reliquie_di_san_Filippo%2C_1510%2C_08_vecchio%2C_ritratto_di_andrea_della_robbia_-_dett.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
+  </si>
+  <si>
+    <t>Je suis né à Florence en 1435 [retour | 5]et mon oncle Luca m'a pris dans son atelier, où il m'a confié son secret : la terre cuite émaillée, blanche et bleue. Luca est mort en 1482 ; j'ai dû faire vivre l'entreprise. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg/960px-Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg | L'Adoration de l'Enfant, Washington, après 1477 | 5]J'ai élargi la palette : à côté du blanc et du bleu, j'ai glissé du vert, du jaune, du violet, pour peindre les feuilles et les fruits des guirlandes qui encadraient mes tableaux. J'ai fait *L'Adoration de l'Enfant* : j'ai agenouillé la Vierge devant le Christ nu, et j'ai ajouté des anges et une guirlande de fruits. Mes figures sont devenues plus tendres, plus familières que celles de mon oncle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg | L'Annonciation, La Verna, 1475 | enchaîné 10]À La Verna, là où saint François avait reçu les stigmates, j'ai livré une *Annonciation* : j'ai placé l'ange et la Vierge face à face dans un blanc éclatant, sur un fond d'azur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Autel des Médicis, Santa Croce, Florence, 1475-1480 | enchaîné 10]À Santa Croce, dans la chapelle des Médicis, j'ai réalisé un autel en haut-relief : la terre cuite émaillée est entrée dans l'église des grandes familles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg | Retable de la Trinité, Arezzo, 1484 | enchaîné 10]À Arezzo, pour la cathédrale, j'ai fait un retable de la *Trinité*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG | Tondi de l'Hôpital des Innocents, Florence, 1487 environ | enchaîné 10]Pour l'Hôpital des Innocents, dessiné par Brunelleschi, j'ai modelé des médaillons : des nourrissons emmaillotés sur un fond bleu, pour rappeler que cette maison recueillait les enfants abandonnés. Ces médaillons sont devenus les images les plus connues de ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg | Lunette de la Vierge entre saint Étienne et saint Laurent, Prato, 1489 | enchaîné 10]À Prato, au-dessus d'une porte de la cathédrale, j'ai fait une lunette : la Vierge entre saint Étienne et saint Laurent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG | Lunette de la Vierge à l'Enfant et anges, Florence, 1489 | enchaîné 10]Pour la cathédrale de Florence, j'ai fait une autre lunette, avec la Vierge, l'Enfant et des anges. L'atelier a travaillé sans relâche : les paroisses toscanes, qui ne pouvaient pas payer le marbre, ont acheté notre terre cuite. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg | Vierge au coussin, Séville, 1520 | enchaîné 10]Vers 1520, j'étais un vieil homme et ma *Vierge au coussin* a pris la mer pour l'Espagne, jusqu'à la cathédrale de Séville. Mes fils Giovanni, Luca le Jeune et Girolamo ont repris l'atelier ; Girolamo est parti en France, travailler pour François Ier. Je suis mort en 1525, presque nonagénaire. [retour | 5]</t>
+  </si>
+  <si>
+    <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Pincio_-_busti_-_Della_Robbia_1270989.JPG/960px-Pincio_-_busti_-_Della_Robbia_1270989.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail</t>
   </si>
 </sst>
 </file>
@@ -14792,10 +14807,8 @@
       <c r="I23" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S23" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né à Florence en 1493, fils d'un orfèvre, et j'ai rêvé de devenir plus grand que Michel-Ange. Tout mon malheur est là. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e2/2793_-_Firenze_-_Palazzo_Medici_Riccardi_-_Baccio_Bandinelli%2C_Orfeo_e_Cerbero_%281519%29_-_Foto_Giovanni_Dall%27Orto%2C_27-Oct-2007.jpg/960px-2793_-_Firenze_-_Palazzo_Medici_Riccardi_-_Baccio_Bandinelli%2C_Orfeo_e_Cerbero_%281519%29_-_Foto_Giovanni_Dall%27Orto%2C_27-Oct-2007.jpg | Orphée charmant Cerbère, Palazzo Medici-Riccardi, Florence, 1519 | 5]Pour le cardinal Jules de Médicis, le futur pape Clément VII, je sculpte en 1519 *Orphée charmant Cerbère* : le poète joue de sa lyre, le chien à trois têtes l'écoute, apaisé. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2f/Baccio_Bandinelli_%28dall%27antico%29%2C_Gruppo_del_Laocoonte%2C_1523-25_ca._02.jpg/960px-Baccio_Bandinelli_%28dall%27antico%29%2C_Gruppo_del_Laocoonte%2C_1523-25_ca._02.jpg | Laocoon, copie du groupe antique, Offices, Florence, 1520-1525 | enchaîné 10]Le même cardinal me demande ensuite une copie du *Laocoon*, découvert à Rome quelques années plus tôt, destinée au roi de France. Je l'achève ; les Médicis la gardent, et elle est aujourd'hui aux Offices. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/bf/Hercule_et_Cacus_Bandinelli_Florence_Signoria.jpg/1280px-Hercule_et_Cacus_Bandinelli_Florence_Signoria.jpg | Hercule et Cacus, Piazza della Signoria, Florence, 1525-1534 | enchaîné 10]En 1525, on me confie un énorme bloc de marbre, destiné d'abord à Michel-Ange : un *Hercule et Cacus*. On raconte que j'ai intrigué auprès du pape pour l'obtenir. Mon groupe est installé en 1534, place de la Seigneurie, tout près du *David* de mon rival, et Florence se moque : Cellini dit qu'il ressemble à un sac de melons, des poèmes satiriques s'accrochent à ses pieds. Je n'ai jamais pardonné. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/eb/Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg/1280px-Baccio_bandinelli%2C_busto_di_cosimo_I%2C_1554-58_%28palatina%29_01.jpg | Buste de Cosme Ier de Médicis, Palais Pitti, Florence, 1554-1558 | enchaîné 10]Quand les Médicis reviennent en maîtres, le duc Cosme Ier devient mon grand protecteur : voici son *Buste*, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Baccio_bandinelli%2C_cosimo_I.JPG/960px-Baccio_bandinelli%2C_cosimo_I.JPG | Monument à Cosme Ier de Médicis, Palazzo Vecchio, Florence, 1547-1572 | enchaîné 10]puis son *Monument*, que je continue jusqu'à ma mort. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg/500px-Baccio_bandinelli%2C_bacco%2C_1547-49_%28palatina%29_02.jpg | Bacchus, Palais Pitti, Florence, 1547-1549 | enchaîné 10]Pour son palais, un *Bacchus*, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg/960px-Baccio_bandinelli%2C_adamo_ed_eva%2C_dal_recinto_del_coro_di_s.m._del_fiore%2C_1551_%28bargello%29_00.jpg | Adam et Ève, Bargello, Florence, 1554-1559 | enchaîné 10]et pour la cathédrale, un *Adam et Ève* en marbre, deux corps nus qui s'appuient sur une étude minutieuse de l'anatomie : mes élèves ne s'en lassent pas, mes ennemis se moquent. J'ai ouvert une académie de dessin : j'y forme des élèves qui deviendront célèbres. Mon style est froid, plus savant que sensible. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/Baccio_bandinelli%2C_piet%C3%A0_per_la_propria_tomba.JPG/960px-Baccio_bandinelli%2C_piet%C3%A0_per_la_propria_tomba.JPG | Pietà, Santissima Annunziata, Florence, 1559 | enchaîné 10]Pour ma propre chapelle, à la Santissima Annunziata, je sculpte une *Pietà* : sous les traits de Nicodème, c'est mon visage. En 1559, Cosme lance le concours de la fontaine de Neptune : c'est Ammannati, mon élève, qui l'emporte, avec le marbre que j'avais commencé. [retour | 5]Je suis mort en 1560, à Florence, et je repose sous ma Pietà.</t>
-        </is>
+      <c r="S23" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="T23" s="1" t="s">
         <v>209</v>
@@ -16077,10 +16090,8 @@
       <c r="I54" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S54" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né en 1529 à Douai, en Flandre, et je m'appelle Jean de Boulogne ; en Italie, on dira Giambologna. J'ai appris à Anvers, puis, en 1550, à Rome, j'ai regardé l'antique et Michel-Ange. Au retour, je m'arrête à Florence : un riche amateur, Bernardo Vecchietti, me retient, me présente aux Médicis, et je n'en repartirai plus. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b0/Giambologna%2C_bacco%2C_1560_ca.%2C_dalle_collezioni_medicee_poi_su_una_fontana_in_borgo_s._jacopo%2C_01.jpg/500px-Giambologna%2C_bacco%2C_1560_ca.%2C_dalle_collezioni_medicee_poi_su_una_fontana_in_borgo_s._jacopo%2C_01.jpg | Bacchus, Bargello, Florence, 1560-1562 | 5]Mon *Bacchus* est un jeune dieu à demi renversé, qui lève sa coupe : on le regarde de face, on tourne autour de lui. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1d/%28Bologna%29_-_Fontana_del_Nettuno.jpg/960px-%28Bologna%29_-_Fontana_del_Nettuno.jpg | Fontaine de Neptune, Bologne, 1564-1566 | enchaîné 10]À Bologne, sur la place, je fonds la *Fontaine de Neptune* : le dieu, nu, bras tendu, domine des nymphes et des dauphins. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg/960px-Firenze_vittoriosa_su_Pisa%2C_Giambologna%2C_Francavilla%2C_1575-80%2C_Bargello_Florenz-01.jpg | Florence triomphant de Pise, Bargello, Florence, 1567-1570 | enchaîné 10]*Florence triomphant de Pise* est une femme debout, qui domine un captif à genoux : un seul bloc, plusieurs points de vue. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/5/5d/Giambologna_raptodasabina.jpg/1280px-Giambologna_raptodasabina.jpg | L'Enlèvement des Sabines, Loggia dei Lanzi, Florence, 1579-1583 | enchaîné 10]Mon plus grand défi est *L'Enlèvement des Sabines* : trois corps, un homme, une femme, un vieillard, taillés dans un seul bloc, qui montent en spirale. Je ne lui avais donné aucun sujet : c'est après coup qu'on lui a trouvé ce titre. Ce qui m'importe, c'est qu'on puisse le regarder de tous côtés. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg/500px-Mercurio_volante%2C_Giambologna%2C_Bargello_Florenz-01.jpg | Mercure volant, Bargello, Florence, 1580 | enchaîné 10]Mon *Mercure volant* tient sur la pointe d'un pied, porté par le souffle du vent : les princes d'Europe s'en arrachent les copies. [image: https://upload.wikimedia.org/wikipedia/commons/d/da/Appennino.jpg | Colosse de l'Apennin, Pratolino, 1579-1583 | enchaîné 10]À Pratolino, pour le prince François, un colosse de pierre, l'*Apennin* : un géant de dix mètres, accroupi, dont le corps est creusé de grottes et de fontaines. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/60/Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg/960px-Giambologna%2C_monumento_equestre_a_cosimo_I%2C_1587-1594%2C_01.jpg | Monument équestre de Cosme Ier de Médicis, Florence, 1594 | enchaîné 10]Après la mort de Cosme Ier, je fonds son *Monument équestre*, place de la Seigneurie. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/9a/Herakles_Nessos_Loggia_dei_Lanzi_2005_09_13.jpg/960px-Herakles_Nessos_Loggia_dei_Lanzi_2005_09_13.jpg | Hercule et le centaure Nessus, Loggia dei Lanzi, Florence, 1595-1600 | enchaîné 10]Puis *Hercule et le centaure Nessus*, deux corps en lutte, à la loge des Lanzi. Mon atelier est une ruche : Pietro Tacca, mon fidèle assistant, et Antonio Susini diffusent mon style en petits bronzes dans toute l'Europe. [retour | 5]Je suis mort à Florence en 1608, flamand de naissance, florentin de cœur.</t>
-        </is>
+      <c r="S54" s="1" t="s">
+        <v>457</v>
       </c>
       <c r="T54" s="1" t="s">
         <v>458</v>
@@ -16942,10 +16953,8 @@
       <c r="I75" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S75" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">On m'a surnommé *il Divino*. Je suis né en 1475 à Caprese, en Toscane, et je suis confié à une nourrice de Settignano, femme d'un tailleur de pierre : je dis souvent que j'ai sucé le ciseau avec le lait. À treize ans, j'entre chez le peintre Ghirlandaio, puis dans le jardin de Laurent de Médicis, où je copie les statues antiques. Un camarade, Torrigiano, me casse le nez d'un coup de poing : je garderai ce nez toute ma vie. À vingt-quatre ans, j'ai déjà sculpté à Rome la *Pietà* de Saint-Pierre. [image: https://upload.wikimedia.org/wikipedia/commons/3/37/Madonna_michelangelo.jpg | Vierge de Bruges, église Notre-Dame, Bruges, 1501-1504 | 5]Voici la *Vierge de Bruges* : une Madone sereine, qui tient son enfant entre ses genoux, destinée à des marchands flamands. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/a/a0/%27David%27_by_Michelangelo_Fir_JBU002.jpg/1280px-%27David%27_by_Michelangelo_Fir_JBU002.jpg | David, Galerie de l'Académie, Florence, 1501-1504 | enchaîné 10]De retour à Florence en 1501, la ville me confie un bloc de marbre abandonné depuis vingt-cinq ans, que deux sculpteurs avaient renoncé à tailler. J'y vois un géant. Trois ans plus tard, le *David* est dressé devant le Palazzo Vecchio : non plus le jeune vainqueur de Donatello, mais le héros avant le combat, tendu, qui regarde l'ennemi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1c/%27Moses%27_by_Michelangelo_JBU010.jpg/960px-%27Moses%27_by_Michelangelo_JBU010.jpg | Tombeau de Jules II, Saint-Pierre-aux-Liens, Rome, 1505-1545 | enchaîné 10]En 1505, le pape Jules II me commande son tombeau : quarante statues, un monument grand comme une maison. Je pars à Carrare choisir les blocs ; le pape change d'avis, me charge du plafond de la Sixtine. Le tombeau me poursuivra quarante ans, et il ne sera jamais celui que j'avais rêvé ; il aura quand même son *Moïse*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e7/0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG/960px-0_l%E2%80%99Esclave_mourant_-_Michelangelo_-_MR_1590_-_Louvre_2.JPG | L'Esclave mourant, Louvre, 1513 | enchaîné 10]Pour le premier projet, j'ai sculpté des Esclaves : le *Mourant*, qui s'abandonne, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/%27Rebellious_Slave%27_Michelangelo_JBU81.jpg/960px-%27Rebellious_Slave%27_Michelangelo_JBU81.jpg | L'Esclave rebelle, Louvre, 1513 | enchaîné 10]et le *Rebelle*, qui se débat contre ses liens. Ils partiront en France, et ils sont aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg/960px-Christ_-_Michelangelo_Buonarroti_-_Sta_Maria_sopra_Minerva_-_Rome.jpg | Le Christ de la Minerve, Rome, 1519-1521 | enchaîné 10]À Rome, mon *Christ de la Minerve* est un Christ nu, dressé, tenant sa croix : on lui a ajouté plus tard un voile de bronze par pudeur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg/960px-The_Sagrestia_Nuova_at_the_Medici_Chapel_-_48169937026.jpg | Tombeau de Laurent de Médicis, chapelles des Médicis, Florence, 1520-1534 | enchaîné 10]À Florence, pour les Médicis, je travaille à la sacristie de San Lorenzo : voici le *Tombeau de Laurent*, duc d'Urbin, avec l'Aurore et le Crépuscule ; en face, celui de son frère Julien porte le Jour et la Nuit. À un poète qui trouvait ma Nuit trop vivante, j'ai fait répondre qu'il m'est doux de dormir, et plus doux encore d'être de pierre, tant que dure la honte. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4c/The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg/960px-The_Florentine_Piet%C3%A0%2C_Museo_dell%27Opera_del_Duomo_-_48199237196.jpg | Pietà Bandini, Florence, 1547-1555 | enchaîné 10]Dans ma *Pietà Bandini*, destinée à ma propre tombe, Nicodème qui soutient le Christ a mon visage. Mécontent d'un défaut du marbre, je l'ai brisée à coups de marteau ; un élève l'a recomposée. [retour | 5]Je suis mort à Rome en 1564, presque nonagénaire, et Florence a ramené mon corps pour l'enterrer à Santa Croce.</t>
-        </is>
+      <c r="S75" s="1" t="s">
+        <v>608</v>
       </c>
       <c r="T75" s="1" t="s">
         <v>609</v>
@@ -17644,10 +17653,8 @@
       <c r="I92" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S92" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né à Florence en 1500. Mon père, musicien, voulait faire de moi un flûtiste ; j'ai préféré l'orfèvrerie, puis la sculpture, deux arts que je n'ai jamais séparés. Ma vie ressemble à un roman : chassé de Florence à seize ans après une rixe, artilleur lors du sac de Rome en 1527, prisonnier au château Saint-Ange d'où je m'évade, plusieurs duels, un meurtre, des fuites. J'ai tout raconté dans ma *Vie*, sans me ménager. [image: https://upload.wikimedia.org/wikipedia/commons/3/39/Saliera_Cellini_Vienna_18_04_2013_01_B.jpg | Salière de François Ier, Vienne, 1540-1543 | 5]François Ier m'accueille à Paris. Pour lui, j'achève la *Salière*, en or et en émail : Neptune, la mer, et la Terre, assise, jambes entrelacées ; une petite barque porte le sel, un petit temple le poivre. Le roi, raconte-t-on, s'écria que c'était cent fois plus divin que tout ce qu'il avait imaginé. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/La_Nymphe_de_Fontainebleau_-_Benvenuto_Cellini_-_Musée_du_Louvre_Sculptures_MR_1706_;_N_15050.jpg | Nymphe de Fontainebleau, Louvre, 1542-1543 | enchaîné 10]Pour la porte du château de Fontainebleau, je fonds la *Nymphe de Fontainebleau* en bronze : longue, allongée, le coude sur un cerf, d'une sensualité toute de ligne et de proportion. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/Bust_of_Cosimo_I_by_Benvenuto_Cellini.jpg | Buste de Cosme Ier de Médicis, Bargello, Florence, 1545-1548 | enchaîné 10]De retour à Florence, le duc Cosme Ier me prend pour son artiste : mon *Buste* de bronze le montre en armure, le regard sûr. [image: https://commons.wikimedia.org/wiki/Special:Redirect/file/Busto_di_Bindo_Altoviti.jpg | Buste de Bindo Altoviti, Boston, 1549 | enchaîné 10]Et voici le banquier Bindo Altoviti, dont j'ai fait le *Buste*, d'une élégance rare. [image: https://upload.wikimedia.org/wikipedia/commons/4/48/Firenze.Loggia.Perseus01.JPG | Persée avec la tête de Méduse, Loggia dei Lanzi, Florence, 1545-1554 | enchaîné 10]Pour la place de la Seigneurie, mon *Persée* est ma plus grande fierté. Le soir de la fonte, la fournaise s'éteint ; je jette dans le métal toute la vaisselle d'étain de la maison, et le bronze coule jusqu'au bout. En 1554, le peuple se presse devant la statue : des sonnets s'accrochent aux piliers. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/Benvenuto_cellini_su_un_torso_antico%2C_ganimede%2C_1548%2C_02.jpg/500px-Benvenuto_cellini_su_un_torso_antico%2C_ganimede%2C_1548%2C_02.jpg | Ganymède, Bargello, Florence, 1545-1550 | enchaîné 10]Je restaure un torse antique en *Ganymède*, et j'y ajoute la tête, les bras, l'aigle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/aa/Benvenuto_cellini%2C_narciso%2C_1545-47%2C_01.jpg/500px-Benvenuto_cellini%2C_narciso%2C_1545-47%2C_01.jpg | Narcisse, Bargello, Florence, 1548-1565 environ | enchaîné 10]Puis mon *Narcisse* s'incline sur lui-même, pour montrer que je sais aussi tailler le marbre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d0/Benvenuto_cellini%2C_crocifisso_di_marmo%2C_1556-1562%2C_03.jpg/960px-Benvenuto_cellini%2C_crocifisso_di_marmo%2C_1556-1562%2C_03.jpg | Crucifix de l'Escurial, 1559-1562 | enchaîné 10]Mon *Crucifix* de marbre blanc sur une croix de marbre noir, je le destinais à ma propre tombe ; il finira offert au roi d'Espagne, à l'Escurial. [retour | 5]Je suis mort en 1571, ayant vécu avec la même flamboyance que mes œuvres, sans renoncer à mon orgueil ni à mon talent.</t>
-        </is>
+      <c r="S92" s="1" t="s">
+        <v>3577</v>
       </c>
       <c r="T92" s="1" t="s">
         <v>732</v>
@@ -18246,11 +18253,8 @@
       <c r="I107" s="7">
         <v>3</v>
       </c>
-      <c r="S107" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né en 1801 à Bolton, dans le Lancashire. À mes dix-sept ans, ma famille a émigré aux États-Unis. J'ai appris à peindre seul, en parcourant les collines et les forêts de l'État de New York.
-[image: https://upload.wikimedia.org/wikipedia/commons/f/fa/Cole_Thomas_Lake_with_Dead_Trees_%28Catskill%29_1825.jpg | Lac aux arbres morts, 1825 | enchaîné 5]À l'été 1825, j'ai exposé dans une vitrine de New York des vues des monts Catskill. Elles ont été remarquées, achetées, admirées. C'était le début de l'école du fleuve [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Oxbow_%28The_Connecticut_River_near_Northampton_1836%29.jpg | Vue depuis le mont Holyoke, après un orage — The Oxbow., 1836 | enchaîné 10]Hudson, dont on m'a appelé le fondateur. Frédéric Edwin Church, mon ami,  et, plus tard, Albert Bierstadt en ont fait partie. J'ai peint la nature américaine, sauvage et grandiose.  J'ai imaginé aussi des allégories à travers des grands cycles. Le premier, *La Vie humaine*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole_-_The_Voyage_of_Life_Childhood%2C_1842_%28National_Gallery_of_Art%29FXD.jpg | Le Voyage de la vie : L'Enfance, 1842 | enchaîné 10] est une série de quatre tableaux où un voyageur navigue sur une rivière dont les changements évoquent les différentes étapes de l'existence. Le second, *Le Cours de l'Empire*, [image: https://commons.wikimedia.org/wiki/Special:FilePath/Cole_Thomas_The_Architect-s_Dream_1840.jpg | Le Rêve de l'Architecte, 1840 | enchaîné 10] est constitué de cinq tableaux qui décrivent la naissance et le déclin d'une civilisation imaginaire. J'ai voulu mettre en garde mes contemporains [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/77/Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg/1280px-Cole_Thomas_The_Course_of_Empire_Desolation_1836.jpg | Le Cours de l'Empire, La Désolation, 1836 | enchaîné 10] en peignant les ravages possibles sur la Nature et la Civilisation d'une course effrénée vers une société industrielle [image: https://commons.wikimedia.org/wiki/Special:FilePath/Thomas_Cole%2C_The_Departure%2C_1837%2C_NGA_166439.jpg | Le Départ, 1837 | enchaîné 10]et marchande.  J'ai été un des pionniers du mouvement environnementaliste. Je me suis installé à Catskill, où je suis mort en 1848, à quarante-sept ans. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/7/79/Gibbon_River_at_Madison_in_Yellowstone.JPG/1280px-Gibbon_River_at_Madison_in_Yellowstone.JPG | La rivière Gibbon dans le parc de Yellowstone. | enchaîné 10]Mes convictions écologistes ont ouvert la voie à la création des grands parcs nationaux américains comme celui de Yellowstone. Je crois cette voie prometteuse pour [retour | 5]l'avenir de l'Amérique.</t>
-        </is>
+      <c r="S107" s="1" t="s">
+        <v>832</v>
       </c>
       <c r="T107" s="1" t="s">
         <v>833</v>
@@ -20937,10 +20941,11 @@
       <c r="I174" s="7">
         <v>1</v>
       </c>
-      <c r="S174" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né à Florence en 1435 et mon oncle Luca m'a pris dans son atelier, où il m'a confié son secret : la terre cuite émaillée, blanche et bleue. Luca est mort en 1482 ; à moi de faire vivre l'entreprise. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/83/Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg/960px-Andrea_della_Robbia%2C_The_Adoration_of_the_Child%2C_after_1477%2C_NGA_46082.jpg | L'Adoration de l'Enfant, Washington, après 1477 | 5]J'élargis la palette : à côté du blanc et du bleu, je glisse du vert, du jaune, du violet, pour peindre les feuilles et les fruits des guirlandes qui encadrent mes tableaux. Ici, *L'Adoration de l'Enfant* : la Vierge à genoux devant le Christ nu, des anges, une guirlande de fruits. Mes figures sont plus tendres, plus familières que celles de mon oncle. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/53/Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg/1280px-Andrea_della_Robbia%2C_Annunciazione%2C_1475_circa_%2802%29.jpg | L'Annonciation, La Verna, 1475 | enchaîné 10]À La Verna, là où saint François a reçu les stigmates, je livre une *Annonciation* : l'ange et la Vierge se font face dans un blanc éclatant, sur un fond d'azur. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a7/Altar_Medici.JPG/1280px-Altar_Medici.JPG | Autel des Médicis, Santa Croce, Florence, 1475-1480 | enchaîné 10]À Santa Croce, dans la chapelle des Médicis, je réalise un autel en haut-relief : la terre cuite émaillée entre dans l'église des grandes familles. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg/1280px-Andrea_e_Giovanni_della_Robbia%2C_Ges%C3%B9_e_la_Vergine_intercedono_presso_l%27Eterno%2C_1495-1500_%2801%29.jpg | Retable de la Trinité, Arezzo, 1484 | enchaîné 10]À Arezzo, pour la cathédrale, un retable de la *Trinité*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG/1280px-Spedale_degli_innocenti%2C_tondo_andrea_della_robbia_12-13.JPG | Tondi de l'Hôpital des Innocents, Florence, 1487 environ | enchaîné 10]Pour l'Hôpital des Innocents, dessiné par Brunelleschi, je modèle des médaillons : des nourrissons emmaillotés sur un fond bleu, qui rappellent que cette maison recueille les enfants abandonnés. Ce sont les images les plus connues de ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg/1280px-Andrea_della_robbia%2C_madonna_col_bambino_tra_i_ss._stefano_e_lorenzo_e_cherubini%2C_1489%2C_01.jpg | Lunette de la Vierge entre saint Étienne et saint Laurent, Prato, 1489 | enchaîné 10]À Prato, au-dessus d'une porte de la cathédrale, une lunette : la Vierge entre saint Étienne et saint Laurent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2b/Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG/1280px-Andrea_della_robbia%2C_lunetta_con_la_madonna_col_bambino_e_angeli%2C_1489.JPG | Lunette de la Vierge à l'Enfant et anges, Florence, 1489 | enchaîné 10]Pour la cathédrale de Florence, une autre lunette, avec la Vierge, l'Enfant et des anges. L'atelier travaille sans relâche : les paroisses toscanes, qui ne peuvent pas payer le marbre, achètent notre terre cuite. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Della-Robbia-Sevilla1.jpg/960px-Della-Robbia-Sevilla1.jpg | Vierge au coussin, Séville, 1520 | enchaîné 10]Vers 1520, je suis un vieil homme et ma *Vierge au coussin* a pris la mer pour l'Espagne, jusqu'à la cathédrale de Séville. Mes fils Giovanni, Luca le Jeune et Girolamo ont repris l'atelier ; Girolamo est parti en France, travailler pour François Ier. [retour | 5]Je suis mort en 1525, presque nonagénaire.</t>
-        </is>
+      <c r="S174" s="1" t="s">
+        <v>3580</v>
+      </c>
+      <c r="T174" s="10" t="s">
+        <v>3579</v>
       </c>
       <c r="U174" s="5" t="s">
         <v>1263</v>
@@ -20979,8 +20984,11 @@
       </c>
       <c r="S175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né à Florence en 1399, et j'ai d'abord appris l'orfèvrerie avant de sculpter le marbre. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | La Cantoria, Florence, 1431-1438 | 5]En 1431, la cathédrale me confie sa *Cantoria*, la tribune des chanteurs : sur dix panneaux de marbre, des enfants chantent, jouent du luth, de la harpe, des cymbales, dansent, comme le psaume qui appelle à louer Dieu par la musique. Donatello fait au même moment la sienne, plus agitée, plus sauvage ; la mienne est plus claire, plus sereine. Mais c'est une autre invention qui va faire ma réputation. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | La Résurrection, Florence, 1442-1444 | enchaîné 10]Au-dessus de la porte de la sacristie, je modèle *La Résurrection* en terre cuite, puis je la recouvre d'une glaçure d'étain, blanche, brillante, qui ne s'altère pas : le Christ blanc sort du tombeau sur un fond bleu intense. Je tiens la recette secrète, je ne la confie qu'à ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | Vierge à la pomme, Bargello, Florence, 1442-1444 | enchaîné 10]La terre cuite émaillée me permet de produire plus vite et à moindre coût que le marbre : voici une *Vierge à la pomme*, douce et grave, qui tient son enfant contre sa joue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | Vierge à l'Enfant avec trois chérubins, Louvre, 1450 environ | enchaîné 10]Mes Vierges à l'Enfant se retrouvent dans toute la Toscane, et jusque dans les collections royales : celle-ci, avec trois chérubins, est aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg | Vierge à l'Enfant, Bargello, Florence, 1450 environ | enchaîné 10]Celle-ci, au Bargello, est plus simple encore : deux visages, un bleu, un blanc, et tout est dit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | Tabernacle de la Sainte Croix, Impruneta, 1445-1450 | enchaîné 10]À Impruneta, le *Tabernacle de la Sainte Croix* mêle bas-relief et haut-relief en terre cuite émaillée : des anges portent des cierges, des enfants soutiennent des guirlandes. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | Porte de bronze de la sacristie, Florence, 1446-1475 | enchaîné 10]Je n'ai pas abandonné le bronze : avec Michelozzo et Maso di Bartolomeo, je réalise la *Porte de la sacristie* de la cathédrale, dix panneaux de saints, de docteurs et d'anges, qui m'occuperont longtemps. [image: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | Les Quatre Vertus cardinales, San Miniato al Monte, Florence, 1461-1466 | enchaîné 10]À San Miniato, dans la chapelle du cardinal de Portugal, j'orne le plafond des *Quatre Vertus cardinales* : la Prudence, la Justice, la Tempérance et la Force entourent le Saint-Esprit. [retour | 5]Je suis mort en 1482, et c'est mon neveu Andrea qui a gardé le secret après moi.</t>
+          <t xml:space="preserve">Je suis né à Florence en 1399, [retour | 5] [image: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | Pianta della Catena, 1490 | 5]et j'ai d'abord appris l'orfèvrerie avant de sculpter [incrust: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | inclusion | detail 50 36.3 3.4 | enchaîné 5]le marbre. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | La Cantoria, Florence, 1431-1438 | enchaîné 10] En 1431, la cathédrale me [incrust-fin]confie sa *Cantoria*, la tribune des chanteurs : sur dix panneaux de marbre, des enfants chantent, [incrust: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | inclusion | detail 46.2 32.5 3.2 | enchaîné 5]jouent du luth, de la harpe, des cymbales, dansent, comme le psaume qui appelle à louer Dieu par la musique. [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG/1280px-Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG | juxtaposition | cadre 77.6 49.2 44.5 | principale 31.8 48.3 70.6 | enchaîné 5] [incrust-fin]Donatello fait au même moment la sienne, plus agitée, plus sauvage [incrust-fin]; la mienne est plus claire, plus sereine. Mais c'est une autre invention qui va faire ma réputation. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | La Résurrection, Florence, 1442-1444 | enchaîné 10] Au-dessus de la porte de la sacristie, je modèle *La Résurrection* en terre cuite, puis je la recouvre d'une glaçure d'étain, blanche, brillante, qui ne s'altère pas [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | inclusion | detail 51 29.1 1.9 | enchaîné 5]: le Christ blanc sort du tombeau sur un fond bleu intense. Je tiens la recette secrète, je ne la confie qu'à ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | Vierge à la pomme, Bargello, Florence, 1442-1444 | coupe]La terre cuite émaillée me permet [incrust-fin]de produire plus vite et à moindre coût que le marbre : voici une *Vierge à la pomme*, douce et grave, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | inclusion | detail 49.4 42.8 4.9 | enchaîné 2]qui tient son enfant contre sa joue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | Vierge à l'Enfant avec trois chérubins, Louvre, 1450 environ | coupe] [incrust-fin]Mes Vierges à l'Enfant se retrouvent dans toute la Toscane, et jusque dans les collections royales [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | inclusion | detail 49.4 33.5 4.9]: celle-ci, avec trois chérubins, est aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg | Vierge à l'Enfant, Bargello, Florence, 1450 environ | coupe] [incrust-fin]Celle-ci, au Bargello, est plus simple encore : deux visages, un bleu, un blanc, et tout est dit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | Tabernacle de la Sainte Croix, Impruneta, 1445-1450 | enchaîné 10]À Impruneta, le *Tabernacle de la Sainte Croix* mêle bas-relief et haut-relief en terre cuite émaillée [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | inclusion | detail 51.8 40.9 4.6 | enchaîné 5]: des anges portent des cierges, des enfants soutiennent des guirlandes. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | Porte de bronze de la sacristie, Florence, 1446-1475 | coupe] [incrust-fin]Je n'ai pas abandonné le bronze : avec Michelozzo et Maso di Bartolomeo, je réalise la *Porte de la sacristie* de la cathédrale de Florence, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | inclusion | detail 48.2 51.5 6.2 | enchaîné 5]dix panneaux de saints, de docteurs et d'anges, qui m'occuperont longtemps. [image: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | Les Quatre Vertus cardinales, San Miniato al Monte, Florence, 1461-1466 | coupe] [incrust-fin]À San Miniato, dans la chapelle du cardinal du Portugal, j'orne le plafond des *Quatre Vertus cardinales* : la Prudence, la [incrust: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | inclusion | detail 51.3 29 6.2 | enchaîné 5]Justice, la Tempérance et la Force entourent le Saint-Esprit. [retour | 5] [incrust-fin]Je suis mort en 1482, [retour | 5]et c'est mon neveu Andrea qui a gardé le secret après moi.</t>
         </is>
+      </c>
+      <c r="T175" s="10" t="s">
+        <v>3581</v>
       </c>
       <c r="U175" s="5" t="s">
         <v>1263</v>
@@ -21389,10 +21397,8 @@
       <c r="I185" s="7">
         <v>1</v>
       </c>
-      <c r="S185" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né à Florence vers 1386, fils d'un cardeur de laine, et l'on m'appelle Donatello, un diminutif affectueux qui a fini par effacer mon vrai nom. J'ai appris le métier dans l'atelier de Ghiberti, puis, avec Brunelleschi, mon ami, j'ai parcouru Rome pour mesurer les ruines antiques. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/3b/David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg/960px-David%2C_Donatello%2C_ca._1408%2C_Bargello_Florenz-02-167.jpg | David, Florence, 1408-1409 | 5]Mon premier *David*, en marbre, sculpté pour la cathédrale, est encore de style gothique : un jeune héros élégant, qui foule du pied la tête de Goliath. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/84/Donatello%2C_san_marco%2C_1411-13%2C_01.JPG/500px-Donatello%2C_san_marco%2C_1411-13%2C_01.JPG | Saint Marc, Orsanmichele, Florence, 1411-1413 | enchaîné 10]Pour Orsanmichele, les tisserands de lin m'ont commandé *Saint Marc*. On raconte que Michel-Ange, devant lui, aurait dit n'avoir jamais vu figure qui eût plus l'air d'un honnête homme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg/960px-St._Georg%2C_Donatello%2C_1416-17%2C_Bargello_Florenz-01.jpg | Saint Georges, Florence, 1415-1417 | enchaîné 10]Mon *Saint Georges*, pour les armuriers, est un jeune soldat debout, les pieds bien plantés, le regard tendu. Sur le socle, j'ai creusé un relief à peine épais où le dragon et la princesse s'enfoncent dans un paysage : c'est la première fois que la perspective entre dans la sculpture. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg/1280px-Baptismal_font_of_the_Siena_Baptistry_la-test_battista_presenta.jpg | Le Festin d'Hérode, Sienne, 1423-1425 | enchaîné 10]À Sienne, pour le baptistère, je fonds *Le Festin d'Hérode* en bronze doré : la tête de saint Jean-Baptiste vient d'être apportée sur un plat, Hérode recule d'horreur, les convives se bousculent, et au fond s'ouvrent des arcades qui fuient. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/95/Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg/960px-Donatello%2C_Annunciazione_Cavalcanti%2C_1435_circa_01.jpg | Annonciation Cavalcanti, Santa Croce, Florence, 1435 environ | enchaîné 10]Dans l'*Annonciation Cavalcanti*, à Santa Croce, la Vierge se détourne avec pudeur de l'ange, entre des pilastres dorés, et des petits enfants ailés jouent au-dessus. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/92/Bronze_David_by_Donatello-Bargello.jpg/1280px-Bronze_David_by_Donatello-Bargello.jpg | David, Bargello, Florence, 1440 environ | enchaîné 10]Vers 1440, sans doute pour Cosme de Médicis, mon protecteur, je coule un nouveau *David*, en bronze : un adolescent nu, coiffé d'un chapeau de berger, le premier nu en ronde-bosse depuis l'Antiquité. Sa nudité, son sourire, son pied sur la tête de Goliath ont fait couler beaucoup d'encre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6d/Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG/1280px-Donatello%2C_Monumento_equestre_al_Gattamelata_06.JPG | Monument à Gattamelata, Padoue, 1445-1453 | enchaîné 10]En 1443, Padoue m'appelle. Pour le général Gattamelata, mort l'année même, je fonds le *Monument équestre* : c'est la première grande statue équestre en bronze depuis l'empereur Marc Aurèle. Je reste dix ans en Vénétie, et mon style inspire toute une génération de peintres, Mantegna le premier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/e1/Donatello%2C_maria_maddalena_02.JPG/960px-Donatello%2C_maria_maddalena_02.JPG | Madeleine pénitente, Florence, 1453-1455 | enchaîné 10]De retour à Florence, vieux et fatigué, je sculpte une *Madeleine pénitente* en bois : un corps décharné, les mains jointes, les joues creusées, l'inverse de la beauté idéale. [retour | 5]Je suis mort en 1466, et Cosme avait demandé que je sois enterré près de lui, à Saint-Laurent.</t>
-        </is>
+      <c r="S185" s="1" t="s">
+        <v>1343</v>
       </c>
       <c r="U185" s="5" t="s">
         <v>1339</v>
@@ -23221,10 +23227,8 @@
       <c r="I230" s="7">
         <v>1</v>
       </c>
-      <c r="S230" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né à Florence en 1378 [retour | 5]et j'ai appris l'orfèvrerie auprès de mon beau-père : ciseler l'or, graver, fondre de petites pièces, c'est là que ma main s'est formée. [image: https://upload.wikimedia.org/wikipedia/commons/5/52/Wga_ghiberti_sacrifice_of_Isaac.jpg | Le Sacrifice d'Isaac, 1401 | 5]En 1401, j'ai vingt-deux ans quand les marchands de Florence ouvrent un concours pour les nouvelles portes de bronze du baptistère. Chaque candidat doit livrer le même panneau, le *Sacrifice d'Isaac*. Mon bronze, fondu d'un seul jet, est jugé le plus léger et le plus gracieux ; Brunelleschi, dit-on, refuse de partager la commande et s'en va. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/0e/Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG/960px-Lorenzo_ghiberti_e_aiuti%2C_porta_nord_del_battistero_di_firenze%2C_01.JPG | Porte nord du baptistère, Florence, 1403-1424 | enchaîné 10]Je vais passer plus de vingt ans sur cette première porte : vingt-huit panneaux sur la vie du Christ, encadrés de quadrilobes comme dans les cathédrales gothiques, avec des figures souples, aux draperies fluides, dans l'élégance courtoise du gothique international. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/fc/San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG/960px-San_Giovanni_Battista_di_Lorenzo_Ghiberti%2C3.JPG | Saint Jean-Baptiste, Orsanmichele, Florence, 1412-1416 | enchaîné 10]Dans le même temps, les marchands de drap me demandent pour Orsanmichele un *Saint Jean-Baptiste* : c'est la première grande statue de bronze de la Renaissance, et je dois apprendre le métier de fondeur à l'échelle d'un homme. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/e/ed/Siena_2014-08-11zc.jpg/1280px-Siena_2014-08-11zc.jpg | Le Baptême du Christ, Sienne, 1417-1427 | enchaîné 10]À Sienne, pour les fonts baptismaux, je livre deux reliefs, aux côtés de Donatello et de Jacopo della Quercia. *Le Baptême du Christ*, en bronze doré, me sert de terrain d'essai pour l'espace en relief. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4d/Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG/1280px-Formella_05%2C_lorenzo_ghiberti%2C_cattura_del_battista%2C_1427.JPG | L'Arrestation de saint Jean-Baptiste, Sienne, 1417-1427 | enchaîné 10]Dans *L'Arrestation de saint Jean-Baptiste*, j'essaie la perspective que Brunelleschi vient de découvrir : les soldats s'avancent dans un espace qui se creuse. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a8/Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG/960px-Museo_di_orsanmichele%2C_lorenzo_ghiberti%2C_san_matteo_04.JPG | Saint Matthieu, Orsanmichele, Florence, 1419-1423 | enchaîné 10]Les banquiers me confient ensuite un *Saint Matthieu* : sa draperie tombe en plis larges, à la manière antique, et le gothique s'éloigne. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg/500px-Lorenzo_ghiberti%2C_s._stefano%2C_1427-29%2C_da_orsanmichele_01.jpg | Saint Étienne, Orsanmichele, Florence, 1425-1429 | enchaîné 10]Pour les lainiers, mon *Saint Étienne* se tient déjà en équilibre, une hanche relevée, comme une statue romaine. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/59/Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG/960px-Lorenzo_ghiberti%2C_porta_del_paradiso%2C_1425-52%2C_00.JPG | La Porte du Paradis, Florence, 1425-1452 | enchaîné 10]En 1425, on me confie la seconde porte. J'abandonne les quadrilobes : dix grands panneaux carrés, en bronze doré, pour l'Ancien Testament. Dans chacun, plusieurs épisodes d'une même histoire se déroulent dans un espace profond, les figures du premier plan presque détachées du fond, celles du lointain à peine effleurées. Il me faudra vingt-sept ans. Michel-Ange, dit-on, la jugea si belle qu'elle méritait d'être la porte du Paradis : le nom lui est resté. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/6f/Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg/1280px-Lorenzo_ghiberti%2C_arca_di_san_zanobi%2C_1432-35_ca.%2C_miracolo_del_bambino_resuscitato_01.jpg | Châsse de saint Zénobe, Florence, 1432-1442 | enchaîné 10]Entre-temps, j'ai sculpté pour la cathédrale la châsse de saint Zénobe, premier évêque de Florence, dont les miracles se déroulent dans des architectures en perspective. Dans mes *Commentaires*, le premier récit de vie écrit par un artiste, je raconte mes maîtres, mes concurrents et l'atelier où Donatello a fait ses débuts, avec Paolo Uccello. [retour | 5]Je suis mort en 1455, après avoir passé presque toute ma vie sur deux portes.</t>
-        </is>
+      <c r="S230" s="1" t="s">
+        <v>3578</v>
       </c>
       <c r="T230" s="10" t="s">
         <v>3576</v>
@@ -23554,10 +23558,8 @@
       <c r="I238" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S238" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né vers 1510, sans doute en Normandie, et l'on ne sait presque rien de ma jeunesse : mon nom apparaît d'abord à Rouen, en 1540. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/28/Tombeau_de_Louis_de_Br%C3%A9z%C3%A9.jpg/960px-Tombeau_de_Louis_de_Br%C3%A9z%C3%A9.jpg | Bas-reliefs du tombeau de Louis de Brézé, cathédrale de Rouen, 1540-1542 | 5]À la cathédrale, on dit que j'ai travaillé au tombeau de Louis de Brézé, le mari de Diane de Poitiers : de l'albâtre blanc, du marbre noir, des figures fines. En 1544, à Paris, j'exécute pour le jubé de Saint-Germain-l'Auxerrois des reliefs si minces qu'on dirait du papier. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/16/D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg/1280px-D%C3%A9ploration_du_Christ_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1731_%3B_N_15099.jpg | Déploration du Christ, Louvre, 1544-1545 | enchaîné 10]Dans la *Déploration du Christ*, les saintes femmes s'inclinent, les plis de leurs robes coulent comme de l'eau. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d4/Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg/960px-Saint_Jean_-_Jean_Goujon_-_Mus%C3%A9e_du_Louvre_Sculptures_ML_16_%3B_N_15101.jpg | Saint Jean, Louvre, 1544-1545 | enchaîné 10]*Saint Jean* a la même grâce, étirée, presque dansante. Je ne suis jamais allé en Italie ; pourtant on me compare aux maniéristes de Fontainebleau. J'ai illustré la première traduction française de Vitruve, et je travaille avec l'architecte Pierre Lescot. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/25/Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg/1280px-Bas_relief_de_la_fontaine_des_Innocents_-_Nymphe_et_triton_%28Louvre%2C_MR_1737%29.jpg | Nymphe et Triton entourés de deux petits génies, Louvre, 1547-1549 | enchaîné 10]Pour la fontaine des Innocents, à Paris, je sculpte des nymphes en bas-relief, aux draperies mouillées qui collent à leur corps : on dirait que l'eau les a façonnées. Ici, *Nymphe et Triton*, aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/de/Tribune-louvre_%283%29.jpg/1280px-Tribune-louvre_%283%29.jpg | Cariatides de la tribune, Louvre, 1547-1549 | enchaîné 10]Au Louvre, pour la nouvelle aile voulue par Henri II, ce sont mes *Cariatides* : quatre femmes de pierre qui soutiennent la tribune des musiciens, d'une élégance qui deviendra l'emblème de la Renaissance française. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c9/Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg/960px-Ceres_Goujon_Cour_Carr%C3%A9e_Louvre.jpg | Cérès, Louvre, 1548-1550 | enchaîné 10]Toujours au Louvre, *Cérès*, déesse des moissons, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a2/Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg/1280px-Ch%C3%A2teau_de_Chantilly-D%C3%A9part_de_Pha%C3%A9ton_%28Jean_Goujon%29-20120917.jpg | Le Départ de Phaéton, Chantilly, 1547-1550 | enchaîné 10]et *Le Départ de Phaéton*, qui est aujourd'hui à Chantilly : les chevaux du soleil emportent le fils d'Apollon. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/67/P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg/1280px-P1330048_Paris_III_Carnavalet_Coysevox_Louis_XIV_ecrasant_la_Fronde_rwk.jpg | Les Quatre Saisons, hôtel Carnavalet, Paris, 1555-1560 | enchaîné 10]Pour l'hôtel de Ligneris, aujourd'hui Carnavalet, *Les Quatre Saisons*. On dit que j'adhère aux idées de la Réforme ; dans la France des guerres de religion, ce n'est pas sans danger. [retour | 5]Ma trace se perd vers 1565, peut-être à Bologne, loin de la France que j'ai tant embellie.</t>
-        </is>
+      <c r="S238" s="1" t="s">
+        <v>1684</v>
       </c>
       <c r="U238" s="5" t="s">
         <v>1682</v>
@@ -28536,10 +28538,8 @@
       <c r="I362" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="S362" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né à Paris vers 1528, fils d'un sculpteur, et j'ai appris l'art de Fontainebleau : des corps allongés, des visages fins, des plis qui ondulent. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a4/Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg/960px-Les_Trois_Gr%C3%A2ces_-_Germain_Pilon_%3B_Domenico_del_Barbiere_-_Mus%C3%A9e_du_Louvre_Sculptures_MR_1591_A_%3B_N_15165.jpg | Monument du cœur d'Henri II, Louvre, 1559 | 5]Quand Henri II meurt en 1559, sa veuve, Catherine de Médicis, me confie le *Monument du cœur* du roi : trois figures de marbre, les Grâces, enlacées, dos à dos, portent sur leur tête l'urne où repose son cœur. Elles ont la grâce d'une danse. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c3/La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg/1280px-La_R%C3%A9surrection_du_Christ_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_2292_%3B_MR_1592_%3B_MR_1593.jpg | Le Christ ressuscité, Louvre, 1565 environ | enchaîné 10]Mon *Christ ressuscité* garde la même élégance : un corps léger, une draperie qui s'envole. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cd/Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG/1280px-Henri_II_Catherine_de_M%C3%A9dicis_Pilon.JPG | Tombeau d'Henri II et de Catherine de Médicis, Saint-Denis, 1560-1573 | enchaîné 10]Catherine me commande ensuite le *Tombeau* d'Henri II et de Catherine, à Saint-Denis, sur des dessins de l'architecte Primatice. Je sculpte le roi et la reine deux fois : nus, couchés sur le sarcophage, dans la vérité crue de la mort ; [image: https://upload.wikimedia.org/wikipedia/commons/thumb/8/84/Henri_II_et_Catherine_de_M%C3%A9dicis.JPG/1280px-Henri_II_et_Catherine_de_M%C3%A9dicis.JPG | Gisants d'Henri II et de Catherine de Médicis, Saint-Denis, 1583 | enchaîné 10]et en haut, agenouillés et vêtus de leurs habits royaux, en prière. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/21/Germain_Pilon_Vierge_et_enfant.jpg/960px-Germain_Pilon_Vierge_et_enfant.jpg | Vierge à l'Enfant, Le Mans, 1570 | enchaîné 10]Pour l'abbaye de la Couture, au Mans, une *Vierge à l'Enfant* de marbre, plus douce. Charles IX me nomme contrôleur général des effigies : je dirige les ateliers royaux, je modèle les visages des rois. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/6/69/Tombeau_Valentine_Balbiani_details_Pilon_LP397_MR1643.png/1280px-Tombeau_Valentine_Balbiani_details_Pilon_LP397_MR1643.png | Tombeau de Valentine Balbiani, Louvre, 1583 | enchaîné 10]Voici le *Tombeau de Valentine Balbiani*, épouse du chancelier René de Birague, avec une vérité de portrait qui saisit, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/0/05/Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg/1280px-Le_Cardinal_Ren%C3%A9_de_Birague_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_LP_396_%3B_N_15131.jpg | Tombeau du cardinal René de Birague, Louvre, 1585 | enchaîné 10]et celui du cardinal de Birague lui-même, en bronze. La France est alors déchirée par les guerres de religion, et mon art devient plus grave. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/2/2c/Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg/960px-Vierge_de_douleur_-_Germain_Pilon_-_Mus%C3%A9e_du_Louvre_Sculptures_RF_3147.jpg | Vierge de douleur, Louvre, 1586 | enchaîné 10]Ma *Vierge de douleur*, en terre cuite peinte, lève un visage ruisselant de larmes : tout le maniérisme élégant de ma jeunesse a cédé la place à une émotion nue. [retour | 5]Je suis mort à Paris en 1590, considéré déjà comme le plus grand sculpteur français de mon siècle.</t>
-        </is>
+      <c r="S362" s="1" t="s">
+        <v>2363</v>
       </c>
       <c r="U362" s="5" t="s">
         <v>2361</v>
@@ -30447,10 +30447,8 @@
       <c r="I412" s="7">
         <v>1</v>
       </c>
-      <c r="S412" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né vers 1467 à Monte San Savino, en Toscane : c'est de cette petite ville que vient mon nom de Sansovino, mon vrai nom étant Contucci. On raconte que, enfant, je gardais les troupeaux en dessinant sur le sol, jusqu'au jour où le sculpteur Antonio Pollaiuolo m'a remarqué. J'ai passé près de dix ans au Portugal, au service du roi. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/5/5f/Andrea_sansovino%2C_madonna_col_bambino%2C_1504%2C_01.JPG/960px-Andrea_sansovino%2C_madonna_col_bambino%2C_1504%2C_01.JPG | Vierge à l'Enfant, cathédrale San Lorenzo, Gênes, 1501-1502 | 5]À Gênes, pour la cathédrale, dans la chapelle de saint Jean-Baptiste, je sculpte en marbre une *Vierge à l'Enfant* d'une grande douceur, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/14/Andrea_sansovino%2C_giovanni_battista%2C_1504%2C_01.JPG/960px-Andrea_sansovino%2C_giovanni_battista%2C_1504%2C_01.JPG | Saint Jean-Baptiste, cathédrale San Lorenzo, Gênes, 1501-1502 | enchaîné 10]et un *Saint Jean-Baptiste* qui lui répond, simple et grave. [image: https://upload.wikimedia.org/wikipedia/commons/f/f6/Andrea_sansovino%2C_battesimo_di_cristo%2C_1502-05_%28con_restauri_di_v._danti_del_1569%29_e_angelo_di_innocenzo_spinazzi%2C_1792%2C_01.JPG | Baptême du Christ, Florence, 1502-1505 | enchaîné 10]À Florence, la ville me confie le *Baptême du Christ* pour le portail du baptistère : le Christ et saint Jean se font face, dans une sérénité qui annonce la Haute Renaissance. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/dc/Santa_Maria_del_Popolo_Presbyterium_Grabmal_Ascanio_Sforza.JPG/960px-Santa_Maria_del_Popolo_Presbyterium_Grabmal_Ascanio_Sforza.JPG | Tombeau d'Ascanio Sforza, Santa Maria del Popolo, Rome, 1505-1507 | enchaîné 10]Le pape Jules II m'appelle à Rome. Pour l'église Santa Maria del Popolo, je sculpte deux tombeaux de cardinaux. Voici celui d'Ascanio Sforza, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/b/b6/Sansovino%2C_monumento_funebre_di_girolamo_basso_della_rovere_01.JPG/960px-Sansovino%2C_monumento_funebre_di_girolamo_basso_della_rovere_01.JPG | Tombeau de Girolamo Basso della Rovere, Santa Maria del Popolo, Rome, 1505-1507 | enchaîné 10]et celui de Girolamo Basso della Rovere. J'y invente un modèle : un arc de triomphe en marbre, où le défunt repose, la tête appuyée sur la main, comme endormi, sous une Vierge qui l'accueille. Pendant des générations, tous les tombeaux de Rome s'en inspireront. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c0/S_Agostino_Anna_selbtritt.jpg/960px-S_Agostino_Anna_selbtritt.jpg | La Vierge à l'Enfant avec sainte Anne, Sant'Agostino, Rome, 1512 | enchaîné 10]À Sant'Agostino, j'ai sculpté *La Vierge à l'Enfant avec sainte Anne* : trois figures liées dans un même bloc, où sainte Anne regarde sa fille et l'Enfant. Au-dessus, Raphaël a peint le prophète Isaïe, comme pour me répondre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/d5/Andrea_sansovino%2C_annunciazione%2C_1523%2C_01.jpg/1280px-Andrea_sansovino%2C_annunciazione%2C_1523%2C_01.jpg | L'Annonciation, Lorette, 1513-1528 | enchaîné 10]À partir de 1513, à Lorette, je recouvre de marbre la Santa Casa, la maison de la Vierge, que les anges, selon la légende, ont transportée de Nazareth. J'y sculpte *L'Annonciation*, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/17/Andrea_sansovino%2C_nativit%C3%A0_di_ges%C3%B9_e_annuncio_ai_pastori_01.jpg/1280px-Andrea_sansovino%2C_nativit%C3%A0_di_ges%C3%B9_e_annuncio_ai_pastori_01.jpg | La Nativité du Christ, Lorette, 1513-1528 | enchaîné 10]puis *La Nativité*, en haut-relief, et j'y travaille jusqu'à la fin de ma vie. Je suis mort en 1529, à Monte San Savino. [retour | 5]Mon élève Jacopo Tatti avait pris mon nom : il est devenu Jacopo Sansovino.</t>
-        </is>
+      <c r="S412" s="1" t="s">
+        <v>2612</v>
       </c>
       <c r="U412" s="5" t="s">
         <v>2610</v>
@@ -30487,10 +30485,8 @@
       <c r="I413" s="7">
         <v>1</v>
       </c>
-      <c r="S413" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Je suis né à Florence en 1486 sous le nom de Jacopo Tatti. Mon maître, Andrea Sansovino, m'a appris le marbre, et par admiration j'ai pris son nom. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f8/Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg/960px-Jacopo_sansovino%2C_san_jacopo_maggiore%2C_1511-1514.jpg | Saint Jacques, cathédrale de Florence, 1511-1518 | 5]À vingt-cinq ans, je sculpte pour la cathédrale de Florence un *Saint Jacques*, l'un des apôtres qui doivent encadrer la nef. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/b/b9/Bacchus_by_Jacopo_Sansovino.jpg/1280px-Bacchus_by_Jacopo_Sansovino.jpg | Bacchus, Bargello, Florence, 1515 | enchaîné 10]Mon *Bacchus*, lui, est un jeune dieu nu, un peu ivre, qui lève sa coupe : Vasari dit qu'on le prenait pour de la chair vivante. Je pars pour Rome, je regarde Bramante, je regarde les statues antiques. En 1527, les soldats de l'empereur mettent Rome à sac ; je m'enfuis, et je m'arrête à Venise. Je comptais repartir pour la France : le doge Gritti me retient, et en 1529 je deviens l'architecte de la République. À Venise, je construis la Monnaie, la Bibliothèque de Saint-Marc, que Palladio dit la plus riche construction depuis l'Antiquité. En 1545, la voûte de la bibliothèque s'effondre : on me jette en prison, on me condamne à une amende ; Titien et l'Arétin, mes amis, plaident pour moi, et je reconstruis à mes frais. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/89/Loggetta_Sansovino_Minerva_Venezia.jpg/960px-Loggetta_Sansovino_Minerva_Venezia.jpg | Minerve, Loggetta, Venise, 1537-1541 | enchaîné 10]Au pied du campanile de la place Saint-Marc, je bâtis la Loggetta, et j'y place quatre bronzes pour célébrer le bon gouvernement de Venise : *Minerve*, la sagesse, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/86/Loggetta_Sansovino_Apollo_Venezia.jpg/960px-Loggetta_Sansovino_Apollo_Venezia.jpg | Apollon, Loggetta, Venise, 1537-1541 | enchaîné 10]*Apollon*, l'harmonie, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/8/8a/Loggetta_Sansovino_Mercurio_Venezia.jpg/960px-Loggetta_Sansovino_Mercurio_Venezia.jpg | Mercure, Loggetta, Venise, 1537-1541 | enchaîné 10]*Mercure*, l'éloquence, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/d/da/Loggetta_Sansovino_allegoria_Pace_Venezia.jpg/960px-Loggetta_Sansovino_allegoria_Pace_Venezia.jpg | La Paix, Loggetta, Venise, 1537-1541 | enchaîné 10]et *La Paix*. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/9/92/Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG/960px-Venezia_-_palazzo_ducale_-_courtyard_-_scala_dei_giganti.JPG | Mars, escalier des Géants, Venise, 1554-1566 | enchaîné 10]Au palais des Doges, je dresse en haut de l'escalier des Géants deux colosses de marbre, *Mars*, le dieu de la guerre, [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/a/a0/Jacopo_sansovino%2C_nettuno%2C_1554%2C_04.jpg/330px-Jacopo_sansovino%2C_nettuno%2C_1554%2C_04.jpg | Neptune, escalier des Géants, Venise, 1554-1566 | enchaîné 10]et *Neptune*, le dieu de la mer : c'est entre eux que les doges sont couronnés. Venise règne alors sur la terre et sur les eaux. [retour | 5]Je suis mort en 1570, ayant fait de la place Saint-Marc ce que l'on voit encore.</t>
-        </is>
+      <c r="S413" s="1" t="s">
+        <v>2615</v>
       </c>
       <c r="U413" s="5" t="s">
         <v>2610</v>
@@ -34277,6 +34273,8 @@
     <hyperlink ref="T333" r:id="rId278" xr:uid="{9980C49E-1986-481B-89F5-F1B7DFC18C63}"/>
     <hyperlink ref="T332" r:id="rId279" xr:uid="{189D77F4-2560-4DF7-BDE1-F9B0047B268D}"/>
     <hyperlink ref="T230" r:id="rId280" xr:uid="{28843888-6AE5-48A8-9403-E28B93F68D75}"/>
+    <hyperlink ref="T174" r:id="rId281" display="https://thumb.wikimedia.org/wikipedia/commons/thumb/8/80/Andrea_del_sarto%2C_Devozione_dei_fiorentini_alle_reliquie_di_san_Filippo%2C_1510%2C_08_vecchio%2C_ritratto_di_andrea_della_robbia_-_dett.jpg/960px-Andrea_del_sarto%2C_Devozione_dei_fiorentini_alle_reliquie_di_san_Filippo%2C_1510%2C_08_vecchio%2C_ritratto_di_andrea_della_robbia_-_dett.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail" xr:uid="{421C7DE7-FEB5-471F-9B0A-75B46A02A06B}"/>
+    <hyperlink ref="T175" r:id="rId282" xr:uid="{E7DDFF24-CEE2-4F00-B299-F7023AEA6EFA}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -20984,7 +20984,7 @@
       </c>
       <c r="S175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né à Florence en 1399, [retour | 5] [image: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | Pianta della Catena, 1490 | 5]et j'ai d'abord appris l'orfèvrerie avant de sculpter [incrust: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | inclusion | detail 50 36.3 3.4 | enchaîné 5]le marbre. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | La Cantoria, Florence, 1431-1438 | enchaîné 10] En 1431, la cathédrale me [incrust-fin]confie sa *Cantoria*, la tribune des chanteurs : sur dix panneaux de marbre, des enfants chantent, [incrust: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | inclusion | detail 46.2 32.5 3.2 | enchaîné 5]jouent du luth, de la harpe, des cymbales, dansent, comme le psaume qui appelle à louer Dieu par la musique. [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG/1280px-Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG | juxtaposition | cadre 77.6 49.2 44.5 | principale 31.8 48.3 70.6 | enchaîné 5] [incrust-fin]Donatello fait au même moment la sienne, plus agitée, plus sauvage [incrust-fin]; la mienne est plus claire, plus sereine. Mais c'est une autre invention qui va faire ma réputation. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | La Résurrection, Florence, 1442-1444 | enchaîné 10] Au-dessus de la porte de la sacristie, je modèle *La Résurrection* en terre cuite, puis je la recouvre d'une glaçure d'étain, blanche, brillante, qui ne s'altère pas [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | inclusion | detail 51 29.1 1.9 | enchaîné 5]: le Christ blanc sort du tombeau sur un fond bleu intense. Je tiens la recette secrète, je ne la confie qu'à ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | Vierge à la pomme, Bargello, Florence, 1442-1444 | coupe]La terre cuite émaillée me permet [incrust-fin]de produire plus vite et à moindre coût que le marbre : voici une *Vierge à la pomme*, douce et grave, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | inclusion | detail 49.4 42.8 4.9 | enchaîné 2]qui tient son enfant contre sa joue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | Vierge à l'Enfant avec trois chérubins, Louvre, 1450 environ | coupe] [incrust-fin]Mes Vierges à l'Enfant se retrouvent dans toute la Toscane, et jusque dans les collections royales [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | inclusion | detail 49.4 33.5 4.9]: celle-ci, avec trois chérubins, est aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg | Vierge à l'Enfant, Bargello, Florence, 1450 environ | coupe] [incrust-fin]Celle-ci, au Bargello, est plus simple encore : deux visages, un bleu, un blanc, et tout est dit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | Tabernacle de la Sainte Croix, Impruneta, 1445-1450 | enchaîné 10]À Impruneta, le *Tabernacle de la Sainte Croix* mêle bas-relief et haut-relief en terre cuite émaillée [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | inclusion | detail 51.8 40.9 4.6 | enchaîné 5]: des anges portent des cierges, des enfants soutiennent des guirlandes. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | Porte de bronze de la sacristie, Florence, 1446-1475 | coupe] [incrust-fin]Je n'ai pas abandonné le bronze : avec Michelozzo et Maso di Bartolomeo, je réalise la *Porte de la sacristie* de la cathédrale de Florence, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | inclusion | detail 48.2 51.5 6.2 | enchaîné 5]dix panneaux de saints, de docteurs et d'anges, qui m'occuperont longtemps. [image: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | Les Quatre Vertus cardinales, San Miniato al Monte, Florence, 1461-1466 | coupe] [incrust-fin]À San Miniato, dans la chapelle du cardinal du Portugal, j'orne le plafond des *Quatre Vertus cardinales* : la Prudence, la [incrust: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | inclusion | detail 51.3 29 6.2 | enchaîné 5]Justice, la Tempérance et la Force entourent le Saint-Esprit. [retour | 5] [incrust-fin]Je suis mort en 1482, [retour | 5]et c'est mon neveu Andrea qui a gardé le secret après moi.</t>
+          <t xml:space="preserve">Je suis né à Florence en 1399, [retour | 5] [image: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | Pianta della Catena, 1490 | 5]et j'ai d'abord appris l'orfèvrerie avant de sculpter [incrust: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | inclusion | detail 50 36.3 3.4 | enchaîné 5]le marbre. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | La Cantoria, Florence, 1431-1438 | coupe] En 1431, la cathédrale me [incrust-fin]confie sa *Cantoria*, la tribune des chanteurs : sur dix panneaux de marbre, des enfants chantent, [incrust: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | inclusion | detail 46.2 32.5 3.2 | enchaîné 5]jouent du luth, de la harpe, des cymbales, dansent, comme le psaume qui appelle à louer Dieu par la musique. [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG/1280px-Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG | juxtaposition | cadre 77.6 49.2 44.5 | principale 31.8 48.3 70.6 | enchaîné 5] [incrust-fin]Donatello fait au même moment la sienne, plus agitée, plus sauvage [incrust-fin]; la mienne est plus claire, plus sereine. Mais c'est une autre invention qui va faire ma réputation. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | La Résurrection, Florence, 1442-1444 | enchaîné 10] Au-dessus de la porte de la sacristie, je modèle *La Résurrection* en terre cuite, puis je la recouvre d'une glaçure d'étain, blanche, brillante, qui ne s'altère pas [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | inclusion | detail 51 29.1 1.9 | enchaîné 5]: le Christ blanc sort du tombeau sur un fond bleu intense. Je tiens la recette secrète, je ne la confie qu'à ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | Vierge à la pomme, Bargello, Florence, 1442-1444 | coupe]La [incrust-fin]terre cuite émaillée me permet de produire plus vite et à moindre coût que le marbre : voici une *Vierge à la pomme*, douce et grave, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | inclusion | detail 49.4 42.8 4.9 | enchaîné 2]qui tient son enfant contre sa joue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | Vierge à l'Enfant avec trois chérubins, Louvre, 1450 environ | coupe] [incrust-fin]Mes Vierges à l'Enfant se retrouvent dans toute la Toscane, et jusque dans les collections royales [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | inclusion | detail 49.4 33.5 4.9]: celle-ci, avec trois chérubins, est aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg | Vierge à l'Enfant, Bargello, Florence, 1450 environ | coupe] [incrust-fin]Celle-ci, au Bargello, est plus simple encore : deux visages, un bleu, un blanc, et tout est dit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | Tabernacle de la Sainte Croix, Impruneta, 1445-1450 | enchaîné 10]À Impruneta, le *Tabernacle de la Sainte Croix* mêle bas-relief et haut-relief en terre cuite émaillée [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | inclusion | detail 51.8 40.9 4.6 | enchaîné 5]: des anges portent des cierges, des enfants soutiennent des guirlandes. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | Porte de bronze de la sacristie, Florence, 1446-1475 | coupe] [incrust-fin]Je n'ai pas abandonné le bronze : avec Michelozzo et Maso di Bartolomeo, je réalise la *Porte de la sacristie* de la cathédrale de Florence, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | inclusion | detail 48.2 51.5 6.2 | enchaîné 5]dix panneaux de saints, de docteurs et d'anges, qui m'occuperont longtemps. [image: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | Les Quatre Vertus cardinales, San Miniato al Monte, Florence, 1461-1466 | coupe] [incrust-fin]À San Miniato, dans la chapelle du cardinal du Portugal, j'orne le plafond des *Quatre Vertus cardinales* : la Prudence, la [incrust: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | inclusion | detail 51.3 29 6.2 | enchaîné 5]Justice, la Tempérance et la Force entourent le Saint-Esprit. [retour | 5] [incrust-fin]Je suis mort en 1482, [retour | 5]et c'est mon neveu Andrea qui a gardé le secret après moi.</t>
         </is>
       </c>
       <c r="T175" s="10" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -13834,7 +13834,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y503"/>
+  <dimension ref="A1:AA503"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18" style="5" customWidth="1"/>
@@ -13854,6 +13854,8 @@
     <col min="22" max="22" width="42" customWidth="1"/>
     <col min="23" max="23" width="90" customWidth="1"/>
     <col min="24" max="24" width="28" customWidth="1"/>
+    <col min="26" max="26" width="22" customWidth="1"/>
+    <col min="27" max="27" width="60" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -13932,6 +13934,16 @@
       <c r="Y1" t="s">
         <v>23</v>
       </c>
+      <c r="Z1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ville de naissance</t>
+        </is>
+      </c>
+      <c r="AA1" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carte</t>
+        </is>
+      </c>
     </row>
     <row r="2" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
@@ -13973,6 +13985,11 @@
       <c r="W2" t="s">
         <v>34</v>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nancy</t>
+        </is>
+      </c>
     </row>
     <row r="3" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
@@ -14055,6 +14072,11 @@
       <c r="W4" t="s">
         <v>52</v>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="5" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
@@ -14093,6 +14115,11 @@
       <c r="W5" t="s">
         <v>61</v>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Stockholm</t>
+        </is>
+      </c>
     </row>
     <row r="6" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
@@ -14134,6 +14161,11 @@
       <c r="W6" t="s">
         <v>71</v>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Théodosie</t>
+        </is>
+      </c>
     </row>
     <row r="7" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
@@ -14175,6 +14207,11 @@
       <c r="W7" t="s">
         <v>81</v>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bologne</t>
+        </is>
+      </c>
     </row>
     <row r="8" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
@@ -14216,6 +14253,11 @@
       <c r="W8" t="s">
         <v>89</v>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="9" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
@@ -14257,6 +14299,11 @@
       <c r="W9" t="s">
         <v>98</v>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dronrijp</t>
+        </is>
+      </c>
     </row>
     <row r="10" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
@@ -14298,6 +14345,11 @@
       <c r="W10" t="s">
         <v>107</v>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ratisbonne</t>
+        </is>
+      </c>
     </row>
     <row r="11" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
@@ -14339,6 +14391,11 @@
       <c r="W11" t="s">
         <v>117</v>
       </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="12" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
@@ -14377,6 +14434,11 @@
       <c r="W12" t="s">
         <v>124</v>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eu</t>
+        </is>
+      </c>
     </row>
     <row r="13" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -14415,6 +14477,11 @@
       <c r="W13" t="s">
         <v>130</v>
       </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Eu</t>
+        </is>
+      </c>
     </row>
     <row r="14" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -14456,6 +14523,11 @@
       <c r="W14" t="s">
         <v>138</v>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Crémone</t>
+        </is>
+      </c>
     </row>
     <row r="15" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
@@ -14497,6 +14569,11 @@
       <c r="W15" t="s">
         <v>146</v>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vilna</t>
+        </is>
+      </c>
     </row>
     <row r="16" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
@@ -14538,6 +14615,11 @@
       <c r="W16" t="s">
         <v>154</v>
       </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milan</t>
+        </is>
+      </c>
     </row>
     <row r="17" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -14579,6 +14661,11 @@
       <c r="W17" t="s">
         <v>162</v>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Padoue</t>
+        </is>
+      </c>
     </row>
     <row r="18" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
@@ -14617,6 +14704,11 @@
       <c r="W18" t="s">
         <v>169</v>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="19" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
@@ -14658,6 +14750,11 @@
       <c r="W19" t="s">
         <v>178</v>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="20" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
@@ -14699,6 +14796,11 @@
       <c r="W20" t="s">
         <v>186</v>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grodno</t>
+        </is>
+      </c>
     </row>
     <row r="21" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
@@ -14740,6 +14842,16 @@
       <c r="W21" t="s">
         <v>195</v>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="22" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
@@ -14781,6 +14893,11 @@
       <c r="W22" t="s">
         <v>203</v>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Souabe</t>
+        </is>
+      </c>
     </row>
     <row r="23" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -14822,6 +14939,16 @@
       <c r="W23" t="s">
         <v>211</v>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="24" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
@@ -14863,6 +14990,11 @@
       <c r="W24" t="s">
         <v>219</v>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="25" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -14907,6 +15039,11 @@
       <c r="W25" t="s">
         <v>228</v>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Castelfranco Veneto</t>
+        </is>
+      </c>
     </row>
     <row r="26" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
@@ -14951,6 +15088,11 @@
       <c r="W26" t="s">
         <v>237</v>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cento</t>
+        </is>
+      </c>
     </row>
     <row r="27" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
@@ -14992,6 +15134,11 @@
       <c r="W27" t="s">
         <v>244</v>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urbino</t>
+        </is>
+      </c>
     </row>
     <row r="28" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
@@ -15033,6 +15180,11 @@
       <c r="W28" t="s">
         <v>252</v>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="29" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
@@ -15074,6 +15226,11 @@
       <c r="W29" t="s">
         <v>260</v>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colmar</t>
+        </is>
+      </c>
     </row>
     <row r="30" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -15115,6 +15272,11 @@
       <c r="W30" t="s">
         <v>268</v>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prato</t>
+        </is>
+      </c>
     </row>
     <row r="31" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
@@ -15156,6 +15318,11 @@
       <c r="W31" t="s">
         <v>275</v>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="32" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
@@ -15197,6 +15364,11 @@
       <c r="W32" t="s">
         <v>282</v>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bassano del Grappa</t>
+        </is>
+      </c>
     </row>
     <row r="33" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -15238,6 +15410,11 @@
       <c r="W33" t="s">
         <v>290</v>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lucques</t>
+        </is>
+      </c>
     </row>
     <row r="34" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
@@ -15279,6 +15456,11 @@
       <c r="W34" t="s">
         <v>297</v>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montpellier</t>
+        </is>
+      </c>
     </row>
     <row r="35" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
@@ -15323,6 +15505,11 @@
       <c r="W35" t="s">
         <v>305</v>
       </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Verceil</t>
+        </is>
+      </c>
     </row>
     <row r="36" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
@@ -15364,6 +15551,11 @@
       <c r="W36" t="s">
         <v>313</v>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sienne</t>
+        </is>
+      </c>
     </row>
     <row r="37" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
@@ -15405,6 +15597,11 @@
       <c r="W37" t="s">
         <v>321</v>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leipzig</t>
+        </is>
+      </c>
     </row>
     <row r="38" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
@@ -15446,6 +15643,11 @@
       <c r="W38" t="s">
         <v>329</v>
       </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Berlin</t>
+        </is>
+      </c>
     </row>
     <row r="39" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -15487,6 +15689,11 @@
       <c r="W39" t="s">
         <v>336</v>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Padoue</t>
+        </is>
+      </c>
     </row>
     <row r="40" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
@@ -15566,6 +15773,11 @@
       <c r="W41" t="s">
         <v>353</v>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="42" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
@@ -15607,6 +15819,11 @@
       <c r="W42" t="s">
         <v>360</v>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="43" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
@@ -15648,6 +15865,11 @@
       <c r="W43" t="s">
         <v>368</v>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="44" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
@@ -15686,6 +15908,11 @@
       <c r="W44" t="s">
         <v>376</v>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cordoue</t>
+        </is>
+      </c>
     </row>
     <row r="45" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
@@ -15727,6 +15954,11 @@
       <c r="W45" t="s">
         <v>384</v>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lille</t>
+        </is>
+      </c>
     </row>
     <row r="46" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
@@ -15815,6 +16047,11 @@
       <c r="W47" t="s">
         <v>400</v>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cortone</t>
+        </is>
+      </c>
     </row>
     <row r="48" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="5" t="s">
@@ -15856,6 +16093,11 @@
       <c r="W48" t="s">
         <v>409</v>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paredes de Nava</t>
+        </is>
+      </c>
     </row>
     <row r="49" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="5" t="s">
@@ -15897,6 +16139,11 @@
       <c r="W49" t="s">
         <v>417</v>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anvers</t>
+        </is>
+      </c>
     </row>
     <row r="50" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="5" t="s">
@@ -15938,6 +16185,11 @@
       <c r="W50" t="s">
         <v>425</v>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Solingen</t>
+        </is>
+      </c>
     </row>
     <row r="51" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="5" t="s">
@@ -15979,6 +16231,11 @@
       <c r="W51" t="s">
         <v>435</v>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="52" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="5" t="s">
@@ -16020,6 +16277,11 @@
       <c r="W52" t="s">
         <v>443</v>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Reggio de Calabre</t>
+        </is>
+      </c>
     </row>
     <row r="53" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="5" t="s">
@@ -16061,6 +16323,11 @@
       <c r="W53" t="s">
         <v>451</v>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bâle</t>
+        </is>
+      </c>
     </row>
     <row r="54" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="5" t="s">
@@ -16105,6 +16372,11 @@
       <c r="W54" t="s">
         <v>460</v>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Douai</t>
+        </is>
+      </c>
     </row>
     <row r="55" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="5" t="s">
@@ -16146,6 +16418,11 @@
       <c r="W55" t="s">
         <v>468</v>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bordeaux</t>
+        </is>
+      </c>
     </row>
     <row r="56" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="5" t="s">
@@ -16187,6 +16464,11 @@
       <c r="W56" t="s">
         <v>477</v>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fontenay</t>
+        </is>
+      </c>
     </row>
     <row r="57" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="5" t="s">
@@ -16266,6 +16548,11 @@
       <c r="W58" t="s">
         <v>491</v>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trévise</t>
+        </is>
+      </c>
     </row>
     <row r="59" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="5" t="s">
@@ -16348,6 +16635,11 @@
       <c r="W60" t="s">
         <v>504</v>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mirgorod</t>
+        </is>
+      </c>
     </row>
     <row r="61" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
@@ -16430,6 +16722,16 @@
       <c r="W62" t="s">
         <v>518</v>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="63" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="5" t="s">
@@ -16471,6 +16773,11 @@
       <c r="W63" t="s">
         <v>527</v>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chaumont</t>
+        </is>
+      </c>
     </row>
     <row r="64" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="5" t="s">
@@ -16512,6 +16819,11 @@
       <c r="W64" t="s">
         <v>534</v>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="65" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="5" t="s">
@@ -16553,6 +16865,11 @@
       <c r="W65" t="s">
         <v>540</v>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bouillé-Ménard</t>
+        </is>
+      </c>
     </row>
     <row r="66" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="5" t="s">
@@ -16594,6 +16911,11 @@
       <c r="W66" t="s">
         <v>544</v>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Rochelle</t>
+        </is>
+      </c>
     </row>
     <row r="67" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="5" t="s">
@@ -16635,6 +16957,11 @@
       <c r="W67" t="s">
         <v>552</v>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montauban</t>
+        </is>
+      </c>
     </row>
     <row r="68" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="5" t="s">
@@ -16676,6 +17003,11 @@
       <c r="W68" t="s">
         <v>560</v>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haarlem</t>
+        </is>
+      </c>
     </row>
     <row r="69" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="5" t="s">
@@ -16717,6 +17049,11 @@
       <c r="W69" t="s">
         <v>567</v>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rome</t>
+        </is>
+      </c>
     </row>
     <row r="70" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="5" t="s">
@@ -16761,6 +17098,16 @@
       <c r="W70" t="s">
         <v>575</v>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="71" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="5" t="s">
@@ -16802,6 +17149,11 @@
       <c r="W71" t="s">
         <v>583</v>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Audenarde</t>
+        </is>
+      </c>
     </row>
     <row r="72" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="5" t="s">
@@ -16885,6 +17237,11 @@
       <c r="W73" t="s">
         <v>596</v>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bruxelles</t>
+        </is>
+      </c>
     </row>
     <row r="74" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="5" t="s">
@@ -16924,6 +17281,11 @@
       <c r="W74" t="s">
         <v>603</v>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="75" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="5" t="s">
@@ -17009,6 +17371,11 @@
       <c r="W76" t="s">
         <v>619</v>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Birmingham</t>
+        </is>
+      </c>
     </row>
     <row r="77" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="5" t="s">
@@ -17050,6 +17417,11 @@
       <c r="W77" t="s">
         <v>626</v>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montpellier</t>
+        </is>
+      </c>
     </row>
     <row r="78" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="5" t="s">
@@ -17091,6 +17463,11 @@
       <c r="W78" t="s">
         <v>635</v>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vittoriosa</t>
+        </is>
+      </c>
     </row>
     <row r="79" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="5" t="s">
@@ -17132,6 +17509,11 @@
       <c r="W79" t="s">
         <v>643</v>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="80" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="5" t="s">
@@ -17173,6 +17555,11 @@
       <c r="W80" t="s">
         <v>651</v>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="81" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="5" t="s">
@@ -17214,6 +17601,11 @@
       <c r="W81" s="1" t="s">
         <v>657</v>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valenciennes</t>
+        </is>
+      </c>
     </row>
     <row r="82" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="5" t="s">
@@ -17258,6 +17650,11 @@
       <c r="W82" t="s">
         <v>665</v>
       </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="83" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="5" t="s">
@@ -17299,6 +17696,11 @@
       <c r="W83" t="s">
         <v>671</v>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grenade</t>
+        </is>
+      </c>
     </row>
     <row r="84" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="5" t="s">
@@ -17378,6 +17780,11 @@
       <c r="W85" t="s">
         <v>683</v>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nava del Rey</t>
+        </is>
+      </c>
     </row>
     <row r="86" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="5" t="s">
@@ -17419,6 +17826,11 @@
       <c r="W86" t="s">
         <v>690</v>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="87" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="5" t="s">
@@ -17460,6 +17872,11 @@
       <c r="W87" t="s">
         <v>696</v>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valenciennes</t>
+        </is>
+      </c>
     </row>
     <row r="88" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="5" t="s">
@@ -17504,6 +17921,11 @@
       <c r="W88" t="s">
         <v>705</v>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bologne</t>
+        </is>
+      </c>
     </row>
     <row r="89" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="5" t="s">
@@ -17545,6 +17967,11 @@
       <c r="W89" t="s">
         <v>712</v>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chioggia</t>
+        </is>
+      </c>
     </row>
     <row r="90" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="5" t="s">
@@ -17586,6 +18013,11 @@
       <c r="W90" t="s">
         <v>720</v>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anizy</t>
+        </is>
+      </c>
     </row>
     <row r="91" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="5" t="s">
@@ -17627,6 +18059,11 @@
       <c r="W91" t="s">
         <v>728</v>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Allegheny City</t>
+        </is>
+      </c>
     </row>
     <row r="92" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="5" t="s">
@@ -17668,6 +18105,16 @@
       <c r="W92" t="s">
         <v>734</v>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="93" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="5" t="s">
@@ -17791,6 +18238,11 @@
       <c r="W95" t="s">
         <v>758</v>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Samaná</t>
+        </is>
+      </c>
     </row>
     <row r="96" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="5" t="s">
@@ -17829,6 +18281,11 @@
       <c r="W96" t="s">
         <v>764</v>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Exeter</t>
+        </is>
+      </c>
     </row>
     <row r="97" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="5" t="s">
@@ -17867,6 +18324,11 @@
       <c r="W97" t="s">
         <v>771</v>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baerle</t>
+        </is>
+      </c>
     </row>
     <row r="98" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="5" t="s">
@@ -17908,6 +18370,11 @@
       <c r="W98" t="s">
         <v>778</v>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hartford</t>
+        </is>
+      </c>
     </row>
     <row r="99" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="5" t="s">
@@ -17946,6 +18413,11 @@
       <c r="W99" t="s">
         <v>783</v>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settignano</t>
+        </is>
+      </c>
     </row>
     <row r="100" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="5" t="s">
@@ -17984,6 +18456,11 @@
       <c r="W100" t="s">
         <v>790</v>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lucques</t>
+        </is>
+      </c>
     </row>
     <row r="101" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="5" t="s">
@@ -18025,6 +18502,11 @@
       <c r="W101" t="s">
         <v>797</v>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Berchem</t>
+        </is>
+      </c>
     </row>
     <row r="102" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="5" t="s">
@@ -18063,6 +18545,11 @@
       <c r="W102" t="s">
         <v>803</v>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haarlem</t>
+        </is>
+      </c>
     </row>
     <row r="103" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="5" t="s">
@@ -18145,6 +18632,11 @@
       <c r="W104" t="s">
         <v>818</v>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Besançon</t>
+        </is>
+      </c>
     </row>
     <row r="105" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="5" t="s">
@@ -18186,6 +18678,11 @@
       <c r="W105" t="s">
         <v>823</v>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tours</t>
+        </is>
+      </c>
     </row>
     <row r="106" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="5" t="s">
@@ -18268,6 +18765,11 @@
       <c r="W107" t="s">
         <v>835</v>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bolton</t>
+        </is>
+      </c>
     </row>
     <row r="108" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="5" t="s">
@@ -18309,6 +18811,11 @@
       <c r="W108" t="s">
         <v>842</v>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t xml:space="preserve">East Bergholt</t>
+        </is>
+      </c>
     </row>
     <row r="109" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="5" t="s">
@@ -18350,6 +18857,11 @@
       <c r="W109" t="s">
         <v>850</v>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boston</t>
+        </is>
+      </c>
     </row>
     <row r="110" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="5" t="s">
@@ -18388,6 +18900,11 @@
       <c r="W110" t="s">
         <v>856</v>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Mihiel</t>
+        </is>
+      </c>
     </row>
     <row r="111" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="5" t="s">
@@ -18429,6 +18946,11 @@
       <c r="W111" t="s">
         <v>861</v>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cambrai</t>
+        </is>
+      </c>
     </row>
     <row r="112" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="5" t="s">
@@ -18470,6 +18992,11 @@
       <c r="W112" t="s">
         <v>869</v>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tapiau</t>
+        </is>
+      </c>
     </row>
     <row r="113" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="5" t="s">
@@ -18511,6 +19038,11 @@
       <c r="W113" t="s">
         <v>876</v>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="114" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="5" t="s">
@@ -18549,6 +19081,11 @@
       <c r="W114" t="s">
         <v>882</v>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="115" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="5" t="s">
@@ -18628,6 +19165,11 @@
       <c r="W116" t="s">
         <v>894</v>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soucy</t>
+        </is>
+      </c>
     </row>
     <row r="117" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="5" t="s">
@@ -18669,6 +19211,11 @@
       <c r="W117" t="s">
         <v>902</v>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lyon</t>
+        </is>
+      </c>
     </row>
     <row r="118" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="5" t="s">
@@ -18710,6 +19257,11 @@
       <c r="W118" t="s">
         <v>910</v>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lyon</t>
+        </is>
+      </c>
     </row>
     <row r="119" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="5" t="s">
@@ -18751,6 +19303,11 @@
       <c r="W119" t="s">
         <v>916</v>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="120" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="5" t="s">
@@ -18792,6 +19349,11 @@
       <c r="W120" t="s">
         <v>923</v>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lyon</t>
+        </is>
+      </c>
     </row>
     <row r="121" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="5" t="s">
@@ -18836,6 +19398,11 @@
       <c r="X121" t="s">
         <v>932</v>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kronach</t>
+        </is>
+      </c>
     </row>
     <row r="122" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="5" t="s">
@@ -18877,6 +19444,11 @@
       <c r="W122" t="s">
         <v>939</v>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wittenberg</t>
+        </is>
+      </c>
     </row>
     <row r="123" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="5" t="s">
@@ -18915,6 +19487,11 @@
       <c r="W123" t="s">
         <v>943</v>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">New York</t>
+        </is>
+      </c>
     </row>
     <row r="124" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="5" t="s">
@@ -18953,6 +19530,11 @@
       <c r="W124" t="s">
         <v>949</v>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="125" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="5" t="s">
@@ -18994,6 +19576,11 @@
       <c r="W125" t="s">
         <v>957</v>
       </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dordrecht</t>
+        </is>
+      </c>
     </row>
     <row r="126" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="5" t="s">
@@ -19079,6 +19666,11 @@
       <c r="W127" t="s">
         <v>972</v>
       </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fabriano</t>
+        </is>
+      </c>
     </row>
     <row r="128" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="5" t="s">
@@ -19119,6 +19711,11 @@
       </c>
       <c r="W128" t="s">
         <v>979</v>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Poppi</t>
+        </is>
       </c>
     </row>
     <row r="129" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19166,6 +19763,11 @@
       <c r="W129" t="s">
         <v>986</v>
       </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Forlì</t>
+        </is>
+      </c>
     </row>
     <row r="130" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="5" t="s">
@@ -19205,6 +19807,11 @@
       <c r="W130" t="s">
         <v>992</v>
       </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="131" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="5" t="s">
@@ -19242,6 +19849,11 @@
       </c>
       <c r="W131" t="s">
         <v>998</v>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Messine</t>
+        </is>
       </c>
     </row>
     <row r="132" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -19289,6 +19901,16 @@
       <c r="W132" s="6" t="s">
         <v>1004</v>
       </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="133" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="5" t="s">
@@ -19327,6 +19949,11 @@
       <c r="W133" t="s">
         <v>1011</v>
       </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Settignano</t>
+        </is>
+      </c>
     </row>
     <row r="134" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="5" t="s">
@@ -19365,6 +19992,11 @@
       <c r="W134" t="s">
         <v>1018</v>
       </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Volterra</t>
+        </is>
+      </c>
     </row>
     <row r="135" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="5" t="s">
@@ -19444,6 +20076,11 @@
       <c r="W136" t="s">
         <v>1030</v>
       </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="137" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="5" t="s">
@@ -19485,6 +20122,11 @@
       <c r="W137" t="s">
         <v>1037</v>
       </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pérouse</t>
+        </is>
+      </c>
     </row>
     <row r="138" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="5" t="s">
@@ -19568,6 +20210,11 @@
       <c r="W139" t="s">
         <v>1052</v>
       </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marseille</t>
+        </is>
+      </c>
     </row>
     <row r="140" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="5" t="s">
@@ -19609,6 +20256,11 @@
       <c r="W140" t="s">
         <v>1060</v>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oudewater</t>
+        </is>
+      </c>
     </row>
     <row r="141" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="5" t="s">
@@ -19650,6 +20302,11 @@
       <c r="W141" t="s">
         <v>1066</v>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="142" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="5" t="s">
@@ -19694,6 +20351,11 @@
       <c r="W142" t="s">
         <v>1073</v>
       </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Angers</t>
+        </is>
+      </c>
     </row>
     <row r="143" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="5" t="s">
@@ -19732,6 +20394,11 @@
       <c r="W143" t="s">
         <v>1079</v>
       </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coulommiers</t>
+        </is>
+      </c>
     </row>
     <row r="144" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="5" t="s">
@@ -19773,6 +20440,11 @@
       <c r="W144" t="s">
         <v>1087</v>
       </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bruxelles</t>
+        </is>
+      </c>
     </row>
     <row r="145" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="5" t="s">
@@ -19817,6 +20489,11 @@
       <c r="W145" t="s">
         <v>1093</v>
       </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cambrai</t>
+        </is>
+      </c>
     </row>
     <row r="146" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="5" t="s">
@@ -19899,6 +20576,11 @@
       <c r="W147" t="s">
         <v>1107</v>
       </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rotterdam</t>
+        </is>
+      </c>
     </row>
     <row r="148" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="5" t="s">
@@ -19937,6 +20619,11 @@
       <c r="W148" t="s">
         <v>1113</v>
       </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Joigny en France</t>
+        </is>
+      </c>
     </row>
     <row r="149" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="5" t="s">
@@ -19978,6 +20665,11 @@
       <c r="W149" t="s">
         <v>1120</v>
       </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utrecht</t>
+        </is>
+      </c>
     </row>
     <row r="150" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="5" t="s">
@@ -20016,6 +20708,11 @@
       <c r="W150" t="s">
         <v>1126</v>
       </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vic</t>
+        </is>
+      </c>
     </row>
     <row r="151" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="5" t="s">
@@ -20057,6 +20754,11 @@
       <c r="W151" t="s">
         <v>1132</v>
       </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Quentin</t>
+        </is>
+      </c>
     </row>
     <row r="152" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="5" t="s">
@@ -20098,6 +20800,11 @@
       <c r="W152" t="s">
         <v>1138</v>
       </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="153" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="5" t="s">
@@ -20136,6 +20843,11 @@
       <c r="W153" t="s">
         <v>1144</v>
       </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Grenade</t>
+        </is>
+      </c>
     </row>
     <row r="154" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="5" t="s">
@@ -20174,6 +20886,11 @@
       <c r="W154" t="s">
         <v>1151</v>
       </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baza</t>
+        </is>
+      </c>
     </row>
     <row r="155" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="5" t="s">
@@ -20215,6 +20932,11 @@
       <c r="W155" t="s">
         <v>1156</v>
       </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Xàtiva</t>
+        </is>
+      </c>
     </row>
     <row r="156" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="5" t="s">
@@ -20253,6 +20975,11 @@
       <c r="W156" t="s">
         <v>1163</v>
       </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ferrare</t>
+        </is>
+      </c>
     </row>
     <row r="157" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="5" t="s">
@@ -20291,6 +21018,11 @@
       <c r="W157" t="s">
         <v>1169</v>
       </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burgos</t>
+        </is>
+      </c>
     </row>
     <row r="158" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="5" t="s">
@@ -20329,6 +21061,11 @@
       <c r="W158" t="s">
         <v>1173</v>
       </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Albi</t>
+        </is>
+      </c>
     </row>
     <row r="159" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="5" t="s">
@@ -20405,6 +21142,11 @@
       <c r="W160" t="s">
         <v>1186</v>
       </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">La Haye</t>
+        </is>
+      </c>
     </row>
     <row r="161" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="5" t="s">
@@ -20443,6 +21185,11 @@
       <c r="W161" t="s">
         <v>1191</v>
       </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fuente de Cantos</t>
+        </is>
+      </c>
     </row>
     <row r="162" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="5" t="s">
@@ -20526,6 +21273,11 @@
       <c r="W163" t="s">
         <v>1206</v>
       </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="164" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="5" t="s">
@@ -20564,6 +21316,11 @@
       <c r="W164" t="s">
         <v>1212</v>
       </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ferrare</t>
+        </is>
+      </c>
     </row>
     <row r="165" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="5" t="s">
@@ -20602,6 +21359,11 @@
       <c r="W165" t="s">
         <v>1218</v>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="166" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="5" t="s">
@@ -20640,6 +21402,16 @@
       <c r="W166" t="s">
         <v>1222</v>
       </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="167" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="5" t="s">
@@ -20678,6 +21450,16 @@
       <c r="W167" t="s">
         <v>1227</v>
       </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="168" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="5" t="s">
@@ -20760,6 +21542,11 @@
       <c r="W169" t="s">
         <v>1241</v>
       </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="170" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="5" t="s">
@@ -20798,6 +21585,11 @@
       <c r="W170" t="s">
         <v>1247</v>
       </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Borgo San Sepolcro</t>
+        </is>
+      </c>
     </row>
     <row r="171" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="5" t="s">
@@ -20839,6 +21631,16 @@
       <c r="W171" t="s">
         <v>1252</v>
       </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="172" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="5" t="s">
@@ -20877,6 +21679,11 @@
       <c r="W172" t="s">
         <v>1257</v>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Côme</t>
+        </is>
+      </c>
     </row>
     <row r="173" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="5" t="s">
@@ -20915,6 +21722,11 @@
       <c r="W173" t="s">
         <v>1262</v>
       </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sienne</t>
+        </is>
+      </c>
     </row>
     <row r="174" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="5" t="s">
@@ -20956,6 +21768,16 @@
       <c r="W174" t="s">
         <v>1267</v>
       </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="175" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="5" t="s">
@@ -20984,7 +21806,7 @@
       </c>
       <c r="S175" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Je suis né à Florence en 1399, [retour | 5] [image: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | Pianta della Catena, 1490 | 5]et j'ai d'abord appris l'orfèvrerie avant de sculpter [incrust: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | inclusion | detail 50 36.3 3.4 | enchaîné 5]le marbre. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | La Cantoria, Florence, 1431-1438 | coupe] En 1431, la cathédrale me [incrust-fin]confie sa *Cantoria*, la tribune des chanteurs : sur dix panneaux de marbre, des enfants chantent, [incrust: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | inclusion | detail 46.2 32.5 3.2 | enchaîné 5]jouent du luth, de la harpe, des cymbales, dansent, comme le psaume qui appelle à louer Dieu par la musique. [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG/1280px-Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG | juxtaposition | cadre 77.6 49.2 44.5 | principale 31.8 48.3 70.6 | enchaîné 5] [incrust-fin]Donatello fait au même moment la sienne, plus agitée, plus sauvage [incrust-fin]; la mienne est plus claire, plus sereine. Mais c'est une autre invention qui va faire ma réputation. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | La Résurrection, Florence, 1442-1444 | enchaîné 10] Au-dessus de la porte de la sacristie, je modèle *La Résurrection* en terre cuite, puis je la recouvre d'une glaçure d'étain, blanche, brillante, qui ne s'altère pas [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | inclusion | detail 51 29.1 1.9 | enchaîné 5]: le Christ blanc sort du tombeau sur un fond bleu intense. Je tiens la recette secrète, je ne la confie qu'à ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | Vierge à la pomme, Bargello, Florence, 1442-1444 | coupe]La [incrust-fin]terre cuite émaillée me permet de produire plus vite et à moindre coût que le marbre : voici une *Vierge à la pomme*, douce et grave, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | inclusion | detail 49.4 42.8 4.9 | enchaîné 2]qui tient son enfant contre sa joue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | Vierge à l'Enfant avec trois chérubins, Louvre, 1450 environ | coupe] [incrust-fin]Mes Vierges à l'Enfant se retrouvent dans toute la Toscane, et jusque dans les collections royales [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | inclusion | detail 49.4 33.5 4.9]: celle-ci, avec trois chérubins, est aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg | Vierge à l'Enfant, Bargello, Florence, 1450 environ | coupe] [incrust-fin]Celle-ci, au Bargello, est plus simple encore : deux visages, un bleu, un blanc, et tout est dit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | Tabernacle de la Sainte Croix, Impruneta, 1445-1450 | enchaîné 10]À Impruneta, le *Tabernacle de la Sainte Croix* mêle bas-relief et haut-relief en terre cuite émaillée [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | inclusion | detail 51.8 40.9 4.6 | enchaîné 5]: des anges portent des cierges, des enfants soutiennent des guirlandes. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | Porte de bronze de la sacristie, Florence, 1446-1475 | coupe] [incrust-fin]Je n'ai pas abandonné le bronze : avec Michelozzo et Maso di Bartolomeo, je réalise la *Porte de la sacristie* de la cathédrale de Florence, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | inclusion | detail 48.2 51.5 6.2 | enchaîné 5]dix panneaux de saints, de docteurs et d'anges, qui m'occuperont longtemps. [image: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | Les Quatre Vertus cardinales, San Miniato al Monte, Florence, 1461-1466 | coupe] [incrust-fin]À San Miniato, dans la chapelle du cardinal du Portugal, j'orne le plafond des *Quatre Vertus cardinales* : la Prudence, la [incrust: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | inclusion | detail 51.3 29 6.2 | enchaîné 5]Justice, la Tempérance et la Force entourent le Saint-Esprit. [retour | 5] [incrust-fin]Je suis mort en 1482, [retour | 5]et c'est mon neveu Andrea qui a gardé le secret après moi.</t>
+          <t xml:space="preserve">Je suis né à Florence en 1399, [retour | 5] [image: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | Pianta della Catena, 1490 | 5]et j'ai d'abord appris l'orfèvrerie avant de sculpter [incrust: https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg | inclusion | detail 50 36.3 3.4 | enchaîné 5]le marbre. [image: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | La Cantoria, Florence, 1431-1438 | coupe | lég: +1,9] En 1431, la cathédrale me [incrust-fin]confie sa *Cantoria*, la tribune des chanteurs : sur dix panneaux de marbre, des enfants chantent, [incrust: https://upload.wikimedia.org/wikipedia/commons/thumb/9/94/Cantoria_di_luca_della_robbia_01.JPG/1280px-Cantoria_di_luca_della_robbia_01.JPG | inclusion | detail 46.2 32.5 3.2 | enchaîné 5]jouent du luth, de la harpe, des cymbales, dansent, comme le psaume qui appelle à louer Dieu par la musique. [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c5/Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG/1280px-Donatello%2C_cantoria%2C_veduta%2C_1433-39%2C_01.JPG | juxtaposition | cadre 77.6 49.2 44.5 | principale 31.8 48.3 70.6 | enchaîné 5] [incrust-fin]Donatello fait au même moment la sienne, plus agitée, plus sauvage [incrust-fin]; la mienne est plus claire, plus sereine. Mais c'est une autre invention qui va faire ma réputation. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | La Résurrection, Florence, 1442-1444 | enchaîné 10] Au-dessus de la porte de la sacristie, je modèle *La Résurrection* en terre cuite, puis je la recouvre d'une glaçure d'étain, blanche, brillante, qui ne s'altère [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/cb/Luca_della_Robbia%2C_resurrezione%2C_1440.JPG/1280px-Luca_della_Robbia%2C_resurrezione%2C_1440.JPG | inclusion | detail 51 29.1 1.9 | enchaîné 5]pas : le Christ blanc sort du tombeau sur un fond bleu intense. Je tiens la recette secrète, je ne la confie qu'à ma famille. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | Vierge à la pomme, Bargello, Florence, 1442-1444 | coupe | lég: +0,5] [incrust-fin]La terre cuite émaillée me permet de produire plus vite et à moindre coût que le marbre : voici une *Vierge à la pomme*, douce et grave, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/3/33/Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg/1920px-Luca_della_Robbia%2C_Madonna_of_the_Apple%2C_Florence%2C_Bargello.jpg | inclusion | detail 49.4 42.8 4.9 | enchaîné 2]qui tient son enfant contre sa joue. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | Vierge à l'Enfant avec trois chérubins, Louvre, 1450 environ | coupe] [incrust-fin]Mes Vierges à l'Enfant se retrouvent dans toute la Toscane, et jusque dans les collections royales [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/15/Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG/960px-Andrea_della_robbia_%28attr.%29%2C_madonna_col_bambino_e_tre_cherubini%2C_1470-1520_ca..JPG | inclusion | detail 49.4 33.5 4.9]: celle-ci, avec trois chérubins, est aujourd'hui au Louvre. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/f/f7/Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg/1920px-Luca_della_robbia%2C_madonna_col_bambino_%28tipo_madonna_genovese%29%2C_1450-55_ca.%2C_dal_monastero_di_Santa_Lucia_01.jpg | Vierge à l'Enfant, Bargello, Florence, 1450 environ | coupe] [incrust-fin]Celle-ci, au Bargello, est plus simple encore : deux visages, un bleu, un blanc, et tout est dit. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | Tabernacle de la Sainte Croix, Impruneta, 1445-1450 | enchaîné 10]À Impruneta, le *Tabernacle de la Sainte Croix* mêle bas-relief et haut-relief en terre cuite émaillée [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/c/c7/Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg/960px-Santa_maria_dell%27impruneta%2C_interno%2C_tempietto_della_vera_croce%2C_di_michelozzo_e_luca_della_robbia%2C_02.jpg | inclusion | detail 51.8 40.9 4.6 | enchaîné 5]: des anges portent des cierges, des enfants soutiennent des guirlandes. [image: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | Porte de bronze de la sacristie, Florence, 1446-1475 | coupe] [incrust-fin]Je n'ai pas abandonné le bronze : avec Michelozzo et Maso di Bartolomeo, je réalise la *Porte de la sacristie* de la cathédrale de Florence, [incrust: https://thumb.wikimedia.org/wikipedia/commons/thumb/1/1e/Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg/500px-Luca_della_robbia%2C_michelozzo%2C_maso_di_bartolomeo_e_altri%2C_porte_della_sagrestia_delle_messe%2C_1445-77%2C_01.jpg | inclusion | detail 48.2 51.5 6.2 | enchaîné 5]dix panneaux de saints, de docteurs et d'anges, qui m'occuperont longtemps. [image: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | Les Quatre Vertus cardinales, San Miniato al Monte, Florence, 1461-1466 | coupe] [incrust-fin]À San Miniato, dans la chapelle du cardinal du Portugal, j'orne le plafond des *Quatre Vertus cardinales* : la Prudence, la [incrust: https://upload.wikimedia.org/wikipedia/commons/6/63/Cappella_del_cardinale_di_portogallo_07_tondi_di_luca_della_robbia_e_affreschi_di_alesso_baldovinetti_01.JPG | inclusion | detail 51.3 29 6.2 | enchaîné 5]Justice, la Tempérance et la Force entourent le Saint-Esprit. [retour | 5] [incrust-fin]Je suis mort en 1482, [retour | 5]et c'est mon neveu Andrea qui a gardé le secret après moi.</t>
         </is>
       </c>
       <c r="T175" s="10" t="s">
@@ -20998,6 +21820,11 @@
       </c>
       <c r="W175" t="s">
         <v>1273</v>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
       </c>
     </row>
     <row r="176" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -21040,6 +21867,11 @@
       <c r="W176" t="s">
         <v>1278</v>
       </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="177" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="5" t="s">
@@ -21081,6 +21913,11 @@
       <c r="W177" t="s">
         <v>1286</v>
       </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gand</t>
+        </is>
+      </c>
     </row>
     <row r="178" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="5" t="s">
@@ -21122,6 +21959,11 @@
       <c r="W178" t="s">
         <v>1292</v>
       </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Granville</t>
+        </is>
+      </c>
     </row>
     <row r="179" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="5" t="s">
@@ -21163,6 +22005,11 @@
       <c r="W179" t="s">
         <v>1300</v>
       </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chatou</t>
+        </is>
+      </c>
     </row>
     <row r="180" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="5" t="s">
@@ -21204,6 +22051,11 @@
       <c r="W180" t="s">
         <v>1308</v>
       </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Breda</t>
+        </is>
+      </c>
     </row>
     <row r="181" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="5" t="s">
@@ -21248,6 +22100,11 @@
       <c r="W181" t="s">
         <v>1317</v>
       </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pérouse</t>
+        </is>
+      </c>
     </row>
     <row r="182" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="5" t="s">
@@ -21286,6 +22143,16 @@
       <c r="W182" t="s">
         <v>1323</v>
       </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="183" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="5" t="s">
@@ -21327,6 +22194,11 @@
       <c r="W183" t="s">
         <v>1331</v>
       </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t xml:space="preserve">San Giovanni Valdarno</t>
+        </is>
+      </c>
     </row>
     <row r="184" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="5" t="s">
@@ -21368,6 +22240,16 @@
       <c r="W184" t="s">
         <v>1337</v>
       </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="185" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="5" t="s">
@@ -21409,6 +22291,11 @@
       <c r="W185" t="s">
         <v>1345</v>
       </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="186" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="5" t="s">
@@ -21453,6 +22340,11 @@
       <c r="X186" t="s">
         <v>1354</v>
       </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="187" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="5" t="s">
@@ -21494,6 +22386,11 @@
       <c r="W187" s="1" t="s">
         <v>1359</v>
       </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vérone</t>
+        </is>
+      </c>
     </row>
     <row r="188" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="5" t="s">
@@ -21535,6 +22432,11 @@
       <c r="W188" t="s">
         <v>1368</v>
       </c>
+      <c r="Z188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vienne</t>
+        </is>
+      </c>
     </row>
     <row r="189" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="5" t="s">
@@ -21576,6 +22478,11 @@
       <c r="W189" t="s">
         <v>1375</v>
       </c>
+      <c r="Z189" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyde</t>
+        </is>
+      </c>
     </row>
     <row r="190" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="5" t="s">
@@ -21614,6 +22521,11 @@
       <c r="W190" t="s">
         <v>1382</v>
       </c>
+      <c r="Z190" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="191" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="5" t="s">
@@ -21655,6 +22567,11 @@
       <c r="W191" t="s">
         <v>1389</v>
       </c>
+      <c r="Z191" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nancy</t>
+        </is>
+      </c>
     </row>
     <row r="192" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="5" t="s">
@@ -21696,6 +22613,11 @@
       <c r="W192" t="s">
         <v>1396</v>
       </c>
+      <c r="Z192" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Havre</t>
+        </is>
+      </c>
     </row>
     <row r="193" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="5" t="s">
@@ -21737,6 +22659,11 @@
       <c r="W193" t="s">
         <v>1401</v>
       </c>
+      <c r="Z193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sienne</t>
+        </is>
+      </c>
     </row>
     <row r="194" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="5" t="s">
@@ -21778,6 +22705,11 @@
       <c r="W194" t="s">
         <v>1408</v>
       </c>
+      <c r="Z194" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bruxelles</t>
+        </is>
+      </c>
     </row>
     <row r="195" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="5" t="s">
@@ -21860,6 +22792,11 @@
       <c r="W196" t="s">
         <v>1420</v>
       </c>
+      <c r="Z196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Philadelphie</t>
+        </is>
+      </c>
     </row>
     <row r="197" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="5" t="s">
@@ -21901,6 +22838,11 @@
       <c r="W197" t="s">
         <v>1428</v>
       </c>
+      <c r="Z197" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ostende</t>
+        </is>
+      </c>
     </row>
     <row r="198" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="5" t="s">
@@ -21942,6 +22884,11 @@
       <c r="W198" t="s">
         <v>1435</v>
       </c>
+      <c r="Z198" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montpellier</t>
+        </is>
+      </c>
     </row>
     <row r="199" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="5" t="s">
@@ -21983,6 +22930,11 @@
       <c r="W199" t="s">
         <v>1442</v>
       </c>
+      <c r="Z199" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Middenbeemster</t>
+        </is>
+      </c>
     </row>
     <row r="200" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="5" t="s">
@@ -22024,6 +22976,11 @@
       <c r="W200" t="s">
         <v>1449</v>
       </c>
+      <c r="Z200" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="201" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="5" t="s">
@@ -22065,6 +23022,11 @@
       <c r="W201" t="s">
         <v>1454</v>
       </c>
+      <c r="Z201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toulouse</t>
+        </is>
+      </c>
     </row>
     <row r="202" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="5" t="s">
@@ -22103,6 +23065,11 @@
       <c r="W202" t="s">
         <v>1460</v>
       </c>
+      <c r="Z202" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bergame</t>
+        </is>
+      </c>
     </row>
     <row r="203" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="5" t="s">
@@ -22144,6 +23111,11 @@
       <c r="W203" t="s">
         <v>1466</v>
       </c>
+      <c r="Z203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Livourne</t>
+        </is>
+      </c>
     </row>
     <row r="204" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="5" t="s">
@@ -22185,6 +23157,11 @@
       <c r="W204" t="s">
         <v>1472</v>
       </c>
+      <c r="Z204" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Galice</t>
+        </is>
+      </c>
     </row>
     <row r="205" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="5" t="s">
@@ -22226,6 +23203,11 @@
       <c r="W205" t="s">
         <v>1478</v>
       </c>
+      <c r="Z205" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pellio Intelvi</t>
+        </is>
+      </c>
     </row>
     <row r="206" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="5" t="s">
@@ -22267,6 +23249,11 @@
       <c r="W206" t="s">
         <v>1485</v>
       </c>
+      <c r="Z206" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chropyn</t>
+        </is>
+      </c>
     </row>
     <row r="207" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="5" t="s">
@@ -22308,6 +23295,11 @@
       <c r="W207" t="s">
         <v>1491</v>
       </c>
+      <c r="Z207" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moscou</t>
+        </is>
+      </c>
     </row>
     <row r="208" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="5" t="s">
@@ -22349,6 +23341,11 @@
       <c r="W208" t="s">
         <v>1498</v>
       </c>
+      <c r="Z208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carrare</t>
+        </is>
+      </c>
     </row>
     <row r="209" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="5" t="s">
@@ -22390,6 +23387,11 @@
       <c r="W209" t="s">
         <v>1504</v>
       </c>
+      <c r="Z209" t="inlineStr">
+        <is>
+          <t xml:space="preserve">York</t>
+        </is>
+      </c>
     </row>
     <row r="210" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="5" t="s">
@@ -22469,6 +23471,11 @@
       <c r="W211" t="s">
         <v>1516</v>
       </c>
+      <c r="Z211" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="212" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="5" t="s">
@@ -22510,6 +23517,11 @@
       <c r="W212" t="s">
         <v>1524</v>
       </c>
+      <c r="Z212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bologne</t>
+        </is>
+      </c>
     </row>
     <row r="213" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="5" t="s">
@@ -22548,6 +23560,11 @@
       <c r="W213" t="s">
         <v>1529</v>
       </c>
+      <c r="Z213" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Brescia</t>
+        </is>
+      </c>
     </row>
     <row r="214" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="5" t="s">
@@ -22586,6 +23603,11 @@
       <c r="W214" t="s">
         <v>1534</v>
       </c>
+      <c r="Z214" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valence</t>
+        </is>
+      </c>
     </row>
     <row r="215" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="5" t="s">
@@ -22627,6 +23649,11 @@
       <c r="W215" t="s">
         <v>1541</v>
       </c>
+      <c r="Z215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tours</t>
+        </is>
+      </c>
     </row>
     <row r="216" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="5" t="s">
@@ -22709,6 +23736,11 @@
       <c r="W217" t="s">
         <v>1556</v>
       </c>
+      <c r="Z217" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="218" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="5" t="s">
@@ -22750,6 +23782,11 @@
       <c r="W218" t="s">
         <v>1564</v>
       </c>
+      <c r="Z218" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Greifswald</t>
+        </is>
+      </c>
     </row>
     <row r="219" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="5" t="s">
@@ -22791,6 +23828,11 @@
       <c r="W219" t="s">
         <v>1570</v>
       </c>
+      <c r="Z219" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Havre</t>
+        </is>
+      </c>
     </row>
     <row r="220" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="5" t="s">
@@ -22832,6 +23874,11 @@
       <c r="W220" t="s">
         <v>1576</v>
       </c>
+      <c r="Z220" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Zurich</t>
+        </is>
+      </c>
     </row>
     <row r="221" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="5" t="s">
@@ -22873,6 +23920,11 @@
       <c r="W221" t="s">
         <v>1581</v>
       </c>
+      <c r="Z221" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sudbury</t>
+        </is>
+      </c>
     </row>
     <row r="222" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="5" t="s">
@@ -22914,6 +23966,11 @@
       <c r="W222" t="s">
         <v>1586</v>
       </c>
+      <c r="Z222" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Jean</t>
+        </is>
+      </c>
     </row>
     <row r="223" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="5" t="s">
@@ -22999,6 +24056,11 @@
       <c r="W224" t="s">
         <v>1601</v>
       </c>
+      <c r="Z224" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Chamagne</t>
+        </is>
+      </c>
     </row>
     <row r="225" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="5" t="s">
@@ -23040,6 +24102,11 @@
       <c r="W225" t="s">
         <v>1607</v>
       </c>
+      <c r="Z225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rome</t>
+        </is>
+      </c>
     </row>
     <row r="226" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="5" t="s">
@@ -23081,6 +24148,11 @@
       <c r="W226" t="s">
         <v>1613</v>
       </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pise</t>
+        </is>
+      </c>
     </row>
     <row r="227" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="5" t="s">
@@ -23119,6 +24191,11 @@
       <c r="W227" t="s">
         <v>1619</v>
       </c>
+      <c r="Z227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pays-Bas</t>
+        </is>
+      </c>
     </row>
     <row r="228" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="5" t="s">
@@ -23160,6 +24237,11 @@
       <c r="W228" t="s">
         <v>1624</v>
       </c>
+      <c r="Z228" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rouen</t>
+        </is>
+      </c>
     </row>
     <row r="229" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="5" t="s">
@@ -23201,6 +24283,11 @@
       <c r="W229" t="s">
         <v>1630</v>
       </c>
+      <c r="Z229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vesoul</t>
+        </is>
+      </c>
     </row>
     <row r="230" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="5" t="s">
@@ -23242,6 +24329,11 @@
       <c r="W230" t="s">
         <v>1635</v>
       </c>
+      <c r="Z230" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="231" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="5" t="s">
@@ -23283,6 +24375,16 @@
       <c r="W231" t="s">
         <v>1641</v>
       </c>
+      <c r="Z231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="232" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="5" t="s">
@@ -23324,6 +24426,11 @@
       <c r="W232" t="s">
         <v>1647</v>
       </c>
+      <c r="Z232" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="233" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="5" t="s">
@@ -23365,6 +24472,11 @@
       <c r="W233" t="s">
         <v>1652</v>
       </c>
+      <c r="Z233" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naples</t>
+        </is>
+      </c>
     </row>
     <row r="234" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="5" t="s">
@@ -23406,6 +24518,11 @@
       <c r="W234" t="s">
         <v>1658</v>
       </c>
+      <c r="Z234" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Troyes</t>
+        </is>
+      </c>
     </row>
     <row r="235" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="5" t="s">
@@ -23447,6 +24564,11 @@
       <c r="W235" t="s">
         <v>1664</v>
       </c>
+      <c r="Z235" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montargis</t>
+        </is>
+      </c>
     </row>
     <row r="236" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="5" t="s">
@@ -23532,6 +24654,11 @@
       <c r="W237" t="s">
         <v>1681</v>
       </c>
+      <c r="Z237" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Maubeuge</t>
+        </is>
+      </c>
     </row>
     <row r="238" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="5" t="s">
@@ -23570,6 +24697,11 @@
       <c r="W238" t="s">
         <v>1686</v>
       </c>
+      <c r="Z238" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normandie</t>
+        </is>
+      </c>
     </row>
     <row r="239" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="5" t="s">
@@ -23611,6 +24743,16 @@
       <c r="W239" t="s">
         <v>1693</v>
       </c>
+      <c r="Z239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="240" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="5" t="s">
@@ -23652,6 +24794,11 @@
       <c r="W240" t="s">
         <v>1701</v>
       </c>
+      <c r="Z240" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Winterthour</t>
+        </is>
+      </c>
     </row>
     <row r="241" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="5" t="s">
@@ -23693,6 +24840,11 @@
       <c r="W241" t="s">
         <v>1706</v>
       </c>
+      <c r="Z241" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tournus</t>
+        </is>
+      </c>
     </row>
     <row r="242" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="5" t="s">
@@ -23734,6 +24886,11 @@
       <c r="W242" t="s">
         <v>1714</v>
       </c>
+      <c r="Z242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rybinsk</t>
+        </is>
+      </c>
     </row>
     <row r="243" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="5" t="s">
@@ -23772,6 +24929,11 @@
       <c r="W243" t="s">
         <v>1720</v>
       </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Wurtzbourg</t>
+        </is>
+      </c>
     </row>
     <row r="244" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="5" t="s">
@@ -23813,6 +24975,11 @@
       <c r="W244" t="s">
         <v>1727</v>
       </c>
+      <c r="Z244" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="245" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="5" t="s">
@@ -23854,6 +25021,11 @@
       <c r="W245" t="s">
         <v>1733</v>
       </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Torano</t>
+        </is>
+      </c>
     </row>
     <row r="246" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="5" t="s">
@@ -23930,6 +25102,11 @@
       <c r="W247" t="s">
         <v>1744</v>
       </c>
+      <c r="Z247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anvers</t>
+        </is>
+      </c>
     </row>
     <row r="248" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="5" t="s">
@@ -23971,6 +25148,11 @@
       <c r="W248" t="s">
         <v>1748</v>
       </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="249" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="5" t="s">
@@ -24012,6 +25194,11 @@
       <c r="W249" t="s">
         <v>1753</v>
       </c>
+      <c r="Z249" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bernwiller</t>
+        </is>
+      </c>
     </row>
     <row r="250" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="5" t="s">
@@ -24053,6 +25240,11 @@
       <c r="W250" t="s">
         <v>1759</v>
       </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amsterdam</t>
+        </is>
+      </c>
     </row>
     <row r="251" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="5" t="s">
@@ -24094,6 +25286,11 @@
       <c r="W251" t="s">
         <v>1766</v>
       </c>
+      <c r="Z251" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Berne</t>
+        </is>
+      </c>
     </row>
     <row r="252" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
@@ -24135,6 +25332,11 @@
       <c r="W252" t="s">
         <v>1771</v>
       </c>
+      <c r="Z252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="253" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
@@ -24176,6 +25378,11 @@
       <c r="W253" t="s">
         <v>1776</v>
       </c>
+      <c r="Z253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Augsbourg</t>
+        </is>
+      </c>
     </row>
     <row r="254" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
@@ -24217,6 +25424,11 @@
       <c r="W254" t="s">
         <v>1781</v>
       </c>
+      <c r="Z254" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Boston</t>
+        </is>
+      </c>
     </row>
     <row r="255" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
@@ -24258,6 +25470,11 @@
       <c r="W255" t="s">
         <v>1786</v>
       </c>
+      <c r="Z255" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Watertown</t>
+        </is>
+      </c>
     </row>
     <row r="256" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
@@ -24299,6 +25516,11 @@
       <c r="W256" t="s">
         <v>1791</v>
       </c>
+      <c r="Z256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Versailles</t>
+        </is>
+      </c>
     </row>
     <row r="257" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
@@ -24337,6 +25559,11 @@
       <c r="W257" t="s">
         <v>1797</v>
       </c>
+      <c r="Z257" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valls</t>
+        </is>
+      </c>
     </row>
     <row r="258" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
@@ -24419,6 +25646,11 @@
       <c r="W259" t="s">
         <v>1808</v>
       </c>
+      <c r="Z259" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haverfordwest</t>
+        </is>
+      </c>
     </row>
     <row r="260" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="5" t="s">
@@ -24460,6 +25692,11 @@
       <c r="W260" t="s">
         <v>1814</v>
       </c>
+      <c r="Z260" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lattrop</t>
+        </is>
+      </c>
     </row>
     <row r="261" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="5" t="s">
@@ -24501,6 +25738,11 @@
       <c r="W261" t="s">
         <v>1819</v>
       </c>
+      <c r="Z261" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anvers</t>
+        </is>
+      </c>
     </row>
     <row r="262" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B262" s="5" t="s">
@@ -24539,6 +25781,11 @@
       <c r="W262" t="s">
         <v>1825</v>
       </c>
+      <c r="Z262" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Madrid</t>
+        </is>
+      </c>
     </row>
     <row r="263" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="5" t="s">
@@ -24577,6 +25824,11 @@
       <c r="W263" t="s">
         <v>1830</v>
       </c>
+      <c r="Z263" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rotterdam</t>
+        </is>
+      </c>
     </row>
     <row r="264" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
@@ -24618,6 +25870,11 @@
       <c r="W264" t="s">
         <v>1836</v>
       </c>
+      <c r="Z264" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Moscou</t>
+        </is>
+      </c>
     </row>
     <row r="265" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
@@ -24656,6 +25913,11 @@
       <c r="W265" t="s">
         <v>1842</v>
       </c>
+      <c r="Z265" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Coire</t>
+        </is>
+      </c>
     </row>
     <row r="266" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
@@ -24697,6 +25959,11 @@
       <c r="W266" t="s">
         <v>1849</v>
       </c>
+      <c r="Z266" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aschaffenburg</t>
+        </is>
+      </c>
     </row>
     <row r="267" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="5" t="s">
@@ -24738,6 +26005,11 @@
       <c r="W267" t="s">
         <v>1856</v>
       </c>
+      <c r="Z267" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cracovie</t>
+        </is>
+      </c>
     </row>
     <row r="268" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="5" t="s">
@@ -24779,6 +26051,11 @@
       <c r="W268" t="s">
         <v>1862</v>
       </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Berne</t>
+        </is>
+      </c>
     </row>
     <row r="269" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
@@ -24820,6 +26097,11 @@
       <c r="W269" t="s">
         <v>1868</v>
       </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Baumgarten</t>
+        </is>
+      </c>
     </row>
     <row r="270" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
@@ -24861,6 +26143,11 @@
       <c r="W270" t="s">
         <v>1874</v>
       </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Pétersbourg</t>
+        </is>
+      </c>
     </row>
     <row r="271" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
@@ -24902,6 +26189,11 @@
       <c r="W271" t="s">
         <v>1880</v>
       </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bohême</t>
+        </is>
+      </c>
     </row>
     <row r="272" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="5" t="s">
@@ -24943,6 +26235,11 @@
       <c r="W272" t="s">
         <v>1888</v>
       </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="273" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
@@ -24984,6 +26281,11 @@
       <c r="W273" t="s">
         <v>1895</v>
       </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="274" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="5" t="s">
@@ -25022,6 +26324,16 @@
       <c r="W274" t="s">
         <v>1901</v>
       </c>
+      <c r="Z274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="275" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="5" t="s">
@@ -25060,6 +26372,11 @@
       <c r="W275" t="s">
         <v>1906</v>
       </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dalmatie</t>
+        </is>
+      </c>
     </row>
     <row r="276" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="5" t="s">
@@ -25101,6 +26418,11 @@
       <c r="W276" t="s">
         <v>1911</v>
       </c>
+      <c r="Z276" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bristol</t>
+        </is>
+      </c>
     </row>
     <row r="277" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="5" t="s">
@@ -25142,6 +26464,11 @@
       <c r="W277" t="s">
         <v>1916</v>
       </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="278" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="5" t="s">
@@ -25183,6 +26510,11 @@
       <c r="W278" t="s">
         <v>1919</v>
       </c>
+      <c r="Z278" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="279" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="5" t="s">
@@ -25224,6 +26556,11 @@
       <c r="W279" t="s">
         <v>1926</v>
       </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laon</t>
+        </is>
+      </c>
     </row>
     <row r="280" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="5" t="s">
@@ -25265,6 +26602,11 @@
       <c r="W280" t="s">
         <v>1933</v>
       </c>
+      <c r="Z280" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="281" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="5" t="s">
@@ -25306,6 +26648,11 @@
       <c r="W281" t="s">
         <v>1938</v>
       </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Soest</t>
+        </is>
+      </c>
     </row>
     <row r="282" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="5" t="s">
@@ -25347,6 +26694,11 @@
       <c r="W282" t="s">
         <v>1945</v>
       </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Normandie</t>
+        </is>
+      </c>
     </row>
     <row r="283" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="5" t="s">
@@ -25388,6 +26740,11 @@
       <c r="W283" t="s">
         <v>1951</v>
       </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meiderich</t>
+        </is>
+      </c>
     </row>
     <row r="284" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="5" t="s">
@@ -25429,6 +26786,11 @@
       <c r="W284" t="s">
         <v>1957</v>
       </c>
+      <c r="Z284" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Scarborough</t>
+        </is>
+      </c>
     </row>
     <row r="285" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="5" t="s">
@@ -25470,6 +26832,11 @@
       <c r="W285" t="s">
         <v>1961</v>
       </c>
+      <c r="Z285" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="286" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="5" t="s">
@@ -25508,6 +26875,11 @@
       <c r="W286" t="s">
         <v>1967</v>
       </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arezzo</t>
+        </is>
+      </c>
     </row>
     <row r="287" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="5" t="s">
@@ -25549,6 +26921,11 @@
       <c r="W287" t="s">
         <v>1970</v>
       </c>
+      <c r="Z287" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milan</t>
+        </is>
+      </c>
     </row>
     <row r="288" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="5" t="s">
@@ -25590,6 +26967,11 @@
       <c r="W288" t="s">
         <v>1975</v>
       </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kiev</t>
+        </is>
+      </c>
     </row>
     <row r="289" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="5" t="s">
@@ -25672,6 +27054,11 @@
       <c r="W290" t="s">
         <v>1985</v>
       </c>
+      <c r="Z290" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haarlem</t>
+        </is>
+      </c>
     </row>
     <row r="291" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="5" t="s">
@@ -25713,6 +27100,11 @@
       <c r="W291" t="s">
         <v>1990</v>
       </c>
+      <c r="Z291" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyde</t>
+        </is>
+      </c>
     </row>
     <row r="292" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="5" t="s">
@@ -25754,6 +27146,11 @@
       <c r="W292" t="s">
         <v>1997</v>
       </c>
+      <c r="Z292" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Genève</t>
+        </is>
+      </c>
     </row>
     <row r="293" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="5" t="s">
@@ -25795,6 +27192,11 @@
       <c r="W293" t="s">
         <v>2003</v>
       </c>
+      <c r="Z293" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prato</t>
+        </is>
+      </c>
     </row>
     <row r="294" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="5" t="s">
@@ -25836,6 +27238,16 @@
       <c r="W294" t="s">
         <v>2008</v>
       </c>
+      <c r="Z294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="295" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
@@ -25874,6 +27286,11 @@
       <c r="W295" t="s">
         <v>2014</v>
       </c>
+      <c r="Z295" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meersburg</t>
+        </is>
+      </c>
     </row>
     <row r="296" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="5" t="s">
@@ -25912,6 +27329,11 @@
       <c r="W296" t="s">
         <v>2018</v>
       </c>
+      <c r="Z296" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lombardie</t>
+        </is>
+      </c>
     </row>
     <row r="297" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="5" t="s">
@@ -25953,6 +27375,11 @@
       <c r="W297" t="s">
         <v>2023</v>
       </c>
+      <c r="Z297" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="298" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="5" t="s">
@@ -25993,6 +27420,11 @@
       </c>
       <c r="W298" t="s">
         <v>2027</v>
+      </c>
+      <c r="Z298" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
       </c>
     </row>
     <row r="299" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -26042,6 +27474,11 @@
       <c r="W299" t="s">
         <v>2031</v>
       </c>
+      <c r="Z299" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Luino</t>
+        </is>
+      </c>
     </row>
     <row r="300" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="5" t="s">
@@ -26086,6 +27523,11 @@
       <c r="W300" t="s">
         <v>2037</v>
       </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Italie du Nord</t>
+        </is>
+      </c>
     </row>
     <row r="301" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="5" t="s">
@@ -26127,6 +27569,11 @@
       <c r="W301" t="s">
         <v>2043</v>
       </c>
+      <c r="Z301" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Meschede</t>
+        </is>
+      </c>
     </row>
     <row r="302" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="5" t="s">
@@ -26165,6 +27612,11 @@
       <c r="W302" t="s">
         <v>2049</v>
       </c>
+      <c r="Z302" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bissone</t>
+        </is>
+      </c>
     </row>
     <row r="303" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="5" t="s">
@@ -26206,6 +27658,11 @@
       <c r="W303" t="s">
         <v>2054</v>
       </c>
+      <c r="Z303" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dordrecht</t>
+        </is>
+      </c>
     </row>
     <row r="304" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="5" t="s">
@@ -26247,6 +27704,11 @@
       <c r="W304" t="s">
         <v>2058</v>
       </c>
+      <c r="Z304" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gênes</t>
+        </is>
+      </c>
     </row>
     <row r="305" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="5" t="s">
@@ -26288,6 +27750,11 @@
       <c r="W305" t="s">
         <v>2063</v>
       </c>
+      <c r="Z305" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Banyuls</t>
+        </is>
+      </c>
     </row>
     <row r="306" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="5" t="s">
@@ -26329,6 +27796,11 @@
       <c r="W306" t="s">
         <v>2069</v>
       </c>
+      <c r="Z306" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kiev</t>
+        </is>
+      </c>
     </row>
     <row r="307" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="5" t="s">
@@ -26411,6 +27883,11 @@
       <c r="W308" t="s">
         <v>2081</v>
       </c>
+      <c r="Z308" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="309" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="5" t="s">
@@ -26452,6 +27929,11 @@
       <c r="W309" t="s">
         <v>2087</v>
       </c>
+      <c r="Z309" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Padoue</t>
+        </is>
+      </c>
     </row>
     <row r="310" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="5" t="s">
@@ -26493,6 +27975,11 @@
       <c r="W310" t="s">
         <v>2093</v>
       </c>
+      <c r="Z310" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Munich</t>
+        </is>
+      </c>
     </row>
     <row r="311" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="5" t="s">
@@ -26534,6 +28021,11 @@
       <c r="X311" t="s">
         <v>2099</v>
       </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vicence</t>
+        </is>
+      </c>
     </row>
     <row r="312" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="5" t="s">
@@ -26572,6 +28064,11 @@
       <c r="W312" t="s">
         <v>2104</v>
       </c>
+      <c r="Z312" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amiens</t>
+        </is>
+      </c>
     </row>
     <row r="313" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="5" t="s">
@@ -26613,6 +28110,11 @@
       <c r="W313" t="s">
         <v>2108</v>
       </c>
+      <c r="Z313" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bordeaux</t>
+        </is>
+      </c>
     </row>
     <row r="314" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="5" t="s">
@@ -26654,6 +28156,11 @@
       <c r="W314" t="s">
         <v>2114</v>
       </c>
+      <c r="Z314" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Alcalá la Real</t>
+        </is>
+      </c>
     </row>
     <row r="315" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="5" t="s">
@@ -26695,6 +28202,11 @@
       <c r="W315" t="s">
         <v>2120</v>
       </c>
+      <c r="Z315" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cateau-Cambrésis</t>
+        </is>
+      </c>
     </row>
     <row r="316" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="5" t="s">
@@ -26739,6 +28251,11 @@
       <c r="W316" t="s">
         <v>2125</v>
       </c>
+      <c r="Z316" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Parme</t>
+        </is>
+      </c>
     </row>
     <row r="317" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="5" t="s">
@@ -26777,6 +28294,11 @@
       <c r="W317" t="s">
         <v>2129</v>
       </c>
+      <c r="Z317" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Modène</t>
+        </is>
+      </c>
     </row>
     <row r="318" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="5" t="s">
@@ -26818,6 +28340,11 @@
       <c r="W318" t="s">
         <v>2134</v>
       </c>
+      <c r="Z318" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naples</t>
+        </is>
+      </c>
     </row>
     <row r="319" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="5" t="s">
@@ -26859,6 +28386,11 @@
       <c r="W319" t="s">
         <v>2138</v>
       </c>
+      <c r="Z319" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mayence</t>
+        </is>
+      </c>
     </row>
     <row r="320" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="5" t="s">
@@ -26900,6 +28432,11 @@
       <c r="W320" t="s">
         <v>2144</v>
       </c>
+      <c r="Z320" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aussig</t>
+        </is>
+      </c>
     </row>
     <row r="321" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="5" t="s">
@@ -26941,6 +28478,11 @@
       <c r="W321" t="s">
         <v>2150</v>
       </c>
+      <c r="Z321" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toulouse</t>
+        </is>
+      </c>
     </row>
     <row r="322" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="5" t="s">
@@ -27026,6 +28568,11 @@
       <c r="W323" t="s">
         <v>2161</v>
       </c>
+      <c r="Z323" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bavière</t>
+        </is>
+      </c>
     </row>
     <row r="324" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="5" t="s">
@@ -27067,6 +28614,11 @@
       <c r="W324" t="s">
         <v>2166</v>
       </c>
+      <c r="Z324" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyde</t>
+        </is>
+      </c>
     </row>
     <row r="325" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="5" t="s">
@@ -27105,6 +28657,11 @@
       <c r="W325" t="s">
         <v>2171</v>
       </c>
+      <c r="Z325" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Louvain</t>
+        </is>
+      </c>
     </row>
     <row r="326" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="5" t="s">
@@ -27146,6 +28703,11 @@
       <c r="W326" t="s">
         <v>2176</v>
       </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Etterbeek</t>
+        </is>
+      </c>
     </row>
     <row r="327" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="5" t="s">
@@ -27187,6 +28749,11 @@
       <c r="W327" t="s">
         <v>2181</v>
       </c>
+      <c r="Z327" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nancy</t>
+        </is>
+      </c>
     </row>
     <row r="328" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="5" t="s">
@@ -27225,6 +28792,11 @@
       <c r="W328" t="s">
         <v>2186</v>
       </c>
+      <c r="Z328" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Southampton</t>
+        </is>
+      </c>
     </row>
     <row r="329" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="5" t="s">
@@ -27263,6 +28835,11 @@
       <c r="W329" t="s">
         <v>2191</v>
       </c>
+      <c r="Z329" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gruchy</t>
+        </is>
+      </c>
     </row>
     <row r="330" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="5" t="s">
@@ -27301,6 +28878,11 @@
       <c r="W330" t="s">
         <v>2196</v>
       </c>
+      <c r="Z330" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gand</t>
+        </is>
+      </c>
     </row>
     <row r="331" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="5" t="s">
@@ -27339,6 +28921,11 @@
       <c r="W331" t="s">
         <v>2201</v>
       </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Montevarchi</t>
+        </is>
+      </c>
     </row>
     <row r="332" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="5" t="s">
@@ -27380,6 +28967,11 @@
       <c r="W332" t="s">
         <v>2207</v>
       </c>
+      <c r="Z332" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Livourne</t>
+        </is>
+      </c>
     </row>
     <row r="333" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="5" t="s">
@@ -27421,6 +29013,11 @@
       <c r="W333" t="s">
         <v>2215</v>
       </c>
+      <c r="Z333" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hongrie</t>
+        </is>
+      </c>
     </row>
     <row r="334" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="5" t="s">
@@ -27459,6 +29056,11 @@
       <c r="W334" t="s">
         <v>2218</v>
       </c>
+      <c r="Z334" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sienne</t>
+        </is>
+      </c>
     </row>
     <row r="335" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="5" t="s">
@@ -27500,6 +29102,11 @@
       <c r="W335" t="s">
         <v>2225</v>
       </c>
+      <c r="Z335" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Amersfoort</t>
+        </is>
+      </c>
     </row>
     <row r="336" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="5" t="s">
@@ -27576,6 +29183,11 @@
       <c r="W337" t="s">
         <v>2233</v>
       </c>
+      <c r="Z337" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="338" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="5" t="s">
@@ -27614,6 +29226,11 @@
       <c r="W338" t="s">
         <v>2238</v>
       </c>
+      <c r="Z338" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bourges</t>
+        </is>
+      </c>
     </row>
     <row r="339" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="5" t="s">
@@ -27652,6 +29269,11 @@
       <c r="W339" t="s">
         <v>2244</v>
       </c>
+      <c r="Z339" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bergame</t>
+        </is>
+      </c>
     </row>
     <row r="340" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="5" t="s">
@@ -27690,6 +29312,11 @@
       <c r="W340" t="s">
         <v>2249</v>
       </c>
+      <c r="Z340" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ivan</t>
+        </is>
+      </c>
     </row>
     <row r="341" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="5" t="s">
@@ -27728,6 +29355,11 @@
       <c r="W341" t="s">
         <v>2255</v>
       </c>
+      <c r="Z341" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liebau</t>
+        </is>
+      </c>
     </row>
     <row r="342" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="5" t="s">
@@ -27769,6 +29401,11 @@
       <c r="W342" t="s">
         <v>2262</v>
       </c>
+      <c r="Z342" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Loten</t>
+        </is>
+      </c>
     </row>
     <row r="343" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="5" t="s">
@@ -27810,6 +29447,11 @@
       <c r="W343" t="s">
         <v>2268</v>
       </c>
+      <c r="Z343" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Séville</t>
+        </is>
+      </c>
     </row>
     <row r="344" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="5" t="s">
@@ -27851,6 +29493,11 @@
       <c r="W344" t="s">
         <v>2272</v>
       </c>
+      <c r="Z344" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="345" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="5" t="s">
@@ -27892,6 +29539,11 @@
       <c r="W345" t="s">
         <v>2277</v>
       </c>
+      <c r="Z345" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nîmes</t>
+        </is>
+      </c>
     </row>
     <row r="346" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="5" t="s">
@@ -27933,6 +29585,11 @@
       <c r="W346" t="s">
         <v>2283</v>
       </c>
+      <c r="Z346" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="347" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="5" t="s">
@@ -27974,6 +29631,11 @@
       <c r="W347" t="s">
         <v>2288</v>
       </c>
+      <c r="Z347" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serina</t>
+        </is>
+      </c>
     </row>
     <row r="348" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="5" t="s">
@@ -28015,6 +29677,11 @@
       <c r="W348" t="s">
         <v>2293</v>
       </c>
+      <c r="Z348" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="349" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="5" t="s">
@@ -28053,6 +29720,11 @@
       <c r="W349" t="s">
         <v>2297</v>
       </c>
+      <c r="Z349" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="350" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="5" t="s">
@@ -28091,6 +29763,11 @@
       <c r="W350" t="s">
         <v>2302</v>
       </c>
+      <c r="Z350" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Burgos</t>
+        </is>
+      </c>
     </row>
     <row r="351" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="5" t="s">
@@ -28129,6 +29806,11 @@
       <c r="W351" t="s">
         <v>2306</v>
       </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="352" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="5" t="s">
@@ -28205,6 +29887,11 @@
       <c r="W353" t="s">
         <v>2319</v>
       </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="354" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="5" t="s">
@@ -28243,6 +29930,11 @@
       <c r="W354" t="s">
         <v>2324</v>
       </c>
+      <c r="Z354" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gênes</t>
+        </is>
+      </c>
     </row>
     <row r="355" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="5" t="s">
@@ -28281,6 +29973,11 @@
       <c r="W355" t="s">
         <v>2329</v>
       </c>
+      <c r="Z355" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vidin</t>
+        </is>
+      </c>
     </row>
     <row r="356" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="5" t="s">
@@ -28319,6 +30016,11 @@
       <c r="W356" t="s">
         <v>2334</v>
       </c>
+      <c r="Z356" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dinant</t>
+        </is>
+      </c>
     </row>
     <row r="357" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="5" t="s">
@@ -28395,6 +30097,11 @@
       <c r="W358" t="s">
         <v>2343</v>
       </c>
+      <c r="Z358" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="359" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="5" t="s">
@@ -28436,6 +30143,11 @@
       <c r="W359" t="s">
         <v>2349</v>
       </c>
+      <c r="Z359" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Città della Pieve</t>
+        </is>
+      </c>
     </row>
     <row r="360" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="5" t="s">
@@ -28474,6 +30186,11 @@
       <c r="W360" t="s">
         <v>2354</v>
       </c>
+      <c r="Z360" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="361" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="5" t="s">
@@ -28512,6 +30229,11 @@
       <c r="W361" t="s">
         <v>2359</v>
       </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="362" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="5" t="s">
@@ -28550,6 +30272,11 @@
       <c r="W362" t="s">
         <v>2365</v>
       </c>
+      <c r="Z362" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="363" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="5" t="s">
@@ -28588,6 +30315,11 @@
       <c r="W363" t="s">
         <v>2369</v>
       </c>
+      <c r="Z363" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Thomas</t>
+        </is>
+      </c>
     </row>
     <row r="364" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="5" t="s">
@@ -28626,6 +30358,16 @@
       <c r="W364" t="s">
         <v>2374</v>
       </c>
+      <c r="Z364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA364" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="365" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="5" t="s">
@@ -28664,6 +30406,11 @@
       <c r="W365" t="s">
         <v>2380</v>
       </c>
+      <c r="Z365" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saulieu</t>
+        </is>
+      </c>
     </row>
     <row r="366" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="5" t="s">
@@ -28702,6 +30449,11 @@
       <c r="W366" t="s">
         <v>2384</v>
       </c>
+      <c r="Z366" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pontorme</t>
+        </is>
+      </c>
     </row>
     <row r="367" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="5" t="s">
@@ -28816,6 +30568,11 @@
       <c r="W369" t="s">
         <v>2401</v>
       </c>
+      <c r="Z369" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Genève</t>
+        </is>
+      </c>
     </row>
     <row r="370" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="5" t="s">
@@ -28854,6 +30611,11 @@
       <c r="W370" t="s">
         <v>2406</v>
       </c>
+      <c r="Z370" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Taverna</t>
+        </is>
+      </c>
     </row>
     <row r="371" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="5" t="s">
@@ -28892,6 +30654,11 @@
       <c r="W371" t="s">
         <v>2411</v>
       </c>
+      <c r="Z371" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bologne</t>
+        </is>
+      </c>
     </row>
     <row r="372" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="5" t="s">
@@ -28930,6 +30697,11 @@
       <c r="W372" t="s">
         <v>2415</v>
       </c>
+      <c r="Z372" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marseille</t>
+        </is>
+      </c>
     </row>
     <row r="373" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="5" t="s">
@@ -28968,6 +30740,11 @@
       <c r="W373" t="s">
         <v>2419</v>
       </c>
+      <c r="Z373" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lyon</t>
+        </is>
+      </c>
     </row>
     <row r="374" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="5" t="s">
@@ -29044,6 +30821,11 @@
       <c r="W375" t="s">
         <v>2429</v>
       </c>
+      <c r="Z375" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gênes</t>
+        </is>
+      </c>
     </row>
     <row r="376" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="5" t="s">
@@ -29082,6 +30864,11 @@
       <c r="W376" t="s">
         <v>2435</v>
       </c>
+      <c r="Z376" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Trond</t>
+        </is>
+      </c>
     </row>
     <row r="377" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="5" t="s">
@@ -29120,6 +30907,11 @@
       <c r="W377" t="s">
         <v>2441</v>
       </c>
+      <c r="Z377" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Édimbourg</t>
+        </is>
+      </c>
     </row>
     <row r="378" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="5" t="s">
@@ -29158,6 +30950,11 @@
       <c r="W378" t="s">
         <v>2446</v>
       </c>
+      <c r="Z378" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vico Morcote</t>
+        </is>
+      </c>
     </row>
     <row r="379" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="5" t="s">
@@ -29196,6 +30993,11 @@
       <c r="W379" t="s">
         <v>2453</v>
       </c>
+      <c r="Z379" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Édimbourg</t>
+        </is>
+      </c>
     </row>
     <row r="380" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="5" t="s">
@@ -29234,6 +31036,11 @@
       <c r="W380" t="s">
         <v>2459</v>
       </c>
+      <c r="Z380" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arolsen</t>
+        </is>
+      </c>
     </row>
     <row r="381" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="5" t="s">
@@ -29272,6 +31079,11 @@
       <c r="W381" t="s">
         <v>2464</v>
       </c>
+      <c r="Z381" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bordeaux</t>
+        </is>
+      </c>
     </row>
     <row r="382" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="5" t="s">
@@ -29310,6 +31122,11 @@
       <c r="W382" t="s">
         <v>2468</v>
       </c>
+      <c r="Z382" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bologne</t>
+        </is>
+      </c>
     </row>
     <row r="383" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="5" t="s">
@@ -29386,6 +31203,11 @@
       <c r="W384" t="s">
         <v>2478</v>
       </c>
+      <c r="Z384" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tchouhouïv</t>
+        </is>
+      </c>
     </row>
     <row r="385" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="5" t="s">
@@ -29424,6 +31246,11 @@
       <c r="W385" t="s">
         <v>2484</v>
       </c>
+      <c r="Z385" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Plympton</t>
+        </is>
+      </c>
     </row>
     <row r="386" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="5" t="s">
@@ -29462,6 +31289,11 @@
       <c r="W386" t="s">
         <v>2489</v>
       </c>
+      <c r="Z386" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Mihiel</t>
+        </is>
+      </c>
     </row>
     <row r="387" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="5" t="s">
@@ -29500,6 +31332,11 @@
       <c r="W387" t="s">
         <v>2494</v>
       </c>
+      <c r="Z387" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saxe</t>
+        </is>
+      </c>
     </row>
     <row r="388" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="5" t="s">
@@ -29538,6 +31375,11 @@
       <c r="W388" t="s">
         <v>2500</v>
       </c>
+      <c r="Z388" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Perpignan</t>
+        </is>
+      </c>
     </row>
     <row r="389" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="5" t="s">
@@ -29576,6 +31418,11 @@
       <c r="W389" t="s">
         <v>2504</v>
       </c>
+      <c r="Z389" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="390" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="5" t="s">
@@ -29617,6 +31464,11 @@
       <c r="W390" t="s">
         <v>2509</v>
       </c>
+      <c r="Z390" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="391" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="5" t="s">
@@ -29693,6 +31545,11 @@
       <c r="W392" t="s">
         <v>2517</v>
       </c>
+      <c r="Z392" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Saint-Pétersbourg</t>
+        </is>
+      </c>
     </row>
     <row r="393" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="5" t="s">
@@ -29769,6 +31626,11 @@
       <c r="W394" t="s">
         <v>2528</v>
       </c>
+      <c r="Z394" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rome</t>
+        </is>
+      </c>
     </row>
     <row r="395" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="5" t="s">
@@ -29807,6 +31669,11 @@
       <c r="W395" t="s">
         <v>2534</v>
       </c>
+      <c r="Z395" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naples</t>
+        </is>
+      </c>
     </row>
     <row r="396" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="5" t="s">
@@ -29845,6 +31712,11 @@
       <c r="W396" t="s">
         <v>2540</v>
       </c>
+      <c r="Z396" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Malmö</t>
+        </is>
+      </c>
     </row>
     <row r="397" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="11" t="s">
@@ -29883,6 +31755,16 @@
       <c r="W397" t="s">
         <v>2544</v>
       </c>
+      <c r="Z397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA397" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="398" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="5" t="s">
@@ -29921,6 +31803,16 @@
       <c r="W398" t="s">
         <v>2547</v>
       </c>
+      <c r="Z398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA398" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="399" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="5" t="s">
@@ -29959,6 +31851,11 @@
       <c r="W399" t="s">
         <v>2552</v>
       </c>
+      <c r="Z399" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="400" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="5" t="s">
@@ -29997,6 +31894,11 @@
       <c r="W400" t="s">
         <v>2557</v>
       </c>
+      <c r="Z400" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Turin</t>
+        </is>
+      </c>
     </row>
     <row r="401" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="5" t="s">
@@ -30035,6 +31937,11 @@
       <c r="W401" t="s">
         <v>2562</v>
       </c>
+      <c r="Z401" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lyon</t>
+        </is>
+      </c>
     </row>
     <row r="402" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="5" t="s">
@@ -30073,6 +31980,11 @@
       <c r="W402" t="s">
         <v>2567</v>
       </c>
+      <c r="Z402" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="403" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="5" t="s">
@@ -30117,6 +32029,11 @@
       <c r="W403" t="s">
         <v>2572</v>
       </c>
+      <c r="Z403" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Laval</t>
+        </is>
+      </c>
     </row>
     <row r="404" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="5" t="s">
@@ -30155,6 +32072,11 @@
       <c r="W404" t="s">
         <v>2577</v>
       </c>
+      <c r="Z404" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lorry</t>
+        </is>
+      </c>
     </row>
     <row r="405" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="5" t="s">
@@ -30231,6 +32153,11 @@
       <c r="W406" t="s">
         <v>2586</v>
       </c>
+      <c r="Z406" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dijon</t>
+        </is>
+      </c>
     </row>
     <row r="407" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="5" t="s">
@@ -30269,6 +32196,11 @@
       <c r="W407" t="s">
         <v>2590</v>
       </c>
+      <c r="Z407" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Milan</t>
+        </is>
+      </c>
     </row>
     <row r="408" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="5" t="s">
@@ -30307,6 +32239,11 @@
       <c r="W408" t="s">
         <v>2595</v>
       </c>
+      <c r="Z408" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anvers</t>
+        </is>
+      </c>
     </row>
     <row r="409" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="5" t="s">
@@ -30345,6 +32282,11 @@
       <c r="W409" t="s">
         <v>2600</v>
       </c>
+      <c r="Z409" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Dublin</t>
+        </is>
+      </c>
     </row>
     <row r="410" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="5" t="s">
@@ -30383,6 +32325,11 @@
       <c r="W410" t="s">
         <v>2605</v>
       </c>
+      <c r="Z410" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murcie</t>
+        </is>
+      </c>
     </row>
     <row r="411" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="5" t="s">
@@ -30421,6 +32368,11 @@
       <c r="W411" t="s">
         <v>2609</v>
       </c>
+      <c r="Z411" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naples</t>
+        </is>
+      </c>
     </row>
     <row r="412" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="5" t="s">
@@ -30459,6 +32411,11 @@
       <c r="W412" t="s">
         <v>2614</v>
       </c>
+      <c r="Z412" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="413" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="5" t="s">
@@ -30497,6 +32454,16 @@
       <c r="W413" t="s">
         <v>2617</v>
       </c>
+      <c r="Z413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA413" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="414" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="5" t="s">
@@ -30538,6 +32505,11 @@
       <c r="W414" t="s">
         <v>2624</v>
       </c>
+      <c r="Z414" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Urbino</t>
+        </is>
+      </c>
     </row>
     <row r="415" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="5" t="s">
@@ -30576,6 +32548,11 @@
       <c r="W415" t="s">
         <v>2629</v>
       </c>
+      <c r="Z415" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="416" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="5" t="s">
@@ -30614,6 +32591,11 @@
       <c r="W416" t="s">
         <v>2634</v>
       </c>
+      <c r="Z416" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Berlin</t>
+        </is>
+      </c>
     </row>
     <row r="417" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="5" t="s">
@@ -30655,6 +32637,11 @@
       <c r="W417" t="s">
         <v>2641</v>
       </c>
+      <c r="Z417" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Tulln</t>
+        </is>
+      </c>
     </row>
     <row r="418" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="5" t="s">
@@ -30693,6 +32680,11 @@
       <c r="W418" t="s">
         <v>2645</v>
       </c>
+      <c r="Z418" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Colmar</t>
+        </is>
+      </c>
     </row>
     <row r="419" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="5" t="s">
@@ -30731,6 +32723,11 @@
       <c r="W419" t="s">
         <v>2650</v>
       </c>
+      <c r="Z419" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Palerme</t>
+        </is>
+      </c>
     </row>
     <row r="420" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="5" t="s">
@@ -30769,6 +32766,11 @@
       <c r="W420" t="s">
         <v>2654</v>
       </c>
+      <c r="Z420" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="421" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="5" t="s">
@@ -30807,6 +32809,11 @@
       <c r="W421" t="s">
         <v>2659</v>
       </c>
+      <c r="Z421" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="422" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="5" t="s">
@@ -30845,6 +32852,11 @@
       <c r="W422" t="s">
         <v>2663</v>
       </c>
+      <c r="Z422" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="423" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="5" t="s">
@@ -30883,6 +32895,11 @@
       <c r="W423" t="s">
         <v>2668</v>
       </c>
+      <c r="Z423" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cortone</t>
+        </is>
+      </c>
     </row>
     <row r="424" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="5" t="s">
@@ -30921,6 +32938,11 @@
       <c r="W424" t="s">
         <v>2675</v>
       </c>
+      <c r="Z424" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trondheim</t>
+        </is>
+      </c>
     </row>
     <row r="425" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="5" t="s">
@@ -30962,6 +32984,11 @@
       <c r="X425" t="s">
         <v>2680</v>
       </c>
+      <c r="Z425" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="426" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="5" t="s">
@@ -31000,6 +33027,11 @@
       <c r="W426" t="s">
         <v>2685</v>
       </c>
+      <c r="Z426" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Landshut</t>
+        </is>
+      </c>
     </row>
     <row r="427" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="5" t="s">
@@ -31038,6 +33070,11 @@
       <c r="W427" t="s">
         <v>2690</v>
       </c>
+      <c r="Z427" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="428" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="5" t="s">
@@ -31076,6 +33113,11 @@
       <c r="W428" t="s">
         <v>2696</v>
       </c>
+      <c r="Z428" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anvers</t>
+        </is>
+      </c>
     </row>
     <row r="429" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="5" t="s">
@@ -31114,6 +33156,11 @@
       <c r="W429" t="s">
         <v>2702</v>
       </c>
+      <c r="Z429" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Smilavichy</t>
+        </is>
+      </c>
     </row>
     <row r="430" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="5" t="s">
@@ -31152,6 +33199,11 @@
       <c r="W430" t="s">
         <v>2707</v>
       </c>
+      <c r="Z430" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyde</t>
+        </is>
+      </c>
     </row>
     <row r="431" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="5" t="s">
@@ -31190,6 +33242,11 @@
       <c r="W431" t="s">
         <v>2712</v>
       </c>
+      <c r="Z431" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Salem</t>
+        </is>
+      </c>
     </row>
     <row r="432" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="5" t="s">
@@ -31228,6 +33285,11 @@
       <c r="W432" t="s">
         <v>2719</v>
       </c>
+      <c r="Z432" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Souabe</t>
+        </is>
+      </c>
     </row>
     <row r="433" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="5" t="s">
@@ -31266,6 +33328,11 @@
       <c r="W433" t="s">
         <v>2725</v>
       </c>
+      <c r="Z433" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gênes</t>
+        </is>
+      </c>
     </row>
     <row r="434" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="5" t="s">
@@ -31304,6 +33371,11 @@
       <c r="W434" t="s">
         <v>2730</v>
       </c>
+      <c r="Z434" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rhode Island</t>
+        </is>
+      </c>
     </row>
     <row r="435" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="5" t="s">
@@ -31342,6 +33414,11 @@
       <c r="W435" t="s">
         <v>2734</v>
       </c>
+      <c r="Z435" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Liverpool</t>
+        </is>
+      </c>
     </row>
     <row r="436" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="5" t="s">
@@ -31380,6 +33457,11 @@
       <c r="W436" t="s">
         <v>2738</v>
       </c>
+      <c r="Z436" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carrare</t>
+        </is>
+      </c>
     </row>
     <row r="437" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="5" t="s">
@@ -31418,6 +33500,11 @@
       <c r="W437" t="s">
         <v>2744</v>
       </c>
+      <c r="Z437" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elmwood</t>
+        </is>
+      </c>
     </row>
     <row r="438" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="5" t="s">
@@ -31456,6 +33543,11 @@
       <c r="W438" t="s">
         <v>2749</v>
       </c>
+      <c r="Z438" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="439" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="5" t="s">
@@ -31494,6 +33586,11 @@
       <c r="W439" t="s">
         <v>2753</v>
       </c>
+      <c r="Z439" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anvers</t>
+        </is>
+      </c>
     </row>
     <row r="440" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="5" t="s">
@@ -31576,6 +33673,11 @@
       <c r="W441" t="s">
         <v>2766</v>
       </c>
+      <c r="Z441" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="442" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="5" t="s">
@@ -31617,6 +33719,11 @@
       <c r="W442" t="s">
         <v>2773</v>
       </c>
+      <c r="Z442" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Copenhague</t>
+        </is>
+      </c>
     </row>
     <row r="443" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="5" t="s">
@@ -31658,6 +33765,11 @@
       <c r="W443" t="s">
         <v>2778</v>
       </c>
+      <c r="Z443" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="444" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="5" t="s">
@@ -31699,6 +33811,11 @@
       <c r="W444" t="s">
         <v>2783</v>
       </c>
+      <c r="Z444" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nantes</t>
+        </is>
+      </c>
     </row>
     <row r="445" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="5" t="s">
@@ -31737,6 +33854,16 @@
       <c r="W445" t="s">
         <v>2787</v>
       </c>
+      <c r="Z445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA445" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="446" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="5" t="s">
@@ -31775,6 +33902,16 @@
       <c r="W446" t="s">
         <v>2793</v>
       </c>
+      <c r="Z446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
+      <c r="AA446" t="inlineStr">
+        <is>
+          <t xml:space="preserve">https://upload.wikimedia.org/wikipedia/commons/7/7b/Francesco_Rosselli_%28attribution%29._Pianta_della_Catena%2C_1470.jpg</t>
+        </is>
+      </c>
     </row>
     <row r="447" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="11" t="s">
@@ -31816,6 +33953,11 @@
       <c r="W447" t="s">
         <v>2799</v>
       </c>
+      <c r="Z447" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Intra</t>
+        </is>
+      </c>
     </row>
     <row r="448" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="5" t="s">
@@ -31854,6 +33996,11 @@
       <c r="W448" t="s">
         <v>2804</v>
       </c>
+      <c r="Z448" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rome</t>
+        </is>
+      </c>
     </row>
     <row r="449" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="5" t="s">
@@ -31892,6 +34039,11 @@
       <c r="W449" t="s">
         <v>2810</v>
       </c>
+      <c r="Z449" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ferrare</t>
+        </is>
+      </c>
     </row>
     <row r="450" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="5" t="s">
@@ -31933,6 +34085,11 @@
       <c r="W450" t="s">
         <v>2817</v>
       </c>
+      <c r="Z450" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Londres</t>
+        </is>
+      </c>
     </row>
     <row r="451" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="5" t="s">
@@ -31977,6 +34134,11 @@
       <c r="X451" t="s">
         <v>2824</v>
       </c>
+      <c r="Z451" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="452" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="5" t="s">
@@ -32018,6 +34180,11 @@
       <c r="W452" t="s">
         <v>2829</v>
       </c>
+      <c r="Z452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="453" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="5" t="s">
@@ -32059,6 +34226,11 @@
       <c r="W453" t="s">
         <v>2835</v>
       </c>
+      <c r="Z453" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bessines</t>
+        </is>
+      </c>
     </row>
     <row r="454" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="5" t="s">
@@ -32100,6 +34272,11 @@
       <c r="W454" t="s">
         <v>2841</v>
       </c>
+      <c r="Z454" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lausanne</t>
+        </is>
+      </c>
     </row>
     <row r="455" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="5" t="s">
@@ -32141,6 +34318,11 @@
       <c r="W455" t="s">
         <v>2847</v>
       </c>
+      <c r="Z455" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyde</t>
+        </is>
+      </c>
     </row>
     <row r="456" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="5" t="s">
@@ -32179,6 +34361,11 @@
       <c r="W456" t="s">
         <v>2852</v>
       </c>
+      <c r="Z456" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gand</t>
+        </is>
+      </c>
     </row>
     <row r="457" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="5" t="s">
@@ -32261,6 +34448,11 @@
       <c r="W458" t="s">
         <v>2863</v>
       </c>
+      <c r="Z458" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utrecht</t>
+        </is>
+      </c>
     </row>
     <row r="459" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="5" t="s">
@@ -32302,6 +34494,11 @@
       <c r="W459" t="s">
         <v>2870</v>
       </c>
+      <c r="Z459" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Anvers</t>
+        </is>
+      </c>
     </row>
     <row r="460" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="5" t="s">
@@ -32419,6 +34616,11 @@
       <c r="W462" t="s">
         <v>2886</v>
       </c>
+      <c r="Z462" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyde</t>
+        </is>
+      </c>
     </row>
     <row r="463" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="5" t="s">
@@ -32457,6 +34659,11 @@
       <c r="W463" t="s">
         <v>2890</v>
       </c>
+      <c r="Z463" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Heemskerk</t>
+        </is>
+      </c>
     </row>
     <row r="464" spans="1:24" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="5" t="s">
@@ -32495,6 +34702,11 @@
       <c r="W464" t="s">
         <v>2895</v>
       </c>
+      <c r="Z464" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Utrecht</t>
+        </is>
+      </c>
     </row>
     <row r="465" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="5" t="s">
@@ -32533,6 +34745,11 @@
       <c r="W465" t="s">
         <v>2899</v>
       </c>
+      <c r="Z465" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Leyde</t>
+        </is>
+      </c>
     </row>
     <row r="466" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="5" t="s">
@@ -32571,6 +34788,11 @@
       <c r="W466" t="s">
         <v>2905</v>
       </c>
+      <c r="Z466" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Nice</t>
+        </is>
+      </c>
     </row>
     <row r="467" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="5" t="s">
@@ -32609,6 +34831,11 @@
       <c r="W467" t="s">
         <v>2909</v>
       </c>
+      <c r="Z467" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haarlem</t>
+        </is>
+      </c>
     </row>
     <row r="468" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="5" t="s">
@@ -32688,6 +34915,11 @@
       <c r="W469" t="s">
         <v>2919</v>
       </c>
+      <c r="Z469" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Haarlem</t>
+        </is>
+      </c>
     </row>
     <row r="470" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="5" t="s">
@@ -32726,6 +34958,11 @@
       <c r="W470" t="s">
         <v>2926</v>
       </c>
+      <c r="Z470" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Naarden</t>
+        </is>
+      </c>
     </row>
     <row r="471" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="5" t="s">
@@ -32764,6 +35001,11 @@
       <c r="W471" t="s">
         <v>2931</v>
       </c>
+      <c r="Z471" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gand</t>
+        </is>
+      </c>
     </row>
     <row r="472" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="5" t="s">
@@ -32802,6 +35044,11 @@
       <c r="W472" t="s">
         <v>2935</v>
       </c>
+      <c r="Z472" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Arezzo</t>
+        </is>
+      </c>
     </row>
     <row r="473" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="5" t="s">
@@ -32881,6 +35128,11 @@
       <c r="W474" t="s">
         <v>2945</v>
       </c>
+      <c r="Z474" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ligornetto</t>
+        </is>
+      </c>
     </row>
     <row r="475" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="5" t="s">
@@ -32957,6 +35209,11 @@
       <c r="W476" t="s">
         <v>2954</v>
       </c>
+      <c r="Z476" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="477" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="5" t="s">
@@ -33033,6 +35290,11 @@
       <c r="W478" t="s">
         <v>2964</v>
       </c>
+      <c r="Z478" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Avignon</t>
+        </is>
+      </c>
     </row>
     <row r="479" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="5" t="s">
@@ -33071,6 +35333,11 @@
       <c r="W479" t="s">
         <v>2969</v>
       </c>
+      <c r="Z479" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vérone</t>
+        </is>
+      </c>
     </row>
     <row r="480" spans="1:25" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="5" t="s">
@@ -33115,6 +35382,11 @@
       <c r="Y480" t="s">
         <v>2977</v>
       </c>
+      <c r="Z480" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="481" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="5" t="s">
@@ -33153,6 +35425,11 @@
       <c r="W481" t="s">
         <v>2980</v>
       </c>
+      <c r="Z481" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trente</t>
+        </is>
+      </c>
     </row>
     <row r="482" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="5" t="s">
@@ -33191,6 +35468,11 @@
       <c r="W482" t="s">
         <v>2987</v>
       </c>
+      <c r="Z482" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Venise</t>
+        </is>
+      </c>
     </row>
     <row r="483" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="5" t="s">
@@ -33229,6 +35511,11 @@
       <c r="W483" t="s">
         <v>2990</v>
       </c>
+      <c r="Z483" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murano</t>
+        </is>
+      </c>
     </row>
     <row r="484" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="5" t="s">
@@ -33267,6 +35554,11 @@
       <c r="W484" t="s">
         <v>2995</v>
       </c>
+      <c r="Z484" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Murano</t>
+        </is>
+      </c>
     </row>
     <row r="485" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="5" t="s">
@@ -33305,6 +35597,11 @@
       <c r="W485" t="s">
         <v>3002</v>
       </c>
+      <c r="Z485" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Marbourg</t>
+        </is>
+      </c>
     </row>
     <row r="486" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="5" t="s">
@@ -33343,6 +35640,11 @@
       <c r="W486" t="s">
         <v>3007</v>
       </c>
+      <c r="Z486" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Torjok</t>
+        </is>
+      </c>
     </row>
     <row r="487" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="5" t="s">
@@ -33381,6 +35683,11 @@
       <c r="W487" t="s">
         <v>3012</v>
       </c>
+      <c r="Z487" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Toula</t>
+        </is>
+      </c>
     </row>
     <row r="488" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="5" t="s">
@@ -33419,6 +35726,11 @@
       <c r="W488" t="s">
         <v>3016</v>
       </c>
+      <c r="Z488" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Paris</t>
+        </is>
+      </c>
     </row>
     <row r="489" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="5" t="s">
@@ -33460,6 +35772,11 @@
       <c r="W489" t="s">
         <v>3022</v>
       </c>
+      <c r="Z489" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Omsk</t>
+        </is>
+      </c>
     </row>
     <row r="490" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="5" t="s">
@@ -33501,6 +35818,11 @@
       <c r="W490" t="s">
         <v>3027</v>
       </c>
+      <c r="Z490" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cuiseaux</t>
+        </is>
+      </c>
     </row>
     <row r="491" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="5" t="s">
@@ -33542,6 +35864,11 @@
       <c r="W491" t="s">
         <v>3034</v>
       </c>
+      <c r="Z491" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Rome</t>
+        </is>
+      </c>
     </row>
     <row r="492" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="5" t="s">
@@ -33583,6 +35910,11 @@
       <c r="W492" t="s">
         <v>3040</v>
       </c>
+      <c r="Z492" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Valenciennes</t>
+        </is>
+      </c>
     </row>
     <row r="493" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="5" t="s">
@@ -33624,6 +35956,11 @@
       <c r="W493" t="s">
         <v>3046</v>
       </c>
+      <c r="Z493" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pennsylvanie</t>
+        </is>
+      </c>
     </row>
     <row r="494" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="5" t="s">
@@ -33665,6 +36002,11 @@
       <c r="W494" t="s">
         <v>3052</v>
       </c>
+      <c r="Z494" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lowell</t>
+        </is>
+      </c>
     </row>
     <row r="495" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="5" t="s">
@@ -33779,6 +36121,11 @@
       <c r="W497" t="s">
         <v>3069</v>
       </c>
+      <c r="Z497" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knowsley</t>
+        </is>
+      </c>
     </row>
     <row r="498" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="5" t="s">
@@ -33817,6 +36164,11 @@
       <c r="W498" t="s">
         <v>3073</v>
       </c>
+      <c r="Z498" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hadleigh</t>
+        </is>
+      </c>
     </row>
     <row r="499" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6" t="s">
@@ -33855,6 +36207,11 @@
       <c r="W499" t="s">
         <v>3079</v>
       </c>
+      <c r="Z499" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Derby</t>
+        </is>
+      </c>
     </row>
     <row r="500" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="5" t="s">
@@ -33896,6 +36253,11 @@
       <c r="W500" t="s">
         <v>3084</v>
       </c>
+      <c r="Z500" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Bologne</t>
+        </is>
+      </c>
     </row>
     <row r="501" spans="1:23" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="5" t="s">
@@ -33937,6 +36299,11 @@
       <c r="W501" t="s">
         <v>3091</v>
       </c>
+      <c r="Z501" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Francfort</t>
+        </is>
+      </c>
     </row>
     <row r="502" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A502" s="5" t="s">
@@ -33963,6 +36330,11 @@
       <c r="I502" s="7">
         <v>3</v>
       </c>
+      <c r="Z502" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Florence</t>
+        </is>
+      </c>
     </row>
     <row r="503" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A503" s="5" t="s">
@@ -33988,6 +36360,11 @@
       </c>
       <c r="I503" s="7">
         <v>3</v>
+      </c>
+      <c r="Z503" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cambrai</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -3286,7 +3286,7 @@
     <t>https://thumb.wikimedia.org/wikipedia/commons/thumb/4/4f/John_Flaxman_by_Guy_Head.jpg/960px-John_Flaxman_by_Guy_Head.jpg?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=thumbnail&amp;uselang=fr</t>
   </si>
   <si>
-    <t>Monument à Lord Mansfield</t>
+    <t>Tombeau de Lord Mansfield</t>
   </si>
   <si>
     <t>Peter</t>
@@ -4129,7 +4129,7 @@
     <t>1550 environ</t>
   </si>
   <si>
-    <t>Quatre éphèbes aux dauphins</t>
+    <t>Statues de la fontaine aux tortues</t>
   </si>
   <si>
     <t>LAURANA</t>
@@ -5119,7 +5119,7 @@
     <t>1714</t>
   </si>
   <si>
-    <t>Tombeau du Maréchal de Saxe</t>
+    <t>Tombe de Maurice de Saxe</t>
   </si>
   <si>
     <t>Germain</t>
@@ -5545,7 +5545,7 @@
     <t>RYSBRACK</t>
   </si>
   <si>
-    <t>Monument à Isaac Newton</t>
+    <t>Tombeau d'Isaac Newton</t>
   </si>
   <si>
     <t>Augustus</t>
@@ -5554,7 +5554,7 @@
     <t>SAINT-GAUDENS</t>
   </si>
   <si>
-    <t>Monument à Robert Gould Shaw et au 54e régiment du Massachusetts</t>
+    <t>Mémorial à Robert Gould Shaw et au 54e régiment du Massachusetts</t>
   </si>
   <si>
     <t>SALZILLO</t>
@@ -6445,7 +6445,7 @@
     <t>Woolner</t>
   </si>
   <si>
-    <t>Statue du Capitaine James Cook</t>
+    <t>Mémorial au Capitaine James Cook</t>
   </si>
   <si>
     <t>WRIGHT of DERBY</t>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -1372,7 +1372,7 @@
     <t>1564</t>
   </si>
   <si>
-    <t>La Parabole des aveugles</t>
+    <t>L'Avocat du village</t>
   </si>
   <si>
     <t>Filippo</t>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7187" uniqueCount="2332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7197" uniqueCount="2332">
   <si>
     <t>Prénom</t>
   </si>
@@ -2611,7 +2611,7 @@
     <t>1452</t>
   </si>
   <si>
-    <t>1517</t>
+    <t>1519</t>
   </si>
   <si>
     <t>La Joconde</t>
@@ -9991,6 +9991,9 @@
       <c r="P62" t="s">
         <v>28</v>
       </c>
+      <c r="S62" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
@@ -10527,6 +10530,9 @@
       <c r="P75" t="s">
         <v>28</v>
       </c>
+      <c r="S75" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
@@ -13408,6 +13414,9 @@
       <c r="P146" t="s">
         <v>28</v>
       </c>
+      <c r="S146" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
@@ -14271,6 +14280,9 @@
       <c r="P168" t="s">
         <v>28</v>
       </c>
+      <c r="S168" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="s">
@@ -18382,6 +18394,9 @@
       <c r="Q269">
         <v>21</v>
       </c>
+      <c r="S269" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="s">
@@ -19925,6 +19940,9 @@
       <c r="P307" t="s">
         <v>28</v>
       </c>
+      <c r="S307" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="s">
@@ -20543,6 +20561,9 @@
       <c r="P322" t="s">
         <v>28</v>
       </c>
+      <c r="S322" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="s">
@@ -21333,6 +21354,9 @@
       <c r="Q342">
         <v>16</v>
       </c>
+      <c r="S342" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="s">
@@ -23222,6 +23246,9 @@
       <c r="P391" t="s">
         <v>28</v>
       </c>
+      <c r="S391" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="s">
@@ -26239,6 +26266,9 @@
         <v>28</v>
       </c>
       <c r="P468" t="s">
+        <v>28</v>
+      </c>
+      <c r="S468" t="s">
         <v>28</v>
       </c>
     </row>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7197" uniqueCount="2332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7201" uniqueCount="2332">
   <si>
     <t>Prénom</t>
   </si>
@@ -11280,6 +11280,12 @@
       <c r="P93" t="s">
         <v>28</v>
       </c>
+      <c r="S93" t="s">
+        <v>28</v>
+      </c>
+      <c r="T93">
+        <v>5</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
@@ -12164,6 +12170,9 @@
       <c r="P115" t="s">
         <v>28</v>
       </c>
+      <c r="S115" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
@@ -19899,6 +19908,9 @@
       <c r="P306" t="s">
         <v>28</v>
       </c>
+      <c r="S306" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="s">
@@ -21118,6 +21130,9 @@
         <v>28</v>
       </c>
       <c r="P336" t="s">
+        <v>28</v>
+      </c>
+      <c r="S336" t="s">
         <v>28</v>
       </c>
     </row>

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -9666,6 +9666,9 @@
       <c r="P54" t="s">
         <v>28</v>
       </c>
+      <c r="Q54">
+        <v>15</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="s">

--- a/quizzes/artistes-nationalites-maitre.xlsx
+++ b/quizzes/artistes-nationalites-maitre.xlsx
@@ -1,38 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steph\Documents\MEMNART\éléments à uploader\vers quizzes\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8126B800-9120-4B25-AC72-98CE99FEC0D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Images" sheetId="2" r:id="rId2"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7201" uniqueCount="2332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7202" uniqueCount="2333">
   <si>
     <t>Prénom</t>
   </si>
@@ -7028,19 +7017,27 @@
   </si>
   <si>
     <t>Statue de Saint-Luc dessinant la Vierge, Tournai</t>
+  </si>
+  <si>
+    <t>https://upload.wikimedia.org/wikipedia/commons/6/62/Casa_vasari_FI%2C_salone%2C_ritratti_a%2C_donatello.JPG?utm_source=commons.wikimedia.org&amp;utm_campaign=index&amp;utm_content=original</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -7063,17 +7060,28 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+  <cellXfs count="2">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Lien hypertexte" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -7398,32 +7406,33 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:T503"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" customWidth="1"/>
-    <col min="2" max="2" width="11.83203125" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" customWidth="1"/>
-    <col min="4" max="4" width="13.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="15.83203125" customWidth="1"/>
-    <col min="8" max="8" width="11.83203125" customWidth="1"/>
-    <col min="9" max="9" width="21.83203125" customWidth="1"/>
-    <col min="10" max="10" width="20.83203125" customWidth="1"/>
-    <col min="11" max="11" width="11.83203125" customWidth="1"/>
-    <col min="12" max="12" width="20.83203125" customWidth="1"/>
-    <col min="13" max="13" width="30.83203125" customWidth="1"/>
-    <col min="14" max="14" width="10.83203125" customWidth="1"/>
-    <col min="15" max="15" width="11.83203125" customWidth="1"/>
-    <col min="16" max="16" width="20.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="14.83203125" customWidth="1"/>
-    <col min="19" max="19" width="26.83203125" customWidth="1"/>
-    <col min="20" max="20" width="20.83203125" customWidth="1"/>
+    <col min="1" max="1" width="10.875" customWidth="1"/>
+    <col min="2" max="2" width="11.875" customWidth="1"/>
+    <col min="3" max="3" width="10.875" customWidth="1"/>
+    <col min="4" max="4" width="13.875" customWidth="1"/>
+    <col min="5" max="5" width="10.875" customWidth="1"/>
+    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="7" max="7" width="15.875" customWidth="1"/>
+    <col min="8" max="8" width="11.875" customWidth="1"/>
+    <col min="9" max="9" width="21.875" customWidth="1"/>
+    <col min="10" max="10" width="20.875" customWidth="1"/>
+    <col min="11" max="11" width="11.875" customWidth="1"/>
+    <col min="12" max="12" width="20.875" customWidth="1"/>
+    <col min="13" max="13" width="30.875" customWidth="1"/>
+    <col min="14" max="14" width="10.875" customWidth="1"/>
+    <col min="15" max="15" width="11.875" customWidth="1"/>
+    <col min="16" max="16" width="20.875" customWidth="1"/>
+    <col min="17" max="17" width="12.875" customWidth="1"/>
+    <col min="18" max="18" width="14.875" customWidth="1"/>
+    <col min="19" max="19" width="26.875" customWidth="1"/>
+    <col min="20" max="20" width="20.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -7485,7 +7494,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -7526,7 +7535,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>29</v>
       </c>
@@ -7567,7 +7576,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>34</v>
       </c>
@@ -7608,7 +7617,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>43</v>
       </c>
@@ -7646,7 +7655,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>50</v>
       </c>
@@ -7687,7 +7696,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>58</v>
       </c>
@@ -7728,7 +7737,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>66</v>
       </c>
@@ -7769,7 +7778,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>72</v>
       </c>
@@ -7810,7 +7819,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>79</v>
       </c>
@@ -7851,7 +7860,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>86</v>
       </c>
@@ -7895,7 +7904,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>94</v>
       </c>
@@ -7933,7 +7942,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>99</v>
       </c>
@@ -7971,7 +7980,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>103</v>
       </c>
@@ -8012,7 +8021,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>109</v>
       </c>
@@ -8053,7 +8062,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>115</v>
       </c>
@@ -8094,7 +8103,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>121</v>
       </c>
@@ -8135,7 +8144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>127</v>
       </c>
@@ -8173,7 +8182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>132</v>
       </c>
@@ -8214,7 +8223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>139</v>
       </c>
@@ -8255,7 +8264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>145</v>
       </c>
@@ -8296,7 +8305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>152</v>
       </c>
@@ -8337,7 +8346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>158</v>
       </c>
@@ -8381,7 +8390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>164</v>
       </c>
@@ -8422,7 +8431,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>170</v>
       </c>
@@ -8466,7 +8475,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>177</v>
       </c>
@@ -8510,7 +8519,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>184</v>
       </c>
@@ -8551,7 +8560,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>189</v>
       </c>
@@ -8592,7 +8601,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>195</v>
       </c>
@@ -8633,7 +8642,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>201</v>
       </c>
@@ -8674,7 +8683,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>207</v>
       </c>
@@ -8715,7 +8724,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>212</v>
       </c>
@@ -8756,7 +8765,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>217</v>
       </c>
@@ -8797,7 +8806,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>223</v>
       </c>
@@ -8838,7 +8847,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>228</v>
       </c>
@@ -8882,7 +8891,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>234</v>
       </c>
@@ -8923,7 +8932,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>240</v>
       </c>
@@ -8964,7 +8973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>246</v>
       </c>
@@ -9005,7 +9014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>86</v>
       </c>
@@ -9046,7 +9055,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>257</v>
       </c>
@@ -9084,7 +9093,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>263</v>
       </c>
@@ -9125,7 +9134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>270</v>
       </c>
@@ -9166,7 +9175,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>275</v>
       </c>
@@ -9207,7 +9216,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>281</v>
       </c>
@@ -9245,7 +9254,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>287</v>
       </c>
@@ -9286,7 +9295,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>293</v>
       </c>
@@ -9333,7 +9342,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>299</v>
       </c>
@@ -9377,7 +9386,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>305</v>
       </c>
@@ -9418,7 +9427,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>312</v>
       </c>
@@ -9459,7 +9468,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>318</v>
       </c>
@@ -9500,7 +9509,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>324</v>
       </c>
@@ -9541,7 +9550,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>332</v>
       </c>
@@ -9582,7 +9591,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>338</v>
       </c>
@@ -9623,7 +9632,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>344</v>
       </c>
@@ -9670,7 +9679,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>351</v>
       </c>
@@ -9711,7 +9720,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>357</v>
       </c>
@@ -9752,7 +9761,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>357</v>
       </c>
@@ -9790,7 +9799,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>368</v>
       </c>
@@ -9831,7 +9840,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>374</v>
       </c>
@@ -9872,7 +9881,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>378</v>
       </c>
@@ -9913,7 +9922,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>383</v>
       </c>
@@ -9954,7 +9963,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>388</v>
       </c>
@@ -9998,7 +10007,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>393</v>
       </c>
@@ -10039,7 +10048,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>94</v>
       </c>
@@ -10080,7 +10089,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>405</v>
       </c>
@@ -10121,7 +10130,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>324</v>
       </c>
@@ -10162,7 +10171,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>411</v>
       </c>
@@ -10203,7 +10212,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>417</v>
       </c>
@@ -10244,7 +10253,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>299</v>
       </c>
@@ -10285,7 +10294,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>428</v>
       </c>
@@ -10329,7 +10338,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>434</v>
       </c>
@@ -10370,7 +10379,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>34</v>
       </c>
@@ -10411,7 +10420,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>34</v>
       </c>
@@ -10452,7 +10461,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>449</v>
       </c>
@@ -10490,7 +10499,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>454</v>
       </c>
@@ -10537,7 +10546,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>460</v>
       </c>
@@ -10578,7 +10587,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>466</v>
       </c>
@@ -10619,7 +10628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>471</v>
       </c>
@@ -10660,7 +10669,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>478</v>
       </c>
@@ -10701,7 +10710,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>484</v>
       </c>
@@ -10742,7 +10751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>490</v>
       </c>
@@ -10786,7 +10795,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>228</v>
       </c>
@@ -10830,7 +10839,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>305</v>
       </c>
@@ -10871,7 +10880,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>504</v>
       </c>
@@ -10912,7 +10921,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>508</v>
       </c>
@@ -10950,7 +10959,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>512</v>
       </c>
@@ -10991,7 +11000,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>517</v>
       </c>
@@ -11032,7 +11041,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>521</v>
       </c>
@@ -11076,7 +11085,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>528</v>
       </c>
@@ -11117,7 +11126,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>533</v>
       </c>
@@ -11158,7 +11167,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>539</v>
       </c>
@@ -11199,7 +11208,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>545</v>
       </c>
@@ -11243,7 +11252,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>549</v>
       </c>
@@ -11290,7 +11299,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>555</v>
       </c>
@@ -11331,7 +11340,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>561</v>
       </c>
@@ -11372,7 +11381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:20" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>567</v>
       </c>
@@ -11410,7 +11419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>571</v>
       </c>
@@ -11448,7 +11457,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>576</v>
       </c>
@@ -11489,7 +11498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>581</v>
       </c>
@@ -11527,7 +11536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>584</v>
       </c>
@@ -11565,7 +11574,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>34</v>
       </c>
@@ -11606,7 +11615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>594</v>
       </c>
@@ -11644,7 +11653,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>598</v>
       </c>
@@ -11685,7 +11694,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>517</v>
       </c>
@@ -11726,7 +11735,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>94</v>
       </c>
@@ -11767,7 +11776,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>344</v>
       </c>
@@ -11808,7 +11817,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>164</v>
       </c>
@@ -11852,7 +11861,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>132</v>
       </c>
@@ -11893,7 +11902,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>625</v>
       </c>
@@ -11934,7 +11943,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>631</v>
       </c>
@@ -11972,7 +11981,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>635</v>
       </c>
@@ -12013,7 +12022,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>638</v>
       </c>
@@ -12054,7 +12063,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>644</v>
       </c>
@@ -12095,7 +12104,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>504</v>
       </c>
@@ -12133,7 +12142,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>484</v>
       </c>
@@ -12177,7 +12186,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>344</v>
       </c>
@@ -12215,7 +12224,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>631</v>
       </c>
@@ -12256,7 +12265,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>667</v>
       </c>
@@ -12297,7 +12306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>667</v>
       </c>
@@ -12338,7 +12347,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>411</v>
       </c>
@@ -12379,7 +12388,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>682</v>
       </c>
@@ -12423,7 +12432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>682</v>
       </c>
@@ -12464,7 +12473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>164</v>
       </c>
@@ -12502,7 +12511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>696</v>
       </c>
@@ -12540,7 +12549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>700</v>
       </c>
@@ -12581,7 +12590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>504</v>
       </c>
@@ -12625,7 +12634,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>263</v>
       </c>
@@ -12666,7 +12675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>717</v>
       </c>
@@ -12707,7 +12716,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>722</v>
       </c>
@@ -12745,7 +12754,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>727</v>
       </c>
@@ -12783,7 +12792,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>731</v>
       </c>
@@ -12821,7 +12830,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>735</v>
       </c>
@@ -12859,7 +12868,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>739</v>
       </c>
@@ -12897,7 +12906,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>744</v>
       </c>
@@ -12935,7 +12944,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>749</v>
       </c>
@@ -12973,7 +12982,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>752</v>
       </c>
@@ -13014,7 +13023,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>757</v>
       </c>
@@ -13055,7 +13064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>762</v>
       </c>
@@ -13096,7 +13105,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>767</v>
       </c>
@@ -13137,7 +13146,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>773</v>
       </c>
@@ -13178,7 +13187,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>779</v>
       </c>
@@ -13219,7 +13228,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>783</v>
       </c>
@@ -13263,7 +13272,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>788</v>
       </c>
@@ -13301,7 +13310,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>792</v>
       </c>
@@ -13342,7 +13351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>357</v>
       </c>
@@ -13386,7 +13395,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>802</v>
       </c>
@@ -13430,7 +13439,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>34</v>
       </c>
@@ -13471,7 +13480,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>812</v>
       </c>
@@ -13509,7 +13518,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>127</v>
       </c>
@@ -13550,7 +13559,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>821</v>
       </c>
@@ -13588,7 +13597,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>825</v>
       </c>
@@ -13629,7 +13638,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>631</v>
       </c>
@@ -13670,7 +13679,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>833</v>
       </c>
@@ -13708,7 +13717,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>837</v>
       </c>
@@ -13746,7 +13755,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>837</v>
       </c>
@@ -13787,7 +13796,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>845</v>
       </c>
@@ -13825,7 +13834,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>850</v>
       </c>
@@ -13863,7 +13872,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>257</v>
       </c>
@@ -13901,7 +13910,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>856</v>
       </c>
@@ -13942,7 +13951,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>434</v>
       </c>
@@ -13980,7 +13989,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>802</v>
       </c>
@@ -14018,7 +14027,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>868</v>
       </c>
@@ -14059,7 +14068,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>873</v>
       </c>
@@ -14100,7 +14109,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>735</v>
       </c>
@@ -14138,7 +14147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>883</v>
       </c>
@@ -14176,7 +14185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>873</v>
       </c>
@@ -14214,7 +14223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>873</v>
       </c>
@@ -14252,7 +14261,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>892</v>
       </c>
@@ -14296,7 +14305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>490</v>
       </c>
@@ -14337,7 +14346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>902</v>
       </c>
@@ -14375,7 +14384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>158</v>
       </c>
@@ -14416,7 +14425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>909</v>
       </c>
@@ -14454,7 +14463,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>212</v>
       </c>
@@ -14492,7 +14501,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>873</v>
       </c>
@@ -14536,7 +14545,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>919</v>
       </c>
@@ -14580,7 +14589,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>449</v>
       </c>
@@ -14621,7 +14630,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>927</v>
       </c>
@@ -14662,7 +14671,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>933</v>
       </c>
@@ -14703,7 +14712,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>937</v>
       </c>
@@ -14744,7 +14753,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>943</v>
       </c>
@@ -14785,7 +14794,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>949</v>
       </c>
@@ -14829,7 +14838,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>902</v>
       </c>
@@ -14867,7 +14876,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>960</v>
       </c>
@@ -14908,7 +14917,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>966</v>
       </c>
@@ -14949,7 +14958,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>970</v>
       </c>
@@ -14977,6 +14986,9 @@
       <c r="I185">
         <v>1</v>
       </c>
+      <c r="J185" s="1" t="s">
+        <v>2332</v>
+      </c>
       <c r="K185" t="s">
         <v>971</v>
       </c>
@@ -14989,8 +15001,11 @@
       <c r="P185" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="186">
+      <c r="Q185">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="186" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>976</v>
       </c>
@@ -15034,7 +15049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>504</v>
       </c>
@@ -15075,7 +15090,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>986</v>
       </c>
@@ -15116,7 +15131,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>773</v>
       </c>
@@ -15157,7 +15172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>998</v>
       </c>
@@ -15195,7 +15210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1003</v>
       </c>
@@ -15236,7 +15251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>1008</v>
       </c>
@@ -15277,7 +15292,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>270</v>
       </c>
@@ -15318,7 +15333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>94</v>
       </c>
@@ -15359,7 +15374,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>79</v>
       </c>
@@ -15400,7 +15415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>164</v>
       </c>
@@ -15441,7 +15456,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1029</v>
       </c>
@@ -15482,7 +15497,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>1035</v>
       </c>
@@ -15523,7 +15538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>1040</v>
       </c>
@@ -15564,7 +15579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1045</v>
       </c>
@@ -15605,7 +15620,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>466</v>
       </c>
@@ -15646,7 +15661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>1053</v>
       </c>
@@ -15684,7 +15699,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>270</v>
       </c>
@@ -15725,7 +15740,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1061</v>
       </c>
@@ -15766,7 +15781,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>845</v>
       </c>
@@ -15807,7 +15822,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1069</v>
       </c>
@@ -15848,7 +15863,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>1074</v>
       </c>
@@ -15889,7 +15904,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>1078</v>
       </c>
@@ -15930,7 +15945,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>132</v>
       </c>
@@ -15971,7 +15986,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>1087</v>
       </c>
@@ -16009,7 +16024,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>966</v>
       </c>
@@ -16050,7 +16065,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>1095</v>
       </c>
@@ -16091,7 +16106,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>757</v>
       </c>
@@ -16129,7 +16144,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1104</v>
       </c>
@@ -16167,7 +16182,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>344</v>
       </c>
@@ -16208,7 +16223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1112</v>
       </c>
@@ -16249,7 +16264,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>1118</v>
       </c>
@@ -16290,7 +16305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>1123</v>
       </c>
@@ -16331,7 +16346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1129</v>
       </c>
@@ -16372,7 +16387,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>1133</v>
       </c>
@@ -16413,7 +16428,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>164</v>
       </c>
@@ -16454,7 +16469,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>257</v>
       </c>
@@ -16495,7 +16510,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>549</v>
       </c>
@@ -16536,7 +16551,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1147</v>
       </c>
@@ -16580,7 +16595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1154</v>
       </c>
@@ -16621,7 +16636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>1158</v>
       </c>
@@ -16662,7 +16677,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>1162</v>
       </c>
@@ -16700,7 +16715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>561</v>
       </c>
@@ -16741,7 +16756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1169</v>
       </c>
@@ -16782,7 +16797,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>201</v>
       </c>
@@ -16826,7 +16841,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>234</v>
       </c>
@@ -16867,7 +16882,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>405</v>
       </c>
@@ -16908,7 +16923,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>919</v>
       </c>
@@ -16949,7 +16964,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>94</v>
       </c>
@@ -16990,7 +17005,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1192</v>
       </c>
@@ -17031,7 +17046,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>1196</v>
       </c>
@@ -17072,7 +17087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>1202</v>
       </c>
@@ -17116,7 +17131,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>344</v>
       </c>
@@ -17154,7 +17169,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>1212</v>
       </c>
@@ -17195,7 +17210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>1217</v>
       </c>
@@ -17236,7 +17251,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>517</v>
       </c>
@@ -17277,7 +17292,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>1226</v>
       </c>
@@ -17318,7 +17333,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>1232</v>
       </c>
@@ -17356,7 +17371,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>735</v>
       </c>
@@ -17397,7 +17412,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>234</v>
       </c>
@@ -17438,7 +17453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>1245</v>
       </c>
@@ -17476,7 +17491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>1248</v>
       </c>
@@ -17514,7 +17529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>735</v>
       </c>
@@ -17555,7 +17570,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>478</v>
       </c>
@@ -17596,7 +17611,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1259</v>
       </c>
@@ -17637,7 +17652,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>1264</v>
       </c>
@@ -17678,7 +17693,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>324</v>
       </c>
@@ -17719,7 +17734,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>152</v>
       </c>
@@ -17760,7 +17775,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1278</v>
       </c>
@@ -17801,7 +17816,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1282</v>
       </c>
@@ -17842,7 +17857,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1286</v>
       </c>
@@ -17883,7 +17898,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1290</v>
       </c>
@@ -17921,7 +17936,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1294</v>
       </c>
@@ -17962,7 +17977,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>1298</v>
       </c>
@@ -18003,7 +18018,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1303</v>
       </c>
@@ -18044,7 +18059,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1308</v>
       </c>
@@ -18085,7 +18100,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B262" t="s">
         <v>1312</v>
       </c>
@@ -18123,7 +18138,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>594</v>
       </c>
@@ -18161,7 +18176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1319</v>
       </c>
@@ -18202,7 +18217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1323</v>
       </c>
@@ -18240,7 +18255,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1327</v>
       </c>
@@ -18281,7 +18296,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1332</v>
       </c>
@@ -18322,7 +18337,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>549</v>
       </c>
@@ -18363,7 +18378,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1341</v>
       </c>
@@ -18410,7 +18425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1345</v>
       </c>
@@ -18451,7 +18466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1349</v>
       </c>
@@ -18492,7 +18507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1353</v>
       </c>
@@ -18533,7 +18548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>631</v>
       </c>
@@ -18574,7 +18589,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1364</v>
       </c>
@@ -18612,7 +18627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>735</v>
       </c>
@@ -18650,7 +18665,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>164</v>
       </c>
@@ -18691,7 +18706,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>635</v>
       </c>
@@ -18732,7 +18747,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>490</v>
       </c>
@@ -18773,7 +18788,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1380</v>
       </c>
@@ -18814,7 +18829,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1386</v>
       </c>
@@ -18855,7 +18870,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1087</v>
       </c>
@@ -18896,7 +18911,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1396</v>
       </c>
@@ -18937,7 +18952,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1402</v>
       </c>
@@ -18978,7 +18993,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1407</v>
       </c>
@@ -19019,7 +19034,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>517</v>
       </c>
@@ -19060,7 +19075,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1415</v>
       </c>
@@ -19098,7 +19113,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>217</v>
       </c>
@@ -19139,7 +19154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1421</v>
       </c>
@@ -19180,7 +19195,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1425</v>
       </c>
@@ -19221,7 +19236,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1430</v>
       </c>
@@ -19262,7 +19277,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1202</v>
       </c>
@@ -19303,7 +19318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1437</v>
       </c>
@@ -19344,7 +19359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1443</v>
       </c>
@@ -19385,7 +19400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>449</v>
       </c>
@@ -19426,7 +19441,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1452</v>
       </c>
@@ -19464,7 +19479,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>299</v>
       </c>
@@ -19502,7 +19517,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>299</v>
       </c>
@@ -19543,7 +19558,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>201</v>
       </c>
@@ -19584,7 +19599,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>949</v>
       </c>
@@ -19625,7 +19640,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1468</v>
       </c>
@@ -19669,7 +19684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1473</v>
       </c>
@@ -19710,7 +19725,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1478</v>
       </c>
@@ -19748,7 +19763,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1482</v>
       </c>
@@ -19789,7 +19804,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>58</v>
       </c>
@@ -19830,7 +19845,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>1489</v>
       </c>
@@ -19871,7 +19886,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>1493</v>
       </c>
@@ -19915,7 +19930,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1498</v>
       </c>
@@ -19959,7 +19974,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>257</v>
       </c>
@@ -20000,7 +20015,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>873</v>
       </c>
@@ -20041,7 +20056,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1512</v>
       </c>
@@ -20082,7 +20097,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1516</v>
       </c>
@@ -20123,7 +20138,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1520</v>
       </c>
@@ -20161,7 +20176,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>318</v>
       </c>
@@ -20202,7 +20217,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>812</v>
       </c>
@@ -20243,7 +20258,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>257</v>
       </c>
@@ -20287,7 +20302,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>735</v>
       </c>
@@ -20331,7 +20346,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>976</v>
       </c>
@@ -20369,7 +20384,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>1541</v>
       </c>
@@ -20410,7 +20425,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>152</v>
       </c>
@@ -20451,7 +20466,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1548</v>
       </c>
@@ -20492,7 +20507,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1553</v>
       </c>
@@ -20533,7 +20548,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>454</v>
       </c>
@@ -20580,7 +20595,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1562</v>
       </c>
@@ -20621,7 +20636,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1567</v>
       </c>
@@ -20662,7 +20677,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>1571</v>
       </c>
@@ -20700,7 +20715,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>1574</v>
       </c>
@@ -20741,7 +20756,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>1147</v>
       </c>
@@ -20782,7 +20797,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>1581</v>
       </c>
@@ -20820,7 +20835,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>1584</v>
       </c>
@@ -20858,7 +20873,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>1587</v>
       </c>
@@ -20896,7 +20911,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>735</v>
       </c>
@@ -20934,7 +20949,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1593</v>
       </c>
@@ -20975,7 +20990,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1598</v>
       </c>
@@ -21016,7 +21031,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>201</v>
       </c>
@@ -21054,7 +21069,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>1606</v>
       </c>
@@ -21098,7 +21113,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>1147</v>
       </c>
@@ -21139,7 +21154,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>484</v>
       </c>
@@ -21177,7 +21192,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1615</v>
       </c>
@@ -21215,7 +21230,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>966</v>
       </c>
@@ -21253,7 +21268,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1622</v>
       </c>
@@ -21291,7 +21306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1625</v>
       </c>
@@ -21329,7 +21344,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>1629</v>
       </c>
@@ -21376,7 +21391,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>1634</v>
       </c>
@@ -21417,7 +21432,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>549</v>
       </c>
@@ -21458,7 +21473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1642</v>
       </c>
@@ -21499,7 +21514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1646</v>
       </c>
@@ -21540,7 +21555,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>212</v>
       </c>
@@ -21581,7 +21596,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>1654</v>
       </c>
@@ -21622,7 +21637,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>1003</v>
       </c>
@@ -21660,7 +21675,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>281</v>
       </c>
@@ -21698,7 +21713,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>517</v>
       </c>
@@ -21736,7 +21751,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>1665</v>
       </c>
@@ -21774,7 +21789,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1669</v>
       </c>
@@ -21812,7 +21827,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>449</v>
       </c>
@@ -21850,7 +21865,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>752</v>
       </c>
@@ -21888,7 +21903,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>312</v>
       </c>
@@ -21926,7 +21941,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>1683</v>
       </c>
@@ -21964,7 +21979,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>517</v>
       </c>
@@ -22002,7 +22017,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>299</v>
       </c>
@@ -22043,7 +22058,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>1692</v>
       </c>
@@ -22081,7 +22096,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>517</v>
       </c>
@@ -22119,7 +22134,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>1698</v>
       </c>
@@ -22157,7 +22172,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>598</v>
       </c>
@@ -22195,7 +22210,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>504</v>
       </c>
@@ -22233,7 +22248,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>94</v>
       </c>
@@ -22271,7 +22286,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>212</v>
       </c>
@@ -22309,7 +22324,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>631</v>
       </c>
@@ -22347,7 +22362,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1716</v>
       </c>
@@ -22385,7 +22400,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1029</v>
       </c>
@@ -22423,7 +22438,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>1724</v>
       </c>
@@ -22461,7 +22476,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>735</v>
       </c>
@@ -22499,7 +22514,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>357</v>
       </c>
@@ -22537,7 +22552,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>357</v>
       </c>
@@ -22575,7 +22590,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>1734</v>
       </c>
@@ -22613,7 +22628,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>735</v>
       </c>
@@ -22651,7 +22666,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1740</v>
       </c>
@@ -22689,7 +22704,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>1133</v>
       </c>
@@ -22727,7 +22742,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>504</v>
       </c>
@@ -22765,7 +22780,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1751</v>
       </c>
@@ -22803,7 +22818,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1756</v>
       </c>
@@ -22844,7 +22859,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>1760</v>
       </c>
@@ -22882,7 +22897,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>976</v>
       </c>
@@ -22920,7 +22935,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1765</v>
       </c>
@@ -22958,7 +22973,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" spans="1:18" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>1768</v>
       </c>
@@ -22996,7 +23011,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1771</v>
       </c>
@@ -23034,7 +23049,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1775</v>
       </c>
@@ -23072,7 +23087,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>1778</v>
       </c>
@@ -23110,7 +23125,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1781</v>
       </c>
@@ -23148,7 +23163,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>1162</v>
       </c>
@@ -23186,7 +23201,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>212</v>
       </c>
@@ -23227,7 +23242,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>195</v>
       </c>
@@ -23268,7 +23283,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>631</v>
       </c>
@@ -23306,7 +23321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1794</v>
       </c>
@@ -23344,7 +23359,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>1798</v>
       </c>
@@ -23382,7 +23397,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1801</v>
       </c>
@@ -23420,7 +23435,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1805</v>
       </c>
@@ -23458,7 +23473,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>275</v>
       </c>
@@ -23496,7 +23511,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>504</v>
       </c>
@@ -23534,7 +23549,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1812</v>
       </c>
@@ -23572,7 +23587,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1815</v>
       </c>
@@ -23610,7 +23625,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1818</v>
       </c>
@@ -23648,7 +23663,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>561</v>
       </c>
@@ -23686,7 +23701,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>257</v>
       </c>
@@ -23733,7 +23748,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>1827</v>
       </c>
@@ -23771,7 +23786,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1830</v>
       </c>
@@ -23809,7 +23824,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>94</v>
       </c>
@@ -23847,7 +23862,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>1516</v>
       </c>
@@ -23885,7 +23900,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>1837</v>
       </c>
@@ -23923,7 +23938,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>1840</v>
       </c>
@@ -23961,7 +23976,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>802</v>
       </c>
@@ -23999,7 +24014,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>115</v>
       </c>
@@ -24037,7 +24052,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>873</v>
       </c>
@@ -24081,7 +24096,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>212</v>
       </c>
@@ -24125,7 +24140,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1854</v>
       </c>
@@ -24166,7 +24181,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>1859</v>
       </c>
@@ -24204,7 +24219,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>1862</v>
       </c>
@@ -24242,7 +24257,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>1865</v>
       </c>
@@ -24286,7 +24301,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>943</v>
       </c>
@@ -24324,7 +24339,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>1872</v>
       </c>
@@ -24362,7 +24377,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>549</v>
       </c>
@@ -24400,7 +24415,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>821</v>
       </c>
@@ -24438,7 +24453,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>549</v>
       </c>
@@ -24476,7 +24491,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>919</v>
       </c>
@@ -24514,7 +24529,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>1885</v>
       </c>
@@ -24552,7 +24567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>405</v>
       </c>
@@ -24593,7 +24608,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>240</v>
       </c>
@@ -24631,7 +24646,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>1896</v>
       </c>
@@ -24669,7 +24684,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1248</v>
       </c>
@@ -24707,7 +24722,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>1903</v>
       </c>
@@ -24745,7 +24760,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>1202</v>
       </c>
@@ -24783,7 +24798,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1910</v>
       </c>
@@ -24821,7 +24836,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" spans="1:17" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>1913</v>
       </c>
@@ -24859,7 +24874,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>275</v>
       </c>
@@ -24897,7 +24912,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>1922</v>
       </c>
@@ -24935,7 +24950,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>1587</v>
       </c>
@@ -24973,7 +24988,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>299</v>
       </c>
@@ -25011,7 +25026,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>1929</v>
       </c>
@@ -25049,7 +25064,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1933</v>
       </c>
@@ -25087,7 +25102,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>459</v>
       </c>
@@ -25125,7 +25140,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1938</v>
       </c>
@@ -25169,7 +25184,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>1944</v>
       </c>
@@ -25207,7 +25222,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1947</v>
       </c>
@@ -25248,7 +25263,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>966</v>
       </c>
@@ -25289,7 +25304,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1029</v>
       </c>
@@ -25330,7 +25345,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>299</v>
       </c>
@@ -25368,7 +25383,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1960</v>
       </c>
@@ -25406,7 +25421,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>1964</v>
       </c>
@@ -25447,7 +25462,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>517</v>
       </c>
@@ -25485,7 +25500,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1971</v>
       </c>
@@ -25523,7 +25538,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1975</v>
       </c>
@@ -25564,7 +25579,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>1964</v>
       </c>
@@ -25608,7 +25623,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>933</v>
       </c>
@@ -25649,7 +25664,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1988</v>
       </c>
@@ -25690,7 +25705,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>1992</v>
       </c>
@@ -25731,7 +25746,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>594</v>
       </c>
@@ -25772,7 +25787,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>2000</v>
       </c>
@@ -25810,7 +25825,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>2003</v>
       </c>
@@ -25851,7 +25866,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>2006</v>
       </c>
@@ -25892,7 +25907,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>411</v>
       </c>
@@ -25933,7 +25948,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>1202</v>
       </c>
@@ -25977,7 +25992,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>2020</v>
       </c>
@@ -26018,7 +26033,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>1202</v>
       </c>
@@ -26056,7 +26071,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>943</v>
       </c>
@@ -26094,7 +26109,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>2027</v>
       </c>
@@ -26132,7 +26147,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>682</v>
       </c>
@@ -26170,7 +26185,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>2032</v>
       </c>
@@ -26208,7 +26223,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>434</v>
       </c>
@@ -26246,7 +26261,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>2038</v>
       </c>
@@ -26290,7 +26305,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1308</v>
       </c>
@@ -26328,7 +26343,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>2044</v>
       </c>
@@ -26366,7 +26381,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>2049</v>
       </c>
@@ -26404,7 +26419,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>170</v>
       </c>
@@ -26442,7 +26457,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>121</v>
       </c>
@@ -26483,7 +26498,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>757</v>
       </c>
@@ -26521,7 +26536,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>850</v>
       </c>
@@ -26562,7 +26577,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>234</v>
       </c>
@@ -26600,7 +26615,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>2065</v>
       </c>
@@ -26638,7 +26653,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>2068</v>
       </c>
@@ -26676,7 +26691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1964</v>
       </c>
@@ -26714,7 +26729,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" spans="1:19" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>2074</v>
       </c>
@@ -26761,7 +26776,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>58</v>
       </c>
@@ -26799,7 +26814,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>2081</v>
       </c>
@@ -26837,7 +26852,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>504</v>
       </c>
@@ -26875,7 +26890,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>86</v>
       </c>
@@ -26913,7 +26928,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>2090</v>
       </c>
@@ -26951,7 +26966,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>2095</v>
       </c>
@@ -26989,7 +27004,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>2098</v>
       </c>
@@ -27027,7 +27042,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>1520</v>
       </c>
@@ -27065,7 +27080,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>2103</v>
       </c>
@@ -27106,7 +27121,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1498</v>
       </c>
@@ -27147,7 +27162,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>2110</v>
       </c>
@@ -27188,7 +27203,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>1286</v>
       </c>
@@ -27229,7 +27244,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>2119</v>
       </c>
@@ -27270,7 +27285,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>2123</v>
       </c>
@@ -27311,7 +27326,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>2127</v>
       </c>
@@ -27349,7 +27364,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>2132</v>
       </c>
@@ -27387,7 +27402,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>1654</v>
       </c>
@@ -27425,7 +27440,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>164</v>
       </c>
@@ -27463,7 +27478,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>1003</v>
       </c>
@@ -27501,7 +27516,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>234</v>
       </c>
@@ -27542,7 +27557,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>2147</v>
       </c>
@@ -27583,7 +27598,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>299</v>
       </c>
@@ -27612,7 +27627,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" spans="1:16" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>2153</v>
       </c>
@@ -27642,17 +27657,22 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="J185" r:id="rId1" xr:uid="{9BDCFD3B-22EB-4FAB-B37B-7E3D61595CAE}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T503"/>
+    <ignoredError sqref="A1:T184 A186:T503 A185:I185 K185:T185" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:U584"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:L584"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -27690,7 +27710,7 @@
         <v>2165</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1938</v>
       </c>
@@ -27701,12 +27721,12 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2166</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>2167</v>
       </c>
@@ -27714,7 +27734,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -27725,7 +27745,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>29</v>
       </c>
@@ -27736,7 +27756,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -27747,7 +27767,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>2168</v>
       </c>
@@ -27758,7 +27778,7 @@
         <v>2170</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>50</v>
       </c>
@@ -27769,7 +27789,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>58</v>
       </c>
@@ -27780,7 +27800,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>66</v>
       </c>
@@ -27791,7 +27811,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>72</v>
       </c>
@@ -27802,7 +27822,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -27813,7 +27833,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>270</v>
       </c>
@@ -27821,7 +27841,7 @@
         <v>2171</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>86</v>
       </c>
@@ -27835,7 +27855,7 @@
         <v>2172</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>94</v>
       </c>
@@ -27843,7 +27863,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>99</v>
       </c>
@@ -27851,7 +27871,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>103</v>
       </c>
@@ -27862,7 +27882,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>109</v>
       </c>
@@ -27873,7 +27893,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>115</v>
       </c>
@@ -27884,7 +27904,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>2173</v>
       </c>
@@ -27895,7 +27915,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>2176</v>
       </c>
@@ -27903,7 +27923,7 @@
         <v>2177</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>2178</v>
       </c>
@@ -27914,7 +27934,7 @@
         <v>2180</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>121</v>
       </c>
@@ -27925,7 +27945,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>127</v>
       </c>
@@ -27933,7 +27953,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>132</v>
       </c>
@@ -27944,7 +27964,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>139</v>
       </c>
@@ -27955,7 +27975,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>145</v>
       </c>
@@ -27966,7 +27986,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>270</v>
       </c>
@@ -27974,7 +27994,7 @@
         <v>2181</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>152</v>
       </c>
@@ -27985,7 +28005,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>164</v>
       </c>
@@ -27996,7 +28016,7 @@
         <v>2183</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>158</v>
       </c>
@@ -28007,7 +28027,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>164</v>
       </c>
@@ -28018,7 +28038,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>170</v>
       </c>
@@ -28029,7 +28049,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>177</v>
       </c>
@@ -28040,7 +28060,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>2184</v>
       </c>
@@ -28051,7 +28071,7 @@
         <v>2186</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>184</v>
       </c>
@@ -28062,7 +28082,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>189</v>
       </c>
@@ -28073,7 +28093,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>195</v>
       </c>
@@ -28084,7 +28104,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>201</v>
       </c>
@@ -28095,7 +28115,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>2187</v>
       </c>
@@ -28103,7 +28123,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>207</v>
       </c>
@@ -28114,7 +28134,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>212</v>
       </c>
@@ -28125,7 +28145,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>217</v>
       </c>
@@ -28136,7 +28156,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>223</v>
       </c>
@@ -28147,7 +28167,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>228</v>
       </c>
@@ -28158,7 +28178,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>937</v>
       </c>
@@ -28166,7 +28186,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>234</v>
       </c>
@@ -28177,7 +28197,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>240</v>
       </c>
@@ -28188,7 +28208,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>246</v>
       </c>
@@ -28199,7 +28219,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>86</v>
       </c>
@@ -28210,7 +28230,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>257</v>
       </c>
@@ -28218,7 +28238,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>263</v>
       </c>
@@ -28229,7 +28249,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>270</v>
       </c>
@@ -28240,7 +28260,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>275</v>
       </c>
@@ -28251,7 +28271,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>2190</v>
       </c>
@@ -28262,7 +28282,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>281</v>
       </c>
@@ -28270,7 +28290,7 @@
         <v>282</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>287</v>
       </c>
@@ -28281,7 +28301,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>1003</v>
       </c>
@@ -28292,7 +28312,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>293</v>
       </c>
@@ -28303,7 +28323,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>299</v>
       </c>
@@ -28314,7 +28334,7 @@
         <v>2194</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>299</v>
       </c>
@@ -28325,7 +28345,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>305</v>
       </c>
@@ -28336,7 +28356,7 @@
         <v>2195</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>949</v>
       </c>
@@ -28347,7 +28367,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>312</v>
       </c>
@@ -28358,7 +28378,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>318</v>
       </c>
@@ -28369,7 +28389,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>324</v>
       </c>
@@ -28380,7 +28400,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>332</v>
       </c>
@@ -28391,7 +28411,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>338</v>
       </c>
@@ -28402,7 +28422,7 @@
         <v>342</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>344</v>
       </c>
@@ -28416,7 +28436,7 @@
         <v>2196</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>2197</v>
       </c>
@@ -28427,7 +28447,7 @@
         <v>2199</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>351</v>
       </c>
@@ -28438,7 +28458,7 @@
         <v>355</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>357</v>
       </c>
@@ -28449,7 +28469,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>357</v>
       </c>
@@ -28457,7 +28477,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>368</v>
       </c>
@@ -28468,7 +28488,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>374</v>
       </c>
@@ -28479,7 +28499,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>378</v>
       </c>
@@ -28490,7 +28510,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>383</v>
       </c>
@@ -28501,7 +28521,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>2200</v>
       </c>
@@ -28509,7 +28529,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>388</v>
       </c>
@@ -28520,7 +28540,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>393</v>
       </c>
@@ -28531,7 +28551,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>405</v>
       </c>
@@ -28542,7 +28562,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>94</v>
       </c>
@@ -28553,7 +28573,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>324</v>
       </c>
@@ -28564,7 +28584,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>788</v>
       </c>
@@ -28572,7 +28592,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>411</v>
       </c>
@@ -28583,7 +28603,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>344</v>
       </c>
@@ -28591,7 +28611,7 @@
         <v>2202</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>417</v>
       </c>
@@ -28602,7 +28622,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>299</v>
       </c>
@@ -28613,7 +28633,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>2203</v>
       </c>
@@ -28621,7 +28641,7 @@
         <v>2204</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>428</v>
       </c>
@@ -28632,7 +28652,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>434</v>
       </c>
@@ -28643,7 +28663,7 @@
         <v>438</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>34</v>
       </c>
@@ -28654,7 +28674,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>635</v>
       </c>
@@ -28665,7 +28685,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>2038</v>
       </c>
@@ -28676,7 +28696,7 @@
         <v>2207</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>454</v>
       </c>
@@ -28687,7 +28707,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>2208</v>
       </c>
@@ -28698,7 +28718,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>460</v>
       </c>
@@ -28709,7 +28729,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>466</v>
       </c>
@@ -28720,7 +28740,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>471</v>
       </c>
@@ -28731,7 +28751,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>478</v>
       </c>
@@ -28742,7 +28762,7 @@
         <v>482</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>484</v>
       </c>
@@ -28753,7 +28773,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>2211</v>
       </c>
@@ -28764,7 +28784,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>2214</v>
       </c>
@@ -28772,7 +28792,7 @@
         <v>2215</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>2216</v>
       </c>
@@ -28780,7 +28800,7 @@
         <v>2217</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>228</v>
       </c>
@@ -28791,7 +28811,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>305</v>
       </c>
@@ -28802,7 +28822,7 @@
         <v>502</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>504</v>
       </c>
@@ -28813,7 +28833,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>508</v>
       </c>
@@ -28821,7 +28841,7 @@
         <v>509</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>512</v>
       </c>
@@ -28832,7 +28852,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>517</v>
       </c>
@@ -28843,7 +28863,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>521</v>
       </c>
@@ -28854,7 +28874,7 @@
         <v>526</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>533</v>
       </c>
@@ -28865,7 +28885,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>528</v>
       </c>
@@ -28876,7 +28896,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>539</v>
       </c>
@@ -28887,7 +28907,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>873</v>
       </c>
@@ -28898,7 +28918,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>545</v>
       </c>
@@ -28909,7 +28929,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>549</v>
       </c>
@@ -28920,7 +28940,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>792</v>
       </c>
@@ -28931,7 +28951,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>555</v>
       </c>
@@ -28942,7 +28962,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>561</v>
       </c>
@@ -28953,7 +28973,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>571</v>
       </c>
@@ -28961,7 +28981,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>576</v>
       </c>
@@ -28972,7 +28992,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B124" t="s">
         <v>2218</v>
       </c>
@@ -28980,7 +29000,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>873</v>
       </c>
@@ -28991,7 +29011,7 @@
         <v>2221</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>2222</v>
       </c>
@@ -28999,7 +29019,7 @@
         <v>2220</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>584</v>
       </c>
@@ -29007,7 +29027,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>34</v>
       </c>
@@ -29018,7 +29038,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>594</v>
       </c>
@@ -29026,7 +29046,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>598</v>
       </c>
@@ -29037,7 +29057,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>517</v>
       </c>
@@ -29048,7 +29068,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>94</v>
       </c>
@@ -29059,7 +29079,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>344</v>
       </c>
@@ -29070,7 +29090,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>164</v>
       </c>
@@ -29084,7 +29104,7 @@
         <v>2223</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>344</v>
       </c>
@@ -29092,7 +29112,7 @@
         <v>2224</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>132</v>
       </c>
@@ -29103,7 +29123,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>625</v>
       </c>
@@ -29114,7 +29134,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>635</v>
       </c>
@@ -29125,7 +29145,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>631</v>
       </c>
@@ -29133,7 +29153,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>638</v>
       </c>
@@ -29144,7 +29164,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>644</v>
       </c>
@@ -29155,7 +29175,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>504</v>
       </c>
@@ -29163,7 +29183,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>504</v>
       </c>
@@ -29174,7 +29194,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>902</v>
       </c>
@@ -29182,7 +29202,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>735</v>
       </c>
@@ -29190,7 +29210,7 @@
         <v>879</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>484</v>
       </c>
@@ -29201,7 +29221,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>344</v>
       </c>
@@ -29209,7 +29229,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>631</v>
       </c>
@@ -29220,7 +29240,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>667</v>
       </c>
@@ -29231,7 +29251,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>667</v>
       </c>
@@ -29242,7 +29262,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>411</v>
       </c>
@@ -29253,7 +29273,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>682</v>
       </c>
@@ -29264,7 +29284,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>682</v>
       </c>
@@ -29275,7 +29295,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>696</v>
       </c>
@@ -29283,7 +29303,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>700</v>
       </c>
@@ -29294,7 +29314,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>275</v>
       </c>
@@ -29302,7 +29322,7 @@
         <v>2225</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>752</v>
       </c>
@@ -29313,7 +29333,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>757</v>
       </c>
@@ -29324,7 +29344,7 @@
         <v>760</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>767</v>
       </c>
@@ -29335,7 +29355,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>773</v>
       </c>
@@ -29346,7 +29366,7 @@
         <v>777</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>779</v>
       </c>
@@ -29357,7 +29377,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>783</v>
       </c>
@@ -29368,7 +29388,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>868</v>
       </c>
@@ -29379,7 +29399,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>892</v>
       </c>
@@ -29390,7 +29410,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>490</v>
       </c>
@@ -29401,7 +29421,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>1960</v>
       </c>
@@ -29409,7 +29429,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>927</v>
       </c>
@@ -29420,7 +29440,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>933</v>
       </c>
@@ -29431,7 +29451,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>2000</v>
       </c>
@@ -29439,7 +29459,7 @@
         <v>2001</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>2003</v>
       </c>
@@ -29450,7 +29470,7 @@
         <v>2005</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>937</v>
       </c>
@@ -29461,7 +29481,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>943</v>
       </c>
@@ -29472,7 +29492,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>635</v>
       </c>
@@ -29483,7 +29503,7 @@
         <v>2228</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>2006</v>
       </c>
@@ -29494,7 +29514,7 @@
         <v>2008</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>986</v>
       </c>
@@ -29505,7 +29525,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>484</v>
       </c>
@@ -29516,7 +29536,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>773</v>
       </c>
@@ -29527,7 +29547,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>998</v>
       </c>
@@ -29535,7 +29555,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>549</v>
       </c>
@@ -29546,7 +29566,7 @@
         <v>2232</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>2233</v>
       </c>
@@ -29554,7 +29574,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>1003</v>
       </c>
@@ -29565,7 +29585,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>1008</v>
       </c>
@@ -29576,7 +29596,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>270</v>
       </c>
@@ -29587,7 +29607,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>94</v>
       </c>
@@ -29598,7 +29618,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>79</v>
       </c>
@@ -29609,7 +29629,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>411</v>
       </c>
@@ -29620,7 +29640,7 @@
         <v>2013</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>164</v>
       </c>
@@ -29631,7 +29651,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>1029</v>
       </c>
@@ -29642,7 +29662,7 @@
         <v>1033</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>2235</v>
       </c>
@@ -29650,7 +29670,7 @@
         <v>2236</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>1202</v>
       </c>
@@ -29661,7 +29681,7 @@
         <v>2018</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>1035</v>
       </c>
@@ -29672,7 +29692,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>263</v>
       </c>
@@ -29683,7 +29703,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>1040</v>
       </c>
@@ -29694,7 +29714,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>1045</v>
       </c>
@@ -29705,7 +29725,7 @@
         <v>1048</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>466</v>
       </c>
@@ -29716,7 +29736,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>1053</v>
       </c>
@@ -29724,7 +29744,7 @@
         <v>2237</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>1053</v>
       </c>
@@ -29732,7 +29752,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>270</v>
       </c>
@@ -29743,7 +29763,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>2238</v>
       </c>
@@ -29751,7 +29771,7 @@
         <v>2239</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>1061</v>
       </c>
@@ -29762,7 +29782,7 @@
         <v>1063</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>845</v>
       </c>
@@ -29773,7 +29793,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>2240</v>
       </c>
@@ -29781,7 +29801,7 @@
         <v>2241</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>717</v>
       </c>
@@ -29792,7 +29812,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>1069</v>
       </c>
@@ -29800,7 +29820,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>1074</v>
       </c>
@@ -29808,7 +29828,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>1078</v>
       </c>
@@ -29816,7 +29836,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>873</v>
       </c>
@@ -29824,7 +29844,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>132</v>
       </c>
@@ -29832,7 +29852,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>1087</v>
       </c>
@@ -29840,7 +29860,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>966</v>
       </c>
@@ -29848,7 +29868,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>1095</v>
       </c>
@@ -29856,7 +29876,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>757</v>
       </c>
@@ -29864,7 +29884,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>722</v>
       </c>
@@ -29872,7 +29892,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>1104</v>
       </c>
@@ -29880,7 +29900,7 @@
         <v>1105</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>344</v>
       </c>
@@ -29888,7 +29908,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>1112</v>
       </c>
@@ -29896,7 +29916,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="217">
+    <row r="217" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>902</v>
       </c>
@@ -29904,7 +29924,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>2243</v>
       </c>
@@ -29912,7 +29932,7 @@
         <v>2244</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>1118</v>
       </c>
@@ -29920,7 +29940,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>2245</v>
       </c>
@@ -29928,7 +29948,7 @@
         <v>2246</v>
       </c>
     </row>
-    <row r="221">
+    <row r="221" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>1123</v>
       </c>
@@ -29936,7 +29956,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="222">
+    <row r="222" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>1129</v>
       </c>
@@ -29944,7 +29964,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="223">
+    <row r="223" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>1133</v>
       </c>
@@ -29952,7 +29972,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="224">
+    <row r="224" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>1364</v>
       </c>
@@ -29960,7 +29980,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="225">
+    <row r="225" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>164</v>
       </c>
@@ -29968,7 +29988,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="226">
+    <row r="226" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>2248</v>
       </c>
@@ -29976,7 +29996,7 @@
         <v>2249</v>
       </c>
     </row>
-    <row r="227">
+    <row r="227" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>549</v>
       </c>
@@ -29984,7 +30004,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="228">
+    <row r="228" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>667</v>
       </c>
@@ -29992,7 +30012,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="229">
+    <row r="229" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>1147</v>
       </c>
@@ -30000,7 +30020,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="230">
+    <row r="230" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>757</v>
       </c>
@@ -30008,7 +30028,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="231">
+    <row r="231" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>1154</v>
       </c>
@@ -30016,7 +30036,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="232">
+    <row r="232" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>1158</v>
       </c>
@@ -30024,7 +30044,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="233">
+    <row r="233" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>1162</v>
       </c>
@@ -30032,7 +30052,7 @@
         <v>1163</v>
       </c>
     </row>
-    <row r="234">
+    <row r="234" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>561</v>
       </c>
@@ -30040,7 +30060,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="235">
+    <row r="235" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>1169</v>
       </c>
@@ -30048,7 +30068,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="236">
+    <row r="236" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>201</v>
       </c>
@@ -30056,7 +30076,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="237">
+    <row r="237" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>234</v>
       </c>
@@ -30064,7 +30084,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="238">
+    <row r="238" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>132</v>
       </c>
@@ -30072,7 +30092,7 @@
         <v>2252</v>
       </c>
     </row>
-    <row r="239">
+    <row r="239" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>405</v>
       </c>
@@ -30080,7 +30100,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="240">
+    <row r="240" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>2253</v>
       </c>
@@ -30088,7 +30108,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="241">
+    <row r="241" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>919</v>
       </c>
@@ -30096,7 +30116,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="242">
+    <row r="242" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>584</v>
       </c>
@@ -30104,7 +30124,7 @@
         <v>2255</v>
       </c>
     </row>
-    <row r="243">
+    <row r="243" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>960</v>
       </c>
@@ -30112,7 +30132,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="244">
+    <row r="244" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>94</v>
       </c>
@@ -30120,7 +30140,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="245">
+    <row r="245" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>1192</v>
       </c>
@@ -30128,7 +30148,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="246">
+    <row r="246" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>2256</v>
       </c>
@@ -30136,7 +30156,7 @@
         <v>2257</v>
       </c>
     </row>
-    <row r="247">
+    <row r="247" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>2020</v>
       </c>
@@ -30144,7 +30164,7 @@
         <v>2021</v>
       </c>
     </row>
-    <row r="248">
+    <row r="248" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>1196</v>
       </c>
@@ -30152,7 +30172,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="249">
+    <row r="249" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>2258</v>
       </c>
@@ -30160,7 +30180,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="250">
+    <row r="250" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>1202</v>
       </c>
@@ -30168,7 +30188,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="251">
+    <row r="251" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>344</v>
       </c>
@@ -30176,7 +30196,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="252">
+    <row r="252" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>802</v>
       </c>
@@ -30184,7 +30204,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="253">
+    <row r="253" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>1202</v>
       </c>
@@ -30192,7 +30212,7 @@
         <v>2023</v>
       </c>
     </row>
-    <row r="254">
+    <row r="254" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>1212</v>
       </c>
@@ -30200,7 +30220,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="255">
+    <row r="255" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1217</v>
       </c>
@@ -30211,7 +30231,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="256">
+    <row r="256" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>517</v>
       </c>
@@ -30222,7 +30242,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="257">
+    <row r="257" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1226</v>
       </c>
@@ -30230,7 +30250,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="258">
+    <row r="258" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1232</v>
       </c>
@@ -30238,7 +30258,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="259">
+    <row r="259" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>735</v>
       </c>
@@ -30246,7 +30266,7 @@
         <v>1236</v>
       </c>
     </row>
-    <row r="260">
+    <row r="260" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>234</v>
       </c>
@@ -30254,7 +30274,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="261">
+    <row r="261" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1245</v>
       </c>
@@ -30262,7 +30282,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="262">
+    <row r="262" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>1248</v>
       </c>
@@ -30270,7 +30290,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="263">
+    <row r="263" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>735</v>
       </c>
@@ -30278,7 +30298,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="264">
+    <row r="264" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>943</v>
       </c>
@@ -30286,7 +30306,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="265">
+    <row r="265" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>478</v>
       </c>
@@ -30294,7 +30314,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="266">
+    <row r="266" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>2090</v>
       </c>
@@ -30302,7 +30322,7 @@
         <v>2091</v>
       </c>
     </row>
-    <row r="267">
+    <row r="267" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1259</v>
       </c>
@@ -30310,7 +30330,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="268">
+    <row r="268" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1264</v>
       </c>
@@ -30318,7 +30338,7 @@
         <v>1265</v>
       </c>
     </row>
-    <row r="269">
+    <row r="269" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>324</v>
       </c>
@@ -30326,7 +30346,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="270">
+    <row r="270" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>152</v>
       </c>
@@ -30334,7 +30354,7 @@
         <v>1274</v>
       </c>
     </row>
-    <row r="271">
+    <row r="271" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1278</v>
       </c>
@@ -30342,7 +30362,7 @@
         <v>1279</v>
       </c>
     </row>
-    <row r="272">
+    <row r="272" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>2027</v>
       </c>
@@ -30350,7 +30370,7 @@
         <v>2028</v>
       </c>
     </row>
-    <row r="273">
+    <row r="273" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>34</v>
       </c>
@@ -30358,7 +30378,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="274">
+    <row r="274" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>1282</v>
       </c>
@@ -30366,7 +30386,7 @@
         <v>1283</v>
       </c>
     </row>
-    <row r="275">
+    <row r="275" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1286</v>
       </c>
@@ -30374,7 +30394,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="276">
+    <row r="276" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>1290</v>
       </c>
@@ -30382,7 +30402,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="277">
+    <row r="277" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1294</v>
       </c>
@@ -30390,7 +30410,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="278">
+    <row r="278" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1286</v>
       </c>
@@ -30398,7 +30418,7 @@
         <v>2260</v>
       </c>
     </row>
-    <row r="279">
+    <row r="279" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>966</v>
       </c>
@@ -30406,7 +30426,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="280">
+    <row r="280" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>2095</v>
       </c>
@@ -30414,7 +30434,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="281">
+    <row r="281" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>1298</v>
       </c>
@@ -30422,7 +30442,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="282">
+    <row r="282" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1303</v>
       </c>
@@ -30430,7 +30450,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="283">
+    <row r="283" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1308</v>
       </c>
@@ -30438,7 +30458,7 @@
         <v>1309</v>
       </c>
     </row>
-    <row r="284">
+    <row r="284" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B284" t="s">
         <v>1312</v>
       </c>
@@ -30446,7 +30466,7 @@
         <v>1314</v>
       </c>
     </row>
-    <row r="285">
+    <row r="285" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>812</v>
       </c>
@@ -30454,7 +30474,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="286">
+    <row r="286" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>594</v>
       </c>
@@ -30462,7 +30482,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="287">
+    <row r="287" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>1319</v>
       </c>
@@ -30470,7 +30490,7 @@
         <v>1320</v>
       </c>
     </row>
-    <row r="288">
+    <row r="288" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1323</v>
       </c>
@@ -30478,7 +30498,7 @@
         <v>1324</v>
       </c>
     </row>
-    <row r="289">
+    <row r="289" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>127</v>
       </c>
@@ -30486,7 +30506,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="290">
+    <row r="290" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1327</v>
       </c>
@@ -30494,7 +30514,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="291">
+    <row r="291" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1332</v>
       </c>
@@ -30502,7 +30522,7 @@
         <v>1333</v>
       </c>
     </row>
-    <row r="292">
+    <row r="292" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>549</v>
       </c>
@@ -30510,7 +30530,7 @@
         <v>1337</v>
       </c>
     </row>
-    <row r="293">
+    <row r="293" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>1341</v>
       </c>
@@ -30521,7 +30541,7 @@
         <v>2261</v>
       </c>
     </row>
-    <row r="294">
+    <row r="294" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>43</v>
       </c>
@@ -30529,7 +30549,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="295">
+    <row r="295" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1345</v>
       </c>
@@ -30537,7 +30557,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="296">
+    <row r="296" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>2262</v>
       </c>
@@ -30545,7 +30565,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="297">
+    <row r="297" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>2264</v>
       </c>
@@ -30553,7 +30573,7 @@
         <v>2265</v>
       </c>
     </row>
-    <row r="298">
+    <row r="298" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1349</v>
       </c>
@@ -30561,7 +30581,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="299">
+    <row r="299" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>1353</v>
       </c>
@@ -30569,7 +30589,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="300">
+    <row r="300" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>2266</v>
       </c>
@@ -30577,7 +30597,7 @@
         <v>2267</v>
       </c>
     </row>
-    <row r="301">
+    <row r="301" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>2268</v>
       </c>
@@ -30585,7 +30605,7 @@
         <v>2269</v>
       </c>
     </row>
-    <row r="302">
+    <row r="302" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>631</v>
       </c>
@@ -30593,7 +30613,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="303">
+    <row r="303" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1364</v>
       </c>
@@ -30601,7 +30621,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="304">
+    <row r="304" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>631</v>
       </c>
@@ -30609,7 +30629,7 @@
         <v>829</v>
       </c>
     </row>
-    <row r="305">
+    <row r="305" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>735</v>
       </c>
@@ -30617,7 +30637,7 @@
         <v>1368</v>
       </c>
     </row>
-    <row r="306">
+    <row r="306" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>164</v>
       </c>
@@ -30625,7 +30645,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="307">
+    <row r="307" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1396</v>
       </c>
@@ -30633,7 +30653,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="308">
+    <row r="308" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1402</v>
       </c>
@@ -30641,7 +30661,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="309">
+    <row r="309" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1407</v>
       </c>
@@ -30649,7 +30669,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="310">
+    <row r="310" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1087</v>
       </c>
@@ -30657,7 +30677,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="311">
+    <row r="311" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>517</v>
       </c>
@@ -30665,7 +30685,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="312">
+    <row r="312" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1415</v>
       </c>
@@ -30673,7 +30693,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="313">
+    <row r="313" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>217</v>
       </c>
@@ -30681,7 +30701,7 @@
         <v>1416</v>
       </c>
     </row>
-    <row r="314">
+    <row r="314" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1421</v>
       </c>
@@ -30689,7 +30709,7 @@
         <v>1422</v>
       </c>
     </row>
-    <row r="315">
+    <row r="315" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1425</v>
       </c>
@@ -30697,7 +30717,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="316">
+    <row r="316" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>682</v>
       </c>
@@ -30705,7 +30725,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="317">
+    <row r="317" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1430</v>
       </c>
@@ -30713,7 +30733,7 @@
         <v>1431</v>
       </c>
     </row>
-    <row r="318">
+    <row r="318" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>344</v>
       </c>
@@ -30721,7 +30741,7 @@
         <v>2270</v>
       </c>
     </row>
-    <row r="319">
+    <row r="319" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1202</v>
       </c>
@@ -30729,7 +30749,7 @@
         <v>1433</v>
       </c>
     </row>
-    <row r="320">
+    <row r="320" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>1437</v>
       </c>
@@ -30737,7 +30757,7 @@
         <v>1438</v>
       </c>
     </row>
-    <row r="321">
+    <row r="321" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>1443</v>
       </c>
@@ -30745,7 +30765,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="322">
+    <row r="322" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>449</v>
       </c>
@@ -30753,7 +30773,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="323">
+    <row r="323" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>1452</v>
       </c>
@@ -30761,7 +30781,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="324">
+    <row r="324" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>299</v>
       </c>
@@ -30769,7 +30789,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="325">
+    <row r="325" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>299</v>
       </c>
@@ -30777,7 +30797,7 @@
         <v>1458</v>
       </c>
     </row>
-    <row r="326">
+    <row r="326" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>2032</v>
       </c>
@@ -30785,7 +30805,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="327">
+    <row r="327" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>2271</v>
       </c>
@@ -30793,7 +30813,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="328">
+    <row r="328" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>299</v>
       </c>
@@ -30801,7 +30821,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="329">
+    <row r="329" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>490</v>
       </c>
@@ -30809,7 +30829,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="330">
+    <row r="330" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>201</v>
       </c>
@@ -30817,7 +30837,7 @@
         <v>1462</v>
       </c>
     </row>
-    <row r="331">
+    <row r="331" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>949</v>
       </c>
@@ -30825,7 +30845,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="332">
+    <row r="332" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>1473</v>
       </c>
@@ -30833,7 +30853,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="333">
+    <row r="333" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>1478</v>
       </c>
@@ -30841,7 +30861,7 @@
         <v>1479</v>
       </c>
     </row>
-    <row r="334">
+    <row r="334" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>1482</v>
       </c>
@@ -30849,7 +30869,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="335">
+    <row r="335" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>58</v>
       </c>
@@ -30857,7 +30877,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="336">
+    <row r="336" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>727</v>
       </c>
@@ -30865,7 +30885,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="337">
+    <row r="337" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1489</v>
       </c>
@@ -30873,7 +30893,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="338">
+    <row r="338" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>201</v>
       </c>
@@ -30881,12 +30901,12 @@
         <v>2273</v>
       </c>
     </row>
-    <row r="339">
+    <row r="339" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B339" t="s">
         <v>2274</v>
       </c>
     </row>
-    <row r="340">
+    <row r="340" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>1493</v>
       </c>
@@ -30894,7 +30914,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="341">
+    <row r="341" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1498</v>
       </c>
@@ -30902,7 +30922,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="342">
+    <row r="342" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>257</v>
       </c>
@@ -30913,7 +30933,7 @@
         <v>1505</v>
       </c>
     </row>
-    <row r="343">
+    <row r="343" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>873</v>
       </c>
@@ -30921,7 +30941,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="344">
+    <row r="344" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>1512</v>
       </c>
@@ -30932,7 +30952,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="345">
+    <row r="345" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1516</v>
       </c>
@@ -30940,7 +30960,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="346">
+    <row r="346" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>1520</v>
       </c>
@@ -30948,7 +30968,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="347">
+    <row r="347" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>318</v>
       </c>
@@ -30956,7 +30976,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="348">
+    <row r="348" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>812</v>
       </c>
@@ -30964,7 +30984,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="349">
+    <row r="349" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>2275</v>
       </c>
@@ -30972,7 +30992,7 @@
         <v>2276</v>
       </c>
     </row>
-    <row r="350">
+    <row r="350" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>257</v>
       </c>
@@ -30980,7 +31000,7 @@
         <v>1531</v>
       </c>
     </row>
-    <row r="351">
+    <row r="351" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>2277</v>
       </c>
@@ -30988,7 +31008,7 @@
         <v>1535</v>
       </c>
     </row>
-    <row r="352">
+    <row r="352" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>976</v>
       </c>
@@ -30996,7 +31016,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="353">
+    <row r="353" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>1541</v>
       </c>
@@ -31004,7 +31024,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="354">
+    <row r="354" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>152</v>
       </c>
@@ -31012,7 +31032,7 @@
         <v>1545</v>
       </c>
     </row>
-    <row r="355">
+    <row r="355" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>2278</v>
       </c>
@@ -31020,7 +31040,7 @@
         <v>2279</v>
       </c>
     </row>
-    <row r="356">
+    <row r="356" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>833</v>
       </c>
@@ -31028,7 +31048,7 @@
         <v>834</v>
       </c>
     </row>
-    <row r="357">
+    <row r="357" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>2280</v>
       </c>
@@ -31036,7 +31056,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="358">
+    <row r="358" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1548</v>
       </c>
@@ -31044,7 +31064,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="359">
+    <row r="359" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>1553</v>
       </c>
@@ -31052,7 +31072,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="360">
+    <row r="360" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>454</v>
       </c>
@@ -31060,7 +31080,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="361">
+    <row r="361" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>1562</v>
       </c>
@@ -31068,7 +31088,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="362">
+    <row r="362" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>731</v>
       </c>
@@ -31076,7 +31096,7 @@
         <v>732</v>
       </c>
     </row>
-    <row r="363">
+    <row r="363" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1567</v>
       </c>
@@ -31084,7 +31104,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="364">
+    <row r="364" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>1571</v>
       </c>
@@ -31092,7 +31112,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="365">
+    <row r="365" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>1574</v>
       </c>
@@ -31100,7 +31120,7 @@
         <v>1575</v>
       </c>
     </row>
-    <row r="366">
+    <row r="366" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>1147</v>
       </c>
@@ -31108,7 +31128,7 @@
         <v>1578</v>
       </c>
     </row>
-    <row r="367">
+    <row r="367" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>1581</v>
       </c>
@@ -31116,7 +31136,7 @@
         <v>1582</v>
       </c>
     </row>
-    <row r="368">
+    <row r="368" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>2282</v>
       </c>
@@ -31124,7 +31144,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="369">
+    <row r="369" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>1584</v>
       </c>
@@ -31132,7 +31152,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="370">
+    <row r="370" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>735</v>
       </c>
@@ -31140,7 +31160,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="371">
+    <row r="371" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>960</v>
       </c>
@@ -31148,7 +31168,7 @@
         <v>2283</v>
       </c>
     </row>
-    <row r="372">
+    <row r="372" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1593</v>
       </c>
@@ -31156,7 +31176,7 @@
         <v>1594</v>
       </c>
     </row>
-    <row r="373">
+    <row r="373" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>1598</v>
       </c>
@@ -31164,7 +31184,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="374">
+    <row r="374" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>201</v>
       </c>
@@ -31172,7 +31192,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="375">
+    <row r="375" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>1606</v>
       </c>
@@ -31180,7 +31200,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="376">
+    <row r="376" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>1147</v>
       </c>
@@ -31188,7 +31208,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="377">
+    <row r="377" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>837</v>
       </c>
@@ -31196,7 +31216,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="378">
+    <row r="378" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>484</v>
       </c>
@@ -31204,7 +31224,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="379">
+    <row r="379" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>2284</v>
       </c>
@@ -31212,7 +31232,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="380">
+    <row r="380" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>1615</v>
       </c>
@@ -31220,7 +31240,7 @@
         <v>1616</v>
       </c>
     </row>
-    <row r="381">
+    <row r="381" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>966</v>
       </c>
@@ -31228,7 +31248,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="382">
+    <row r="382" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>1622</v>
       </c>
@@ -31236,7 +31256,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="383">
+    <row r="383" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>1625</v>
       </c>
@@ -31244,7 +31264,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="384">
+    <row r="384" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>2285</v>
       </c>
@@ -31252,7 +31272,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="385">
+    <row r="385" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>1629</v>
       </c>
@@ -31263,7 +31283,7 @@
         <v>2287</v>
       </c>
     </row>
-    <row r="386">
+    <row r="386" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1634</v>
       </c>
@@ -31271,7 +31291,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="387">
+    <row r="387" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>2288</v>
       </c>
@@ -31279,7 +31299,7 @@
         <v>2289</v>
       </c>
     </row>
-    <row r="388">
+    <row r="388" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>1380</v>
       </c>
@@ -31287,7 +31307,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="389">
+    <row r="389" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>549</v>
       </c>
@@ -31295,7 +31315,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="390">
+    <row r="390" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1642</v>
       </c>
@@ -31303,7 +31323,7 @@
         <v>1643</v>
       </c>
     </row>
-    <row r="391">
+    <row r="391" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>1646</v>
       </c>
@@ -31311,7 +31331,7 @@
         <v>1647</v>
       </c>
     </row>
-    <row r="392">
+    <row r="392" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>212</v>
       </c>
@@ -31319,7 +31339,7 @@
         <v>1651</v>
       </c>
     </row>
-    <row r="393">
+    <row r="393" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>1654</v>
       </c>
@@ -31327,7 +31347,7 @@
         <v>1655</v>
       </c>
     </row>
-    <row r="394">
+    <row r="394" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>970</v>
       </c>
@@ -31335,7 +31355,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="395">
+    <row r="395" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>1003</v>
       </c>
@@ -31343,7 +31363,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="396">
+    <row r="396" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>281</v>
       </c>
@@ -31351,7 +31371,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="397">
+    <row r="397" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>434</v>
       </c>
@@ -31359,7 +31379,7 @@
         <v>2036</v>
       </c>
     </row>
-    <row r="398">
+    <row r="398" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>517</v>
       </c>
@@ -31367,7 +31387,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="399">
+    <row r="399" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>1665</v>
       </c>
@@ -31375,7 +31395,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="400">
+    <row r="400" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>1669</v>
       </c>
@@ -31383,7 +31403,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="401">
+    <row r="401" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>1087</v>
       </c>
@@ -31391,7 +31411,7 @@
         <v>2290</v>
       </c>
     </row>
-    <row r="402">
+    <row r="402" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>449</v>
       </c>
@@ -31399,7 +31419,7 @@
         <v>1674</v>
       </c>
     </row>
-    <row r="403">
+    <row r="403" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>752</v>
       </c>
@@ -31407,7 +31427,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="404">
+    <row r="404" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>312</v>
       </c>
@@ -31415,7 +31435,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="405">
+    <row r="405" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>1683</v>
       </c>
@@ -31423,7 +31443,7 @@
         <v>1684</v>
       </c>
     </row>
-    <row r="406">
+    <row r="406" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>344</v>
       </c>
@@ -31431,7 +31451,7 @@
         <v>2291</v>
       </c>
     </row>
-    <row r="407">
+    <row r="407" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>2292</v>
       </c>
@@ -31439,7 +31459,7 @@
         <v>2293</v>
       </c>
     </row>
-    <row r="408">
+    <row r="408" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>517</v>
       </c>
@@ -31447,7 +31467,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="409">
+    <row r="409" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>299</v>
       </c>
@@ -31455,7 +31475,7 @@
         <v>1688</v>
       </c>
     </row>
-    <row r="410">
+    <row r="410" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>1692</v>
       </c>
@@ -31463,7 +31483,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="411">
+    <row r="411" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>976</v>
       </c>
@@ -31471,7 +31491,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="412">
+    <row r="412" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>201</v>
       </c>
@@ -31479,7 +31499,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="413">
+    <row r="413" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>517</v>
       </c>
@@ -31487,7 +31507,7 @@
         <v>1695</v>
       </c>
     </row>
-    <row r="414">
+    <row r="414" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>1698</v>
       </c>
@@ -31495,7 +31515,7 @@
         <v>1699</v>
       </c>
     </row>
-    <row r="415">
+    <row r="415" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>883</v>
       </c>
@@ -31503,7 +31523,7 @@
         <v>884</v>
       </c>
     </row>
-    <row r="416">
+    <row r="416" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>873</v>
       </c>
@@ -31511,7 +31531,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="417">
+    <row r="417" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>270</v>
       </c>
@@ -31519,7 +31539,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="418">
+    <row r="418" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>2295</v>
       </c>
@@ -31527,7 +31547,7 @@
         <v>2294</v>
       </c>
     </row>
-    <row r="419">
+    <row r="419" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>598</v>
       </c>
@@ -31535,7 +31555,7 @@
         <v>1702</v>
       </c>
     </row>
-    <row r="420">
+    <row r="420" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>504</v>
       </c>
@@ -31543,7 +31563,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="421">
+    <row r="421" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>94</v>
       </c>
@@ -31551,7 +31571,7 @@
         <v>1707</v>
       </c>
     </row>
-    <row r="422">
+    <row r="422" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>212</v>
       </c>
@@ -31559,7 +31579,7 @@
         <v>1711</v>
       </c>
     </row>
-    <row r="423">
+    <row r="423" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>966</v>
       </c>
@@ -31567,7 +31587,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="424">
+    <row r="424" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>909</v>
       </c>
@@ -31575,7 +31595,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="425">
+    <row r="425" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>631</v>
       </c>
@@ -31583,7 +31603,7 @@
         <v>1713</v>
       </c>
     </row>
-    <row r="426">
+    <row r="426" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>1716</v>
       </c>
@@ -31591,7 +31611,7 @@
         <v>1717</v>
       </c>
     </row>
-    <row r="427">
+    <row r="427" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>344</v>
       </c>
@@ -31599,7 +31619,7 @@
         <v>2296</v>
       </c>
     </row>
-    <row r="428">
+    <row r="428" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>1029</v>
       </c>
@@ -31607,7 +31627,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="429">
+    <row r="429" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>2297</v>
       </c>
@@ -31615,7 +31635,7 @@
         <v>2298</v>
       </c>
     </row>
-    <row r="430">
+    <row r="430" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>195</v>
       </c>
@@ -31623,7 +31643,7 @@
         <v>2299</v>
       </c>
     </row>
-    <row r="431">
+    <row r="431" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>1724</v>
       </c>
@@ -31631,7 +31651,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="432">
+    <row r="432" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>735</v>
       </c>
@@ -31639,7 +31659,7 @@
         <v>1727</v>
       </c>
     </row>
-    <row r="433">
+    <row r="433" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>344</v>
       </c>
@@ -31647,7 +31667,7 @@
         <v>2300</v>
       </c>
     </row>
-    <row r="434">
+    <row r="434" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>357</v>
       </c>
@@ -31655,7 +31675,7 @@
         <v>1730</v>
       </c>
     </row>
-    <row r="435">
+    <row r="435" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>357</v>
       </c>
@@ -31663,7 +31683,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="436">
+    <row r="436" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>1734</v>
       </c>
@@ -31671,7 +31691,7 @@
         <v>1735</v>
       </c>
     </row>
-    <row r="437">
+    <row r="437" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>735</v>
       </c>
@@ -31679,7 +31699,7 @@
         <v>1738</v>
       </c>
     </row>
-    <row r="438">
+    <row r="438" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>1740</v>
       </c>
@@ -31687,7 +31707,7 @@
         <v>1741</v>
       </c>
     </row>
-    <row r="439">
+    <row r="439" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>212</v>
       </c>
@@ -31695,7 +31715,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="440">
+    <row r="440" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>1133</v>
       </c>
@@ -31703,7 +31723,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="441">
+    <row r="441" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>504</v>
       </c>
@@ -31711,7 +31731,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="442">
+    <row r="442" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>1751</v>
       </c>
@@ -31719,7 +31739,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="443">
+    <row r="443" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>1756</v>
       </c>
@@ -31727,7 +31747,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="444">
+    <row r="444" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>1760</v>
       </c>
@@ -31735,7 +31755,7 @@
         <v>1761</v>
       </c>
     </row>
-    <row r="445">
+    <row r="445" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>164</v>
       </c>
@@ -31743,7 +31763,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="446">
+    <row r="446" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>1407</v>
       </c>
@@ -31751,7 +31771,7 @@
         <v>2302</v>
       </c>
     </row>
-    <row r="447">
+    <row r="447" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>976</v>
       </c>
@@ -31759,7 +31779,7 @@
         <v>1763</v>
       </c>
     </row>
-    <row r="448">
+    <row r="448" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>1765</v>
       </c>
@@ -31767,7 +31787,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="449">
+    <row r="449" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>1768</v>
       </c>
@@ -31775,7 +31795,7 @@
         <v>1769</v>
       </c>
     </row>
-    <row r="450">
+    <row r="450" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>1771</v>
       </c>
@@ -31783,7 +31803,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="451">
+    <row r="451" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>837</v>
       </c>
@@ -31791,7 +31811,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="452">
+    <row r="452" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>1775</v>
       </c>
@@ -31799,7 +31819,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="453">
+    <row r="453" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>1778</v>
       </c>
@@ -31807,7 +31827,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="454">
+    <row r="454" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>2184</v>
       </c>
@@ -31815,7 +31835,7 @@
         <v>2303</v>
       </c>
     </row>
-    <row r="455">
+    <row r="455" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>1781</v>
       </c>
@@ -31823,7 +31843,7 @@
         <v>1782</v>
       </c>
     </row>
-    <row r="456">
+    <row r="456" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>2038</v>
       </c>
@@ -31831,7 +31851,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="457">
+    <row r="457" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>873</v>
       </c>
@@ -31839,7 +31859,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="458">
+    <row r="458" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>919</v>
       </c>
@@ -31847,7 +31867,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="459">
+    <row r="459" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>1162</v>
       </c>
@@ -31855,7 +31875,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="460">
+    <row r="460" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>845</v>
       </c>
@@ -31863,7 +31883,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="461">
+    <row r="461" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>212</v>
       </c>
@@ -31871,7 +31891,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="462">
+    <row r="462" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>195</v>
       </c>
@@ -31879,7 +31899,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="463">
+    <row r="463" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>631</v>
       </c>
@@ -31887,7 +31907,7 @@
         <v>1792</v>
       </c>
     </row>
-    <row r="464">
+    <row r="464" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>2304</v>
       </c>
@@ -31895,7 +31915,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="465">
+    <row r="465" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>1794</v>
       </c>
@@ -31903,7 +31923,7 @@
         <v>1795</v>
       </c>
     </row>
-    <row r="466">
+    <row r="466" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>1798</v>
       </c>
@@ -31911,7 +31931,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="467">
+    <row r="467" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>1801</v>
       </c>
@@ -31919,7 +31939,7 @@
         <v>1802</v>
       </c>
     </row>
-    <row r="468">
+    <row r="468" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>1805</v>
       </c>
@@ -31927,7 +31947,7 @@
         <v>1806</v>
       </c>
     </row>
-    <row r="469">
+    <row r="469" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>1053</v>
       </c>
@@ -31935,7 +31955,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="470">
+    <row r="470" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>504</v>
       </c>
@@ -31943,7 +31963,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="471">
+    <row r="471" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>275</v>
       </c>
@@ -31951,7 +31971,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="472">
+    <row r="472" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>1812</v>
       </c>
@@ -31959,7 +31979,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="473">
+    <row r="473" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>1818</v>
       </c>
@@ -31967,7 +31987,7 @@
         <v>1819</v>
       </c>
     </row>
-    <row r="474">
+    <row r="474" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>257</v>
       </c>
@@ -31975,7 +31995,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="475">
+    <row r="475" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>561</v>
       </c>
@@ -31983,7 +32003,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="476">
+    <row r="476" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>1827</v>
       </c>
@@ -31991,7 +32011,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="477">
+    <row r="477" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>1830</v>
       </c>
@@ -31999,7 +32019,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="478">
+    <row r="478" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>94</v>
       </c>
@@ -32007,7 +32027,7 @@
         <v>1833</v>
       </c>
     </row>
-    <row r="479">
+    <row r="479" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>1308</v>
       </c>
@@ -32015,7 +32035,7 @@
         <v>2042</v>
       </c>
     </row>
-    <row r="480">
+    <row r="480" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>1516</v>
       </c>
@@ -32023,7 +32043,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="481">
+    <row r="481" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>2044</v>
       </c>
@@ -32031,7 +32051,7 @@
         <v>2045</v>
       </c>
     </row>
-    <row r="482">
+    <row r="482" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>1837</v>
       </c>
@@ -32039,7 +32059,7 @@
         <v>1838</v>
       </c>
     </row>
-    <row r="483">
+    <row r="483" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>2049</v>
       </c>
@@ -32047,7 +32067,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="484">
+    <row r="484" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>1840</v>
       </c>
@@ -32055,7 +32075,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="485">
+    <row r="485" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>802</v>
       </c>
@@ -32063,7 +32083,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="486">
+    <row r="486" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>735</v>
       </c>
@@ -32071,7 +32091,7 @@
         <v>736</v>
       </c>
     </row>
-    <row r="487">
+    <row r="487" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>115</v>
       </c>
@@ -32079,7 +32099,7 @@
         <v>1846</v>
       </c>
     </row>
-    <row r="488">
+    <row r="488" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>873</v>
       </c>
@@ -32087,7 +32107,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="489">
+    <row r="489" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>212</v>
       </c>
@@ -32095,7 +32115,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="490">
+    <row r="490" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>1854</v>
       </c>
@@ -32103,7 +32123,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="491">
+    <row r="491" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>1859</v>
       </c>
@@ -32111,7 +32131,7 @@
         <v>1860</v>
       </c>
     </row>
-    <row r="492">
+    <row r="492" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>873</v>
       </c>
@@ -32119,7 +32139,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="493">
+    <row r="493" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>1862</v>
       </c>
@@ -32127,7 +32147,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="494">
+    <row r="494" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>1865</v>
       </c>
@@ -32138,7 +32158,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="495">
+    <row r="495" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>1872</v>
       </c>
@@ -32146,7 +32166,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="496">
+    <row r="496" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>1290</v>
       </c>
@@ -32154,7 +32174,7 @@
         <v>2308</v>
       </c>
     </row>
-    <row r="497">
+    <row r="497" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>549</v>
       </c>
@@ -32162,7 +32182,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="498">
+    <row r="498" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>739</v>
       </c>
@@ -32170,7 +32190,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="499">
+    <row r="499" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>821</v>
       </c>
@@ -32178,7 +32198,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="500">
+    <row r="500" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>2309</v>
       </c>
@@ -32186,7 +32206,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="501">
+    <row r="501" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>549</v>
       </c>
@@ -32194,7 +32214,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="502">
+    <row r="502" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>919</v>
       </c>
@@ -32202,7 +32222,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="503">
+    <row r="503" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>850</v>
       </c>
@@ -32210,7 +32230,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="504">
+    <row r="504" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>1885</v>
       </c>
@@ -32218,7 +32238,7 @@
         <v>1886</v>
       </c>
     </row>
-    <row r="505">
+    <row r="505" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>405</v>
       </c>
@@ -32226,7 +32246,7 @@
         <v>1890</v>
       </c>
     </row>
-    <row r="506">
+    <row r="506" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>240</v>
       </c>
@@ -32234,7 +32254,7 @@
         <v>1893</v>
       </c>
     </row>
-    <row r="507">
+    <row r="507" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>1896</v>
       </c>
@@ -32242,7 +32262,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="508">
+    <row r="508" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>2311</v>
       </c>
@@ -32250,7 +32270,7 @@
         <v>2312</v>
       </c>
     </row>
-    <row r="509">
+    <row r="509" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>1248</v>
       </c>
@@ -32258,7 +32278,7 @@
         <v>1899</v>
       </c>
     </row>
-    <row r="510">
+    <row r="510" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>1903</v>
       </c>
@@ -32266,7 +32286,7 @@
         <v>1904</v>
       </c>
     </row>
-    <row r="511">
+    <row r="511" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>631</v>
       </c>
@@ -32274,7 +32294,7 @@
         <v>2313</v>
       </c>
     </row>
-    <row r="512">
+    <row r="512" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>1202</v>
       </c>
@@ -32282,7 +32302,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="513">
+    <row r="513" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>405</v>
       </c>
@@ -32290,7 +32310,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="514">
+    <row r="514" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>1910</v>
       </c>
@@ -32298,7 +32318,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="515">
+    <row r="515" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>1913</v>
       </c>
@@ -32306,7 +32326,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="516">
+    <row r="516" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>517</v>
       </c>
@@ -32314,7 +32334,7 @@
         <v>2315</v>
       </c>
     </row>
-    <row r="517">
+    <row r="517" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A517" t="s">
         <v>275</v>
       </c>
@@ -32322,7 +32342,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="518">
+    <row r="518" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A518" t="s">
         <v>1922</v>
       </c>
@@ -32330,7 +32350,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="519">
+    <row r="519" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A519" t="s">
         <v>1587</v>
       </c>
@@ -32338,7 +32358,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="520">
+    <row r="520" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A520" t="s">
         <v>1386</v>
       </c>
@@ -32346,7 +32366,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="521">
+    <row r="521" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A521" t="s">
         <v>299</v>
       </c>
@@ -32354,7 +32374,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="522">
+    <row r="522" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A522" t="s">
         <v>1929</v>
       </c>
@@ -32362,7 +32382,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="523">
+    <row r="523" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A523" t="s">
         <v>1933</v>
       </c>
@@ -32370,7 +32390,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="524">
+    <row r="524" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A524" t="s">
         <v>459</v>
       </c>
@@ -32378,7 +32398,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="525">
+    <row r="525" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A525" t="s">
         <v>594</v>
       </c>
@@ -32386,7 +32406,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="526">
+    <row r="526" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A526" t="s">
         <v>1944</v>
       </c>
@@ -32394,7 +32414,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="527">
+    <row r="527" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A527" t="s">
         <v>1947</v>
       </c>
@@ -32402,7 +32422,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="528">
+    <row r="528" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A528" t="s">
         <v>966</v>
       </c>
@@ -32410,7 +32430,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="529">
+    <row r="529" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A529" t="s">
         <v>1029</v>
       </c>
@@ -32418,7 +32438,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="530">
+    <row r="530" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A530" t="s">
         <v>299</v>
       </c>
@@ -32426,7 +32446,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="531">
+    <row r="531" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A531" t="s">
         <v>257</v>
       </c>
@@ -32434,7 +32454,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="532">
+    <row r="532" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A532" t="s">
         <v>821</v>
       </c>
@@ -32442,7 +32462,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="533">
+    <row r="533" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A533" t="s">
         <v>825</v>
       </c>
@@ -32450,7 +32470,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="534">
+    <row r="534" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A534" t="s">
         <v>1960</v>
       </c>
@@ -32458,7 +32478,7 @@
         <v>1961</v>
       </c>
     </row>
-    <row r="535">
+    <row r="535" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A535" t="s">
         <v>549</v>
       </c>
@@ -32466,7 +32486,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="536">
+    <row r="536" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A536" t="s">
         <v>517</v>
       </c>
@@ -32474,7 +32494,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="537">
+    <row r="537" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A537" t="s">
         <v>1971</v>
       </c>
@@ -32482,7 +32502,7 @@
         <v>1972</v>
       </c>
     </row>
-    <row r="538">
+    <row r="538" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A538" t="s">
         <v>1975</v>
       </c>
@@ -32490,7 +32510,7 @@
         <v>1976</v>
       </c>
     </row>
-    <row r="539">
+    <row r="539" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A539" t="s">
         <v>1964</v>
       </c>
@@ -32498,7 +32518,7 @@
         <v>1980</v>
       </c>
     </row>
-    <row r="540">
+    <row r="540" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A540" t="s">
         <v>933</v>
       </c>
@@ -32506,7 +32526,7 @@
         <v>1985</v>
       </c>
     </row>
-    <row r="541">
+    <row r="541" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A541" t="s">
         <v>1988</v>
       </c>
@@ -32517,7 +32537,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="542">
+    <row r="542" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A542" t="s">
         <v>449</v>
       </c>
@@ -32528,7 +32548,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="543">
+    <row r="543" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A543" t="s">
         <v>1992</v>
       </c>
@@ -32536,7 +32556,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="544">
+    <row r="544" spans="1:3" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A544" t="s">
         <v>170</v>
       </c>
@@ -32544,7 +32564,7 @@
         <v>2052</v>
       </c>
     </row>
-    <row r="545">
+    <row r="545" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A545" t="s">
         <v>121</v>
       </c>
@@ -32552,7 +32572,7 @@
         <v>2054</v>
       </c>
     </row>
-    <row r="546">
+    <row r="546" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A546" t="s">
         <v>757</v>
       </c>
@@ -32560,7 +32580,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="547">
+    <row r="547" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A547" t="s">
         <v>850</v>
       </c>
@@ -32568,7 +32588,7 @@
         <v>2060</v>
       </c>
     </row>
-    <row r="548">
+    <row r="548" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A548" t="s">
         <v>594</v>
       </c>
@@ -32576,7 +32596,7 @@
         <v>1996</v>
       </c>
     </row>
-    <row r="549">
+    <row r="549" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A549" t="s">
         <v>234</v>
       </c>
@@ -32584,7 +32604,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="550">
+    <row r="550" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A550" t="s">
         <v>1964</v>
       </c>
@@ -32592,7 +32612,7 @@
         <v>2062</v>
       </c>
     </row>
-    <row r="551">
+    <row r="551" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A551" t="s">
         <v>428</v>
       </c>
@@ -32600,7 +32620,7 @@
         <v>2317</v>
       </c>
     </row>
-    <row r="552">
+    <row r="552" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A552" t="s">
         <v>2318</v>
       </c>
@@ -32608,7 +32628,7 @@
         <v>2319</v>
       </c>
     </row>
-    <row r="553">
+    <row r="553" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A553" t="s">
         <v>2065</v>
       </c>
@@ -32616,7 +32636,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="554">
+    <row r="554" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A554" t="s">
         <v>2068</v>
       </c>
@@ -32624,7 +32644,7 @@
         <v>2069</v>
       </c>
     </row>
-    <row r="555">
+    <row r="555" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A555" t="s">
         <v>1964</v>
       </c>
@@ -32632,7 +32652,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="556">
+    <row r="556" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A556" t="s">
         <v>873</v>
       </c>
@@ -32640,7 +32660,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="557">
+    <row r="557" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A557" t="s">
         <v>2074</v>
       </c>
@@ -32651,7 +32671,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="558">
+    <row r="558" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A558" t="s">
         <v>2321</v>
       </c>
@@ -32659,7 +32679,7 @@
         <v>2322</v>
       </c>
     </row>
-    <row r="559">
+    <row r="559" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A559" t="s">
         <v>856</v>
       </c>
@@ -32667,7 +32687,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="560">
+    <row r="560" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A560" t="s">
         <v>58</v>
       </c>
@@ -32675,7 +32695,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="561">
+    <row r="561" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A561" t="s">
         <v>2081</v>
       </c>
@@ -32683,7 +32703,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="562">
+    <row r="562" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A562" t="s">
         <v>504</v>
       </c>
@@ -32691,7 +32711,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="563">
+    <row r="563" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A563" t="s">
         <v>86</v>
       </c>
@@ -32699,7 +32719,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="564">
+    <row r="564" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A564" t="s">
         <v>744</v>
       </c>
@@ -32707,7 +32727,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="565">
+    <row r="565" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A565" t="s">
         <v>1520</v>
       </c>
@@ -32715,7 +32735,7 @@
         <v>2101</v>
       </c>
     </row>
-    <row r="566">
+    <row r="566" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A566" t="s">
         <v>434</v>
       </c>
@@ -32723,7 +32743,7 @@
         <v>861</v>
       </c>
     </row>
-    <row r="567">
+    <row r="567" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A567" t="s">
         <v>2103</v>
       </c>
@@ -32731,7 +32751,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="568">
+    <row r="568" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A568" t="s">
         <v>1498</v>
       </c>
@@ -32739,7 +32759,7 @@
         <v>2107</v>
       </c>
     </row>
-    <row r="569">
+    <row r="569" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A569" t="s">
         <v>2110</v>
       </c>
@@ -32747,7 +32767,7 @@
         <v>2111</v>
       </c>
     </row>
-    <row r="570">
+    <row r="570" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A570" t="s">
         <v>1286</v>
       </c>
@@ -32755,7 +32775,7 @@
         <v>2115</v>
       </c>
     </row>
-    <row r="571">
+    <row r="571" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A571" t="s">
         <v>2098</v>
       </c>
@@ -32763,7 +32783,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="572">
+    <row r="572" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A572" t="s">
         <v>2119</v>
       </c>
@@ -32771,7 +32791,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="573">
+    <row r="573" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A573" t="s">
         <v>2123</v>
       </c>
@@ -32779,7 +32799,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="574">
+    <row r="574" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A574" t="s">
         <v>2127</v>
       </c>
@@ -32787,7 +32807,7 @@
         <v>2128</v>
       </c>
     </row>
-    <row r="575">
+    <row r="575" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A575" t="s">
         <v>2323</v>
       </c>
@@ -32795,7 +32815,7 @@
         <v>2324</v>
       </c>
     </row>
-    <row r="576">
+    <row r="576" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A576" t="s">
         <v>2132</v>
       </c>
@@ -32803,7 +32823,7 @@
         <v>2133</v>
       </c>
     </row>
-    <row r="577">
+    <row r="577" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A577" t="s">
         <v>2325</v>
       </c>
@@ -32811,7 +32831,7 @@
         <v>2326</v>
       </c>
     </row>
-    <row r="578">
+    <row r="578" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A578" t="s">
         <v>1654</v>
       </c>
@@ -32819,7 +32839,7 @@
         <v>2136</v>
       </c>
     </row>
-    <row r="579">
+    <row r="579" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A579" t="s">
         <v>1003</v>
       </c>
@@ -32827,7 +32847,7 @@
         <v>2140</v>
       </c>
     </row>
-    <row r="580">
+    <row r="580" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A580" t="s">
         <v>2327</v>
       </c>
@@ -32835,7 +32855,7 @@
         <v>2328</v>
       </c>
     </row>
-    <row r="581">
+    <row r="581" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A581" t="s">
         <v>2147</v>
       </c>
@@ -32846,7 +32866,7 @@
         <v>2150</v>
       </c>
     </row>
-    <row r="582">
+    <row r="582" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A582" t="s">
         <v>802</v>
       </c>
@@ -32854,7 +32874,7 @@
         <v>865</v>
       </c>
     </row>
-    <row r="583">
+    <row r="583" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A583" t="s">
         <v>2329</v>
       </c>
@@ -32862,7 +32882,7 @@
         <v>2330</v>
       </c>
     </row>
-    <row r="584">
+    <row r="584" spans="1:4" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A584" t="s">
         <v>490</v>
       </c>
@@ -32876,7 +32896,7 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:U584"/>
+    <ignoredError sqref="A1:U584" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>